--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCRO</t>
+          <t>AMOC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.49</v>
+        <v>8.91</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0294</v>
+        <v>0.176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.015</v>
+        <v>0.0992</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.7062</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>39446506</v>
+        <v>7877205</v>
       </c>
       <c r="I2" t="n">
-        <v>74498234</v>
+        <v>44465398</v>
       </c>
       <c r="J2" t="n">
-        <v>1.889</v>
+        <v>5.645</v>
       </c>
       <c r="K2" t="n">
-        <v>29063477</v>
+        <v>3221256</v>
       </c>
       <c r="L2" t="n">
-        <v>37249117</v>
+        <v>32668440</v>
       </c>
       <c r="M2" t="n">
-        <v>1.282</v>
+        <v>10.142</v>
       </c>
       <c r="N2" t="n">
-        <v>1.32</v>
+        <v>8.24</v>
       </c>
       <c r="O2" t="n">
-        <v>1.57</v>
+        <v>9.15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.2914</v>
+        <v>8.142200000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.1768</v>
+        <v>7.6183</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>1.3229</v>
+        <v>8.148</v>
       </c>
       <c r="U2" t="n">
-        <v>1.149</v>
+        <v>7.8589</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -710,21 +710,21 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>67.7</v>
+        <v>70.42</v>
       </c>
       <c r="X2" t="n">
-        <v>1.4204</v>
+        <v>8.3286</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-31 23:43:15</t>
+          <t>2026-08-01 10:32:27</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>1.4204</v>
+        <v>8.3286</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.32</v>
+        <v>8.24</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -732,52 +732,52 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>1.5067</v>
+        <v>9.09</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.5748</v>
+        <v>10.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.6338</v>
+        <v>10.9978</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 1.51; TP2: Bollinger Upper Band at 1.57; TP3: Extension at 1.63</t>
+          <t>TP1: Classic R2 at 9.09; TP2: Classic R3 at 10.26; TP3: Extension at 11.0</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0.86</v>
+        <v>8.59</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.54</v>
+        <v>21.79</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.13</v>
+        <v>30.12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6.08</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AK2" t="n">
-        <v>10.87</v>
+        <v>23.19</v>
       </c>
       <c r="AL2" t="n">
-        <v>15.03</v>
+        <v>32.05</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 67.7))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (70.4); entry: enhanced entry at VWMA (overbought (RSI: 70.4))</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GGCC</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -786,51 +786,51 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>56.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0164</v>
+        <v>1.1079</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0066</v>
+        <v>0.1368</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0617</v>
+        <v>1.1667</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19600606</v>
+        <v>714703</v>
       </c>
       <c r="I3" t="n">
-        <v>28606169</v>
+        <v>578784</v>
       </c>
       <c r="J3" t="n">
-        <v>1.459</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>22304846</v>
+        <v>216885</v>
       </c>
       <c r="L3" t="n">
-        <v>16253501</v>
+        <v>270098</v>
       </c>
       <c r="M3" t="n">
-        <v>0.729</v>
+        <v>1.245</v>
       </c>
       <c r="N3" t="n">
-        <v>0.595</v>
+        <v>54.31</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9399999999999999</v>
+        <v>56.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5344</v>
+        <v>56.1242</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4219</v>
+        <v>51.1871</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>0.5926</v>
+        <v>55.5855</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4452</v>
+        <v>49.7698</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -854,189 +854,7079 @@
         </is>
       </c>
       <c r="W3" t="n">
-        <v>71.81999999999999</v>
+        <v>50.33</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7138</v>
+        <v>56.3002</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-31 23:43:16</t>
+          <t>2026-08-01 10:32:29</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.7138</v>
+        <v>55.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.595</v>
+        <v>55.2826</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>1.0109</v>
+        <v>57.6009</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1595</v>
+        <v>58.9186</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.081</v>
+        <v>59.26</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1.01; TP2: Extension at 1.16; TP3: Extension at 1.08</t>
+          <t>TP1: Bollinger Upper Band at 57.6; TP2: Fibonacci R1 at 58.92; TP3: Classic R1 at 59.26</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>2.5</v>
+        <v>3.96</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.75</v>
+        <v>6.78</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.09</v>
+        <v>7.51</v>
       </c>
       <c r="AJ3" t="n">
-        <v>41.63</v>
+        <v>3.32</v>
       </c>
       <c r="AK3" t="n">
-        <v>62.45</v>
+        <v>5.68</v>
       </c>
       <c r="AL3" t="n">
-        <v>51.45</v>
+        <v>6.3</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, RSI overbought (71.8); entry: enhanced entry at VWMA (overbought (RSI: 71.8))</t>
+          <t>Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.3))</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>EFID</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>27.24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.6373</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1535296</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1474237</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1063344</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1349299</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="N4" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="O4" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="P4" t="n">
+        <v>28.0156</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>26.8432</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>27.9294</v>
+      </c>
+      <c r="U4" t="n">
+        <v>25.9092</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>27.7959</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:30</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>26.9043</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>26.8432</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>stop at 200 SMA</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>27.9887</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>28.8767</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>28.8898</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>TP1: 100 SMA at 27.99; TP2: Bollinger Upper Band at 28.88; TP3: Fibonacci R1 at 28.89</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EFIH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2204</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3187957</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2344381</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1152876</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1483784</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="N5" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21.8262</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>19.2476</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>21.8449</v>
+      </c>
+      <c r="U5" t="n">
+        <v>19.4131</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="X5" t="n">
+        <v>22.7323</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:31</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>22.7414</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>23.8033</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>23.807</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R2 at 22.74; TP2: Classic R2 at 23.8; TP3: Bollinger Upper Band at 23.81</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>13.87</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.2))</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EGAL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>296.19</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5.8491</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.1963</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.3929</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>306304</v>
+      </c>
+      <c r="I6" t="n">
+        <v>88537</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="K6" t="n">
+        <v>54499</v>
+      </c>
+      <c r="L6" t="n">
+        <v>26250</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="N6" t="n">
+        <v>294.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>302.7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>305.7806</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>256.9986</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>299.3498</v>
+      </c>
+      <c r="U6" t="n">
+        <v>261.8413</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="X6" t="n">
+        <v>299.6988</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:32</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>287.64</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>274.1058</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>298.7249</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>308.234</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>321.9475</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>TP1: 100 SMA at 298.72; TP2: Bollinger Upper Band at 308.23; TP3: Fibonacci R1 at 321.95</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.5))</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ISPH</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2245</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5963583</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3182475</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3319555</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1172488</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.7704</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.2998</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>11.5956</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11.0178</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>42.19</v>
+      </c>
+      <c r="X7" t="n">
+        <v>11.5447</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:33</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>11.2998</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>stop at 200 SMA</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.7464</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12.4583</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 11.75; TP2: Fibonacci R1 at 12.46; TP3: Classic R1 at 12.54</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>2972.22</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>7712.19</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>8256.17</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 42.2))</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>JUFO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>28.67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.2592</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1257994</v>
+      </c>
+      <c r="I8" t="n">
+        <v>718576</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="K8" t="n">
+        <v>514514</v>
+      </c>
+      <c r="L8" t="n">
+        <v>390085</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="P8" t="n">
+        <v>29.6804</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>26.9828</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>29.418</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.3193</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="X8" t="n">
+        <v>29.5599</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:34</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>28.4284</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>28.0358</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>31.5052</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>31.6449</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>31.9833</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 31.51; TP2: Fibonacci R1 at 31.64; TP3: Classic R1 at 31.98</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 39.7))</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MCQE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>182.43</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.6026</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1847</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4.2525</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>190685</v>
+      </c>
+      <c r="I9" t="n">
+        <v>86436</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="K9" t="n">
+        <v>35126</v>
+      </c>
+      <c r="L9" t="n">
+        <v>66942</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.906</v>
+      </c>
+      <c r="N9" t="n">
+        <v>175</v>
+      </c>
+      <c r="O9" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>182.9374</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>160.317</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>182.1341</v>
+      </c>
+      <c r="U9" t="n">
+        <v>156.8251</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="X9" t="n">
+        <v>182.6138</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:35</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>180.83</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>175</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>184.6849</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>191.54</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>191.8359</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>TP1: 100 SMA at 184.68; TP2: Classic R1 at 191.54; TP3: Fibonacci R1 at 191.84</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.6))</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORAS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.4031</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.0005</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>193879</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>724.5394</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>541.5338</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>696.5584</v>
+      </c>
+      <c r="U10" t="n">
+        <v>563.7071</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="X10" t="n">
+        <v>702.4604</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:36</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>67.4975</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>541.5338</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>629.5273999999999</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>731.4788</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>TP1: 200 SMA at 541.53; TP2: 100 SMA at 629.53; TP3: Bollinger Upper Band at 731.48</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>132.44</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>157.21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>185.91</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>662.1900000000001</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>786.03</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>929.53</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: no pullback level identified; current price as reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORWE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9237</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1198269</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1055301</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="K11" t="n">
+        <v>608115</v>
+      </c>
+      <c r="L11" t="n">
+        <v>125634</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>22.9378</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22.9377</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>22.9162</v>
+      </c>
+      <c r="U11" t="n">
+        <v>22.9066</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>22.9516</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:37</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>22.3727</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>21.9856</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>22.8104</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>22.9377</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>23.3803</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>TP1: 100 SMA at 22.81; TP2: 200 SMA at 22.94; TP3: Bollinger Upper Band at 23.38</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.4))</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PHDC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>17325026</v>
+      </c>
+      <c r="I12" t="n">
+        <v>11673760</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7241829</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7782507</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="O12" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="P12" t="n">
+        <v>14.8526</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10.3365</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>14.2671</v>
+      </c>
+      <c r="U12" t="n">
+        <v>11.175</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="X12" t="n">
+        <v>14.8298</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:38</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>14.2677</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>15.1485</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>15.9256</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>16.4377</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 15.15; TP2: Fibonacci R1 at 15.93; TP3: Fibonacci R2 at 16.44</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 44.7))</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ETEL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.0459</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.1239</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1021769</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1511598</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.479</v>
+      </c>
+      <c r="K13" t="n">
+        <v>352101</v>
+      </c>
+      <c r="L13" t="n">
+        <v>296050</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="N13" t="n">
+        <v>93.01000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>112.98</v>
+      </c>
+      <c r="P13" t="n">
+        <v>96.42440000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>79.50109999999999</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>96.9744</v>
+      </c>
+      <c r="U13" t="n">
+        <v>81.1778</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="X13" t="n">
+        <v>100.8252</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:40</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>100.8252</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>99.0941</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>107.2343</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>115.1632</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 107.23; TP2: Classic R3 at 111.2; TP3: Extension at 115.16</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RMDA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1043</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1565</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>12075718</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8245937</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5009453</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7853283</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.0642</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.0365</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>4.9738</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.2529</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5.1267</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:41</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.1267</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.2833</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5.3989</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>5.6167</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>TP1: Classic R1 at 5.28; TP2: Fibonacci R2 at 5.4; TP3: Classic R2 at 5.62</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 64.3))</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AMER</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.08890000000000001</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>24343135</v>
+      </c>
+      <c r="I15" t="n">
+        <v>14864993</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="K15" t="n">
+        <v>15475726</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2702724</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.0124</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.1883</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1702</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.3112</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.5103</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:43</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.336</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.1555</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>5.5653</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>5.3489</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 5.16; TP2: Extension at 5.57; TP3: Extension at 5.35</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>28.35</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, RSI overbought (75.9); entry: enhanced entry at Parabolic SAR (overbought (RSI: 75.9))</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ARAB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>268716267</v>
+      </c>
+      <c r="I16" t="n">
+        <v>285915220</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="K16" t="n">
+        <v>153946169</v>
+      </c>
+      <c r="L16" t="n">
+        <v>95305232</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.2195</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1792</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>0.2228</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:44</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.2335</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 0.26; TP2: Extension at 0.27; TP3: Extension at 0.27</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.7))</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>COSG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>32349173</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20767425</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="K17" t="n">
+        <v>11262912</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2966775</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.6014</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.4678</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>1.5952</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.5047</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.6559</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:45</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.6798</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.7435</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 1.68; TP2: Fibonacci R2 at 1.74; TP3: Bollinger Upper Band at 1.75</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 45.3))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>POUL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.7451</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1342299</v>
+      </c>
+      <c r="I18" t="n">
+        <v>444890</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="K18" t="n">
+        <v>421515</v>
+      </c>
+      <c r="L18" t="n">
+        <v>364810</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="N18" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="O18" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="P18" t="n">
+        <v>37.738</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>30.7229</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>37.4861</v>
+      </c>
+      <c r="U18" t="n">
+        <v>31.3569</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>39.1299</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:46</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>35.4175</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AC18" t="n">
+        <v>40.0092</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>40.4019</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>40.4367</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 40.01; TP2: Bollinger Upper Band at 40.4; TP3: Classic R1 at 40.44</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 45.3))</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PRCL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.6813</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.09229999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1230298</v>
+      </c>
+      <c r="I19" t="n">
+        <v>431378</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="K19" t="n">
+        <v>708724</v>
+      </c>
+      <c r="L19" t="n">
+        <v>46219</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="N19" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="O19" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="P19" t="n">
+        <v>29.4694</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>19.2682</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>30.3545</v>
+      </c>
+      <c r="U19" t="n">
+        <v>21.1737</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>54.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>35.6583</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:47</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>33.5793</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>33.0916</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>34.8467</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>34.8853</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>37.9264</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>TP1: Classic R1 at 34.85; TP2: Fibonacci R2 at 34.89; TP3: Bollinger Upper Band at 37.93</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: enhanced entry at Parabolic SAR (overbought (RSI: 54.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ETRS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>4425370</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3092784</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3053793</v>
+      </c>
+      <c r="L20" t="n">
+        <v>3092784</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="O20" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="P20" t="n">
+        <v>9.8576</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.8918</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>9.979900000000001</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8.1972</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="X20" t="n">
+        <v>10.8525</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:48</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>10.5646</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>8.6655</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AC20" t="n">
+        <v>11.0774</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11.6145</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 11.08; TP2: Fibonacci R1 at 11.61; TP3: Classic R1 at 12.35</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 54.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OBRI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.6398</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.8411</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>686404</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1357439</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="K21" t="n">
+        <v>245844</v>
+      </c>
+      <c r="L21" t="n">
+        <v>159699</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N21" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>35.3746</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>32.3364</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>35.4223</v>
+      </c>
+      <c r="U21" t="n">
+        <v>31.4211</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="X21" t="n">
+        <v>35.7764</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:49</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>30.4767</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>stop at Classic S1</t>
+        </is>
+      </c>
+      <c r="AC21" t="n">
+        <v>35.9121</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>36.0598</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>36.2267</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>TP1: 100 SMA at 35.91; TP2: Fibonacci R1 at 36.06; TP3: Classic R1 at 36.23</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>15.01</v>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 34.8))</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NIPH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>224</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.4235</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4.6514</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>365646</v>
+      </c>
+      <c r="I22" t="n">
+        <v>920165</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="K22" t="n">
+        <v>290852</v>
+      </c>
+      <c r="L22" t="n">
+        <v>693940</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.386</v>
+      </c>
+      <c r="N22" t="n">
+        <v>157.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>242</v>
+      </c>
+      <c r="P22" t="n">
+        <v>178.5166</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>123.574</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>181.0852</v>
+      </c>
+      <c r="U22" t="n">
+        <v>128.0531</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>69.81999999999999</v>
+      </c>
+      <c r="X22" t="n">
+        <v>201.2921</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-01 10:32:50</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>201.2921</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>158.382</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AC22" t="n">
+        <v>250.7205</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>275.4347</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>262.3856</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 250.72; TP2: Extension at 275.43; TP3: Extension at 262.39</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 69.8))</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SWDY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>93</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.8366</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.2436</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>280675</v>
+      </c>
+      <c r="I23" t="n">
+        <v>270010</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="K23" t="n">
+        <v>97939</v>
+      </c>
+      <c r="L23" t="n">
+        <v>120900</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="N23" t="n">
+        <v>87.02</v>
+      </c>
+      <c r="O23" t="n">
+        <v>93</v>
+      </c>
+      <c r="P23" t="n">
+        <v>88.9806</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>81.6082</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>89.2056</v>
+      </c>
+      <c r="U23" t="n">
+        <v>83.1311</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="n">
+        <v>88.9806</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>84.5316</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ENGC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.1281</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.8573</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>397041</v>
+      </c>
+      <c r="I24" t="n">
+        <v>602042</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="K24" t="n">
+        <v>277385</v>
+      </c>
+      <c r="L24" t="n">
+        <v>243334</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="N24" t="n">
+        <v>36.55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="P24" t="n">
+        <v>37.1912</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>34.8356</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>38.3056</v>
+      </c>
+      <c r="U24" t="n">
+        <v>34.0231</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>37.1912</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>35.3316</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ZEOT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>3065911</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3756109</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1360330</v>
+      </c>
+      <c r="L25" t="n">
+        <v>337628</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="N25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10.4832</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>8.200699999999999</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>10.7922</v>
+      </c>
+      <c r="U25" t="n">
+        <v>8.4533</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="n">
+        <v>10.4832</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>9.959</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BIOC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>239.76</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.7348</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.7348</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>152954</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1143733</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7.478</v>
+      </c>
+      <c r="K26" t="n">
+        <v>202414</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1143733</v>
+      </c>
+      <c r="M26" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="N26" t="n">
+        <v>70</v>
+      </c>
+      <c r="O26" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>86.928</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>70.264</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>97.279</v>
+      </c>
+      <c r="U26" t="n">
+        <v>72.2825</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>90.98</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="n">
+        <v>86.928</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>82.58159999999999</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (91.0); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IFAP</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0407</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.6127</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>688663</v>
+      </c>
+      <c r="I27" t="n">
+        <v>595730</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="K27" t="n">
+        <v>188956</v>
+      </c>
+      <c r="L27" t="n">
+        <v>506370</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N27" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="O27" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P27" t="n">
+        <v>19.5404</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>19.3014</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>19.5437</v>
+      </c>
+      <c r="U27" t="n">
+        <v>19.2442</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>50.24</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>18.5345</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ICFC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>922568</v>
+      </c>
+      <c r="I28" t="n">
+        <v>951836</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.032</v>
+      </c>
+      <c r="K28" t="n">
+        <v>266129</v>
+      </c>
+      <c r="L28" t="n">
+        <v>571102</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="N28" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="P28" t="n">
+        <v>15.3166</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>15.2584</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>15.3073</v>
+      </c>
+      <c r="U28" t="n">
+        <v>16.0911</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>14.6585</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ISMA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.6059</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0893</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9099</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1437614</v>
+      </c>
+      <c r="I29" t="n">
+        <v>576276</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="K29" t="n">
+        <v>531676</v>
+      </c>
+      <c r="L29" t="n">
+        <v>296946</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="N29" t="n">
+        <v>26.54</v>
+      </c>
+      <c r="O29" t="n">
+        <v>36.45</v>
+      </c>
+      <c r="P29" t="n">
+        <v>28.4514</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>17.7319</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>27.3248</v>
+      </c>
+      <c r="U29" t="n">
+        <v>19.6655</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="n">
+        <v>28.4514</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>27.0288</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LCSW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.9952</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>793094</v>
+      </c>
+      <c r="I30" t="n">
+        <v>979267</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.235</v>
+      </c>
+      <c r="K30" t="n">
+        <v>825593</v>
+      </c>
+      <c r="L30" t="n">
+        <v>869099</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="N30" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="O30" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="P30" t="n">
+        <v>29.5852</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>26.7614</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>30.4642</v>
+      </c>
+      <c r="U30" t="n">
+        <v>27.4039</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>62</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="n">
+        <v>29.5852</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>28.1059</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MPCO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>34354934</v>
+      </c>
+      <c r="I31" t="n">
+        <v>59000414</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.717</v>
+      </c>
+      <c r="K31" t="n">
+        <v>22336100</v>
+      </c>
+      <c r="L31" t="n">
+        <v>39333635</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.8034</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.7522</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>1.8137</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.7253</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="n">
+        <v>1.8034</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.7132</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ATQA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1931</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>5521781</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4909177</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1231880</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1436831</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="N32" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="O32" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="P32" t="n">
+        <v>9.620799999999999</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>9.5969</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>9.645099999999999</v>
+      </c>
+      <c r="U32" t="n">
+        <v>9.471399999999999</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>52.59</v>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>9.243499999999999</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MTIE</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.06519999999999999</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>2591517</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3286835</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="K33" t="n">
+        <v>979317</v>
+      </c>
+      <c r="L33" t="n">
+        <v>821706</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="O33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>9.213800000000001</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>8.026899999999999</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>9.179600000000001</v>
+      </c>
+      <c r="U33" t="n">
+        <v>8.3499</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="n">
+        <v>9.213800000000001</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>8.7531</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RACC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1973</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0602</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>2317029</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1634022</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="K34" t="n">
+        <v>610489</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1034878</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="N34" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="O34" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>9.9582</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>9.2225</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>9.916700000000001</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9.112500000000001</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>9.4145</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SKPC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2108</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.4218</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>2815474</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4712227</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="K35" t="n">
+        <v>607874</v>
+      </c>
+      <c r="L35" t="n">
+        <v>906202</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="N35" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="O35" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="P35" t="n">
+        <v>16.436</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>17.4475</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>16.376</v>
+      </c>
+      <c r="U35" t="n">
+        <v>17.4985</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>no stop loss (no entry)</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SCEM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.5818</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.2275</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>709475</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1466664</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="K36" t="n">
+        <v>349204</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>67</v>
+      </c>
+      <c r="P36" t="n">
+        <v>66.4798</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>63.0929</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>68.1281</v>
+      </c>
+      <c r="U36" t="n">
+        <v>60.7481</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="n">
+        <v>66.4798</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>63.1558</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OCDI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>28.03</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5535</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.0432</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>2065579</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2971302</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1916849</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1400759</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="N37" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="P37" t="n">
+        <v>23.9762</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>24.8526</v>
+      </c>
+      <c r="U37" t="n">
+        <v>24.8831</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>64.45999999999999</v>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="n">
+        <v>23.9762</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>22.7774</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SVCE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0329</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>7804852</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2113471</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2251403</v>
+      </c>
+      <c r="L38" t="n">
+        <v>778646</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="N38" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="O38" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="P38" t="n">
+        <v>9.2026</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>8.082800000000001</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>9.0657</v>
+      </c>
+      <c r="U38" t="n">
+        <v>8.0314</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>8.673500000000001</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: no pullback level identified; current price as reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MOED</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>26574144</v>
+      </c>
+      <c r="I39" t="n">
+        <v>54367201</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7895646</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4530544</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.7847</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>0.7204</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.7269</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>no stop loss (no entry)</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RREI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>6225072</v>
+      </c>
+      <c r="I40" t="n">
+        <v>44142417</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7.091</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4755720</v>
+      </c>
+      <c r="L40" t="n">
+        <v>3484900</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3.6826</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.9805</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>3.7544</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3.1014</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="n">
+        <v>3.6826</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.4985</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ADIB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>52.85</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.0437</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1743</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.3764</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>2164018</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3603967</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1300532</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3603967</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.771</v>
+      </c>
+      <c r="N41" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="O41" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="P41" t="n">
+        <v>47.3466</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>37.8286</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>47.2913</v>
+      </c>
+      <c r="U41" t="n">
+        <v>40.4368</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="n">
+        <v>47.3466</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>44.9793</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (71.9); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MFPC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7232</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.5496</v>
+      </c>
+      <c r="F42" t="n">
+        <v>23.0888</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1868672</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2788929</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="K42" t="n">
+        <v>910122</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2278533</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="N42" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="O42" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="P42" t="n">
+        <v>38.9266</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>36.0122</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>38.5049</v>
+      </c>
+      <c r="U42" t="n">
+        <v>38.3309</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>34.789</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: no pullback level identified; current price as reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NCCW</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>2883990</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4574285</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.586</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2388184</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1386146</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="O43" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="P43" t="n">
+        <v>6.1834</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5.8042</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>6.2481</v>
+      </c>
+      <c r="U43" t="n">
+        <v>5.7598</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="n">
+        <v>6.1834</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>5.8742</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EALR</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>391.98</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7.7408</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.442399999999999</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>33705</v>
+      </c>
+      <c r="I44" t="n">
+        <v>426740</v>
+      </c>
+      <c r="J44" t="n">
+        <v>12.661</v>
+      </c>
+      <c r="K44" t="n">
+        <v>12577</v>
+      </c>
+      <c r="L44" t="n">
+        <v>171843</v>
+      </c>
+      <c r="M44" t="n">
+        <v>13.664</v>
+      </c>
+      <c r="N44" t="n">
+        <v>360</v>
+      </c>
+      <c r="O44" t="n">
+        <v>396</v>
+      </c>
+      <c r="P44" t="n">
+        <v>359.4272</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>343.015</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>360.9185</v>
+      </c>
+      <c r="U44" t="n">
+        <v>321.9733</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="n">
+        <v>359.4272</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>341.4558</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AALR</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>273.78</v>
+      </c>
+      <c r="D45" t="n">
+        <v>5.4066</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.4772</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.4066</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>90812</v>
+      </c>
+      <c r="I45" t="n">
+        <v>681524</v>
+      </c>
+      <c r="J45" t="n">
+        <v>7.505</v>
+      </c>
+      <c r="K45" t="n">
+        <v>30216</v>
+      </c>
+      <c r="L45" t="n">
+        <v>466063</v>
+      </c>
+      <c r="M45" t="n">
+        <v>15.424</v>
+      </c>
+      <c r="N45" t="n">
+        <v>200</v>
+      </c>
+      <c r="O45" t="n">
+        <v>247.97</v>
+      </c>
+      <c r="P45" t="n">
+        <v>216.2166</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>186.5941</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>219.3528</v>
+      </c>
+      <c r="U45" t="n">
+        <v>181.9095</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>77.62</v>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="n">
+        <v>216.2166</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>205.4058</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (77.6); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KABO</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.1596</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.0239</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1726</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>2478481</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2721102</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2518339</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2565607</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="N46" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O46" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="P46" t="n">
+        <v>6.8496</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6.3976</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>7.1264</v>
+      </c>
+      <c r="U46" t="n">
+        <v>6.3148</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>63.07</v>
+      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="n">
+        <v>6.8496</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>6.5071</v>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MCRO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>39446506</v>
+      </c>
+      <c r="I47" t="n">
+        <v>74498234</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.889</v>
+      </c>
+      <c r="K47" t="n">
+        <v>29063477</v>
+      </c>
+      <c r="L47" t="n">
+        <v>37249117</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.2902</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.4737</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>1.3249</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.4965</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W47" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>no stop loss (no entry)</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>undervalued, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GGCC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>19600606</v>
+      </c>
+      <c r="I48" t="n">
+        <v>28606169</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="K48" t="n">
+        <v>22304846</v>
+      </c>
+      <c r="L48" t="n">
+        <v>16253501</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.5318000000000001</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>0.5983000000000001</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0.5225</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, RSI overbought (71.9); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>INEG</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C49" t="n">
         <v>0.521</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D49" t="n">
         <v>0.0103</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E49" t="n">
         <v>0.0031</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F49" t="n">
         <v>0.0321</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
         <v>20426292</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I49" t="n">
         <v>41065579</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J49" t="n">
         <v>2.01</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K49" t="n">
         <v>18818578</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L49" t="n">
         <v>12167599</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M49" t="n">
         <v>0.647</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N49" t="n">
         <v>0.507</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O49" t="n">
         <v>0.53</v>
       </c>
-      <c r="P4" t="n">
-        <v>0.4435</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.4651</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T4" t="n">
-        <v>0.4604</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.4411</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>60.96</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.5144</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-07-31 23:43:17</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
+      <c r="P49" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>61.08</v>
+      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>no stop loss (no entry)</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr">
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>no take profit levels (insufficient TA data)</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CPCI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>461.39</v>
+      </c>
+      <c r="D50" t="n">
+        <v>9.111499999999999</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.7323</v>
+      </c>
+      <c r="F50" t="n">
+        <v>9.3431</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>11630</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6210</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6840</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2346</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="N50" t="n">
+        <v>265</v>
+      </c>
+      <c r="O50" t="n">
+        <v>512</v>
+      </c>
+      <c r="P50" t="n">
+        <v>392.8994</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>301.337</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>401.3569</v>
+      </c>
+      <c r="U50" t="n">
+        <v>310.5535</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" t="n">
+        <v>67.28</v>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="n">
+        <v>392.8994</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>373.2544</v>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AXPH</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1209.64</v>
+      </c>
+      <c r="D51" t="n">
+        <v>23.8879</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.7028</v>
+      </c>
+      <c r="F51" t="n">
+        <v>24.6917</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>2311</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2962</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="K51" t="n">
+        <v>861</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2302</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.673</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1122</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1239</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1155.3762</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>913.357</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>1142.8082</v>
+      </c>
+      <c r="U51" t="n">
+        <v>925.4806</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W51" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="n">
+        <v>1155.3762</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1097.6074</v>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MBSC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>242.15</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.782</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.5921</v>
+      </c>
+      <c r="F52" t="n">
+        <v>6.3084</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>92947</v>
+      </c>
+      <c r="I52" t="n">
+        <v>33758</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="K52" t="n">
+        <v>39168</v>
+      </c>
+      <c r="L52" t="n">
+        <v>12024</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="N52" t="n">
+        <v>242</v>
+      </c>
+      <c r="O52" t="n">
+        <v>245</v>
+      </c>
+      <c r="P52" t="n">
+        <v>255.509</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>247.1768</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>250.8222</v>
+      </c>
+      <c r="U52" t="n">
+        <v>235.2446</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="n">
+        <v>242</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>229.9</v>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MILS</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>190.3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3.758</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3.8143</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>90592</v>
+      </c>
+      <c r="I53" t="n">
+        <v>547338</v>
+      </c>
+      <c r="J53" t="n">
+        <v>6.042</v>
+      </c>
+      <c r="K53" t="n">
+        <v>89582</v>
+      </c>
+      <c r="L53" t="n">
+        <v>108474</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="N53" t="n">
+        <v>127.01</v>
+      </c>
+      <c r="O53" t="n">
+        <v>197.49</v>
+      </c>
+      <c r="P53" t="n">
+        <v>143.273</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>122.8783</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>145.5481</v>
+      </c>
+      <c r="U53" t="n">
+        <v>119.2906</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" t="n">
+        <v>67.79000000000001</v>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="n">
+        <v>143.273</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>136.1093</v>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ZMID</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0619</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>24706539</v>
+      </c>
+      <c r="I54" t="n">
+        <v>50026435</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="K54" t="n">
+        <v>15027796</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="O54" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="P54" t="n">
+        <v>6.5684</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>5.8431</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>6.7267</v>
+      </c>
+      <c r="U54" t="n">
+        <v>5.8408</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W54" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="n">
+        <v>6.5684</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AMIA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>3433424</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1042031</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="K55" t="n">
+        <v>757029</v>
+      </c>
+      <c r="L55" t="n">
+        <v>674255</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="N55" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="O55" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="P55" t="n">
+        <v>9.239800000000001</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>9.2349</v>
+      </c>
+      <c r="U55" t="n">
+        <v>6.7256</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="n">
+        <v>9.239800000000001</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>8.777799999999999</v>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MISR</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>9</v>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="P56" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="U56" t="n">
+        <v>5.5037</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" t="n">
+        <v>100</v>
+      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>no stop loss (no entry)</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>undervalued, trend undetermined; entry: trend undetermined (insufficient 200‑period history)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MPCI</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>290</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5.7269</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5.8254</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>367014</v>
+      </c>
+      <c r="I57" t="n">
+        <v>431879</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="K57" t="n">
+        <v>175426</v>
+      </c>
+      <c r="L57" t="n">
+        <v>145255</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="N57" t="n">
+        <v>204.36</v>
+      </c>
+      <c r="O57" t="n">
+        <v>252.69</v>
+      </c>
+      <c r="P57" t="n">
+        <v>235.7932</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>183.9306</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>239.0054</v>
+      </c>
+      <c r="U57" t="n">
+        <v>185.2179</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" t="n">
+        <v>75.28</v>
+      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="n">
+        <v>235.7932</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>224.0035</v>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, RSI overbought (75.3); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TALM</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.3674</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>706832</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4724740</v>
+      </c>
+      <c r="J58" t="n">
+        <v>6.684</v>
+      </c>
+      <c r="K58" t="n">
+        <v>457851</v>
+      </c>
+      <c r="L58" t="n">
+        <v>922802</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2.016</v>
+      </c>
+      <c r="N58" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="O58" t="n">
+        <v>18</v>
+      </c>
+      <c r="P58" t="n">
+        <v>15.8808</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>15.6628</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>15.9126</v>
+      </c>
+      <c r="U58" t="n">
+        <v>14.9781</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" t="n">
+        <v>69.63</v>
+      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="n">
+        <v>15.8808</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>15.0868</v>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>stop at 5% below entry (default)</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Hold</t>
+        </is>
+      </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN58"/>
+  <dimension ref="A1:AP58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,105 +526,115 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>20 EMA</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>50 EMA</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>200 EMA</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>EMA Bullish (50&gt;200) (Yes/No)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Diamond Cross (20&gt;50) (Yes/No)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>RSI (%)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>VWMA</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>TA Data As Of</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Optimal Entry Price</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Stop Loss Basis</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Take Profit 1</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Take Profit 2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Take Profit 3</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Take Profit Basis</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>TP1 Risk/Reward</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>TP2 Risk/Reward</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>TP3 Risk/Reward</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>TP1 Reward %</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>TP2 Reward %</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>TP3 Reward %</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Recommendation Basis</t>
         </is>
@@ -699,78 +709,86 @@
         </is>
       </c>
       <c r="T2" t="n">
+        <v>8.236700000000001</v>
+      </c>
+      <c r="U2" t="n">
         <v>8.148</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>7.8589</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>70.42</v>
-      </c>
-      <c r="X2" t="n">
-        <v>8.3286</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:27</t>
-        </is>
       </c>
       <c r="Z2" t="n">
         <v>8.3286</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.3286</v>
+      </c>
+      <c r="AC2" t="n">
         <v>8.24</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>9.09</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>10.26</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>10.9978</v>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>TP1: Classic R2 at 9.09; TP2: Classic R3 at 10.26; TP3: Extension at 11.0</t>
         </is>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>8.59</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
         <v>21.79</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AK2" t="n">
         <v>30.12</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
         <v>9.140000000000001</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
         <v>23.19</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AN2" t="n">
         <v>32.05</v>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (70.4); entry: enhanced entry at VWMA (overbought (RSI: 70.4))</t>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.4); entry: enhanced entry at VWMA (overbought (RSI: 70.4))</t>
         </is>
       </c>
     </row>
@@ -843,78 +861,86 @@
         </is>
       </c>
       <c r="T3" t="n">
+        <v>56.1556</v>
+      </c>
+      <c r="U3" t="n">
         <v>55.5855</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>49.7698</v>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>50.33</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>56.3002</v>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:29</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
         <v>55.75</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>55.2826</v>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>stop at Parabolic SAR</t>
         </is>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>57.6009</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>58.9186</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>59.26</v>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 57.6; TP2: Fibonacci R1 at 58.92; TP3: Classic R1 at 59.26</t>
         </is>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>3.96</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>6.78</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>7.51</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
         <v>3.32</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>5.68</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AN3" t="n">
         <v>6.3</v>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.3))</t>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.3))</t>
         </is>
       </c>
     </row>
@@ -987,76 +1013,84 @@
         </is>
       </c>
       <c r="T4" t="n">
+        <v>27.6933</v>
+      </c>
+      <c r="U4" t="n">
         <v>27.9294</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>25.9092</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
         <v>43</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>27.7959</v>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:30</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
         <v>26.9043</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>26.8432</v>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>stop at 200 SMA</t>
         </is>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>27.9887</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>28.8767</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>28.8898</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>TP1: 100 SMA at 27.99; TP2: Bollinger Upper Band at 28.88; TP3: Fibonacci R1 at 28.89</t>
         </is>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>17.73</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>32.26</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>32.47</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AL4" t="n">
         <v>4.03</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>7.33</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>7.38</v>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.0))</t>
         </is>
@@ -1131,78 +1165,86 @@
         </is>
       </c>
       <c r="T5" t="n">
+        <v>22.4043</v>
+      </c>
+      <c r="U5" t="n">
         <v>21.8449</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>19.4131</v>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
         <v>54.24</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>22.7323</v>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:31</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
         <v>22</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>21.87</v>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>22.7414</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>23.8033</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>23.807</v>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>TP1: Fibonacci R2 at 22.74; TP2: Classic R2 at 23.8; TP3: Bollinger Upper Band at 23.81</t>
         </is>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>5.7</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>13.87</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>13.9</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AL5" t="n">
         <v>3.37</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AM5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.2))</t>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.2))</t>
         </is>
       </c>
     </row>
@@ -1275,76 +1317,84 @@
         </is>
       </c>
       <c r="T6" t="n">
+        <v>298.6042</v>
+      </c>
+      <c r="U6" t="n">
         <v>299.3498</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>261.8413</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
         <v>46.47</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>299.6988</v>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:32</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
         <v>287.64</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>274.1058</v>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>stop at Fibonacci S1</t>
         </is>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>298.7249</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>308.234</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>321.9475</v>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>TP1: 100 SMA at 298.72; TP2: Bollinger Upper Band at 308.23; TP3: Fibonacci R1 at 321.95</t>
         </is>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.82</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>1.52</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>2.53</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AL6" t="n">
         <v>3.85</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AM6" t="n">
         <v>7.16</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>11.93</v>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>Hold</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.5))</t>
         </is>
@@ -1419,76 +1469,84 @@
         </is>
       </c>
       <c r="T7" t="n">
+        <v>11.5838</v>
+      </c>
+      <c r="U7" t="n">
         <v>11.5956</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>11.0178</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
         <v>42.19</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>11.5447</v>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:33</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
         <v>11.3</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>11.2998</v>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>stop at 200 SMA</t>
         </is>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>11.7464</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>12.4583</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>12.54</v>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 11.75; TP2: Fibonacci R1 at 12.46; TP3: Classic R1 at 12.54</t>
         </is>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>2972.22</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>7712.19</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>8256.17</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AL7" t="n">
         <v>3.95</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
         <v>10.25</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
         <v>10.97</v>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 42.2))</t>
         </is>
@@ -1563,78 +1621,86 @@
         </is>
       </c>
       <c r="T8" t="n">
+        <v>29.4753</v>
+      </c>
+      <c r="U8" t="n">
         <v>29.418</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>27.3193</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
         <v>39.7</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>29.5599</v>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:34</t>
-        </is>
-      </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
         <v>28.4284</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>28.0358</v>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>31.5052</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>31.6449</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>31.9833</v>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 31.51; TP2: Fibonacci R1 at 31.64; TP3: Classic R1 at 31.98</t>
         </is>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>7.84</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>8.19</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AL8" t="n">
         <v>10.82</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AM8" t="n">
         <v>11.31</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AN8" t="n">
         <v>12.5</v>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 39.7))</t>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 39.7))</t>
         </is>
       </c>
     </row>
@@ -1707,78 +1773,86 @@
         </is>
       </c>
       <c r="T9" t="n">
+        <v>182.4461</v>
+      </c>
+      <c r="U9" t="n">
         <v>182.1341</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>156.8251</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
         <v>50.57</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>182.6138</v>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:35</t>
-        </is>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
         <v>180.83</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>175</v>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>184.6849</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>191.54</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>191.8359</v>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>TP1: 100 SMA at 184.68; TP2: Classic R1 at 191.54; TP3: Fibonacci R1 at 191.84</t>
         </is>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.66</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>1.84</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>1.89</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AL9" t="n">
         <v>2.13</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AM9" t="n">
         <v>5.92</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AN9" t="n">
         <v>6.09</v>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.6))</t>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.6))</t>
         </is>
       </c>
     </row>
@@ -1837,78 +1911,86 @@
         </is>
       </c>
       <c r="T10" t="n">
+        <v>711.3390000000001</v>
+      </c>
+      <c r="U10" t="n">
         <v>696.5584</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>563.7071</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
         <v>50.42</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>702.4604</v>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:36</t>
-        </is>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
         <v>71.05</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>67.4975</v>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>stop at 5% below entry (default)</t>
         </is>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>541.5338</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>629.5273999999999</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>731.4788</v>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>TP1: 200 SMA at 541.53; TP2: 100 SMA at 629.53; TP3: Bollinger Upper Band at 731.48</t>
         </is>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>132.44</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AJ10" t="n">
         <v>157.21</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AK10" t="n">
         <v>185.91</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AL10" t="n">
         <v>662.1900000000001</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AM10" t="n">
         <v>786.03</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AN10" t="n">
         <v>929.53</v>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: no pullback level identified; current price as reference</t>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: no pullback level identified; current price as reference</t>
         </is>
       </c>
     </row>
@@ -1981,76 +2063,84 @@
         </is>
       </c>
       <c r="T11" t="n">
+        <v>22.9107</v>
+      </c>
+      <c r="U11" t="n">
         <v>22.9162</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>22.9066</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
         <v>43.4</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>22.9516</v>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:37</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
         <v>22.3727</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>21.9856</v>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>stop at Fibonacci S1</t>
         </is>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>22.8104</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>22.9377</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>23.3803</v>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>TP1: 100 SMA at 22.81; TP2: 200 SMA at 22.94; TP3: Bollinger Upper Band at 23.38</t>
         </is>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>1.13</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>1.46</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>2.6</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AL11" t="n">
         <v>1.96</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AM11" t="n">
         <v>2.53</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AN11" t="n">
         <v>4.5</v>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.4))</t>
         </is>
@@ -2125,78 +2215,86 @@
         </is>
       </c>
       <c r="T12" t="n">
+        <v>14.7864</v>
+      </c>
+      <c r="U12" t="n">
         <v>14.2671</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>11.175</v>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
         <v>44.65</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>14.8298</v>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:38</t>
-        </is>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
         <v>14.43</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>14.2677</v>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>stop at Fibonacci S1</t>
         </is>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>15.1485</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>15.9256</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>16.4377</v>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 15.15; TP2: Fibonacci R1 at 15.93; TP3: Fibonacci R2 at 16.44</t>
         </is>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>4.43</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AJ12" t="n">
         <v>9.220000000000001</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AK12" t="n">
         <v>12.37</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AL12" t="n">
         <v>4.98</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AM12" t="n">
         <v>10.36</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AN12" t="n">
         <v>13.91</v>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 44.7))</t>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (neutral (RSI: 44.7))</t>
         </is>
       </c>
     </row>
@@ -2269,78 +2367,86 @@
         </is>
       </c>
       <c r="T13" t="n">
+        <v>100.4262</v>
+      </c>
+      <c r="U13" t="n">
         <v>96.9744</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>81.1778</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
         <v>62.41</v>
-      </c>
-      <c r="X13" t="n">
-        <v>100.8252</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:40</t>
-        </is>
       </c>
       <c r="Z13" t="n">
         <v>100.8252</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>100.8252</v>
+      </c>
+      <c r="AC13" t="n">
         <v>99.0941</v>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>stop at Parabolic SAR</t>
         </is>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>107.2343</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>111.2</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>115.1632</v>
       </c>
-      <c r="AF13" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 107.23; TP2: Classic R3 at 111.2; TP3: Extension at 115.16</t>
         </is>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>3.7</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>5.99</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AK13" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AL13" t="n">
         <v>6.36</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AM13" t="n">
         <v>10.29</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AN13" t="n">
         <v>14.22</v>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
         </is>
       </c>
     </row>
@@ -2413,78 +2519,86 @@
         </is>
       </c>
       <c r="T14" t="n">
+        <v>5.0834</v>
+      </c>
+      <c r="U14" t="n">
         <v>4.9738</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>4.2529</v>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
         <v>64.26000000000001</v>
-      </c>
-      <c r="X14" t="n">
-        <v>5.1267</v>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:41</t>
-        </is>
       </c>
       <c r="Z14" t="n">
         <v>5.1267</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.1267</v>
+      </c>
+      <c r="AC14" t="n">
         <v>5.04</v>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>5.2833</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>5.3989</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>5.6167</v>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AH14" t="inlineStr">
         <is>
           <t>TP1: Classic R1 at 5.28; TP2: Fibonacci R2 at 5.4; TP3: Classic R2 at 5.62</t>
         </is>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>1.81</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AJ14" t="n">
         <v>3.14</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AK14" t="n">
         <v>5.65</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AL14" t="n">
         <v>3.05</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AM14" t="n">
         <v>5.31</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AN14" t="n">
         <v>9.56</v>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 64.3))</t>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.3))</t>
         </is>
       </c>
     </row>
@@ -2557,78 +2671,86 @@
         </is>
       </c>
       <c r="T15" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="U15" t="n">
         <v>3.1702</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>2.3112</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W15" t="n">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
         <v>75.92</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>3.5103</v>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:43</t>
-        </is>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
         <v>4.336</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>2.52</v>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>5.1555</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>5.5653</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>5.3489</v>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AH15" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 5.16; TP2: Extension at 5.57; TP3: Extension at 5.35</t>
         </is>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.45</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
         <v>0.68</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AK15" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AL15" t="n">
         <v>18.9</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AM15" t="n">
         <v>28.35</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AN15" t="n">
         <v>23.36</v>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed, RSI overbought (75.9); entry: enhanced entry at Parabolic SAR (overbought (RSI: 75.9))</t>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.9); entry: enhanced entry at Parabolic SAR (overbought (RSI: 75.9))</t>
         </is>
       </c>
     </row>
@@ -2701,78 +2823,86 @@
         </is>
       </c>
       <c r="T16" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="U16" t="n">
         <v>0.2228</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.1917</v>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W16" t="n">
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
         <v>53.68</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>0.238</v>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:44</t>
-        </is>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
         <v>0.2335</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.232</v>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.26</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.2732</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.2663</v>
       </c>
-      <c r="AF16" t="inlineStr">
+      <c r="AH16" t="inlineStr">
         <is>
           <t>TP1: Classic R3 at 0.26; TP2: Extension at 0.27; TP3: Extension at 0.27</t>
         </is>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>17.67</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AJ16" t="n">
         <v>26.47</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AK16" t="n">
         <v>21.87</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AL16" t="n">
         <v>11.35</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AM16" t="n">
         <v>17</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AN16" t="n">
         <v>14.05</v>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.7))</t>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.7))</t>
         </is>
       </c>
     </row>
@@ -2845,78 +2975,86 @@
         </is>
       </c>
       <c r="T17" t="n">
+        <v>1.6512</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.5952</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>1.5047</v>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W17" t="n">
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
         <v>45.34</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>1.6559</v>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:45</t>
-        </is>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>1.54</v>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>1.6798</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>1.7435</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>1.752</v>
       </c>
-      <c r="AF17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>TP1: Fibonacci R1 at 1.68; TP2: Fibonacci R2 at 1.74; TP3: Bollinger Upper Band at 1.75</t>
         </is>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>12.95</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AJ17" t="n">
         <v>19.3</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AK17" t="n">
         <v>20.15</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AL17" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AM17" t="n">
         <v>12.48</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AN17" t="n">
         <v>13.03</v>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 45.3))</t>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 45.3))</t>
         </is>
       </c>
     </row>
@@ -2989,78 +3127,86 @@
         </is>
       </c>
       <c r="T18" t="n">
+        <v>38.4537</v>
+      </c>
+      <c r="U18" t="n">
         <v>37.4861</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>31.3569</v>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W18" t="n">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
         <v>45.29</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>39.1299</v>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:46</t>
-        </is>
-      </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
         <v>35.4175</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>34.99</v>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>40.0092</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
         <v>40.4019</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AG18" t="n">
         <v>40.4367</v>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>TP1: Fibonacci R1 at 40.01; TP2: Bollinger Upper Band at 40.4; TP3: Classic R1 at 40.44</t>
         </is>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>10.74</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AJ18" t="n">
         <v>11.66</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AK18" t="n">
         <v>11.74</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AL18" t="n">
         <v>12.96</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AM18" t="n">
         <v>14.07</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AN18" t="n">
         <v>14.17</v>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 45.3))</t>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 45.3))</t>
         </is>
       </c>
     </row>
@@ -3133,78 +3279,86 @@
         </is>
       </c>
       <c r="T19" t="n">
+        <v>34.6157</v>
+      </c>
+      <c r="U19" t="n">
         <v>30.3545</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>21.1737</v>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
         <v>54.04</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>35.6583</v>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:47</t>
-        </is>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
         <v>33.5793</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>33.0916</v>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>34.8467</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>34.8853</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>37.9264</v>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>TP1: Classic R1 at 34.85; TP2: Fibonacci R2 at 34.89; TP3: Bollinger Upper Band at 37.93</t>
         </is>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AJ19" t="n">
         <v>2.68</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AK19" t="n">
         <v>8.91</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AL19" t="n">
         <v>3.77</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AM19" t="n">
         <v>3.89</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AN19" t="n">
         <v>12.95</v>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: enhanced entry at Parabolic SAR (overbought (RSI: 54.0))</t>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 54.0))</t>
         </is>
       </c>
     </row>
@@ -3277,78 +3431,86 @@
         </is>
       </c>
       <c r="T20" t="n">
+        <v>10.6709</v>
+      </c>
+      <c r="U20" t="n">
         <v>9.979900000000001</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>8.1972</v>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W20" t="n">
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
         <v>53.97</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>10.8525</v>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:48</t>
-        </is>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
         <v>10.5646</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>8.6655</v>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>stop at Fibonacci S1</t>
         </is>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>11.0774</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>11.6145</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>12.35</v>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AH20" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 11.08; TP2: Fibonacci R1 at 11.61; TP3: Classic R1 at 12.35</t>
         </is>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AK20" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AL20" t="n">
         <v>4.85</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AM20" t="n">
         <v>9.94</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AN20" t="n">
         <v>16.9</v>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 54.0))</t>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 54.0))</t>
         </is>
       </c>
     </row>
@@ -3421,76 +3583,84 @@
         </is>
       </c>
       <c r="T21" t="n">
+        <v>34.9552</v>
+      </c>
+      <c r="U21" t="n">
         <v>35.4223</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>31.4211</v>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W21" t="n">
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
         <v>34.85</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>35.7764</v>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:49</t>
-        </is>
-      </c>
-      <c r="Z21" t="n">
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
         <v>31.5</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>30.4767</v>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>stop at Classic S1</t>
         </is>
       </c>
-      <c r="AC21" t="n">
+      <c r="AE21" t="n">
         <v>35.9121</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>36.0598</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
         <v>36.2267</v>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>TP1: 100 SMA at 35.91; TP2: Fibonacci R1 at 36.06; TP3: Classic R1 at 36.23</t>
         </is>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>4.31</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>4.46</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>4.62</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AL21" t="n">
         <v>14.01</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AM21" t="n">
         <v>14.48</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AN21" t="n">
         <v>15.01</v>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AP21" t="inlineStr">
         <is>
           <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 34.8))</t>
         </is>
@@ -3565,78 +3735,86 @@
         </is>
       </c>
       <c r="T22" t="n">
+        <v>206.132</v>
+      </c>
+      <c r="U22" t="n">
         <v>181.0852</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>128.0531</v>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W22" t="n">
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
         <v>69.81999999999999</v>
-      </c>
-      <c r="X22" t="n">
-        <v>201.2921</v>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-08-01 10:32:50</t>
-        </is>
       </c>
       <c r="Z22" t="n">
         <v>201.2921</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>201.2921</v>
+      </c>
+      <c r="AC22" t="n">
         <v>158.382</v>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>stop at Fibonacci S1</t>
         </is>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>250.7205</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>275.4347</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AG22" t="n">
         <v>262.3856</v>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AH22" t="inlineStr">
         <is>
           <t>TP1: Bollinger Upper Band at 250.72; TP2: Extension at 275.43; TP3: Extension at 262.39</t>
         </is>
       </c>
-      <c r="AG22" t="n">
+      <c r="AI22" t="n">
         <v>1.15</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>1.73</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>1.42</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AL22" t="n">
         <v>24.56</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AM22" t="n">
         <v>36.83</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AN22" t="n">
         <v>30.35</v>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 69.8))</t>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.8))</t>
         </is>
       </c>
     </row>
@@ -3693,10 +3871,10 @@
         <v>93</v>
       </c>
       <c r="P23" t="n">
-        <v>88.9806</v>
+        <v>89.0424</v>
       </c>
       <c r="Q23" t="n">
-        <v>81.6082</v>
+        <v>81.3045</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -3709,54 +3887,86 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>89.2056</v>
+        <v>91.8026</v>
       </c>
       <c r="U23" t="n">
-        <v>83.1311</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W23" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
+        <v>89.121</v>
+      </c>
+      <c r="V23" t="n">
+        <v>82.90989999999999</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>57.76</v>
+      </c>
       <c r="Z23" t="n">
-        <v>88.9806</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>84.5316</v>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>92.26649999999999</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>92.26649999999999</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>90.5284</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>94.7967</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>96.996</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>102.3867</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>TP1: Classic R2 at 94.8; TP2: Bollinger Upper Band at 97.0; TP3: Classic R3 at 102.39</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.8))</t>
         </is>
       </c>
     </row>
@@ -3813,10 +4023,10 @@
         <v>44.89</v>
       </c>
       <c r="P24" t="n">
-        <v>37.1912</v>
+        <v>37.255</v>
       </c>
       <c r="Q24" t="n">
-        <v>34.8356</v>
+        <v>34.7312</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -3829,54 +4039,86 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>38.3056</v>
+        <v>40.9255</v>
       </c>
       <c r="U24" t="n">
-        <v>34.0231</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
+        <v>38.3029</v>
+      </c>
+      <c r="V24" t="n">
+        <v>33.9859</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>55.5</v>
+      </c>
       <c r="Z24" t="n">
-        <v>37.1912</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>35.3316</v>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>41.3738</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>36.5519</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>41.5133</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>45.3501</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>46.9933</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>TP1: Classic R2 at 41.51; TP2: Bollinger Upper Band at 45.35; TP3: Classic R3 at 46.99</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.5))</t>
         </is>
       </c>
     </row>
@@ -3933,10 +4175,10 @@
         <v>12.3</v>
       </c>
       <c r="P25" t="n">
-        <v>10.4832</v>
+        <v>10.4942</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.200699999999999</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -3949,54 +4191,86 @@
         </is>
       </c>
       <c r="T25" t="n">
-        <v>10.7922</v>
+        <v>11.59</v>
       </c>
       <c r="U25" t="n">
-        <v>8.4533</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W25" t="n">
-        <v>65.76000000000001</v>
-      </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
+        <v>10.7807</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.3912</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>64.92</v>
+      </c>
       <c r="Z25" t="n">
-        <v>10.4832</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>9.959</v>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>11.6201</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>11.695</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>12.3494</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>12.9025</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>13.4833</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 12.35; TP2: Fibonacci R1 at 12.9; TP3: Classic R1 at 13.48</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.9))</t>
         </is>
       </c>
     </row>
@@ -4053,10 +4327,10 @@
         <v>74.2</v>
       </c>
       <c r="P26" t="n">
-        <v>86.928</v>
+        <v>87.16840000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>70.264</v>
+        <v>70.0688</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -4069,54 +4343,64 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>97.279</v>
+        <v>125.7031</v>
       </c>
       <c r="U26" t="n">
-        <v>72.2825</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>90.98</v>
-      </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
+        <v>97.1628</v>
+      </c>
+      <c r="V26" t="n">
+        <v>71.9948</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>90.90000000000001</v>
+      </c>
       <c r="Z26" t="n">
-        <v>86.928</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>82.58159999999999</v>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
+        <v>149.3587</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>153.255</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>126.0564</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
       <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr">
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (91.0); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (90.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 90.9))</t>
         </is>
       </c>
     </row>
@@ -4173,10 +4457,10 @@
         <v>19.7</v>
       </c>
       <c r="P27" t="n">
-        <v>19.5404</v>
+        <v>19.6032</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.3014</v>
+        <v>19.3066</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -4189,54 +4473,86 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>19.5437</v>
+        <v>19.4957</v>
       </c>
       <c r="U27" t="n">
-        <v>19.2442</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W27" t="n">
-        <v>50.24</v>
-      </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
+        <v>19.5395</v>
+      </c>
+      <c r="V27" t="n">
+        <v>18.7078</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>50.21</v>
+      </c>
       <c r="Z27" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>18.5345</v>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr">
+        <v>19.5184</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>19.375</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>19.3066</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>stop at 200 SMA</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>19.5211</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>19.8969</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>22.4073</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>TP1: 100 SMA at 19.52; TP2: Bollinger Upper Band at 19.9; TP3: Fibonacci R1 at 22.41</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="AO27" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.2))</t>
         </is>
       </c>
     </row>
@@ -4293,10 +4609,10 @@
         <v>15.78</v>
       </c>
       <c r="P28" t="n">
-        <v>15.3166</v>
+        <v>15.363</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.2584</v>
+        <v>15.2781</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -4309,54 +4625,86 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>15.3073</v>
+        <v>15.3139</v>
       </c>
       <c r="U28" t="n">
-        <v>16.0911</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W28" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
+        <v>15.3077</v>
+      </c>
+      <c r="V28" t="n">
+        <v>14.8836</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>54.72</v>
+      </c>
       <c r="Z28" t="n">
+        <v>15.3761</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
         <v>15.43</v>
       </c>
-      <c r="AA28" t="n">
-        <v>14.6585</v>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+      <c r="AC28" t="n">
+        <v>15.2781</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>stop at 200 SMA</t>
+        </is>
+      </c>
+      <c r="AE28" t="n">
+        <v>15.7333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>15.741</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>15.7866</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>TP1: Classic R1 at 15.73; TP2: Fibonacci R1 at 15.74; TP3: Bollinger Upper Band at 15.79</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 54.7))</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4761,10 @@
         <v>36.45</v>
       </c>
       <c r="P29" t="n">
-        <v>28.4514</v>
+        <v>28.1316</v>
       </c>
       <c r="Q29" t="n">
-        <v>17.7319</v>
+        <v>17.4312</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -4429,54 +4777,86 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>27.3248</v>
+        <v>29.3518</v>
       </c>
       <c r="U29" t="n">
-        <v>19.6655</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W29" t="n">
-        <v>62.94</v>
-      </c>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
+        <v>27.0708</v>
+      </c>
+      <c r="V29" t="n">
+        <v>19.3331</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>63.19</v>
+      </c>
       <c r="Z29" t="n">
-        <v>28.4514</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>27.0288</v>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>29.4364</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>28.9561</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>32.0079</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>34.3743</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>34.7767</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 32.01; TP2: Fibonacci R1 at 34.37; TP3: Classic R1 at 34.78</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 63.2))</t>
         </is>
       </c>
     </row>
@@ -4533,10 +4913,10 @@
         <v>31.33</v>
       </c>
       <c r="P30" t="n">
-        <v>29.5852</v>
+        <v>29.4926</v>
       </c>
       <c r="Q30" t="n">
-        <v>26.7614</v>
+        <v>26.6924</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -4549,54 +4929,86 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>30.4642</v>
+        <v>32.759</v>
       </c>
       <c r="U30" t="n">
-        <v>27.4039</v>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W30" t="n">
-        <v>62</v>
-      </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
+        <v>30.283</v>
+      </c>
+      <c r="V30" t="n">
+        <v>27.3043</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>62.18</v>
+      </c>
       <c r="Z30" t="n">
-        <v>29.5852</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>28.1059</v>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>32.0235</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>32.0235</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>28.0639</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>36.9281</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>39.0767</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>41.771</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 36.93; TP2: Classic R3 at 39.08; TP3: Extension at 41.77</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.2))</t>
         </is>
       </c>
     </row>
@@ -4653,10 +5065,10 @@
         <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8034</v>
+        <v>1.8022</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.7522</v>
+        <v>1.6931</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -4669,54 +5081,86 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>1.8137</v>
+        <v>1.8754</v>
       </c>
       <c r="U31" t="n">
-        <v>1.7253</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W31" t="n">
-        <v>58.98</v>
-      </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
+        <v>1.8097</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.6226</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>59.04</v>
+      </c>
       <c r="Z31" t="n">
-        <v>1.8034</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.7132</v>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>1.9044</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.9044</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.9599</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.9924</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.0533</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 1.96; TP2: Fibonacci R1 at 1.99; TP3: Classic R1 at 2.05</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.0))</t>
         </is>
       </c>
     </row>
@@ -4773,10 +5217,10 @@
         <v>9.84</v>
       </c>
       <c r="P32" t="n">
-        <v>9.620799999999999</v>
+        <v>9.654</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.5969</v>
+        <v>9.65</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -4789,54 +5233,86 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>9.645099999999999</v>
+        <v>9.7372</v>
       </c>
       <c r="U32" t="n">
-        <v>9.471399999999999</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W32" t="n">
-        <v>52.59</v>
-      </c>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
+        <v>9.6433</v>
+      </c>
+      <c r="V32" t="n">
+        <v>9.472799999999999</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>52.55</v>
+      </c>
       <c r="Z32" t="n">
+        <v>9.780099999999999</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
         <v>9.73</v>
       </c>
-      <c r="AA32" t="n">
-        <v>9.243499999999999</v>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+      <c r="AC32" t="n">
+        <v>9.6591</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>10.0437</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>10.0572</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 10.04; TP2: Bollinger Upper Band at 10.06; TP3: Classic R1 at 10.12</t>
+        </is>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 52.5))</t>
         </is>
       </c>
     </row>
@@ -4893,10 +5369,10 @@
         <v>9.6</v>
       </c>
       <c r="P33" t="n">
-        <v>9.213800000000001</v>
+        <v>9.208600000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>8.026899999999999</v>
+        <v>7.9732</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -4909,54 +5385,86 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>9.179600000000001</v>
+        <v>9.3826</v>
       </c>
       <c r="U33" t="n">
-        <v>8.3499</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>52.14</v>
-      </c>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
+        <v>9.147500000000001</v>
+      </c>
+      <c r="V33" t="n">
+        <v>8.124599999999999</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>52.35</v>
+      </c>
       <c r="Z33" t="n">
-        <v>9.213800000000001</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>8.7531</v>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>9.485900000000001</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9.211399999999999</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.4329</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>9.6571</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 9.43; TP2: Classic R1 at 9.49; TP3: Fibonacci R2 at 9.66</t>
+        </is>
+      </c>
+      <c r="AI33" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.3))</t>
         </is>
       </c>
     </row>
@@ -5013,10 +5521,10 @@
         <v>10.3</v>
       </c>
       <c r="P34" t="n">
-        <v>9.9582</v>
+        <v>9.9594</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.2225</v>
+        <v>9.2111</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -5029,54 +5537,86 @@
         </is>
       </c>
       <c r="T34" t="n">
-        <v>9.916700000000001</v>
+        <v>10.0779</v>
       </c>
       <c r="U34" t="n">
-        <v>9.112500000000001</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>48.26</v>
-      </c>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
+        <v>9.9047</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9.079599999999999</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>48.33</v>
+      </c>
       <c r="Z34" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>9.4145</v>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr">
+        <v>10.2399</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>9.834</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.403700000000001</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AE34" t="n">
+        <v>10.183</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>10.2267</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>10.4237</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 10.18; TP2: Classic R1 at 10.23; TP3: Fibonacci R2 at 10.42</t>
+        </is>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO34" t="inlineStr">
         <is>
           <t>Buy</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 48.3))</t>
         </is>
       </c>
     </row>
@@ -5133,66 +5673,102 @@
         <v>15.77</v>
       </c>
       <c r="P35" t="n">
-        <v>16.436</v>
+        <v>16.4918</v>
       </c>
       <c r="Q35" t="n">
-        <v>17.4475</v>
+        <v>16.2599</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T35" t="n">
-        <v>16.376</v>
+        <v>16.0461</v>
       </c>
       <c r="U35" t="n">
-        <v>17.4985</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>42.72</v>
-      </c>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>no stop loss (no entry)</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+        <v>16.3709</v>
+      </c>
+      <c r="V35" t="n">
+        <v>16.4502</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>16.0495</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>15.5799</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>15.3806</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AE35" t="n">
+        <v>16.2599</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>16.7124</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>17.0033</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>TP1: 200 SMA at 16.26; TP2: Bollinger Upper Band at 16.71; TP3: 100 SMA at 17.0</t>
+        </is>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 42.8))</t>
         </is>
       </c>
     </row>
@@ -5247,10 +5823,10 @@
         <v>67</v>
       </c>
       <c r="P36" t="n">
-        <v>66.4798</v>
+        <v>66.6896</v>
       </c>
       <c r="Q36" t="n">
-        <v>63.0929</v>
+        <v>62.8355</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -5263,54 +5839,86 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>68.1281</v>
+        <v>73.66419999999999</v>
       </c>
       <c r="U36" t="n">
-        <v>60.7481</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
+        <v>68.06399999999999</v>
+      </c>
+      <c r="V36" t="n">
+        <v>60.5435</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>65.63</v>
+      </c>
       <c r="Z36" t="n">
-        <v>66.4798</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>63.1558</v>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>76.3087</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>76.3087</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>73.8415</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE36" t="n">
+        <v>88.58920000000001</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>94.7295</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>91.48739999999999</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 88.59; TP2: Extension at 94.73; TP3: Extension at 91.49</t>
+        </is>
+      </c>
+      <c r="AI36" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.6))</t>
         </is>
       </c>
     </row>
@@ -5367,10 +5975,10 @@
         <v>28.7</v>
       </c>
       <c r="P37" t="n">
-        <v>23.9762</v>
+        <v>24.0836</v>
       </c>
       <c r="Q37" t="n">
-        <v>20.22</v>
+        <v>20.1065</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -5383,54 +5991,86 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>24.8526</v>
+        <v>26.9089</v>
       </c>
       <c r="U37" t="n">
-        <v>24.8831</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>64.45999999999999</v>
-      </c>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
+        <v>24.857</v>
+      </c>
+      <c r="V37" t="n">
+        <v>20.8564</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>64.14</v>
+      </c>
       <c r="Z37" t="n">
-        <v>23.9762</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>22.7774</v>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>27.3583</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB37" t="n">
+        <v>27.3583</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>26.652</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE37" t="n">
+        <v>28.8758</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>29.4467</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>35.3367</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 28.88; TP2: Classic R2 at 29.45; TP3: Classic R3 at 35.34</t>
+        </is>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.1))</t>
         </is>
       </c>
     </row>
@@ -5490,7 +6130,7 @@
         <v>9.2026</v>
       </c>
       <c r="Q38" t="n">
-        <v>8.082800000000001</v>
+        <v>7.248</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -5503,54 +6143,86 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>9.0657</v>
+        <v>9.2759</v>
       </c>
       <c r="U38" t="n">
-        <v>8.0314</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>46.16</v>
-      </c>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
+        <v>8.9658</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7.4306</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>46.78</v>
+      </c>
       <c r="Z38" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>8.673500000000001</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: no pullback level identified; current price as reference</t>
+        <v>9.4832</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB38" t="n">
+        <v>8.297700000000001</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>stop at Classic S1</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>9.642300000000001</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>9.6944</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 9.64; TP2: Bollinger Upper Band at 9.69; TP3: Classic R1 at 9.83</t>
+        </is>
+      </c>
+      <c r="AI38" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.8))</t>
         </is>
       </c>
     </row>
@@ -5607,10 +6279,10 @@
         <v>0.721</v>
       </c>
       <c r="P39" t="n">
-        <v>0.7025</v>
+        <v>0.7074</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.7847</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -5623,50 +6295,64 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>0.7204</v>
+        <v>0.7062</v>
       </c>
       <c r="U39" t="n">
+        <v>0.7228</v>
+      </c>
+      <c r="V39" t="n">
         <v>0.7269</v>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W39" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr">
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>37.53</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.7122000000000001</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>no stop loss (no entry)</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr">
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr">
         <is>
           <t>no take profit levels (insufficient TA data)</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr">
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
     </row>
@@ -5723,10 +6409,10 @@
         <v>4.11</v>
       </c>
       <c r="P40" t="n">
-        <v>3.6826</v>
+        <v>3.6948</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.9805</v>
+        <v>2.9562</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -5739,54 +6425,86 @@
         </is>
       </c>
       <c r="T40" t="n">
-        <v>3.7544</v>
+        <v>4.0321</v>
       </c>
       <c r="U40" t="n">
-        <v>3.1014</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W40" t="n">
-        <v>68.79000000000001</v>
-      </c>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
+        <v>3.7491</v>
+      </c>
+      <c r="V40" t="n">
+        <v>3.0828</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>68.59</v>
+      </c>
       <c r="Z40" t="n">
-        <v>3.6826</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.4985</v>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>4.2457</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>4.2457</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.991</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
+        <v>4.6831</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>4.9018</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>4.7863</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 4.68; TP2: Extension at 4.9; TP3: Extension at 4.79</t>
+        </is>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.6))</t>
         </is>
       </c>
     </row>
@@ -5843,10 +6561,10 @@
         <v>48.49</v>
       </c>
       <c r="P41" t="n">
-        <v>47.3466</v>
+        <v>47.329</v>
       </c>
       <c r="Q41" t="n">
-        <v>37.8286</v>
+        <v>36.7077</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -5859,54 +6577,86 @@
         </is>
       </c>
       <c r="T41" t="n">
-        <v>47.2913</v>
+        <v>48.9149</v>
       </c>
       <c r="U41" t="n">
-        <v>40.4368</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W41" t="n">
-        <v>71.88</v>
-      </c>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
+        <v>47.1388</v>
+      </c>
+      <c r="V41" t="n">
+        <v>38.3881</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>71.48</v>
+      </c>
       <c r="Z41" t="n">
-        <v>47.3466</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>44.9793</v>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr">
+        <v>48.6622</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>48.6622</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>47.6032</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>55.9567</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>59.604</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>57.6782</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 55.96; TP2: Extension at 59.6; TP3: Extension at 57.68</t>
+        </is>
+      </c>
+      <c r="AI41" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="AO41" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (71.9); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.5); entry: enhanced entry at VWMA (overbought (RSI: 71.5))</t>
         </is>
       </c>
     </row>
@@ -5963,10 +6713,10 @@
         <v>38.28</v>
       </c>
       <c r="P42" t="n">
-        <v>38.9266</v>
+        <v>39.1026</v>
       </c>
       <c r="Q42" t="n">
-        <v>36.0122</v>
+        <v>35.6823</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -5979,54 +6729,86 @@
         </is>
       </c>
       <c r="T42" t="n">
-        <v>38.5049</v>
+        <v>37.1869</v>
       </c>
       <c r="U42" t="n">
-        <v>38.3309</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W42" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
+        <v>38.5094</v>
+      </c>
+      <c r="V42" t="n">
+        <v>36.6576</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>42.78</v>
+      </c>
       <c r="Z42" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>34.789</v>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr">
+        <v>37.1431</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>35.4296</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>38.6744</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>41.0836</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>41.3733</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 38.67; TP2: 100 SMA at 41.08; TP3: Classic R1 at 41.37</t>
+        </is>
+      </c>
+      <c r="AI42" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="AO42" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: no pullback level identified; current price as reference</t>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 42.8))</t>
         </is>
       </c>
     </row>
@@ -6083,10 +6865,10 @@
         <v>6.91</v>
       </c>
       <c r="P43" t="n">
-        <v>6.1834</v>
+        <v>6.1786</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.8042</v>
+        <v>5.859</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -6099,54 +6881,86 @@
         </is>
       </c>
       <c r="T43" t="n">
-        <v>6.2481</v>
+        <v>6.629</v>
       </c>
       <c r="U43" t="n">
-        <v>5.7598</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W43" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
+        <v>6.2406</v>
+      </c>
+      <c r="V43" t="n">
+        <v>5.6614</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>61</v>
+      </c>
       <c r="Z43" t="n">
-        <v>6.1834</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>5.8742</v>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>6.7001</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>6.7001</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>6.4163</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE43" t="n">
+        <v>6.9833</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>7.1484</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>7.1749</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>TP1: Classic R1 at 6.98; TP2: Bollinger Upper Band at 7.15; TP3: Fibonacci R2 at 7.17</t>
+        </is>
+      </c>
+      <c r="AI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.0))</t>
         </is>
       </c>
     </row>
@@ -6203,10 +7017,10 @@
         <v>396</v>
       </c>
       <c r="P44" t="n">
-        <v>359.4272</v>
+        <v>360.7776</v>
       </c>
       <c r="Q44" t="n">
-        <v>343.015</v>
+        <v>341.2588</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -6219,54 +7033,86 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>360.9185</v>
+        <v>366.8971</v>
       </c>
       <c r="U44" t="n">
-        <v>321.9733</v>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W44" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="inlineStr"/>
+        <v>360.7054</v>
+      </c>
+      <c r="V44" t="n">
+        <v>320.0468</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y44" t="n">
+        <v>64.95999999999999</v>
+      </c>
       <c r="Z44" t="n">
-        <v>359.4272</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>341.4558</v>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>378.0295</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>382</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>360</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>398.67</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>446.67</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>471.3739</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>TP1: Classic R2 at 398.67; TP2: Classic R3 at 446.67; TP3: Extension at 471.37</t>
+        </is>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.0))</t>
         </is>
       </c>
     </row>
@@ -6323,10 +7169,10 @@
         <v>247.97</v>
       </c>
       <c r="P45" t="n">
-        <v>216.2166</v>
+        <v>217.2328</v>
       </c>
       <c r="Q45" t="n">
-        <v>186.5941</v>
+        <v>185.8681</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -6339,54 +7185,86 @@
         </is>
       </c>
       <c r="T45" t="n">
-        <v>219.3528</v>
+        <v>234.7347</v>
       </c>
       <c r="U45" t="n">
-        <v>181.9095</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W45" t="n">
-        <v>77.62</v>
-      </c>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
+        <v>219.0224</v>
+      </c>
+      <c r="V45" t="n">
+        <v>180.7661</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y45" t="n">
+        <v>76.81</v>
+      </c>
       <c r="Z45" t="n">
-        <v>216.2166</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>205.4058</v>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr">
+        <v>244.1101</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>244.1101</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>228.7645</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>279.68</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>297.4649</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>288.0745</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 279.68; TP2: Extension at 297.46; TP3: Extension at 288.07</t>
+        </is>
+      </c>
+      <c r="AI45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>18.01</v>
+      </c>
+      <c r="AO45" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, RSI overbought (77.6); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.8); entry: enhanced entry at VWMA (overbought (RSI: 76.8))</t>
         </is>
       </c>
     </row>
@@ -6443,10 +7321,10 @@
         <v>6.56</v>
       </c>
       <c r="P46" t="n">
-        <v>6.8496</v>
+        <v>6.833</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.3976</v>
+        <v>6.3811</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -6459,54 +7337,86 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>7.1264</v>
+        <v>7.7984</v>
       </c>
       <c r="U46" t="n">
-        <v>6.3148</v>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W46" t="n">
-        <v>63.07</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
-      <c r="Y46" t="inlineStr"/>
+        <v>7.1216</v>
+      </c>
+      <c r="V46" t="n">
+        <v>6.2865</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y46" t="n">
+        <v>62.87</v>
+      </c>
       <c r="Z46" t="n">
-        <v>6.8496</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>6.5071</v>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>7.7199</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>7.7199</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.092700000000001</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>9.7791</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>9.416700000000001</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 9.09; TP2: Extension at 9.78; TP3: Extension at 9.42</t>
+        </is>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.9))</t>
         </is>
       </c>
     </row>
@@ -6563,66 +7473,102 @@
         <v>1.57</v>
       </c>
       <c r="P47" t="n">
-        <v>1.2902</v>
+        <v>1.2914</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.4737</v>
+        <v>1.1768</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T47" t="n">
-        <v>1.3249</v>
+        <v>1.3947</v>
       </c>
       <c r="U47" t="n">
-        <v>1.4965</v>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W47" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>no stop loss (no entry)</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>undervalued, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+        <v>1.3229</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y47" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.4204</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.4204</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.5067</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.5748</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.6338</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 1.51; TP2: Bollinger Upper Band at 1.57; TP3: Extension at 1.63</t>
+        </is>
+      </c>
+      <c r="AI47" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.7))</t>
         </is>
       </c>
     </row>
@@ -6679,10 +7625,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5334</v>
+        <v>0.5344</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.4219</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -6695,54 +7641,86 @@
         </is>
       </c>
       <c r="T48" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.7326</v>
       </c>
       <c r="U48" t="n">
-        <v>0.5225</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W48" t="n">
-        <v>71.93000000000001</v>
-      </c>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr"/>
+        <v>0.5926</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y48" t="n">
+        <v>71.81999999999999</v>
+      </c>
       <c r="Z48" t="n">
-        <v>0.5334</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0.5068</v>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr">
+        <v>0.7138</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>0.7138</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>stop at Swing Support</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.0109</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.1595</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 1.01; TP2: Extension at 1.16; TP3: Extension at 1.08</t>
+        </is>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>62.45</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>51.45</v>
+      </c>
+      <c r="AO48" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed, RSI overbought (71.9); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.8); entry: enhanced entry at VWMA (overbought (RSI: 71.8))</t>
         </is>
       </c>
     </row>
@@ -6799,10 +7777,10 @@
         <v>0.53</v>
       </c>
       <c r="P49" t="n">
-        <v>0.4425</v>
+        <v>0.4435</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4662</v>
+        <v>0.4651</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -6815,50 +7793,64 @@
         </is>
       </c>
       <c r="T49" t="n">
-        <v>0.4595</v>
+        <v>0.4879</v>
       </c>
       <c r="U49" t="n">
-        <v>0.4412</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W49" t="n">
-        <v>61.08</v>
-      </c>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr">
+        <v>0.4604</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y49" t="n">
+        <v>60.96</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.5144</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr">
         <is>
           <t>no stop loss (no entry)</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr">
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr">
         <is>
           <t>no take profit levels (insufficient TA data)</t>
         </is>
       </c>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
       <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr">
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr">
         <is>
           <t>Avoid</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: confirmed downtrend (Death Cross); no technical entry recommended</t>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
     </row>
@@ -6915,10 +7907,10 @@
         <v>512</v>
       </c>
       <c r="P50" t="n">
-        <v>392.8994</v>
+        <v>393.5748</v>
       </c>
       <c r="Q50" t="n">
-        <v>301.337</v>
+        <v>298.9647</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -6931,54 +7923,86 @@
         </is>
       </c>
       <c r="T50" t="n">
-        <v>401.3569</v>
+        <v>442.6711</v>
       </c>
       <c r="U50" t="n">
-        <v>310.5535</v>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W50" t="n">
-        <v>67.28</v>
-      </c>
-      <c r="X50" t="inlineStr"/>
-      <c r="Y50" t="inlineStr"/>
+        <v>400.6695</v>
+      </c>
+      <c r="V50" t="n">
+        <v>308.3784</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y50" t="n">
+        <v>68.23</v>
+      </c>
       <c r="Z50" t="n">
-        <v>392.8994</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>373.2544</v>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>456.6532</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>456.6532</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>436.5087</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>480.12</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>503.7643</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>568</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>TP1: Classic R2 at 480.12; TP2: Bollinger Upper Band at 503.76; TP3: Classic R3 at 568</t>
+        </is>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.2))</t>
         </is>
       </c>
     </row>
@@ -7035,10 +8059,10 @@
         <v>1239</v>
       </c>
       <c r="P51" t="n">
-        <v>1155.3762</v>
+        <v>1160.9628</v>
       </c>
       <c r="Q51" t="n">
-        <v>913.357</v>
+        <v>905.4366</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -7051,54 +8075,86 @@
         </is>
       </c>
       <c r="T51" t="n">
-        <v>1142.8082</v>
+        <v>1201.8052</v>
       </c>
       <c r="U51" t="n">
-        <v>925.4806</v>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W51" t="n">
-        <v>57.58</v>
-      </c>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr"/>
+        <v>1140.0868</v>
+      </c>
+      <c r="V51" t="n">
+        <v>917.8674</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y51" t="n">
+        <v>59.33</v>
+      </c>
       <c r="Z51" t="n">
-        <v>1155.3762</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1097.6074</v>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>1207.6791</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB51" t="n">
+        <v>1208.95</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1173.2802</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AE51" t="n">
+        <v>1223.3267</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1248.0458</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1324.3267</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>TP1: Classic R2 at 1223.33; TP2: Bollinger Upper Band at 1248.05; TP3: Classic R3 at 1324.33</t>
+        </is>
+      </c>
+      <c r="AI51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 59.3))</t>
         </is>
       </c>
     </row>
@@ -7155,10 +8211,10 @@
         <v>245</v>
       </c>
       <c r="P52" t="n">
-        <v>255.509</v>
+        <v>255.449</v>
       </c>
       <c r="Q52" t="n">
-        <v>247.1768</v>
+        <v>244.2572</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -7171,54 +8227,86 @@
         </is>
       </c>
       <c r="T52" t="n">
-        <v>250.8222</v>
+        <v>244.9669</v>
       </c>
       <c r="U52" t="n">
-        <v>235.2446</v>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W52" t="n">
-        <v>43.87</v>
-      </c>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
+        <v>250.9607</v>
+      </c>
+      <c r="V52" t="n">
+        <v>233.9408</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y52" t="n">
+        <v>46.08</v>
+      </c>
       <c r="Z52" t="n">
-        <v>242</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>229.9</v>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr">
+        <v>243.2553</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>236.29</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>233.5066</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE52" t="n">
+        <v>244.2572</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>250.1703</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>260.212</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>TP1: 200 SMA at 244.26; TP2: Bollinger Upper Band at 250.17; TP3: 100 SMA at 260.21</t>
+        </is>
+      </c>
+      <c r="AI52" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="AO52" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: pullback entry at swing‑low support in a confirmed uptrend</t>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 46.1))</t>
         </is>
       </c>
     </row>
@@ -7275,10 +8363,10 @@
         <v>197.49</v>
       </c>
       <c r="P53" t="n">
-        <v>143.273</v>
+        <v>143.6372</v>
       </c>
       <c r="Q53" t="n">
-        <v>122.8783</v>
+        <v>121.9894</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -7291,54 +8379,86 @@
         </is>
       </c>
       <c r="T53" t="n">
-        <v>145.5481</v>
+        <v>160.8445</v>
       </c>
       <c r="U53" t="n">
-        <v>119.2906</v>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W53" t="n">
-        <v>67.79000000000001</v>
-      </c>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
+        <v>145.1147</v>
+      </c>
+      <c r="V53" t="n">
+        <v>118.4574</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y53" t="n">
+        <v>67.83</v>
+      </c>
       <c r="Z53" t="n">
-        <v>143.273</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>136.1093</v>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>170.2966</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>170.2966</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>161.957</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE53" t="n">
+        <v>199.318</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>213.8287</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>206.1671</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 199.32; TP2: Extension at 213.83; TP3: Extension at 206.17</t>
+        </is>
+      </c>
+      <c r="AI53" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.8))</t>
         </is>
       </c>
     </row>
@@ -7393,10 +8513,10 @@
         <v>6.69</v>
       </c>
       <c r="P54" t="n">
-        <v>6.5684</v>
+        <v>6.5954</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.8431</v>
+        <v>5.8196</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -7409,54 +8529,86 @@
         </is>
       </c>
       <c r="T54" t="n">
-        <v>6.7267</v>
+        <v>7.2134</v>
       </c>
       <c r="U54" t="n">
-        <v>5.8408</v>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W54" t="n">
-        <v>52.68</v>
-      </c>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
+        <v>6.7233</v>
+      </c>
+      <c r="V54" t="n">
+        <v>5.7611</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y54" t="n">
+        <v>52.63</v>
+      </c>
       <c r="Z54" t="n">
-        <v>6.5684</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>undervalued, Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>7.2537</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>6.495</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>7.932</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>TP1: Classic R2 at 7.22; TP2: Bollinger Upper Band at 7.93; TP3: Classic R3 at 8.09</t>
+        </is>
+      </c>
+      <c r="AI54" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.6))</t>
         </is>
       </c>
     </row>
@@ -7513,10 +8665,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="P55" t="n">
-        <v>9.239800000000001</v>
+        <v>9.252599999999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.19</v>
+        <v>6.0707</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -7529,54 +8681,86 @@
         </is>
       </c>
       <c r="T55" t="n">
-        <v>9.2349</v>
+        <v>10.0824</v>
       </c>
       <c r="U55" t="n">
-        <v>6.7256</v>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W55" t="n">
-        <v>69.51000000000001</v>
-      </c>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
+        <v>9.1845</v>
+      </c>
+      <c r="V55" t="n">
+        <v>6.6227</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y55" t="n">
+        <v>69.61</v>
+      </c>
       <c r="Z55" t="n">
-        <v>9.239800000000001</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>8.777799999999999</v>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>10.0523</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>10.0523</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>10.0353</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE55" t="n">
+        <v>11.7159</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>12.5477</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>12.1085</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 11.72; TP2: Extension at 12.55; TP3: Extension at 12.11</t>
+        </is>
+      </c>
+      <c r="AI55" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>146.74</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>120.91</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>24.82</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.6))</t>
         </is>
       </c>
     </row>
@@ -7627,14 +8811,14 @@
         <v>5.56</v>
       </c>
       <c r="P56" t="n">
-        <v>5.51</v>
+        <v>5.4146</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.51</v>
+        <v>5.2911</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -7643,50 +8827,86 @@
         </is>
       </c>
       <c r="T56" t="n">
-        <v>5.51</v>
+        <v>5.551</v>
       </c>
       <c r="U56" t="n">
-        <v>5.5037</v>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W56" t="n">
-        <v>100</v>
-      </c>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>no stop loss (no entry)</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>undervalued, trend undetermined; entry: trend undetermined (insufficient 200‑period history)</t>
+        <v>5.4683</v>
+      </c>
+      <c r="V56" t="n">
+        <v>5.3241</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y56" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>5.766</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>5.4146</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>5.3534</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>stop at Bollinger Lower Band</t>
+        </is>
+      </c>
+      <c r="AE56" t="n">
+        <v>5.5624</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>5.5742</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>5.5767</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 5.56; TP2: Fibonacci R2 at 5.57; TP3: Classic R1 at 5.58</t>
+        </is>
+      </c>
+      <c r="AI56" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (neutral (RSI: 48.3))</t>
         </is>
       </c>
     </row>
@@ -7743,10 +8963,10 @@
         <v>252.69</v>
       </c>
       <c r="P57" t="n">
-        <v>235.7932</v>
+        <v>235.8538</v>
       </c>
       <c r="Q57" t="n">
-        <v>183.9306</v>
+        <v>182.7898</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -7759,54 +8979,86 @@
         </is>
       </c>
       <c r="T57" t="n">
-        <v>239.0054</v>
+        <v>263.8467</v>
       </c>
       <c r="U57" t="n">
-        <v>185.2179</v>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W57" t="n">
-        <v>75.28</v>
-      </c>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
+        <v>238.1021</v>
+      </c>
+      <c r="V57" t="n">
+        <v>183.2799</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y57" t="n">
+        <v>74.61</v>
+      </c>
       <c r="Z57" t="n">
-        <v>235.7932</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>224.0035</v>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr">
+        <v>262.4663</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>262.4663</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>252.8158</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE57" t="n">
+        <v>300.5617</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>336.1233</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>364.2603</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 300.56; TP2: Classic R3 at 336.12; TP3: Extension at 364.26</t>
+        </is>
+      </c>
+      <c r="AI57" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>38.78</v>
+      </c>
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>Golden Cross confirmed, RSI overbought (75.3); entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.6); entry: enhanced entry at VWMA (overbought (RSI: 74.6))</t>
         </is>
       </c>
     </row>
@@ -7863,10 +9115,10 @@
         <v>18</v>
       </c>
       <c r="P58" t="n">
-        <v>15.8808</v>
+        <v>15.9354</v>
       </c>
       <c r="Q58" t="n">
-        <v>15.6628</v>
+        <v>15.5829</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -7879,54 +9131,86 @@
         </is>
       </c>
       <c r="T58" t="n">
-        <v>15.9126</v>
+        <v>16.1568</v>
       </c>
       <c r="U58" t="n">
-        <v>14.9781</v>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W58" t="n">
-        <v>69.63</v>
-      </c>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
+        <v>15.9116</v>
+      </c>
+      <c r="V58" t="n">
+        <v>14.9443</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y58" t="n">
+        <v>69.11</v>
+      </c>
       <c r="Z58" t="n">
-        <v>15.8808</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>15.0868</v>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>stop at 5% below entry (default)</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>no take profit levels (insufficient TA data)</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Hold</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: pullback entry at the rising 50 SMA in a confirmed uptrend</t>
+        <v>16.7411</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-01 11:26:12</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AE58" t="n">
+        <v>18.1733</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>18.545</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>18.3488</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 18.17; TP2: Extension at 18.55; TP3: Extension at 18.35</t>
+        </is>
+      </c>
+      <c r="AI58" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 69.1))</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB11" t="n">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB30" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB33" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:04</t>
+          <t>2026-08-01 16:05:18</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB56" t="n">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB57" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-01 11:26:12</t>
+          <t>2026-08-01 16:05:27</t>
         </is>
       </c>
       <c r="AB58" t="n">

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -672,10 +672,10 @@
         <v>7877205</v>
       </c>
       <c r="I2" t="n">
-        <v>44465398</v>
+        <v>27786983</v>
       </c>
       <c r="J2" t="n">
-        <v>5.645</v>
+        <v>3.528</v>
       </c>
       <c r="K2" t="n">
         <v>3221256</v>
@@ -693,10 +693,10 @@
         <v>9.15</v>
       </c>
       <c r="P2" t="n">
-        <v>8.142200000000001</v>
+        <v>8.1632</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.6183</v>
+        <v>7.6284</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>8.236700000000001</v>
+        <v>8.364599999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>8.148</v>
+        <v>8.2042</v>
       </c>
       <c r="V2" t="n">
-        <v>7.8589</v>
+        <v>7.8761</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -728,18 +728,18 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>70.42</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>8.3286</v>
+        <v>8.5009</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>8.3286</v>
+        <v>8.595000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>8.24</v>
@@ -750,36 +750,36 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>9.09</v>
+        <v>9.049799999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.26</v>
+        <v>9.064299999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.9978</v>
+        <v>9.3924</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 9.09; TP2: Classic R3 at 10.26; TP3: Extension at 11.0</t>
+          <t>TP1: Bollinger Upper Band at 9.05; TP2: Fibonacci R1 at 9.06; TP3: Fibonacci R2 at 9.39</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>8.59</v>
+        <v>1.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21.79</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>30.12</v>
+        <v>2.25</v>
       </c>
       <c r="AL2" t="n">
-        <v>9.140000000000001</v>
+        <v>5.29</v>
       </c>
       <c r="AM2" t="n">
-        <v>23.19</v>
+        <v>5.46</v>
       </c>
       <c r="AN2" t="n">
-        <v>32.05</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.4); entry: enhanced entry at VWMA (overbought (RSI: 70.4))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.6))</t>
         </is>
       </c>
     </row>
@@ -824,10 +824,10 @@
         <v>714703</v>
       </c>
       <c r="I3" t="n">
-        <v>578784</v>
+        <v>315322</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="K3" t="n">
         <v>216885</v>
@@ -845,10 +845,10 @@
         <v>56.7</v>
       </c>
       <c r="P3" t="n">
-        <v>56.1242</v>
+        <v>56.0988</v>
       </c>
       <c r="Q3" t="n">
-        <v>51.1871</v>
+        <v>51.2767</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="T3" t="n">
-        <v>56.1556</v>
+        <v>56.1817</v>
       </c>
       <c r="U3" t="n">
-        <v>55.5855</v>
+        <v>55.6186</v>
       </c>
       <c r="V3" t="n">
-        <v>49.7698</v>
+        <v>49.8361</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>50.33</v>
+        <v>52.39</v>
       </c>
       <c r="Z3" t="n">
-        <v>56.3002</v>
+        <v>56.327</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>55.75</v>
+        <v>56.0988</v>
       </c>
       <c r="AC3" t="n">
-        <v>55.2826</v>
+        <v>55.4</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -902,36 +902,36 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>57.6009</v>
+        <v>57.6413</v>
       </c>
       <c r="AF3" t="n">
-        <v>58.9186</v>
+        <v>57.9093</v>
       </c>
       <c r="AG3" t="n">
-        <v>59.26</v>
+        <v>58.3333</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 57.6; TP2: Fibonacci R1 at 58.92; TP3: Classic R1 at 59.26</t>
+          <t>TP1: Bollinger Upper Band at 57.64; TP2: Fibonacci R1 at 57.91; TP3: Classic R1 at 58.33</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>3.96</v>
+        <v>2.21</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6.78</v>
+        <v>2.59</v>
       </c>
       <c r="AK3" t="n">
-        <v>7.51</v>
+        <v>3.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.32</v>
+        <v>2.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.68</v>
+        <v>3.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.3</v>
+        <v>3.98</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 52.4))</t>
         </is>
       </c>
     </row>
@@ -976,10 +976,10 @@
         <v>1535296</v>
       </c>
       <c r="I4" t="n">
-        <v>1474237</v>
+        <v>1062269</v>
       </c>
       <c r="J4" t="n">
-        <v>0.96</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>1063344</v>
@@ -997,10 +997,10 @@
         <v>28.96</v>
       </c>
       <c r="P4" t="n">
-        <v>28.0156</v>
+        <v>27.9998</v>
       </c>
       <c r="Q4" t="n">
-        <v>26.8432</v>
+        <v>26.88</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="T4" t="n">
-        <v>27.6933</v>
+        <v>27.6626</v>
       </c>
       <c r="U4" t="n">
-        <v>27.9294</v>
+        <v>27.9075</v>
       </c>
       <c r="V4" t="n">
-        <v>25.9092</v>
+        <v>25.9237</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>43</v>
+        <v>44.87</v>
       </c>
       <c r="Z4" t="n">
-        <v>27.7959</v>
+        <v>27.7909</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>26.9043</v>
+        <v>26.9091</v>
       </c>
       <c r="AC4" t="n">
-        <v>26.8432</v>
+        <v>26.88</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1054,36 +1054,36 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>27.9887</v>
+        <v>27.9824</v>
       </c>
       <c r="AF4" t="n">
-        <v>28.8767</v>
+        <v>28.521</v>
       </c>
       <c r="AG4" t="n">
-        <v>28.8898</v>
+        <v>28.6067</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 27.99; TP2: Bollinger Upper Band at 28.88; TP3: Fibonacci R1 at 28.89</t>
+          <t>TP1: 100 SMA at 27.98; TP2: Fibonacci R1 at 28.52; TP3: Classic R1 at 28.61</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>17.73</v>
+        <v>36.93</v>
       </c>
       <c r="AJ4" t="n">
-        <v>32.26</v>
+        <v>55.46</v>
       </c>
       <c r="AK4" t="n">
-        <v>32.47</v>
+        <v>58.41</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="AM4" t="n">
-        <v>7.33</v>
+        <v>5.99</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.38</v>
+        <v>6.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.0))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.9))</t>
         </is>
       </c>
     </row>
@@ -1128,10 +1128,10 @@
         <v>3187957</v>
       </c>
       <c r="I5" t="n">
-        <v>2344381</v>
+        <v>2901186</v>
       </c>
       <c r="J5" t="n">
-        <v>0.735</v>
+        <v>0.91</v>
       </c>
       <c r="K5" t="n">
         <v>1152876</v>
@@ -1149,10 +1149,10 @@
         <v>22.78</v>
       </c>
       <c r="P5" t="n">
-        <v>21.8262</v>
+        <v>21.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>19.2476</v>
+        <v>19.2971</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="T5" t="n">
-        <v>22.4043</v>
+        <v>22.4372</v>
       </c>
       <c r="U5" t="n">
-        <v>21.8449</v>
+        <v>21.8804</v>
       </c>
       <c r="V5" t="n">
-        <v>19.4131</v>
+        <v>19.4463</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1184,14 +1184,14 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>54.24</v>
+        <v>55.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.7323</v>
+        <v>22.7874</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1206,36 +1206,36 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>22.7414</v>
+        <v>23.6529</v>
       </c>
       <c r="AF5" t="n">
-        <v>23.8033</v>
+        <v>23.7306</v>
       </c>
       <c r="AG5" t="n">
-        <v>23.807</v>
+        <v>24.3367</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 22.74; TP2: Classic R2 at 23.8; TP3: Bollinger Upper Band at 23.81</t>
+          <t>TP1: Bollinger Upper Band at 23.65; TP2: Fibonacci R1 at 23.73; TP3: Classic R1 at 24.34</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>5.7</v>
+        <v>12.71</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13.87</v>
+        <v>13.31</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.9</v>
+        <v>17.97</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.37</v>
+        <v>7.51</v>
       </c>
       <c r="AM5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.87</v>
       </c>
       <c r="AN5" t="n">
-        <v>8.210000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.2))</t>
         </is>
       </c>
     </row>
@@ -1280,10 +1280,10 @@
         <v>306304</v>
       </c>
       <c r="I6" t="n">
-        <v>88537</v>
+        <v>96256</v>
       </c>
       <c r="J6" t="n">
-        <v>0.289</v>
+        <v>0.314</v>
       </c>
       <c r="K6" t="n">
         <v>54499</v>
@@ -1301,10 +1301,10 @@
         <v>302.7</v>
       </c>
       <c r="P6" t="n">
-        <v>305.7806</v>
+        <v>305.026</v>
       </c>
       <c r="Q6" t="n">
-        <v>256.9986</v>
+        <v>257.7349</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="T6" t="n">
-        <v>298.6042</v>
+        <v>298.7628</v>
       </c>
       <c r="U6" t="n">
-        <v>299.3498</v>
+        <v>299.3859</v>
       </c>
       <c r="V6" t="n">
-        <v>261.8413</v>
+        <v>262.2237</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1336,58 +1336,58 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>46.47</v>
+        <v>51.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>299.6988</v>
+        <v>300.2409</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>287.64</v>
+        <v>294.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>274.1058</v>
+        <v>289.9403</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>298.7249</v>
+        <v>299.4776</v>
       </c>
       <c r="AF6" t="n">
-        <v>308.234</v>
+        <v>307.3727</v>
       </c>
       <c r="AG6" t="n">
-        <v>321.9475</v>
+        <v>308.3187</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 298.72; TP2: Bollinger Upper Band at 308.23; TP3: Fibonacci R1 at 321.95</t>
+          <t>TP1: 100 SMA at 299.48; TP2: Bollinger Upper Band at 307.37; TP3: Fibonacci R1 at 308.32</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.53</v>
+        <v>3.03</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.85</v>
+        <v>1.69</v>
       </c>
       <c r="AM6" t="n">
-        <v>7.16</v>
+        <v>4.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>11.93</v>
+        <v>4.69</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.5))</t>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (overbought (RSI: 51.4))</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         <v>5963583</v>
       </c>
       <c r="I7" t="n">
-        <v>3182475</v>
+        <v>6520568</v>
       </c>
       <c r="J7" t="n">
-        <v>0.534</v>
+        <v>1.093</v>
       </c>
       <c r="K7" t="n">
         <v>3319555</v>
@@ -1453,10 +1453,10 @@
         <v>11.37</v>
       </c>
       <c r="P7" t="n">
-        <v>11.7704</v>
+        <v>11.7666</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.2998</v>
+        <v>11.3018</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="T7" t="n">
-        <v>11.5838</v>
+        <v>11.6006</v>
       </c>
       <c r="U7" t="n">
-        <v>11.5956</v>
+        <v>11.602</v>
       </c>
       <c r="V7" t="n">
-        <v>11.0178</v>
+        <v>11.0252</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1488,21 +1488,21 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>42.19</v>
+        <v>53.94</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.5447</v>
+        <v>11.5593</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>11.3</v>
+        <v>11.3164</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.2998</v>
+        <v>11.3018</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1510,36 +1510,36 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>11.7464</v>
+        <v>11.7359</v>
       </c>
       <c r="AF7" t="n">
-        <v>12.4583</v>
+        <v>11.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.54</v>
+        <v>11.7746</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 11.75; TP2: Fibonacci R1 at 12.46; TP3: Classic R1 at 12.54</t>
+          <t>TP1: Fibonacci R1 at 11.74; TP2: Classic R1 at 11.76; TP3: Bollinger Upper Band at 11.77</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>2972.22</v>
+        <v>28.79</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7712.19</v>
+        <v>30.44</v>
       </c>
       <c r="AK7" t="n">
-        <v>8256.17</v>
+        <v>31.44</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.95</v>
+        <v>3.71</v>
       </c>
       <c r="AM7" t="n">
-        <v>10.25</v>
+        <v>3.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>10.97</v>
+        <v>4.05</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 42.2))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 53.9))</t>
         </is>
       </c>
     </row>
@@ -1584,10 +1584,10 @@
         <v>1257994</v>
       </c>
       <c r="I8" t="n">
-        <v>718576</v>
+        <v>615921</v>
       </c>
       <c r="J8" t="n">
-        <v>0.571</v>
+        <v>0.49</v>
       </c>
       <c r="K8" t="n">
         <v>514514</v>
@@ -1605,10 +1605,10 @@
         <v>29.95</v>
       </c>
       <c r="P8" t="n">
-        <v>29.6804</v>
+        <v>29.6712</v>
       </c>
       <c r="Q8" t="n">
-        <v>26.9828</v>
+        <v>27.015</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>29.4753</v>
+        <v>29.4529</v>
       </c>
       <c r="U8" t="n">
-        <v>29.418</v>
+        <v>29.411</v>
       </c>
       <c r="V8" t="n">
-        <v>27.3193</v>
+        <v>27.3384</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>39.7</v>
+        <v>46.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>29.5599</v>
+        <v>29.546</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>28.4284</v>
+        <v>28.3793</v>
       </c>
       <c r="AC8" t="n">
-        <v>28.0358</v>
+        <v>27.9949</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1662,36 +1662,36 @@
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>31.5052</v>
+        <v>30.8533</v>
       </c>
       <c r="AF8" t="n">
-        <v>31.6449</v>
+        <v>30.954</v>
       </c>
       <c r="AG8" t="n">
-        <v>31.9833</v>
+        <v>31.4951</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 31.51; TP2: Fibonacci R1 at 31.64; TP3: Classic R1 at 31.98</t>
+          <t>TP1: Classic R1 at 30.85; TP2: Fibonacci R1 at 30.95; TP3: Bollinger Upper Band at 31.5</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>7.84</v>
+        <v>6.44</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8.19</v>
+        <v>6.7</v>
       </c>
       <c r="AK8" t="n">
-        <v>9.050000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AL8" t="n">
-        <v>10.82</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>11.31</v>
+        <v>9.07</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.5</v>
+        <v>10.98</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 39.7))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.7))</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>190685</v>
       </c>
       <c r="I9" t="n">
-        <v>86436</v>
+        <v>75454</v>
       </c>
       <c r="J9" t="n">
-        <v>0.453</v>
+        <v>0.396</v>
       </c>
       <c r="K9" t="n">
         <v>35126</v>
@@ -1757,10 +1757,10 @@
         <v>185.7</v>
       </c>
       <c r="P9" t="n">
-        <v>182.9374</v>
+        <v>182.7628</v>
       </c>
       <c r="Q9" t="n">
-        <v>160.317</v>
+        <v>160.8832</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>182.4461</v>
+        <v>182.6731</v>
       </c>
       <c r="U9" t="n">
-        <v>182.1341</v>
+        <v>182.2398</v>
       </c>
       <c r="V9" t="n">
-        <v>156.8251</v>
+        <v>157.1037</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1792,14 +1792,14 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>50.57</v>
+        <v>53.93</v>
       </c>
       <c r="Z9" t="n">
-        <v>182.6138</v>
+        <v>183.1928</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1814,36 +1814,36 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>184.6849</v>
+        <v>184.5034</v>
       </c>
       <c r="AF9" t="n">
-        <v>191.54</v>
+        <v>192.0267</v>
       </c>
       <c r="AG9" t="n">
-        <v>191.8359</v>
+        <v>192.6719</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 184.68; TP2: Classic R1 at 191.54; TP3: Fibonacci R1 at 191.84</t>
+          <t>TP1: 100 SMA at 184.5; TP2: Fibonacci R1 at 192.03; TP3: Bollinger Upper Band at 192.67</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.92</v>
+        <v>6.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.09</v>
+        <v>6.55</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.9))</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>193879</v>
+        <v>98211</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>724.5394</v>
+        <v>724.7194</v>
       </c>
       <c r="Q10" t="n">
-        <v>541.5338</v>
+        <v>542.9888</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>711.3390000000001</v>
+        <v>711.5924</v>
       </c>
       <c r="U10" t="n">
-        <v>696.5584</v>
+        <v>697.2424</v>
       </c>
       <c r="V10" t="n">
-        <v>563.7071</v>
+        <v>565.2025</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1930,14 +1930,14 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>50.42</v>
+        <v>51.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>702.4604</v>
+        <v>701.3951</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -1952,36 +1952,36 @@
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>541.5338</v>
+        <v>542.9888</v>
       </c>
       <c r="AF10" t="n">
-        <v>629.5273999999999</v>
+        <v>631.8499</v>
       </c>
       <c r="AG10" t="n">
-        <v>731.4788</v>
+        <v>728.4585</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 541.53; TP2: 100 SMA at 629.53; TP3: Bollinger Upper Band at 731.48</t>
+          <t>TP1: 200 SMA at 542.99; TP2: 100 SMA at 631.85; TP3: Bollinger Upper Band at 728.46</t>
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>132.44</v>
+        <v>132.85</v>
       </c>
       <c r="AJ10" t="n">
-        <v>157.21</v>
+        <v>157.86</v>
       </c>
       <c r="AK10" t="n">
-        <v>185.91</v>
+        <v>185.06</v>
       </c>
       <c r="AL10" t="n">
-        <v>662.1900000000001</v>
+        <v>664.23</v>
       </c>
       <c r="AM10" t="n">
-        <v>786.03</v>
+        <v>789.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>929.53</v>
+        <v>925.28</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         <v>1198269</v>
       </c>
       <c r="I11" t="n">
-        <v>1055301</v>
+        <v>1001409</v>
       </c>
       <c r="J11" t="n">
-        <v>0.881</v>
+        <v>0.836</v>
       </c>
       <c r="K11" t="n">
         <v>608115</v>
@@ -2047,29 +2047,29 @@
         <v>22.8</v>
       </c>
       <c r="P11" t="n">
-        <v>22.9378</v>
+        <v>22.9288</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.9377</v>
+        <v>22.9433</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T11" t="n">
-        <v>22.9107</v>
+        <v>22.9173</v>
       </c>
       <c r="U11" t="n">
-        <v>22.9162</v>
+        <v>22.9187</v>
       </c>
       <c r="V11" t="n">
-        <v>22.9066</v>
+        <v>22.9073</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -2082,67 +2082,45 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>43.4</v>
+        <v>51.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.9516</v>
+        <v>22.969</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>22.3727</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>21.9856</v>
-      </c>
+          <t>2026-08-02 12:02:53</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
-        </is>
-      </c>
-      <c r="AE11" t="n">
-        <v>22.8104</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>22.9377</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>23.3803</v>
-      </c>
+          <t>no stop loss (no entry)</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 22.81; TP2: 200 SMA at 22.94; TP3: Bollinger Upper Band at 23.38</t>
-        </is>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>4.5</v>
-      </c>
+          <t>no take profit levels (insufficient TA data)</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.4))</t>
+          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
     </row>
@@ -2178,10 +2156,10 @@
         <v>17325026</v>
       </c>
       <c r="I12" t="n">
-        <v>11673760</v>
+        <v>6124458</v>
       </c>
       <c r="J12" t="n">
-        <v>0.674</v>
+        <v>0.354</v>
       </c>
       <c r="K12" t="n">
         <v>7241829</v>
@@ -2199,10 +2177,10 @@
         <v>14.99</v>
       </c>
       <c r="P12" t="n">
-        <v>14.8526</v>
+        <v>14.8562</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.3365</v>
+        <v>10.3721</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2215,13 +2193,13 @@
         </is>
       </c>
       <c r="T12" t="n">
-        <v>14.7864</v>
+        <v>14.7572</v>
       </c>
       <c r="U12" t="n">
-        <v>14.2671</v>
+        <v>14.2754</v>
       </c>
       <c r="V12" t="n">
-        <v>11.175</v>
+        <v>11.2079</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -2234,21 +2212,21 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>44.65</v>
+        <v>44.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.8298</v>
+        <v>14.8343</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>14.43</v>
+        <v>14.4223</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.2677</v>
+        <v>14.3284</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2256,36 +2234,36 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>15.1485</v>
+        <v>15.1383</v>
       </c>
       <c r="AF12" t="n">
-        <v>15.9256</v>
+        <v>15.1467</v>
       </c>
       <c r="AG12" t="n">
-        <v>16.4377</v>
+        <v>15.1557</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 15.15; TP2: Fibonacci R1 at 15.93; TP3: Fibonacci R2 at 16.44</t>
+          <t>TP1: Fibonacci R1 at 15.14; TP2: Classic R1 at 15.15; TP3: Bollinger Upper Band at 15.16</t>
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>4.43</v>
+        <v>7.63</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.220000000000001</v>
+        <v>7.72</v>
       </c>
       <c r="AK12" t="n">
-        <v>12.37</v>
+        <v>7.81</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.98</v>
+        <v>4.96</v>
       </c>
       <c r="AM12" t="n">
-        <v>10.36</v>
+        <v>5.02</v>
       </c>
       <c r="AN12" t="n">
-        <v>13.91</v>
+        <v>5.09</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -2294,7 +2272,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (neutral (RSI: 44.7))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.3))</t>
         </is>
       </c>
     </row>
@@ -2330,10 +2308,10 @@
         <v>1021769</v>
       </c>
       <c r="I13" t="n">
-        <v>1511598</v>
+        <v>1454997</v>
       </c>
       <c r="J13" t="n">
-        <v>1.479</v>
+        <v>1.424</v>
       </c>
       <c r="K13" t="n">
         <v>352101</v>
@@ -2351,10 +2329,10 @@
         <v>112.98</v>
       </c>
       <c r="P13" t="n">
-        <v>96.42440000000001</v>
+        <v>96.7546</v>
       </c>
       <c r="Q13" t="n">
-        <v>79.50109999999999</v>
+        <v>79.8116</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2367,13 +2345,13 @@
         </is>
       </c>
       <c r="T13" t="n">
-        <v>100.4262</v>
+        <v>101.6342</v>
       </c>
       <c r="U13" t="n">
-        <v>96.9744</v>
+        <v>97.6071</v>
       </c>
       <c r="V13" t="n">
-        <v>81.1778</v>
+        <v>81.49550000000001</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -2386,21 +2364,21 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>62.41</v>
+        <v>75.83</v>
       </c>
       <c r="Z13" t="n">
-        <v>100.8252</v>
+        <v>101.8988</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>100.8252</v>
+        <v>101.8988</v>
       </c>
       <c r="AC13" t="n">
-        <v>99.0941</v>
+        <v>100.1628</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2408,36 +2386,36 @@
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>107.2343</v>
+        <v>107.311</v>
       </c>
       <c r="AF13" t="n">
-        <v>111.2</v>
+        <v>109.6165</v>
       </c>
       <c r="AG13" t="n">
-        <v>115.1632</v>
+        <v>110.3933</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 107.23; TP2: Classic R3 at 111.2; TP3: Extension at 115.16</t>
+          <t>TP1: Fibonacci R1 at 107.31; TP2: Bollinger Upper Band at 109.62; TP3: Classic R1 at 110.39</t>
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.99</v>
+        <v>4.45</v>
       </c>
       <c r="AK13" t="n">
-        <v>8.279999999999999</v>
+        <v>4.89</v>
       </c>
       <c r="AL13" t="n">
-        <v>6.36</v>
+        <v>5.31</v>
       </c>
       <c r="AM13" t="n">
-        <v>10.29</v>
+        <v>7.57</v>
       </c>
       <c r="AN13" t="n">
-        <v>14.22</v>
+        <v>8.34</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -2446,7 +2424,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.8); entry: enhanced entry at VWMA (overbought (RSI: 75.8))</t>
         </is>
       </c>
     </row>
@@ -2482,10 +2460,10 @@
         <v>12075718</v>
       </c>
       <c r="I14" t="n">
-        <v>8245937</v>
+        <v>40168665</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6830000000000001</v>
+        <v>3.326</v>
       </c>
       <c r="K14" t="n">
         <v>5009453</v>
@@ -2503,10 +2481,10 @@
         <v>5.38</v>
       </c>
       <c r="P14" t="n">
-        <v>5.0642</v>
+        <v>5.074</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.0365</v>
+        <v>4.048</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2519,13 +2497,13 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>5.0834</v>
+        <v>5.1307</v>
       </c>
       <c r="U14" t="n">
-        <v>4.9738</v>
+        <v>4.9976</v>
       </c>
       <c r="V14" t="n">
-        <v>4.2529</v>
+        <v>4.2661</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2538,18 +2516,18 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>64.26000000000001</v>
+        <v>74.34</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.1267</v>
+        <v>5.2443</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>5.1267</v>
+        <v>5.2443</v>
       </c>
       <c r="AC14" t="n">
         <v>5.04</v>
@@ -2560,36 +2538,36 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>5.2833</v>
+        <v>5.3481</v>
       </c>
       <c r="AF14" t="n">
-        <v>5.3989</v>
+        <v>5.3964</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.6167</v>
+        <v>5.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 5.28; TP2: Fibonacci R2 at 5.4; TP3: Classic R2 at 5.62</t>
+          <t>TP1: Fibonacci R1 at 5.35; TP2: Bollinger Upper Band at 5.4; TP3: Classic R1 at 5.45</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>1.81</v>
+        <v>0.51</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.14</v>
+        <v>0.74</v>
       </c>
       <c r="AK14" t="n">
-        <v>5.65</v>
+        <v>1.01</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.31</v>
+        <v>2.9</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.56</v>
+        <v>3.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -2598,7 +2576,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.3))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.3); entry: enhanced entry at VWMA (overbought (RSI: 74.3))</t>
         </is>
       </c>
     </row>
@@ -2634,10 +2612,10 @@
         <v>24343135</v>
       </c>
       <c r="I15" t="n">
-        <v>14864993</v>
+        <v>14509599</v>
       </c>
       <c r="J15" t="n">
-        <v>0.611</v>
+        <v>0.596</v>
       </c>
       <c r="K15" t="n">
         <v>15475726</v>
@@ -2655,10 +2633,10 @@
         <v>4.65</v>
       </c>
       <c r="P15" t="n">
-        <v>3.0124</v>
+        <v>3.0564</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1883</v>
+        <v>2.2066</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2671,13 +2649,13 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>3.81</v>
+        <v>3.91</v>
       </c>
       <c r="U15" t="n">
-        <v>3.1702</v>
+        <v>3.2365</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3112</v>
+        <v>2.3365</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2690,58 +2668,58 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>75.92</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5103</v>
+        <v>3.5646</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>4.336</v>
+        <v>4.4288</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>5.1555</v>
+        <v>4.8168</v>
       </c>
       <c r="AF15" t="n">
-        <v>5.5653</v>
+        <v>5.2673</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.3489</v>
+        <v>5.3832</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 5.16; TP2: Extension at 5.57; TP3: Extension at 5.35</t>
+          <t>TP1: Fibonacci R1 at 4.82; TP2: Bollinger Upper Band at 5.27; TP3: Fibonacci R2 at 5.38</t>
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>0.45</v>
+        <v>0.27</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>18.9</v>
+        <v>8.76</v>
       </c>
       <c r="AM15" t="n">
-        <v>28.35</v>
+        <v>18.93</v>
       </c>
       <c r="AN15" t="n">
-        <v>23.36</v>
+        <v>21.55</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -2750,7 +2728,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.9); entry: enhanced entry at Parabolic SAR (overbought (RSI: 75.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (80.0); entry: enhanced entry at Parabolic SAR (overbought (RSI: 80.0))</t>
         </is>
       </c>
     </row>
@@ -2786,10 +2764,10 @@
         <v>268716267</v>
       </c>
       <c r="I16" t="n">
-        <v>285915220</v>
+        <v>187237898</v>
       </c>
       <c r="J16" t="n">
-        <v>1.064</v>
+        <v>0.697</v>
       </c>
       <c r="K16" t="n">
         <v>153946169</v>
@@ -2807,10 +2785,10 @@
         <v>0.265</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2195</v>
+        <v>0.2201</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1792</v>
+        <v>0.1797</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2823,13 +2801,13 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>0.2369</v>
+        <v>0.2374</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2228</v>
+        <v>0.2236</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1917</v>
+        <v>0.1922</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2842,14 +2820,14 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>53.68</v>
+        <v>56.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.238</v>
+        <v>0.2384</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2864,36 +2842,36 @@
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>0.26</v>
+        <v>0.2589</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2732</v>
+        <v>0.267</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.2663</v>
+        <v>0.296</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 0.26; TP2: Extension at 0.27; TP3: Extension at 0.27</t>
+          <t>TP1: Fibonacci R1 at 0.26; TP2: Classic R1 at 0.27; TP3: Classic R2 at 0.3</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>17.67</v>
+        <v>16.93</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26.47</v>
+        <v>22.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>21.87</v>
+        <v>41.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>11.35</v>
+        <v>10.88</v>
       </c>
       <c r="AM16" t="n">
-        <v>17</v>
+        <v>14.35</v>
       </c>
       <c r="AN16" t="n">
-        <v>14.05</v>
+        <v>26.77</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -2902,7 +2880,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.7))</t>
+          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 56.3))</t>
         </is>
       </c>
     </row>
@@ -2938,10 +2916,10 @@
         <v>32349173</v>
       </c>
       <c r="I17" t="n">
-        <v>20767425</v>
+        <v>12201267</v>
       </c>
       <c r="J17" t="n">
-        <v>0.642</v>
+        <v>0.377</v>
       </c>
       <c r="K17" t="n">
         <v>11262912</v>
@@ -2959,10 +2937,10 @@
         <v>1.65</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6014</v>
+        <v>1.6052</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.4678</v>
+        <v>1.469</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2975,13 +2953,13 @@
         </is>
       </c>
       <c r="T17" t="n">
-        <v>1.6512</v>
+        <v>1.6549</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5952</v>
+        <v>1.5989</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5047</v>
+        <v>1.5065</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2994,58 +2972,58 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>45.34</v>
+        <v>57.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.6559</v>
+        <v>1.6597</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.6052</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.54</v>
+        <v>1.5701</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>1.6798</v>
+        <v>1.737</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7435</v>
+        <v>1.7469</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.752</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 1.68; TP2: Fibonacci R2 at 1.74; TP3: Bollinger Upper Band at 1.75</t>
+          <t>TP1: Fibonacci R1 at 1.74; TP2: Bollinger Upper Band at 1.75; TP3: Classic R1 at 1.76</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>12.95</v>
+        <v>3.76</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.3</v>
+        <v>4.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>20.15</v>
+        <v>4.41</v>
       </c>
       <c r="AL17" t="n">
-        <v>8.369999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AM17" t="n">
-        <v>12.48</v>
+        <v>8.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>13.03</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -3054,7 +3032,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 45.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 57.1))</t>
         </is>
       </c>
     </row>
@@ -3090,10 +3068,10 @@
         <v>1342299</v>
       </c>
       <c r="I18" t="n">
-        <v>444890</v>
+        <v>354392</v>
       </c>
       <c r="J18" t="n">
-        <v>0.331</v>
+        <v>0.264</v>
       </c>
       <c r="K18" t="n">
         <v>421515</v>
@@ -3111,10 +3089,10 @@
         <v>38.59</v>
       </c>
       <c r="P18" t="n">
-        <v>37.738</v>
+        <v>37.7608</v>
       </c>
       <c r="Q18" t="n">
-        <v>30.7229</v>
+        <v>30.8075</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3127,13 +3105,13 @@
         </is>
       </c>
       <c r="T18" t="n">
-        <v>38.4537</v>
+        <v>38.4028</v>
       </c>
       <c r="U18" t="n">
-        <v>37.4861</v>
+        <v>37.5031</v>
       </c>
       <c r="V18" t="n">
-        <v>31.3569</v>
+        <v>31.4222</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -3146,58 +3124,58 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>45.29</v>
+        <v>46.92</v>
       </c>
       <c r="Z18" t="n">
-        <v>39.1299</v>
+        <v>39.1837</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>35.4175</v>
+        <v>36.6681</v>
       </c>
       <c r="AC18" t="n">
-        <v>34.99</v>
+        <v>35.6633</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>40.0092</v>
+        <v>40.4079</v>
       </c>
       <c r="AF18" t="n">
-        <v>40.4019</v>
+        <v>40.4652</v>
       </c>
       <c r="AG18" t="n">
-        <v>40.4367</v>
+        <v>40.6333</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 40.01; TP2: Bollinger Upper Band at 40.4; TP3: Classic R1 at 40.44</t>
+          <t>TP1: Bollinger Upper Band at 40.41; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>10.74</v>
+        <v>3.72</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11.66</v>
+        <v>3.78</v>
       </c>
       <c r="AK18" t="n">
-        <v>11.74</v>
+        <v>3.95</v>
       </c>
       <c r="AL18" t="n">
-        <v>12.96</v>
+        <v>10.2</v>
       </c>
       <c r="AM18" t="n">
-        <v>14.07</v>
+        <v>10.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>14.17</v>
+        <v>10.81</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -3206,7 +3184,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 45.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.9))</t>
         </is>
       </c>
     </row>
@@ -3242,10 +3220,10 @@
         <v>1230298</v>
       </c>
       <c r="I19" t="n">
-        <v>431378</v>
+        <v>707434</v>
       </c>
       <c r="J19" t="n">
-        <v>0.351</v>
+        <v>0.575</v>
       </c>
       <c r="K19" t="n">
         <v>708724</v>
@@ -3263,10 +3241,10 @@
         <v>38.25</v>
       </c>
       <c r="P19" t="n">
-        <v>29.4694</v>
+        <v>29.739</v>
       </c>
       <c r="Q19" t="n">
-        <v>19.2682</v>
+        <v>19.3855</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3279,13 +3257,13 @@
         </is>
       </c>
       <c r="T19" t="n">
-        <v>34.6157</v>
+        <v>34.8237</v>
       </c>
       <c r="U19" t="n">
-        <v>30.3545</v>
+        <v>30.6073</v>
       </c>
       <c r="V19" t="n">
-        <v>21.1737</v>
+        <v>21.3292</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -3298,21 +3276,21 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>54.04</v>
+        <v>61.79</v>
       </c>
       <c r="Z19" t="n">
-        <v>35.6583</v>
+        <v>35.9118</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>33.5793</v>
+        <v>33.6727</v>
       </c>
       <c r="AC19" t="n">
-        <v>33.0916</v>
+        <v>33.5444</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3320,36 +3298,36 @@
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>34.8467</v>
+        <v>37.3616</v>
       </c>
       <c r="AF19" t="n">
-        <v>34.8853</v>
+        <v>37.8636</v>
       </c>
       <c r="AG19" t="n">
-        <v>37.9264</v>
+        <v>38.2267</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 34.85; TP2: Fibonacci R2 at 34.89; TP3: Bollinger Upper Band at 37.93</t>
+          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.86; TP3: Classic R1 at 38.23</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>2.6</v>
+        <v>28.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.68</v>
+        <v>32.66</v>
       </c>
       <c r="AK19" t="n">
-        <v>8.91</v>
+        <v>35.49</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.77</v>
+        <v>10.96</v>
       </c>
       <c r="AM19" t="n">
-        <v>3.89</v>
+        <v>12.45</v>
       </c>
       <c r="AN19" t="n">
-        <v>12.95</v>
+        <v>13.52</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -3358,7 +3336,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 54.0))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 61.8))</t>
         </is>
       </c>
     </row>
@@ -3394,10 +3372,10 @@
         <v>4425370</v>
       </c>
       <c r="I20" t="n">
-        <v>3092784</v>
+        <v>3042822</v>
       </c>
       <c r="J20" t="n">
-        <v>0.699</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>3053793</v>
@@ -3415,10 +3393,10 @@
         <v>11.04</v>
       </c>
       <c r="P20" t="n">
-        <v>9.8576</v>
+        <v>9.9122</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.8918</v>
+        <v>7.9108</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -3431,13 +3409,13 @@
         </is>
       </c>
       <c r="T20" t="n">
-        <v>10.6709</v>
+        <v>10.6689</v>
       </c>
       <c r="U20" t="n">
-        <v>9.979900000000001</v>
+        <v>10.0062</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1972</v>
+        <v>8.2216</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -3450,21 +3428,21 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>53.97</v>
+        <v>53.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.8525</v>
+        <v>10.8717</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>10.5646</v>
+        <v>10.5797</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6655</v>
+        <v>10.3209</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3472,36 +3450,36 @@
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>11.0774</v>
+        <v>11.0391</v>
       </c>
       <c r="AF20" t="n">
-        <v>11.6145</v>
+        <v>11.0693</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.35</v>
+        <v>11.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 11.08; TP2: Fibonacci R1 at 11.61; TP3: Classic R1 at 12.35</t>
+          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.07; TP3: Classic R1 at 11.15</t>
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>0.27</v>
+        <v>1.78</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.55</v>
+        <v>1.89</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="AL20" t="n">
-        <v>4.85</v>
+        <v>4.34</v>
       </c>
       <c r="AM20" t="n">
-        <v>9.94</v>
+        <v>4.63</v>
       </c>
       <c r="AN20" t="n">
-        <v>16.9</v>
+        <v>5.39</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -3510,7 +3488,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 54.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 53.1))</t>
         </is>
       </c>
     </row>
@@ -3546,10 +3524,10 @@
         <v>686404</v>
       </c>
       <c r="I21" t="n">
-        <v>1357439</v>
+        <v>1228294</v>
       </c>
       <c r="J21" t="n">
-        <v>1.978</v>
+        <v>1.789</v>
       </c>
       <c r="K21" t="n">
         <v>245844</v>
@@ -3567,10 +3545,10 @@
         <v>36.7</v>
       </c>
       <c r="P21" t="n">
-        <v>35.3746</v>
+        <v>35.2502</v>
       </c>
       <c r="Q21" t="n">
-        <v>32.3364</v>
+        <v>32.4106</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -3583,13 +3561,13 @@
         </is>
       </c>
       <c r="T21" t="n">
-        <v>34.9552</v>
+        <v>34.7043</v>
       </c>
       <c r="U21" t="n">
-        <v>35.4223</v>
+        <v>35.3007</v>
       </c>
       <c r="V21" t="n">
-        <v>31.4211</v>
+        <v>31.43</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -3602,21 +3580,21 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>34.85</v>
+        <v>34.54</v>
       </c>
       <c r="Z21" t="n">
-        <v>35.7764</v>
+        <v>35.6699</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB21" t="n">
         <v>31.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>30.4767</v>
+        <v>29.9767</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3624,36 +3602,36 @@
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>35.9121</v>
+        <v>32.4106</v>
       </c>
       <c r="AF21" t="n">
-        <v>36.0598</v>
+        <v>35.9053</v>
       </c>
       <c r="AG21" t="n">
-        <v>36.2267</v>
+        <v>37.0467</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 35.91; TP2: Fibonacci R1 at 36.06; TP3: Classic R1 at 36.23</t>
+          <t>TP1: 200 SMA at 32.41; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>4.31</v>
+        <v>0.6</v>
       </c>
       <c r="AJ21" t="n">
-        <v>4.46</v>
+        <v>2.89</v>
       </c>
       <c r="AK21" t="n">
-        <v>4.62</v>
+        <v>3.64</v>
       </c>
       <c r="AL21" t="n">
-        <v>14.01</v>
+        <v>2.89</v>
       </c>
       <c r="AM21" t="n">
-        <v>14.48</v>
+        <v>13.99</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.01</v>
+        <v>17.61</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -3662,7 +3640,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 34.8))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 34.5))</t>
         </is>
       </c>
     </row>
@@ -3698,10 +3676,10 @@
         <v>365646</v>
       </c>
       <c r="I22" t="n">
-        <v>920165</v>
+        <v>878556</v>
       </c>
       <c r="J22" t="n">
-        <v>2.517</v>
+        <v>2.403</v>
       </c>
       <c r="K22" t="n">
         <v>290852</v>
@@ -3719,10 +3697,10 @@
         <v>242</v>
       </c>
       <c r="P22" t="n">
-        <v>178.5166</v>
+        <v>179.6746</v>
       </c>
       <c r="Q22" t="n">
-        <v>123.574</v>
+        <v>124.3292</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -3735,13 +3713,13 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>206.132</v>
+        <v>208.6909</v>
       </c>
       <c r="U22" t="n">
-        <v>181.0852</v>
+        <v>183.1211</v>
       </c>
       <c r="V22" t="n">
-        <v>128.0531</v>
+        <v>129.0973</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -3754,21 +3732,21 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>69.81999999999999</v>
+        <v>73.56</v>
       </c>
       <c r="Z22" t="n">
-        <v>201.2921</v>
+        <v>205.5366</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>201.2921</v>
+        <v>205.5366</v>
       </c>
       <c r="AC22" t="n">
-        <v>158.382</v>
+        <v>180.2255</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3776,36 +3754,36 @@
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>250.7205</v>
+        <v>239.7945</v>
       </c>
       <c r="AF22" t="n">
-        <v>275.4347</v>
+        <v>254.2116</v>
       </c>
       <c r="AG22" t="n">
-        <v>262.3856</v>
+        <v>255.99</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 250.72; TP2: Extension at 275.43; TP3: Extension at 262.39</t>
+          <t>TP1: Fibonacci R1 at 239.79; TP2: Bollinger Upper Band at 254.21; TP3: Classic R1 at 255.99</t>
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="AL22" t="n">
-        <v>24.56</v>
+        <v>16.67</v>
       </c>
       <c r="AM22" t="n">
-        <v>36.83</v>
+        <v>23.68</v>
       </c>
       <c r="AN22" t="n">
-        <v>30.35</v>
+        <v>24.55</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -3814,7 +3792,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.8))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.6); entry: enhanced entry at VWMA (overbought (RSI: 73.6))</t>
         </is>
       </c>
     </row>
@@ -3850,10 +3828,10 @@
         <v>280675</v>
       </c>
       <c r="I23" t="n">
-        <v>270010</v>
+        <v>299430</v>
       </c>
       <c r="J23" t="n">
-        <v>0.962</v>
+        <v>1.067</v>
       </c>
       <c r="K23" t="n">
         <v>97939</v>
@@ -3871,10 +3849,10 @@
         <v>93</v>
       </c>
       <c r="P23" t="n">
-        <v>89.0424</v>
+        <v>89.164</v>
       </c>
       <c r="Q23" t="n">
-        <v>81.3045</v>
+        <v>81.41240000000001</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -3887,13 +3865,13 @@
         </is>
       </c>
       <c r="T23" t="n">
-        <v>91.8026</v>
+        <v>92.1528</v>
       </c>
       <c r="U23" t="n">
-        <v>89.121</v>
+        <v>89.3704</v>
       </c>
       <c r="V23" t="n">
-        <v>82.90989999999999</v>
+        <v>83.035</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3906,21 +3884,21 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>57.76</v>
+        <v>64.59</v>
       </c>
       <c r="Z23" t="n">
-        <v>92.26649999999999</v>
+        <v>92.5522</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>92.26649999999999</v>
+        <v>92.5522</v>
       </c>
       <c r="AC23" t="n">
-        <v>90.5284</v>
+        <v>91.2256</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3928,36 +3906,36 @@
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>94.7967</v>
+        <v>96.5592</v>
       </c>
       <c r="AF23" t="n">
-        <v>96.996</v>
+        <v>97.4401</v>
       </c>
       <c r="AG23" t="n">
-        <v>102.3867</v>
+        <v>98.33</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 94.8; TP2: Bollinger Upper Band at 97.0; TP3: Classic R3 at 102.39</t>
+          <t>TP1: Fibonacci R1 at 96.56; TP2: Bollinger Upper Band at 97.44; TP3: Classic R1 at 98.33</t>
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>1.46</v>
+        <v>3.02</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.72</v>
+        <v>3.68</v>
       </c>
       <c r="AK23" t="n">
-        <v>5.82</v>
+        <v>4.36</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.74</v>
+        <v>4.33</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.13</v>
+        <v>5.28</v>
       </c>
       <c r="AN23" t="n">
-        <v>10.97</v>
+        <v>6.24</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -3966,7 +3944,7 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.6))</t>
         </is>
       </c>
     </row>
@@ -4002,10 +3980,10 @@
         <v>397041</v>
       </c>
       <c r="I24" t="n">
-        <v>602042</v>
+        <v>516351</v>
       </c>
       <c r="J24" t="n">
-        <v>1.516</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
         <v>277385</v>
@@ -4023,10 +4001,10 @@
         <v>44.89</v>
       </c>
       <c r="P24" t="n">
-        <v>37.255</v>
+        <v>37.4058</v>
       </c>
       <c r="Q24" t="n">
-        <v>34.7312</v>
+        <v>34.7997</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -4039,13 +4017,13 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>40.9255</v>
+        <v>41.004</v>
       </c>
       <c r="U24" t="n">
-        <v>38.3029</v>
+        <v>38.4381</v>
       </c>
       <c r="V24" t="n">
-        <v>33.9859</v>
+        <v>34.0632</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -4058,58 +4036,58 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>55.5</v>
+        <v>57.53</v>
       </c>
       <c r="Z24" t="n">
-        <v>41.3738</v>
+        <v>41.454</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB24" t="n">
         <v>39.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>36.5519</v>
+        <v>37.5458</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>41.5133</v>
+        <v>44.1009</v>
       </c>
       <c r="AF24" t="n">
-        <v>45.3501</v>
+        <v>45.1364</v>
       </c>
       <c r="AG24" t="n">
-        <v>46.9933</v>
+        <v>45.3367</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 41.51; TP2: Bollinger Upper Band at 45.35; TP3: Classic R3 at 46.99</t>
+          <t>TP1: Fibonacci R1 at 44.1; TP2: Bollinger Upper Band at 45.14; TP3: Classic R1 at 45.34</t>
         </is>
       </c>
       <c r="AI24" t="n">
-        <v>0.74</v>
+        <v>2.54</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.09</v>
+        <v>3.09</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.36</v>
+        <v>11.93</v>
       </c>
       <c r="AM24" t="n">
-        <v>15.1</v>
+        <v>14.56</v>
       </c>
       <c r="AN24" t="n">
-        <v>19.27</v>
+        <v>15.07</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -4118,7 +4096,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 57.5))</t>
         </is>
       </c>
     </row>
@@ -4154,10 +4132,10 @@
         <v>3065911</v>
       </c>
       <c r="I25" t="n">
-        <v>3756109</v>
+        <v>1766269</v>
       </c>
       <c r="J25" t="n">
-        <v>1.225</v>
+        <v>0.576</v>
       </c>
       <c r="K25" t="n">
         <v>1360330</v>
@@ -4175,10 +4153,10 @@
         <v>12.3</v>
       </c>
       <c r="P25" t="n">
-        <v>10.4942</v>
+        <v>10.5612</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.111000000000001</v>
+        <v>8.1494</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -4191,13 +4169,13 @@
         </is>
       </c>
       <c r="T25" t="n">
-        <v>11.59</v>
+        <v>11.6948</v>
       </c>
       <c r="U25" t="n">
-        <v>10.7807</v>
+        <v>10.8556</v>
       </c>
       <c r="V25" t="n">
-        <v>8.3912</v>
+        <v>8.433999999999999</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -4210,58 +4188,58 @@
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>64.92</v>
+        <v>70.52</v>
       </c>
       <c r="Z25" t="n">
-        <v>11.6201</v>
+        <v>11.7044</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>11.695</v>
+        <v>11.7044</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.91</v>
+        <v>11.1606</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>12.3494</v>
+        <v>12.5325</v>
       </c>
       <c r="AF25" t="n">
-        <v>12.9025</v>
+        <v>12.8261</v>
       </c>
       <c r="AG25" t="n">
-        <v>13.4833</v>
+        <v>13.1767</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 12.35; TP2: Fibonacci R1 at 12.9; TP3: Classic R1 at 13.48</t>
+          <t>TP1: Bollinger Upper Band at 12.53; TP2: Fibonacci R1 at 12.83; TP3: Classic R1 at 13.18</t>
         </is>
       </c>
       <c r="AI25" t="n">
-        <v>0.83</v>
+        <v>1.52</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.28</v>
+        <v>2.71</v>
       </c>
       <c r="AL25" t="n">
-        <v>5.6</v>
+        <v>7.08</v>
       </c>
       <c r="AM25" t="n">
-        <v>10.32</v>
+        <v>9.58</v>
       </c>
       <c r="AN25" t="n">
-        <v>15.29</v>
+        <v>12.58</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -4270,7 +4248,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
         </is>
       </c>
     </row>
@@ -4306,10 +4284,10 @@
         <v>152954</v>
       </c>
       <c r="I26" t="n">
-        <v>1143733</v>
+        <v>1095102</v>
       </c>
       <c r="J26" t="n">
-        <v>7.478</v>
+        <v>7.16</v>
       </c>
       <c r="K26" t="n">
         <v>202414</v>
@@ -4327,10 +4305,10 @@
         <v>74.2</v>
       </c>
       <c r="P26" t="n">
-        <v>87.16840000000001</v>
+        <v>91.3626</v>
       </c>
       <c r="Q26" t="n">
-        <v>70.0688</v>
+        <v>71.197</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -4343,13 +4321,13 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>125.7031</v>
+        <v>141.1324</v>
       </c>
       <c r="U26" t="n">
-        <v>97.1628</v>
+        <v>104.6352</v>
       </c>
       <c r="V26" t="n">
-        <v>71.9948</v>
+        <v>74.1413</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -4362,37 +4340,59 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>90.90000000000001</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="Z26" t="n">
-        <v>149.3587</v>
+        <v>162.5638</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>153.255</v>
+        <v>177.23</v>
       </c>
       <c r="AC26" t="n">
-        <v>126.0564</v>
+        <v>146.523</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
           <t>stop at Parabolic SAR</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>248.0655</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>288.3412</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>296.6467</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 248.07; TP2: Fibonacci R2 at 288.34; TP3: Classic R1 at 296.65</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>67.38</v>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (90.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 90.9))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (93.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 93.1))</t>
         </is>
       </c>
     </row>
@@ -4436,10 +4436,10 @@
         <v>688663</v>
       </c>
       <c r="I27" t="n">
-        <v>595730</v>
+        <v>382870</v>
       </c>
       <c r="J27" t="n">
-        <v>0.865</v>
+        <v>0.556</v>
       </c>
       <c r="K27" t="n">
         <v>188956</v>
@@ -4457,10 +4457,10 @@
         <v>19.7</v>
       </c>
       <c r="P27" t="n">
-        <v>19.6032</v>
+        <v>19.578</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.3066</v>
+        <v>19.2993</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>19.4957</v>
+        <v>19.5332</v>
       </c>
       <c r="U27" t="n">
-        <v>19.5395</v>
+        <v>19.5533</v>
       </c>
       <c r="V27" t="n">
-        <v>18.7078</v>
+        <v>18.7195</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>50.21</v>
+        <v>58.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5184</v>
+        <v>19.5335</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB27" t="n">
         <v>19.375</v>
       </c>
       <c r="AC27" t="n">
-        <v>19.3066</v>
+        <v>19.2993</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4514,36 +4514,36 @@
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>19.5211</v>
+        <v>19.535</v>
       </c>
       <c r="AF27" t="n">
-        <v>19.8969</v>
+        <v>19.9555</v>
       </c>
       <c r="AG27" t="n">
-        <v>22.4073</v>
+        <v>20.0876</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 19.52; TP2: Bollinger Upper Band at 19.9; TP3: Fibonacci R1 at 22.41</t>
+          <t>TP1: 100 SMA at 19.54; TP2: Bollinger Upper Band at 19.96; TP3: Fibonacci R1 at 20.09</t>
         </is>
       </c>
       <c r="AI27" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7.62</v>
+        <v>7.66</v>
       </c>
       <c r="AK27" t="n">
-        <v>44.3</v>
+        <v>9.41</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="AM27" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AN27" t="n">
-        <v>15.65</v>
+        <v>3.68</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 50.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 58.1))</t>
         </is>
       </c>
     </row>
@@ -4588,10 +4588,10 @@
         <v>922568</v>
       </c>
       <c r="I28" t="n">
-        <v>951836</v>
+        <v>697763</v>
       </c>
       <c r="J28" t="n">
-        <v>1.032</v>
+        <v>0.756</v>
       </c>
       <c r="K28" t="n">
         <v>266129</v>
@@ -4609,10 +4609,10 @@
         <v>15.78</v>
       </c>
       <c r="P28" t="n">
-        <v>15.363</v>
+        <v>15.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.2781</v>
+        <v>15.2723</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>15.3139</v>
+        <v>15.3554</v>
       </c>
       <c r="U28" t="n">
-        <v>15.3077</v>
+        <v>15.325</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8836</v>
+        <v>14.8922</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>54.72</v>
+        <v>59.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>15.3761</v>
+        <v>15.408</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB28" t="n">
         <v>15.43</v>
       </c>
       <c r="AC28" t="n">
-        <v>15.2781</v>
+        <v>15.2723</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4666,36 +4666,36 @@
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>15.7333</v>
+        <v>15.799</v>
       </c>
       <c r="AF28" t="n">
-        <v>15.741</v>
+        <v>15.8064</v>
       </c>
       <c r="AG28" t="n">
-        <v>15.7866</v>
+        <v>16.0667</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 15.73; TP2: Fibonacci R1 at 15.74; TP3: Bollinger Upper Band at 15.79</t>
+          <t>TP1: Fibonacci R1 at 15.8; TP2: Bollinger Upper Band at 15.81; TP3: Classic R1 at 16.07</t>
         </is>
       </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.35</v>
+        <v>4.04</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="AM28" t="n">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.31</v>
+        <v>4.13</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 54.7))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 59.4))</t>
         </is>
       </c>
     </row>
@@ -4740,10 +4740,10 @@
         <v>1437614</v>
       </c>
       <c r="I29" t="n">
-        <v>576276</v>
+        <v>258681</v>
       </c>
       <c r="J29" t="n">
-        <v>0.401</v>
+        <v>0.18</v>
       </c>
       <c r="K29" t="n">
         <v>531676</v>
@@ -4761,10 +4761,10 @@
         <v>36.45</v>
       </c>
       <c r="P29" t="n">
-        <v>28.1316</v>
+        <v>28.3016</v>
       </c>
       <c r="Q29" t="n">
-        <v>17.4312</v>
+        <v>17.5262</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>29.3518</v>
+        <v>29.5088</v>
       </c>
       <c r="U29" t="n">
-        <v>27.0708</v>
+        <v>27.2249</v>
       </c>
       <c r="V29" t="n">
-        <v>19.3331</v>
+        <v>19.4492</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -4796,21 +4796,21 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>63.19</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>29.4364</v>
+        <v>29.5002</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB29" t="n">
         <v>29.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>28.9561</v>
+        <v>29.4803</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4818,36 +4818,36 @@
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>32.0079</v>
+        <v>32.2847</v>
       </c>
       <c r="AF29" t="n">
-        <v>34.3743</v>
+        <v>32.3265</v>
       </c>
       <c r="AG29" t="n">
-        <v>34.7767</v>
+        <v>33.4067</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 32.01; TP2: Fibonacci R1 at 34.37; TP3: Classic R1 at 34.78</t>
+          <t>TP1: Bollinger Upper Band at 32.28; TP2: Fibonacci R1 at 32.33; TP3: Classic R1 at 33.41</t>
         </is>
       </c>
       <c r="AI29" t="n">
-        <v>3.6</v>
+        <v>19.07</v>
       </c>
       <c r="AJ29" t="n">
-        <v>7.16</v>
+        <v>19.37</v>
       </c>
       <c r="AK29" t="n">
-        <v>7.77</v>
+        <v>27.1</v>
       </c>
       <c r="AL29" t="n">
-        <v>8.06</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>16.05</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AN29" t="n">
-        <v>17.41</v>
+        <v>12.78</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 63.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.9))</t>
         </is>
       </c>
     </row>
@@ -4892,10 +4892,10 @@
         <v>793094</v>
       </c>
       <c r="I30" t="n">
-        <v>979267</v>
+        <v>691778</v>
       </c>
       <c r="J30" t="n">
-        <v>1.235</v>
+        <v>0.872</v>
       </c>
       <c r="K30" t="n">
         <v>825593</v>
@@ -4913,10 +4913,10 @@
         <v>31.33</v>
       </c>
       <c r="P30" t="n">
-        <v>29.4926</v>
+        <v>29.6276</v>
       </c>
       <c r="Q30" t="n">
-        <v>26.6924</v>
+        <v>26.7444</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -4929,13 +4929,13 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>32.759</v>
+        <v>32.9906</v>
       </c>
       <c r="U30" t="n">
-        <v>30.283</v>
+        <v>30.4754</v>
       </c>
       <c r="V30" t="n">
-        <v>27.3043</v>
+        <v>27.3827</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -4948,58 +4948,58 @@
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>62.18</v>
+        <v>65.47</v>
       </c>
       <c r="Z30" t="n">
-        <v>32.0235</v>
+        <v>32.4486</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>32.0235</v>
+        <v>32.4486</v>
       </c>
       <c r="AC30" t="n">
-        <v>28.0639</v>
+        <v>29.4011</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>36.9281</v>
+        <v>36.5522</v>
       </c>
       <c r="AF30" t="n">
-        <v>39.0767</v>
+        <v>37.0004</v>
       </c>
       <c r="AG30" t="n">
-        <v>41.771</v>
+        <v>38.3133</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 36.93; TP2: Classic R3 at 39.08; TP3: Extension at 41.77</t>
+          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.0; TP3: Classic R1 at 38.31</t>
         </is>
       </c>
       <c r="AI30" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.46</v>
+        <v>1.92</v>
       </c>
       <c r="AL30" t="n">
-        <v>15.32</v>
+        <v>12.65</v>
       </c>
       <c r="AM30" t="n">
-        <v>22.03</v>
+        <v>14.03</v>
       </c>
       <c r="AN30" t="n">
-        <v>30.44</v>
+        <v>18.07</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.5))</t>
         </is>
       </c>
     </row>
@@ -5044,10 +5044,10 @@
         <v>34354934</v>
       </c>
       <c r="I31" t="n">
-        <v>59000414</v>
+        <v>23578787</v>
       </c>
       <c r="J31" t="n">
-        <v>1.717</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>22336100</v>
@@ -5065,10 +5065,10 @@
         <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8022</v>
+        <v>1.8074</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.6931</v>
+        <v>1.6943</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -5081,13 +5081,13 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>1.8754</v>
+        <v>1.8853</v>
       </c>
       <c r="U31" t="n">
-        <v>1.8097</v>
+        <v>1.8164</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6226</v>
+        <v>1.6261</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -5100,58 +5100,58 @@
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>59.04</v>
+        <v>62.43</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9044</v>
+        <v>1.9079</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB31" t="n">
-        <v>1.9044</v>
+        <v>1.9079</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.82</v>
+        <v>1.8311</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>1.9599</v>
+        <v>1.9773</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.9924</v>
+        <v>2.0413</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.0533</v>
+        <v>2.0833</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1.96; TP2: Fibonacci R1 at 1.99; TP3: Classic R1 at 2.05</t>
+          <t>TP1: Bollinger Upper Band at 1.98; TP2: Fibonacci R1 at 2.04; TP3: Classic R1 at 2.08</t>
         </is>
       </c>
       <c r="AI31" t="n">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.76</v>
+        <v>2.28</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.91</v>
+        <v>3.64</v>
       </c>
       <c r="AM31" t="n">
-        <v>4.62</v>
+        <v>6.99</v>
       </c>
       <c r="AN31" t="n">
-        <v>7.82</v>
+        <v>9.19</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
         </is>
       </c>
     </row>
@@ -5196,10 +5196,10 @@
         <v>5521781</v>
       </c>
       <c r="I32" t="n">
-        <v>4909177</v>
+        <v>2229590</v>
       </c>
       <c r="J32" t="n">
-        <v>0.889</v>
+        <v>0.404</v>
       </c>
       <c r="K32" t="n">
         <v>1231880</v>
@@ -5217,10 +5217,10 @@
         <v>9.84</v>
       </c>
       <c r="P32" t="n">
-        <v>9.654</v>
+        <v>9.646800000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.65</v>
+        <v>9.644</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>9.7372</v>
+        <v>9.751799999999999</v>
       </c>
       <c r="U32" t="n">
-        <v>9.6433</v>
+        <v>9.652900000000001</v>
       </c>
       <c r="V32" t="n">
-        <v>9.472799999999999</v>
+        <v>9.476900000000001</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -5252,21 +5252,21 @@
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>52.55</v>
+        <v>55.87</v>
       </c>
       <c r="Z32" t="n">
-        <v>9.780099999999999</v>
+        <v>9.800800000000001</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB32" t="n">
         <v>9.73</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.6591</v>
+        <v>9.66</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -5274,36 +5274,36 @@
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>10.0437</v>
+        <v>10.0704</v>
       </c>
       <c r="AF32" t="n">
-        <v>10.0572</v>
+        <v>10.2191</v>
       </c>
       <c r="AG32" t="n">
-        <v>10.12</v>
+        <v>10.29</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 10.04; TP2: Bollinger Upper Band at 10.06; TP3: Classic R1 at 10.12</t>
+          <t>TP1: Bollinger Upper Band at 10.07; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
         </is>
       </c>
       <c r="AI32" t="n">
-        <v>4.42</v>
+        <v>4.86</v>
       </c>
       <c r="AJ32" t="n">
-        <v>4.61</v>
+        <v>6.99</v>
       </c>
       <c r="AK32" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="AM32" t="n">
-        <v>3.36</v>
+        <v>5.03</v>
       </c>
       <c r="AN32" t="n">
-        <v>4.01</v>
+        <v>5.76</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 52.5))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 55.9))</t>
         </is>
       </c>
     </row>
@@ -5348,10 +5348,10 @@
         <v>2591517</v>
       </c>
       <c r="I33" t="n">
-        <v>3286835</v>
+        <v>2609559</v>
       </c>
       <c r="J33" t="n">
-        <v>1.268</v>
+        <v>1.007</v>
       </c>
       <c r="K33" t="n">
         <v>979317</v>
@@ -5369,10 +5369,10 @@
         <v>9.6</v>
       </c>
       <c r="P33" t="n">
-        <v>9.208600000000001</v>
+        <v>9.2178</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.9732</v>
+        <v>7.9872</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -5385,13 +5385,13 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>9.3826</v>
+        <v>9.411</v>
       </c>
       <c r="U33" t="n">
-        <v>9.147500000000001</v>
+        <v>9.1684</v>
       </c>
       <c r="V33" t="n">
-        <v>8.124599999999999</v>
+        <v>8.1401</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -5404,58 +5404,58 @@
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>52.35</v>
+        <v>60.51</v>
       </c>
       <c r="Z33" t="n">
-        <v>9.485900000000001</v>
+        <v>9.5091</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB33" t="n">
         <v>9.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.211399999999999</v>
+        <v>9.222200000000001</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>9.4329</v>
+        <v>9.6737</v>
       </c>
       <c r="AF33" t="n">
-        <v>9.49</v>
+        <v>9.708600000000001</v>
       </c>
       <c r="AG33" t="n">
-        <v>9.6571</v>
+        <v>9.7933</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 9.43; TP2: Classic R1 at 9.49; TP3: Fibonacci R2 at 9.66</t>
+          <t>TP1: Fibonacci R1 at 9.67; TP2: Bollinger Upper Band at 9.71; TP3: Classic R1 at 9.79</t>
         </is>
       </c>
       <c r="AI33" t="n">
-        <v>4.74</v>
+        <v>15.26</v>
       </c>
       <c r="AJ33" t="n">
-        <v>6.22</v>
+        <v>16.52</v>
       </c>
       <c r="AK33" t="n">
-        <v>10.54</v>
+        <v>19.57</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.98</v>
+        <v>4.58</v>
       </c>
       <c r="AM33" t="n">
-        <v>2.59</v>
+        <v>4.96</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.4</v>
+        <v>5.87</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 60.5))</t>
         </is>
       </c>
     </row>
@@ -5500,10 +5500,10 @@
         <v>2317029</v>
       </c>
       <c r="I34" t="n">
-        <v>1634022</v>
+        <v>1894030</v>
       </c>
       <c r="J34" t="n">
-        <v>0.705</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K34" t="n">
         <v>610489</v>
@@ -5521,10 +5521,10 @@
         <v>10.3</v>
       </c>
       <c r="P34" t="n">
-        <v>9.9594</v>
+        <v>9.9572</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.2111</v>
+        <v>9.2173</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -5537,13 +5537,13 @@
         </is>
       </c>
       <c r="T34" t="n">
-        <v>10.0779</v>
+        <v>10.0838</v>
       </c>
       <c r="U34" t="n">
-        <v>9.9047</v>
+        <v>9.9139</v>
       </c>
       <c r="V34" t="n">
-        <v>9.079599999999999</v>
+        <v>9.090199999999999</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -5556,58 +5556,58 @@
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>48.33</v>
+        <v>52.59</v>
       </c>
       <c r="Z34" t="n">
-        <v>10.2399</v>
+        <v>10.239</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB34" t="n">
-        <v>9.834</v>
+        <v>9.9572</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.403700000000001</v>
+        <v>9.91</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>10.183</v>
+        <v>10.4159</v>
       </c>
       <c r="AF34" t="n">
-        <v>10.2267</v>
+        <v>10.6503</v>
       </c>
       <c r="AG34" t="n">
-        <v>10.4237</v>
+        <v>10.7033</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 10.18; TP2: Classic R1 at 10.23; TP3: Fibonacci R2 at 10.42</t>
+          <t>TP1: Bollinger Upper Band at 10.42; TP2: Fibonacci R1 at 10.65; TP3: Classic R1 at 10.7</t>
         </is>
       </c>
       <c r="AI34" t="n">
-        <v>0.8100000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.91</v>
+        <v>14.68</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.37</v>
+        <v>15.81</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.55</v>
+        <v>4.61</v>
       </c>
       <c r="AM34" t="n">
-        <v>3.99</v>
+        <v>6.96</v>
       </c>
       <c r="AN34" t="n">
-        <v>6</v>
+        <v>7.49</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 48.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 52.6))</t>
         </is>
       </c>
     </row>
@@ -5652,10 +5652,10 @@
         <v>2815474</v>
       </c>
       <c r="I35" t="n">
-        <v>4712227</v>
+        <v>1988382</v>
       </c>
       <c r="J35" t="n">
-        <v>1.674</v>
+        <v>0.706</v>
       </c>
       <c r="K35" t="n">
         <v>607874</v>
@@ -5673,10 +5673,10 @@
         <v>15.77</v>
       </c>
       <c r="P35" t="n">
-        <v>16.4918</v>
+        <v>16.4556</v>
       </c>
       <c r="Q35" t="n">
-        <v>16.2599</v>
+        <v>16.259</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -5689,13 +5689,13 @@
         </is>
       </c>
       <c r="T35" t="n">
-        <v>16.0461</v>
+        <v>16.0312</v>
       </c>
       <c r="U35" t="n">
-        <v>16.3709</v>
+        <v>16.352</v>
       </c>
       <c r="V35" t="n">
-        <v>16.4502</v>
+        <v>16.4446</v>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -5708,58 +5708,58 @@
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>42.82</v>
+        <v>46.15</v>
       </c>
       <c r="Z35" t="n">
-        <v>16.0495</v>
+        <v>16.0476</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>15.5799</v>
+        <v>15.3806</v>
       </c>
       <c r="AC35" t="n">
-        <v>15.3806</v>
+        <v>15.0075</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>16.2599</v>
+        <v>16.259</v>
       </c>
       <c r="AF35" t="n">
+        <v>16.5125</v>
+      </c>
+      <c r="AG35" t="n">
         <v>16.7124</v>
       </c>
-      <c r="AG35" t="n">
-        <v>17.0033</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 16.26; TP2: Bollinger Upper Band at 16.71; TP3: 100 SMA at 17.0</t>
+          <t>TP1: 200 SMA at 16.26; TP2: Fibonacci R1 at 16.51; TP3: Bollinger Upper Band at 16.71</t>
         </is>
       </c>
       <c r="AI35" t="n">
-        <v>3.41</v>
+        <v>2.35</v>
       </c>
       <c r="AJ35" t="n">
-        <v>5.68</v>
+        <v>3.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>7.14</v>
+        <v>3.57</v>
       </c>
       <c r="AL35" t="n">
-        <v>4.36</v>
+        <v>5.71</v>
       </c>
       <c r="AM35" t="n">
-        <v>7.27</v>
+        <v>7.36</v>
       </c>
       <c r="AN35" t="n">
-        <v>9.140000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 42.8))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.1))</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>709475</v>
       </c>
       <c r="I36" t="n">
-        <v>1466664</v>
+        <v>1586127</v>
       </c>
       <c r="J36" t="n">
-        <v>2.067</v>
+        <v>2.236</v>
       </c>
       <c r="K36" t="n">
         <v>349204</v>
@@ -5823,10 +5823,10 @@
         <v>67</v>
       </c>
       <c r="P36" t="n">
-        <v>66.6896</v>
+        <v>66.8536</v>
       </c>
       <c r="Q36" t="n">
-        <v>62.8355</v>
+        <v>62.9675</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -5839,13 +5839,13 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>73.66419999999999</v>
+        <v>74.0391</v>
       </c>
       <c r="U36" t="n">
-        <v>68.06399999999999</v>
+        <v>68.438</v>
       </c>
       <c r="V36" t="n">
-        <v>60.5435</v>
+        <v>60.7132</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -5858,21 +5858,21 @@
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>65.63</v>
+        <v>60.07</v>
       </c>
       <c r="Z36" t="n">
-        <v>76.3087</v>
+        <v>76.501</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>76.3087</v>
+        <v>76.501</v>
       </c>
       <c r="AC36" t="n">
-        <v>73.8415</v>
+        <v>75.8223</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -5880,36 +5880,36 @@
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>88.58920000000001</v>
+        <v>86.65989999999999</v>
       </c>
       <c r="AF36" t="n">
-        <v>94.7295</v>
+        <v>89.17010000000001</v>
       </c>
       <c r="AG36" t="n">
-        <v>91.48739999999999</v>
+        <v>91.63330000000001</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 88.59; TP2: Extension at 94.73; TP3: Extension at 91.49</t>
+          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 89.17; TP3: Classic R1 at 91.63</t>
         </is>
       </c>
       <c r="AI36" t="n">
-        <v>4.98</v>
+        <v>14.97</v>
       </c>
       <c r="AJ36" t="n">
-        <v>7.47</v>
+        <v>18.67</v>
       </c>
       <c r="AK36" t="n">
-        <v>6.15</v>
+        <v>22.29</v>
       </c>
       <c r="AL36" t="n">
-        <v>16.09</v>
+        <v>13.28</v>
       </c>
       <c r="AM36" t="n">
-        <v>24.14</v>
+        <v>16.56</v>
       </c>
       <c r="AN36" t="n">
-        <v>19.89</v>
+        <v>19.78</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.1))</t>
         </is>
       </c>
     </row>
@@ -5954,10 +5954,10 @@
         <v>2065579</v>
       </c>
       <c r="I37" t="n">
-        <v>2971302</v>
+        <v>8379706</v>
       </c>
       <c r="J37" t="n">
-        <v>1.438</v>
+        <v>4.057</v>
       </c>
       <c r="K37" t="n">
         <v>1916849</v>
@@ -5975,10 +5975,10 @@
         <v>28.7</v>
       </c>
       <c r="P37" t="n">
-        <v>24.0836</v>
+        <v>24.2086</v>
       </c>
       <c r="Q37" t="n">
-        <v>20.1065</v>
+        <v>20.1765</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>26.9089</v>
+        <v>27.1452</v>
       </c>
       <c r="U37" t="n">
-        <v>24.857</v>
+        <v>25.0348</v>
       </c>
       <c r="V37" t="n">
-        <v>20.8564</v>
+        <v>20.9413</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -6010,21 +6010,21 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>64.14</v>
+        <v>70.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>27.3583</v>
+        <v>27.7014</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>27.3583</v>
+        <v>27.7014</v>
       </c>
       <c r="AC37" t="n">
-        <v>26.652</v>
+        <v>26.703</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
@@ -6032,36 +6032,36 @@
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>28.8758</v>
+        <v>29.0407</v>
       </c>
       <c r="AF37" t="n">
-        <v>29.4467</v>
+        <v>29.0849</v>
       </c>
       <c r="AG37" t="n">
-        <v>35.3367</v>
+        <v>30</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 28.88; TP2: Classic R2 at 29.45; TP3: Classic R3 at 35.34</t>
+          <t>TP1: Fibonacci R1 at 29.04; TP2: Bollinger Upper Band at 29.08; TP3: Classic R1 at 30</t>
         </is>
       </c>
       <c r="AI37" t="n">
-        <v>2.15</v>
+        <v>1.34</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.96</v>
+        <v>1.39</v>
       </c>
       <c r="AK37" t="n">
-        <v>11.3</v>
+        <v>2.3</v>
       </c>
       <c r="AL37" t="n">
-        <v>5.55</v>
+        <v>4.83</v>
       </c>
       <c r="AM37" t="n">
-        <v>7.63</v>
+        <v>4.99</v>
       </c>
       <c r="AN37" t="n">
-        <v>29.16</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.8); entry: enhanced entry at VWMA (overbought (RSI: 70.8))</t>
         </is>
       </c>
     </row>
@@ -6106,10 +6106,10 @@
         <v>7804852</v>
       </c>
       <c r="I38" t="n">
-        <v>2113471</v>
+        <v>1790510</v>
       </c>
       <c r="J38" t="n">
-        <v>0.271</v>
+        <v>0.229</v>
       </c>
       <c r="K38" t="n">
         <v>2251403</v>
@@ -6127,10 +6127,10 @@
         <v>9.75</v>
       </c>
       <c r="P38" t="n">
-        <v>9.2026</v>
+        <v>9.212400000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.248</v>
+        <v>7.2672</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -6143,13 +6143,13 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>9.2759</v>
+        <v>9.272500000000001</v>
       </c>
       <c r="U38" t="n">
-        <v>8.9658</v>
+        <v>8.9765</v>
       </c>
       <c r="V38" t="n">
-        <v>7.4306</v>
+        <v>7.4486</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -6162,58 +6162,58 @@
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>46.78</v>
+        <v>50.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>9.4832</v>
+        <v>9.4587</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>8.297700000000001</v>
+        <v>9.061999999999999</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.07</v>
+        <v>8.944599999999999</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>stop at Classic S1</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>9.642300000000001</v>
+        <v>9.663</v>
       </c>
       <c r="AF38" t="n">
-        <v>9.6944</v>
+        <v>9.7621</v>
       </c>
       <c r="AG38" t="n">
-        <v>9.83</v>
+        <v>9.7767</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 9.64; TP2: Bollinger Upper Band at 9.69; TP3: Classic R1 at 9.83</t>
+          <t>TP1: Bollinger Upper Band at 9.66; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
         </is>
       </c>
       <c r="AI38" t="n">
-        <v>5.91</v>
+        <v>5.12</v>
       </c>
       <c r="AJ38" t="n">
-        <v>6.13</v>
+        <v>5.96</v>
       </c>
       <c r="AK38" t="n">
-        <v>6.73</v>
+        <v>6.09</v>
       </c>
       <c r="AL38" t="n">
-        <v>16.2</v>
+        <v>6.63</v>
       </c>
       <c r="AM38" t="n">
-        <v>16.83</v>
+        <v>7.73</v>
       </c>
       <c r="AN38" t="n">
-        <v>18.47</v>
+        <v>7.89</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 50.2))</t>
         </is>
       </c>
     </row>
@@ -6258,10 +6258,10 @@
         <v>26574144</v>
       </c>
       <c r="I39" t="n">
-        <v>54367201</v>
+        <v>55653476</v>
       </c>
       <c r="J39" t="n">
-        <v>2.046</v>
+        <v>2.094</v>
       </c>
       <c r="K39" t="n">
         <v>7895646</v>
@@ -6279,10 +6279,10 @@
         <v>0.721</v>
       </c>
       <c r="P39" t="n">
-        <v>0.7074</v>
+        <v>0.7049</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7803</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>0.7062</v>
+        <v>0.7036</v>
       </c>
       <c r="U39" t="n">
-        <v>0.7228</v>
+        <v>0.7211</v>
       </c>
       <c r="V39" t="n">
-        <v>0.7269</v>
+        <v>0.7264</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -6314,14 +6314,14 @@
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>37.53</v>
+        <v>38.04</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:18</t>
+          <t>2026-08-02 12:02:53</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         <v>6225072</v>
       </c>
       <c r="I40" t="n">
-        <v>44142417</v>
+        <v>8677976</v>
       </c>
       <c r="J40" t="n">
-        <v>7.091</v>
+        <v>1.394</v>
       </c>
       <c r="K40" t="n">
         <v>4755720</v>
@@ -6409,10 +6409,10 @@
         <v>4.11</v>
       </c>
       <c r="P40" t="n">
-        <v>3.6948</v>
+        <v>3.712</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.9562</v>
+        <v>2.9679</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="T40" t="n">
-        <v>4.0321</v>
+        <v>4.0871</v>
       </c>
       <c r="U40" t="n">
-        <v>3.7491</v>
+        <v>3.7829</v>
       </c>
       <c r="V40" t="n">
-        <v>3.0828</v>
+        <v>3.098</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -6444,21 +6444,21 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>68.59</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.2457</v>
+        <v>4.2602</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>4.2457</v>
+        <v>4.2602</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.991</v>
+        <v>4.1295</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -6466,36 +6466,36 @@
         </is>
       </c>
       <c r="AE40" t="n">
-        <v>4.6831</v>
+        <v>4.7631</v>
       </c>
       <c r="AF40" t="n">
-        <v>4.9018</v>
+        <v>4.9278</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.7863</v>
+        <v>5.2367</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 4.68; TP2: Extension at 4.9; TP3: Extension at 4.79</t>
+          <t>TP1: Bollinger Upper Band at 4.76; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
         </is>
       </c>
       <c r="AI40" t="n">
-        <v>1.72</v>
+        <v>3.85</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.58</v>
+        <v>5.11</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.12</v>
+        <v>7.47</v>
       </c>
       <c r="AL40" t="n">
-        <v>10.3</v>
+        <v>11.81</v>
       </c>
       <c r="AM40" t="n">
-        <v>15.45</v>
+        <v>15.67</v>
       </c>
       <c r="AN40" t="n">
-        <v>12.73</v>
+        <v>22.92</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.8))</t>
         </is>
       </c>
     </row>
@@ -6540,10 +6540,10 @@
         <v>2164018</v>
       </c>
       <c r="I41" t="n">
-        <v>3603967</v>
+        <v>1005883</v>
       </c>
       <c r="J41" t="n">
-        <v>1.665</v>
+        <v>0.465</v>
       </c>
       <c r="K41" t="n">
         <v>1300532</v>
@@ -6561,10 +6561,10 @@
         <v>48.49</v>
       </c>
       <c r="P41" t="n">
-        <v>47.329</v>
+        <v>47.401</v>
       </c>
       <c r="Q41" t="n">
-        <v>36.7077</v>
+        <v>36.8791</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -6577,13 +6577,13 @@
         </is>
       </c>
       <c r="T41" t="n">
-        <v>48.9149</v>
+        <v>49.323</v>
       </c>
       <c r="U41" t="n">
-        <v>47.1388</v>
+        <v>47.3765</v>
       </c>
       <c r="V41" t="n">
-        <v>38.3881</v>
+        <v>38.5355</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -6596,58 +6596,58 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>71.48</v>
+        <v>72.41</v>
       </c>
       <c r="Z41" t="n">
-        <v>48.6622</v>
+        <v>48.7998</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>48.6622</v>
+        <v>48.7998</v>
       </c>
       <c r="AC41" t="n">
-        <v>47.6032</v>
+        <v>48.2733</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>55.9567</v>
+        <v>53.2048</v>
       </c>
       <c r="AF41" t="n">
-        <v>59.604</v>
+        <v>53.363</v>
       </c>
       <c r="AG41" t="n">
-        <v>57.6782</v>
+        <v>54.8285</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 55.96; TP2: Extension at 59.6; TP3: Extension at 57.68</t>
+          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 53.36; TP3: Fibonacci R2 at 54.83</t>
         </is>
       </c>
       <c r="AI41" t="n">
-        <v>6.89</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AJ41" t="n">
-        <v>10.33</v>
+        <v>8.67</v>
       </c>
       <c r="AK41" t="n">
-        <v>8.51</v>
+        <v>11.45</v>
       </c>
       <c r="AL41" t="n">
-        <v>14.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AM41" t="n">
-        <v>22.49</v>
+        <v>9.35</v>
       </c>
       <c r="AN41" t="n">
-        <v>18.53</v>
+        <v>12.35</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.5); entry: enhanced entry at VWMA (overbought (RSI: 71.5))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.4); entry: enhanced entry at VWMA (overbought (RSI: 72.4))</t>
         </is>
       </c>
     </row>
@@ -6692,10 +6692,10 @@
         <v>1868672</v>
       </c>
       <c r="I42" t="n">
-        <v>2788929</v>
+        <v>2565066</v>
       </c>
       <c r="J42" t="n">
-        <v>1.492</v>
+        <v>1.373</v>
       </c>
       <c r="K42" t="n">
         <v>910122</v>
@@ -6713,10 +6713,10 @@
         <v>38.28</v>
       </c>
       <c r="P42" t="n">
-        <v>39.1026</v>
+        <v>38.9628</v>
       </c>
       <c r="Q42" t="n">
-        <v>35.6823</v>
+        <v>35.7208</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -6729,13 +6729,13 @@
         </is>
       </c>
       <c r="T42" t="n">
-        <v>37.1869</v>
+        <v>37.2405</v>
       </c>
       <c r="U42" t="n">
-        <v>38.5094</v>
+        <v>38.4796</v>
       </c>
       <c r="V42" t="n">
-        <v>36.6576</v>
+        <v>36.6684</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -6748,58 +6748,58 @@
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>42.78</v>
+        <v>51.72</v>
       </c>
       <c r="Z42" t="n">
-        <v>37.1431</v>
+        <v>37.2052</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>35.4296</v>
+        <v>36.51</v>
       </c>
       <c r="AC42" t="n">
-        <v>34.75</v>
+        <v>35.7208</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at 200 SMA</t>
         </is>
       </c>
       <c r="AE42" t="n">
-        <v>38.6744</v>
+        <v>38.25</v>
       </c>
       <c r="AF42" t="n">
-        <v>41.0836</v>
+        <v>38.5567</v>
       </c>
       <c r="AG42" t="n">
-        <v>41.3733</v>
+        <v>38.7135</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 38.67; TP2: 100 SMA at 41.08; TP3: Classic R1 at 41.37</t>
+          <t>TP1: Fibonacci R1 at 38.25; TP2: Classic R1 at 38.56; TP3: Bollinger Upper Band at 38.71</t>
         </is>
       </c>
       <c r="AI42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AL42" t="n">
         <v>4.77</v>
       </c>
-      <c r="AJ42" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>9.16</v>
-      </c>
       <c r="AM42" t="n">
-        <v>15.96</v>
+        <v>5.61</v>
       </c>
       <c r="AN42" t="n">
-        <v>16.78</v>
+        <v>6.04</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 42.8))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 51.7))</t>
         </is>
       </c>
     </row>
@@ -6844,10 +6844,10 @@
         <v>2883990</v>
       </c>
       <c r="I43" t="n">
-        <v>4574285</v>
+        <v>3300712</v>
       </c>
       <c r="J43" t="n">
-        <v>1.586</v>
+        <v>1.144</v>
       </c>
       <c r="K43" t="n">
         <v>2388184</v>
@@ -6865,10 +6865,10 @@
         <v>6.91</v>
       </c>
       <c r="P43" t="n">
-        <v>6.1786</v>
+        <v>6.2104</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.859</v>
+        <v>5.8577</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -6881,13 +6881,13 @@
         </is>
       </c>
       <c r="T43" t="n">
-        <v>6.629</v>
+        <v>6.6777</v>
       </c>
       <c r="U43" t="n">
-        <v>6.2406</v>
+        <v>6.2759</v>
       </c>
       <c r="V43" t="n">
-        <v>5.6614</v>
+        <v>5.6762</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -6900,21 +6900,21 @@
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>61</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.7001</v>
+        <v>6.7256</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>6.7001</v>
+        <v>6.7256</v>
       </c>
       <c r="AC43" t="n">
-        <v>6.4163</v>
+        <v>6.4854</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
@@ -6922,36 +6922,36 @@
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>6.9833</v>
+        <v>7.2151</v>
       </c>
       <c r="AF43" t="n">
-        <v>7.1484</v>
+        <v>7.45</v>
       </c>
       <c r="AG43" t="n">
-        <v>7.1749</v>
+        <v>7.5149</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 6.98; TP2: Bollinger Upper Band at 7.15; TP3: Fibonacci R2 at 7.17</t>
+          <t>TP1: Fibonacci R1 at 7.22; TP2: Classic R1 at 7.45; TP3: Fibonacci R2 at 7.51</t>
         </is>
       </c>
       <c r="AI43" t="n">
-        <v>1</v>
+        <v>2.04</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.58</v>
+        <v>3.02</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.67</v>
+        <v>3.29</v>
       </c>
       <c r="AL43" t="n">
-        <v>4.23</v>
+        <v>7.28</v>
       </c>
       <c r="AM43" t="n">
-        <v>6.69</v>
+        <v>10.77</v>
       </c>
       <c r="AN43" t="n">
-        <v>7.09</v>
+        <v>11.74</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.8))</t>
         </is>
       </c>
     </row>
@@ -6996,10 +6996,10 @@
         <v>33705</v>
       </c>
       <c r="I44" t="n">
-        <v>426740</v>
+        <v>211589</v>
       </c>
       <c r="J44" t="n">
-        <v>12.661</v>
+        <v>6.278</v>
       </c>
       <c r="K44" t="n">
         <v>12577</v>
@@ -7017,10 +7017,10 @@
         <v>396</v>
       </c>
       <c r="P44" t="n">
-        <v>360.7776</v>
+        <v>361.1776</v>
       </c>
       <c r="Q44" t="n">
-        <v>341.2588</v>
+        <v>341.8762</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -7033,13 +7033,13 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>366.8971</v>
+        <v>369.9545</v>
       </c>
       <c r="U44" t="n">
-        <v>360.7054</v>
+        <v>362.2072</v>
       </c>
       <c r="V44" t="n">
-        <v>320.0468</v>
+        <v>320.8324</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -7052,21 +7052,21 @@
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>64.95999999999999</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="Z44" t="n">
-        <v>378.0295</v>
+        <v>380.9074</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB44" t="n">
         <v>382</v>
       </c>
       <c r="AC44" t="n">
-        <v>360</v>
+        <v>361.44</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
@@ -7074,36 +7074,36 @@
         </is>
       </c>
       <c r="AE44" t="n">
-        <v>398.67</v>
+        <v>392.6456</v>
       </c>
       <c r="AF44" t="n">
-        <v>446.67</v>
+        <v>423.2347</v>
       </c>
       <c r="AG44" t="n">
-        <v>471.3739</v>
+        <v>436.6533</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 398.67; TP2: Classic R3 at 446.67; TP3: Extension at 471.37</t>
+          <t>TP1: Bollinger Upper Band at 392.65; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
         </is>
       </c>
       <c r="AI44" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.94</v>
+        <v>2.01</v>
       </c>
       <c r="AK44" t="n">
-        <v>4.06</v>
+        <v>2.66</v>
       </c>
       <c r="AL44" t="n">
-        <v>4.36</v>
+        <v>2.79</v>
       </c>
       <c r="AM44" t="n">
-        <v>16.93</v>
+        <v>10.79</v>
       </c>
       <c r="AN44" t="n">
-        <v>23.4</v>
+        <v>14.31</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.0))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 67.5))</t>
         </is>
       </c>
     </row>
@@ -7148,10 +7148,10 @@
         <v>90812</v>
       </c>
       <c r="I45" t="n">
-        <v>681524</v>
+        <v>410244</v>
       </c>
       <c r="J45" t="n">
-        <v>7.505</v>
+        <v>4.517</v>
       </c>
       <c r="K45" t="n">
         <v>30216</v>
@@ -7169,10 +7169,10 @@
         <v>247.97</v>
       </c>
       <c r="P45" t="n">
-        <v>217.2328</v>
+        <v>218.9268</v>
       </c>
       <c r="Q45" t="n">
-        <v>185.8681</v>
+        <v>186.6207</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -7185,13 +7185,13 @@
         </is>
       </c>
       <c r="T45" t="n">
-        <v>234.7347</v>
+        <v>241.6171</v>
       </c>
       <c r="U45" t="n">
-        <v>219.0224</v>
+        <v>222.4725</v>
       </c>
       <c r="V45" t="n">
-        <v>180.7661</v>
+        <v>182.0222</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -7204,21 +7204,21 @@
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>76.81</v>
+        <v>83.52</v>
       </c>
       <c r="Z45" t="n">
-        <v>244.1101</v>
+        <v>253.6316</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB45" t="n">
-        <v>244.1101</v>
+        <v>256.995</v>
       </c>
       <c r="AC45" t="n">
-        <v>228.7645</v>
+        <v>234.8051</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
@@ -7226,36 +7226,36 @@
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>279.68</v>
+        <v>278.6404</v>
       </c>
       <c r="AF45" t="n">
-        <v>297.4649</v>
+        <v>288.2818</v>
       </c>
       <c r="AG45" t="n">
-        <v>288.0745</v>
+        <v>307.9633</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 279.68; TP2: Extension at 297.46; TP3: Extension at 288.07</t>
+          <t>TP1: Bollinger Upper Band at 278.64; TP2: Fibonacci R1 at 288.28; TP3: Classic R1 at 307.96</t>
         </is>
       </c>
       <c r="AI45" t="n">
-        <v>2.32</v>
+        <v>0.98</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3.48</v>
+        <v>1.41</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.86</v>
+        <v>2.3</v>
       </c>
       <c r="AL45" t="n">
-        <v>14.57</v>
+        <v>8.42</v>
       </c>
       <c r="AM45" t="n">
-        <v>21.86</v>
+        <v>12.17</v>
       </c>
       <c r="AN45" t="n">
-        <v>18.01</v>
+        <v>19.83</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.8); entry: enhanced entry at VWMA (overbought (RSI: 76.8))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (83.5); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 83.5))</t>
         </is>
       </c>
     </row>
@@ -7300,10 +7300,10 @@
         <v>2478481</v>
       </c>
       <c r="I46" t="n">
-        <v>2721102</v>
+        <v>2588085</v>
       </c>
       <c r="J46" t="n">
-        <v>1.098</v>
+        <v>1.044</v>
       </c>
       <c r="K46" t="n">
         <v>2518339</v>
@@ -7321,10 +7321,10 @@
         <v>6.56</v>
       </c>
       <c r="P46" t="n">
-        <v>6.833</v>
+        <v>6.8706</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.3811</v>
+        <v>6.3935</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -7337,13 +7337,13 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>7.7984</v>
+        <v>7.81</v>
       </c>
       <c r="U46" t="n">
-        <v>7.1216</v>
+        <v>7.1529</v>
       </c>
       <c r="V46" t="n">
-        <v>6.2865</v>
+        <v>6.3028</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -7356,58 +7356,58 @@
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>62.87</v>
+        <v>58.07</v>
       </c>
       <c r="Z46" t="n">
-        <v>7.7199</v>
+        <v>7.7478</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>7.7199</v>
+        <v>7.7478</v>
       </c>
       <c r="AC46" t="n">
-        <v>6.55</v>
+        <v>6.7382</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>9.092700000000001</v>
+        <v>8.755100000000001</v>
       </c>
       <c r="AF46" t="n">
-        <v>9.7791</v>
+        <v>9.002800000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>9.416700000000001</v>
+        <v>9.2333</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.09; TP2: Extension at 9.78; TP3: Extension at 9.42</t>
+          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 9.0; TP3: Classic R1 at 9.23</t>
         </is>
       </c>
       <c r="AI46" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL46" t="n">
-        <v>17.78</v>
+        <v>13</v>
       </c>
       <c r="AM46" t="n">
-        <v>26.67</v>
+        <v>16.2</v>
       </c>
       <c r="AN46" t="n">
-        <v>21.98</v>
+        <v>19.17</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.1))</t>
         </is>
       </c>
     </row>
@@ -7452,10 +7452,10 @@
         <v>39446506</v>
       </c>
       <c r="I47" t="n">
-        <v>74498234</v>
+        <v>105558462</v>
       </c>
       <c r="J47" t="n">
-        <v>1.889</v>
+        <v>2.676</v>
       </c>
       <c r="K47" t="n">
         <v>29063477</v>
@@ -7473,10 +7473,10 @@
         <v>1.57</v>
       </c>
       <c r="P47" t="n">
-        <v>1.2914</v>
+        <v>1.2954</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.1768</v>
+        <v>1.1814</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -7489,13 +7489,13 @@
         </is>
       </c>
       <c r="T47" t="n">
-        <v>1.3947</v>
+        <v>1.4048</v>
       </c>
       <c r="U47" t="n">
-        <v>1.3229</v>
+        <v>1.3299</v>
       </c>
       <c r="V47" t="n">
-        <v>1.149</v>
+        <v>1.1525</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -7508,18 +7508,18 @@
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>67.7</v>
+        <v>68.61</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.4204</v>
+        <v>1.4258</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>1.4204</v>
+        <v>1.4258</v>
       </c>
       <c r="AC47" t="n">
         <v>1.32</v>
@@ -7530,36 +7530,36 @@
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>1.5067</v>
+        <v>1.5828</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.5748</v>
+        <v>1.66</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.6338</v>
+        <v>1.6772</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 1.51; TP2: Bollinger Upper Band at 1.57; TP3: Extension at 1.63</t>
+          <t>TP1: Fibonacci R1 at 1.58; TP2: Classic R1 at 1.66; TP3: Fibonacci R2 at 1.68</t>
         </is>
       </c>
       <c r="AI47" t="n">
-        <v>0.86</v>
+        <v>1.48</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="AL47" t="n">
-        <v>6.08</v>
+        <v>11.01</v>
       </c>
       <c r="AM47" t="n">
-        <v>10.87</v>
+        <v>16.42</v>
       </c>
       <c r="AN47" t="n">
-        <v>15.03</v>
+        <v>17.63</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.6))</t>
         </is>
       </c>
     </row>
@@ -7604,10 +7604,10 @@
         <v>19600606</v>
       </c>
       <c r="I48" t="n">
-        <v>28606169</v>
+        <v>16480892</v>
       </c>
       <c r="J48" t="n">
-        <v>1.459</v>
+        <v>0.841</v>
       </c>
       <c r="K48" t="n">
         <v>22304846</v>
@@ -7625,10 +7625,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="P48" t="n">
-        <v>0.5344</v>
+        <v>0.5434</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4219</v>
+        <v>0.4245</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -7641,13 +7641,13 @@
         </is>
       </c>
       <c r="T48" t="n">
-        <v>0.7326</v>
+        <v>0.7448</v>
       </c>
       <c r="U48" t="n">
-        <v>0.5926</v>
+        <v>0.603</v>
       </c>
       <c r="V48" t="n">
-        <v>0.4452</v>
+        <v>0.4493</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -7660,18 +7660,18 @@
         </is>
       </c>
       <c r="Y48" t="n">
-        <v>71.81999999999999</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.7138</v>
+        <v>0.7278</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>0.7138</v>
+        <v>0.7278</v>
       </c>
       <c r="AC48" t="n">
         <v>0.595</v>
@@ -7682,36 +7682,36 @@
         </is>
       </c>
       <c r="AE48" t="n">
-        <v>1.0109</v>
+        <v>0.9255</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.1595</v>
+        <v>1.0187</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.081</v>
+        <v>1.0331</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1.01; TP2: Extension at 1.16; TP3: Extension at 1.08</t>
+          <t>TP1: Fibonacci R1 at 0.93; TP2: Classic R1 at 1.02; TP3: Fibonacci R2 at 1.03</t>
         </is>
       </c>
       <c r="AI48" t="n">
-        <v>2.5</v>
+        <v>1.49</v>
       </c>
       <c r="AJ48" t="n">
-        <v>3.75</v>
+        <v>2.19</v>
       </c>
       <c r="AK48" t="n">
-        <v>3.09</v>
+        <v>2.3</v>
       </c>
       <c r="AL48" t="n">
-        <v>41.63</v>
+        <v>27.16</v>
       </c>
       <c r="AM48" t="n">
-        <v>62.45</v>
+        <v>39.96</v>
       </c>
       <c r="AN48" t="n">
-        <v>51.45</v>
+        <v>41.94</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.8); entry: enhanced entry at VWMA (overbought (RSI: 71.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.2); entry: enhanced entry at VWMA (overbought (RSI: 74.2))</t>
         </is>
       </c>
     </row>
@@ -7756,10 +7756,10 @@
         <v>20426292</v>
       </c>
       <c r="I49" t="n">
-        <v>41065579</v>
+        <v>55295778</v>
       </c>
       <c r="J49" t="n">
-        <v>2.01</v>
+        <v>2.707</v>
       </c>
       <c r="K49" t="n">
         <v>18818578</v>
@@ -7777,10 +7777,10 @@
         <v>0.53</v>
       </c>
       <c r="P49" t="n">
-        <v>0.4435</v>
+        <v>0.4457</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4651</v>
+        <v>0.4659</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -7793,13 +7793,13 @@
         </is>
       </c>
       <c r="T49" t="n">
-        <v>0.4879</v>
+        <v>0.4923</v>
       </c>
       <c r="U49" t="n">
-        <v>0.4604</v>
+        <v>0.4633</v>
       </c>
       <c r="V49" t="n">
-        <v>0.4411</v>
+        <v>0.4421</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -7812,14 +7812,14 @@
         </is>
       </c>
       <c r="Y49" t="n">
-        <v>60.96</v>
+        <v>63.32</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.5144</v>
+        <v>0.5157</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -7886,10 +7886,10 @@
         <v>11630</v>
       </c>
       <c r="I50" t="n">
-        <v>6210</v>
+        <v>42506</v>
       </c>
       <c r="J50" t="n">
-        <v>0.534</v>
+        <v>3.655</v>
       </c>
       <c r="K50" t="n">
         <v>6840</v>
@@ -7907,10 +7907,10 @@
         <v>512</v>
       </c>
       <c r="P50" t="n">
-        <v>393.5748</v>
+        <v>396.0696</v>
       </c>
       <c r="Q50" t="n">
-        <v>298.9647</v>
+        <v>300.2514</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="T50" t="n">
-        <v>442.6711</v>
+        <v>446.4005</v>
       </c>
       <c r="U50" t="n">
-        <v>400.6695</v>
+        <v>403.8523</v>
       </c>
       <c r="V50" t="n">
-        <v>308.3784</v>
+        <v>310.1043</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -7942,21 +7942,21 @@
         </is>
       </c>
       <c r="Y50" t="n">
-        <v>68.23</v>
+        <v>73.87</v>
       </c>
       <c r="Z50" t="n">
-        <v>456.6532</v>
+        <v>460.6768</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>456.6532</v>
+        <v>460.6768</v>
       </c>
       <c r="AC50" t="n">
-        <v>436.5087</v>
+        <v>439.5284</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
@@ -7964,36 +7964,36 @@
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>480.12</v>
+        <v>501.4547</v>
       </c>
       <c r="AF50" t="n">
-        <v>503.7643</v>
+        <v>507.7685</v>
       </c>
       <c r="AG50" t="n">
-        <v>568</v>
+        <v>518.9933</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 480.12; TP2: Bollinger Upper Band at 503.76; TP3: Classic R3 at 568</t>
+          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 507.77; TP3: Classic R1 at 518.99</t>
         </is>
       </c>
       <c r="AI50" t="n">
-        <v>1.16</v>
+        <v>1.93</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="AK50" t="n">
-        <v>5.53</v>
+        <v>2.76</v>
       </c>
       <c r="AL50" t="n">
-        <v>5.14</v>
+        <v>8.85</v>
       </c>
       <c r="AM50" t="n">
-        <v>10.32</v>
+        <v>10.22</v>
       </c>
       <c r="AN50" t="n">
-        <v>24.38</v>
+        <v>12.66</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.9); entry: enhanced entry at VWMA (overbought (RSI: 73.9))</t>
         </is>
       </c>
     </row>
@@ -8038,10 +8038,10 @@
         <v>2311</v>
       </c>
       <c r="I51" t="n">
-        <v>2962</v>
+        <v>5875</v>
       </c>
       <c r="J51" t="n">
-        <v>1.282</v>
+        <v>2.542</v>
       </c>
       <c r="K51" t="n">
         <v>861</v>
@@ -8059,10 +8059,10 @@
         <v>1239</v>
       </c>
       <c r="P51" t="n">
-        <v>1160.9628</v>
+        <v>1162.3418</v>
       </c>
       <c r="Q51" t="n">
-        <v>905.4366</v>
+        <v>908.1762</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -8075,13 +8075,13 @@
         </is>
       </c>
       <c r="T51" t="n">
-        <v>1201.8052</v>
+        <v>1206.1018</v>
       </c>
       <c r="U51" t="n">
-        <v>1140.0868</v>
+        <v>1144.2763</v>
       </c>
       <c r="V51" t="n">
-        <v>917.8674</v>
+        <v>921.1415</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -8094,21 +8094,21 @@
         </is>
       </c>
       <c r="Y51" t="n">
-        <v>59.33</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="Z51" t="n">
-        <v>1207.6791</v>
+        <v>1210.3521</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB51" t="n">
         <v>1208.95</v>
       </c>
       <c r="AC51" t="n">
-        <v>1173.2802</v>
+        <v>1171.7975</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
@@ -8116,36 +8116,36 @@
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>1223.3267</v>
+        <v>1252.9855</v>
       </c>
       <c r="AF51" t="n">
-        <v>1248.0458</v>
+        <v>1312.2368</v>
       </c>
       <c r="AG51" t="n">
-        <v>1324.3267</v>
+        <v>1341.2533</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 1223.33; TP2: Bollinger Upper Band at 1248.05; TP3: Classic R3 at 1324.33</t>
+          <t>TP1: Bollinger Upper Band at 1252.99; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
         </is>
       </c>
       <c r="AI51" t="n">
-        <v>0.4</v>
+        <v>1.19</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="AK51" t="n">
-        <v>3.23</v>
+        <v>3.56</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.19</v>
+        <v>3.64</v>
       </c>
       <c r="AM51" t="n">
-        <v>3.23</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AN51" t="n">
-        <v>9.539999999999999</v>
+        <v>10.94</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 59.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 67.3))</t>
         </is>
       </c>
     </row>
@@ -8190,10 +8190,10 @@
         <v>92947</v>
       </c>
       <c r="I52" t="n">
-        <v>33758</v>
+        <v>55095</v>
       </c>
       <c r="J52" t="n">
-        <v>0.363</v>
+        <v>0.593</v>
       </c>
       <c r="K52" t="n">
         <v>39168</v>
@@ -8211,10 +8211,10 @@
         <v>245</v>
       </c>
       <c r="P52" t="n">
-        <v>255.449</v>
+        <v>255.0494</v>
       </c>
       <c r="Q52" t="n">
-        <v>244.2572</v>
+        <v>244.7297</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -8227,13 +8227,13 @@
         </is>
       </c>
       <c r="T52" t="n">
-        <v>244.9669</v>
+        <v>244.9224</v>
       </c>
       <c r="U52" t="n">
-        <v>250.9607</v>
+        <v>250.7073</v>
       </c>
       <c r="V52" t="n">
-        <v>233.9408</v>
+        <v>234.0459</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -8246,58 +8246,58 @@
         </is>
       </c>
       <c r="Y52" t="n">
-        <v>46.08</v>
+        <v>47.09</v>
       </c>
       <c r="Z52" t="n">
-        <v>243.2553</v>
+        <v>243.3248</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>236.29</v>
+        <v>235.83</v>
       </c>
       <c r="AC52" t="n">
-        <v>233.5066</v>
+        <v>234.7855</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE52" t="n">
-        <v>244.2572</v>
+        <v>244.7297</v>
       </c>
       <c r="AF52" t="n">
-        <v>250.1703</v>
+        <v>248.1478</v>
       </c>
       <c r="AG52" t="n">
-        <v>260.212</v>
+        <v>250.2892</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 244.26; TP2: Bollinger Upper Band at 250.17; TP3: 100 SMA at 260.21</t>
+          <t>TP1: 200 SMA at 244.73; TP2: Fibonacci R1 at 248.15; TP3: Bollinger Upper Band at 250.29</t>
         </is>
       </c>
       <c r="AI52" t="n">
-        <v>2.86</v>
+        <v>8.52</v>
       </c>
       <c r="AJ52" t="n">
-        <v>4.99</v>
+        <v>11.79</v>
       </c>
       <c r="AK52" t="n">
-        <v>8.59</v>
+        <v>13.84</v>
       </c>
       <c r="AL52" t="n">
-        <v>3.37</v>
+        <v>3.77</v>
       </c>
       <c r="AM52" t="n">
-        <v>5.87</v>
+        <v>5.22</v>
       </c>
       <c r="AN52" t="n">
-        <v>10.12</v>
+        <v>6.13</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 46.1))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 47.1))</t>
         </is>
       </c>
     </row>
@@ -8342,10 +8342,10 @@
         <v>90592</v>
       </c>
       <c r="I53" t="n">
-        <v>547338</v>
+        <v>357019</v>
       </c>
       <c r="J53" t="n">
-        <v>6.042</v>
+        <v>3.941</v>
       </c>
       <c r="K53" t="n">
         <v>89582</v>
@@ -8363,10 +8363,10 @@
         <v>197.49</v>
       </c>
       <c r="P53" t="n">
-        <v>143.6372</v>
+        <v>145.1638</v>
       </c>
       <c r="Q53" t="n">
-        <v>121.9894</v>
+        <v>122.5782</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -8379,13 +8379,13 @@
         </is>
       </c>
       <c r="T53" t="n">
-        <v>160.8445</v>
+        <v>165.3117</v>
       </c>
       <c r="U53" t="n">
-        <v>145.1147</v>
+        <v>147.5709</v>
       </c>
       <c r="V53" t="n">
-        <v>118.4574</v>
+        <v>119.3458</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -8398,21 +8398,21 @@
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>67.83</v>
+        <v>72.73</v>
       </c>
       <c r="Z53" t="n">
-        <v>170.2966</v>
+        <v>172.6528</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>170.2966</v>
+        <v>172.6528</v>
       </c>
       <c r="AC53" t="n">
-        <v>161.957</v>
+        <v>167</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
@@ -8420,36 +8420,36 @@
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>199.318</v>
+        <v>207.5428</v>
       </c>
       <c r="AF53" t="n">
-        <v>213.8287</v>
+        <v>208.4527</v>
       </c>
       <c r="AG53" t="n">
-        <v>206.1671</v>
+        <v>224.8967</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 199.32; TP2: Extension at 213.83; TP3: Extension at 206.17</t>
+          <t>TP1: Bollinger Upper Band at 207.54; TP2: Fibonacci R1 at 208.45; TP3: Classic R1 at 224.9</t>
         </is>
       </c>
       <c r="AI53" t="n">
-        <v>3.48</v>
+        <v>6.17</v>
       </c>
       <c r="AJ53" t="n">
-        <v>5.22</v>
+        <v>6.33</v>
       </c>
       <c r="AK53" t="n">
-        <v>4.3</v>
+        <v>9.24</v>
       </c>
       <c r="AL53" t="n">
-        <v>17.04</v>
+        <v>20.21</v>
       </c>
       <c r="AM53" t="n">
-        <v>25.56</v>
+        <v>20.74</v>
       </c>
       <c r="AN53" t="n">
-        <v>21.06</v>
+        <v>30.26</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.7); entry: enhanced entry at VWMA (overbought (RSI: 72.7))</t>
         </is>
       </c>
     </row>
@@ -8494,10 +8494,10 @@
         <v>24706539</v>
       </c>
       <c r="I54" t="n">
-        <v>50026435</v>
+        <v>32961095</v>
       </c>
       <c r="J54" t="n">
-        <v>2.025</v>
+        <v>1.334</v>
       </c>
       <c r="K54" t="n">
         <v>15027796</v>
@@ -8513,10 +8513,10 @@
         <v>6.69</v>
       </c>
       <c r="P54" t="n">
-        <v>6.5954</v>
+        <v>6.6156</v>
       </c>
       <c r="Q54" t="n">
-        <v>5.8196</v>
+        <v>5.8322</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -8529,13 +8529,13 @@
         </is>
       </c>
       <c r="T54" t="n">
-        <v>7.2134</v>
+        <v>7.2121</v>
       </c>
       <c r="U54" t="n">
-        <v>6.7233</v>
+        <v>6.742</v>
       </c>
       <c r="V54" t="n">
-        <v>5.7611</v>
+        <v>5.7754</v>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -8548,58 +8548,58 @@
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>52.63</v>
+        <v>53.4</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.2537</v>
+        <v>7.2661</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB54" t="n">
         <v>6.99</v>
       </c>
       <c r="AC54" t="n">
-        <v>6.495</v>
+        <v>6.6391</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AE54" t="n">
-        <v>7.22</v>
+        <v>7.6476</v>
       </c>
       <c r="AF54" t="n">
-        <v>7.932</v>
+        <v>7.8167</v>
       </c>
       <c r="AG54" t="n">
-        <v>8.09</v>
+        <v>7.8885</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 7.22; TP2: Bollinger Upper Band at 7.93; TP3: Classic R3 at 8.09</t>
+          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.89</t>
         </is>
       </c>
       <c r="AI54" t="n">
-        <v>0.46</v>
+        <v>1.87</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="AL54" t="n">
-        <v>3.29</v>
+        <v>9.41</v>
       </c>
       <c r="AM54" t="n">
-        <v>13.48</v>
+        <v>11.83</v>
       </c>
       <c r="AN54" t="n">
-        <v>15.74</v>
+        <v>12.85</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.4))</t>
         </is>
       </c>
     </row>
@@ -8644,10 +8644,10 @@
         <v>3433424</v>
       </c>
       <c r="I55" t="n">
-        <v>1042031</v>
+        <v>792465</v>
       </c>
       <c r="J55" t="n">
-        <v>0.303</v>
+        <v>0.231</v>
       </c>
       <c r="K55" t="n">
         <v>757029</v>
@@ -8665,10 +8665,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="P55" t="n">
-        <v>9.252599999999999</v>
+        <v>9.301</v>
       </c>
       <c r="Q55" t="n">
-        <v>6.0707</v>
+        <v>6.1138</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="T55" t="n">
-        <v>10.0824</v>
+        <v>10.2546</v>
       </c>
       <c r="U55" t="n">
-        <v>9.1845</v>
+        <v>9.2906</v>
       </c>
       <c r="V55" t="n">
-        <v>6.6227</v>
+        <v>6.6751</v>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -8700,58 +8700,58 @@
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>69.61</v>
+        <v>74.09</v>
       </c>
       <c r="Z55" t="n">
-        <v>10.0523</v>
+        <v>10.1156</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>10.0523</v>
+        <v>10.2473</v>
       </c>
       <c r="AC55" t="n">
-        <v>10.0353</v>
+        <v>9.4033</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AE55" t="n">
-        <v>11.7159</v>
+        <v>11.5959</v>
       </c>
       <c r="AF55" t="n">
-        <v>12.5477</v>
+        <v>12.0143</v>
       </c>
       <c r="AG55" t="n">
-        <v>12.1085</v>
+        <v>12.2874</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 11.72; TP2: Extension at 12.55; TP3: Extension at 12.11</t>
+          <t>TP1: Fibonacci R1 at 11.6; TP2: Bollinger Upper Band at 12.01; TP3: Fibonacci R2 at 12.29</t>
         </is>
       </c>
       <c r="AI55" t="n">
-        <v>97.81999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="AJ55" t="n">
-        <v>146.74</v>
+        <v>2.09</v>
       </c>
       <c r="AK55" t="n">
-        <v>120.91</v>
+        <v>2.42</v>
       </c>
       <c r="AL55" t="n">
-        <v>16.55</v>
+        <v>13.16</v>
       </c>
       <c r="AM55" t="n">
-        <v>24.82</v>
+        <v>17.24</v>
       </c>
       <c r="AN55" t="n">
-        <v>20.46</v>
+        <v>19.91</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.1); entry: enhanced entry at Parabolic SAR (overbought (RSI: 74.1))</t>
         </is>
       </c>
     </row>
@@ -8811,10 +8811,10 @@
         <v>5.56</v>
       </c>
       <c r="P56" t="n">
-        <v>5.4146</v>
+        <v>5.4198</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.2911</v>
+        <v>5.2924</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="T56" t="n">
-        <v>5.551</v>
+        <v>5.5471</v>
       </c>
       <c r="U56" t="n">
-        <v>5.4683</v>
+        <v>5.47</v>
       </c>
       <c r="V56" t="n">
-        <v>5.3241</v>
+        <v>5.326</v>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -8849,15 +8849,15 @@
         <v>48.33</v>
       </c>
       <c r="Z56" t="n">
-        <v>5.766</v>
+        <v>5.7785</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB56" t="n">
-        <v>5.4146</v>
+        <v>5.42</v>
       </c>
       <c r="AC56" t="n">
         <v>5.3534</v>
@@ -8868,36 +8868,36 @@
         </is>
       </c>
       <c r="AE56" t="n">
-        <v>5.5624</v>
+        <v>5.69</v>
       </c>
       <c r="AF56" t="n">
-        <v>5.5742</v>
+        <v>5.7031</v>
       </c>
       <c r="AG56" t="n">
-        <v>5.5767</v>
+        <v>5.7669</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 5.56; TP2: Fibonacci R2 at 5.57; TP3: Classic R1 at 5.58</t>
+          <t>TP1: Classic R1 at 5.69; TP2: Fibonacci R1 at 5.7; TP3: Fibonacci R2 at 5.77</t>
         </is>
       </c>
       <c r="AI56" t="n">
-        <v>2.42</v>
+        <v>4.06</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.61</v>
+        <v>4.25</v>
       </c>
       <c r="AK56" t="n">
-        <v>2.65</v>
+        <v>5.21</v>
       </c>
       <c r="AL56" t="n">
-        <v>2.73</v>
+        <v>4.98</v>
       </c>
       <c r="AM56" t="n">
-        <v>2.95</v>
+        <v>5.22</v>
       </c>
       <c r="AN56" t="n">
-        <v>2.99</v>
+        <v>6.4</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (neutral (RSI: 48.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Classic S1 (neutral (RSI: 48.3))</t>
         </is>
       </c>
     </row>
@@ -8942,10 +8942,10 @@
         <v>367014</v>
       </c>
       <c r="I57" t="n">
-        <v>431879</v>
+        <v>278499</v>
       </c>
       <c r="J57" t="n">
-        <v>1.177</v>
+        <v>0.759</v>
       </c>
       <c r="K57" t="n">
         <v>175426</v>
@@ -8963,10 +8963,10 @@
         <v>252.69</v>
       </c>
       <c r="P57" t="n">
-        <v>235.8538</v>
+        <v>237.53</v>
       </c>
       <c r="Q57" t="n">
-        <v>182.7898</v>
+        <v>183.4909</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -8979,13 +8979,13 @@
         </is>
       </c>
       <c r="T57" t="n">
-        <v>263.8467</v>
+        <v>266.5575</v>
       </c>
       <c r="U57" t="n">
-        <v>238.1021</v>
+        <v>240.2279</v>
       </c>
       <c r="V57" t="n">
-        <v>183.2799</v>
+        <v>184.3648</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -8998,21 +8998,21 @@
         </is>
       </c>
       <c r="Y57" t="n">
-        <v>74.61</v>
+        <v>75.45</v>
       </c>
       <c r="Z57" t="n">
-        <v>262.4663</v>
+        <v>264.7912</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB57" t="n">
-        <v>262.4663</v>
+        <v>264.7912</v>
       </c>
       <c r="AC57" t="n">
-        <v>252.8158</v>
+        <v>258.3459</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
@@ -9020,36 +9020,36 @@
         </is>
       </c>
       <c r="AE57" t="n">
-        <v>300.5617</v>
+        <v>298.94</v>
       </c>
       <c r="AF57" t="n">
-        <v>336.1233</v>
+        <v>304.8566</v>
       </c>
       <c r="AG57" t="n">
-        <v>364.2603</v>
+        <v>313.52</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 300.56; TP2: Classic R3 at 336.12; TP3: Extension at 364.26</t>
+          <t>TP1: Fibonacci R1 at 298.94; TP2: Bollinger Upper Band at 304.86; TP3: Fibonacci R2 at 313.52</t>
         </is>
       </c>
       <c r="AI57" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AJ57" t="n">
-        <v>7.63</v>
+        <v>6.22</v>
       </c>
       <c r="AK57" t="n">
-        <v>10.55</v>
+        <v>7.56</v>
       </c>
       <c r="AL57" t="n">
-        <v>14.51</v>
+        <v>12.9</v>
       </c>
       <c r="AM57" t="n">
-        <v>28.06</v>
+        <v>15.13</v>
       </c>
       <c r="AN57" t="n">
-        <v>38.78</v>
+        <v>18.4</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.6); entry: enhanced entry at VWMA (overbought (RSI: 74.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.4); entry: enhanced entry at VWMA (overbought (RSI: 75.4))</t>
         </is>
       </c>
     </row>
@@ -9094,10 +9094,10 @@
         <v>706832</v>
       </c>
       <c r="I58" t="n">
-        <v>4724740</v>
+        <v>4188116</v>
       </c>
       <c r="J58" t="n">
-        <v>6.684</v>
+        <v>5.925</v>
       </c>
       <c r="K58" t="n">
         <v>457851</v>
@@ -9115,10 +9115,10 @@
         <v>18</v>
       </c>
       <c r="P58" t="n">
-        <v>15.9354</v>
+        <v>15.976</v>
       </c>
       <c r="Q58" t="n">
-        <v>15.5829</v>
+        <v>15.614</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -9131,13 +9131,13 @@
         </is>
       </c>
       <c r="T58" t="n">
-        <v>16.1568</v>
+        <v>16.3771</v>
       </c>
       <c r="U58" t="n">
-        <v>15.9116</v>
+        <v>16.012</v>
       </c>
       <c r="V58" t="n">
-        <v>14.9443</v>
+        <v>14.9794</v>
       </c>
       <c r="W58" t="inlineStr">
         <is>
@@ -9150,21 +9150,21 @@
         </is>
       </c>
       <c r="Y58" t="n">
-        <v>69.11</v>
+        <v>75.92</v>
       </c>
       <c r="Z58" t="n">
-        <v>16.7411</v>
+        <v>16.923</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-01 16:05:27</t>
+          <t>2026-08-02 12:02:59</t>
         </is>
       </c>
       <c r="AB58" t="n">
         <v>17.43</v>
       </c>
       <c r="AC58" t="n">
-        <v>15.76</v>
+        <v>16.0664</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
@@ -9172,36 +9172,36 @@
         </is>
       </c>
       <c r="AE58" t="n">
-        <v>18.1733</v>
+        <v>17.7438</v>
       </c>
       <c r="AF58" t="n">
-        <v>18.545</v>
+        <v>19.0869</v>
       </c>
       <c r="AG58" t="n">
-        <v>18.3488</v>
+        <v>19.6033</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 18.17; TP2: Extension at 18.55; TP3: Extension at 18.35</t>
+          <t>TP1: Bollinger Upper Band at 17.74; TP2: Fibonacci R1 at 19.09; TP3: Classic R1 at 19.6</t>
         </is>
       </c>
       <c r="AI58" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.55</v>
+        <v>1.59</v>
       </c>
       <c r="AL58" t="n">
-        <v>4.26</v>
+        <v>1.8</v>
       </c>
       <c r="AM58" t="n">
-        <v>6.4</v>
+        <v>9.51</v>
       </c>
       <c r="AN58" t="n">
-        <v>5.27</v>
+        <v>12.47</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 69.1))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.9))</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB30" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB33" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:53</t>
+          <t>2026-08-02 12:26:34</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB56" t="n">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB57" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-02 12:02:59</t>
+          <t>2026-08-02 12:26:42</t>
         </is>
       </c>
       <c r="AB58" t="n">

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB30" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB33" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:34</t>
+          <t>2026-08-02 14:10:11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB56" t="n">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB57" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-02 12:26:42</t>
+          <t>2026-08-02 14:10:17</t>
         </is>
       </c>
       <c r="AB58" t="n">

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP58"/>
+  <dimension ref="A1:AP59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,7 +735,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB30" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB33" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:11</t>
+          <t>2026-08-02 15:52:56</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB56" t="n">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB57" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-02 14:10:17</t>
+          <t>2026-08-02 15:53:04</t>
         </is>
       </c>
       <c r="AB58" t="n">
@@ -9211,6 +9211,158 @@
       <c r="AP58" t="inlineStr">
         <is>
           <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.9))</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>LUTS</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>22289607</v>
+      </c>
+      <c r="I59" t="n">
+        <v>37379572</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="K59" t="n">
+        <v>25821852</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2253684</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0.5453</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.4854</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y59" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-02 15:53:04</t>
+        </is>
+      </c>
+      <c r="AB59" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0.5368000000000001</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AE59" t="n">
+        <v>0.5994</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0.6556999999999999</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>TP1: Classic R1 at 0.6; TP2: Fibonacci R2 at 0.62; TP3: Classic R2 at 0.66</t>
+        </is>
+      </c>
+      <c r="AI59" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>10.81</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 53.3))</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB2" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB3" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB4" t="n">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB5" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB6" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB7" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB8" t="n">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB9" t="n">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB10" t="n">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB23" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB24" t="n">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB25" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB26" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB27" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB28" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB29" t="n">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB30" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB31" t="n">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB32" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB33" t="n">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-02 15:52:56</t>
+          <t>2026-08-02 16:05:06</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -7667,7 +7667,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB55" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB56" t="n">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB57" t="n">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB58" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-02 15:53:04</t>
+          <t>2026-08-02 16:05:14</t>
         </is>
       </c>
       <c r="AB59" t="n">

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ59"/>
+  <dimension ref="A1:AQ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,7 +648,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.58</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>0.176</v>
@@ -682,10 +682,10 @@
         <v>7877205</v>
       </c>
       <c r="J2" t="n">
-        <v>27786983</v>
+        <v>9383921</v>
       </c>
       <c r="K2" t="n">
-        <v>3.528</v>
+        <v>1.191</v>
       </c>
       <c r="L2" t="n">
         <v>3221256</v>
@@ -703,10 +703,10 @@
         <v>9.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.1632</v>
+        <v>8.177199999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>7.6284</v>
+        <v>7.6366</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>8.364599999999999</v>
+        <v>8.4442</v>
       </c>
       <c r="V2" t="n">
-        <v>8.2042</v>
+        <v>8.2432</v>
       </c>
       <c r="W2" t="n">
-        <v>7.8761</v>
+        <v>7.8892</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -738,74 +738,74 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>78.59999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.5009</v>
+        <v>8.542999999999999</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC2" t="n">
         <v>8.595000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.24</v>
+        <v>8.291600000000001</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AF2" t="n">
+        <v>9.3924</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9.416700000000001</v>
+      </c>
+      <c r="AH2" t="n">
         <v>9.923299999999999</v>
       </c>
-      <c r="AG2" t="n">
-        <v>11.3133</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>12.3517</v>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 9.92; TP2: Classic R3 at 11.31; TP3: Extension at 12.35</t>
+          <t>TP1: Fibonacci R2 at 9.39; TP2: Classic R1 at 9.42; TP3: Classic R2 at 9.92</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>3.74</v>
+        <v>2.63</v>
       </c>
       <c r="AK2" t="n">
-        <v>7.66</v>
+        <v>2.71</v>
       </c>
       <c r="AL2" t="n">
-        <v>10.58</v>
+        <v>4.38</v>
       </c>
       <c r="AM2" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="AO2" t="n">
         <v>15.45</v>
       </c>
-      <c r="AN2" t="n">
-        <v>31.63</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>43.71</v>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 67.2))</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56.43</v>
+        <v>56.2</v>
       </c>
       <c r="E3" t="n">
         <v>1.1079</v>
@@ -839,10 +839,10 @@
         <v>714703</v>
       </c>
       <c r="J3" t="n">
-        <v>315322</v>
+        <v>181170</v>
       </c>
       <c r="K3" t="n">
-        <v>0.441</v>
+        <v>0.253</v>
       </c>
       <c r="L3" t="n">
         <v>216885</v>
@@ -860,10 +860,10 @@
         <v>56.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>56.0988</v>
+        <v>56.0788</v>
       </c>
       <c r="R3" t="n">
-        <v>51.2767</v>
+        <v>51.3652</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>56.1817</v>
+        <v>56.1835</v>
       </c>
       <c r="V3" t="n">
-        <v>55.6186</v>
+        <v>55.6414</v>
       </c>
       <c r="W3" t="n">
-        <v>49.8361</v>
+        <v>49.8994</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -895,18 +895,18 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>52.39</v>
+        <v>50.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>56.327</v>
+        <v>56.3266</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>56.327</v>
+        <v>56.0788</v>
       </c>
       <c r="AD3" t="n">
         <v>55.4</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>57.6413</v>
+        <v>57.6376</v>
       </c>
       <c r="AG3" t="n">
         <v>57.9093</v>
@@ -931,22 +931,22 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>2.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.16</v>
+        <v>3.32</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.81</v>
+        <v>3.26</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.56</v>
+        <v>4.02</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -955,14 +955,14 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 52.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.8))</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.37</v>
+        <v>27.27</v>
       </c>
       <c r="E4" t="n">
         <v>0.5379</v>
@@ -985,7 +985,7 @@
         <v>0.2552</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6373</v>
+        <v>1.5752</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         <v>1535296</v>
       </c>
       <c r="J4" t="n">
-        <v>1062269</v>
+        <v>247297</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.161</v>
       </c>
       <c r="L4" t="n">
         <v>1063344</v>
@@ -1017,10 +1017,10 @@
         <v>28.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.9998</v>
+        <v>27.9842</v>
       </c>
       <c r="R4" t="n">
-        <v>26.88</v>
+        <v>26.9069</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>27.6626</v>
+        <v>27.6252</v>
       </c>
       <c r="V4" t="n">
-        <v>27.9075</v>
+        <v>27.8825</v>
       </c>
       <c r="W4" t="n">
-        <v>25.9237</v>
+        <v>25.9371</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1052,29 +1052,29 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>44.87</v>
+        <v>43.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>27.7909</v>
+        <v>27.7552</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>26.9091</v>
+        <v>26.8436</v>
       </c>
       <c r="AD4" t="n">
-        <v>26.88</v>
+        <v>26.7256</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>stop at 200 SMA</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>27.9824</v>
+        <v>27.9893</v>
       </c>
       <c r="AG4" t="n">
         <v>28.521</v>
@@ -1084,26 +1084,26 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 27.98; TP2: Fibonacci R1 at 28.52; TP3: Classic R1 at 28.61</t>
+          <t>TP1: 100 SMA at 27.99; TP2: Fibonacci R1 at 28.52; TP3: Classic R1 at 28.61</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>36.93</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>55.46</v>
+        <v>14.21</v>
       </c>
       <c r="AL4" t="n">
-        <v>58.41</v>
+        <v>14.94</v>
       </c>
       <c r="AM4" t="n">
-        <v>3.99</v>
+        <v>4.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.99</v>
+        <v>6.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.31</v>
+        <v>6.57</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1112,14 +1112,14 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.9))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.7))</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.75</v>
+        <v>23.34</v>
       </c>
       <c r="E5" t="n">
         <v>0.4473</v>
@@ -1153,10 +1153,10 @@
         <v>3187957</v>
       </c>
       <c r="J5" t="n">
-        <v>2901186</v>
+        <v>2171828</v>
       </c>
       <c r="K5" t="n">
-        <v>0.91</v>
+        <v>0.681</v>
       </c>
       <c r="L5" t="n">
         <v>1152876</v>
@@ -1174,10 +1174,10 @@
         <v>22.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.85</v>
+        <v>21.877</v>
       </c>
       <c r="R5" t="n">
-        <v>19.2971</v>
+        <v>19.3498</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>22.4372</v>
+        <v>22.5232</v>
       </c>
       <c r="V5" t="n">
-        <v>21.8804</v>
+        <v>21.9376</v>
       </c>
       <c r="W5" t="n">
-        <v>19.4463</v>
+        <v>19.4851</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1209,18 +1209,18 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>55.18</v>
+        <v>60.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.7874</v>
+        <v>22.8564</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>22</v>
+        <v>22.8564</v>
       </c>
       <c r="AD5" t="n">
         <v>21.87</v>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>23.6529</v>
+        <v>23.6782</v>
       </c>
       <c r="AG5" t="n">
         <v>23.7306</v>
@@ -1241,26 +1241,26 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 23.65; TP2: Fibonacci R1 at 23.73; TP3: Classic R1 at 24.34</t>
+          <t>TP1: Bollinger Upper Band at 23.68; TP2: Fibonacci R1 at 23.73; TP3: Classic R1 at 24.34</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>12.71</v>
+        <v>0.83</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.31</v>
+        <v>0.89</v>
       </c>
       <c r="AL5" t="n">
-        <v>17.97</v>
+        <v>1.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>7.51</v>
+        <v>3.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.87</v>
+        <v>3.82</v>
       </c>
       <c r="AO5" t="n">
-        <v>10.62</v>
+        <v>6.48</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1269,14 +1269,14 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.3))</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>300.27</v>
+        <v>298.55</v>
       </c>
       <c r="E6" t="n">
         <v>5.8491</v>
@@ -1310,10 +1310,10 @@
         <v>306304</v>
       </c>
       <c r="J6" t="n">
-        <v>96256</v>
+        <v>45910</v>
       </c>
       <c r="K6" t="n">
-        <v>0.314</v>
+        <v>0.15</v>
       </c>
       <c r="L6" t="n">
         <v>54499</v>
@@ -1331,10 +1331,10 @@
         <v>302.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>305.026</v>
+        <v>304.3568</v>
       </c>
       <c r="R6" t="n">
-        <v>257.7349</v>
+        <v>258.4452</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>298.7628</v>
+        <v>298.7425</v>
       </c>
       <c r="V6" t="n">
-        <v>299.3859</v>
+        <v>299.3531</v>
       </c>
       <c r="W6" t="n">
-        <v>262.2237</v>
+        <v>262.5851</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1366,58 +1366,58 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>51.4</v>
+        <v>49.34</v>
       </c>
       <c r="AA6" t="n">
-        <v>300.2409</v>
+        <v>300.4322</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>300.2409</v>
+        <v>290.429</v>
       </c>
       <c r="AD6" t="n">
-        <v>294.5</v>
+        <v>285.9946</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>307.3727</v>
+        <v>300.2659</v>
       </c>
       <c r="AG6" t="n">
+        <v>307.337</v>
+      </c>
+      <c r="AH6" t="n">
         <v>308.3187</v>
       </c>
-      <c r="AH6" t="n">
-        <v>311.2833</v>
-      </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 307.37; TP2: Fibonacci R1 at 308.32; TP3: Classic R1 at 311.28</t>
+          <t>TP1: 100 SMA at 300.27; TP2: Bollinger Upper Band at 307.34; TP3: Fibonacci R1 at 308.32</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.41</v>
+        <v>3.81</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.92</v>
+        <v>4.03</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.38</v>
+        <v>3.39</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.69</v>
+        <v>5.82</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.68</v>
+        <v>6.16</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1426,14 +1426,14 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 51.4))</t>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.3))</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.76</v>
+        <v>12.83</v>
       </c>
       <c r="E7" t="n">
         <v>0.2245</v>
@@ -1467,10 +1467,10 @@
         <v>5963583</v>
       </c>
       <c r="J7" t="n">
-        <v>6520568</v>
+        <v>34538230</v>
       </c>
       <c r="K7" t="n">
-        <v>1.093</v>
+        <v>5.792</v>
       </c>
       <c r="L7" t="n">
         <v>3319555</v>
@@ -1488,10 +1488,10 @@
         <v>11.37</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.7666</v>
+        <v>11.7882</v>
       </c>
       <c r="R7" t="n">
-        <v>11.3018</v>
+        <v>11.3084</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>11.6006</v>
+        <v>11.7176</v>
       </c>
       <c r="V7" t="n">
-        <v>11.602</v>
+        <v>11.6502</v>
       </c>
       <c r="W7" t="n">
-        <v>11.0252</v>
+        <v>11.0431</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1519,78 +1519,56 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>53.94</v>
+        <v>71.22</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.5593</v>
+        <v>11.9263</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>11.5593</v>
+        <v>12.185</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.3164</v>
+        <v>11.3084</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
-        </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>11.7746</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.8941</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>TP1: Bollinger Upper Band at 11.77; TP2: Fibonacci R2 at 11.89; TP3: Classic R2 at 12.15</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>5.11</v>
-      </c>
+          <t>stop at 200 SMA</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 53.9))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 71.2))</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1604,7 +1582,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.24</v>
+        <v>29.79</v>
       </c>
       <c r="E8" t="n">
         <v>0.5662</v>
@@ -1624,10 +1602,10 @@
         <v>1257994</v>
       </c>
       <c r="J8" t="n">
-        <v>615921</v>
+        <v>527127</v>
       </c>
       <c r="K8" t="n">
-        <v>0.49</v>
+        <v>0.419</v>
       </c>
       <c r="L8" t="n">
         <v>514514</v>
@@ -1645,10 +1623,10 @@
         <v>29.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.6712</v>
+        <v>29.678</v>
       </c>
       <c r="R8" t="n">
-        <v>27.015</v>
+        <v>27.0496</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1661,13 +1639,13 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>29.4529</v>
+        <v>29.485</v>
       </c>
       <c r="V8" t="n">
-        <v>29.411</v>
+        <v>29.4259</v>
       </c>
       <c r="W8" t="n">
-        <v>27.3384</v>
+        <v>27.3628</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1680,25 +1658,25 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>46.74</v>
+        <v>52.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>29.546</v>
+        <v>29.5462</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>28.3793</v>
+        <v>29.678</v>
       </c>
       <c r="AD8" t="n">
-        <v>27.9949</v>
+        <v>28.5</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF8" t="n">
@@ -1708,46 +1686,46 @@
         <v>30.954</v>
       </c>
       <c r="AH8" t="n">
-        <v>31.4951</v>
+        <v>31.4832</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 30.85; TP2: Fibonacci R1 at 30.95; TP3: Bollinger Upper Band at 31.5</t>
+          <t>TP1: Classic R1 at 30.85; TP2: Fibonacci R1 at 30.95; TP3: Bollinger Upper Band at 31.48</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>6.44</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>6.7</v>
+        <v>1.08</v>
       </c>
       <c r="AL8" t="n">
-        <v>8.109999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="AM8" t="n">
-        <v>8.720000000000001</v>
+        <v>3.96</v>
       </c>
       <c r="AN8" t="n">
-        <v>9.07</v>
+        <v>4.3</v>
       </c>
       <c r="AO8" t="n">
-        <v>10.98</v>
+        <v>6.08</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 52.5))</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1761,7 +1739,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>184.83</v>
+        <v>185</v>
       </c>
       <c r="E9" t="n">
         <v>3.6026</v>
@@ -1781,10 +1759,10 @@
         <v>190685</v>
       </c>
       <c r="J9" t="n">
-        <v>75454</v>
+        <v>23722</v>
       </c>
       <c r="K9" t="n">
-        <v>0.396</v>
+        <v>0.124</v>
       </c>
       <c r="L9" t="n">
         <v>35126</v>
@@ -1802,10 +1780,10 @@
         <v>185.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>182.7628</v>
+        <v>182.5628</v>
       </c>
       <c r="R9" t="n">
-        <v>160.8832</v>
+        <v>161.4491</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1818,13 +1796,13 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>182.6731</v>
+        <v>182.8947</v>
       </c>
       <c r="V9" t="n">
-        <v>182.2398</v>
+        <v>182.3481</v>
       </c>
       <c r="W9" t="n">
-        <v>157.1037</v>
+        <v>157.3813</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1837,18 +1815,18 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>53.93</v>
+        <v>54.17</v>
       </c>
       <c r="AA9" t="n">
-        <v>183.1928</v>
+        <v>183.963</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>183.1928</v>
+        <v>183.963</v>
       </c>
       <c r="AD9" t="n">
         <v>175</v>
@@ -1862,33 +1840,33 @@
         <v>192.0267</v>
       </c>
       <c r="AG9" t="n">
-        <v>192.6719</v>
+        <v>192.4687</v>
       </c>
       <c r="AH9" t="n">
         <v>194.9533</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 192.03; TP2: Bollinger Upper Band at 192.67; TP3: Classic R1 at 194.95</t>
+          <t>TP1: Fibonacci R1 at 192.03; TP2: Bollinger Upper Band at 192.47; TP3: Classic R1 at 194.95</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.16</v>
+        <v>0.95</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.82</v>
+        <v>4.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>5.17</v>
+        <v>4.62</v>
       </c>
       <c r="AO9" t="n">
-        <v>6.42</v>
+        <v>5.97</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1897,14 +1875,14 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 53.9))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 54.2))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1918,7 +1896,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>714</v>
+        <v>710.01</v>
       </c>
       <c r="E10" t="n">
         <v>1.4031</v>
@@ -1936,7 +1914,7 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>98211</v>
+        <v>51604</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1945,10 +1923,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>724.7194</v>
+        <v>724.7796</v>
       </c>
       <c r="R10" t="n">
-        <v>542.9888</v>
+        <v>544.4338</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1961,13 +1939,13 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>711.5924</v>
+        <v>711.4417</v>
       </c>
       <c r="V10" t="n">
-        <v>697.2424</v>
+        <v>697.7431</v>
       </c>
       <c r="W10" t="n">
-        <v>565.2025</v>
+        <v>566.6434</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1980,29 +1958,29 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>51.25</v>
+        <v>49.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>701.3951</v>
+        <v>701.0931</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>701.3951</v>
+        <v>688.154</v>
       </c>
       <c r="AD10" t="n">
-        <v>688.154</v>
+        <v>683.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>728.4585</v>
+        <v>727.2512</v>
       </c>
       <c r="AG10" t="n">
         <v>728.646</v>
@@ -2012,26 +1990,26 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 728.46; TP2: Fibonacci R1 at 728.65; TP3: Classic R1 at 736.8</t>
+          <t>TP1: Bollinger Upper Band at 727.25; TP2: Fibonacci R1 at 728.65; TP3: Classic R1 at 736.8</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>2.04</v>
+        <v>8.98</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.06</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.67</v>
+        <v>11.17</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.86</v>
+        <v>5.68</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.89</v>
+        <v>5.88</v>
       </c>
       <c r="AO10" t="n">
-        <v>5.05</v>
+        <v>7.07</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2040,14 +2018,14 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 51.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 49.3))</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2061,7 +2039,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22.98</v>
+        <v>23</v>
       </c>
       <c r="E11" t="n">
         <v>0.4463</v>
@@ -2081,10 +2059,10 @@
         <v>1198269</v>
       </c>
       <c r="J11" t="n">
-        <v>1001409</v>
+        <v>370717</v>
       </c>
       <c r="K11" t="n">
-        <v>0.836</v>
+        <v>0.309</v>
       </c>
       <c r="L11" t="n">
         <v>608115</v>
@@ -2102,10 +2080,10 @@
         <v>22.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.9288</v>
+        <v>22.9208</v>
       </c>
       <c r="R11" t="n">
-        <v>22.9433</v>
+        <v>22.9504</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -2118,13 +2096,13 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>22.9173</v>
+        <v>22.9252</v>
       </c>
       <c r="V11" t="n">
-        <v>22.9187</v>
+        <v>22.9219</v>
       </c>
       <c r="W11" t="n">
-        <v>22.9073</v>
+        <v>22.9082</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2133,18 +2111,18 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>51.18</v>
+        <v>51.56</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.969</v>
+        <v>22.9775</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2182,7 +2160,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2196,7 +2174,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.48</v>
+        <v>14.82</v>
       </c>
       <c r="E12" t="n">
         <v>0.2863</v>
@@ -2216,10 +2194,10 @@
         <v>17325026</v>
       </c>
       <c r="J12" t="n">
-        <v>6124458</v>
+        <v>6964273</v>
       </c>
       <c r="K12" t="n">
-        <v>0.354</v>
+        <v>0.402</v>
       </c>
       <c r="L12" t="n">
         <v>7241829</v>
@@ -2237,10 +2215,10 @@
         <v>14.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.8562</v>
+        <v>14.8746</v>
       </c>
       <c r="R12" t="n">
-        <v>10.3721</v>
+        <v>10.4091</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2253,13 +2231,13 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>14.7572</v>
+        <v>14.7632</v>
       </c>
       <c r="V12" t="n">
-        <v>14.2754</v>
+        <v>14.2968</v>
       </c>
       <c r="W12" t="n">
-        <v>11.2079</v>
+        <v>11.2439</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2272,25 +2250,25 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>44.28</v>
+        <v>51.71</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.8343</v>
+        <v>14.8411</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>14.4223</v>
+        <v>14.4304</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.3284</v>
+        <v>14.43</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF12" t="n">
@@ -2300,7 +2278,7 @@
         <v>15.1467</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.1557</v>
+        <v>15.1596</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
@@ -2308,22 +2286,22 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>7.63</v>
+        <v>1813.69</v>
       </c>
       <c r="AK12" t="n">
-        <v>7.72</v>
+        <v>1835.21</v>
       </c>
       <c r="AL12" t="n">
-        <v>7.81</v>
+        <v>1868.26</v>
       </c>
       <c r="AM12" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AN12" t="n">
         <v>4.96</v>
       </c>
-      <c r="AN12" t="n">
-        <v>5.02</v>
-      </c>
       <c r="AO12" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -2332,14 +2310,14 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.3))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 51.7))</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2353,7 +2331,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>113.11</v>
+        <v>113.5</v>
       </c>
       <c r="E13" t="n">
         <v>2.0459</v>
@@ -2373,10 +2351,10 @@
         <v>1021769</v>
       </c>
       <c r="J13" t="n">
-        <v>1454997</v>
+        <v>393605</v>
       </c>
       <c r="K13" t="n">
-        <v>1.424</v>
+        <v>0.385</v>
       </c>
       <c r="L13" t="n">
         <v>352101</v>
@@ -2394,10 +2372,10 @@
         <v>112.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>96.7546</v>
+        <v>97.0926</v>
       </c>
       <c r="R13" t="n">
-        <v>79.8116</v>
+        <v>80.1301</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2410,13 +2388,13 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>101.6342</v>
+        <v>102.7643</v>
       </c>
       <c r="V13" t="n">
-        <v>97.6071</v>
+        <v>98.2304</v>
       </c>
       <c r="W13" t="n">
-        <v>81.49550000000001</v>
+        <v>81.81399999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2429,21 +2407,21 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>75.83</v>
+        <v>76.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>101.8988</v>
+        <v>102.2592</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>101.8988</v>
+        <v>102.2592</v>
       </c>
       <c r="AD13" t="n">
-        <v>100.1628</v>
+        <v>102.1</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2457,30 +2435,30 @@
         <v>133.1667</v>
       </c>
       <c r="AH13" t="n">
-        <v>145.111</v>
+        <v>144.9733</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 117.19; TP2: Classic R3 at 133.17; TP3: Extension at 145.11</t>
+          <t>TP1: Classic R2 at 117.19; TP2: Classic R3 at 133.17; TP3: Extension at 144.97</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>8.81</v>
+        <v>93.75</v>
       </c>
       <c r="AK13" t="n">
-        <v>18.01</v>
+        <v>194.12</v>
       </c>
       <c r="AL13" t="n">
-        <v>24.89</v>
+        <v>268.27</v>
       </c>
       <c r="AM13" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="AN13" t="n">
-        <v>30.69</v>
+        <v>30.22</v>
       </c>
       <c r="AO13" t="n">
-        <v>42.41</v>
+        <v>41.77</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2489,14 +2467,14 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.8); entry: enhanced entry at VWMA (overbought (RSI: 75.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.2); entry: enhanced entry at VWMA (overbought (RSI: 76.2))</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2510,7 +2488,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.58</v>
+        <v>5.7</v>
       </c>
       <c r="E14" t="n">
         <v>0.1043</v>
@@ -2530,10 +2508,10 @@
         <v>12075718</v>
       </c>
       <c r="J14" t="n">
-        <v>40168665</v>
+        <v>21019306</v>
       </c>
       <c r="K14" t="n">
-        <v>3.326</v>
+        <v>1.741</v>
       </c>
       <c r="L14" t="n">
         <v>5009453</v>
@@ -2551,10 +2529,10 @@
         <v>5.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.074</v>
+        <v>5.0854</v>
       </c>
       <c r="R14" t="n">
-        <v>4.048</v>
+        <v>4.0602</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2567,13 +2545,13 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>5.1307</v>
+        <v>5.1849</v>
       </c>
       <c r="V14" t="n">
-        <v>4.9976</v>
+        <v>5.0251</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2661</v>
+        <v>4.2804</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2586,18 +2564,18 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>74.34</v>
+        <v>77.12</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.2443</v>
+        <v>5.3015</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>5.2443</v>
+        <v>5.3015</v>
       </c>
       <c r="AD14" t="n">
         <v>5.04</v>
@@ -2608,36 +2586,36 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>5.62</v>
+        <v>6.06</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.06</v>
+        <v>6.4393</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.3716</v>
+        <v>6.239</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 5.62; TP2: Classic R3 at 6.06; TP3: Extension at 6.37</t>
+          <t>TP1: Classic R3 at 6.06; TP2: Extension at 6.44; TP3: Extension at 6.24</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.84</v>
+        <v>2.9</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.99</v>
+        <v>4.35</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.52</v>
+        <v>3.59</v>
       </c>
       <c r="AM14" t="n">
-        <v>7.16</v>
+        <v>14.31</v>
       </c>
       <c r="AN14" t="n">
-        <v>15.55</v>
+        <v>21.46</v>
       </c>
       <c r="AO14" t="n">
-        <v>21.5</v>
+        <v>17.68</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -2646,14 +2624,14 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.3); entry: enhanced entry at VWMA (overbought (RSI: 74.3))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.1); entry: enhanced entry at VWMA (overbought (RSI: 77.1))</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2667,7 +2645,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.86</v>
+        <v>5.08</v>
       </c>
       <c r="E15" t="n">
         <v>0.08890000000000001</v>
@@ -2687,10 +2665,10 @@
         <v>24343135</v>
       </c>
       <c r="J15" t="n">
-        <v>14509599</v>
+        <v>9587378</v>
       </c>
       <c r="K15" t="n">
-        <v>0.596</v>
+        <v>0.394</v>
       </c>
       <c r="L15" t="n">
         <v>15475726</v>
@@ -2708,10 +2686,10 @@
         <v>4.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.0564</v>
+        <v>3.1028</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2066</v>
+        <v>2.226</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2724,13 +2702,13 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>3.91</v>
+        <v>4.0215</v>
       </c>
       <c r="V15" t="n">
-        <v>3.2365</v>
+        <v>3.3088</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3365</v>
+        <v>2.3638</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2743,18 +2721,18 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>80.04000000000001</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.5646</v>
+        <v>3.6139</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>4.4288</v>
+        <v>4.44</v>
       </c>
       <c r="AD15" t="n">
         <v>3</v>
@@ -2765,36 +2743,36 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>5.2673</v>
+        <v>5.3832</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.3832</v>
+        <v>5.389</v>
       </c>
       <c r="AH15" t="n">
         <v>5.4</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 5.27; TP2: Fibonacci R2 at 5.38; TP3: Classic R1 at 5.4</t>
+          <t>TP1: Fibonacci R2 at 5.38; TP2: Bollinger Upper Band at 5.39; TP3: Classic R1 at 5.4</t>
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="AK15" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AL15" t="n">
         <v>0.67</v>
       </c>
-      <c r="AL15" t="n">
-        <v>0.68</v>
-      </c>
       <c r="AM15" t="n">
-        <v>18.93</v>
+        <v>21.24</v>
       </c>
       <c r="AN15" t="n">
-        <v>21.55</v>
+        <v>21.37</v>
       </c>
       <c r="AO15" t="n">
-        <v>21.93</v>
+        <v>21.62</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -2803,14 +2781,14 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (80.0); entry: enhanced entry at Parabolic SAR (overbought (RSI: 80.0))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.1); entry: enhanced entry at Parabolic SAR (overbought (RSI: 82.1))</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2824,7 +2802,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.242</v>
+        <v>0.243</v>
       </c>
       <c r="E16" t="n">
         <v>0.0047</v>
@@ -2844,10 +2822,10 @@
         <v>268716267</v>
       </c>
       <c r="J16" t="n">
-        <v>187237898</v>
+        <v>107618557</v>
       </c>
       <c r="K16" t="n">
-        <v>0.697</v>
+        <v>0.4</v>
       </c>
       <c r="L16" t="n">
         <v>153946169</v>
@@ -2865,10 +2843,10 @@
         <v>0.265</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2201</v>
+        <v>0.2208</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1797</v>
+        <v>0.1802</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -2881,13 +2859,13 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>0.2374</v>
+        <v>0.2379</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2236</v>
+        <v>0.2243</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1922</v>
+        <v>0.1927</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2900,18 +2878,18 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>56.33</v>
+        <v>56.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2384</v>
+        <v>0.2396</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>0.2384</v>
+        <v>0.2396</v>
       </c>
       <c r="AD16" t="n">
         <v>0.232</v>
@@ -2936,22 +2914,22 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>3.19</v>
+        <v>2.56</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.45</v>
+        <v>3.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.960000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="AM16" t="n">
-        <v>8.59</v>
+        <v>8.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>11.98</v>
+        <v>11.46</v>
       </c>
       <c r="AO16" t="n">
-        <v>24.15</v>
+        <v>23.56</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -2960,14 +2938,14 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.0))</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2981,7 +2959,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="E17" t="n">
         <v>0.0318</v>
@@ -3001,10 +2979,10 @@
         <v>32349173</v>
       </c>
       <c r="J17" t="n">
-        <v>12201267</v>
+        <v>8455042</v>
       </c>
       <c r="K17" t="n">
-        <v>0.377</v>
+        <v>0.261</v>
       </c>
       <c r="L17" t="n">
         <v>11262912</v>
@@ -3022,10 +3000,10 @@
         <v>1.65</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6052</v>
+        <v>1.6076</v>
       </c>
       <c r="R17" t="n">
-        <v>1.469</v>
+        <v>1.4704</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -3038,13 +3016,13 @@
         </is>
       </c>
       <c r="U17" t="n">
-        <v>1.6549</v>
+        <v>1.6592</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5989</v>
+        <v>1.6029</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5065</v>
+        <v>1.5084</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3057,21 +3035,21 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>57.12</v>
+        <v>58.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6597</v>
+        <v>1.665</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>1.6597</v>
+        <v>1.665</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5701</v>
+        <v>1.5879</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -3082,33 +3060,33 @@
         <v>1.737</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7469</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.76</v>
+        <v>1.803</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 1.74; TP2: Bollinger Upper Band at 1.75; TP3: Classic R1 at 1.76</t>
+          <t>TP1: Fibonacci R1 at 1.74; TP2: Classic R1 at 1.76; TP3: Fibonacci R2 at 1.8</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.97</v>
+        <v>1.23</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.12</v>
+        <v>1.79</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.66</v>
+        <v>4.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.26</v>
+        <v>5.71</v>
       </c>
       <c r="AO17" t="n">
-        <v>6.04</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3117,14 +3095,14 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.3))</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3138,7 +3116,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37.92</v>
+        <v>37.63</v>
       </c>
       <c r="E18" t="n">
         <v>0.7451</v>
@@ -3158,10 +3136,10 @@
         <v>1342299</v>
       </c>
       <c r="J18" t="n">
-        <v>354392</v>
+        <v>189692</v>
       </c>
       <c r="K18" t="n">
-        <v>0.264</v>
+        <v>0.141</v>
       </c>
       <c r="L18" t="n">
         <v>421515</v>
@@ -3179,10 +3157,10 @@
         <v>38.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>37.7608</v>
+        <v>37.7734</v>
       </c>
       <c r="R18" t="n">
-        <v>30.8075</v>
+        <v>30.8907</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3195,13 +3173,13 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>38.4028</v>
+        <v>38.3292</v>
       </c>
       <c r="V18" t="n">
-        <v>37.5031</v>
+        <v>37.5081</v>
       </c>
       <c r="W18" t="n">
-        <v>31.4222</v>
+        <v>31.4839</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3214,29 +3192,29 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>46.92</v>
+        <v>44.73</v>
       </c>
       <c r="AA18" t="n">
-        <v>39.1837</v>
+        <v>39.1917</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC18" t="n">
-        <v>37.3861</v>
+        <v>36.6681</v>
       </c>
       <c r="AD18" t="n">
-        <v>36.6681</v>
+        <v>35.6633</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>40.4079</v>
+        <v>40.4363</v>
       </c>
       <c r="AG18" t="n">
         <v>40.4652</v>
@@ -3246,26 +3224,26 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 40.41; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
+          <t>TP1: Bollinger Upper Band at 40.44; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>4.21</v>
+        <v>3.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>4.29</v>
+        <v>3.78</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.52</v>
+        <v>3.95</v>
       </c>
       <c r="AM18" t="n">
-        <v>8.08</v>
+        <v>10.28</v>
       </c>
       <c r="AN18" t="n">
-        <v>8.24</v>
+        <v>10.36</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.69</v>
+        <v>10.81</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -3274,14 +3252,14 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 44.7))</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3295,7 +3273,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>36.8</v>
+        <v>36.95</v>
       </c>
       <c r="E19" t="n">
         <v>0.6813</v>
@@ -3315,10 +3293,10 @@
         <v>1230298</v>
       </c>
       <c r="J19" t="n">
-        <v>707434</v>
+        <v>695893</v>
       </c>
       <c r="K19" t="n">
-        <v>0.575</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="L19" t="n">
         <v>708724</v>
@@ -3336,10 +3314,10 @@
         <v>38.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.739</v>
+        <v>30.027</v>
       </c>
       <c r="R19" t="n">
-        <v>19.3855</v>
+        <v>19.5046</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3352,13 +3330,13 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>34.8237</v>
+        <v>35.0262</v>
       </c>
       <c r="V19" t="n">
-        <v>30.6073</v>
+        <v>30.856</v>
       </c>
       <c r="W19" t="n">
-        <v>21.3292</v>
+        <v>21.4846</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3371,58 +3349,58 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>61.79</v>
+        <v>62.24</v>
       </c>
       <c r="AA19" t="n">
-        <v>35.9118</v>
+        <v>36.1219</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>35.9118</v>
+        <v>36.1219</v>
       </c>
       <c r="AD19" t="n">
-        <v>33.6727</v>
+        <v>33.7878</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AF19" t="n">
         <v>37.3616</v>
       </c>
       <c r="AG19" t="n">
-        <v>37.8636</v>
+        <v>37.9202</v>
       </c>
       <c r="AH19" t="n">
         <v>38.2267</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.86; TP3: Classic R1 at 38.23</t>
+          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.92; TP3: Classic R1 at 38.23</t>
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="AM19" t="n">
-        <v>4.04</v>
+        <v>3.43</v>
       </c>
       <c r="AN19" t="n">
-        <v>5.44</v>
+        <v>4.98</v>
       </c>
       <c r="AO19" t="n">
-        <v>6.45</v>
+        <v>5.83</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3431,14 +3409,14 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.2))</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3452,7 +3430,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.65</v>
+        <v>10.56</v>
       </c>
       <c r="E20" t="n">
         <v>0.2109</v>
@@ -3472,10 +3450,10 @@
         <v>4425370</v>
       </c>
       <c r="J20" t="n">
-        <v>3042822</v>
+        <v>337333</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.076</v>
       </c>
       <c r="L20" t="n">
         <v>3053793</v>
@@ -3493,10 +3471,10 @@
         <v>11.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.9122</v>
+        <v>9.962999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>7.9108</v>
+        <v>7.93</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -3509,13 +3487,13 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>10.6689</v>
+        <v>10.6586</v>
       </c>
       <c r="V20" t="n">
-        <v>10.0062</v>
+        <v>10.0279</v>
       </c>
       <c r="W20" t="n">
-        <v>8.2216</v>
+        <v>8.2448</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3528,18 +3506,18 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>53.14</v>
+        <v>50.61</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.8717</v>
+        <v>10.8798</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>10.5797</v>
+        <v>10.5449</v>
       </c>
       <c r="AD20" t="n">
         <v>10.3209</v>
@@ -3553,33 +3531,33 @@
         <v>11.0391</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.0693</v>
+        <v>11.0841</v>
       </c>
       <c r="AH20" t="n">
         <v>11.15</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.07; TP3: Classic R1 at 11.15</t>
+          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.08; TP3: Classic R1 at 11.15</t>
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.89</v>
+        <v>2.41</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.34</v>
+        <v>4.69</v>
       </c>
       <c r="AN20" t="n">
-        <v>4.63</v>
+        <v>5.11</v>
       </c>
       <c r="AO20" t="n">
-        <v>5.39</v>
+        <v>5.74</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3588,14 +3566,14 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 53.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 50.6))</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3609,7 +3587,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>32.32</v>
+        <v>32.6</v>
       </c>
       <c r="E21" t="n">
         <v>0.6398</v>
@@ -3629,10 +3607,10 @@
         <v>686404</v>
       </c>
       <c r="J21" t="n">
-        <v>1228294</v>
+        <v>675310</v>
       </c>
       <c r="K21" t="n">
-        <v>1.789</v>
+        <v>0.984</v>
       </c>
       <c r="L21" t="n">
         <v>245844</v>
@@ -3650,10 +3628,10 @@
         <v>36.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>35.2502</v>
+        <v>35.136</v>
       </c>
       <c r="R21" t="n">
-        <v>32.4106</v>
+        <v>32.49</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -3666,13 +3644,13 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>34.7043</v>
+        <v>34.5039</v>
       </c>
       <c r="V21" t="n">
-        <v>35.3007</v>
+        <v>35.1948</v>
       </c>
       <c r="W21" t="n">
-        <v>31.43</v>
+        <v>31.4417</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3685,74 +3663,74 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>34.54</v>
+        <v>36.66</v>
       </c>
       <c r="AA21" t="n">
-        <v>35.6699</v>
+        <v>35.1189</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC21" t="n">
+        <v>31.9226</v>
+      </c>
+      <c r="AD21" t="n">
         <v>31.5</v>
       </c>
-      <c r="AD21" t="n">
-        <v>29.9767</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>stop at Classic S1</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>32.4106</v>
+        <v>35.9174</v>
       </c>
       <c r="AG21" t="n">
-        <v>35.9053</v>
+        <v>37.0467</v>
       </c>
       <c r="AH21" t="n">
-        <v>37.0467</v>
+        <v>37.3241</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 32.41; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
+          <t>TP1: 100 SMA at 35.92; TP2: Classic R1 at 37.05; TP3: Fibonacci R1 at 37.32</t>
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0.6</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.89</v>
+        <v>12.13</v>
       </c>
       <c r="AL21" t="n">
-        <v>3.64</v>
+        <v>12.78</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.89</v>
+        <v>12.51</v>
       </c>
       <c r="AN21" t="n">
-        <v>13.99</v>
+        <v>16.05</v>
       </c>
       <c r="AO21" t="n">
-        <v>17.61</v>
+        <v>16.92</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 34.5))</t>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 36.7))</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3766,7 +3744,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>233</v>
+        <v>240.59</v>
       </c>
       <c r="E22" t="n">
         <v>4.4235</v>
@@ -3786,10 +3764,10 @@
         <v>365646</v>
       </c>
       <c r="J22" t="n">
-        <v>878556</v>
+        <v>397758</v>
       </c>
       <c r="K22" t="n">
-        <v>2.403</v>
+        <v>1.088</v>
       </c>
       <c r="L22" t="n">
         <v>290852</v>
@@ -3807,10 +3785,10 @@
         <v>242</v>
       </c>
       <c r="Q22" t="n">
-        <v>179.6746</v>
+        <v>181.1184</v>
       </c>
       <c r="R22" t="n">
-        <v>124.3292</v>
+        <v>125.1201</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -3823,13 +3801,13 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>208.6909</v>
+        <v>211.7289</v>
       </c>
       <c r="V22" t="n">
-        <v>183.1211</v>
+        <v>185.3747</v>
       </c>
       <c r="W22" t="n">
-        <v>129.0973</v>
+        <v>130.2067</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3842,18 +3820,18 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>73.56</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="AA22" t="n">
-        <v>205.5366</v>
+        <v>208.3982</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC22" t="n">
-        <v>205.5366</v>
+        <v>209</v>
       </c>
       <c r="AD22" t="n">
         <v>180.2255</v>
@@ -3864,36 +3842,36 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>239.7945</v>
+        <v>255.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>254.2116</v>
+        <v>257.9278</v>
       </c>
       <c r="AH22" t="n">
-        <v>255.99</v>
+        <v>258.1955</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 239.79; TP2: Bollinger Upper Band at 254.21; TP3: Classic R1 at 255.99</t>
+          <t>TP1: Classic R1 at 255.99; TP2: Bollinger Upper Band at 257.93; TP3: Fibonacci R2 at 258.2</t>
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.99</v>
+        <v>1.71</v>
       </c>
       <c r="AM22" t="n">
-        <v>16.67</v>
+        <v>22.48</v>
       </c>
       <c r="AN22" t="n">
-        <v>23.68</v>
+        <v>23.41</v>
       </c>
       <c r="AO22" t="n">
-        <v>24.55</v>
+        <v>23.54</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -3902,14 +3880,14 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.6); entry: enhanced entry at VWMA (overbought (RSI: 73.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.2); entry: enhanced entry at Parabolic SAR (overbought (RSI: 76.2))</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3923,7 +3901,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>95.48</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>1.8366</v>
@@ -3943,10 +3921,10 @@
         <v>280675</v>
       </c>
       <c r="J23" t="n">
-        <v>299430</v>
+        <v>235002</v>
       </c>
       <c r="K23" t="n">
-        <v>1.067</v>
+        <v>0.837</v>
       </c>
       <c r="L23" t="n">
         <v>97939</v>
@@ -3964,10 +3942,10 @@
         <v>93</v>
       </c>
       <c r="Q23" t="n">
-        <v>89.164</v>
+        <v>89.31780000000001</v>
       </c>
       <c r="R23" t="n">
-        <v>81.41240000000001</v>
+        <v>81.53060000000001</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -3980,13 +3958,13 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>92.1528</v>
+        <v>92.6611</v>
       </c>
       <c r="V23" t="n">
-        <v>89.3704</v>
+        <v>89.6888</v>
       </c>
       <c r="W23" t="n">
-        <v>83.035</v>
+        <v>83.1788</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3999,21 +3977,21 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>64.59</v>
+        <v>68.97</v>
       </c>
       <c r="AA23" t="n">
-        <v>92.5522</v>
+        <v>92.89279999999999</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>92.5522</v>
+        <v>92.89279999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>91.2256</v>
+        <v>91.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -4021,36 +3999,36 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>96.5592</v>
+        <v>98.17959999999999</v>
       </c>
       <c r="AG23" t="n">
-        <v>97.4401</v>
+        <v>98.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>98.33</v>
+        <v>99.27079999999999</v>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 96.56; TP2: Bollinger Upper Band at 97.44; TP3: Classic R1 at 98.33</t>
+          <t>TP1: Bollinger Upper Band at 98.18; TP2: Classic R1 at 98.33; TP3: Fibonacci R2 at 99.27</t>
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>3.02</v>
+        <v>4.84</v>
       </c>
       <c r="AK23" t="n">
-        <v>3.68</v>
+        <v>4.98</v>
       </c>
       <c r="AL23" t="n">
-        <v>4.36</v>
+        <v>5.84</v>
       </c>
       <c r="AM23" t="n">
-        <v>4.33</v>
+        <v>5.69</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.28</v>
+        <v>5.85</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.24</v>
+        <v>6.87</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -4059,14 +4037,14 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.0))</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4080,7 +4058,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.75</v>
+        <v>43.25</v>
       </c>
       <c r="E24" t="n">
         <v>0.8149999999999999</v>
@@ -4100,10 +4078,10 @@
         <v>397041</v>
       </c>
       <c r="J24" t="n">
-        <v>516351</v>
+        <v>532683</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3</v>
+        <v>1.342</v>
       </c>
       <c r="L24" t="n">
         <v>277385</v>
@@ -4121,10 +4099,10 @@
         <v>44.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>37.4058</v>
+        <v>37.5754</v>
       </c>
       <c r="R24" t="n">
-        <v>34.7997</v>
+        <v>34.8774</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4137,13 +4115,13 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>41.004</v>
+        <v>41.2179</v>
       </c>
       <c r="V24" t="n">
-        <v>38.4381</v>
+        <v>38.6268</v>
       </c>
       <c r="W24" t="n">
-        <v>34.0632</v>
+        <v>34.1546</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4156,58 +4134,58 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>57.53</v>
+        <v>63.17</v>
       </c>
       <c r="AA24" t="n">
-        <v>41.454</v>
+        <v>41.5869</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>41.454</v>
+        <v>41.5869</v>
       </c>
       <c r="AD24" t="n">
-        <v>37.5458</v>
+        <v>37.9853</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AF24" t="n">
         <v>44.1009</v>
       </c>
       <c r="AG24" t="n">
-        <v>45.1364</v>
+        <v>45.0487</v>
       </c>
       <c r="AH24" t="n">
         <v>45.3367</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 44.1; TP2: Bollinger Upper Band at 45.14; TP3: Classic R1 at 45.34</t>
+          <t>TP1: Fibonacci R1 at 44.1; TP2: Bollinger Upper Band at 45.05; TP3: Classic R1 at 45.34</t>
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="AM24" t="n">
-        <v>6.39</v>
+        <v>6.05</v>
       </c>
       <c r="AN24" t="n">
-        <v>8.880000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="AO24" t="n">
-        <v>9.369999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -4216,14 +4194,14 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.2))</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4237,7 +4215,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.69</v>
+        <v>12.76</v>
       </c>
       <c r="E25" t="n">
         <v>0.2405</v>
@@ -4257,10 +4235,10 @@
         <v>3065911</v>
       </c>
       <c r="J25" t="n">
-        <v>1766269</v>
+        <v>1027204</v>
       </c>
       <c r="K25" t="n">
-        <v>0.576</v>
+        <v>0.335</v>
       </c>
       <c r="L25" t="n">
         <v>1360330</v>
@@ -4278,10 +4256,10 @@
         <v>12.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.5612</v>
+        <v>10.6304</v>
       </c>
       <c r="R25" t="n">
-        <v>8.1494</v>
+        <v>8.186199999999999</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -4294,13 +4272,13 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>11.6948</v>
+        <v>11.7962</v>
       </c>
       <c r="V25" t="n">
-        <v>10.8556</v>
+        <v>10.9302</v>
       </c>
       <c r="W25" t="n">
-        <v>8.433999999999999</v>
+        <v>8.477</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -4313,18 +4291,18 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>70.52</v>
+        <v>71.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.7044</v>
+        <v>11.7592</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>11.7044</v>
+        <v>11.7592</v>
       </c>
       <c r="AD25" t="n">
         <v>11.1606</v>
@@ -4349,22 +4327,22 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.71</v>
+        <v>2.37</v>
       </c>
       <c r="AL25" t="n">
-        <v>3.01</v>
+        <v>2.64</v>
       </c>
       <c r="AM25" t="n">
-        <v>9.58</v>
+        <v>9.07</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.58</v>
+        <v>12.05</v>
       </c>
       <c r="AO25" t="n">
-        <v>13.98</v>
+        <v>13.45</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4373,14 +4351,14 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.2); entry: enhanced entry at VWMA (overbought (RSI: 71.2))</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4394,7 +4372,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>287.71</v>
+        <v>339.5</v>
       </c>
       <c r="E26" t="n">
         <v>4.7348</v>
@@ -4414,10 +4392,10 @@
         <v>152954</v>
       </c>
       <c r="J26" t="n">
-        <v>1095102</v>
+        <v>378734</v>
       </c>
       <c r="K26" t="n">
-        <v>7.16</v>
+        <v>2.476</v>
       </c>
       <c r="L26" t="n">
         <v>202414</v>
@@ -4435,10 +4413,10 @@
         <v>74.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>91.3626</v>
+        <v>96.62220000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>71.197</v>
+        <v>72.5834</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4451,13 +4429,13 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>141.1324</v>
+        <v>160.0245</v>
       </c>
       <c r="V26" t="n">
-        <v>104.6352</v>
+        <v>113.8456</v>
       </c>
       <c r="W26" t="n">
-        <v>74.1413</v>
+        <v>76.7816</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -4470,21 +4448,21 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>93.06999999999999</v>
+        <v>94.58</v>
       </c>
       <c r="AA26" t="n">
-        <v>162.5638</v>
+        <v>168.4464</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>177.23</v>
+        <v>203.365</v>
       </c>
       <c r="AD26" t="n">
-        <v>146.523</v>
+        <v>174.7604</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -4492,36 +4470,36 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>288.3412</v>
+        <v>353.5333</v>
       </c>
       <c r="AG26" t="n">
-        <v>296.6467</v>
+        <v>524.1933</v>
       </c>
       <c r="AH26" t="n">
-        <v>353.5333</v>
+        <v>646.7497</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 288.34; TP2: Classic R1 at 296.65; TP3: Classic R2 at 353.53</t>
+          <t>TP1: Classic R2 at 353.53; TP2: Classic R3 at 524.19; TP3: Extension at 646.75</t>
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>3.62</v>
+        <v>5.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.89</v>
+        <v>11.22</v>
       </c>
       <c r="AL26" t="n">
-        <v>5.74</v>
+        <v>15.5</v>
       </c>
       <c r="AM26" t="n">
-        <v>62.69</v>
+        <v>73.84</v>
       </c>
       <c r="AN26" t="n">
-        <v>67.38</v>
+        <v>157.76</v>
       </c>
       <c r="AO26" t="n">
-        <v>99.48</v>
+        <v>218.02</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -4530,14 +4508,14 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (93.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 93.1))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (94.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 94.6))</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4551,7 +4529,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19.89</v>
+        <v>19.73</v>
       </c>
       <c r="E27" t="n">
         <v>0.3853</v>
@@ -4571,10 +4549,10 @@
         <v>688663</v>
       </c>
       <c r="J27" t="n">
-        <v>382870</v>
+        <v>178807</v>
       </c>
       <c r="K27" t="n">
-        <v>0.556</v>
+        <v>0.26</v>
       </c>
       <c r="L27" t="n">
         <v>188956</v>
@@ -4592,10 +4570,10 @@
         <v>19.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.578</v>
+        <v>19.5496</v>
       </c>
       <c r="R27" t="n">
-        <v>19.2993</v>
+        <v>19.2989</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4608,13 +4586,13 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>19.5332</v>
+        <v>19.552</v>
       </c>
       <c r="V27" t="n">
-        <v>19.5533</v>
+        <v>19.5602</v>
       </c>
       <c r="W27" t="n">
-        <v>18.7195</v>
+        <v>18.7296</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -4627,18 +4605,18 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>58.14</v>
+        <v>54.23</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.5335</v>
+        <v>19.539</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>19.578</v>
+        <v>19.5496</v>
       </c>
       <c r="AD27" t="n">
         <v>19.51</v>
@@ -4649,7 +4627,7 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>19.9555</v>
+        <v>19.9791</v>
       </c>
       <c r="AG27" t="n">
         <v>20.0876</v>
@@ -4659,26 +4637,26 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 19.96; TP2: Fibonacci R1 at 20.09; TP3: Classic R1 at 20.21</t>
+          <t>TP1: Bollinger Upper Band at 19.98; TP2: Fibonacci R1 at 20.09; TP3: Classic R1 at 20.21</t>
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>5.55</v>
+        <v>10.85</v>
       </c>
       <c r="AK27" t="n">
-        <v>7.49</v>
+        <v>13.59</v>
       </c>
       <c r="AL27" t="n">
-        <v>9.25</v>
+        <v>16.59</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AO27" t="n">
-        <v>3.21</v>
+        <v>3.36</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4687,14 +4665,14 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 58.1))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 54.2))</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4708,7 +4686,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.75</v>
+        <v>15.72</v>
       </c>
       <c r="E28" t="n">
         <v>0.3061</v>
@@ -4728,10 +4706,10 @@
         <v>922568</v>
       </c>
       <c r="J28" t="n">
-        <v>697763</v>
+        <v>327585</v>
       </c>
       <c r="K28" t="n">
-        <v>0.756</v>
+        <v>0.355</v>
       </c>
       <c r="L28" t="n">
         <v>266129</v>
@@ -4749,10 +4727,10 @@
         <v>15.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.35</v>
+        <v>15.3386</v>
       </c>
       <c r="R28" t="n">
-        <v>15.2723</v>
+        <v>15.2683</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -4765,13 +4743,13 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>15.3554</v>
+        <v>15.3901</v>
       </c>
       <c r="V28" t="n">
-        <v>15.325</v>
+        <v>15.3405</v>
       </c>
       <c r="W28" t="n">
-        <v>14.8922</v>
+        <v>14.9004</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -4784,21 +4762,21 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>59.4</v>
+        <v>58.62</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.408</v>
+        <v>15.4271</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC28" t="n">
         <v>15.43</v>
       </c>
       <c r="AD28" t="n">
-        <v>15.2723</v>
+        <v>15.2683</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4809,30 +4787,30 @@
         <v>15.799</v>
       </c>
       <c r="AG28" t="n">
-        <v>15.8064</v>
+        <v>15.8182</v>
       </c>
       <c r="AH28" t="n">
         <v>16.0667</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 15.8; TP2: Bollinger Upper Band at 15.81; TP3: Classic R1 at 16.07</t>
+          <t>TP1: Fibonacci R1 at 15.8; TP2: Bollinger Upper Band at 15.82; TP3: Classic R1 at 16.07</t>
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AL28" t="n">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="AM28" t="n">
         <v>2.39</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="AO28" t="n">
         <v>4.13</v>
@@ -4844,14 +4822,14 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 59.4))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 58.6))</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4865,7 +4843,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>31.3</v>
       </c>
       <c r="E29" t="n">
         <v>0.6059</v>
@@ -4885,10 +4863,10 @@
         <v>1437614</v>
       </c>
       <c r="J29" t="n">
-        <v>258681</v>
+        <v>268484</v>
       </c>
       <c r="K29" t="n">
-        <v>0.18</v>
+        <v>0.187</v>
       </c>
       <c r="L29" t="n">
         <v>531676</v>
@@ -4906,10 +4884,10 @@
         <v>36.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>28.3016</v>
+        <v>28.4676</v>
       </c>
       <c r="R29" t="n">
-        <v>17.5262</v>
+        <v>17.6242</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -4922,13 +4900,13 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>29.5088</v>
+        <v>29.6794</v>
       </c>
       <c r="V29" t="n">
-        <v>27.2249</v>
+        <v>27.3847</v>
       </c>
       <c r="W29" t="n">
-        <v>19.4492</v>
+        <v>19.5672</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4941,21 +4919,21 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>64.84999999999999</v>
+        <v>66.39</v>
       </c>
       <c r="AA29" t="n">
-        <v>29.5002</v>
+        <v>29.5865</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC29" t="n">
         <v>29.62</v>
       </c>
       <c r="AD29" t="n">
-        <v>29.4803</v>
+        <v>29.5</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4963,33 +4941,33 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>32.2847</v>
+        <v>32.3265</v>
       </c>
       <c r="AG29" t="n">
-        <v>32.3265</v>
+        <v>32.5883</v>
       </c>
       <c r="AH29" t="n">
         <v>33.4067</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 32.28; TP2: Fibonacci R1 at 32.33; TP3: Classic R1 at 33.41</t>
+          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 32.59; TP3: Classic R1 at 33.41</t>
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>19.07</v>
+        <v>22.55</v>
       </c>
       <c r="AK29" t="n">
-        <v>19.37</v>
+        <v>24.74</v>
       </c>
       <c r="AL29" t="n">
-        <v>27.1</v>
+        <v>31.56</v>
       </c>
       <c r="AM29" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AN29" t="n">
-        <v>9.140000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="AO29" t="n">
         <v>12.78</v>
@@ -5001,14 +4979,14 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 66.4))</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5022,7 +5000,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35.19</v>
+        <v>35.83</v>
       </c>
       <c r="E30" t="n">
         <v>0.6772</v>
@@ -5042,10 +5020,10 @@
         <v>793094</v>
       </c>
       <c r="J30" t="n">
-        <v>691778</v>
+        <v>461203</v>
       </c>
       <c r="K30" t="n">
-        <v>0.872</v>
+        <v>0.582</v>
       </c>
       <c r="L30" t="n">
         <v>825593</v>
@@ -5063,10 +5041,10 @@
         <v>31.33</v>
       </c>
       <c r="Q30" t="n">
-        <v>29.6276</v>
+        <v>29.7764</v>
       </c>
       <c r="R30" t="n">
-        <v>26.7444</v>
+        <v>26.7965</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -5079,13 +5057,13 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>32.9906</v>
+        <v>33.261</v>
       </c>
       <c r="V30" t="n">
-        <v>30.4754</v>
+        <v>30.6854</v>
       </c>
       <c r="W30" t="n">
-        <v>27.3827</v>
+        <v>27.4668</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -5098,18 +5076,18 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>65.47</v>
+        <v>67.62</v>
       </c>
       <c r="AA30" t="n">
-        <v>32.4486</v>
+        <v>32.6535</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>32.4486</v>
+        <v>32.6535</v>
       </c>
       <c r="AD30" t="n">
         <v>29.4011</v>
@@ -5123,33 +5101,33 @@
         <v>36.5522</v>
       </c>
       <c r="AG30" t="n">
-        <v>37.0004</v>
+        <v>37.0381</v>
       </c>
       <c r="AH30" t="n">
         <v>38.3133</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.0; TP3: Classic R1 at 38.31</t>
+          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.04; TP3: Classic R1 at 38.31</t>
         </is>
       </c>
       <c r="AJ30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.35</v>
       </c>
-      <c r="AK30" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AL30" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AM30" t="n">
-        <v>12.65</v>
+        <v>11.94</v>
       </c>
       <c r="AN30" t="n">
-        <v>14.03</v>
+        <v>13.43</v>
       </c>
       <c r="AO30" t="n">
-        <v>18.07</v>
+        <v>17.33</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -5158,14 +5136,14 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.6))</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5179,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="E31" t="n">
         <v>0.0383</v>
@@ -5199,10 +5177,10 @@
         <v>34354934</v>
       </c>
       <c r="J31" t="n">
-        <v>23578787</v>
+        <v>28837890</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.839</v>
       </c>
       <c r="L31" t="n">
         <v>22336100</v>
@@ -5220,10 +5198,10 @@
         <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8074</v>
+        <v>1.8134</v>
       </c>
       <c r="R31" t="n">
-        <v>1.6943</v>
+        <v>1.6957</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -5236,13 +5214,13 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>1.8853</v>
+        <v>1.8972</v>
       </c>
       <c r="V31" t="n">
-        <v>1.8164</v>
+        <v>1.824</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6261</v>
+        <v>1.63</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -5255,21 +5233,21 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>62.43</v>
+        <v>64.78</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9079</v>
+        <v>1.9125</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>1.9079</v>
+        <v>1.9125</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8311</v>
+        <v>1.8454</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -5291,22 +5269,22 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.66</v>
+        <v>2.98</v>
       </c>
       <c r="AM31" t="n">
-        <v>6.99</v>
+        <v>6.74</v>
       </c>
       <c r="AN31" t="n">
-        <v>9.19</v>
+        <v>8.93</v>
       </c>
       <c r="AO31" t="n">
-        <v>10.7</v>
+        <v>10.44</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -5315,14 +5293,14 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.8))</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5336,7 +5314,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.890000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="E32" t="n">
         <v>0.1931</v>
@@ -5356,10 +5334,10 @@
         <v>5521781</v>
       </c>
       <c r="J32" t="n">
-        <v>2229590</v>
+        <v>668369</v>
       </c>
       <c r="K32" t="n">
-        <v>0.404</v>
+        <v>0.121</v>
       </c>
       <c r="L32" t="n">
         <v>1231880</v>
@@ -5377,10 +5355,10 @@
         <v>9.84</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.646800000000001</v>
+        <v>9.6442</v>
       </c>
       <c r="R32" t="n">
-        <v>9.644</v>
+        <v>9.6365</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -5393,13 +5371,13 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>9.751799999999999</v>
+        <v>9.7668</v>
       </c>
       <c r="V32" t="n">
-        <v>9.652900000000001</v>
+        <v>9.663</v>
       </c>
       <c r="W32" t="n">
-        <v>9.476900000000001</v>
+        <v>9.481199999999999</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -5412,18 +5390,18 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>55.87</v>
+        <v>56.47</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.800800000000001</v>
+        <v>9.8126</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>9.800800000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AD32" t="n">
         <v>9.73</v>
@@ -5434,7 +5412,7 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>10.0704</v>
+        <v>10.091</v>
       </c>
       <c r="AG32" t="n">
         <v>10.2191</v>
@@ -5444,26 +5422,26 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 10.07; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
+          <t>TP1: Bollinger Upper Band at 10.09; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>3.81</v>
+        <v>1.78</v>
       </c>
       <c r="AK32" t="n">
-        <v>5.91</v>
+        <v>2.76</v>
       </c>
       <c r="AL32" t="n">
-        <v>6.91</v>
+        <v>3.31</v>
       </c>
       <c r="AM32" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="AN32" t="n">
-        <v>4.27</v>
+        <v>3.64</v>
       </c>
       <c r="AO32" t="n">
-        <v>4.99</v>
+        <v>4.36</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -5472,14 +5450,14 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 55.9))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 56.5))</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5493,7 +5471,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9.68</v>
+        <v>9.74</v>
       </c>
       <c r="E33" t="n">
         <v>0.1856</v>
@@ -5513,10 +5491,10 @@
         <v>2591517</v>
       </c>
       <c r="J33" t="n">
-        <v>2609559</v>
+        <v>1851674</v>
       </c>
       <c r="K33" t="n">
-        <v>1.007</v>
+        <v>0.715</v>
       </c>
       <c r="L33" t="n">
         <v>979317</v>
@@ -5534,10 +5512,10 @@
         <v>9.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>9.2178</v>
+        <v>9.228400000000001</v>
       </c>
       <c r="R33" t="n">
-        <v>7.9872</v>
+        <v>8.001899999999999</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -5550,13 +5528,13 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>9.411</v>
+        <v>9.442299999999999</v>
       </c>
       <c r="V33" t="n">
-        <v>9.1684</v>
+        <v>9.190799999999999</v>
       </c>
       <c r="W33" t="n">
-        <v>8.1401</v>
+        <v>8.156000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -5569,21 +5547,21 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>60.51</v>
+        <v>62.02</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.5091</v>
+        <v>9.5139</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>9.5091</v>
+        <v>9.5139</v>
       </c>
       <c r="AD33" t="n">
-        <v>9.222200000000001</v>
+        <v>9.2433</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -5591,7 +5569,7 @@
         </is>
       </c>
       <c r="AF33" t="n">
-        <v>9.708600000000001</v>
+        <v>9.744300000000001</v>
       </c>
       <c r="AG33" t="n">
         <v>9.7933</v>
@@ -5601,26 +5579,26 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.71; TP2: Classic R1 at 9.79; TP3: Fibonacci R2 at 9.87</t>
+          <t>TP1: Bollinger Upper Band at 9.74; TP2: Classic R1 at 9.79; TP3: Fibonacci R2 at 9.87</t>
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AM33" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AO33" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -5629,14 +5607,14 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.0))</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5650,7 +5628,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.14</v>
+        <v>10.07</v>
       </c>
       <c r="E34" t="n">
         <v>0.1973</v>
@@ -5670,10 +5648,10 @@
         <v>2317029</v>
       </c>
       <c r="J34" t="n">
-        <v>1894030</v>
+        <v>389133</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="L34" t="n">
         <v>610489</v>
@@ -5691,10 +5669,10 @@
         <v>10.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.9572</v>
+        <v>9.9556</v>
       </c>
       <c r="R34" t="n">
-        <v>9.2173</v>
+        <v>9.2232</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5707,13 +5685,13 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>10.0838</v>
+        <v>10.0825</v>
       </c>
       <c r="V34" t="n">
-        <v>9.9139</v>
+        <v>9.9201</v>
       </c>
       <c r="W34" t="n">
-        <v>9.090199999999999</v>
+        <v>9.0999</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -5726,18 +5704,18 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>52.59</v>
+        <v>50.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>10.239</v>
+        <v>10.2412</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>10.125</v>
+        <v>9.9556</v>
       </c>
       <c r="AD34" t="n">
         <v>9.91</v>
@@ -5748,7 +5726,7 @@
         </is>
       </c>
       <c r="AF34" t="n">
-        <v>10.4159</v>
+        <v>10.4102</v>
       </c>
       <c r="AG34" t="n">
         <v>10.6503</v>
@@ -5758,26 +5736,26 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 10.42; TP2: Fibonacci R1 at 10.65; TP3: Classic R1 at 10.7</t>
+          <t>TP1: Bollinger Upper Band at 10.41; TP2: Fibonacci R1 at 10.65; TP3: Classic R1 at 10.7</t>
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.35</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.44</v>
+        <v>15.23</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.69</v>
+        <v>16.4</v>
       </c>
       <c r="AM34" t="n">
-        <v>2.87</v>
+        <v>4.57</v>
       </c>
       <c r="AN34" t="n">
-        <v>5.19</v>
+        <v>6.98</v>
       </c>
       <c r="AO34" t="n">
-        <v>5.71</v>
+        <v>7.51</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -5786,14 +5764,14 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.5))</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5807,7 +5785,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.89</v>
+        <v>15.88</v>
       </c>
       <c r="E35" t="n">
         <v>0.3102</v>
@@ -5827,10 +5805,10 @@
         <v>2815474</v>
       </c>
       <c r="J35" t="n">
-        <v>1988382</v>
+        <v>522325</v>
       </c>
       <c r="K35" t="n">
-        <v>0.706</v>
+        <v>0.186</v>
       </c>
       <c r="L35" t="n">
         <v>607874</v>
@@ -5848,10 +5826,10 @@
         <v>15.77</v>
       </c>
       <c r="Q35" t="n">
-        <v>16.4556</v>
+        <v>16.4224</v>
       </c>
       <c r="R35" t="n">
-        <v>16.259</v>
+        <v>16.2584</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -5864,13 +5842,13 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>16.0312</v>
+        <v>16.0168</v>
       </c>
       <c r="V35" t="n">
-        <v>16.352</v>
+        <v>16.3335</v>
       </c>
       <c r="W35" t="n">
-        <v>16.4446</v>
+        <v>16.439</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -5883,18 +5861,18 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>46.15</v>
+        <v>45.99</v>
       </c>
       <c r="AA35" t="n">
-        <v>16.0476</v>
+        <v>16.0413</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>15.3806</v>
+        <v>15.3648</v>
       </c>
       <c r="AD35" t="n">
         <v>15.0075</v>
@@ -5905,36 +5883,36 @@
         </is>
       </c>
       <c r="AF35" t="n">
-        <v>16.259</v>
+        <v>16.2584</v>
       </c>
       <c r="AG35" t="n">
         <v>16.5125</v>
       </c>
       <c r="AH35" t="n">
-        <v>16.7124</v>
+        <v>16.6982</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 16.26; TP2: Fibonacci R1 at 16.51; TP3: Bollinger Upper Band at 16.71</t>
+          <t>TP1: 200 SMA at 16.26; TP2: Fibonacci R1 at 16.51; TP3: Bollinger Upper Band at 16.7</t>
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>3.03</v>
+        <v>3.21</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.57</v>
+        <v>3.73</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.71</v>
+        <v>5.82</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.36</v>
+        <v>7.47</v>
       </c>
       <c r="AO35" t="n">
-        <v>8.66</v>
+        <v>8.68</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -5943,14 +5921,14 @@
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.1))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.0))</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5964,7 +5942,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="E36" t="n">
         <v>1.5818</v>
@@ -5973,7 +5951,7 @@
         <v>0.1693</v>
       </c>
       <c r="G36" t="n">
-        <v>2.2275</v>
+        <v>2.2273</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -5984,10 +5962,10 @@
         <v>709475</v>
       </c>
       <c r="J36" t="n">
-        <v>1586127</v>
+        <v>641864</v>
       </c>
       <c r="K36" t="n">
-        <v>2.236</v>
+        <v>0.905</v>
       </c>
       <c r="L36" t="n">
         <v>349204</v>
@@ -6003,10 +5981,10 @@
         <v>67</v>
       </c>
       <c r="Q36" t="n">
-        <v>66.8536</v>
+        <v>67.06359999999999</v>
       </c>
       <c r="R36" t="n">
-        <v>62.9675</v>
+        <v>63.103</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -6019,13 +5997,13 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>74.0391</v>
+        <v>74.41630000000001</v>
       </c>
       <c r="V36" t="n">
-        <v>68.438</v>
+        <v>68.813</v>
       </c>
       <c r="W36" t="n">
-        <v>60.7132</v>
+        <v>60.8852</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -6038,58 +6016,58 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>60.07</v>
+        <v>60.65</v>
       </c>
       <c r="AA36" t="n">
-        <v>76.501</v>
+        <v>76.8031</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>76.501</v>
+        <v>76.8031</v>
       </c>
       <c r="AD36" t="n">
-        <v>75.8223</v>
+        <v>66.2534</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AF36" t="n">
         <v>86.65989999999999</v>
       </c>
       <c r="AG36" t="n">
-        <v>89.17010000000001</v>
+        <v>89.76439999999999</v>
       </c>
       <c r="AH36" t="n">
         <v>91.63330000000001</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 89.17; TP3: Classic R1 at 91.63</t>
+          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 89.76; TP3: Classic R1 at 91.63</t>
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>14.97</v>
+        <v>0.93</v>
       </c>
       <c r="AK36" t="n">
-        <v>18.67</v>
+        <v>1.23</v>
       </c>
       <c r="AL36" t="n">
-        <v>22.29</v>
+        <v>1.41</v>
       </c>
       <c r="AM36" t="n">
-        <v>13.28</v>
+        <v>12.83</v>
       </c>
       <c r="AN36" t="n">
-        <v>16.56</v>
+        <v>16.88</v>
       </c>
       <c r="AO36" t="n">
-        <v>19.78</v>
+        <v>19.31</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -6098,14 +6076,14 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.6))</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6119,7 +6097,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>29.39</v>
+        <v>29.4</v>
       </c>
       <c r="E37" t="n">
         <v>0.5535</v>
@@ -6139,10 +6117,10 @@
         <v>2065579</v>
       </c>
       <c r="J37" t="n">
-        <v>8379706</v>
+        <v>780769</v>
       </c>
       <c r="K37" t="n">
-        <v>4.057</v>
+        <v>0.378</v>
       </c>
       <c r="L37" t="n">
         <v>1916849</v>
@@ -6160,10 +6138,10 @@
         <v>28.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.2086</v>
+        <v>24.3406</v>
       </c>
       <c r="R37" t="n">
-        <v>20.1765</v>
+        <v>20.2469</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6176,13 +6154,13 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>27.1452</v>
+        <v>27.36</v>
       </c>
       <c r="V37" t="n">
-        <v>25.0348</v>
+        <v>25.206</v>
       </c>
       <c r="W37" t="n">
-        <v>20.9413</v>
+        <v>21.0255</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -6195,21 +6173,21 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>70.8</v>
+        <v>70.84</v>
       </c>
       <c r="AA37" t="n">
-        <v>27.7014</v>
+        <v>27.7843</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>27.7014</v>
+        <v>27.7843</v>
       </c>
       <c r="AD37" t="n">
-        <v>26.703</v>
+        <v>26.8104</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -6231,22 +6209,22 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="AM37" t="n">
-        <v>8.300000000000001</v>
+        <v>7.97</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.869999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AO37" t="n">
-        <v>15.41</v>
+        <v>15.07</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -6262,7 +6240,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6276,7 +6254,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.24</v>
+        <v>9.18</v>
       </c>
       <c r="E38" t="n">
         <v>0.1803</v>
@@ -6296,10 +6274,10 @@
         <v>7804852</v>
       </c>
       <c r="J38" t="n">
-        <v>1790510</v>
+        <v>986670</v>
       </c>
       <c r="K38" t="n">
-        <v>0.229</v>
+        <v>0.126</v>
       </c>
       <c r="L38" t="n">
         <v>2251403</v>
@@ -6317,10 +6295,10 @@
         <v>9.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.212400000000001</v>
+        <v>9.215999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>7.2672</v>
+        <v>7.2865</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6333,13 +6311,13 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>9.272500000000001</v>
+        <v>9.2637</v>
       </c>
       <c r="V38" t="n">
-        <v>8.9765</v>
+        <v>8.984500000000001</v>
       </c>
       <c r="W38" t="n">
-        <v>7.4486</v>
+        <v>7.4658</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -6352,29 +6330,29 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>50.2</v>
+        <v>48.37</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.4587</v>
+        <v>9.406499999999999</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>9.212400000000001</v>
+        <v>8.944599999999999</v>
       </c>
       <c r="AD38" t="n">
-        <v>9.061999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>9.663</v>
+        <v>9.6006</v>
       </c>
       <c r="AG38" t="n">
         <v>9.7621</v>
@@ -6384,26 +6362,26 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.66; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
+          <t>TP1: Bollinger Upper Band at 9.6; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="AK38" t="n">
-        <v>3.65</v>
+        <v>4.43</v>
       </c>
       <c r="AL38" t="n">
-        <v>3.75</v>
+        <v>4.51</v>
       </c>
       <c r="AM38" t="n">
-        <v>4.89</v>
+        <v>7.33</v>
       </c>
       <c r="AN38" t="n">
-        <v>5.97</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AO38" t="n">
-        <v>6.13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -6412,14 +6390,14 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 48.4))</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6433,7 +6411,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.679</v>
+        <v>0.681</v>
       </c>
       <c r="E39" t="n">
         <v>0.0134</v>
@@ -6453,10 +6431,10 @@
         <v>26574144</v>
       </c>
       <c r="J39" t="n">
-        <v>55653476</v>
+        <v>15102670</v>
       </c>
       <c r="K39" t="n">
-        <v>2.094</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L39" t="n">
         <v>7895646</v>
@@ -6474,10 +6452,10 @@
         <v>0.721</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.7049</v>
+        <v>0.7024</v>
       </c>
       <c r="R39" t="n">
-        <v>0.7803</v>
+        <v>0.781</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -6490,13 +6468,13 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>0.7036</v>
+        <v>0.7014</v>
       </c>
       <c r="V39" t="n">
-        <v>0.7211</v>
+        <v>0.7195</v>
       </c>
       <c r="W39" t="n">
-        <v>0.7264</v>
+        <v>0.726</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -6509,14 +6487,14 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>38.04</v>
+        <v>39.12</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.71</v>
+        <v>0.7096</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:10</t>
+          <t>2026-08-03 08:43:51</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6554,7 +6532,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6568,7 +6546,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4.61</v>
+        <v>4.66</v>
       </c>
       <c r="E40" t="n">
         <v>0.09080000000000001</v>
@@ -6588,10 +6566,10 @@
         <v>6225072</v>
       </c>
       <c r="J40" t="n">
-        <v>8677976</v>
+        <v>1878538</v>
       </c>
       <c r="K40" t="n">
-        <v>1.394</v>
+        <v>0.302</v>
       </c>
       <c r="L40" t="n">
         <v>4755720</v>
@@ -6609,10 +6587,10 @@
         <v>4.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.712</v>
+        <v>3.731</v>
       </c>
       <c r="R40" t="n">
-        <v>2.9679</v>
+        <v>2.9799</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -6625,13 +6603,13 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>4.0871</v>
+        <v>4.1417</v>
       </c>
       <c r="V40" t="n">
-        <v>3.7829</v>
+        <v>3.8173</v>
       </c>
       <c r="W40" t="n">
-        <v>3.098</v>
+        <v>3.1136</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -6644,21 +6622,21 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>68.76000000000001</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.2602</v>
+        <v>4.2704</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>4.2602</v>
+        <v>4.2704</v>
       </c>
       <c r="AD40" t="n">
-        <v>4.1295</v>
+        <v>4.2485</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -6666,7 +6644,7 @@
         </is>
       </c>
       <c r="AF40" t="n">
-        <v>4.7631</v>
+        <v>4.8427</v>
       </c>
       <c r="AG40" t="n">
         <v>4.9278</v>
@@ -6676,26 +6654,26 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 4.76; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
+          <t>TP1: Bollinger Upper Band at 4.84; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>3.85</v>
+        <v>26.16</v>
       </c>
       <c r="AK40" t="n">
-        <v>5.11</v>
+        <v>30.05</v>
       </c>
       <c r="AL40" t="n">
-        <v>7.47</v>
+        <v>44.17</v>
       </c>
       <c r="AM40" t="n">
-        <v>11.81</v>
+        <v>13.4</v>
       </c>
       <c r="AN40" t="n">
-        <v>15.67</v>
+        <v>15.39</v>
       </c>
       <c r="AO40" t="n">
-        <v>22.92</v>
+        <v>22.63</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -6704,14 +6682,14 @@
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.7))</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6725,7 +6703,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>53.2</v>
+        <v>52.97</v>
       </c>
       <c r="E41" t="n">
         <v>1.0437</v>
@@ -6745,10 +6723,10 @@
         <v>2164018</v>
       </c>
       <c r="J41" t="n">
-        <v>1005883</v>
+        <v>310505</v>
       </c>
       <c r="K41" t="n">
-        <v>0.465</v>
+        <v>0.143</v>
       </c>
       <c r="L41" t="n">
         <v>1300532</v>
@@ -6766,10 +6744,10 @@
         <v>48.49</v>
       </c>
       <c r="Q41" t="n">
-        <v>47.401</v>
+        <v>47.4864</v>
       </c>
       <c r="R41" t="n">
-        <v>36.8791</v>
+        <v>37.0481</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6782,13 +6760,13 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>49.323</v>
+        <v>49.6703</v>
       </c>
       <c r="V41" t="n">
-        <v>47.3765</v>
+        <v>47.5959</v>
       </c>
       <c r="W41" t="n">
-        <v>38.5355</v>
+        <v>38.6792</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -6801,58 +6779,58 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>72.41</v>
+        <v>70.78</v>
       </c>
       <c r="AA41" t="n">
-        <v>48.7998</v>
+        <v>48.8559</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>48.7998</v>
+        <v>48.8559</v>
       </c>
       <c r="AD41" t="n">
-        <v>48.2733</v>
+        <v>48.7632</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>stop at Classic S1</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AF41" t="n">
         <v>53.2048</v>
       </c>
       <c r="AG41" t="n">
-        <v>53.363</v>
+        <v>53.9614</v>
       </c>
       <c r="AH41" t="n">
         <v>54.8285</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 53.36; TP3: Fibonacci R2 at 54.83</t>
+          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 53.96; TP3: Fibonacci R2 at 54.83</t>
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>8.369999999999999</v>
+        <v>46.92</v>
       </c>
       <c r="AK41" t="n">
-        <v>8.67</v>
+        <v>55.09</v>
       </c>
       <c r="AL41" t="n">
-        <v>11.45</v>
+        <v>64.44</v>
       </c>
       <c r="AM41" t="n">
-        <v>9.029999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="AN41" t="n">
-        <v>9.35</v>
+        <v>10.45</v>
       </c>
       <c r="AO41" t="n">
-        <v>12.35</v>
+        <v>12.22</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -6861,14 +6839,14 @@
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.4); entry: enhanced entry at VWMA (overbought (RSI: 72.4))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.8); entry: enhanced entry at VWMA (overbought (RSI: 70.8))</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6882,7 +6860,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>37.75</v>
+        <v>37.24</v>
       </c>
       <c r="E42" t="n">
         <v>0.7232</v>
@@ -6902,10 +6880,10 @@
         <v>1868672</v>
       </c>
       <c r="J42" t="n">
-        <v>2565066</v>
+        <v>620342</v>
       </c>
       <c r="K42" t="n">
-        <v>1.373</v>
+        <v>0.332</v>
       </c>
       <c r="L42" t="n">
         <v>910122</v>
@@ -6923,10 +6901,10 @@
         <v>38.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>38.9628</v>
+        <v>38.8184</v>
       </c>
       <c r="R42" t="n">
-        <v>35.7208</v>
+        <v>35.7588</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -6942,10 +6920,10 @@
         <v>37.2405</v>
       </c>
       <c r="V42" t="n">
-        <v>38.4796</v>
+        <v>38.431</v>
       </c>
       <c r="W42" t="n">
-        <v>36.6684</v>
+        <v>36.6741</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -6958,25 +6936,25 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>51.72</v>
+        <v>48.07</v>
       </c>
       <c r="AA42" t="n">
-        <v>37.2052</v>
+        <v>37.2356</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>37.2052</v>
+        <v>35.6602</v>
       </c>
       <c r="AD42" t="n">
-        <v>35.7208</v>
+        <v>35.4767</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>stop at 200 SMA</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AF42" t="n">
@@ -6986,7 +6964,7 @@
         <v>38.5567</v>
       </c>
       <c r="AH42" t="n">
-        <v>38.7135</v>
+        <v>38.7128</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
@@ -6994,22 +6972,22 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0.7</v>
+        <v>14.12</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.91</v>
+        <v>15.79</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.02</v>
+        <v>16.64</v>
       </c>
       <c r="AM42" t="n">
-        <v>2.81</v>
+        <v>7.26</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.63</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AO42" t="n">
-        <v>4.05</v>
+        <v>8.56</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -7018,14 +6996,14 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 51.7))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 48.1))</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7059,10 +7037,10 @@
         <v>2883990</v>
       </c>
       <c r="J43" t="n">
-        <v>3300712</v>
+        <v>1047600</v>
       </c>
       <c r="K43" t="n">
-        <v>1.144</v>
+        <v>0.363</v>
       </c>
       <c r="L43" t="n">
         <v>2388184</v>
@@ -7080,10 +7058,10 @@
         <v>6.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.2104</v>
+        <v>6.2432</v>
       </c>
       <c r="R43" t="n">
-        <v>5.8577</v>
+        <v>5.8568</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -7096,13 +7074,13 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>6.6777</v>
+        <v>6.7217</v>
       </c>
       <c r="V43" t="n">
-        <v>6.2759</v>
+        <v>6.3097</v>
       </c>
       <c r="W43" t="n">
-        <v>5.6762</v>
+        <v>5.6907</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -7118,18 +7096,18 @@
         <v>65.81999999999999</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.7256</v>
+        <v>6.7388</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>6.7256</v>
+        <v>6.7388</v>
       </c>
       <c r="AD43" t="n">
-        <v>6.4854</v>
+        <v>6.549</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -7140,33 +7118,33 @@
         <v>7.2151</v>
       </c>
       <c r="AG43" t="n">
+        <v>7.288</v>
+      </c>
+      <c r="AH43" t="n">
         <v>7.45</v>
       </c>
-      <c r="AH43" t="n">
-        <v>7.5149</v>
-      </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.22; TP2: Classic R1 at 7.45; TP3: Fibonacci R2 at 7.51</t>
+          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.29; TP3: Classic R1 at 7.45</t>
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>2.04</v>
+        <v>2.51</v>
       </c>
       <c r="AK43" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="AL43" t="n">
-        <v>3.29</v>
+        <v>3.75</v>
       </c>
       <c r="AM43" t="n">
-        <v>7.28</v>
+        <v>7.07</v>
       </c>
       <c r="AN43" t="n">
-        <v>10.77</v>
+        <v>8.15</v>
       </c>
       <c r="AO43" t="n">
-        <v>11.74</v>
+        <v>10.55</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -7182,7 +7160,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7196,7 +7174,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>399</v>
+        <v>386.99</v>
       </c>
       <c r="E44" t="n">
         <v>7.7408</v>
@@ -7216,10 +7194,10 @@
         <v>33705</v>
       </c>
       <c r="J44" t="n">
-        <v>211589</v>
+        <v>46270</v>
       </c>
       <c r="K44" t="n">
-        <v>6.278</v>
+        <v>1.373</v>
       </c>
       <c r="L44" t="n">
         <v>12577</v>
@@ -7237,10 +7215,10 @@
         <v>396</v>
       </c>
       <c r="Q44" t="n">
-        <v>361.1776</v>
+        <v>361.342</v>
       </c>
       <c r="R44" t="n">
-        <v>341.8762</v>
+        <v>342.3811</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7253,13 +7231,13 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>369.9545</v>
+        <v>371.5769</v>
       </c>
       <c r="V44" t="n">
-        <v>362.2072</v>
+        <v>363.1791</v>
       </c>
       <c r="W44" t="n">
-        <v>320.8324</v>
+        <v>321.4907</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -7272,21 +7250,21 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>67.48999999999999</v>
+        <v>59.56</v>
       </c>
       <c r="AA44" t="n">
-        <v>380.9074</v>
+        <v>381.193</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC44" t="n">
         <v>382</v>
       </c>
       <c r="AD44" t="n">
-        <v>361.44</v>
+        <v>362.8512</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -7294,37 +7272,37 @@
         </is>
       </c>
       <c r="AF44" t="n">
+        <v>392.4141</v>
+      </c>
+      <c r="AG44" t="n">
         <v>423.2347</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AH44" t="n">
         <v>436.6533</v>
       </c>
-      <c r="AH44" t="n">
-        <v>445.4187</v>
-      </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 423.23; TP2: Classic R1 at 436.65; TP3: Fibonacci R2 at 445.42</t>
+          <t>TP1: Bollinger Upper Band at 392.41; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>2.01</v>
+        <v>0.54</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="AL44" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="AM44" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AN44" t="n">
         <v>10.79</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>14.31</v>
       </c>
-      <c r="AO44" t="n">
-        <v>16.6</v>
-      </c>
       <c r="AP44" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -7332,14 +7310,14 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 67.5))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 59.6))</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7353,7 +7331,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="E45" t="n">
         <v>5.4066</v>
@@ -7373,10 +7351,10 @@
         <v>90812</v>
       </c>
       <c r="J45" t="n">
-        <v>410244</v>
+        <v>74082</v>
       </c>
       <c r="K45" t="n">
-        <v>4.517</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L45" t="n">
         <v>30216</v>
@@ -7394,10 +7372,10 @@
         <v>247.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>218.9268</v>
+        <v>220.3926</v>
       </c>
       <c r="R45" t="n">
-        <v>186.6207</v>
+        <v>187.2457</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -7410,13 +7388,13 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>241.6171</v>
+        <v>246.3203</v>
       </c>
       <c r="V45" t="n">
-        <v>222.4725</v>
+        <v>225.1599</v>
       </c>
       <c r="W45" t="n">
-        <v>182.0222</v>
+        <v>183.1066</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -7429,21 +7407,21 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>83.52</v>
+        <v>72.61</v>
       </c>
       <c r="AA45" t="n">
-        <v>253.6316</v>
+        <v>254.7748</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC45" t="n">
         <v>256.995</v>
       </c>
       <c r="AD45" t="n">
-        <v>234.8051</v>
+        <v>240.49</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -7465,13 +7443,13 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>2.3</v>
+        <v>3.09</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AL45" t="n">
-        <v>3.84</v>
+        <v>5.16</v>
       </c>
       <c r="AM45" t="n">
         <v>19.83</v>
@@ -7489,14 +7467,14 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (83.5); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 83.5))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 72.6))</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7510,7 +7488,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>7.92</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
         <v>0.1596</v>
@@ -7530,10 +7508,10 @@
         <v>2478481</v>
       </c>
       <c r="J46" t="n">
-        <v>2588085</v>
+        <v>638829</v>
       </c>
       <c r="K46" t="n">
-        <v>1.044</v>
+        <v>0.258</v>
       </c>
       <c r="L46" t="n">
         <v>2518339</v>
@@ -7551,10 +7529,10 @@
         <v>6.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.8706</v>
+        <v>6.9088</v>
       </c>
       <c r="R46" t="n">
-        <v>6.3935</v>
+        <v>6.4069</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7567,13 +7545,13 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>7.81</v>
+        <v>7.8281</v>
       </c>
       <c r="V46" t="n">
-        <v>7.1529</v>
+        <v>7.1861</v>
       </c>
       <c r="W46" t="n">
-        <v>6.3028</v>
+        <v>6.3197</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -7586,58 +7564,58 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>58.07</v>
+        <v>59.73</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.7478</v>
+        <v>7.7722</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>7.7478</v>
+        <v>7.7722</v>
       </c>
       <c r="AD46" t="n">
-        <v>6.7382</v>
+        <v>6.9676</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AF46" t="n">
         <v>8.755100000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>9.002800000000001</v>
+        <v>8.8764</v>
       </c>
       <c r="AH46" t="n">
         <v>9.2333</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 9.0; TP3: Classic R1 at 9.23</t>
+          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.88; TP3: Classic R1 at 9.23</t>
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AM46" t="n">
-        <v>13</v>
+        <v>12.65</v>
       </c>
       <c r="AN46" t="n">
-        <v>16.2</v>
+        <v>14.21</v>
       </c>
       <c r="AO46" t="n">
-        <v>19.17</v>
+        <v>18.8</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -7646,14 +7624,14 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.7))</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7667,7 +7645,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="E47" t="n">
         <v>0.0294</v>
@@ -7687,10 +7665,10 @@
         <v>39446506</v>
       </c>
       <c r="J47" t="n">
-        <v>105558462</v>
+        <v>91475072</v>
       </c>
       <c r="K47" t="n">
-        <v>2.676</v>
+        <v>2.319</v>
       </c>
       <c r="L47" t="n">
         <v>29063477</v>
@@ -7708,10 +7686,10 @@
         <v>1.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.2954</v>
+        <v>1.3008</v>
       </c>
       <c r="R47" t="n">
-        <v>1.1814</v>
+        <v>1.1856</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7724,13 +7702,13 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>1.4048</v>
+        <v>1.4186</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3299</v>
+        <v>1.3385</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1525</v>
+        <v>1.1565</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -7743,18 +7721,18 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>68.61</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.4258</v>
+        <v>1.433</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>1.4258</v>
+        <v>1.433</v>
       </c>
       <c r="AD47" t="n">
         <v>1.32</v>
@@ -7768,33 +7746,33 @@
         <v>1.5828</v>
       </c>
       <c r="AG47" t="n">
+        <v>1.6003</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.66</v>
       </c>
-      <c r="AH47" t="n">
-        <v>1.6772</v>
-      </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 1.58; TP2: Classic R1 at 1.66; TP3: Fibonacci R2 at 1.68</t>
+          <t>TP1: Fibonacci R1 at 1.58; TP2: Bollinger Upper Band at 1.6; TP3: Classic R1 at 1.66</t>
         </is>
       </c>
       <c r="AJ47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK47" t="n">
         <v>1.48</v>
       </c>
-      <c r="AK47" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AL47" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AM47" t="n">
-        <v>11.01</v>
+        <v>10.45</v>
       </c>
       <c r="AN47" t="n">
-        <v>16.42</v>
+        <v>11.68</v>
       </c>
       <c r="AO47" t="n">
-        <v>17.63</v>
+        <v>15.84</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -7803,14 +7781,14 @@
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.7); entry: enhanced entry at VWMA (overbought (RSI: 72.7))</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7824,7 +7802,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.86</v>
+        <v>0.885</v>
       </c>
       <c r="E48" t="n">
         <v>0.0164</v>
@@ -7844,10 +7822,10 @@
         <v>19600606</v>
       </c>
       <c r="J48" t="n">
-        <v>16480892</v>
+        <v>20176187</v>
       </c>
       <c r="K48" t="n">
-        <v>0.841</v>
+        <v>1.029</v>
       </c>
       <c r="L48" t="n">
         <v>22304846</v>
@@ -7865,10 +7843,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5434</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="R48" t="n">
-        <v>0.4245</v>
+        <v>0.4272</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -7881,13 +7859,13 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>0.7448</v>
+        <v>0.7581</v>
       </c>
       <c r="V48" t="n">
-        <v>0.603</v>
+        <v>0.6141</v>
       </c>
       <c r="W48" t="n">
-        <v>0.4493</v>
+        <v>0.4537</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -7900,18 +7878,18 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>74.18000000000001</v>
+        <v>75.98</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.7278</v>
+        <v>0.7428</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>0.7278</v>
+        <v>0.7428</v>
       </c>
       <c r="AD48" t="n">
         <v>0.595</v>
@@ -7928,30 +7906,30 @@
         <v>1.0187</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.0331</v>
+        <v>1.029</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 0.93; TP2: Classic R1 at 1.02; TP3: Fibonacci R2 at 1.03</t>
+          <t>TP1: Fibonacci R1 at 0.93; TP2: Classic R1 at 1.02; TP3: Bollinger Upper Band at 1.03</t>
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AM48" t="n">
-        <v>27.16</v>
+        <v>24.59</v>
       </c>
       <c r="AN48" t="n">
-        <v>39.96</v>
+        <v>37.14</v>
       </c>
       <c r="AO48" t="n">
-        <v>41.94</v>
+        <v>38.52</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -7960,14 +7938,14 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.2); entry: enhanced entry at VWMA (overbought (RSI: 74.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.0); entry: enhanced entry at VWMA (overbought (RSI: 76.0))</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7981,7 +7959,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.534</v>
+        <v>0.533</v>
       </c>
       <c r="E49" t="n">
         <v>0.0103</v>
@@ -8001,10 +7979,10 @@
         <v>20426292</v>
       </c>
       <c r="J49" t="n">
-        <v>55295778</v>
+        <v>11678035</v>
       </c>
       <c r="K49" t="n">
-        <v>2.707</v>
+        <v>0.572</v>
       </c>
       <c r="L49" t="n">
         <v>18818578</v>
@@ -8022,10 +8000,10 @@
         <v>0.53</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4457</v>
+        <v>0.4478</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4659</v>
+        <v>0.4667</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8038,13 +8016,13 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>0.4923</v>
+        <v>0.4961</v>
       </c>
       <c r="V49" t="n">
-        <v>0.4633</v>
+        <v>0.466</v>
       </c>
       <c r="W49" t="n">
-        <v>0.4421</v>
+        <v>0.443</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -8057,14 +8035,14 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>63.32</v>
+        <v>63.01</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.5157</v>
+        <v>0.517</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -8102,7 +8080,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8116,7 +8094,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>481.83</v>
+        <v>489</v>
       </c>
       <c r="E50" t="n">
         <v>9.111499999999999</v>
@@ -8136,10 +8114,10 @@
         <v>11630</v>
       </c>
       <c r="J50" t="n">
-        <v>42506</v>
+        <v>6214</v>
       </c>
       <c r="K50" t="n">
-        <v>3.655</v>
+        <v>0.534</v>
       </c>
       <c r="L50" t="n">
         <v>6840</v>
@@ -8157,10 +8135,10 @@
         <v>512</v>
       </c>
       <c r="Q50" t="n">
-        <v>396.0696</v>
+        <v>398.6898</v>
       </c>
       <c r="R50" t="n">
-        <v>300.2514</v>
+        <v>301.5876</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -8173,13 +8151,13 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>446.4005</v>
+        <v>450.4576</v>
       </c>
       <c r="V50" t="n">
-        <v>403.8523</v>
+        <v>407.1914</v>
       </c>
       <c r="W50" t="n">
-        <v>310.1043</v>
+        <v>311.8843</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -8192,21 +8170,21 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>73.87</v>
+        <v>75.64</v>
       </c>
       <c r="AA50" t="n">
-        <v>460.6768</v>
+        <v>461.8072</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>460.6768</v>
+        <v>461.8072</v>
       </c>
       <c r="AD50" t="n">
-        <v>439.5284</v>
+        <v>442.4273</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -8217,33 +8195,33 @@
         <v>501.4547</v>
       </c>
       <c r="AG50" t="n">
-        <v>507.7685</v>
+        <v>511.5489</v>
       </c>
       <c r="AH50" t="n">
         <v>518.9933</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 507.77; TP3: Classic R1 at 518.99</t>
+          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 511.55; TP3: Classic R1 at 518.99</t>
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AK50" t="n">
-        <v>2.23</v>
+        <v>2.57</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="AM50" t="n">
-        <v>8.85</v>
+        <v>8.59</v>
       </c>
       <c r="AN50" t="n">
-        <v>10.22</v>
+        <v>10.77</v>
       </c>
       <c r="AO50" t="n">
-        <v>12.66</v>
+        <v>12.38</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -8252,14 +8230,14 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.9); entry: enhanced entry at VWMA (overbought (RSI: 73.9))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.6); entry: enhanced entry at VWMA (overbought (RSI: 75.6))</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8273,7 +8251,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1246.92</v>
+        <v>1255.06</v>
       </c>
       <c r="E51" t="n">
         <v>23.8879</v>
@@ -8293,10 +8271,10 @@
         <v>2311</v>
       </c>
       <c r="J51" t="n">
-        <v>5875</v>
+        <v>1641</v>
       </c>
       <c r="K51" t="n">
-        <v>2.542</v>
+        <v>0.71</v>
       </c>
       <c r="L51" t="n">
         <v>861</v>
@@ -8314,10 +8292,10 @@
         <v>1239</v>
       </c>
       <c r="Q51" t="n">
-        <v>1162.3418</v>
+        <v>1164.0746</v>
       </c>
       <c r="R51" t="n">
-        <v>908.1762</v>
+        <v>910.9515</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8330,13 +8308,13 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>1206.1018</v>
+        <v>1210.7645</v>
       </c>
       <c r="V51" t="n">
-        <v>1144.2763</v>
+        <v>1148.6208</v>
       </c>
       <c r="W51" t="n">
-        <v>921.1415</v>
+        <v>924.4641</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -8349,21 +8327,21 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>67.26000000000001</v>
+        <v>68.87</v>
       </c>
       <c r="AA51" t="n">
-        <v>1210.3521</v>
+        <v>1212.5021</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC51" t="n">
-        <v>1210.3521</v>
+        <v>1212.5021</v>
       </c>
       <c r="AD51" t="n">
-        <v>1171.7975</v>
+        <v>1170.9559</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -8371,7 +8349,7 @@
         </is>
       </c>
       <c r="AF51" t="n">
-        <v>1252.9855</v>
+        <v>1259.3171</v>
       </c>
       <c r="AG51" t="n">
         <v>1312.2368</v>
@@ -8381,26 +8359,26 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1252.99; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
+          <t>TP1: Bollinger Upper Band at 1259.32; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK51" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="AL51" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AM51" t="n">
-        <v>3.52</v>
+        <v>3.86</v>
       </c>
       <c r="AN51" t="n">
-        <v>8.42</v>
+        <v>8.23</v>
       </c>
       <c r="AO51" t="n">
-        <v>10.82</v>
+        <v>10.62</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -8409,14 +8387,14 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.9))</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8430,7 +8408,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>244.5</v>
+        <v>244.12</v>
       </c>
       <c r="E52" t="n">
         <v>4.782</v>
@@ -8450,10 +8428,10 @@
         <v>92947</v>
       </c>
       <c r="J52" t="n">
-        <v>55095</v>
+        <v>22130</v>
       </c>
       <c r="K52" t="n">
-        <v>0.593</v>
+        <v>0.238</v>
       </c>
       <c r="L52" t="n">
         <v>39168</v>
@@ -8471,10 +8449,10 @@
         <v>245</v>
       </c>
       <c r="Q52" t="n">
-        <v>255.0494</v>
+        <v>254.6718</v>
       </c>
       <c r="R52" t="n">
-        <v>244.7297</v>
+        <v>245.2027</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8487,13 +8465,13 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>244.9224</v>
+        <v>244.846</v>
       </c>
       <c r="V52" t="n">
-        <v>250.7073</v>
+        <v>250.449</v>
       </c>
       <c r="W52" t="n">
-        <v>234.0459</v>
+        <v>234.1461</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -8506,14 +8484,14 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>47.09</v>
+        <v>46.51</v>
       </c>
       <c r="AA52" t="n">
-        <v>243.3248</v>
+        <v>243.3215</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC52" t="n">
@@ -8528,21 +8506,21 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>244.7297</v>
+        <v>245.2027</v>
       </c>
       <c r="AG52" t="n">
         <v>248.1478</v>
       </c>
       <c r="AH52" t="n">
-        <v>250.2892</v>
+        <v>250.2848</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 244.73; TP2: Fibonacci R1 at 248.15; TP3: Bollinger Upper Band at 250.29</t>
+          <t>TP1: 200 SMA at 245.2; TP2: Fibonacci R1 at 248.15; TP3: Bollinger Upper Band at 250.28</t>
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>8.52</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AK52" t="n">
         <v>11.79</v>
@@ -8551,7 +8529,7 @@
         <v>13.84</v>
       </c>
       <c r="AM52" t="n">
-        <v>3.77</v>
+        <v>3.97</v>
       </c>
       <c r="AN52" t="n">
         <v>5.22</v>
@@ -8566,14 +8544,14 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 47.1))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 46.5))</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8587,7 +8565,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>207.75</v>
+        <v>200</v>
       </c>
       <c r="E53" t="n">
         <v>3.758</v>
@@ -8607,10 +8585,10 @@
         <v>90592</v>
       </c>
       <c r="J53" t="n">
-        <v>357019</v>
+        <v>58847</v>
       </c>
       <c r="K53" t="n">
-        <v>3.941</v>
+        <v>0.65</v>
       </c>
       <c r="L53" t="n">
         <v>89582</v>
@@ -8628,10 +8606,10 @@
         <v>197.49</v>
       </c>
       <c r="Q53" t="n">
-        <v>145.1638</v>
+        <v>146.3338</v>
       </c>
       <c r="R53" t="n">
-        <v>122.5782</v>
+        <v>123.124</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8644,13 +8622,13 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>165.3117</v>
+        <v>168.6154</v>
       </c>
       <c r="V53" t="n">
-        <v>147.5709</v>
+        <v>149.627</v>
       </c>
       <c r="W53" t="n">
-        <v>119.3458</v>
+        <v>120.1484</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -8663,21 +8641,21 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>72.73</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="AA53" t="n">
-        <v>172.6528</v>
+        <v>173.3037</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>172.6528</v>
+        <v>173.3037</v>
       </c>
       <c r="AD53" t="n">
-        <v>167</v>
+        <v>172.34</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -8688,33 +8666,33 @@
         <v>208.4527</v>
       </c>
       <c r="AG53" t="n">
+        <v>212.6765</v>
+      </c>
+      <c r="AH53" t="n">
         <v>224.8967</v>
       </c>
-      <c r="AH53" t="n">
-        <v>227.944</v>
-      </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 208.45; TP2: Classic R1 at 224.9; TP3: Fibonacci R2 at 227.94</t>
+          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 212.68; TP3: Classic R1 at 224.9</t>
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>6.33</v>
+        <v>36.47</v>
       </c>
       <c r="AK53" t="n">
-        <v>9.24</v>
+        <v>40.86</v>
       </c>
       <c r="AL53" t="n">
-        <v>9.779999999999999</v>
+        <v>53.54</v>
       </c>
       <c r="AM53" t="n">
-        <v>20.74</v>
+        <v>20.28</v>
       </c>
       <c r="AN53" t="n">
-        <v>30.26</v>
+        <v>22.72</v>
       </c>
       <c r="AO53" t="n">
-        <v>32.02</v>
+        <v>29.77</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -8723,14 +8701,14 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.7); entry: enhanced entry at VWMA (overbought (RSI: 72.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.8))</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8744,7 +8722,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.2</v>
+        <v>7.24</v>
       </c>
       <c r="E54" t="n">
         <v>0.1416</v>
@@ -8764,10 +8742,10 @@
         <v>24706539</v>
       </c>
       <c r="J54" t="n">
-        <v>32961095</v>
+        <v>7067957</v>
       </c>
       <c r="K54" t="n">
-        <v>1.334</v>
+        <v>0.286</v>
       </c>
       <c r="L54" t="n">
         <v>15027796</v>
@@ -8783,10 +8761,10 @@
         <v>6.69</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6156</v>
+        <v>6.6358</v>
       </c>
       <c r="R54" t="n">
-        <v>5.8322</v>
+        <v>5.8447</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -8799,13 +8777,13 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>7.2121</v>
+        <v>7.2148</v>
       </c>
       <c r="V54" t="n">
-        <v>6.742</v>
+        <v>6.7615</v>
       </c>
       <c r="W54" t="n">
-        <v>5.7754</v>
+        <v>5.79</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -8818,25 +8796,25 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>53.4</v>
+        <v>54.46</v>
       </c>
       <c r="AA54" t="n">
-        <v>7.2661</v>
+        <v>7.2918</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC54" t="n">
         <v>6.99</v>
       </c>
       <c r="AD54" t="n">
-        <v>6.6391</v>
+        <v>6.6643</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AF54" t="n">
@@ -8846,21 +8824,21 @@
         <v>7.8167</v>
       </c>
       <c r="AH54" t="n">
-        <v>7.8885</v>
+        <v>7.8767</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.89</t>
+          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.88</t>
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="AM54" t="n">
         <v>9.41</v>
@@ -8869,7 +8847,7 @@
         <v>11.83</v>
       </c>
       <c r="AO54" t="n">
-        <v>12.85</v>
+        <v>12.69</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -8878,14 +8856,14 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.5))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8899,7 +8877,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.89</v>
+        <v>12.8</v>
       </c>
       <c r="E55" t="n">
         <v>0.2222</v>
@@ -8919,10 +8897,10 @@
         <v>3433424</v>
       </c>
       <c r="J55" t="n">
-        <v>792465</v>
+        <v>1695796</v>
       </c>
       <c r="K55" t="n">
-        <v>0.231</v>
+        <v>0.494</v>
       </c>
       <c r="L55" t="n">
         <v>757029</v>
@@ -8940,10 +8918,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>9.301</v>
+        <v>9.3728</v>
       </c>
       <c r="R55" t="n">
-        <v>6.1138</v>
+        <v>6.1614</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -8956,13 +8934,13 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>10.2546</v>
+        <v>10.497</v>
       </c>
       <c r="V55" t="n">
-        <v>9.2906</v>
+        <v>9.4283</v>
       </c>
       <c r="W55" t="n">
-        <v>6.6751</v>
+        <v>6.736</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -8975,58 +8953,58 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>74.09</v>
+        <v>78.92</v>
       </c>
       <c r="AA55" t="n">
-        <v>10.1156</v>
+        <v>10.2725</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>10.2473</v>
+        <v>10.95</v>
       </c>
       <c r="AD55" t="n">
-        <v>9.4033</v>
+        <v>10.5102</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>stop at Classic S1</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AF55" t="n">
-        <v>12.0143</v>
+        <v>13.4067</v>
       </c>
       <c r="AG55" t="n">
-        <v>12.2874</v>
+        <v>16.3367</v>
       </c>
       <c r="AH55" t="n">
-        <v>12.3333</v>
+        <v>18.3944</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 12.01; TP2: Fibonacci R2 at 12.29; TP3: Classic R1 at 12.33</t>
+          <t>TP1: Classic R2 at 13.41; TP2: Classic R3 at 16.34; TP3: Extension at 18.39</t>
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>2.09</v>
+        <v>5.59</v>
       </c>
       <c r="AK55" t="n">
-        <v>2.42</v>
+        <v>12.25</v>
       </c>
       <c r="AL55" t="n">
-        <v>2.47</v>
+        <v>16.93</v>
       </c>
       <c r="AM55" t="n">
-        <v>17.24</v>
+        <v>22.44</v>
       </c>
       <c r="AN55" t="n">
-        <v>19.91</v>
+        <v>49.19</v>
       </c>
       <c r="AO55" t="n">
-        <v>20.36</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -9035,14 +9013,14 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.1); entry: enhanced entry at Parabolic SAR (overbought (RSI: 74.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.9))</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9133,7 +9111,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC56" t="n">
@@ -9193,7 +9171,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9207,7 +9185,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>292.31</v>
+        <v>297.95</v>
       </c>
       <c r="E57" t="n">
         <v>5.7269</v>
@@ -9227,10 +9205,10 @@
         <v>367014</v>
       </c>
       <c r="J57" t="n">
-        <v>278499</v>
+        <v>63790</v>
       </c>
       <c r="K57" t="n">
-        <v>0.759</v>
+        <v>0.174</v>
       </c>
       <c r="L57" t="n">
         <v>175426</v>
@@ -9248,10 +9226,10 @@
         <v>252.69</v>
       </c>
       <c r="Q57" t="n">
-        <v>237.53</v>
+        <v>239.148</v>
       </c>
       <c r="R57" t="n">
-        <v>183.4909</v>
+        <v>184.2107</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -9264,13 +9242,13 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>266.5575</v>
+        <v>269.5472</v>
       </c>
       <c r="V57" t="n">
-        <v>240.2279</v>
+        <v>242.4915</v>
       </c>
       <c r="W57" t="n">
-        <v>184.3648</v>
+        <v>185.495</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -9283,21 +9261,21 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>75.45</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AA57" t="n">
-        <v>264.7912</v>
+        <v>265.6297</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>264.7912</v>
+        <v>265.6297</v>
       </c>
       <c r="AD57" t="n">
-        <v>258.3459</v>
+        <v>264.2685</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -9308,33 +9286,33 @@
         <v>298.94</v>
       </c>
       <c r="AG57" t="n">
-        <v>304.8566</v>
+        <v>309.6607</v>
       </c>
       <c r="AH57" t="n">
         <v>313.52</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 298.94; TP2: Bollinger Upper Band at 304.86; TP3: Fibonacci R2 at 313.52</t>
+          <t>TP1: Fibonacci R1 at 298.94; TP2: Bollinger Upper Band at 309.66; TP3: Fibonacci R2 at 313.52</t>
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>5.3</v>
+        <v>24.47</v>
       </c>
       <c r="AK57" t="n">
-        <v>6.22</v>
+        <v>32.35</v>
       </c>
       <c r="AL57" t="n">
-        <v>7.56</v>
+        <v>35.18</v>
       </c>
       <c r="AM57" t="n">
-        <v>12.9</v>
+        <v>12.54</v>
       </c>
       <c r="AN57" t="n">
-        <v>15.13</v>
+        <v>16.58</v>
       </c>
       <c r="AO57" t="n">
-        <v>18.4</v>
+        <v>18.03</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -9343,14 +9321,14 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.4); entry: enhanced entry at VWMA (overbought (RSI: 75.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.4); entry: enhanced entry at VWMA (overbought (RSI: 77.4))</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9364,7 +9342,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18.47</v>
+        <v>18.44</v>
       </c>
       <c r="E58" t="n">
         <v>0.3446</v>
@@ -9384,10 +9362,10 @@
         <v>706832</v>
       </c>
       <c r="J58" t="n">
-        <v>4188116</v>
+        <v>1864617</v>
       </c>
       <c r="K58" t="n">
-        <v>5.925</v>
+        <v>2.638</v>
       </c>
       <c r="L58" t="n">
         <v>457851</v>
@@ -9405,10 +9383,10 @@
         <v>18</v>
       </c>
       <c r="Q58" t="n">
-        <v>15.976</v>
+        <v>16.0148</v>
       </c>
       <c r="R58" t="n">
-        <v>15.614</v>
+        <v>15.6444</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9421,13 +9399,13 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>16.3771</v>
+        <v>16.5736</v>
       </c>
       <c r="V58" t="n">
-        <v>16.012</v>
+        <v>16.1072</v>
       </c>
       <c r="W58" t="n">
-        <v>14.9794</v>
+        <v>15.0138</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -9440,21 +9418,21 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>75.92</v>
+        <v>75.39</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.923</v>
+        <v>16.9896</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC58" t="n">
         <v>17.43</v>
       </c>
       <c r="AD58" t="n">
-        <v>16.0664</v>
+        <v>16.3483</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -9476,13 +9454,13 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.59</v>
+        <v>2.01</v>
       </c>
       <c r="AL58" t="n">
-        <v>1.96</v>
+        <v>2.47</v>
       </c>
       <c r="AM58" t="n">
         <v>9.51</v>
@@ -9500,14 +9478,14 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.9))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.4))</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9521,7 +9499,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.58</v>
+        <v>0.592</v>
       </c>
       <c r="E59" t="n">
         <v>0.0107</v>
@@ -9541,10 +9519,10 @@
         <v>22289607</v>
       </c>
       <c r="J59" t="n">
-        <v>37379572</v>
+        <v>19118194</v>
       </c>
       <c r="K59" t="n">
-        <v>1.677</v>
+        <v>0.858</v>
       </c>
       <c r="L59" t="n">
         <v>25821852</v>
@@ -9562,10 +9540,10 @@
         <v>0.552</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.5409</v>
+        <v>0.5437</v>
       </c>
       <c r="R59" t="n">
-        <v>0.4724</v>
+        <v>0.4731</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -9578,13 +9556,13 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>0.5744</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="V59" t="n">
-        <v>0.5453</v>
+        <v>0.5471</v>
       </c>
       <c r="W59" t="n">
-        <v>0.4854</v>
+        <v>0.4864</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -9597,25 +9575,25 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>53.32</v>
+        <v>56.47</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.5855</v>
+        <v>0.586</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-08-02 16:17:19</t>
+          <t>2026-08-03 08:43:56</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>0.5579</v>
+        <v>0.586</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.543</v>
+        <v>0.5583</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AF59" t="n">
@@ -9633,22 +9611,22 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>2.78</v>
+        <v>0.49</v>
       </c>
       <c r="AK59" t="n">
-        <v>4.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL59" t="n">
-        <v>6.56</v>
+        <v>2.52</v>
       </c>
       <c r="AM59" t="n">
-        <v>7.44</v>
+        <v>2.29</v>
       </c>
       <c r="AN59" t="n">
-        <v>11.65</v>
+        <v>6.3</v>
       </c>
       <c r="AO59" t="n">
-        <v>17.53</v>
+        <v>11.9</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -9657,7 +9635,478 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 53.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.5))</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>INFI</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>123</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.1067</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2.8411</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>120613</v>
+      </c>
+      <c r="J60" t="n">
+        <v>678473</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="L60" t="n">
+        <v>31483</v>
+      </c>
+      <c r="M60" t="n">
+        <v>111145</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O60" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="P60" t="n">
+        <v>106.99</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>100.4728</v>
+      </c>
+      <c r="R60" t="n">
+        <v>89.6511</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>105.6194</v>
+      </c>
+      <c r="V60" t="n">
+        <v>100.9863</v>
+      </c>
+      <c r="W60" t="n">
+        <v>89.0457</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>82</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>107.3772</v>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:43:56</t>
+        </is>
+      </c>
+      <c r="AC60" t="n">
+        <v>107.3772</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>104</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AF60" t="n">
+        <v>123.2533</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>143.7933</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>157.7043</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>TP1: Classic R2 at 123.25; TP2: Classic R3 at 143.79; TP3: Extension at 157.7</t>
+        </is>
+      </c>
+      <c r="AJ60" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.0); entry: enhanced entry at VWMA (overbought (RSI: 82.0))</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EPCO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.2074</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1638976</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1272326</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L61" t="n">
+        <v>592572</v>
+      </c>
+      <c r="M61" t="n">
+        <v>284973</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="O61" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="P61" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>9.5684</v>
+      </c>
+      <c r="R61" t="n">
+        <v>8.109299999999999</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>10.4811</v>
+      </c>
+      <c r="V61" t="n">
+        <v>9.8164</v>
+      </c>
+      <c r="W61" t="n">
+        <v>8.3786</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:43:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>9.059100000000001</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>stop at Fibonacci S1</t>
+        </is>
+      </c>
+      <c r="AF61" t="n">
+        <v>11.4809</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>12.0621</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.06</t>
+        </is>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.5))</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>EGAS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.0421</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="G62" t="n">
+        <v>3.9587</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>225345</v>
+      </c>
+      <c r="J62" t="n">
+        <v>987741</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4.383</v>
+      </c>
+      <c r="L62" t="n">
+        <v>85700</v>
+      </c>
+      <c r="M62" t="n">
+        <v>192662</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="O62" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="P62" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>51.1384</v>
+      </c>
+      <c r="R62" t="n">
+        <v>45.7212</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>53.6849</v>
+      </c>
+      <c r="V62" t="n">
+        <v>51.1778</v>
+      </c>
+      <c r="W62" t="n">
+        <v>46.2809</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>55.6854</v>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:43:56</t>
+        </is>
+      </c>
+      <c r="AC62" t="n">
+        <v>57.105</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>50.5423</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>stop at Parabolic SAR</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
+        <v>64.6233</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>68.38249999999999</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>66.3977</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 64.62; TP2: Extension at 68.38; TP3: Extension at 66.4</t>
+        </is>
+      </c>
+      <c r="AJ62" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 82.0))</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -658,11 +658,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="E2" t="n">
         <v>0.176</v>
@@ -679,34 +679,34 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7877205</v>
+        <v>7930246</v>
       </c>
       <c r="J2" t="n">
-        <v>9383921</v>
+        <v>19313373</v>
       </c>
       <c r="K2" t="n">
-        <v>1.191</v>
+        <v>2.435</v>
       </c>
       <c r="L2" t="n">
-        <v>3221256</v>
+        <v>3556819</v>
       </c>
       <c r="M2" t="n">
-        <v>32668440</v>
+        <v>19132005</v>
       </c>
       <c r="N2" t="n">
-        <v>10.142</v>
+        <v>5.379</v>
       </c>
       <c r="O2" t="n">
         <v>8.24</v>
       </c>
       <c r="P2" t="n">
-        <v>9.15</v>
+        <v>9.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.177199999999999</v>
+        <v>8.1752</v>
       </c>
       <c r="R2" t="n">
-        <v>7.6366</v>
+        <v>7.6361</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>8.4442</v>
+        <v>8.4346</v>
       </c>
       <c r="V2" t="n">
-        <v>8.2432</v>
+        <v>8.2393</v>
       </c>
       <c r="W2" t="n">
-        <v>7.8892</v>
+        <v>7.8882</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -738,14 +738,14 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>67.25</v>
+        <v>64.78</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.542999999999999</v>
+        <v>8.5631</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC2" t="n">
@@ -760,37 +760,37 @@
         </is>
       </c>
       <c r="AF2" t="n">
+        <v>9.1684</v>
+      </c>
+      <c r="AG2" t="n">
         <v>9.3924</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>9.416700000000001</v>
       </c>
-      <c r="AH2" t="n">
-        <v>9.923299999999999</v>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 9.39; TP2: Classic R1 at 9.42; TP3: Classic R2 at 9.92</t>
+          <t>TP1: Bollinger Upper Band at 9.17; TP2: Fibonacci R2 at 9.39; TP3: Classic R1 at 9.42</t>
         </is>
       </c>
       <c r="AJ2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AK2" t="n">
         <v>2.63</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>2.71</v>
       </c>
-      <c r="AL2" t="n">
-        <v>4.38</v>
-      </c>
       <c r="AM2" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AN2" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>9.56</v>
       </c>
-      <c r="AO2" t="n">
-        <v>15.45</v>
-      </c>
       <c r="AP2" t="inlineStr">
         <is>
           <t>Buy</t>
@@ -798,7 +798,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 67.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.8))</t>
         </is>
       </c>
     </row>
@@ -815,11 +815,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="E3" t="n">
         <v>1.1079</v>
@@ -836,22 +836,22 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>714703</v>
+        <v>713921</v>
       </c>
       <c r="J3" t="n">
-        <v>181170</v>
+        <v>796770</v>
       </c>
       <c r="K3" t="n">
-        <v>0.253</v>
+        <v>1.116</v>
       </c>
       <c r="L3" t="n">
-        <v>216885</v>
+        <v>199463</v>
       </c>
       <c r="M3" t="n">
-        <v>270098</v>
+        <v>294758</v>
       </c>
       <c r="N3" t="n">
-        <v>1.245</v>
+        <v>1.478</v>
       </c>
       <c r="O3" t="n">
         <v>54.31</v>
@@ -860,10 +860,10 @@
         <v>56.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>56.0788</v>
+        <v>56.0708</v>
       </c>
       <c r="R3" t="n">
-        <v>51.3652</v>
+        <v>51.3632</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>56.1835</v>
+        <v>56.1454</v>
       </c>
       <c r="V3" t="n">
-        <v>55.6414</v>
+        <v>55.6257</v>
       </c>
       <c r="W3" t="n">
-        <v>49.8994</v>
+        <v>49.8954</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -895,29 +895,29 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>50.81</v>
+        <v>48.27</v>
       </c>
       <c r="AA3" t="n">
-        <v>56.3266</v>
+        <v>56.2891</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>56.0788</v>
+        <v>54.4044</v>
       </c>
       <c r="AD3" t="n">
-        <v>55.4</v>
+        <v>54.31</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF3" t="n">
-        <v>57.6376</v>
+        <v>57.6186</v>
       </c>
       <c r="AG3" t="n">
         <v>57.9093</v>
@@ -927,26 +927,26 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 57.64; TP2: Fibonacci R1 at 57.91; TP3: Classic R1 at 58.33</t>
+          <t>TP1: Bollinger Upper Band at 57.62; TP2: Fibonacci R1 at 57.91; TP3: Classic R1 at 58.33</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>2.3</v>
+        <v>34.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.7</v>
+        <v>37.14</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.32</v>
+        <v>41.64</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.78</v>
+        <v>5.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.26</v>
+        <v>6.44</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.02</v>
+        <v>7.22</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.8))</t>
+          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 48.3))</t>
         </is>
       </c>
     </row>
@@ -972,11 +972,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27.27</v>
+        <v>27.5</v>
       </c>
       <c r="E4" t="n">
         <v>0.5379</v>
@@ -993,22 +993,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1535296</v>
+        <v>1531665</v>
       </c>
       <c r="J4" t="n">
-        <v>247297</v>
+        <v>971317</v>
       </c>
       <c r="K4" t="n">
-        <v>0.161</v>
+        <v>0.634</v>
       </c>
       <c r="L4" t="n">
-        <v>1063344</v>
+        <v>1061237</v>
       </c>
       <c r="M4" t="n">
-        <v>1349299</v>
+        <v>786081</v>
       </c>
       <c r="N4" t="n">
-        <v>1.269</v>
+        <v>0.741</v>
       </c>
       <c r="O4" t="n">
         <v>27.06</v>
@@ -1017,10 +1017,10 @@
         <v>28.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>27.9842</v>
+        <v>27.9888</v>
       </c>
       <c r="R4" t="n">
-        <v>26.9069</v>
+        <v>26.908</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>27.6252</v>
+        <v>27.6471</v>
       </c>
       <c r="V4" t="n">
-        <v>27.8825</v>
+        <v>27.8915</v>
       </c>
       <c r="W4" t="n">
-        <v>25.9371</v>
+        <v>25.9394</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1052,18 +1052,18 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>43.68</v>
+        <v>46.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>27.7552</v>
+        <v>27.7512</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>26.8436</v>
+        <v>26.8766</v>
       </c>
       <c r="AD4" t="n">
         <v>26.7256</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="AF4" t="n">
-        <v>27.9893</v>
+        <v>27.9916</v>
       </c>
       <c r="AG4" t="n">
         <v>28.521</v>
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>9.710000000000001</v>
+        <v>7.39</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.21</v>
+        <v>10.89</v>
       </c>
       <c r="AL4" t="n">
-        <v>14.94</v>
+        <v>11.46</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.27</v>
+        <v>4.15</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.25</v>
+        <v>6.12</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.57</v>
+        <v>6.44</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 43.7))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.8))</t>
         </is>
       </c>
     </row>
@@ -1129,11 +1129,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.34</v>
+        <v>23.49</v>
       </c>
       <c r="E5" t="n">
         <v>0.4473</v>
@@ -1150,22 +1150,22 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3187957</v>
+        <v>3194125</v>
       </c>
       <c r="J5" t="n">
-        <v>2171828</v>
+        <v>7115369</v>
       </c>
       <c r="K5" t="n">
-        <v>0.681</v>
+        <v>2.228</v>
       </c>
       <c r="L5" t="n">
-        <v>1152876</v>
+        <v>1163435</v>
       </c>
       <c r="M5" t="n">
-        <v>1483784</v>
+        <v>1526942</v>
       </c>
       <c r="N5" t="n">
-        <v>1.287</v>
+        <v>1.312</v>
       </c>
       <c r="O5" t="n">
         <v>21.87</v>
@@ -1174,10 +1174,10 @@
         <v>22.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>21.877</v>
+        <v>21.88</v>
       </c>
       <c r="R5" t="n">
-        <v>19.3498</v>
+        <v>19.3505</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1190,13 +1190,13 @@
         </is>
       </c>
       <c r="U5" t="n">
-        <v>22.5232</v>
+        <v>22.5375</v>
       </c>
       <c r="V5" t="n">
-        <v>21.9376</v>
+        <v>21.9435</v>
       </c>
       <c r="W5" t="n">
-        <v>19.4851</v>
+        <v>19.4866</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1209,18 +1209,18 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>60.31</v>
+        <v>61.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.8564</v>
+        <v>22.9109</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>22.8564</v>
+        <v>22.9109</v>
       </c>
       <c r="AD5" t="n">
         <v>21.87</v>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="AF5" t="n">
-        <v>23.6782</v>
+        <v>23.7076</v>
       </c>
       <c r="AG5" t="n">
         <v>23.7306</v>
@@ -1241,26 +1241,26 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 23.68; TP2: Fibonacci R1 at 23.73; TP3: Classic R1 at 24.34</t>
+          <t>TP1: Bollinger Upper Band at 23.71; TP2: Fibonacci R1 at 23.73; TP3: Classic R1 at 24.34</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.48</v>
+        <v>6.22</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
         </is>
       </c>
     </row>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>298.55</v>
+        <v>297.01</v>
       </c>
       <c r="E6" t="n">
         <v>5.8491</v>
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>306304</v>
+        <v>306408</v>
       </c>
       <c r="J6" t="n">
-        <v>45910</v>
+        <v>106507</v>
       </c>
       <c r="K6" t="n">
-        <v>0.15</v>
+        <v>0.348</v>
       </c>
       <c r="L6" t="n">
-        <v>54499</v>
+        <v>53250</v>
       </c>
       <c r="M6" t="n">
-        <v>26250</v>
+        <v>69078</v>
       </c>
       <c r="N6" t="n">
-        <v>0.482</v>
+        <v>1.297</v>
       </c>
       <c r="O6" t="n">
         <v>294.5</v>
@@ -1331,10 +1331,10 @@
         <v>302.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>304.3568</v>
+        <v>304.326</v>
       </c>
       <c r="R6" t="n">
-        <v>258.4452</v>
+        <v>258.4375</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         </is>
       </c>
       <c r="U6" t="n">
-        <v>298.7425</v>
+        <v>298.5959</v>
       </c>
       <c r="V6" t="n">
-        <v>299.3531</v>
+        <v>299.2927</v>
       </c>
       <c r="W6" t="n">
-        <v>262.5851</v>
+        <v>262.5698</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1366,18 +1366,18 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>49.34</v>
+        <v>47.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>300.4322</v>
+        <v>300.332</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>290.429</v>
+        <v>290.3133</v>
       </c>
       <c r="AD6" t="n">
         <v>285.9946</v>
@@ -1388,36 +1388,36 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>300.2659</v>
+        <v>300.2505</v>
       </c>
       <c r="AG6" t="n">
-        <v>307.337</v>
+        <v>307.2987</v>
       </c>
       <c r="AH6" t="n">
         <v>308.3187</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 300.27; TP2: Bollinger Upper Band at 307.34; TP3: Fibonacci R1 at 308.32</t>
+          <t>TP1: 100 SMA at 300.25; TP2: Bollinger Upper Band at 307.3; TP3: Fibonacci R1 at 308.32</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.81</v>
+        <v>3.93</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.03</v>
+        <v>4.17</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.82</v>
+        <v>5.85</v>
       </c>
       <c r="AO6" t="n">
-        <v>6.16</v>
+        <v>6.2</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.3))</t>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 47.6))</t>
         </is>
       </c>
     </row>
@@ -1443,11 +1443,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.83</v>
+        <v>14.11</v>
       </c>
       <c r="E7" t="n">
         <v>0.2245</v>
@@ -1464,34 +1464,34 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5963583</v>
+        <v>5976389</v>
       </c>
       <c r="J7" t="n">
-        <v>34538230</v>
+        <v>79327908</v>
       </c>
       <c r="K7" t="n">
-        <v>5.792</v>
+        <v>13.274</v>
       </c>
       <c r="L7" t="n">
-        <v>3319555</v>
+        <v>3349388</v>
       </c>
       <c r="M7" t="n">
-        <v>1172488</v>
+        <v>6168113</v>
       </c>
       <c r="N7" t="n">
-        <v>0.353</v>
+        <v>1.842</v>
       </c>
       <c r="O7" t="n">
         <v>11.3</v>
       </c>
       <c r="P7" t="n">
-        <v>11.37</v>
+        <v>11.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.7882</v>
+        <v>11.8138</v>
       </c>
       <c r="R7" t="n">
-        <v>11.3084</v>
+        <v>11.3148</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="U7" t="n">
-        <v>11.7176</v>
+        <v>11.8395</v>
       </c>
       <c r="V7" t="n">
-        <v>11.6502</v>
+        <v>11.7004</v>
       </c>
       <c r="W7" t="n">
-        <v>11.0431</v>
+        <v>11.0559</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>71.22</v>
+        <v>80.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.9263</v>
+        <v>12.7928</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC7" t="n">
-        <v>12.185</v>
+        <v>12.7928</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.3084</v>
+        <v>11.3148</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 71.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (80.1); entry: enhanced entry at VWMA (overbought (RSI: 80.1))</t>
         </is>
       </c>
     </row>
@@ -1578,11 +1578,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29.79</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
         <v>0.5662</v>
@@ -1599,34 +1599,34 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1257994</v>
+        <v>1258394</v>
       </c>
       <c r="J8" t="n">
-        <v>527127</v>
+        <v>1965823</v>
       </c>
       <c r="K8" t="n">
-        <v>0.419</v>
+        <v>1.562</v>
       </c>
       <c r="L8" t="n">
-        <v>514514</v>
+        <v>504608</v>
       </c>
       <c r="M8" t="n">
-        <v>390085</v>
+        <v>508379</v>
       </c>
       <c r="N8" t="n">
-        <v>0.758</v>
+        <v>1.007</v>
       </c>
       <c r="O8" t="n">
-        <v>28.5</v>
+        <v>29.1</v>
       </c>
       <c r="P8" t="n">
         <v>29.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>29.678</v>
+        <v>29.6822</v>
       </c>
       <c r="R8" t="n">
-        <v>27.0496</v>
+        <v>27.0506</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>29.485</v>
+        <v>29.505</v>
       </c>
       <c r="V8" t="n">
-        <v>29.4259</v>
+        <v>29.4341</v>
       </c>
       <c r="W8" t="n">
-        <v>27.3628</v>
+        <v>27.3648</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>52.49</v>
+        <v>54.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>29.5462</v>
+        <v>29.5847</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>29.678</v>
+        <v>29.6822</v>
       </c>
       <c r="AD8" t="n">
-        <v>28.5</v>
+        <v>29.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1686,30 +1686,30 @@
         <v>30.954</v>
       </c>
       <c r="AH8" t="n">
-        <v>31.4832</v>
+        <v>31.4974</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 30.85; TP2: Fibonacci R1 at 30.95; TP3: Bollinger Upper Band at 31.48</t>
+          <t>TP1: Classic R1 at 30.85; TP2: Fibonacci R1 at 30.95; TP3: Bollinger Upper Band at 31.5</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>2.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.08</v>
+        <v>2.18</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.53</v>
+        <v>3.12</v>
       </c>
       <c r="AM8" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="AO8" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 52.5))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 54.4))</t>
         </is>
       </c>
     </row>
@@ -1735,11 +1735,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>183.35</v>
       </c>
       <c r="E9" t="n">
         <v>3.6026</v>
@@ -1756,22 +1756,22 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>190685</v>
+        <v>188989</v>
       </c>
       <c r="J9" t="n">
-        <v>23722</v>
+        <v>66559</v>
       </c>
       <c r="K9" t="n">
-        <v>0.124</v>
+        <v>0.352</v>
       </c>
       <c r="L9" t="n">
-        <v>35126</v>
+        <v>33725</v>
       </c>
       <c r="M9" t="n">
-        <v>66942</v>
+        <v>32298</v>
       </c>
       <c r="N9" t="n">
-        <v>1.906</v>
+        <v>0.958</v>
       </c>
       <c r="O9" t="n">
         <v>175</v>
@@ -1780,10 +1780,10 @@
         <v>185.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>182.5628</v>
+        <v>182.5298</v>
       </c>
       <c r="R9" t="n">
-        <v>161.4491</v>
+        <v>161.4409</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>182.8947</v>
+        <v>182.7376</v>
       </c>
       <c r="V9" t="n">
-        <v>182.3481</v>
+        <v>182.2833</v>
       </c>
       <c r="W9" t="n">
-        <v>157.3813</v>
+        <v>157.3649</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1815,18 +1815,18 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>54.17</v>
+        <v>51.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>183.963</v>
+        <v>183.9291</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>183.963</v>
+        <v>182.5298</v>
       </c>
       <c r="AD9" t="n">
         <v>175</v>
@@ -1837,36 +1837,36 @@
         </is>
       </c>
       <c r="AF9" t="n">
+        <v>184.4084</v>
+      </c>
+      <c r="AG9" t="n">
         <v>192.0267</v>
       </c>
-      <c r="AG9" t="n">
-        <v>192.4687</v>
-      </c>
       <c r="AH9" t="n">
-        <v>194.9533</v>
+        <v>192.3239</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 192.03; TP2: Bollinger Upper Band at 192.47; TP3: Classic R1 at 194.95</t>
+          <t>TP1: 100 SMA at 184.41; TP2: Fibonacci R1 at 192.03; TP3: Bollinger Upper Band at 192.32</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0.9</v>
+        <v>0.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.95</v>
+        <v>1.26</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.38</v>
+        <v>1.03</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.62</v>
+        <v>5.2</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.97</v>
+        <v>5.37</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 54.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 51.6))</t>
         </is>
       </c>
     </row>
@@ -1892,11 +1892,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>710.01</v>
+        <v>695.2</v>
       </c>
       <c r="E10" t="n">
         <v>1.4031</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>51604</v>
+        <v>320375</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>724.7796</v>
+        <v>724.4834</v>
       </c>
       <c r="R10" t="n">
-        <v>544.4338</v>
+        <v>544.3598</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>711.4417</v>
+        <v>710.0312</v>
       </c>
       <c r="V10" t="n">
-        <v>697.7431</v>
+        <v>697.1623</v>
       </c>
       <c r="W10" t="n">
-        <v>566.6434</v>
+        <v>566.496</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1958,29 +1958,29 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>49.29</v>
+        <v>43.16</v>
       </c>
       <c r="AA10" t="n">
-        <v>701.0931</v>
+        <v>700.5961</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>688.154</v>
+        <v>683.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>683.8</v>
+        <v>678.2089</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>stop at Classic S1</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AF10" t="n">
-        <v>727.2512</v>
+        <v>726.5271</v>
       </c>
       <c r="AG10" t="n">
         <v>728.646</v>
@@ -1990,26 +1990,26 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 727.25; TP2: Fibonacci R1 at 728.65; TP3: Classic R1 at 736.8</t>
+          <t>TP1: Bollinger Upper Band at 726.53; TP2: Fibonacci R1 at 728.65; TP3: Classic R1 at 736.8</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>8.98</v>
+        <v>7.64</v>
       </c>
       <c r="AK10" t="n">
-        <v>9.300000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="AL10" t="n">
-        <v>11.17</v>
+        <v>9.48</v>
       </c>
       <c r="AM10" t="n">
-        <v>5.68</v>
+        <v>6.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.88</v>
+        <v>6.56</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.07</v>
+        <v>7.75</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 49.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Classic S1 (neutral (RSI: 43.2))</t>
         </is>
       </c>
     </row>
@@ -2035,11 +2035,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>23.08</v>
       </c>
       <c r="E11" t="n">
         <v>0.4463</v>
@@ -2056,34 +2056,34 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1198269</v>
+        <v>1199694</v>
       </c>
       <c r="J11" t="n">
-        <v>370717</v>
+        <v>2151889</v>
       </c>
       <c r="K11" t="n">
-        <v>0.309</v>
+        <v>1.794</v>
       </c>
       <c r="L11" t="n">
-        <v>608115</v>
+        <v>570452</v>
       </c>
       <c r="M11" t="n">
-        <v>125634</v>
+        <v>929878</v>
       </c>
       <c r="N11" t="n">
-        <v>0.207</v>
+        <v>1.63</v>
       </c>
       <c r="O11" t="n">
-        <v>22.6</v>
+        <v>22.65</v>
       </c>
       <c r="P11" t="n">
-        <v>22.8</v>
+        <v>23.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.9208</v>
+        <v>22.9224</v>
       </c>
       <c r="R11" t="n">
-        <v>22.9504</v>
+        <v>22.9508</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -2096,13 +2096,13 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>22.9252</v>
+        <v>22.9328</v>
       </c>
       <c r="V11" t="n">
-        <v>22.9219</v>
+        <v>22.925</v>
       </c>
       <c r="W11" t="n">
-        <v>22.9082</v>
+        <v>22.909</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2115,14 +2115,14 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>51.56</v>
+        <v>53.01</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.9775</v>
+        <v>22.9864</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
     </row>
@@ -2170,11 +2170,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.82</v>
+        <v>14.95</v>
       </c>
       <c r="E12" t="n">
         <v>0.2863</v>
@@ -2191,22 +2191,22 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>17325026</v>
+        <v>17293558</v>
       </c>
       <c r="J12" t="n">
-        <v>6964273</v>
+        <v>16828713</v>
       </c>
       <c r="K12" t="n">
-        <v>0.402</v>
+        <v>0.973</v>
       </c>
       <c r="L12" t="n">
-        <v>7241829</v>
+        <v>6525912</v>
       </c>
       <c r="M12" t="n">
-        <v>7782507</v>
+        <v>2721974</v>
       </c>
       <c r="N12" t="n">
-        <v>1.075</v>
+        <v>0.417</v>
       </c>
       <c r="O12" t="n">
         <v>14.43</v>
@@ -2215,10 +2215,10 @@
         <v>14.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.8746</v>
+        <v>14.8772</v>
       </c>
       <c r="R12" t="n">
-        <v>10.4091</v>
+        <v>10.4097</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="U12" t="n">
-        <v>14.7632</v>
+        <v>14.7756</v>
       </c>
       <c r="V12" t="n">
-        <v>14.2968</v>
+        <v>14.3019</v>
       </c>
       <c r="W12" t="n">
-        <v>11.2439</v>
+        <v>11.2452</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2250,25 +2250,25 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>51.71</v>
+        <v>54.06</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.8411</v>
+        <v>14.8475</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>14.4304</v>
+        <v>14.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.43</v>
+        <v>14.4308</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AF12" t="n">
@@ -2278,39 +2278,39 @@
         <v>15.1467</v>
       </c>
       <c r="AH12" t="n">
-        <v>15.1596</v>
+        <v>15.1722</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 15.14; TP2: Classic R1 at 15.15; TP3: Bollinger Upper Band at 15.16</t>
+          <t>TP1: Fibonacci R1 at 15.14; TP2: Classic R1 at 15.15; TP3: Bollinger Upper Band at 15.17</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1813.69</v>
+        <v>0.57</v>
       </c>
       <c r="AK12" t="n">
-        <v>1835.21</v>
+        <v>0.59</v>
       </c>
       <c r="AL12" t="n">
-        <v>1868.26</v>
+        <v>0.65</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.91</v>
+        <v>1.74</v>
       </c>
       <c r="AN12" t="n">
-        <v>4.96</v>
+        <v>1.79</v>
       </c>
       <c r="AO12" t="n">
-        <v>5.05</v>
+        <v>1.96</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 51.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.1))</t>
         </is>
       </c>
     </row>
@@ -2327,11 +2327,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>113.5</v>
+        <v>107.3</v>
       </c>
       <c r="E13" t="n">
         <v>2.0459</v>
@@ -2348,34 +2348,34 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1021769</v>
+        <v>1025038</v>
       </c>
       <c r="J13" t="n">
-        <v>393605</v>
+        <v>1293622</v>
       </c>
       <c r="K13" t="n">
-        <v>0.385</v>
+        <v>1.262</v>
       </c>
       <c r="L13" t="n">
-        <v>352101</v>
+        <v>367755</v>
       </c>
       <c r="M13" t="n">
-        <v>296050</v>
+        <v>1324852</v>
       </c>
       <c r="N13" t="n">
-        <v>0.841</v>
+        <v>3.603</v>
       </c>
       <c r="O13" t="n">
         <v>93.01000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>112.98</v>
+        <v>101.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>97.0926</v>
+        <v>96.9686</v>
       </c>
       <c r="R13" t="n">
-        <v>80.1301</v>
+        <v>80.09910000000001</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="U13" t="n">
-        <v>102.7643</v>
+        <v>102.1738</v>
       </c>
       <c r="V13" t="n">
-        <v>98.2304</v>
+        <v>97.9872</v>
       </c>
       <c r="W13" t="n">
-        <v>81.81399999999999</v>
+        <v>81.75230000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2407,18 +2407,18 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>76.2</v>
+        <v>61.41</v>
       </c>
       <c r="AA13" t="n">
-        <v>102.2592</v>
+        <v>102.3653</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC13" t="n">
-        <v>102.2592</v>
+        <v>102.3653</v>
       </c>
       <c r="AD13" t="n">
         <v>102.1</v>
@@ -2429,36 +2429,36 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>117.1867</v>
+        <v>107.311</v>
       </c>
       <c r="AG13" t="n">
-        <v>133.1667</v>
+        <v>110.0319</v>
       </c>
       <c r="AH13" t="n">
-        <v>144.9733</v>
+        <v>110.3933</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 117.19; TP2: Classic R3 at 133.17; TP3: Extension at 144.97</t>
+          <t>TP1: Fibonacci R1 at 107.31; TP2: Bollinger Upper Band at 110.03; TP3: Classic R1 at 110.39</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>93.75</v>
+        <v>18.64</v>
       </c>
       <c r="AK13" t="n">
-        <v>194.12</v>
+        <v>28.9</v>
       </c>
       <c r="AL13" t="n">
-        <v>268.27</v>
+        <v>30.26</v>
       </c>
       <c r="AM13" t="n">
-        <v>14.6</v>
+        <v>4.83</v>
       </c>
       <c r="AN13" t="n">
-        <v>30.22</v>
+        <v>7.49</v>
       </c>
       <c r="AO13" t="n">
-        <v>41.77</v>
+        <v>7.84</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.2); entry: enhanced entry at VWMA (overbought (RSI: 76.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
         </is>
       </c>
     </row>
@@ -2484,11 +2484,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.7</v>
+        <v>6.29</v>
       </c>
       <c r="E14" t="n">
         <v>0.1043</v>
@@ -2505,34 +2505,34 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12075718</v>
+        <v>12224958</v>
       </c>
       <c r="J14" t="n">
-        <v>21019306</v>
+        <v>87656166</v>
       </c>
       <c r="K14" t="n">
-        <v>1.741</v>
+        <v>7.17</v>
       </c>
       <c r="L14" t="n">
-        <v>5009453</v>
+        <v>5910925</v>
       </c>
       <c r="M14" t="n">
-        <v>7853283</v>
+        <v>40168665</v>
       </c>
       <c r="N14" t="n">
-        <v>1.568</v>
+        <v>6.796</v>
       </c>
       <c r="O14" t="n">
         <v>5.04</v>
       </c>
       <c r="P14" t="n">
-        <v>5.38</v>
+        <v>5.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.0854</v>
+        <v>5.0972</v>
       </c>
       <c r="R14" t="n">
-        <v>4.0602</v>
+        <v>4.0632</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2545,13 +2545,13 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>5.1849</v>
+        <v>5.2411</v>
       </c>
       <c r="V14" t="n">
-        <v>5.0251</v>
+        <v>5.0483</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2804</v>
+        <v>4.2863</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2564,18 +2564,18 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>77.12</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.3015</v>
+        <v>5.6244</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>5.3015</v>
+        <v>5.655</v>
       </c>
       <c r="AD14" t="n">
         <v>5.04</v>
@@ -2585,38 +2585,16 @@
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AF14" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>6.4393</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>6.239</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>TP1: Classic R3 at 6.06; TP2: Extension at 6.44; TP3: Extension at 6.24</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>14.31</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>21.46</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>17.68</v>
-      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -2624,7 +2602,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.1); entry: enhanced entry at VWMA (overbought (RSI: 77.1))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (85.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 85.1))</t>
         </is>
       </c>
     </row>
@@ -2641,11 +2619,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.08</v>
+        <v>5.05</v>
       </c>
       <c r="E15" t="n">
         <v>0.08890000000000001</v>
@@ -2662,22 +2640,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>24343135</v>
+        <v>24381688</v>
       </c>
       <c r="J15" t="n">
-        <v>9587378</v>
+        <v>15425965</v>
       </c>
       <c r="K15" t="n">
-        <v>0.394</v>
+        <v>0.633</v>
       </c>
       <c r="L15" t="n">
-        <v>15475726</v>
+        <v>15156982</v>
       </c>
       <c r="M15" t="n">
-        <v>2702724</v>
+        <v>14509599</v>
       </c>
       <c r="N15" t="n">
-        <v>0.175</v>
+        <v>0.957</v>
       </c>
       <c r="O15" t="n">
         <v>2.52</v>
@@ -2686,10 +2664,10 @@
         <v>4.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1028</v>
+        <v>3.1022</v>
       </c>
       <c r="R15" t="n">
-        <v>2.226</v>
+        <v>2.2259</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2702,13 +2680,13 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>4.0215</v>
+        <v>4.0186</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3088</v>
+        <v>3.3076</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3638</v>
+        <v>2.3635</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2721,14 +2699,14 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>82.06999999999999</v>
+        <v>81.81</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.6139</v>
+        <v>3.6264</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC15" t="n">
@@ -2743,36 +2721,36 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>5.3832</v>
+        <v>5.3827</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.389</v>
+        <v>5.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 5.38; TP2: Bollinger Upper Band at 5.39; TP3: Classic R1 at 5.4</t>
+          <t>TP1: Bollinger Upper Band at 5.38; TP2: Classic R1 at 5.4; TP3: Classic R2 at 6.3</t>
         </is>
       </c>
       <c r="AJ15" t="n">
         <v>0.65</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.67</v>
+        <v>1.29</v>
       </c>
       <c r="AM15" t="n">
-        <v>21.24</v>
+        <v>21.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>21.37</v>
+        <v>21.62</v>
       </c>
       <c r="AO15" t="n">
-        <v>21.62</v>
+        <v>41.89</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -2781,7 +2759,7 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.1); entry: enhanced entry at Parabolic SAR (overbought (RSI: 82.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.8); entry: enhanced entry at Parabolic SAR (overbought (RSI: 81.8))</t>
         </is>
       </c>
     </row>
@@ -2798,11 +2776,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.243</v>
+        <v>0.239</v>
       </c>
       <c r="E16" t="n">
         <v>0.0047</v>
@@ -2819,22 +2797,22 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>268716267</v>
+        <v>268605836</v>
       </c>
       <c r="J16" t="n">
-        <v>107618557</v>
+        <v>276496230</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4</v>
+        <v>1.029</v>
       </c>
       <c r="L16" t="n">
-        <v>153946169</v>
+        <v>154154120</v>
       </c>
       <c r="M16" t="n">
-        <v>95305232</v>
+        <v>80244813</v>
       </c>
       <c r="N16" t="n">
-        <v>0.619</v>
+        <v>0.521</v>
       </c>
       <c r="O16" t="n">
         <v>0.232</v>
@@ -2843,7 +2821,7 @@
         <v>0.265</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2208</v>
+        <v>0.2207</v>
       </c>
       <c r="R16" t="n">
         <v>0.1802</v>
@@ -2859,10 +2837,10 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>0.2379</v>
+        <v>0.2376</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2243</v>
+        <v>0.2242</v>
       </c>
       <c r="W16" t="n">
         <v>0.1927</v>
@@ -2878,18 +2856,18 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>56.99</v>
+        <v>53.84</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2396</v>
+        <v>0.2395</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>0.2396</v>
+        <v>0.2335</v>
       </c>
       <c r="AD16" t="n">
         <v>0.232</v>
@@ -2914,22 +2892,22 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.56</v>
+        <v>16.93</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.63</v>
+        <v>22.33</v>
       </c>
       <c r="AL16" t="n">
-        <v>7.47</v>
+        <v>41.67</v>
       </c>
       <c r="AM16" t="n">
-        <v>8.08</v>
+        <v>10.88</v>
       </c>
       <c r="AN16" t="n">
-        <v>11.46</v>
+        <v>14.35</v>
       </c>
       <c r="AO16" t="n">
-        <v>23.56</v>
+        <v>26.77</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -2938,7 +2916,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.0))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.8))</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2933,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2976,28 +2954,28 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>32349173</v>
+        <v>31363648</v>
       </c>
       <c r="J17" t="n">
-        <v>8455042</v>
+        <v>14906022</v>
       </c>
       <c r="K17" t="n">
-        <v>0.261</v>
+        <v>0.475</v>
       </c>
       <c r="L17" t="n">
-        <v>11262912</v>
+        <v>11458173</v>
       </c>
       <c r="M17" t="n">
-        <v>2966775</v>
+        <v>12201267</v>
       </c>
       <c r="N17" t="n">
-        <v>0.263</v>
+        <v>1.065</v>
       </c>
       <c r="O17" t="n">
         <v>1.54</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="Q17" t="n">
         <v>1.6076</v>
@@ -3038,15 +3016,15 @@
         <v>58.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.665</v>
+        <v>1.6654</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>1.665</v>
+        <v>1.6654</v>
       </c>
       <c r="AD17" t="n">
         <v>1.5879</v>
@@ -3071,22 +3049,22 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.71</v>
+        <v>5.68</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.289999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -3112,11 +3090,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37.63</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
         <v>0.7451</v>
@@ -3133,22 +3111,22 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1342299</v>
+        <v>1334297</v>
       </c>
       <c r="J18" t="n">
-        <v>189692</v>
+        <v>797746</v>
       </c>
       <c r="K18" t="n">
-        <v>0.141</v>
+        <v>0.598</v>
       </c>
       <c r="L18" t="n">
-        <v>421515</v>
+        <v>401221</v>
       </c>
       <c r="M18" t="n">
-        <v>364810</v>
+        <v>158865</v>
       </c>
       <c r="N18" t="n">
-        <v>0.865</v>
+        <v>0.396</v>
       </c>
       <c r="O18" t="n">
         <v>34.99</v>
@@ -3157,10 +3135,10 @@
         <v>38.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>37.7734</v>
+        <v>37.7608</v>
       </c>
       <c r="R18" t="n">
-        <v>30.8907</v>
+        <v>30.8875</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3173,13 +3151,13 @@
         </is>
       </c>
       <c r="U18" t="n">
-        <v>38.3292</v>
+        <v>38.2692</v>
       </c>
       <c r="V18" t="n">
-        <v>37.5081</v>
+        <v>37.4834</v>
       </c>
       <c r="W18" t="n">
-        <v>31.4839</v>
+        <v>31.4777</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3192,14 +3170,14 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>44.73</v>
+        <v>40.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>39.1917</v>
+        <v>39.1064</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC18" t="n">
@@ -3214,33 +3192,33 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>40.4363</v>
+        <v>40.4652</v>
       </c>
       <c r="AG18" t="n">
-        <v>40.4652</v>
+        <v>40.5258</v>
       </c>
       <c r="AH18" t="n">
         <v>40.6333</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 40.44; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
+          <t>TP1: Fibonacci R1 at 40.47; TP2: Bollinger Upper Band at 40.53; TP3: Classic R1 at 40.63</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="AL18" t="n">
         <v>3.95</v>
       </c>
       <c r="AM18" t="n">
-        <v>10.28</v>
+        <v>10.36</v>
       </c>
       <c r="AN18" t="n">
-        <v>10.36</v>
+        <v>10.52</v>
       </c>
       <c r="AO18" t="n">
         <v>10.81</v>
@@ -3252,7 +3230,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 44.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 40.6))</t>
         </is>
       </c>
     </row>
@@ -3269,11 +3247,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>36.95</v>
+        <v>35.87</v>
       </c>
       <c r="E19" t="n">
         <v>0.6813</v>
@@ -3290,22 +3268,22 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1230298</v>
+        <v>1232113</v>
       </c>
       <c r="J19" t="n">
-        <v>695893</v>
+        <v>1302576</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5659999999999999</v>
+        <v>1.057</v>
       </c>
       <c r="L19" t="n">
-        <v>708724</v>
+        <v>696425</v>
       </c>
       <c r="M19" t="n">
-        <v>46219</v>
+        <v>695899</v>
       </c>
       <c r="N19" t="n">
-        <v>0.065</v>
+        <v>0.999</v>
       </c>
       <c r="O19" t="n">
         <v>32.76</v>
@@ -3314,10 +3292,10 @@
         <v>38.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>30.027</v>
+        <v>30.0054</v>
       </c>
       <c r="R19" t="n">
-        <v>19.5046</v>
+        <v>19.4992</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3330,13 +3308,13 @@
         </is>
       </c>
       <c r="U19" t="n">
-        <v>35.0262</v>
+        <v>34.9233</v>
       </c>
       <c r="V19" t="n">
-        <v>30.856</v>
+        <v>30.8137</v>
       </c>
       <c r="W19" t="n">
-        <v>21.4846</v>
+        <v>21.4739</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3349,58 +3327,58 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>62.24</v>
+        <v>57.57</v>
       </c>
       <c r="AA19" t="n">
-        <v>36.1219</v>
+        <v>36.0849</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC19" t="n">
-        <v>36.1219</v>
+        <v>33.7957</v>
       </c>
       <c r="AD19" t="n">
-        <v>33.7878</v>
+        <v>33.7643</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AF19" t="n">
         <v>37.3616</v>
       </c>
       <c r="AG19" t="n">
-        <v>37.9202</v>
+        <v>37.8043</v>
       </c>
       <c r="AH19" t="n">
         <v>38.2267</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.92; TP3: Classic R1 at 38.23</t>
+          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.8; TP3: Classic R1 at 38.23</t>
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0.53</v>
+        <v>113.4</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.77</v>
+        <v>127.48</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.9</v>
+        <v>140.92</v>
       </c>
       <c r="AM19" t="n">
-        <v>3.43</v>
+        <v>10.55</v>
       </c>
       <c r="AN19" t="n">
-        <v>4.98</v>
+        <v>11.86</v>
       </c>
       <c r="AO19" t="n">
-        <v>5.83</v>
+        <v>13.11</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -3409,7 +3387,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 57.6))</t>
         </is>
       </c>
     </row>
@@ -3426,11 +3404,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
       <c r="E20" t="n">
         <v>0.2109</v>
@@ -3447,22 +3425,22 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4425370</v>
+        <v>4415186</v>
       </c>
       <c r="J20" t="n">
-        <v>337333</v>
+        <v>3269000</v>
       </c>
       <c r="K20" t="n">
-        <v>0.076</v>
+        <v>0.74</v>
       </c>
       <c r="L20" t="n">
-        <v>3053793</v>
+        <v>2705737</v>
       </c>
       <c r="M20" t="n">
-        <v>3092784</v>
+        <v>2505841</v>
       </c>
       <c r="N20" t="n">
-        <v>1.013</v>
+        <v>0.926</v>
       </c>
       <c r="O20" t="n">
         <v>7.58</v>
@@ -3471,7 +3449,7 @@
         <v>11.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.962999999999999</v>
+        <v>9.9628</v>
       </c>
       <c r="R20" t="n">
         <v>7.93</v>
@@ -3487,13 +3465,13 @@
         </is>
       </c>
       <c r="U20" t="n">
-        <v>10.6586</v>
+        <v>10.6576</v>
       </c>
       <c r="V20" t="n">
-        <v>10.0279</v>
+        <v>10.0275</v>
       </c>
       <c r="W20" t="n">
-        <v>8.2448</v>
+        <v>8.2447</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3506,18 +3484,18 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>50.61</v>
+        <v>50.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.8798</v>
+        <v>10.8661</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC20" t="n">
-        <v>10.5449</v>
+        <v>10.5425</v>
       </c>
       <c r="AD20" t="n">
         <v>10.3209</v>
@@ -3531,33 +3509,33 @@
         <v>11.0391</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.0841</v>
+        <v>11.0855</v>
       </c>
       <c r="AH20" t="n">
         <v>11.15</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.08; TP3: Classic R1 at 11.15</t>
+          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.09; TP3: Classic R1 at 11.15</t>
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="AO20" t="n">
-        <v>5.74</v>
+        <v>5.76</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -3566,7 +3544,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 50.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 50.3))</t>
         </is>
       </c>
     </row>
@@ -3583,11 +3561,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>32.6</v>
+        <v>31.8</v>
       </c>
       <c r="E21" t="n">
         <v>0.6398</v>
@@ -3604,22 +3582,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>686404</v>
+        <v>690373</v>
       </c>
       <c r="J21" t="n">
-        <v>675310</v>
+        <v>1655113</v>
       </c>
       <c r="K21" t="n">
-        <v>0.984</v>
+        <v>2.397</v>
       </c>
       <c r="L21" t="n">
-        <v>245844</v>
+        <v>245906</v>
       </c>
       <c r="M21" t="n">
-        <v>159699</v>
+        <v>75203</v>
       </c>
       <c r="N21" t="n">
-        <v>0.65</v>
+        <v>0.306</v>
       </c>
       <c r="O21" t="n">
         <v>31.5</v>
@@ -3628,10 +3606,10 @@
         <v>36.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>35.136</v>
+        <v>35.12</v>
       </c>
       <c r="R21" t="n">
-        <v>32.49</v>
+        <v>32.486</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -3644,13 +3622,13 @@
         </is>
       </c>
       <c r="U21" t="n">
-        <v>34.5039</v>
+        <v>34.4277</v>
       </c>
       <c r="V21" t="n">
-        <v>35.1948</v>
+        <v>35.1634</v>
       </c>
       <c r="W21" t="n">
-        <v>31.4417</v>
+        <v>31.4337</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3663,67 +3641,67 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>36.66</v>
+        <v>32.52</v>
       </c>
       <c r="AA21" t="n">
-        <v>35.1189</v>
+        <v>34.9385</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC21" t="n">
-        <v>31.9226</v>
+        <v>31.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>31.5</v>
+        <v>29.9767</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>35.9174</v>
+        <v>32.486</v>
       </c>
       <c r="AG21" t="n">
+        <v>35.9094</v>
+      </c>
+      <c r="AH21" t="n">
         <v>37.0467</v>
       </c>
-      <c r="AH21" t="n">
-        <v>37.3241</v>
-      </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 35.92; TP2: Classic R1 at 37.05; TP3: Fibonacci R1 at 37.32</t>
+          <t>TP1: 200 SMA at 32.49; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>9.449999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="AK21" t="n">
-        <v>12.13</v>
+        <v>2.89</v>
       </c>
       <c r="AL21" t="n">
-        <v>12.78</v>
+        <v>3.64</v>
       </c>
       <c r="AM21" t="n">
-        <v>12.51</v>
+        <v>3.13</v>
       </c>
       <c r="AN21" t="n">
-        <v>16.05</v>
+        <v>14</v>
       </c>
       <c r="AO21" t="n">
-        <v>16.92</v>
+        <v>17.61</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 36.7))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 32.5))</t>
         </is>
       </c>
     </row>
@@ -3740,11 +3718,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>240.59</v>
+        <v>279.6</v>
       </c>
       <c r="E22" t="n">
         <v>4.4235</v>
@@ -3761,22 +3739,22 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>365646</v>
+        <v>368909</v>
       </c>
       <c r="J22" t="n">
-        <v>397758</v>
+        <v>2009657</v>
       </c>
       <c r="K22" t="n">
-        <v>1.088</v>
+        <v>5.448</v>
       </c>
       <c r="L22" t="n">
-        <v>290852</v>
+        <v>301029</v>
       </c>
       <c r="M22" t="n">
-        <v>693940</v>
+        <v>482810</v>
       </c>
       <c r="N22" t="n">
-        <v>2.386</v>
+        <v>1.604</v>
       </c>
       <c r="O22" t="n">
         <v>157.1</v>
@@ -3785,10 +3763,10 @@
         <v>242</v>
       </c>
       <c r="Q22" t="n">
-        <v>181.1184</v>
+        <v>181.8986</v>
       </c>
       <c r="R22" t="n">
-        <v>125.1201</v>
+        <v>125.3152</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -3801,13 +3779,13 @@
         </is>
       </c>
       <c r="U22" t="n">
-        <v>211.7289</v>
+        <v>215.4441</v>
       </c>
       <c r="V22" t="n">
-        <v>185.3747</v>
+        <v>186.9045</v>
       </c>
       <c r="W22" t="n">
-        <v>130.2067</v>
+        <v>130.5949</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3820,58 +3798,58 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>76.23999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="AA22" t="n">
-        <v>208.3982</v>
+        <v>216.3197</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC22" t="n">
+        <v>218.305</v>
+      </c>
+      <c r="AD22" t="n">
         <v>209</v>
       </c>
-      <c r="AD22" t="n">
-        <v>180.2255</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>255.99</v>
+        <v>287.98</v>
       </c>
       <c r="AG22" t="n">
-        <v>257.9278</v>
+        <v>365.95</v>
       </c>
       <c r="AH22" t="n">
-        <v>258.1955</v>
+        <v>422.3504</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 255.99; TP2: Bollinger Upper Band at 257.93; TP3: Fibonacci R2 at 258.2</t>
+          <t>TP1: Classic R2 at 287.98; TP2: Classic R3 at 365.95; TP3: Extension at 422.35</t>
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.63</v>
+        <v>7.49</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.7</v>
+        <v>15.87</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.71</v>
+        <v>21.93</v>
       </c>
       <c r="AM22" t="n">
-        <v>22.48</v>
+        <v>31.92</v>
       </c>
       <c r="AN22" t="n">
-        <v>23.41</v>
+        <v>67.63</v>
       </c>
       <c r="AO22" t="n">
-        <v>23.54</v>
+        <v>93.47</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -3880,7 +3858,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.2); entry: enhanced entry at Parabolic SAR (overbought (RSI: 76.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (84.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 84.4))</t>
         </is>
       </c>
     </row>
@@ -3897,11 +3875,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>97.48999999999999</v>
+        <v>95.55</v>
       </c>
       <c r="E23" t="n">
         <v>1.8366</v>
@@ -3918,34 +3896,34 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>280675</v>
+        <v>281658</v>
       </c>
       <c r="J23" t="n">
-        <v>235002</v>
+        <v>371446</v>
       </c>
       <c r="K23" t="n">
-        <v>0.837</v>
+        <v>1.319</v>
       </c>
       <c r="L23" t="n">
-        <v>97939</v>
+        <v>94273</v>
       </c>
       <c r="M23" t="n">
-        <v>120900</v>
+        <v>298429</v>
       </c>
       <c r="N23" t="n">
-        <v>1.234</v>
+        <v>3.166</v>
       </c>
       <c r="O23" t="n">
         <v>87.02</v>
       </c>
       <c r="P23" t="n">
-        <v>93</v>
+        <v>97.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>89.31780000000001</v>
+        <v>89.279</v>
       </c>
       <c r="R23" t="n">
-        <v>81.53060000000001</v>
+        <v>81.5209</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -3958,13 +3936,13 @@
         </is>
       </c>
       <c r="U23" t="n">
-        <v>92.6611</v>
+        <v>92.47629999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>89.6888</v>
+        <v>89.6127</v>
       </c>
       <c r="W23" t="n">
-        <v>83.1788</v>
+        <v>83.15949999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3977,18 +3955,18 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>68.97</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="AA23" t="n">
-        <v>92.89279999999999</v>
+        <v>92.8747</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC23" t="n">
-        <v>92.89279999999999</v>
+        <v>92.8747</v>
       </c>
       <c r="AD23" t="n">
         <v>91.8</v>
@@ -3999,45 +3977,45 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>98.17959999999999</v>
+        <v>96.5592</v>
       </c>
       <c r="AG23" t="n">
+        <v>97.78919999999999</v>
+      </c>
+      <c r="AH23" t="n">
         <v>98.33</v>
       </c>
-      <c r="AH23" t="n">
-        <v>99.27079999999999</v>
-      </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 98.18; TP2: Classic R1 at 98.33; TP3: Fibonacci R2 at 99.27</t>
+          <t>TP1: Fibonacci R1 at 96.56; TP2: Bollinger Upper Band at 97.79; TP3: Classic R1 at 98.33</t>
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>4.84</v>
+        <v>3.43</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.98</v>
+        <v>4.57</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.84</v>
+        <v>5.08</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.69</v>
+        <v>3.97</v>
       </c>
       <c r="AN23" t="n">
-        <v>5.85</v>
+        <v>5.29</v>
       </c>
       <c r="AO23" t="n">
-        <v>6.87</v>
+        <v>5.87</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.8))</t>
         </is>
       </c>
     </row>
@@ -4054,11 +4032,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>43.25</v>
+        <v>43</v>
       </c>
       <c r="E24" t="n">
         <v>0.8149999999999999</v>
@@ -4075,22 +4053,22 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>397041</v>
+        <v>397511</v>
       </c>
       <c r="J24" t="n">
-        <v>532683</v>
+        <v>1350669</v>
       </c>
       <c r="K24" t="n">
-        <v>1.342</v>
+        <v>3.398</v>
       </c>
       <c r="L24" t="n">
-        <v>277385</v>
+        <v>283208</v>
       </c>
       <c r="M24" t="n">
-        <v>243334</v>
+        <v>307423</v>
       </c>
       <c r="N24" t="n">
-        <v>0.877</v>
+        <v>1.086</v>
       </c>
       <c r="O24" t="n">
         <v>36.55</v>
@@ -4099,10 +4077,10 @@
         <v>44.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>37.5754</v>
+        <v>37.5704</v>
       </c>
       <c r="R24" t="n">
-        <v>34.8774</v>
+        <v>34.8761</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -4115,13 +4093,13 @@
         </is>
       </c>
       <c r="U24" t="n">
-        <v>41.2179</v>
+        <v>41.1941</v>
       </c>
       <c r="V24" t="n">
-        <v>38.6268</v>
+        <v>38.617</v>
       </c>
       <c r="W24" t="n">
-        <v>34.1546</v>
+        <v>34.1521</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4134,21 +4112,21 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>63.17</v>
+        <v>62.33</v>
       </c>
       <c r="AA24" t="n">
-        <v>41.5869</v>
+        <v>41.6594</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC24" t="n">
-        <v>41.5869</v>
+        <v>41.6594</v>
       </c>
       <c r="AD24" t="n">
-        <v>37.9853</v>
+        <v>37.9958</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -4159,33 +4137,33 @@
         <v>44.1009</v>
       </c>
       <c r="AG24" t="n">
-        <v>45.0487</v>
+        <v>45.0132</v>
       </c>
       <c r="AH24" t="n">
         <v>45.3367</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 44.1; TP2: Bollinger Upper Band at 45.05; TP3: Classic R1 at 45.34</t>
+          <t>TP1: Fibonacci R1 at 44.1; TP2: Bollinger Upper Band at 45.01; TP3: Classic R1 at 45.34</t>
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AM24" t="n">
-        <v>6.05</v>
+        <v>5.86</v>
       </c>
       <c r="AN24" t="n">
-        <v>8.32</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AO24" t="n">
-        <v>9.02</v>
+        <v>8.83</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -4194,7 +4172,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.3))</t>
         </is>
       </c>
     </row>
@@ -4211,11 +4189,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.76</v>
+        <v>12.68</v>
       </c>
       <c r="E25" t="n">
         <v>0.2405</v>
@@ -4232,22 +4210,22 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3065911</v>
+        <v>3067925</v>
       </c>
       <c r="J25" t="n">
-        <v>1027204</v>
+        <v>1968151</v>
       </c>
       <c r="K25" t="n">
-        <v>0.335</v>
+        <v>0.642</v>
       </c>
       <c r="L25" t="n">
-        <v>1360330</v>
+        <v>1392261</v>
       </c>
       <c r="M25" t="n">
-        <v>337628</v>
+        <v>1518369</v>
       </c>
       <c r="N25" t="n">
-        <v>0.248</v>
+        <v>1.091</v>
       </c>
       <c r="O25" t="n">
         <v>10.4</v>
@@ -4256,10 +4234,10 @@
         <v>12.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.6304</v>
+        <v>10.6288</v>
       </c>
       <c r="R25" t="n">
-        <v>8.186199999999999</v>
+        <v>8.1858</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -4272,13 +4250,13 @@
         </is>
       </c>
       <c r="U25" t="n">
-        <v>11.7962</v>
+        <v>11.7886</v>
       </c>
       <c r="V25" t="n">
-        <v>10.9302</v>
+        <v>10.9271</v>
       </c>
       <c r="W25" t="n">
-        <v>8.477</v>
+        <v>8.4762</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -4291,18 +4269,18 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>71.2</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.7592</v>
+        <v>11.7749</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC25" t="n">
-        <v>11.7592</v>
+        <v>11.7749</v>
       </c>
       <c r="AD25" t="n">
         <v>11.1606</v>
@@ -4313,36 +4291,36 @@
         </is>
       </c>
       <c r="AF25" t="n">
+        <v>12.6806</v>
+      </c>
+      <c r="AG25" t="n">
         <v>12.8261</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>13.1767</v>
       </c>
-      <c r="AH25" t="n">
-        <v>13.3406</v>
-      </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 12.83; TP2: Classic R1 at 13.18; TP3: Fibonacci R2 at 13.34</t>
+          <t>TP1: Bollinger Upper Band at 12.68; TP2: Fibonacci R1 at 12.83; TP3: Classic R1 at 13.18</t>
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="AM25" t="n">
-        <v>9.07</v>
+        <v>7.69</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.05</v>
+        <v>8.93</v>
       </c>
       <c r="AO25" t="n">
-        <v>13.45</v>
+        <v>11.91</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -4351,7 +4329,7 @@
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.2); entry: enhanced entry at VWMA (overbought (RSI: 71.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.3); entry: enhanced entry at VWMA (overbought (RSI: 70.3))</t>
         </is>
       </c>
     </row>
@@ -4368,11 +4346,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>339.5</v>
+        <v>345.25</v>
       </c>
       <c r="E26" t="n">
         <v>4.7348</v>
@@ -4389,22 +4367,22 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>152954</v>
+        <v>156711</v>
       </c>
       <c r="J26" t="n">
-        <v>378734</v>
+        <v>559339</v>
       </c>
       <c r="K26" t="n">
-        <v>2.476</v>
+        <v>3.569</v>
       </c>
       <c r="L26" t="n">
-        <v>202414</v>
+        <v>228119</v>
       </c>
       <c r="M26" t="n">
-        <v>1143733</v>
+        <v>1095102</v>
       </c>
       <c r="N26" t="n">
-        <v>5.65</v>
+        <v>4.801</v>
       </c>
       <c r="O26" t="n">
         <v>70</v>
@@ -4413,10 +4391,10 @@
         <v>74.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>96.62220000000001</v>
+        <v>96.7372</v>
       </c>
       <c r="R26" t="n">
-        <v>72.5834</v>
+        <v>72.6122</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -4429,13 +4407,13 @@
         </is>
       </c>
       <c r="U26" t="n">
-        <v>160.0245</v>
+        <v>160.5721</v>
       </c>
       <c r="V26" t="n">
-        <v>113.8456</v>
+        <v>114.0711</v>
       </c>
       <c r="W26" t="n">
-        <v>76.7816</v>
+        <v>76.8389</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -4448,18 +4426,18 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>94.58</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="AA26" t="n">
-        <v>168.4464</v>
+        <v>171.2504</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>203.365</v>
+        <v>206</v>
       </c>
       <c r="AD26" t="n">
         <v>174.7604</v>
@@ -4476,30 +4454,30 @@
         <v>524.1933</v>
       </c>
       <c r="AH26" t="n">
-        <v>646.7497</v>
+        <v>645.7431</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 353.53; TP2: Classic R3 at 524.19; TP3: Extension at 646.75</t>
+          <t>TP1: Classic R2 at 353.53; TP2: Classic R3 at 524.19; TP3: Extension at 645.74</t>
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>5.25</v>
+        <v>4.72</v>
       </c>
       <c r="AK26" t="n">
-        <v>11.22</v>
+        <v>10.19</v>
       </c>
       <c r="AL26" t="n">
-        <v>15.5</v>
+        <v>14.08</v>
       </c>
       <c r="AM26" t="n">
-        <v>73.84</v>
+        <v>71.62</v>
       </c>
       <c r="AN26" t="n">
-        <v>157.76</v>
+        <v>154.46</v>
       </c>
       <c r="AO26" t="n">
-        <v>218.02</v>
+        <v>213.47</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -4508,7 +4486,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (94.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 94.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (94.7); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 94.7))</t>
         </is>
       </c>
     </row>
@@ -4525,11 +4503,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19.73</v>
+        <v>20</v>
       </c>
       <c r="E27" t="n">
         <v>0.3853</v>
@@ -4546,34 +4524,34 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>688663</v>
+        <v>686446</v>
       </c>
       <c r="J27" t="n">
-        <v>178807</v>
+        <v>2243474</v>
       </c>
       <c r="K27" t="n">
-        <v>0.26</v>
+        <v>3.268</v>
       </c>
       <c r="L27" t="n">
-        <v>188956</v>
+        <v>193759</v>
       </c>
       <c r="M27" t="n">
-        <v>506370</v>
+        <v>382870</v>
       </c>
       <c r="N27" t="n">
-        <v>2.68</v>
+        <v>1.976</v>
       </c>
       <c r="O27" t="n">
         <v>19.51</v>
       </c>
       <c r="P27" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.5496</v>
+        <v>19.555</v>
       </c>
       <c r="R27" t="n">
-        <v>19.2989</v>
+        <v>19.3002</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4586,13 +4564,13 @@
         </is>
       </c>
       <c r="U27" t="n">
-        <v>19.552</v>
+        <v>19.5777</v>
       </c>
       <c r="V27" t="n">
-        <v>19.5602</v>
+        <v>19.5708</v>
       </c>
       <c r="W27" t="n">
-        <v>18.7296</v>
+        <v>18.7323</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -4601,22 +4579,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>54.23</v>
+        <v>60.12</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.539</v>
+        <v>19.6193</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC27" t="n">
-        <v>19.5496</v>
+        <v>19.6193</v>
       </c>
       <c r="AD27" t="n">
         <v>19.51</v>
@@ -4627,7 +4605,7 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>19.9791</v>
+        <v>20.0308</v>
       </c>
       <c r="AG27" t="n">
         <v>20.0876</v>
@@ -4637,26 +4615,26 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 19.98; TP2: Fibonacci R1 at 20.09; TP3: Classic R1 at 20.21</t>
+          <t>TP1: Bollinger Upper Band at 20.03; TP2: Fibonacci R1 at 20.09; TP3: Classic R1 at 20.21</t>
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>10.85</v>
+        <v>3.76</v>
       </c>
       <c r="AK27" t="n">
-        <v>13.59</v>
+        <v>4.28</v>
       </c>
       <c r="AL27" t="n">
-        <v>16.59</v>
+        <v>5.37</v>
       </c>
       <c r="AM27" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="AO27" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -4665,7 +4643,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 54.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.1))</t>
         </is>
       </c>
     </row>
@@ -4682,11 +4660,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.72</v>
+        <v>15.5</v>
       </c>
       <c r="E28" t="n">
         <v>0.3061</v>
@@ -4703,22 +4681,22 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>922568</v>
+        <v>923595</v>
       </c>
       <c r="J28" t="n">
-        <v>327585</v>
+        <v>901528</v>
       </c>
       <c r="K28" t="n">
-        <v>0.355</v>
+        <v>0.976</v>
       </c>
       <c r="L28" t="n">
-        <v>266129</v>
+        <v>278772</v>
       </c>
       <c r="M28" t="n">
-        <v>571102</v>
+        <v>697763</v>
       </c>
       <c r="N28" t="n">
-        <v>2.146</v>
+        <v>2.503</v>
       </c>
       <c r="O28" t="n">
         <v>15.43</v>
@@ -4727,10 +4705,10 @@
         <v>15.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.3386</v>
+        <v>15.3342</v>
       </c>
       <c r="R28" t="n">
-        <v>15.2683</v>
+        <v>15.2672</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -4743,13 +4721,13 @@
         </is>
       </c>
       <c r="U28" t="n">
-        <v>15.3901</v>
+        <v>15.3692</v>
       </c>
       <c r="V28" t="n">
-        <v>15.3405</v>
+        <v>15.3319</v>
       </c>
       <c r="W28" t="n">
-        <v>14.9004</v>
+        <v>14.8982</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -4762,21 +4740,21 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>58.62</v>
+        <v>53.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.4271</v>
+        <v>15.4253</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC28" t="n">
         <v>15.43</v>
       </c>
       <c r="AD28" t="n">
-        <v>15.2683</v>
+        <v>15.2672</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4784,33 +4762,33 @@
         </is>
       </c>
       <c r="AF28" t="n">
+        <v>15.7816</v>
+      </c>
+      <c r="AG28" t="n">
         <v>15.799</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>15.8182</v>
       </c>
       <c r="AH28" t="n">
         <v>16.0667</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 15.8; TP2: Bollinger Upper Band at 15.82; TP3: Classic R1 at 16.07</t>
+          <t>TP1: Bollinger Upper Band at 15.78; TP2: Fibonacci R1 at 15.8; TP3: Classic R1 at 16.07</t>
         </is>
       </c>
       <c r="AJ28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AM28" t="n">
         <v>2.28</v>
       </c>
-      <c r="AK28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AM28" t="n">
+      <c r="AN28" t="n">
         <v>2.39</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>2.52</v>
       </c>
       <c r="AO28" t="n">
         <v>4.13</v>
@@ -4822,7 +4800,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 58.6))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 53.5))</t>
         </is>
       </c>
     </row>
@@ -4839,11 +4817,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>31.3</v>
+        <v>31.17</v>
       </c>
       <c r="E29" t="n">
         <v>0.6059</v>
@@ -4860,22 +4838,22 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1437614</v>
+        <v>1437989</v>
       </c>
       <c r="J29" t="n">
-        <v>268484</v>
+        <v>530249</v>
       </c>
       <c r="K29" t="n">
-        <v>0.187</v>
+        <v>0.369</v>
       </c>
       <c r="L29" t="n">
-        <v>531676</v>
+        <v>531102</v>
       </c>
       <c r="M29" t="n">
-        <v>296946</v>
+        <v>226346</v>
       </c>
       <c r="N29" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.426</v>
       </c>
       <c r="O29" t="n">
         <v>26.54</v>
@@ -4884,10 +4862,10 @@
         <v>36.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>28.4676</v>
+        <v>28.465</v>
       </c>
       <c r="R29" t="n">
-        <v>17.6242</v>
+        <v>17.6235</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -4900,13 +4878,13 @@
         </is>
       </c>
       <c r="U29" t="n">
-        <v>29.6794</v>
+        <v>29.667</v>
       </c>
       <c r="V29" t="n">
-        <v>27.3847</v>
+        <v>27.3796</v>
       </c>
       <c r="W29" t="n">
-        <v>19.5672</v>
+        <v>19.5659</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4919,14 +4897,14 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>66.39</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="AA29" t="n">
-        <v>29.5865</v>
+        <v>29.6087</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC29" t="n">
@@ -4944,21 +4922,21 @@
         <v>32.3265</v>
       </c>
       <c r="AG29" t="n">
-        <v>32.5883</v>
+        <v>32.5655</v>
       </c>
       <c r="AH29" t="n">
         <v>33.4067</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 32.59; TP3: Classic R1 at 33.41</t>
+          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 32.57; TP3: Classic R1 at 33.41</t>
         </is>
       </c>
       <c r="AJ29" t="n">
         <v>22.55</v>
       </c>
       <c r="AK29" t="n">
-        <v>24.74</v>
+        <v>24.55</v>
       </c>
       <c r="AL29" t="n">
         <v>31.56</v>
@@ -4967,7 +4945,7 @@
         <v>9.140000000000001</v>
       </c>
       <c r="AN29" t="n">
-        <v>10.02</v>
+        <v>9.94</v>
       </c>
       <c r="AO29" t="n">
         <v>12.78</v>
@@ -4979,7 +4957,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 66.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.7))</t>
         </is>
       </c>
     </row>
@@ -4996,11 +4974,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35.83</v>
+        <v>36.82</v>
       </c>
       <c r="E30" t="n">
         <v>0.6772</v>
@@ -5017,34 +4995,34 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>793094</v>
+        <v>793904</v>
       </c>
       <c r="J30" t="n">
-        <v>461203</v>
+        <v>1448512</v>
       </c>
       <c r="K30" t="n">
-        <v>0.582</v>
+        <v>1.825</v>
       </c>
       <c r="L30" t="n">
-        <v>825593</v>
+        <v>837459</v>
       </c>
       <c r="M30" t="n">
-        <v>869099</v>
+        <v>687912</v>
       </c>
       <c r="N30" t="n">
-        <v>1.053</v>
+        <v>0.821</v>
       </c>
       <c r="O30" t="n">
         <v>27.01</v>
       </c>
       <c r="P30" t="n">
-        <v>31.33</v>
+        <v>37</v>
       </c>
       <c r="Q30" t="n">
-        <v>29.7764</v>
+        <v>29.7962</v>
       </c>
       <c r="R30" t="n">
-        <v>26.7965</v>
+        <v>26.8014</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -5057,13 +5035,13 @@
         </is>
       </c>
       <c r="U30" t="n">
-        <v>33.261</v>
+        <v>33.3553</v>
       </c>
       <c r="V30" t="n">
-        <v>30.6854</v>
+        <v>30.7242</v>
       </c>
       <c r="W30" t="n">
-        <v>27.4668</v>
+        <v>27.4766</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -5076,58 +5054,58 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>67.62</v>
+        <v>70.47</v>
       </c>
       <c r="AA30" t="n">
-        <v>32.6535</v>
+        <v>32.7762</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC30" t="n">
-        <v>32.6535</v>
+        <v>32.7762</v>
       </c>
       <c r="AD30" t="n">
-        <v>29.4011</v>
+        <v>30.2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>36.5522</v>
+        <v>37.2443</v>
       </c>
       <c r="AG30" t="n">
-        <v>37.0381</v>
+        <v>38.3133</v>
       </c>
       <c r="AH30" t="n">
-        <v>38.3133</v>
+        <v>38.7611</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.04; TP3: Classic R1 at 38.31</t>
+          <t>TP1: Bollinger Upper Band at 37.24; TP2: Classic R1 at 38.31; TP3: Fibonacci R2 at 38.76</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.74</v>
+        <v>2.32</v>
       </c>
       <c r="AM30" t="n">
-        <v>11.94</v>
+        <v>13.63</v>
       </c>
       <c r="AN30" t="n">
-        <v>13.43</v>
+        <v>16.89</v>
       </c>
       <c r="AO30" t="n">
-        <v>17.33</v>
+        <v>18.26</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -5136,7 +5114,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
         </is>
       </c>
     </row>
@@ -5153,11 +5131,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="E31" t="n">
         <v>0.0383</v>
@@ -5174,34 +5152,34 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>34354934</v>
+        <v>34437426</v>
       </c>
       <c r="J31" t="n">
-        <v>28837890</v>
+        <v>55896003</v>
       </c>
       <c r="K31" t="n">
-        <v>0.839</v>
+        <v>1.623</v>
       </c>
       <c r="L31" t="n">
-        <v>22336100</v>
+        <v>22621100</v>
       </c>
       <c r="M31" t="n">
-        <v>39333635</v>
+        <v>23578787</v>
       </c>
       <c r="N31" t="n">
-        <v>1.761</v>
+        <v>1.042</v>
       </c>
       <c r="O31" t="n">
         <v>1.82</v>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8134</v>
+        <v>1.812</v>
       </c>
       <c r="R31" t="n">
-        <v>1.6957</v>
+        <v>1.6954</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -5214,13 +5192,13 @@
         </is>
       </c>
       <c r="U31" t="n">
-        <v>1.8972</v>
+        <v>1.8905</v>
       </c>
       <c r="V31" t="n">
-        <v>1.824</v>
+        <v>1.8213</v>
       </c>
       <c r="W31" t="n">
-        <v>1.63</v>
+        <v>1.6293</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -5233,18 +5211,18 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>64.78</v>
+        <v>57.32</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9125</v>
+        <v>1.9111</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC31" t="n">
-        <v>1.9125</v>
+        <v>1.9111</v>
       </c>
       <c r="AD31" t="n">
         <v>1.8454</v>
@@ -5255,45 +5233,45 @@
         </is>
       </c>
       <c r="AF31" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.0413</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
         <v>2.0833</v>
       </c>
-      <c r="AH31" t="n">
-        <v>2.1121</v>
-      </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 2.04; TP2: Classic R1 at 2.08; TP3: Fibonacci R2 at 2.11</t>
+          <t>TP1: Bollinger Upper Band at 1.98; TP2: Fibonacci R1 at 2.04; TP3: Classic R1 at 2.08</t>
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="AM31" t="n">
-        <v>6.74</v>
+        <v>3.8</v>
       </c>
       <c r="AN31" t="n">
-        <v>8.93</v>
+        <v>6.81</v>
       </c>
       <c r="AO31" t="n">
-        <v>10.44</v>
+        <v>9.01</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.3))</t>
         </is>
       </c>
     </row>
@@ -5310,11 +5288,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.91</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E32" t="n">
         <v>0.1931</v>
@@ -5331,34 +5309,34 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5521781</v>
+        <v>5516330</v>
       </c>
       <c r="J32" t="n">
-        <v>668369</v>
+        <v>2908950</v>
       </c>
       <c r="K32" t="n">
-        <v>0.121</v>
+        <v>0.527</v>
       </c>
       <c r="L32" t="n">
-        <v>1231880</v>
+        <v>1206295</v>
       </c>
       <c r="M32" t="n">
-        <v>1436831</v>
+        <v>1560722</v>
       </c>
       <c r="N32" t="n">
-        <v>1.166</v>
+        <v>1.294</v>
       </c>
       <c r="O32" t="n">
         <v>9.73</v>
       </c>
       <c r="P32" t="n">
-        <v>9.84</v>
+        <v>9.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.6442</v>
+        <v>9.641999999999999</v>
       </c>
       <c r="R32" t="n">
-        <v>9.6365</v>
+        <v>9.635999999999999</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -5371,13 +5349,13 @@
         </is>
       </c>
       <c r="U32" t="n">
-        <v>9.7668</v>
+        <v>9.756399999999999</v>
       </c>
       <c r="V32" t="n">
-        <v>9.663</v>
+        <v>9.6587</v>
       </c>
       <c r="W32" t="n">
-        <v>9.481199999999999</v>
+        <v>9.4801</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -5390,29 +5368,29 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>56.47</v>
+        <v>52.62</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.8126</v>
+        <v>9.811299999999999</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>9.859999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="AD32" t="n">
-        <v>9.73</v>
+        <v>9.66</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>10.091</v>
+        <v>10.0775</v>
       </c>
       <c r="AG32" t="n">
         <v>10.2191</v>
@@ -5422,26 +5400,26 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 10.09; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
+          <t>TP1: Bollinger Upper Band at 10.08; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.78</v>
+        <v>4.96</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.76</v>
+        <v>6.99</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.31</v>
+        <v>8</v>
       </c>
       <c r="AM32" t="n">
-        <v>2.34</v>
+        <v>3.57</v>
       </c>
       <c r="AN32" t="n">
-        <v>3.64</v>
+        <v>5.03</v>
       </c>
       <c r="AO32" t="n">
-        <v>4.36</v>
+        <v>5.76</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -5450,7 +5428,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 56.5))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 52.6))</t>
         </is>
       </c>
     </row>
@@ -5467,11 +5445,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9.74</v>
+        <v>9.65</v>
       </c>
       <c r="E33" t="n">
         <v>0.1856</v>
@@ -5488,34 +5466,34 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2591517</v>
+        <v>2598810</v>
       </c>
       <c r="J33" t="n">
-        <v>1851674</v>
+        <v>3344129</v>
       </c>
       <c r="K33" t="n">
-        <v>0.715</v>
+        <v>1.287</v>
       </c>
       <c r="L33" t="n">
-        <v>979317</v>
+        <v>1017025</v>
       </c>
       <c r="M33" t="n">
-        <v>821706</v>
+        <v>2423166</v>
       </c>
       <c r="N33" t="n">
-        <v>0.839</v>
+        <v>2.383</v>
       </c>
       <c r="O33" t="n">
-        <v>8.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="P33" t="n">
-        <v>9.6</v>
+        <v>9.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>9.228400000000001</v>
+        <v>9.226599999999999</v>
       </c>
       <c r="R33" t="n">
-        <v>8.001899999999999</v>
+        <v>8.0015</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -5528,13 +5506,13 @@
         </is>
       </c>
       <c r="U33" t="n">
-        <v>9.442299999999999</v>
+        <v>9.4337</v>
       </c>
       <c r="V33" t="n">
-        <v>9.190799999999999</v>
+        <v>9.1873</v>
       </c>
       <c r="W33" t="n">
-        <v>8.156000000000001</v>
+        <v>8.155099999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -5547,58 +5525,58 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>62.02</v>
+        <v>59.34</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.5139</v>
+        <v>9.514699999999999</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>9.5139</v>
+        <v>9.514699999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>9.2433</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF33" t="n">
-        <v>9.744300000000001</v>
+        <v>9.6737</v>
       </c>
       <c r="AG33" t="n">
+        <v>9.724500000000001</v>
+      </c>
+      <c r="AH33" t="n">
         <v>9.7933</v>
       </c>
-      <c r="AH33" t="n">
-        <v>9.8696</v>
-      </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.74; TP2: Classic R1 at 9.79; TP3: Fibonacci R2 at 9.87</t>
+          <t>TP1: Fibonacci R1 at 9.67; TP2: Bollinger Upper Band at 9.72; TP3: Classic R1 at 9.79</t>
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.03</v>
+        <v>0.98</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AM33" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.94</v>
+        <v>2.21</v>
       </c>
       <c r="AO33" t="n">
-        <v>3.74</v>
+        <v>2.93</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -5607,7 +5585,7 @@
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.0))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.3))</t>
         </is>
       </c>
     </row>
@@ -5624,11 +5602,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
       <c r="E34" t="n">
         <v>0.1973</v>
@@ -5645,22 +5623,22 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2317029</v>
+        <v>2323879</v>
       </c>
       <c r="J34" t="n">
-        <v>389133</v>
+        <v>1031422</v>
       </c>
       <c r="K34" t="n">
-        <v>0.168</v>
+        <v>0.444</v>
       </c>
       <c r="L34" t="n">
-        <v>610489</v>
+        <v>639967</v>
       </c>
       <c r="M34" t="n">
-        <v>1034878</v>
+        <v>1799335</v>
       </c>
       <c r="N34" t="n">
-        <v>1.695</v>
+        <v>2.812</v>
       </c>
       <c r="O34" t="n">
         <v>9.91</v>
@@ -5669,10 +5647,10 @@
         <v>10.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.9556</v>
+        <v>9.955399999999999</v>
       </c>
       <c r="R34" t="n">
-        <v>9.2232</v>
+        <v>9.223100000000001</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -5685,13 +5663,13 @@
         </is>
       </c>
       <c r="U34" t="n">
-        <v>10.0825</v>
+        <v>10.0815</v>
       </c>
       <c r="V34" t="n">
-        <v>9.9201</v>
+        <v>9.919700000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>9.0999</v>
+        <v>9.0998</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -5704,18 +5682,18 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>50.5</v>
+        <v>50.21</v>
       </c>
       <c r="AA34" t="n">
-        <v>10.2412</v>
+        <v>10.2386</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>9.9556</v>
+        <v>9.955399999999999</v>
       </c>
       <c r="AD34" t="n">
         <v>9.91</v>
@@ -5726,7 +5704,7 @@
         </is>
       </c>
       <c r="AF34" t="n">
-        <v>10.4102</v>
+        <v>10.4103</v>
       </c>
       <c r="AG34" t="n">
         <v>10.6503</v>
@@ -5740,13 +5718,13 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>9.970000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>15.23</v>
+        <v>15.31</v>
       </c>
       <c r="AL34" t="n">
-        <v>16.4</v>
+        <v>16.47</v>
       </c>
       <c r="AM34" t="n">
         <v>4.57</v>
@@ -5764,7 +5742,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.5))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.2))</t>
         </is>
       </c>
     </row>
@@ -5781,11 +5759,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.88</v>
+        <v>15.81</v>
       </c>
       <c r="E35" t="n">
         <v>0.3102</v>
@@ -5802,34 +5780,34 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2815474</v>
+        <v>2820657</v>
       </c>
       <c r="J35" t="n">
-        <v>522325</v>
+        <v>3350341</v>
       </c>
       <c r="K35" t="n">
-        <v>0.186</v>
+        <v>1.188</v>
       </c>
       <c r="L35" t="n">
-        <v>607874</v>
+        <v>596133</v>
       </c>
       <c r="M35" t="n">
-        <v>906202</v>
+        <v>1136222</v>
       </c>
       <c r="N35" t="n">
-        <v>1.491</v>
+        <v>1.906</v>
       </c>
       <c r="O35" t="n">
         <v>15.58</v>
       </c>
       <c r="P35" t="n">
-        <v>15.77</v>
+        <v>16.77</v>
       </c>
       <c r="Q35" t="n">
-        <v>16.4224</v>
+        <v>16.421</v>
       </c>
       <c r="R35" t="n">
-        <v>16.2584</v>
+        <v>16.258</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -5842,13 +5820,13 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>16.0168</v>
+        <v>16.0101</v>
       </c>
       <c r="V35" t="n">
-        <v>16.3335</v>
+        <v>16.3308</v>
       </c>
       <c r="W35" t="n">
-        <v>16.439</v>
+        <v>16.4383</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -5861,18 +5839,18 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>45.99</v>
+        <v>44.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>16.0413</v>
+        <v>16.0273</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>15.3648</v>
+        <v>15.3575</v>
       </c>
       <c r="AD35" t="n">
         <v>15.0075</v>
@@ -5883,13 +5861,13 @@
         </is>
       </c>
       <c r="AF35" t="n">
-        <v>16.2584</v>
+        <v>16.258</v>
       </c>
       <c r="AG35" t="n">
         <v>16.5125</v>
       </c>
       <c r="AH35" t="n">
-        <v>16.6982</v>
+        <v>16.6985</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
@@ -5897,31 +5875,31 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="AK35" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>3.73</v>
+        <v>3.83</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.82</v>
+        <v>5.86</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.47</v>
+        <v>7.52</v>
       </c>
       <c r="AO35" t="n">
-        <v>8.68</v>
+        <v>8.73</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.9))</t>
         </is>
       </c>
     </row>
@@ -5938,11 +5916,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E36" t="n">
         <v>1.5818</v>
@@ -5959,16 +5937,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>709475</v>
+        <v>714482</v>
       </c>
       <c r="J36" t="n">
-        <v>641864</v>
+        <v>1410083</v>
       </c>
       <c r="K36" t="n">
-        <v>0.905</v>
+        <v>1.974</v>
       </c>
       <c r="L36" t="n">
-        <v>349204</v>
+        <v>339265</v>
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
@@ -5981,10 +5959,10 @@
         <v>67</v>
       </c>
       <c r="Q36" t="n">
-        <v>67.06359999999999</v>
+        <v>67.0836</v>
       </c>
       <c r="R36" t="n">
-        <v>63.103</v>
+        <v>63.108</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -5997,13 +5975,13 @@
         </is>
       </c>
       <c r="U36" t="n">
-        <v>74.41630000000001</v>
+        <v>74.5115</v>
       </c>
       <c r="V36" t="n">
-        <v>68.813</v>
+        <v>68.8522</v>
       </c>
       <c r="W36" t="n">
-        <v>60.8852</v>
+        <v>60.8951</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -6016,18 +5994,18 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>60.65</v>
+        <v>62.01</v>
       </c>
       <c r="AA36" t="n">
-        <v>76.8031</v>
+        <v>76.9058</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>76.8031</v>
+        <v>76.9058</v>
       </c>
       <c r="AD36" t="n">
         <v>66.2534</v>
@@ -6041,33 +6019,33 @@
         <v>86.65989999999999</v>
       </c>
       <c r="AG36" t="n">
-        <v>89.76439999999999</v>
+        <v>89.88500000000001</v>
       </c>
       <c r="AH36" t="n">
         <v>91.63330000000001</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 89.76; TP3: Classic R1 at 91.63</t>
+          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 89.89; TP3: Classic R1 at 91.63</t>
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AM36" t="n">
-        <v>12.83</v>
+        <v>12.68</v>
       </c>
       <c r="AN36" t="n">
         <v>16.88</v>
       </c>
       <c r="AO36" t="n">
-        <v>19.31</v>
+        <v>19.15</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -6076,7 +6054,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.0))</t>
         </is>
       </c>
     </row>
@@ -6093,11 +6071,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>29.4</v>
+        <v>29.36</v>
       </c>
       <c r="E37" t="n">
         <v>0.5535</v>
@@ -6114,34 +6092,34 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2065579</v>
+        <v>2098172</v>
       </c>
       <c r="J37" t="n">
-        <v>780769</v>
+        <v>3842449</v>
       </c>
       <c r="K37" t="n">
-        <v>0.378</v>
+        <v>1.831</v>
       </c>
       <c r="L37" t="n">
-        <v>1916849</v>
+        <v>2043158</v>
       </c>
       <c r="M37" t="n">
-        <v>1400759</v>
+        <v>8379706</v>
       </c>
       <c r="N37" t="n">
-        <v>0.731</v>
+        <v>4.101</v>
       </c>
       <c r="O37" t="n">
-        <v>26.2</v>
+        <v>26.6</v>
       </c>
       <c r="P37" t="n">
         <v>28.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>24.3406</v>
+        <v>24.3398</v>
       </c>
       <c r="R37" t="n">
-        <v>20.2469</v>
+        <v>20.2467</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -6154,13 +6132,13 @@
         </is>
       </c>
       <c r="U37" t="n">
-        <v>27.36</v>
+        <v>27.3562</v>
       </c>
       <c r="V37" t="n">
-        <v>25.206</v>
+        <v>25.2044</v>
       </c>
       <c r="W37" t="n">
-        <v>21.0255</v>
+        <v>21.0251</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -6173,18 +6151,18 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>70.84</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="AA37" t="n">
-        <v>27.7843</v>
+        <v>27.8456</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>27.7843</v>
+        <v>27.8456</v>
       </c>
       <c r="AD37" t="n">
         <v>26.8104</v>
@@ -6209,22 +6187,22 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="AM37" t="n">
-        <v>7.97</v>
+        <v>7.74</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.550000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="AO37" t="n">
-        <v>15.07</v>
+        <v>14.81</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -6233,7 +6211,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.8); entry: enhanced entry at VWMA (overbought (RSI: 70.8))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
         </is>
       </c>
     </row>
@@ -6250,11 +6228,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.18</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E38" t="n">
         <v>0.1803</v>
@@ -6271,22 +6249,22 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7804852</v>
+        <v>7767167</v>
       </c>
       <c r="J38" t="n">
-        <v>986670</v>
+        <v>3076807</v>
       </c>
       <c r="K38" t="n">
-        <v>0.126</v>
+        <v>0.396</v>
       </c>
       <c r="L38" t="n">
-        <v>2251403</v>
+        <v>2126205</v>
       </c>
       <c r="M38" t="n">
-        <v>778646</v>
+        <v>1671140</v>
       </c>
       <c r="N38" t="n">
-        <v>0.346</v>
+        <v>0.786</v>
       </c>
       <c r="O38" t="n">
         <v>8.76</v>
@@ -6295,10 +6273,10 @@
         <v>9.75</v>
       </c>
       <c r="Q38" t="n">
-        <v>9.215999999999999</v>
+        <v>9.2148</v>
       </c>
       <c r="R38" t="n">
-        <v>7.2865</v>
+        <v>7.2862</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6311,13 +6289,13 @@
         </is>
       </c>
       <c r="U38" t="n">
-        <v>9.2637</v>
+        <v>9.257999999999999</v>
       </c>
       <c r="V38" t="n">
-        <v>8.984500000000001</v>
+        <v>8.982100000000001</v>
       </c>
       <c r="W38" t="n">
-        <v>7.4658</v>
+        <v>7.4652</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -6330,14 +6308,14 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>48.37</v>
+        <v>46.68</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.406499999999999</v>
+        <v>9.398899999999999</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC38" t="n">
@@ -6352,7 +6330,7 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>9.6006</v>
+        <v>9.6058</v>
       </c>
       <c r="AG38" t="n">
         <v>9.7621</v>
@@ -6362,11 +6340,11 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.6; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
+          <t>TP1: Bollinger Upper Band at 9.61; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AK38" t="n">
         <v>4.43</v>
@@ -6375,7 +6353,7 @@
         <v>4.51</v>
       </c>
       <c r="AM38" t="n">
-        <v>7.33</v>
+        <v>7.39</v>
       </c>
       <c r="AN38" t="n">
         <v>9.140000000000001</v>
@@ -6390,7 +6368,7 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 48.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.7))</t>
         </is>
       </c>
     </row>
@@ -6407,11 +6385,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.681</v>
+        <v>0.677</v>
       </c>
       <c r="E39" t="n">
         <v>0.0134</v>
@@ -6428,22 +6406,22 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>26574144</v>
+        <v>26742704</v>
       </c>
       <c r="J39" t="n">
-        <v>15102670</v>
+        <v>27554417</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5679999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L39" t="n">
-        <v>7895646</v>
+        <v>8853419</v>
       </c>
       <c r="M39" t="n">
-        <v>4530544</v>
+        <v>44832018</v>
       </c>
       <c r="N39" t="n">
-        <v>0.574</v>
+        <v>5.064</v>
       </c>
       <c r="O39" t="n">
         <v>0.675</v>
@@ -6452,7 +6430,7 @@
         <v>0.721</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.7024</v>
+        <v>0.7023</v>
       </c>
       <c r="R39" t="n">
         <v>0.781</v>
@@ -6468,13 +6446,13 @@
         </is>
       </c>
       <c r="U39" t="n">
-        <v>0.7014</v>
+        <v>0.701</v>
       </c>
       <c r="V39" t="n">
-        <v>0.7195</v>
+        <v>0.7194</v>
       </c>
       <c r="W39" t="n">
-        <v>0.726</v>
+        <v>0.7259</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -6487,14 +6465,14 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>39.12</v>
+        <v>37.38</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.7096</v>
+        <v>0.709</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:51</t>
+          <t>2026-08-03 17:13:03</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6525,7 +6503,7 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
     </row>
@@ -6542,11 +6520,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4.66</v>
+        <v>4.5</v>
       </c>
       <c r="E40" t="n">
         <v>0.09080000000000001</v>
@@ -6563,22 +6541,22 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6225072</v>
+        <v>6219845</v>
       </c>
       <c r="J40" t="n">
-        <v>1878538</v>
+        <v>6485880</v>
       </c>
       <c r="K40" t="n">
-        <v>0.302</v>
+        <v>1.043</v>
       </c>
       <c r="L40" t="n">
-        <v>4755720</v>
+        <v>4697839</v>
       </c>
       <c r="M40" t="n">
-        <v>3484900</v>
+        <v>578545</v>
       </c>
       <c r="N40" t="n">
-        <v>0.733</v>
+        <v>0.123</v>
       </c>
       <c r="O40" t="n">
         <v>3.72</v>
@@ -6587,10 +6565,10 @@
         <v>4.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.731</v>
+        <v>3.7278</v>
       </c>
       <c r="R40" t="n">
-        <v>2.9799</v>
+        <v>2.9791</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -6603,13 +6581,13 @@
         </is>
       </c>
       <c r="U40" t="n">
-        <v>4.1417</v>
+        <v>4.1265</v>
       </c>
       <c r="V40" t="n">
-        <v>3.8173</v>
+        <v>3.811</v>
       </c>
       <c r="W40" t="n">
-        <v>3.1136</v>
+        <v>3.112</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -6622,18 +6600,18 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>69.68000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.2704</v>
+        <v>4.2728</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>4.2704</v>
+        <v>4.2728</v>
       </c>
       <c r="AD40" t="n">
         <v>4.2485</v>
@@ -6644,7 +6622,7 @@
         </is>
       </c>
       <c r="AF40" t="n">
-        <v>4.8427</v>
+        <v>4.8128</v>
       </c>
       <c r="AG40" t="n">
         <v>4.9278</v>
@@ -6654,26 +6632,26 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 4.84; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
+          <t>TP1: Bollinger Upper Band at 4.81; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>26.16</v>
+        <v>22.22</v>
       </c>
       <c r="AK40" t="n">
-        <v>30.05</v>
+        <v>26.96</v>
       </c>
       <c r="AL40" t="n">
-        <v>44.17</v>
+        <v>39.67</v>
       </c>
       <c r="AM40" t="n">
-        <v>13.4</v>
+        <v>12.64</v>
       </c>
       <c r="AN40" t="n">
-        <v>15.39</v>
+        <v>15.33</v>
       </c>
       <c r="AO40" t="n">
-        <v>22.63</v>
+        <v>22.56</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -6682,7 +6660,7 @@
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.5))</t>
         </is>
       </c>
     </row>
@@ -6699,11 +6677,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>52.97</v>
+        <v>52.35</v>
       </c>
       <c r="E41" t="n">
         <v>1.0437</v>
@@ -6720,22 +6698,22 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2164018</v>
+        <v>2150582</v>
       </c>
       <c r="J41" t="n">
-        <v>310505</v>
+        <v>985068</v>
       </c>
       <c r="K41" t="n">
-        <v>0.143</v>
+        <v>0.458</v>
       </c>
       <c r="L41" t="n">
-        <v>1300532</v>
+        <v>1271079</v>
       </c>
       <c r="M41" t="n">
-        <v>3603967</v>
+        <v>640108</v>
       </c>
       <c r="N41" t="n">
-        <v>2.771</v>
+        <v>0.504</v>
       </c>
       <c r="O41" t="n">
         <v>46.02</v>
@@ -6744,10 +6722,10 @@
         <v>48.49</v>
       </c>
       <c r="Q41" t="n">
-        <v>47.4864</v>
+        <v>47.474</v>
       </c>
       <c r="R41" t="n">
-        <v>37.0481</v>
+        <v>37.045</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6760,13 +6738,13 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>49.6703</v>
+        <v>49.6113</v>
       </c>
       <c r="V41" t="n">
-        <v>47.5959</v>
+        <v>47.5716</v>
       </c>
       <c r="W41" t="n">
-        <v>38.6792</v>
+        <v>38.673</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -6779,18 +6757,18 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>70.78</v>
+        <v>66.72</v>
       </c>
       <c r="AA41" t="n">
-        <v>48.8559</v>
+        <v>48.8941</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>48.8559</v>
+        <v>48.8941</v>
       </c>
       <c r="AD41" t="n">
         <v>48.7632</v>
@@ -6804,33 +6782,33 @@
         <v>53.2048</v>
       </c>
       <c r="AG41" t="n">
-        <v>53.9614</v>
+        <v>53.8368</v>
       </c>
       <c r="AH41" t="n">
         <v>54.8285</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 53.96; TP3: Fibonacci R2 at 54.83</t>
+          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 53.84; TP3: Fibonacci R2 at 54.83</t>
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>46.92</v>
+        <v>32.94</v>
       </c>
       <c r="AK41" t="n">
-        <v>55.09</v>
+        <v>37.77</v>
       </c>
       <c r="AL41" t="n">
-        <v>64.44</v>
+        <v>45.35</v>
       </c>
       <c r="AM41" t="n">
-        <v>8.9</v>
+        <v>8.82</v>
       </c>
       <c r="AN41" t="n">
-        <v>10.45</v>
+        <v>10.11</v>
       </c>
       <c r="AO41" t="n">
-        <v>12.22</v>
+        <v>12.14</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -6839,7 +6817,7 @@
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.8); entry: enhanced entry at VWMA (overbought (RSI: 70.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.7))</t>
         </is>
       </c>
     </row>
@@ -6856,11 +6834,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>37.24</v>
+        <v>36.94</v>
       </c>
       <c r="E42" t="n">
         <v>0.7232</v>
@@ -6877,22 +6855,22 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1868672</v>
+        <v>1877096</v>
       </c>
       <c r="J42" t="n">
-        <v>620342</v>
+        <v>1685954</v>
       </c>
       <c r="K42" t="n">
-        <v>0.332</v>
+        <v>0.898</v>
       </c>
       <c r="L42" t="n">
-        <v>910122</v>
+        <v>950485</v>
       </c>
       <c r="M42" t="n">
-        <v>2278533</v>
+        <v>2509303</v>
       </c>
       <c r="N42" t="n">
-        <v>2.504</v>
+        <v>2.64</v>
       </c>
       <c r="O42" t="n">
         <v>34.75</v>
@@ -6901,10 +6879,10 @@
         <v>38.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>38.8184</v>
+        <v>38.8124</v>
       </c>
       <c r="R42" t="n">
-        <v>35.7588</v>
+        <v>35.7573</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -6917,13 +6895,13 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>37.2405</v>
+        <v>37.2119</v>
       </c>
       <c r="V42" t="n">
-        <v>38.431</v>
+        <v>38.4193</v>
       </c>
       <c r="W42" t="n">
-        <v>36.6741</v>
+        <v>36.6711</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -6936,18 +6914,18 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>48.07</v>
+        <v>46.16</v>
       </c>
       <c r="AA42" t="n">
-        <v>37.2356</v>
+        <v>37.2257</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>35.6602</v>
+        <v>35.6417</v>
       </c>
       <c r="AD42" t="n">
         <v>35.4767</v>
@@ -6964,30 +6942,30 @@
         <v>38.5567</v>
       </c>
       <c r="AH42" t="n">
-        <v>38.7128</v>
+        <v>38.7013</v>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 38.25; TP2: Classic R1 at 38.56; TP3: Bollinger Upper Band at 38.71</t>
+          <t>TP1: Fibonacci R1 at 38.25; TP2: Classic R1 at 38.56; TP3: Bollinger Upper Band at 38.7</t>
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>14.12</v>
+        <v>15.81</v>
       </c>
       <c r="AK42" t="n">
-        <v>15.79</v>
+        <v>17.67</v>
       </c>
       <c r="AL42" t="n">
-        <v>16.64</v>
+        <v>18.54</v>
       </c>
       <c r="AM42" t="n">
-        <v>7.26</v>
+        <v>7.32</v>
       </c>
       <c r="AN42" t="n">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="AO42" t="n">
-        <v>8.56</v>
+        <v>8.58</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -6996,7 +6974,7 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 48.1))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.2))</t>
         </is>
       </c>
     </row>
@@ -7013,11 +6991,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7.14</v>
+        <v>7</v>
       </c>
       <c r="E43" t="n">
         <v>0.1363</v>
@@ -7034,22 +7012,22 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2883990</v>
+        <v>2863794</v>
       </c>
       <c r="J43" t="n">
-        <v>1047600</v>
+        <v>3252041</v>
       </c>
       <c r="K43" t="n">
-        <v>0.363</v>
+        <v>1.136</v>
       </c>
       <c r="L43" t="n">
-        <v>2388184</v>
+        <v>2447417</v>
       </c>
       <c r="M43" t="n">
-        <v>1386146</v>
+        <v>3300712</v>
       </c>
       <c r="N43" t="n">
-        <v>0.58</v>
+        <v>1.349</v>
       </c>
       <c r="O43" t="n">
         <v>5.82</v>
@@ -7058,10 +7036,10 @@
         <v>6.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.2432</v>
+        <v>6.2404</v>
       </c>
       <c r="R43" t="n">
-        <v>5.8568</v>
+        <v>5.856</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -7074,13 +7052,13 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>6.7217</v>
+        <v>6.7084</v>
       </c>
       <c r="V43" t="n">
-        <v>6.3097</v>
+        <v>6.3043</v>
       </c>
       <c r="W43" t="n">
-        <v>5.6907</v>
+        <v>5.6893</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -7093,18 +7071,18 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>65.81999999999999</v>
+        <v>61.08</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.7388</v>
+        <v>6.7436</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>6.7388</v>
+        <v>6.7436</v>
       </c>
       <c r="AD43" t="n">
         <v>6.549</v>
@@ -7118,33 +7096,33 @@
         <v>7.2151</v>
       </c>
       <c r="AG43" t="n">
-        <v>7.288</v>
+        <v>7.2622</v>
       </c>
       <c r="AH43" t="n">
         <v>7.45</v>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.29; TP3: Classic R1 at 7.45</t>
+          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.26; TP3: Classic R1 at 7.45</t>
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="AL43" t="n">
-        <v>3.75</v>
+        <v>3.63</v>
       </c>
       <c r="AM43" t="n">
-        <v>7.07</v>
+        <v>6.99</v>
       </c>
       <c r="AN43" t="n">
-        <v>8.15</v>
+        <v>7.69</v>
       </c>
       <c r="AO43" t="n">
-        <v>10.55</v>
+        <v>10.48</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -7153,7 +7131,7 @@
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.1))</t>
         </is>
       </c>
     </row>
@@ -7170,11 +7148,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>386.99</v>
+        <v>380.1</v>
       </c>
       <c r="E44" t="n">
         <v>7.7408</v>
@@ -7191,34 +7169,34 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>33705</v>
+        <v>34531</v>
       </c>
       <c r="J44" t="n">
-        <v>46270</v>
+        <v>97060</v>
       </c>
       <c r="K44" t="n">
-        <v>1.373</v>
+        <v>2.811</v>
       </c>
       <c r="L44" t="n">
-        <v>12577</v>
+        <v>13078</v>
       </c>
       <c r="M44" t="n">
-        <v>171843</v>
+        <v>22823</v>
       </c>
       <c r="N44" t="n">
-        <v>13.664</v>
+        <v>1.745</v>
       </c>
       <c r="O44" t="n">
         <v>360</v>
       </c>
       <c r="P44" t="n">
-        <v>396</v>
+        <v>409.99</v>
       </c>
       <c r="Q44" t="n">
-        <v>361.342</v>
+        <v>361.2042</v>
       </c>
       <c r="R44" t="n">
-        <v>342.3811</v>
+        <v>342.3466</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7231,13 +7209,13 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>371.5769</v>
+        <v>370.9207</v>
       </c>
       <c r="V44" t="n">
-        <v>363.1791</v>
+        <v>362.9089</v>
       </c>
       <c r="W44" t="n">
-        <v>321.4907</v>
+        <v>321.4222</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -7250,29 +7228,29 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>59.56</v>
+        <v>55.8</v>
       </c>
       <c r="AA44" t="n">
-        <v>381.193</v>
+        <v>380.9765</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>382</v>
+        <v>362.8512</v>
       </c>
       <c r="AD44" t="n">
-        <v>362.8512</v>
+        <v>360</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF44" t="n">
-        <v>392.4141</v>
+        <v>391.2441</v>
       </c>
       <c r="AG44" t="n">
         <v>423.2347</v>
@@ -7282,26 +7260,26 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 392.41; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
+          <t>TP1: Bollinger Upper Band at 391.24; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0.54</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.15</v>
+        <v>21.18</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.85</v>
+        <v>25.88</v>
       </c>
       <c r="AM44" t="n">
-        <v>2.73</v>
+        <v>7.82</v>
       </c>
       <c r="AN44" t="n">
-        <v>10.79</v>
+        <v>16.64</v>
       </c>
       <c r="AO44" t="n">
-        <v>14.31</v>
+        <v>20.34</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -7310,7 +7288,7 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 59.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 55.8))</t>
         </is>
       </c>
     </row>
@@ -7327,11 +7305,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>291</v>
+        <v>279.14</v>
       </c>
       <c r="E45" t="n">
         <v>5.4066</v>
@@ -7348,22 +7326,22 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>90812</v>
+        <v>92397</v>
       </c>
       <c r="J45" t="n">
-        <v>74082</v>
+        <v>170473</v>
       </c>
       <c r="K45" t="n">
-        <v>0.8159999999999999</v>
+        <v>1.845</v>
       </c>
       <c r="L45" t="n">
-        <v>30216</v>
+        <v>36770</v>
       </c>
       <c r="M45" t="n">
-        <v>466063</v>
+        <v>294610</v>
       </c>
       <c r="N45" t="n">
-        <v>15.424</v>
+        <v>8.012</v>
       </c>
       <c r="O45" t="n">
         <v>200</v>
@@ -7372,10 +7350,10 @@
         <v>247.97</v>
       </c>
       <c r="Q45" t="n">
-        <v>220.3926</v>
+        <v>220.1554</v>
       </c>
       <c r="R45" t="n">
-        <v>187.2457</v>
+        <v>187.1864</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -7388,13 +7366,13 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>246.3203</v>
+        <v>245.1907</v>
       </c>
       <c r="V45" t="n">
-        <v>225.1599</v>
+        <v>224.6948</v>
       </c>
       <c r="W45" t="n">
-        <v>183.1066</v>
+        <v>182.9885</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -7407,14 +7385,14 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>72.61</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="AA45" t="n">
-        <v>254.7748</v>
+        <v>255.2713</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC45" t="n">
@@ -7429,37 +7407,37 @@
         </is>
       </c>
       <c r="AF45" t="n">
+        <v>283.3896</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>288.2818</v>
+      </c>
+      <c r="AH45" t="n">
         <v>307.9633</v>
       </c>
-      <c r="AG45" t="n">
-        <v>308.8515</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>342.1467</v>
-      </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 307.96; TP2: Fibonacci R2 at 308.85; TP3: Classic R2 at 342.15</t>
+          <t>TP1: Bollinger Upper Band at 283.39; TP2: Fibonacci R1 at 288.28; TP3: Classic R1 at 307.96</t>
         </is>
       </c>
       <c r="AJ45" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL45" t="n">
         <v>3.09</v>
       </c>
-      <c r="AK45" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>5.16</v>
-      </c>
       <c r="AM45" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AO45" t="n">
         <v>19.83</v>
       </c>
-      <c r="AN45" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>33.13</v>
-      </c>
       <c r="AP45" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -7467,7 +7445,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 72.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 66.2))</t>
         </is>
       </c>
     </row>
@@ -7484,11 +7462,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>8.15</v>
       </c>
       <c r="E46" t="n">
         <v>0.1596</v>
@@ -7505,22 +7483,22 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2478481</v>
+        <v>2487325</v>
       </c>
       <c r="J46" t="n">
-        <v>638829</v>
+        <v>2708107</v>
       </c>
       <c r="K46" t="n">
-        <v>0.258</v>
+        <v>1.089</v>
       </c>
       <c r="L46" t="n">
-        <v>2518339</v>
+        <v>2366094</v>
       </c>
       <c r="M46" t="n">
-        <v>2565607</v>
+        <v>287565</v>
       </c>
       <c r="N46" t="n">
-        <v>1.019</v>
+        <v>0.122</v>
       </c>
       <c r="O46" t="n">
         <v>6.55</v>
@@ -7529,10 +7507,10 @@
         <v>6.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.9088</v>
+        <v>6.9118</v>
       </c>
       <c r="R46" t="n">
-        <v>6.4069</v>
+        <v>6.4076</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7545,13 +7523,13 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>7.8281</v>
+        <v>7.8424</v>
       </c>
       <c r="V46" t="n">
-        <v>7.1861</v>
+        <v>7.192</v>
       </c>
       <c r="W46" t="n">
-        <v>6.3197</v>
+        <v>6.3212</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -7564,21 +7542,21 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>59.73</v>
+        <v>62.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.7722</v>
+        <v>7.7791</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>7.7722</v>
+        <v>7.7791</v>
       </c>
       <c r="AD46" t="n">
-        <v>6.9676</v>
+        <v>6.9704</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -7589,33 +7567,33 @@
         <v>8.755100000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>8.8764</v>
+        <v>8.8886</v>
       </c>
       <c r="AH46" t="n">
         <v>9.2333</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.88; TP3: Classic R1 at 9.23</t>
+          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.89; TP3: Classic R1 at 9.23</t>
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK46" t="n">
         <v>1.37</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AM46" t="n">
-        <v>12.65</v>
+        <v>12.55</v>
       </c>
       <c r="AN46" t="n">
-        <v>14.21</v>
+        <v>14.26</v>
       </c>
       <c r="AO46" t="n">
-        <v>18.8</v>
+        <v>18.69</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -7624,7 +7602,7 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.5))</t>
         </is>
       </c>
     </row>
@@ -7641,11 +7619,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="E47" t="n">
         <v>0.0294</v>
@@ -7662,22 +7640,22 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>39446506</v>
+        <v>39851604</v>
       </c>
       <c r="J47" t="n">
-        <v>91475072</v>
+        <v>171902548</v>
       </c>
       <c r="K47" t="n">
-        <v>2.319</v>
+        <v>4.314</v>
       </c>
       <c r="L47" t="n">
-        <v>29063477</v>
+        <v>29028496</v>
       </c>
       <c r="M47" t="n">
-        <v>37249117</v>
+        <v>30159561</v>
       </c>
       <c r="N47" t="n">
-        <v>1.282</v>
+        <v>1.039</v>
       </c>
       <c r="O47" t="n">
         <v>1.32</v>
@@ -7686,10 +7664,10 @@
         <v>1.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.3008</v>
+        <v>1.3016</v>
       </c>
       <c r="R47" t="n">
-        <v>1.1856</v>
+        <v>1.1858</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7702,13 +7680,13 @@
         </is>
       </c>
       <c r="U47" t="n">
-        <v>1.4186</v>
+        <v>1.4224</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3385</v>
+        <v>1.3401</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1565</v>
+        <v>1.1568</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -7721,18 +7699,18 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>72.73999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.433</v>
+        <v>1.4405</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>1.433</v>
+        <v>1.4405</v>
       </c>
       <c r="AD47" t="n">
         <v>1.32</v>
@@ -7743,36 +7721,36 @@
         </is>
       </c>
       <c r="AF47" t="n">
-        <v>1.5828</v>
+        <v>1.6089</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.6003</v>
+        <v>1.66</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.66</v>
+        <v>1.6772</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 1.58; TP2: Bollinger Upper Band at 1.6; TP3: Classic R1 at 1.66</t>
+          <t>TP1: Bollinger Upper Band at 1.61; TP2: Classic R1 at 1.66; TP3: Fibonacci R2 at 1.68</t>
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AM47" t="n">
-        <v>10.45</v>
+        <v>11.69</v>
       </c>
       <c r="AN47" t="n">
-        <v>11.68</v>
+        <v>15.24</v>
       </c>
       <c r="AO47" t="n">
-        <v>15.84</v>
+        <v>16.44</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -7781,7 +7759,7 @@
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.7); entry: enhanced entry at VWMA (overbought (RSI: 72.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.3); entry: enhanced entry at VWMA (overbought (RSI: 75.3))</t>
         </is>
       </c>
     </row>
@@ -7798,11 +7776,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.885</v>
+        <v>0.901</v>
       </c>
       <c r="E48" t="n">
         <v>0.0164</v>
@@ -7819,22 +7797,22 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>19600606</v>
+        <v>19634877</v>
       </c>
       <c r="J48" t="n">
-        <v>20176187</v>
+        <v>36073167</v>
       </c>
       <c r="K48" t="n">
-        <v>1.029</v>
+        <v>1.837</v>
       </c>
       <c r="L48" t="n">
-        <v>22304846</v>
+        <v>22450213</v>
       </c>
       <c r="M48" t="n">
-        <v>16253501</v>
+        <v>12648129</v>
       </c>
       <c r="N48" t="n">
-        <v>0.729</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="O48" t="n">
         <v>0.595</v>
@@ -7843,7 +7821,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5532</v>
       </c>
       <c r="R48" t="n">
         <v>0.4272</v>
@@ -7859,13 +7837,13 @@
         </is>
       </c>
       <c r="U48" t="n">
-        <v>0.7581</v>
+        <v>0.7597</v>
       </c>
       <c r="V48" t="n">
-        <v>0.6141</v>
+        <v>0.6147</v>
       </c>
       <c r="W48" t="n">
-        <v>0.4537</v>
+        <v>0.4538</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -7878,18 +7856,18 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>75.98</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.7428</v>
+        <v>0.7456</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>0.7428</v>
+        <v>0.7456</v>
       </c>
       <c r="AD48" t="n">
         <v>0.595</v>
@@ -7906,7 +7884,7 @@
         <v>1.0187</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.029</v>
+        <v>1.0314</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -7914,22 +7892,22 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AM48" t="n">
-        <v>24.59</v>
+        <v>24.12</v>
       </c>
       <c r="AN48" t="n">
-        <v>37.14</v>
+        <v>36.62</v>
       </c>
       <c r="AO48" t="n">
-        <v>38.52</v>
+        <v>38.33</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -7938,7 +7916,7 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.0); entry: enhanced entry at VWMA (overbought (RSI: 76.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.0); entry: enhanced entry at VWMA (overbought (RSI: 77.0))</t>
         </is>
       </c>
     </row>
@@ -7955,11 +7933,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.533</v>
+        <v>0.53</v>
       </c>
       <c r="E49" t="n">
         <v>0.0103</v>
@@ -7976,34 +7954,34 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>20426292</v>
+        <v>20532324</v>
       </c>
       <c r="J49" t="n">
-        <v>11678035</v>
+        <v>32612460</v>
       </c>
       <c r="K49" t="n">
-        <v>0.572</v>
+        <v>1.588</v>
       </c>
       <c r="L49" t="n">
-        <v>18818578</v>
+        <v>19286208</v>
       </c>
       <c r="M49" t="n">
-        <v>12167599</v>
+        <v>23911647</v>
       </c>
       <c r="N49" t="n">
-        <v>0.647</v>
+        <v>1.24</v>
       </c>
       <c r="O49" t="n">
         <v>0.507</v>
       </c>
       <c r="P49" t="n">
-        <v>0.53</v>
+        <v>0.546</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4478</v>
+        <v>0.4477</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4667</v>
+        <v>0.4666</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -8016,13 +7994,13 @@
         </is>
       </c>
       <c r="U49" t="n">
-        <v>0.4961</v>
+        <v>0.4959</v>
       </c>
       <c r="V49" t="n">
-        <v>0.466</v>
+        <v>0.4659</v>
       </c>
       <c r="W49" t="n">
-        <v>0.443</v>
+        <v>0.4429</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -8035,14 +8013,14 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>63.01</v>
+        <v>62.08</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.517</v>
+        <v>0.5172</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -8090,11 +8068,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>489</v>
+        <v>503.7</v>
       </c>
       <c r="E50" t="n">
         <v>9.111499999999999</v>
@@ -8111,22 +8089,22 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>11630</v>
+        <v>11790</v>
       </c>
       <c r="J50" t="n">
-        <v>6214</v>
+        <v>45500</v>
       </c>
       <c r="K50" t="n">
-        <v>0.534</v>
+        <v>3.859</v>
       </c>
       <c r="L50" t="n">
-        <v>6840</v>
+        <v>7222</v>
       </c>
       <c r="M50" t="n">
-        <v>2346</v>
+        <v>19630</v>
       </c>
       <c r="N50" t="n">
-        <v>0.343</v>
+        <v>2.718</v>
       </c>
       <c r="O50" t="n">
         <v>265</v>
@@ -8135,10 +8113,10 @@
         <v>512</v>
       </c>
       <c r="Q50" t="n">
-        <v>398.6898</v>
+        <v>398.9838</v>
       </c>
       <c r="R50" t="n">
-        <v>301.5876</v>
+        <v>301.6611</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -8151,13 +8129,13 @@
         </is>
       </c>
       <c r="U50" t="n">
-        <v>450.4576</v>
+        <v>451.8576</v>
       </c>
       <c r="V50" t="n">
-        <v>407.1914</v>
+        <v>407.7679</v>
       </c>
       <c r="W50" t="n">
-        <v>311.8843</v>
+        <v>312.0306</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -8170,18 +8148,18 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>75.64</v>
+        <v>78.61</v>
       </c>
       <c r="AA50" t="n">
-        <v>461.8072</v>
+        <v>464.9611</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>461.8072</v>
+        <v>464.9611</v>
       </c>
       <c r="AD50" t="n">
         <v>442.4273</v>
@@ -8192,36 +8170,36 @@
         </is>
       </c>
       <c r="AF50" t="n">
-        <v>501.4547</v>
+        <v>514.4535</v>
       </c>
       <c r="AG50" t="n">
-        <v>511.5489</v>
+        <v>518.9933</v>
       </c>
       <c r="AH50" t="n">
-        <v>518.9933</v>
+        <v>529.5386999999999</v>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 511.55; TP3: Classic R1 at 518.99</t>
+          <t>TP1: Bollinger Upper Band at 514.45; TP2: Classic R1 at 518.99; TP3: Fibonacci R2 at 529.54</t>
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AK50" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AL50" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AM50" t="n">
-        <v>8.59</v>
+        <v>10.64</v>
       </c>
       <c r="AN50" t="n">
-        <v>10.77</v>
+        <v>11.62</v>
       </c>
       <c r="AO50" t="n">
-        <v>12.38</v>
+        <v>13.89</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -8230,7 +8208,7 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.6); entry: enhanced entry at VWMA (overbought (RSI: 75.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.6); entry: enhanced entry at VWMA (overbought (RSI: 78.6))</t>
         </is>
       </c>
     </row>
@@ -8247,11 +8225,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1255.06</v>
+        <v>1327.71</v>
       </c>
       <c r="E51" t="n">
         <v>23.8879</v>
@@ -8268,34 +8246,34 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2311</v>
+        <v>2326</v>
       </c>
       <c r="J51" t="n">
-        <v>1641</v>
+        <v>13978</v>
       </c>
       <c r="K51" t="n">
-        <v>0.71</v>
+        <v>6.009</v>
       </c>
       <c r="L51" t="n">
-        <v>861</v>
+        <v>942</v>
       </c>
       <c r="M51" t="n">
-        <v>2302</v>
+        <v>3766</v>
       </c>
       <c r="N51" t="n">
-        <v>2.673</v>
+        <v>3.998</v>
       </c>
       <c r="O51" t="n">
         <v>1122</v>
       </c>
       <c r="P51" t="n">
-        <v>1239</v>
+        <v>1275</v>
       </c>
       <c r="Q51" t="n">
-        <v>1164.0746</v>
+        <v>1165.5276</v>
       </c>
       <c r="R51" t="n">
-        <v>910.9515</v>
+        <v>911.3147</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8308,13 +8286,13 @@
         </is>
       </c>
       <c r="U51" t="n">
-        <v>1210.7645</v>
+        <v>1217.6836</v>
       </c>
       <c r="V51" t="n">
-        <v>1148.6208</v>
+        <v>1151.4698</v>
       </c>
       <c r="W51" t="n">
-        <v>924.4641</v>
+        <v>925.187</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -8327,21 +8305,21 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>68.87</v>
+        <v>78.39</v>
       </c>
       <c r="AA51" t="n">
-        <v>1212.5021</v>
+        <v>1236.1014</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC51" t="n">
-        <v>1212.5021</v>
+        <v>1257</v>
       </c>
       <c r="AD51" t="n">
-        <v>1170.9559</v>
+        <v>1154.6213</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -8349,45 +8327,45 @@
         </is>
       </c>
       <c r="AF51" t="n">
-        <v>1259.3171</v>
+        <v>1341.2533</v>
       </c>
       <c r="AG51" t="n">
-        <v>1312.2368</v>
+        <v>1371.9165</v>
       </c>
       <c r="AH51" t="n">
-        <v>1341.2533</v>
+        <v>1468.5167</v>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1259.32; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
+          <t>TP1: Classic R1 at 1341.25; TP2: Fibonacci R2 at 1371.92; TP3: Classic R2 at 1468.52</t>
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.13</v>
+        <v>0.82</v>
       </c>
       <c r="AK51" t="n">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="AL51" t="n">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="AM51" t="n">
-        <v>3.86</v>
+        <v>6.7</v>
       </c>
       <c r="AN51" t="n">
-        <v>8.23</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AO51" t="n">
-        <v>10.62</v>
+        <v>16.83</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.9))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.4))</t>
         </is>
       </c>
     </row>
@@ -8404,11 +8382,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>244.12</v>
+        <v>244</v>
       </c>
       <c r="E52" t="n">
         <v>4.782</v>
@@ -8425,22 +8403,22 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>92947</v>
+        <v>93109</v>
       </c>
       <c r="J52" t="n">
-        <v>22130</v>
+        <v>59521</v>
       </c>
       <c r="K52" t="n">
-        <v>0.238</v>
+        <v>0.639</v>
       </c>
       <c r="L52" t="n">
-        <v>39168</v>
+        <v>39811</v>
       </c>
       <c r="M52" t="n">
-        <v>12024</v>
+        <v>41547</v>
       </c>
       <c r="N52" t="n">
-        <v>0.307</v>
+        <v>1.044</v>
       </c>
       <c r="O52" t="n">
         <v>242</v>
@@ -8449,10 +8427,10 @@
         <v>245</v>
       </c>
       <c r="Q52" t="n">
-        <v>254.6718</v>
+        <v>254.6694</v>
       </c>
       <c r="R52" t="n">
-        <v>245.2027</v>
+        <v>245.2021</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8465,13 +8443,13 @@
         </is>
       </c>
       <c r="U52" t="n">
-        <v>244.846</v>
+        <v>244.8346</v>
       </c>
       <c r="V52" t="n">
-        <v>250.449</v>
+        <v>250.4443</v>
       </c>
       <c r="W52" t="n">
-        <v>234.1461</v>
+        <v>234.1449</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -8484,14 +8462,14 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>46.51</v>
+        <v>46.32</v>
       </c>
       <c r="AA52" t="n">
-        <v>243.3215</v>
+        <v>243.3361</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC52" t="n">
@@ -8506,13 +8484,13 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>245.2027</v>
+        <v>245.2021</v>
       </c>
       <c r="AG52" t="n">
         <v>248.1478</v>
       </c>
       <c r="AH52" t="n">
-        <v>250.2848</v>
+        <v>250.2763</v>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
@@ -8526,7 +8504,7 @@
         <v>11.79</v>
       </c>
       <c r="AL52" t="n">
-        <v>13.84</v>
+        <v>13.83</v>
       </c>
       <c r="AM52" t="n">
         <v>3.97</v>
@@ -8544,7 +8522,7 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 46.5))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 46.3))</t>
         </is>
       </c>
     </row>
@@ -8561,11 +8539,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>200</v>
+        <v>186.94</v>
       </c>
       <c r="E53" t="n">
         <v>3.758</v>
@@ -8582,22 +8560,22 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>90592</v>
+        <v>91987</v>
       </c>
       <c r="J53" t="n">
-        <v>58847</v>
+        <v>142761</v>
       </c>
       <c r="K53" t="n">
-        <v>0.65</v>
+        <v>1.552</v>
       </c>
       <c r="L53" t="n">
-        <v>89582</v>
+        <v>95843</v>
       </c>
       <c r="M53" t="n">
-        <v>108474</v>
+        <v>313265</v>
       </c>
       <c r="N53" t="n">
-        <v>1.211</v>
+        <v>3.269</v>
       </c>
       <c r="O53" t="n">
         <v>127.01</v>
@@ -8606,10 +8584,10 @@
         <v>197.49</v>
       </c>
       <c r="Q53" t="n">
-        <v>146.3338</v>
+        <v>146.0726</v>
       </c>
       <c r="R53" t="n">
-        <v>123.124</v>
+        <v>123.0587</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8622,13 +8600,13 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>168.6154</v>
+        <v>167.3716</v>
       </c>
       <c r="V53" t="n">
-        <v>149.627</v>
+        <v>149.1148</v>
       </c>
       <c r="W53" t="n">
-        <v>120.1484</v>
+        <v>120.0184</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -8641,18 +8619,18 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>67.79000000000001</v>
+        <v>60.83</v>
       </c>
       <c r="AA53" t="n">
-        <v>173.3037</v>
+        <v>173.3633</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>173.3037</v>
+        <v>173.3633</v>
       </c>
       <c r="AD53" t="n">
         <v>172.34</v>
@@ -8666,33 +8644,33 @@
         <v>208.4527</v>
       </c>
       <c r="AG53" t="n">
-        <v>212.6765</v>
+        <v>210.3357</v>
       </c>
       <c r="AH53" t="n">
         <v>224.8967</v>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 212.68; TP3: Classic R1 at 224.9</t>
+          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 210.34; TP3: Classic R1 at 224.9</t>
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>36.47</v>
+        <v>34.29</v>
       </c>
       <c r="AK53" t="n">
-        <v>40.86</v>
+        <v>36.13</v>
       </c>
       <c r="AL53" t="n">
-        <v>53.54</v>
+        <v>50.36</v>
       </c>
       <c r="AM53" t="n">
-        <v>20.28</v>
+        <v>20.24</v>
       </c>
       <c r="AN53" t="n">
-        <v>22.72</v>
+        <v>21.33</v>
       </c>
       <c r="AO53" t="n">
-        <v>29.77</v>
+        <v>29.73</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -8701,7 +8679,7 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.8))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.8))</t>
         </is>
       </c>
     </row>
@@ -8718,11 +8696,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.24</v>
+        <v>7.15</v>
       </c>
       <c r="E54" t="n">
         <v>0.1416</v>
@@ -8739,20 +8717,22 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>24706539</v>
+        <v>24738418</v>
       </c>
       <c r="J54" t="n">
-        <v>7067957</v>
+        <v>40424958</v>
       </c>
       <c r="K54" t="n">
-        <v>0.286</v>
+        <v>1.634</v>
       </c>
       <c r="L54" t="n">
-        <v>15027796</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
+        <v>14803414</v>
+      </c>
+      <c r="M54" t="n">
+        <v>13572150</v>
+      </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.917</v>
       </c>
       <c r="O54" t="n">
         <v>6.19</v>
@@ -8761,10 +8741,10 @@
         <v>6.69</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.6358</v>
+        <v>6.634</v>
       </c>
       <c r="R54" t="n">
-        <v>5.8447</v>
+        <v>5.8443</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -8777,13 +8757,13 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>7.2148</v>
+        <v>7.2062</v>
       </c>
       <c r="V54" t="n">
-        <v>6.7615</v>
+        <v>6.758</v>
       </c>
       <c r="W54" t="n">
-        <v>5.79</v>
+        <v>5.7891</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -8796,21 +8776,21 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>54.46</v>
+        <v>51.89</v>
       </c>
       <c r="AA54" t="n">
-        <v>7.2918</v>
+        <v>7.2847</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC54" t="n">
         <v>6.99</v>
       </c>
       <c r="AD54" t="n">
-        <v>6.6643</v>
+        <v>6.6577</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -8824,21 +8804,21 @@
         <v>7.8167</v>
       </c>
       <c r="AH54" t="n">
-        <v>7.8767</v>
+        <v>7.8743</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.88</t>
+          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.87</t>
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AK54" t="n">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="AL54" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AM54" t="n">
         <v>9.41</v>
@@ -8847,7 +8827,7 @@
         <v>11.83</v>
       </c>
       <c r="AO54" t="n">
-        <v>12.69</v>
+        <v>12.65</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -8856,7 +8836,7 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.5))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 51.9))</t>
         </is>
       </c>
     </row>
@@ -8873,11 +8853,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.8</v>
+        <v>12.65</v>
       </c>
       <c r="E55" t="n">
         <v>0.2222</v>
@@ -8894,22 +8874,22 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3433424</v>
+        <v>3424205</v>
       </c>
       <c r="J55" t="n">
-        <v>1695796</v>
+        <v>2650610</v>
       </c>
       <c r="K55" t="n">
-        <v>0.494</v>
+        <v>0.774</v>
       </c>
       <c r="L55" t="n">
-        <v>757029</v>
+        <v>754146</v>
       </c>
       <c r="M55" t="n">
-        <v>674255</v>
+        <v>792465</v>
       </c>
       <c r="N55" t="n">
-        <v>0.891</v>
+        <v>1.051</v>
       </c>
       <c r="O55" t="n">
         <v>8.74</v>
@@ -8918,10 +8898,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>9.3728</v>
+        <v>9.3698</v>
       </c>
       <c r="R55" t="n">
-        <v>6.1614</v>
+        <v>6.1606</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -8934,13 +8914,13 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>10.497</v>
+        <v>10.4827</v>
       </c>
       <c r="V55" t="n">
-        <v>9.4283</v>
+        <v>9.4224</v>
       </c>
       <c r="W55" t="n">
-        <v>6.736</v>
+        <v>6.7345</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -8953,14 +8933,14 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>78.92</v>
+        <v>78.25</v>
       </c>
       <c r="AA55" t="n">
-        <v>10.2725</v>
+        <v>10.3341</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC55" t="n">
@@ -9013,7 +8993,7 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.2))</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9010,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -9069,10 +9049,10 @@
         <v>5.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.4198</v>
+        <v>5.4298</v>
       </c>
       <c r="R56" t="n">
-        <v>5.2924</v>
+        <v>5.2937</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -9085,13 +9065,13 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>5.5471</v>
+        <v>5.5436</v>
       </c>
       <c r="V56" t="n">
-        <v>5.47</v>
+        <v>5.4715</v>
       </c>
       <c r="W56" t="n">
-        <v>5.326</v>
+        <v>5.3278</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -9107,22 +9087,22 @@
         <v>48.33</v>
       </c>
       <c r="AA56" t="n">
-        <v>5.7785</v>
+        <v>5.7227</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC56" t="n">
+        <v>5.4298</v>
+      </c>
+      <c r="AD56" t="n">
         <v>5.42</v>
       </c>
-      <c r="AD56" t="n">
-        <v>5.3534</v>
-      </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AF56" t="n">
@@ -9140,22 +9120,22 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>4.06</v>
+        <v>26.55</v>
       </c>
       <c r="AK56" t="n">
-        <v>4.25</v>
+        <v>27.89</v>
       </c>
       <c r="AL56" t="n">
-        <v>5.21</v>
+        <v>34.4</v>
       </c>
       <c r="AM56" t="n">
-        <v>4.98</v>
+        <v>4.79</v>
       </c>
       <c r="AN56" t="n">
-        <v>5.22</v>
+        <v>5.03</v>
       </c>
       <c r="AO56" t="n">
-        <v>6.4</v>
+        <v>6.21</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -9164,7 +9144,7 @@
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Classic S1 (neutral (RSI: 48.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (neutral (RSI: 48.3))</t>
         </is>
       </c>
     </row>
@@ -9181,11 +9161,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>297.95</v>
+        <v>333</v>
       </c>
       <c r="E57" t="n">
         <v>5.7269</v>
@@ -9202,22 +9182,22 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>367014</v>
+        <v>366899</v>
       </c>
       <c r="J57" t="n">
-        <v>63790</v>
+        <v>989538</v>
       </c>
       <c r="K57" t="n">
-        <v>0.174</v>
+        <v>2.697</v>
       </c>
       <c r="L57" t="n">
-        <v>175426</v>
+        <v>173022</v>
       </c>
       <c r="M57" t="n">
-        <v>145255</v>
+        <v>42694</v>
       </c>
       <c r="N57" t="n">
-        <v>0.828</v>
+        <v>0.247</v>
       </c>
       <c r="O57" t="n">
         <v>204.36</v>
@@ -9226,10 +9206,10 @@
         <v>252.69</v>
       </c>
       <c r="Q57" t="n">
-        <v>239.148</v>
+        <v>239.849</v>
       </c>
       <c r="R57" t="n">
-        <v>184.2107</v>
+        <v>184.386</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -9242,13 +9222,13 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>269.5472</v>
+        <v>272.8853</v>
       </c>
       <c r="V57" t="n">
-        <v>242.4915</v>
+        <v>243.866</v>
       </c>
       <c r="W57" t="n">
-        <v>185.495</v>
+        <v>185.8437</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -9261,18 +9241,18 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>77.40000000000001</v>
+        <v>84.89</v>
       </c>
       <c r="AA57" t="n">
-        <v>265.6297</v>
+        <v>273.6773</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>265.6297</v>
+        <v>280.775</v>
       </c>
       <c r="AD57" t="n">
         <v>264.2685</v>
@@ -9283,36 +9263,36 @@
         </is>
       </c>
       <c r="AF57" t="n">
-        <v>298.94</v>
+        <v>337.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>309.6607</v>
+        <v>398.9</v>
       </c>
       <c r="AH57" t="n">
-        <v>313.52</v>
+        <v>444.0237</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 298.94; TP2: Bollinger Upper Band at 309.66; TP3: Fibonacci R2 at 313.52</t>
+          <t>TP1: Classic R2 at 337.12; TP2: Classic R3 at 398.9; TP3: Extension at 444.02</t>
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>24.47</v>
+        <v>3.41</v>
       </c>
       <c r="AK57" t="n">
-        <v>32.35</v>
+        <v>7.16</v>
       </c>
       <c r="AL57" t="n">
-        <v>35.18</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AM57" t="n">
-        <v>12.54</v>
+        <v>20.07</v>
       </c>
       <c r="AN57" t="n">
-        <v>16.58</v>
+        <v>42.07</v>
       </c>
       <c r="AO57" t="n">
-        <v>18.03</v>
+        <v>58.14</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -9321,7 +9301,7 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.4); entry: enhanced entry at VWMA (overbought (RSI: 77.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (84.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 84.9))</t>
         </is>
       </c>
     </row>
@@ -9338,11 +9318,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18.44</v>
+        <v>19.2</v>
       </c>
       <c r="E58" t="n">
         <v>0.3446</v>
@@ -9359,34 +9339,34 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>706832</v>
+        <v>723230</v>
       </c>
       <c r="J58" t="n">
-        <v>1864617</v>
+        <v>4819169</v>
       </c>
       <c r="K58" t="n">
-        <v>2.638</v>
+        <v>6.663</v>
       </c>
       <c r="L58" t="n">
-        <v>457851</v>
+        <v>507451</v>
       </c>
       <c r="M58" t="n">
-        <v>922802</v>
+        <v>2284424</v>
       </c>
       <c r="N58" t="n">
-        <v>2.016</v>
+        <v>4.502</v>
       </c>
       <c r="O58" t="n">
         <v>15.68</v>
       </c>
       <c r="P58" t="n">
-        <v>18</v>
+        <v>16.34</v>
       </c>
       <c r="Q58" t="n">
-        <v>16.0148</v>
+        <v>16.03</v>
       </c>
       <c r="R58" t="n">
-        <v>15.6444</v>
+        <v>15.6482</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9399,13 +9379,13 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>16.5736</v>
+        <v>16.6459</v>
       </c>
       <c r="V58" t="n">
-        <v>16.1072</v>
+        <v>16.137</v>
       </c>
       <c r="W58" t="n">
-        <v>15.0138</v>
+        <v>15.0214</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -9418,14 +9398,14 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>75.39</v>
+        <v>79.41</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.9896</v>
+        <v>17.1589</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC58" t="n">
@@ -9440,36 +9420,36 @@
         </is>
       </c>
       <c r="AF58" t="n">
-        <v>19.0869</v>
+        <v>19.6033</v>
       </c>
       <c r="AG58" t="n">
-        <v>19.6033</v>
+        <v>20.1064</v>
       </c>
       <c r="AH58" t="n">
-        <v>20.1064</v>
+        <v>21.7567</v>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 19.09; TP2: Classic R1 at 19.6; TP3: Fibonacci R2 at 20.11</t>
+          <t>TP1: Classic R1 at 19.6; TP2: Fibonacci R2 at 20.11; TP3: Classic R2 at 21.76</t>
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.53</v>
+        <v>2.01</v>
       </c>
       <c r="AK58" t="n">
-        <v>2.01</v>
+        <v>2.47</v>
       </c>
       <c r="AL58" t="n">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="AM58" t="n">
-        <v>9.51</v>
+        <v>12.47</v>
       </c>
       <c r="AN58" t="n">
-        <v>12.47</v>
+        <v>15.36</v>
       </c>
       <c r="AO58" t="n">
-        <v>15.36</v>
+        <v>24.82</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -9478,7 +9458,7 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.4))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.4))</t>
         </is>
       </c>
     </row>
@@ -9495,11 +9475,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.592</v>
+        <v>0.597</v>
       </c>
       <c r="E59" t="n">
         <v>0.0107</v>
@@ -9516,31 +9496,31 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>22289607</v>
+        <v>22425456</v>
       </c>
       <c r="J59" t="n">
-        <v>19118194</v>
+        <v>94427036</v>
       </c>
       <c r="K59" t="n">
-        <v>0.858</v>
+        <v>4.211</v>
       </c>
       <c r="L59" t="n">
-        <v>25821852</v>
+        <v>26338384</v>
       </c>
       <c r="M59" t="n">
-        <v>2253684</v>
+        <v>29903632</v>
       </c>
       <c r="N59" t="n">
-        <v>0.08699999999999999</v>
+        <v>1.135</v>
       </c>
       <c r="O59" t="n">
-        <v>0.543</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="P59" t="n">
-        <v>0.552</v>
+        <v>0.582</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.5437</v>
+        <v>0.5438</v>
       </c>
       <c r="R59" t="n">
         <v>0.4731</v>
@@ -9556,13 +9536,13 @@
         </is>
       </c>
       <c r="U59" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5765</v>
       </c>
       <c r="V59" t="n">
-        <v>0.5471</v>
+        <v>0.5473</v>
       </c>
       <c r="W59" t="n">
-        <v>0.4864</v>
+        <v>0.4865</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -9575,58 +9555,58 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>56.47</v>
+        <v>57.66</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.586</v>
+        <v>0.5868</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>0.586</v>
+        <v>0.5868</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.5583</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AF59" t="n">
         <v>0.5994</v>
       </c>
       <c r="AG59" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="AH59" t="n">
         <v>0.6229</v>
       </c>
-      <c r="AH59" t="n">
-        <v>0.6556999999999999</v>
-      </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 0.6; TP2: Fibonacci R2 at 0.62; TP3: Classic R2 at 0.66</t>
+          <t>TP1: Classic R1 at 0.6; TP2: Bollinger Upper Band at 0.61; TP3: Fibonacci R2 at 0.62</t>
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0.49</v>
+        <v>1.3</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AL59" t="n">
-        <v>2.52</v>
+        <v>3.73</v>
       </c>
       <c r="AM59" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AN59" t="n">
-        <v>6.3</v>
+        <v>3.19</v>
       </c>
       <c r="AO59" t="n">
-        <v>11.9</v>
+        <v>6.15</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -9635,7 +9615,7 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.7))</t>
         </is>
       </c>
     </row>
@@ -9652,11 +9632,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>123</v>
+        <v>118.54</v>
       </c>
       <c r="E60" t="n">
         <v>2.1067</v>
@@ -9673,34 +9653,34 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>120613</v>
+        <v>122002</v>
       </c>
       <c r="J60" t="n">
-        <v>678473</v>
+        <v>996104</v>
       </c>
       <c r="K60" t="n">
-        <v>5.625</v>
+        <v>8.164999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>31483</v>
+        <v>39546</v>
       </c>
       <c r="M60" t="n">
-        <v>111145</v>
+        <v>349853</v>
       </c>
       <c r="N60" t="n">
-        <v>3.53</v>
+        <v>8.847</v>
       </c>
       <c r="O60" t="n">
         <v>100.05</v>
       </c>
       <c r="P60" t="n">
-        <v>106.99</v>
+        <v>136.77</v>
       </c>
       <c r="Q60" t="n">
-        <v>100.4728</v>
+        <v>100.3836</v>
       </c>
       <c r="R60" t="n">
-        <v>89.6511</v>
+        <v>89.6288</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -9713,13 +9693,13 @@
         </is>
       </c>
       <c r="U60" t="n">
-        <v>105.6194</v>
+        <v>105.1947</v>
       </c>
       <c r="V60" t="n">
-        <v>100.9863</v>
+        <v>100.8114</v>
       </c>
       <c r="W60" t="n">
-        <v>89.0457</v>
+        <v>89.0014</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -9732,18 +9712,18 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>82</v>
+        <v>79.09</v>
       </c>
       <c r="AA60" t="n">
-        <v>107.3772</v>
+        <v>107.4858</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC60" t="n">
-        <v>107.3772</v>
+        <v>107.4858</v>
       </c>
       <c r="AD60" t="n">
         <v>104</v>
@@ -9760,30 +9740,30 @@
         <v>143.7933</v>
       </c>
       <c r="AH60" t="n">
-        <v>157.7043</v>
+        <v>157.6628</v>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 123.25; TP2: Classic R3 at 143.79; TP3: Extension at 157.7</t>
+          <t>TP1: Classic R2 at 123.25; TP2: Classic R3 at 143.79; TP3: Extension at 157.66</t>
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>4.7</v>
+        <v>4.52</v>
       </c>
       <c r="AK60" t="n">
-        <v>10.78</v>
+        <v>10.42</v>
       </c>
       <c r="AL60" t="n">
-        <v>14.9</v>
+        <v>14.39</v>
       </c>
       <c r="AM60" t="n">
-        <v>14.79</v>
+        <v>14.67</v>
       </c>
       <c r="AN60" t="n">
-        <v>33.91</v>
+        <v>33.78</v>
       </c>
       <c r="AO60" t="n">
-        <v>46.87</v>
+        <v>46.68</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -9792,7 +9772,7 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.0); entry: enhanced entry at VWMA (overbought (RSI: 82.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.1); entry: enhanced entry at VWMA (overbought (RSI: 79.1))</t>
         </is>
       </c>
     </row>
@@ -9809,11 +9789,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.42</v>
+        <v>11.23</v>
       </c>
       <c r="E61" t="n">
         <v>0.2074</v>
@@ -9830,34 +9810,34 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1638976</v>
+        <v>1631553</v>
       </c>
       <c r="J61" t="n">
-        <v>1272326</v>
+        <v>2069935</v>
       </c>
       <c r="K61" t="n">
-        <v>0.776</v>
+        <v>1.269</v>
       </c>
       <c r="L61" t="n">
-        <v>592572</v>
+        <v>622861</v>
       </c>
       <c r="M61" t="n">
-        <v>284973</v>
+        <v>1388933</v>
       </c>
       <c r="N61" t="n">
-        <v>0.481</v>
+        <v>2.23</v>
       </c>
       <c r="O61" t="n">
         <v>8.92</v>
       </c>
       <c r="P61" t="n">
-        <v>12.25</v>
+        <v>11.74</v>
       </c>
       <c r="Q61" t="n">
-        <v>9.5684</v>
+        <v>9.5646</v>
       </c>
       <c r="R61" t="n">
-        <v>8.109299999999999</v>
+        <v>8.1084</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9870,13 +9850,13 @@
         </is>
       </c>
       <c r="U61" t="n">
-        <v>10.4811</v>
+        <v>10.463</v>
       </c>
       <c r="V61" t="n">
-        <v>9.8164</v>
+        <v>9.808999999999999</v>
       </c>
       <c r="W61" t="n">
-        <v>8.3786</v>
+        <v>8.3767</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -9889,18 +9869,18 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>68.5</v>
+        <v>66.62</v>
       </c>
       <c r="AA61" t="n">
-        <v>10.5485</v>
+        <v>10.5535</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC61" t="n">
-        <v>10.5485</v>
+        <v>10.5535</v>
       </c>
       <c r="AD61" t="n">
         <v>9.059100000000001</v>
@@ -9917,39 +9897,39 @@
         <v>11.97</v>
       </c>
       <c r="AH61" t="n">
-        <v>12.0621</v>
+        <v>12.0307</v>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.06</t>
+          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.03</t>
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="AK61" t="n">
         <v>0.95</v>
       </c>
       <c r="AL61" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="AM61" t="n">
-        <v>8.84</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AN61" t="n">
-        <v>13.48</v>
+        <v>13.42</v>
       </c>
       <c r="AO61" t="n">
-        <v>14.35</v>
+        <v>14</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.5))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.6))</t>
         </is>
       </c>
     </row>
@@ -9966,11 +9946,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>63.63</v>
+        <v>60.31</v>
       </c>
       <c r="E62" t="n">
         <v>1.0421</v>
@@ -9987,22 +9967,22 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>225345</v>
+        <v>233984</v>
       </c>
       <c r="J62" t="n">
-        <v>987741</v>
+        <v>1396945</v>
       </c>
       <c r="K62" t="n">
-        <v>4.383</v>
+        <v>5.97</v>
       </c>
       <c r="L62" t="n">
-        <v>85700</v>
+        <v>127057</v>
       </c>
       <c r="M62" t="n">
-        <v>192662</v>
+        <v>1760025</v>
       </c>
       <c r="N62" t="n">
-        <v>2.248</v>
+        <v>13.852</v>
       </c>
       <c r="O62" t="n">
         <v>48.5</v>
@@ -10011,10 +9991,10 @@
         <v>54.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>51.1384</v>
+        <v>51.072</v>
       </c>
       <c r="R62" t="n">
-        <v>45.7212</v>
+        <v>45.7046</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -10027,13 +10007,13 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>53.6849</v>
+        <v>53.3687</v>
       </c>
       <c r="V62" t="n">
-        <v>51.1778</v>
+        <v>51.0476</v>
       </c>
       <c r="W62" t="n">
-        <v>46.2809</v>
+        <v>46.2478</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -10046,14 +10026,14 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>82.01000000000001</v>
+        <v>77.94</v>
       </c>
       <c r="AA62" t="n">
-        <v>55.6854</v>
+        <v>55.5267</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-08-03 08:43:56</t>
+          <t>2026-08-03 17:13:12</t>
         </is>
       </c>
       <c r="AC62" t="n">
@@ -10106,7 +10086,7 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 82.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 77.9))</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI2" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI3" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI4" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI5" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI6" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI7" t="n">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI8" t="n">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI9" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI10" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI12" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI13" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI14" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI15" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI16" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI17" t="n">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI18" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI19" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI20" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI21" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI22" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI23" t="n">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI24" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI25" t="n">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI26" t="n">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI27" t="n">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI28" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI29" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI30" t="n">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI31" t="n">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI32" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI33" t="n">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI34" t="n">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI35" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI36" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI37" t="n">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI38" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:12</t>
+          <t>2026-08-03 19:24:16</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI40" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI41" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI42" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI43" t="n">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI44" t="n">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI45" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI46" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI47" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI48" t="n">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI50" t="n">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI51" t="n">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI52" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI53" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI54" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI55" t="n">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI56" t="n">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI57" t="n">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI58" t="n">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI59" t="n">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI60" t="n">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI61" t="n">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI62" t="n">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI63" t="n">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:20</t>
+          <t>2026-08-03 19:24:26</t>
         </is>
       </c>
       <c r="AI65" t="n">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:21</t>
+          <t>2026-08-03 19:24:27</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-03 19:14:21</t>
+          <t>2026-08-03 19:24:27</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SHARIAH</t>
+          <t>EGX33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -796,7 +796,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI2" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI3" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI4" t="n">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI5" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI6" t="n">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI7" t="n">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI8" t="n">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI9" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI10" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr"/>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI12" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI13" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI14" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI15" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI16" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI17" t="n">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI18" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI19" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI20" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI21" t="n">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI22" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI23" t="n">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI24" t="n">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI25" t="n">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI26" t="n">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI27" t="n">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI28" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI29" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI30" t="n">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI31" t="n">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI32" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI33" t="n">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI34" t="n">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI35" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI36" t="n">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI37" t="n">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI38" t="n">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:16</t>
+          <t>2026-08-03 19:27:34</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr"/>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI40" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI41" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI42" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI43" t="n">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI44" t="n">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI45" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI46" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI47" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI48" t="n">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI50" t="n">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI51" t="n">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI52" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI53" t="n">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI54" t="n">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI55" t="n">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI56" t="n">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI57" t="n">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI58" t="n">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI59" t="n">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI60" t="n">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI61" t="n">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI62" t="n">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI63" t="n">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:26</t>
+          <t>2026-08-03 19:27:42</t>
         </is>
       </c>
       <c r="AI65" t="n">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:27</t>
+          <t>2026-08-03 19:27:43</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-03 19:24:27</t>
+          <t>2026-08-03 19:27:43</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EGX33</t>
+          <t>EGX33SHARIAH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock_Analysis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Indices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indices" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK2" t="n">
@@ -870,7 +870,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK3" t="n">
@@ -1053,7 +1053,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1236,7 +1236,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -1419,7 +1419,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1606,7 +1606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -1771,7 +1771,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -1958,7 +1958,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -2141,7 +2141,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2314,7 +2314,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
@@ -2479,7 +2479,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -2666,7 +2666,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2851,7 +2851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -3014,7 +3014,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3195,7 +3195,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3378,7 +3378,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3563,7 +3563,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3746,7 +3746,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -3927,7 +3927,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4110,7 +4110,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4295,7 +4295,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK22" t="n">
@@ -4480,7 +4480,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4663,7 +4663,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -4844,7 +4844,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -5025,7 +5025,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK26" t="n">
@@ -5206,7 +5206,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -5389,7 +5389,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK28" t="n">
@@ -5572,7 +5572,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -5753,7 +5753,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK30" t="n">
@@ -5936,7 +5936,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK31" t="n">
@@ -6119,7 +6119,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK32" t="n">
@@ -6302,7 +6302,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK33" t="n">
@@ -6489,7 +6489,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK34" t="n">
@@ -6672,7 +6672,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK35" t="n">
@@ -6855,7 +6855,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK36" t="n">
@@ -7034,7 +7034,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK37" t="n">
@@ -7215,7 +7215,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK38" t="n">
@@ -7398,7 +7398,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:01</t>
+          <t>2026-08-04 00:02:12</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7559,7 +7559,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -7740,7 +7740,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK41" t="n">
@@ -7925,7 +7925,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK42" t="n">
@@ -8108,7 +8108,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK43" t="n">
@@ -8289,7 +8289,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK44" t="n">
@@ -8474,7 +8474,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK45" t="n">
@@ -8655,7 +8655,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK46" t="n">
@@ -8836,7 +8836,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8957,7 +8957,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK47" t="n">
@@ -9017,7 +9017,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK48" t="n">
@@ -9202,7 +9202,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9325,7 +9325,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9363,7 +9363,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK50" t="n">
@@ -9544,7 +9544,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK51" t="n">
@@ -9727,7 +9727,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK52" t="n">
@@ -9910,7 +9910,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK53" t="n">
@@ -10091,7 +10091,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK54" t="n">
@@ -10274,7 +10274,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK55" t="n">
@@ -10459,7 +10459,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10638,7 +10638,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK57" t="n">
@@ -10823,7 +10823,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK58" t="n">
@@ -11008,7 +11008,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK59" t="n">
@@ -11191,7 +11191,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK60" t="n">
@@ -11374,7 +11374,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK61" t="n">
@@ -11555,7 +11555,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK62" t="n">
@@ -11738,7 +11738,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11863,7 +11863,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK63" t="n">
@@ -11923,7 +11923,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr"/>
@@ -12084,7 +12084,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:11</t>
+          <t>2026-08-04 00:02:21</t>
         </is>
       </c>
       <c r="AK65" t="n">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:33</t>
+          <t>2026-08-04 00:02:36</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12467,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-03 20:57:33</t>
+          <t>2026-08-04 00:02:36</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_Analysis" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stock_Analysis" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Indices" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -721,17 +721,23 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>11.7081</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.1383</v>
+      </c>
       <c r="N2" t="n">
         <v>7930246</v>
       </c>
@@ -810,7 +816,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK2" t="n">
@@ -858,19 +864,19 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.8))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.8))</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -906,15 +912,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>56.1901</v>
+        <v>390.688</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>55.9931</v>
+      </c>
       <c r="N3" t="n">
         <v>713921</v>
       </c>
@@ -993,7 +1003,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK3" t="n">
@@ -1053,7 +1063,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1085,19 +1095,23 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>28.2144</v>
+        <v>21.6716</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.3141</v>
+      </c>
       <c r="N4" t="n">
         <v>1531665</v>
       </c>
@@ -1176,7 +1190,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1224,19 +1238,19 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.8))</t>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.8))</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1268,19 +1282,23 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23.2685</v>
+        <v>6.8621</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>35.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.6394</v>
+      </c>
       <c r="N5" t="n">
         <v>3194125</v>
       </c>
@@ -1359,7 +1377,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -1412,14 +1430,14 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1451,22 +1469,22 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>294.0735</v>
+        <v>620.4558</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>11.41</v>
+        <v>3.96</v>
       </c>
       <c r="M6" t="n">
-        <v>26.0326</v>
+        <v>74.8164</v>
       </c>
       <c r="N6" t="n">
         <v>306408</v>
@@ -1546,7 +1564,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1594,19 +1612,19 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 47.6))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 47.6))</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1642,18 +1660,18 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11.8696</v>
+        <v>25.6427</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>17.11</v>
+        <v>3.67</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8245</v>
+        <v>3.0975</v>
       </c>
       <c r="N7" t="n">
         <v>5976389</v>
@@ -1733,7 +1751,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -1771,7 +1789,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1803,22 +1821,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29.2548</v>
+        <v>25.2896</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>21.62</v>
+        <v>11.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3872</v>
+        <v>2.4977</v>
       </c>
       <c r="N8" t="n">
         <v>1258394</v>
@@ -1898,7 +1916,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -1951,14 +1969,14 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 54.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 54.4))</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1994,15 +2012,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>182.8395</v>
+        <v>1685.4091</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M9" t="n">
+        <v>246.0436</v>
+      </c>
       <c r="N9" t="n">
         <v>188989</v>
       </c>
@@ -2081,7 +2103,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -2141,7 +2163,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2177,18 +2199,18 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>114.5967</v>
+        <v>107.1044</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.17</v>
+        <v>5.19</v>
       </c>
       <c r="M10" t="n">
-        <v>112.7166</v>
+        <v>13.68</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
@@ -2254,7 +2276,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2314,7 +2336,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2350,18 +2372,18 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>23.0355</v>
+        <v>38.1354</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.01</v>
+        <v>8.48</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2917</v>
+        <v>2.6657</v>
       </c>
       <c r="N11" t="n">
         <v>1199694</v>
@@ -2441,7 +2463,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
@@ -2479,7 +2501,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2515,18 +2537,18 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14.952</v>
+        <v>37.1315</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.15</v>
+        <v>3.52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4734</v>
+        <v>4.1165</v>
       </c>
       <c r="N12" t="n">
         <v>17293558</v>
@@ -2606,7 +2628,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -2666,7 +2688,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2698,20 +2720,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>296.8833</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.119999999999999</v>
+        <v>2.94</v>
       </c>
       <c r="M13" t="n">
-        <v>13.2125</v>
+        <v>35.2499</v>
       </c>
       <c r="N13" t="n">
         <v>1025038</v>
@@ -2791,7 +2815,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2839,19 +2863,19 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2886,17 +2910,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>3.3532</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.46</v>
+        <v>16.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1778</v>
+        <v>0.3228</v>
       </c>
       <c r="N14" t="n">
         <v>12224958</v>
@@ -2976,7 +3002,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -3014,7 +3040,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3135,7 +3161,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3195,7 +3221,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3318,7 +3344,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3378,7 +3404,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3503,7 +3529,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3563,7 +3589,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3595,19 +3621,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>36.9444</v>
+        <v>160.6145</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M18" t="n">
+        <v>19.7695</v>
+      </c>
       <c r="N18" t="n">
         <v>1334297</v>
       </c>
@@ -3686,7 +3716,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3739,14 +3769,14 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 40.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 40.6))</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3867,7 +3897,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -3927,7 +3957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4050,7 +4080,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4110,7 +4140,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4235,7 +4265,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4295,7 +4325,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4330,17 +4360,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>136.1878</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>44.91</v>
+        <v>14.54</v>
       </c>
       <c r="M22" t="n">
-        <v>6.2253</v>
+        <v>15.4084</v>
       </c>
       <c r="N22" t="n">
         <v>368909</v>
@@ -4420,7 +4452,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK22" t="n">
@@ -4480,7 +4512,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4516,15 +4548,19 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>95.3321</v>
+        <v>138.9692</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>14.4112</v>
+      </c>
       <c r="N23" t="n">
         <v>281658</v>
       </c>
@@ -4603,7 +4639,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4663,7 +4699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4695,17 +4731,23 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>94.5438</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="M24" t="n">
+        <v>10.0273</v>
+      </c>
       <c r="N24" t="n">
         <v>397511</v>
       </c>
@@ -4784,7 +4826,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -4837,14 +4879,14 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.3))</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4965,7 +5007,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -5025,7 +5067,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5057,17 +5099,23 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>6829.0468</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1071.5117</v>
+      </c>
       <c r="N26" t="n">
         <v>156711</v>
       </c>
@@ -5146,7 +5194,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK26" t="n">
@@ -5199,14 +5247,14 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (94.7); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 94.7))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (94.7); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 94.7))</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5329,7 +5377,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -5389,7 +5437,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5512,7 +5560,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK28" t="n">
@@ -5572,7 +5620,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5693,7 +5741,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -5753,7 +5801,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5785,18 +5833,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>64.5389</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>10.05</v>
+      </c>
       <c r="M30" t="n">
-        <v>2.7226</v>
+        <v>3.4135</v>
       </c>
       <c r="N30" t="n">
         <v>793904</v>
@@ -5876,7 +5928,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK30" t="n">
@@ -5929,14 +5981,14 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6059,7 +6111,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK31" t="n">
@@ -6119,7 +6171,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6242,7 +6294,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK32" t="n">
@@ -6302,7 +6354,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6338,18 +6390,18 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>9.315300000000001</v>
+        <v>6.4785</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>14.38</v>
+        <v>16.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0.6711</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="N33" t="n">
         <v>2598810</v>
@@ -6429,7 +6481,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK33" t="n">
@@ -6489,7 +6541,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6612,7 +6664,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK34" t="n">
@@ -6672,7 +6724,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6704,19 +6756,23 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>25.3174</v>
+        <v>5.1506</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>48.73</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3224</v>
+      </c>
       <c r="N35" t="n">
         <v>2820657</v>
       </c>
@@ -6795,7 +6851,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK35" t="n">
@@ -6843,19 +6899,19 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.9))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.9))</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6887,17 +6943,23 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>599.4378</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M36" t="n">
+        <v>81.28489999999999</v>
+      </c>
       <c r="N36" t="n">
         <v>714482</v>
       </c>
@@ -6974,7 +7036,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK36" t="n">
@@ -7027,14 +7089,14 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.0))</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7069,14 +7131,20 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>23.0852</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.9133</v>
+      </c>
       <c r="N37" t="n">
         <v>2098172</v>
       </c>
@@ -7155,7 +7223,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK37" t="n">
@@ -7215,7 +7283,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7251,15 +7319,19 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>9.154400000000001</v>
+        <v>14.1145</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.2372</v>
+      </c>
       <c r="N38" t="n">
         <v>7767167</v>
       </c>
@@ -7338,7 +7410,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK38" t="n">
@@ -7398,7 +7470,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7521,7 +7593,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:12</t>
+          <t>2026-08-03 21:20:39</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7559,7 +7631,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7680,7 +7752,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -7740,7 +7812,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7772,20 +7844,22 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>134.1338</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>5.07</v>
+        <v>3.74</v>
       </c>
       <c r="M41" t="n">
-        <v>10.3202</v>
+        <v>14.1296</v>
       </c>
       <c r="N41" t="n">
         <v>2150582</v>
@@ -7865,7 +7939,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK41" t="n">
@@ -7918,14 +7992,14 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.7))</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7961,15 +8035,19 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>37.8133</v>
+        <v>44.5196</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4.0132</v>
+      </c>
       <c r="N42" t="n">
         <v>1877096</v>
       </c>
@@ -8048,7 +8126,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK42" t="n">
@@ -8108,7 +8186,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8229,7 +8307,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK43" t="n">
@@ -8289,7 +8367,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8414,7 +8492,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK44" t="n">
@@ -8474,7 +8552,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8595,7 +8673,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK45" t="n">
@@ -8655,7 +8733,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8776,7 +8854,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK46" t="n">
@@ -8836,7 +8914,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8871,14 +8949,20 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>0.5286</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.0413</v>
+      </c>
       <c r="N47" t="n">
         <v>39851604</v>
       </c>
@@ -8957,7 +9041,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK47" t="n">
@@ -9017,7 +9101,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9142,7 +9226,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK48" t="n">
@@ -9202,7 +9286,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9325,7 +9409,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9363,7 +9447,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9484,7 +9568,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK50" t="n">
@@ -9544,7 +9628,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9667,7 +9751,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK51" t="n">
@@ -9727,7 +9811,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9763,15 +9847,19 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>244.5608</v>
+        <v>320.841</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M52" t="n">
+        <v>31.5025</v>
+      </c>
       <c r="N52" t="n">
         <v>93109</v>
       </c>
@@ -9850,7 +9938,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK52" t="n">
@@ -9910,7 +9998,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10031,7 +10119,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK53" t="n">
@@ -10091,7 +10179,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10123,19 +10211,23 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>11.9106</v>
+        <v>6.1428</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.5698</v>
+      </c>
       <c r="N54" t="n">
         <v>24738418</v>
       </c>
@@ -10214,7 +10306,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK54" t="n">
@@ -10267,14 +10359,14 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 51.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 51.9))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10399,7 +10491,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK55" t="n">
@@ -10459,7 +10551,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10578,7 +10670,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10638,7 +10730,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10763,7 +10855,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK57" t="n">
@@ -10823,7 +10915,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10858,17 +10950,19 @@
           <t>No</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>16.1382</v>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>22.98</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8356</v>
+        <v>1.8104</v>
       </c>
       <c r="N58" t="n">
         <v>723230</v>
@@ -10948,7 +11042,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK58" t="n">
@@ -11008,7 +11102,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11131,7 +11225,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK59" t="n">
@@ -11191,7 +11285,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11314,7 +11408,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK60" t="n">
@@ -11374,7 +11468,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11495,7 +11589,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK61" t="n">
@@ -11555,7 +11649,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11591,15 +11685,19 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>54.4692</v>
+        <v>57.2568</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4.5734</v>
+      </c>
       <c r="N62" t="n">
         <v>233984</v>
       </c>
@@ -11678,7 +11776,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK62" t="n">
@@ -11738,7 +11836,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11770,20 +11868,22 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>25.7518</v>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Blended (Graham+PE)</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>5.57</v>
+        <v>2.97</v>
       </c>
       <c r="M63" t="n">
-        <v>1.438</v>
+        <v>2.685</v>
       </c>
       <c r="N63" t="n">
         <v>6699518</v>
@@ -11863,7 +11963,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK63" t="n">
@@ -11916,14 +12016,14 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 55.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 55.4))</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -11959,15 +12059,19 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>23.4021</v>
+        <v>33.5548</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="M64" t="n">
+        <v>4.1161</v>
+      </c>
       <c r="N64" t="n">
         <v>654460</v>
       </c>
@@ -12046,7 +12150,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr"/>
@@ -12084,7 +12188,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12120,16 +12224,18 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>39.6478</v>
+        <v>115.1699</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>USD-Comparison (fallback)</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>Blended (Graham+PE)</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>2.94</v>
+      </c>
       <c r="M65" t="n">
-        <v>4.6304</v>
+        <v>13.3926</v>
       </c>
       <c r="N65" t="n">
         <v>3823357</v>
@@ -12209,7 +12315,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:21</t>
+          <t>2026-08-03 21:20:47</t>
         </is>
       </c>
       <c r="AK65" t="n">
@@ -12410,7 +12516,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:36</t>
+          <t>2026-08-03 21:20:54</t>
         </is>
       </c>
     </row>
@@ -12467,7 +12573,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-04 00:02:36</t>
+          <t>2026-08-03 21:20:54</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9.1</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>0.176</v>
@@ -742,10 +742,10 @@
         <v>7930246</v>
       </c>
       <c r="O2" t="n">
-        <v>19313373</v>
+        <v>1190024</v>
       </c>
       <c r="P2" t="n">
-        <v>2.435</v>
+        <v>0.15</v>
       </c>
       <c r="Q2" t="n">
         <v>3556819</v>
@@ -763,10 +763,10 @@
         <v>8.49</v>
       </c>
       <c r="V2" t="n">
-        <v>8.1752</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6361</v>
+        <v>7.6434</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>8.4346</v>
+        <v>8.501799999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.2393</v>
+        <v>8.2746</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.8882</v>
+        <v>7.9007</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>0.257</v>
+        <v>0.2797</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1387</v>
+        <v>0.1669</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>64.78</v>
+        <v>65.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.5631</v>
+        <v>8.5891</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK2" t="n">
         <v>8.595000000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>8.291600000000001</v>
+        <v>8.3507</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>9.1684</v>
+        <v>9.266999999999999</v>
       </c>
       <c r="AO2" t="n">
         <v>9.3924</v>
@@ -841,20 +841,20 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.17; TP2: Fibonacci R2 at 9.39; TP3: Classic R1 at 9.42</t>
+          <t>TP1: Bollinger Upper Band at 9.27; TP2: Fibonacci R2 at 9.39; TP3: Classic R1 at 9.42</t>
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.63</v>
+        <v>3.26</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.71</v>
+        <v>3.36</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.67</v>
+        <v>7.82</v>
       </c>
       <c r="AV2" t="n">
         <v>9.279999999999999</v>
@@ -869,14 +869,14 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.8))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.3))</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>55.8</v>
+        <v>56.1</v>
       </c>
       <c r="F3" t="n">
         <v>1.1079</v>
@@ -929,10 +929,10 @@
         <v>713921</v>
       </c>
       <c r="O3" t="n">
-        <v>796770</v>
+        <v>71233</v>
       </c>
       <c r="P3" t="n">
-        <v>1.116</v>
+        <v>0.1</v>
       </c>
       <c r="Q3" t="n">
         <v>199463</v>
@@ -950,10 +950,10 @@
         <v>56.7</v>
       </c>
       <c r="V3" t="n">
-        <v>56.0708</v>
+        <v>56.0928</v>
       </c>
       <c r="W3" t="n">
-        <v>51.3632</v>
+        <v>51.4487</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>56.1454</v>
+        <v>56.141</v>
       </c>
       <c r="AA3" t="n">
-        <v>55.6257</v>
+        <v>55.6443</v>
       </c>
       <c r="AB3" t="n">
-        <v>49.8954</v>
+        <v>49.9572</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -985,40 +985,40 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>0.1992</v>
+        <v>0.1709</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1946</v>
+        <v>0.1898</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>48.27</v>
+        <v>50.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>56.2891</v>
+        <v>56.2899</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>54.4044</v>
+        <v>56.0928</v>
       </c>
       <c r="AL3" t="n">
-        <v>54.31</v>
+        <v>55.586</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>57.6186</v>
+        <v>57.6126</v>
       </c>
       <c r="AO3" t="n">
         <v>57.9093</v>
@@ -1028,42 +1028,42 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 57.62; TP2: Fibonacci R1 at 57.91; TP3: Classic R1 at 58.33</t>
+          <t>TP1: Bollinger Upper Band at 57.61; TP2: Fibonacci R1 at 57.91; TP3: Classic R1 at 58.33</t>
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>34.06</v>
+        <v>3</v>
       </c>
       <c r="AS3" t="n">
-        <v>37.14</v>
+        <v>3.58</v>
       </c>
       <c r="AT3" t="n">
-        <v>41.64</v>
+        <v>4.42</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.91</v>
+        <v>2.71</v>
       </c>
       <c r="AV3" t="n">
-        <v>6.44</v>
+        <v>3.24</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.22</v>
+        <v>3.99</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 48.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.3))</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27.5</v>
+        <v>30.3</v>
       </c>
       <c r="F4" t="n">
         <v>0.5379</v>
@@ -1116,10 +1116,10 @@
         <v>1531665</v>
       </c>
       <c r="O4" t="n">
-        <v>971317</v>
+        <v>5922644</v>
       </c>
       <c r="P4" t="n">
-        <v>0.634</v>
+        <v>3.867</v>
       </c>
       <c r="Q4" t="n">
         <v>1061237</v>
@@ -1137,10 +1137,10 @@
         <v>28.0973</v>
       </c>
       <c r="V4" t="n">
-        <v>27.9888</v>
+        <v>28.039</v>
       </c>
       <c r="W4" t="n">
-        <v>26.908</v>
+        <v>26.9495</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>27.6471</v>
+        <v>27.8997</v>
       </c>
       <c r="AA4" t="n">
-        <v>27.8915</v>
+        <v>27.9859</v>
       </c>
       <c r="AB4" t="n">
-        <v>25.9394</v>
+        <v>25.9828</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1172,85 +1172,85 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>-0.1935</v>
+        <v>0.0422</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1571</v>
+        <v>-0.1172</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>46.75</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>27.7512</v>
+        <v>28.106</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>26.8766</v>
+        <v>28.106</v>
       </c>
       <c r="AL4" t="n">
-        <v>26.7256</v>
+        <v>27.2726</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN4" t="n">
-        <v>27.9916</v>
+        <v>32.3233</v>
       </c>
       <c r="AO4" t="n">
-        <v>28.521</v>
+        <v>34.432</v>
       </c>
       <c r="AP4" t="n">
-        <v>28.6067</v>
+        <v>33.3186</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 27.99; TP2: Fibonacci R1 at 28.52; TP3: Classic R1 at 28.61</t>
+          <t>TP1: Classic R3 at 32.32; TP2: Extension at 34.43; TP3: Extension at 33.32</t>
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>7.39</v>
+        <v>5.06</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.89</v>
+        <v>7.59</v>
       </c>
       <c r="AT4" t="n">
-        <v>11.46</v>
+        <v>6.25</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.15</v>
+        <v>15.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.12</v>
+        <v>22.51</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.44</v>
+        <v>18.55</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.8))</t>
+          <t>Golden Cross confirmed, RSI overbought (70.3); entry: enhanced entry at VWMA (overbought (RSI: 70.3))</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23.49</v>
+        <v>23.82</v>
       </c>
       <c r="F5" t="n">
         <v>0.4473</v>
@@ -1303,10 +1303,10 @@
         <v>3194125</v>
       </c>
       <c r="O5" t="n">
-        <v>7115369</v>
+        <v>1721924</v>
       </c>
       <c r="P5" t="n">
-        <v>2.228</v>
+        <v>0.539</v>
       </c>
       <c r="Q5" t="n">
         <v>1163435</v>
@@ -1324,10 +1324,10 @@
         <v>23.2073</v>
       </c>
       <c r="V5" t="n">
-        <v>21.88</v>
+        <v>21.9242</v>
       </c>
       <c r="W5" t="n">
-        <v>19.3505</v>
+        <v>19.4056</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>22.5375</v>
+        <v>22.6597</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.9435</v>
+        <v>22.0171</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.4866</v>
+        <v>19.5297</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.3929</v>
+        <v>0.4468</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3622</v>
+        <v>0.3791</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1370,58 +1370,58 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>61.44</v>
+        <v>63.86</v>
       </c>
       <c r="AI5" t="n">
-        <v>22.9109</v>
+        <v>22.8746</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>22.9109</v>
+        <v>22.8746</v>
       </c>
       <c r="AL5" t="n">
-        <v>21.87</v>
+        <v>22.15</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>23.7076</v>
+        <v>24.3367</v>
       </c>
       <c r="AO5" t="n">
-        <v>23.7306</v>
+        <v>24.6061</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.3367</v>
+        <v>26.0233</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 23.71; TP2: Fibonacci R1 at 23.73; TP3: Classic R1 at 24.34</t>
+          <t>TP1: Classic R1 at 24.34; TP2: Fibonacci R2 at 24.61; TP3: Classic R2 at 26.02</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.77</v>
+        <v>2.02</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.79</v>
+        <v>2.39</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.37</v>
+        <v>4.35</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.48</v>
+        <v>6.39</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.58</v>
+        <v>7.57</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.22</v>
+        <v>13.76</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1430,14 +1430,14 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.9))</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>297.01</v>
+        <v>297.15</v>
       </c>
       <c r="F6" t="n">
         <v>5.8491</v>
@@ -1490,10 +1490,10 @@
         <v>306408</v>
       </c>
       <c r="O6" t="n">
-        <v>106507</v>
+        <v>26086</v>
       </c>
       <c r="P6" t="n">
-        <v>0.348</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q6" t="n">
         <v>53250</v>
@@ -1511,10 +1511,10 @@
         <v>302.7</v>
       </c>
       <c r="V6" t="n">
-        <v>304.326</v>
+        <v>303.809</v>
       </c>
       <c r="W6" t="n">
-        <v>258.4375</v>
+        <v>259.1232</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1527,13 +1527,13 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>298.5959</v>
+        <v>298.4582</v>
       </c>
       <c r="AA6" t="n">
-        <v>299.2927</v>
+        <v>299.2087</v>
       </c>
       <c r="AB6" t="n">
-        <v>262.5698</v>
+        <v>262.9139</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>-0.3193</v>
+        <v>-0.4102</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.4502</v>
+        <v>-0.4422</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1557,18 +1557,18 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>300.332</v>
+        <v>300.47</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>290.3133</v>
+        <v>290.2837</v>
       </c>
       <c r="AL6" t="n">
         <v>285.9946</v>
@@ -1579,36 +1579,36 @@
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>300.2505</v>
+        <v>300.932</v>
       </c>
       <c r="AO6" t="n">
-        <v>307.2987</v>
+        <v>307.2933</v>
       </c>
       <c r="AP6" t="n">
         <v>308.3187</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 300.25; TP2: Bollinger Upper Band at 307.3; TP3: Fibonacci R1 at 308.32</t>
+          <t>TP1: 100 SMA at 300.93; TP2: Bollinger Upper Band at 307.29; TP3: Fibonacci R1 at 308.32</t>
         </is>
       </c>
       <c r="AR6" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.42</v>
+        <v>3.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>6.21</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1617,14 +1617,14 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 47.6))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 47.8))</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.11</v>
+        <v>14.3</v>
       </c>
       <c r="F7" t="n">
         <v>0.2245</v>
@@ -1677,10 +1677,10 @@
         <v>5976389</v>
       </c>
       <c r="O7" t="n">
-        <v>79327908</v>
+        <v>21138731</v>
       </c>
       <c r="P7" t="n">
-        <v>13.274</v>
+        <v>3.537</v>
       </c>
       <c r="Q7" t="n">
         <v>3349388</v>
@@ -1698,10 +1698,10 @@
         <v>11.87</v>
       </c>
       <c r="V7" t="n">
-        <v>11.8138</v>
+        <v>11.8686</v>
       </c>
       <c r="W7" t="n">
-        <v>11.3148</v>
+        <v>11.3296</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>11.8395</v>
+        <v>12.0739</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.7004</v>
+        <v>11.8023</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.0559</v>
+        <v>11.0881</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.1623</v>
+        <v>0.3366</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.0151</v>
+        <v>0.0553</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>80.14</v>
+        <v>81.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>12.7928</v>
+        <v>12.9898</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>12.7928</v>
+        <v>14.065</v>
       </c>
       <c r="AL7" t="n">
-        <v>11.3148</v>
+        <v>11.3296</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
@@ -1782,14 +1782,14 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (80.1); entry: enhanced entry at VWMA (overbought (RSI: 80.1))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 81.1))</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>34.6</v>
       </c>
       <c r="F8" t="n">
         <v>0.5662</v>
@@ -1842,10 +1842,10 @@
         <v>1258394</v>
       </c>
       <c r="O8" t="n">
-        <v>1965823</v>
+        <v>5296925</v>
       </c>
       <c r="P8" t="n">
-        <v>1.562</v>
+        <v>4.209</v>
       </c>
       <c r="Q8" t="n">
         <v>504608</v>
@@ -1863,10 +1863,10 @@
         <v>29.5707</v>
       </c>
       <c r="V8" t="n">
-        <v>29.6822</v>
+        <v>29.7962</v>
       </c>
       <c r="W8" t="n">
-        <v>27.0506</v>
+        <v>27.1073</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>29.505</v>
+        <v>29.9902</v>
       </c>
       <c r="AA8" t="n">
-        <v>29.4341</v>
+        <v>29.6367</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.3648</v>
+        <v>27.4368</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1898,29 +1898,29 @@
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>-0.22</v>
+        <v>0.2155</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.201</v>
+        <v>-0.1177</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>54.38</v>
+        <v>76.42</v>
       </c>
       <c r="AI8" t="n">
-        <v>29.5847</v>
+        <v>30.6494</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>29.6822</v>
+        <v>32.24</v>
       </c>
       <c r="AL8" t="n">
         <v>29.1</v>
@@ -1931,36 +1931,36 @@
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>30.8533</v>
+        <v>36.4067</v>
       </c>
       <c r="AO8" t="n">
-        <v>30.954</v>
+        <v>38.49</v>
       </c>
       <c r="AP8" t="n">
-        <v>31.4974</v>
+        <v>37.39</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 30.85; TP2: Fibonacci R1 at 30.95; TP3: Bollinger Upper Band at 31.5</t>
+          <t>TP1: Classic R3 at 36.41; TP2: Extension at 38.49; TP3: Extension at 37.39</t>
         </is>
       </c>
       <c r="AR8" t="n">
-        <v>2.01</v>
+        <v>1.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.12</v>
+        <v>1.64</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.95</v>
+        <v>12.92</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.28</v>
+        <v>19.39</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.12</v>
+        <v>15.97</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -1969,14 +1969,14 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 54.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.4))</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>183.35</v>
+        <v>182.2</v>
       </c>
       <c r="F9" t="n">
         <v>3.6026</v>
@@ -2029,10 +2029,10 @@
         <v>188989</v>
       </c>
       <c r="O9" t="n">
-        <v>66559</v>
+        <v>11631</v>
       </c>
       <c r="P9" t="n">
-        <v>0.352</v>
+        <v>0.062</v>
       </c>
       <c r="Q9" t="n">
         <v>33725</v>
@@ -2050,10 +2050,10 @@
         <v>187.3056</v>
       </c>
       <c r="V9" t="n">
-        <v>182.5298</v>
+        <v>182.354</v>
       </c>
       <c r="W9" t="n">
-        <v>161.4409</v>
+        <v>161.9794</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>182.7376</v>
+        <v>182.6864</v>
       </c>
       <c r="AA9" t="n">
-        <v>182.2833</v>
+        <v>182.2801</v>
       </c>
       <c r="AB9" t="n">
-        <v>157.3649</v>
+        <v>157.612</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>1.4657</v>
+        <v>1.227</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.2133</v>
+        <v>1.2161</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -2096,58 +2096,58 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>51.6</v>
+        <v>49.8</v>
       </c>
       <c r="AI9" t="n">
-        <v>183.9291</v>
+        <v>184.3539</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>182.5298</v>
+        <v>172.9267</v>
       </c>
       <c r="AL9" t="n">
-        <v>174</v>
+        <v>172.5107</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>184.4084</v>
+        <v>184.2943</v>
       </c>
       <c r="AO9" t="n">
         <v>192.0267</v>
       </c>
       <c r="AP9" t="n">
-        <v>192.3239</v>
+        <v>192.3473</v>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 184.41; TP2: Fibonacci R1 at 192.03; TP3: Bollinger Upper Band at 192.32</t>
+          <t>TP1: 100 SMA at 184.29; TP2: Fibonacci R1 at 192.03; TP3: Bollinger Upper Band at 192.35</t>
         </is>
       </c>
       <c r="AR9" t="n">
-        <v>0.22</v>
+        <v>27.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.11</v>
+        <v>45.92</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.15</v>
+        <v>46.69</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>6.57</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.2</v>
+        <v>11.05</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.37</v>
+        <v>11.23</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2156,14 +2156,14 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 51.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 49.8))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>695.2</v>
+        <v>699.75</v>
       </c>
       <c r="F10" t="n">
         <v>1.4031</v>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>320375</v>
+        <v>29479</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>724.4834</v>
+        <v>724.5184</v>
       </c>
       <c r="W10" t="n">
-        <v>544.3598</v>
+        <v>545.7186</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>710.0312</v>
+        <v>709.0521</v>
       </c>
       <c r="AA10" t="n">
-        <v>697.1623</v>
+        <v>697.2637999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>566.496</v>
+        <v>567.8219</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2258,32 +2258,32 @@
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>-2.0759</v>
+        <v>-2.6077</v>
       </c>
       <c r="AF10" t="n">
-        <v>-2.3</v>
+        <v>-2.3615</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>43.16</v>
+        <v>45.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>700.5961</v>
+        <v>700.4705</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK10" t="n">
         <v>683.8</v>
       </c>
       <c r="AL10" t="n">
-        <v>678.2089</v>
+        <v>678.0697</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="AN10" t="n">
-        <v>726.5271</v>
+        <v>726.4413</v>
       </c>
       <c r="AO10" t="n">
         <v>728.646</v>
@@ -2301,20 +2301,20 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 726.53; TP2: Fibonacci R1 at 728.65; TP3: Classic R1 at 736.8</t>
+          <t>TP1: Bollinger Upper Band at 726.44; TP2: Fibonacci R1 at 728.65; TP3: Classic R1 at 736.8</t>
         </is>
       </c>
       <c r="AR10" t="n">
-        <v>7.64</v>
+        <v>7.44</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.02</v>
+        <v>7.83</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.48</v>
+        <v>9.25</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.25</v>
+        <v>6.24</v>
       </c>
       <c r="AV10" t="n">
         <v>6.56</v>
@@ -2329,14 +2329,14 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Classic S1 (neutral (RSI: 43.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Classic S1 (neutral (RSI: 45.4))</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.08</v>
+        <v>23.25</v>
       </c>
       <c r="F11" t="n">
         <v>0.4463</v>
@@ -2389,10 +2389,10 @@
         <v>1199694</v>
       </c>
       <c r="O11" t="n">
-        <v>2151889</v>
+        <v>689829</v>
       </c>
       <c r="P11" t="n">
-        <v>1.794</v>
+        <v>0.575</v>
       </c>
       <c r="Q11" t="n">
         <v>570452</v>
@@ -2410,10 +2410,10 @@
         <v>23.24</v>
       </c>
       <c r="V11" t="n">
-        <v>22.9224</v>
+        <v>22.9244</v>
       </c>
       <c r="W11" t="n">
-        <v>22.9508</v>
+        <v>22.9574</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>22.9328</v>
+        <v>22.963</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.925</v>
+        <v>22.9377</v>
       </c>
       <c r="AB11" t="n">
-        <v>22.909</v>
+        <v>22.9124</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.0127</v>
+        <v>0.0362</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0063</v>
+        <v>0.0123</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2456,14 +2456,14 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>53.01</v>
+        <v>56.03</v>
       </c>
       <c r="AI11" t="n">
-        <v>22.9864</v>
+        <v>22.9925</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2520,7 +2520,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14.95</v>
+        <v>14.9</v>
       </c>
       <c r="F12" t="n">
         <v>0.2863</v>
@@ -2554,10 +2554,10 @@
         <v>17293558</v>
       </c>
       <c r="O12" t="n">
-        <v>16828713</v>
+        <v>2273242</v>
       </c>
       <c r="P12" t="n">
-        <v>0.973</v>
+        <v>0.131</v>
       </c>
       <c r="Q12" t="n">
         <v>6525912</v>
@@ -2575,10 +2575,10 @@
         <v>14.99</v>
       </c>
       <c r="V12" t="n">
-        <v>14.8772</v>
+        <v>14.9044</v>
       </c>
       <c r="W12" t="n">
-        <v>10.4097</v>
+        <v>10.4467</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>14.7756</v>
+        <v>14.7874</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.3019</v>
+        <v>14.3253</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.2452</v>
+        <v>11.2815</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>-0.0175</v>
+        <v>-0.0033</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0199</v>
+        <v>0.0153</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>54.06</v>
+        <v>52.99</v>
       </c>
       <c r="AI12" t="n">
-        <v>14.8475</v>
+        <v>14.8496</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>14.88</v>
+        <v>14.8496</v>
       </c>
       <c r="AL12" t="n">
-        <v>14.4308</v>
+        <v>14.4319</v>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
@@ -2649,30 +2649,30 @@
         <v>15.1467</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.1722</v>
+        <v>15.1781</v>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 15.14; TP2: Classic R1 at 15.15; TP3: Bollinger Upper Band at 15.17</t>
+          <t>TP1: Fibonacci R1 at 15.14; TP2: Classic R1 at 15.15; TP3: Bollinger Upper Band at 15.18</t>
         </is>
       </c>
       <c r="AR12" t="n">
-        <v>0.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.65</v>
+        <v>0.79</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.96</v>
+        <v>2.21</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2681,14 +2681,14 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 53.0))</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>107.3</v>
+        <v>108.45</v>
       </c>
       <c r="F13" t="n">
         <v>2.0459</v>
@@ -2741,10 +2741,10 @@
         <v>1025038</v>
       </c>
       <c r="O13" t="n">
-        <v>1293622</v>
+        <v>165894</v>
       </c>
       <c r="P13" t="n">
-        <v>1.262</v>
+        <v>0.162</v>
       </c>
       <c r="Q13" t="n">
         <v>367755</v>
@@ -2762,10 +2762,10 @@
         <v>101.5</v>
       </c>
       <c r="V13" t="n">
-        <v>96.9686</v>
+        <v>97.2526</v>
       </c>
       <c r="W13" t="n">
-        <v>80.09910000000001</v>
+        <v>80.3964</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>102.1738</v>
+        <v>102.7715</v>
       </c>
       <c r="AA13" t="n">
-        <v>97.9872</v>
+        <v>98.39749999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>81.75230000000001</v>
+        <v>82.0179</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>3.413</v>
+        <v>3.4825</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5957</v>
+        <v>2.7731</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2808,58 +2808,58 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>61.41</v>
+        <v>62.91</v>
       </c>
       <c r="AI13" t="n">
-        <v>102.3653</v>
+        <v>102.7396</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>102.3653</v>
+        <v>103.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>102.1</v>
+        <v>95.1023</v>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>107.311</v>
+        <v>110.3933</v>
       </c>
       <c r="AO13" t="n">
-        <v>110.0319</v>
+        <v>110.8551</v>
       </c>
       <c r="AP13" t="n">
-        <v>110.3933</v>
+        <v>111.0823</v>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 107.31; TP2: Bollinger Upper Band at 110.03; TP3: Classic R1 at 110.39</t>
+          <t>TP1: Classic R1 at 110.39; TP2: Bollinger Upper Band at 110.86; TP3: Fibonacci R2 at 111.08</t>
         </is>
       </c>
       <c r="AR13" t="n">
-        <v>18.64</v>
+        <v>0.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>28.9</v>
+        <v>0.85</v>
       </c>
       <c r="AT13" t="n">
-        <v>30.26</v>
+        <v>0.88</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.83</v>
+        <v>6.56</v>
       </c>
       <c r="AV13" t="n">
-        <v>7.49</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.84</v>
+        <v>7.22</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 62.9))</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="F14" t="n">
         <v>0.1043</v>
@@ -2928,10 +2928,10 @@
         <v>12224958</v>
       </c>
       <c r="O14" t="n">
-        <v>87656166</v>
+        <v>24750698</v>
       </c>
       <c r="P14" t="n">
-        <v>7.17</v>
+        <v>2.025</v>
       </c>
       <c r="Q14" t="n">
         <v>5910925</v>
@@ -2949,10 +2949,10 @@
         <v>5.15</v>
       </c>
       <c r="V14" t="n">
-        <v>5.0972</v>
+        <v>5.1196</v>
       </c>
       <c r="W14" t="n">
-        <v>4.0632</v>
+        <v>4.0776</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>5.2411</v>
+        <v>5.3248</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.0483</v>
+        <v>5.0903</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.2863</v>
+        <v>4.3045</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>0.1703</v>
+        <v>0.2182</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0954</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2995,21 +2995,21 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>85.06999999999999</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.6244</v>
+        <v>5.6936</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>5.655</v>
+        <v>5.705</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.0304</v>
+        <v>5.2068</v>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
@@ -3033,14 +3033,14 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (85.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 85.1))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.8); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.8))</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="F15" t="n">
         <v>0.08890000000000001</v>
@@ -3087,10 +3087,10 @@
         <v>24381688</v>
       </c>
       <c r="O15" t="n">
-        <v>15425965</v>
+        <v>4323681</v>
       </c>
       <c r="P15" t="n">
-        <v>0.633</v>
+        <v>0.177</v>
       </c>
       <c r="Q15" t="n">
         <v>15156982</v>
@@ -3108,10 +3108,10 @@
         <v>4.65</v>
       </c>
       <c r="V15" t="n">
-        <v>3.1022</v>
+        <v>3.1522</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2259</v>
+        <v>2.2456</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>4.0186</v>
+        <v>4.1263</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.3076</v>
+        <v>3.3799</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.3635</v>
+        <v>2.3912</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>0.5657</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.4779</v>
+        <v>0.4993</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -3154,18 +3154,18 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>81.81</v>
+        <v>82.69</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.6264</v>
+        <v>3.6563</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3176,36 +3176,36 @@
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>5.3827</v>
+        <v>5.3832</v>
       </c>
       <c r="AO15" t="n">
         <v>5.4</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.3</v>
+        <v>5.478</v>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 5.38; TP2: Classic R1 at 5.4; TP3: Classic R2 at 6.3</t>
+          <t>TP1: Fibonacci R2 at 5.38; TP2: Classic R1 at 5.4; TP3: Bollinger Upper Band at 5.48</t>
         </is>
       </c>
       <c r="AR15" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.29</v>
+        <v>0.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>21.23</v>
+        <v>20.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>21.62</v>
+        <v>21.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>41.89</v>
+        <v>22.83</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
@@ -3214,14 +3214,14 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.8); entry: enhanced entry at Parabolic SAR (overbought (RSI: 81.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.7); entry: enhanced entry at Parabolic SAR (overbought (RSI: 82.7))</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.239</v>
+        <v>0.24</v>
       </c>
       <c r="F16" t="n">
         <v>0.0047</v>
@@ -3270,10 +3270,10 @@
         <v>268605836</v>
       </c>
       <c r="O16" t="n">
-        <v>276496230</v>
+        <v>44401880</v>
       </c>
       <c r="P16" t="n">
-        <v>1.029</v>
+        <v>0.165</v>
       </c>
       <c r="Q16" t="n">
         <v>154154120</v>
@@ -3291,10 +3291,10 @@
         <v>0.265</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2207</v>
+        <v>0.2215</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1802</v>
+        <v>0.1807</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3307,13 +3307,13 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0.2376</v>
+        <v>0.2378</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2242</v>
+        <v>0.2248</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1927</v>
+        <v>0.1932</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>0.0063</v>
+        <v>0.0058</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.008</v>
+        <v>0.0075</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -3337,14 +3337,14 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>53.84</v>
+        <v>54.56</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.2395</v>
+        <v>0.2411</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 0.26; TP2: Classic R1 at 0.27; TP3: Classic R2 at 0.3</t>
+          <t>TP1: Bollinger Upper Band at 0.26; TP2: Classic R1 at 0.27; TP3: Classic R2 at 0.3</t>
         </is>
       </c>
       <c r="AR16" t="n">
@@ -3397,14 +3397,14 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.6))</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3455,10 +3455,10 @@
         <v>31363648</v>
       </c>
       <c r="O17" t="n">
-        <v>14906022</v>
+        <v>3081686</v>
       </c>
       <c r="P17" t="n">
-        <v>0.475</v>
+        <v>0.098</v>
       </c>
       <c r="Q17" t="n">
         <v>11458173</v>
@@ -3476,10 +3476,10 @@
         <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6076</v>
+        <v>1.61</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4704</v>
+        <v>1.4717</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1.6592</v>
+        <v>1.6631</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6029</v>
+        <v>1.6067</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5084</v>
+        <v>1.5103</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>0.0275</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0312</v>
+        <v>0.0304</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -3525,18 +3525,18 @@
         <v>58.33</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.6654</v>
+        <v>1.6711</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>1.6654</v>
+        <v>1.6711</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.5879</v>
+        <v>1.5977</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -3558,22 +3558,22 @@
         </is>
       </c>
       <c r="AR17" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.3</v>
+        <v>3.94</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.68</v>
+        <v>5.32</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.26</v>
+        <v>7.89</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3608,7 +3608,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37</v>
+        <v>37.29</v>
       </c>
       <c r="F18" t="n">
         <v>0.7451</v>
@@ -3642,10 +3642,10 @@
         <v>1334297</v>
       </c>
       <c r="O18" t="n">
-        <v>797746</v>
+        <v>156354</v>
       </c>
       <c r="P18" t="n">
-        <v>0.598</v>
+        <v>0.117</v>
       </c>
       <c r="Q18" t="n">
         <v>401221</v>
@@ -3663,10 +3663,10 @@
         <v>38.59</v>
       </c>
       <c r="V18" t="n">
-        <v>37.7608</v>
+        <v>37.7936</v>
       </c>
       <c r="W18" t="n">
-        <v>30.8875</v>
+        <v>30.9614</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>38.2692</v>
+        <v>38.176</v>
       </c>
       <c r="AA18" t="n">
-        <v>37.4834</v>
+        <v>37.4758</v>
       </c>
       <c r="AB18" t="n">
-        <v>31.4777</v>
+        <v>31.5355</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0626</v>
+        <v>-0.1264</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.2296</v>
+        <v>0.1584</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3709,14 +3709,14 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>40.61</v>
+        <v>43.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>39.1064</v>
+        <v>39.0067</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3734,21 +3734,21 @@
         <v>40.4652</v>
       </c>
       <c r="AO18" t="n">
-        <v>40.5258</v>
+        <v>40.4817</v>
       </c>
       <c r="AP18" t="n">
         <v>40.6333</v>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 40.47; TP2: Bollinger Upper Band at 40.53; TP3: Classic R1 at 40.63</t>
+          <t>TP1: Fibonacci R1 at 40.47; TP2: Bollinger Upper Band at 40.48; TP3: Classic R1 at 40.63</t>
         </is>
       </c>
       <c r="AR18" t="n">
         <v>3.78</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AT18" t="n">
         <v>3.95</v>
@@ -3757,7 +3757,7 @@
         <v>10.36</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.52</v>
+        <v>10.4</v>
       </c>
       <c r="AW18" t="n">
         <v>10.81</v>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 40.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 43.2))</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3823,10 +3823,10 @@
         <v>1232113</v>
       </c>
       <c r="O19" t="n">
-        <v>1302576</v>
+        <v>18245</v>
       </c>
       <c r="P19" t="n">
-        <v>1.057</v>
+        <v>0.015</v>
       </c>
       <c r="Q19" t="n">
         <v>696425</v>
@@ -3844,10 +3844,10 @@
         <v>38.25</v>
       </c>
       <c r="V19" t="n">
-        <v>30.0054</v>
+        <v>30.2694</v>
       </c>
       <c r="W19" t="n">
-        <v>19.4992</v>
+        <v>19.6071</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>34.9233</v>
+        <v>35.0135</v>
       </c>
       <c r="AA19" t="n">
-        <v>30.8137</v>
+        <v>31.012</v>
       </c>
       <c r="AB19" t="n">
-        <v>21.4739</v>
+        <v>21.6171</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>1.6504</v>
+        <v>1.5375</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.0933</v>
+        <v>1.9821</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3893,55 +3893,55 @@
         <v>57.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>36.0849</v>
+        <v>36.1847</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>33.7957</v>
+        <v>34.23</v>
       </c>
       <c r="AL19" t="n">
-        <v>33.7643</v>
+        <v>34.0937</v>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AN19" t="n">
         <v>37.3616</v>
       </c>
       <c r="AO19" t="n">
-        <v>37.8043</v>
+        <v>37.7033</v>
       </c>
       <c r="AP19" t="n">
         <v>38.2267</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.8; TP3: Classic R1 at 38.23</t>
+          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.7; TP3: Classic R1 at 38.23</t>
         </is>
       </c>
       <c r="AR19" t="n">
-        <v>113.4</v>
+        <v>22.97</v>
       </c>
       <c r="AS19" t="n">
-        <v>127.48</v>
+        <v>25.48</v>
       </c>
       <c r="AT19" t="n">
-        <v>140.92</v>
+        <v>29.32</v>
       </c>
       <c r="AU19" t="n">
-        <v>10.55</v>
+        <v>9.15</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.86</v>
+        <v>10.15</v>
       </c>
       <c r="AW19" t="n">
-        <v>13.11</v>
+        <v>11.68</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 57.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 57.6))</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.55</v>
+        <v>10.56</v>
       </c>
       <c r="F20" t="n">
         <v>0.2109</v>
@@ -4006,10 +4006,10 @@
         <v>4415186</v>
       </c>
       <c r="O20" t="n">
-        <v>3269000</v>
+        <v>185195</v>
       </c>
       <c r="P20" t="n">
-        <v>0.74</v>
+        <v>0.042</v>
       </c>
       <c r="Q20" t="n">
         <v>2705737</v>
@@ -4027,10 +4027,10 @@
         <v>10.6802</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9628</v>
+        <v>10.0134</v>
       </c>
       <c r="W20" t="n">
-        <v>7.93</v>
+        <v>7.9482</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>10.6576</v>
+        <v>10.6483</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.0275</v>
+        <v>10.0484</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.2447</v>
+        <v>8.267799999999999</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -4062,10 +4062,10 @@
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>0.1511</v>
+        <v>0.1281</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.2546</v>
+        <v>0.2293</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -4073,18 +4073,18 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>50.35</v>
+        <v>50.63</v>
       </c>
       <c r="AI20" t="n">
-        <v>10.8661</v>
+        <v>10.8028</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>10.5425</v>
+        <v>10.5315</v>
       </c>
       <c r="AL20" t="n">
         <v>10.3209</v>
@@ -4098,33 +4098,33 @@
         <v>11.0391</v>
       </c>
       <c r="AO20" t="n">
-        <v>11.0855</v>
+        <v>11.15</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.15</v>
+        <v>11.2609</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.09; TP3: Classic R1 at 11.15</t>
+          <t>TP1: Fibonacci R1 at 11.04; TP2: Classic R1 at 11.15; TP3: Fibonacci R2 at 11.26</t>
         </is>
       </c>
       <c r="AR20" t="n">
-        <v>2.24</v>
+        <v>2.41</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.74</v>
+        <v>3.46</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.71</v>
+        <v>4.82</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.15</v>
+        <v>5.87</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.76</v>
+        <v>6.93</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
@@ -4133,14 +4133,14 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 50.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 50.6))</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="F21" t="n">
         <v>0.6398</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>20.42</v>
+        <v>20.62</v>
       </c>
       <c r="M21" t="n">
         <v>1.557</v>
@@ -4191,10 +4191,10 @@
         <v>690373</v>
       </c>
       <c r="O21" t="n">
-        <v>1655113</v>
+        <v>210649</v>
       </c>
       <c r="P21" t="n">
-        <v>2.397</v>
+        <v>0.305</v>
       </c>
       <c r="Q21" t="n">
         <v>245906</v>
@@ -4212,10 +4212,10 @@
         <v>36.7</v>
       </c>
       <c r="V21" t="n">
-        <v>35.12</v>
+        <v>35.0186</v>
       </c>
       <c r="W21" t="n">
-        <v>32.486</v>
+        <v>32.5608</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>34.4277</v>
+        <v>34.206</v>
       </c>
       <c r="AA21" t="n">
-        <v>35.1634</v>
+        <v>35.0433</v>
       </c>
       <c r="AB21" t="n">
-        <v>31.4337</v>
+        <v>31.4403</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>-0.7478</v>
+        <v>-0.8365</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.3289</v>
+        <v>-0.4304</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -4258,58 +4258,58 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>32.52</v>
+        <v>34.89</v>
       </c>
       <c r="AI21" t="n">
-        <v>34.9385</v>
+        <v>34.806</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK21" t="n">
+        <v>31.8155</v>
+      </c>
+      <c r="AL21" t="n">
         <v>31.5</v>
       </c>
-      <c r="AL21" t="n">
-        <v>29.9767</v>
-      </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>stop at Classic S1</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN21" t="n">
-        <v>32.486</v>
+        <v>32.5608</v>
       </c>
       <c r="AO21" t="n">
-        <v>35.9094</v>
+        <v>35.9013</v>
       </c>
       <c r="AP21" t="n">
         <v>37.0467</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 32.49; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
+          <t>TP1: 200 SMA at 32.56; TP2: 100 SMA at 35.9; TP3: Classic R1 at 37.05</t>
         </is>
       </c>
       <c r="AR21" t="n">
-        <v>0.65</v>
+        <v>2.36</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.89</v>
+        <v>12.95</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.64</v>
+        <v>16.58</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.13</v>
+        <v>2.34</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>12.84</v>
       </c>
       <c r="AW21" t="n">
-        <v>17.61</v>
+        <v>16.44</v>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
@@ -4318,14 +4318,14 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 32.5))</t>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 34.9))</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>279.6</v>
+        <v>273.02</v>
       </c>
       <c r="F22" t="n">
         <v>4.4235</v>
@@ -4378,10 +4378,10 @@
         <v>368909</v>
       </c>
       <c r="O22" t="n">
-        <v>2009657</v>
+        <v>490827</v>
       </c>
       <c r="P22" t="n">
-        <v>5.448</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
         <v>301029</v>
@@ -4399,10 +4399,10 @@
         <v>242</v>
       </c>
       <c r="V22" t="n">
-        <v>181.8986</v>
+        <v>184.059</v>
       </c>
       <c r="W22" t="n">
-        <v>125.3152</v>
+        <v>126.2703</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -4415,13 +4415,13 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>215.4441</v>
+        <v>220.9276</v>
       </c>
       <c r="AA22" t="n">
-        <v>186.9045</v>
+        <v>190.2816</v>
       </c>
       <c r="AB22" t="n">
-        <v>130.5949</v>
+        <v>132.012</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>20.5638</v>
+        <v>22.5899</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5926</v>
+        <v>17.7921</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4445,21 +4445,21 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>84.37</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>216.3197</v>
+        <v>219.7362</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>218.305</v>
+        <v>223.505</v>
       </c>
       <c r="AL22" t="n">
-        <v>209</v>
+        <v>210.412</v>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
@@ -4467,36 +4467,36 @@
         </is>
       </c>
       <c r="AN22" t="n">
+        <v>276.3811</v>
+      </c>
+      <c r="AO22" t="n">
         <v>287.98</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>365.95</v>
       </c>
-      <c r="AP22" t="n">
-        <v>422.3504</v>
-      </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 287.98; TP2: Classic R3 at 365.95; TP3: Extension at 422.35</t>
+          <t>TP1: Bollinger Upper Band at 276.38; TP2: Classic R2 at 287.98; TP3: Classic R3 at 365.95</t>
         </is>
       </c>
       <c r="AR22" t="n">
-        <v>7.49</v>
+        <v>4.04</v>
       </c>
       <c r="AS22" t="n">
-        <v>15.87</v>
+        <v>4.92</v>
       </c>
       <c r="AT22" t="n">
-        <v>21.93</v>
+        <v>10.88</v>
       </c>
       <c r="AU22" t="n">
-        <v>31.92</v>
+        <v>23.66</v>
       </c>
       <c r="AV22" t="n">
-        <v>67.63</v>
+        <v>28.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>93.47</v>
+        <v>63.73</v>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (84.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 84.4))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.4))</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>95.55</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F23" t="n">
         <v>1.8366</v>
@@ -4565,10 +4565,10 @@
         <v>281658</v>
       </c>
       <c r="O23" t="n">
-        <v>371446</v>
+        <v>50492</v>
       </c>
       <c r="P23" t="n">
-        <v>1.319</v>
+        <v>0.179</v>
       </c>
       <c r="Q23" t="n">
         <v>94273</v>
@@ -4586,10 +4586,10 @@
         <v>97.5</v>
       </c>
       <c r="V23" t="n">
-        <v>89.279</v>
+        <v>89.4174</v>
       </c>
       <c r="W23" t="n">
-        <v>81.5209</v>
+        <v>81.63030000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>92.47629999999999</v>
+        <v>92.80240000000001</v>
       </c>
       <c r="AA23" t="n">
-        <v>89.6127</v>
+        <v>89.8593</v>
       </c>
       <c r="AB23" t="n">
-        <v>83.15949999999999</v>
+        <v>83.2863</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>2.0194</v>
+        <v>2.041</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7728</v>
+        <v>1.8264</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -4632,21 +4632,21 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>64.76000000000001</v>
+        <v>65.66</v>
       </c>
       <c r="AI23" t="n">
-        <v>92.8747</v>
+        <v>93.0005</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>92.8747</v>
+        <v>93.0005</v>
       </c>
       <c r="AL23" t="n">
-        <v>91.8</v>
+        <v>92.5</v>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
@@ -4657,33 +4657,33 @@
         <v>96.5592</v>
       </c>
       <c r="AO23" t="n">
-        <v>97.78919999999999</v>
+        <v>98.1254</v>
       </c>
       <c r="AP23" t="n">
         <v>98.33</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 96.56; TP2: Bollinger Upper Band at 97.79; TP3: Classic R1 at 98.33</t>
+          <t>TP1: Fibonacci R1 at 96.56; TP2: Bollinger Upper Band at 98.13; TP3: Classic R1 at 98.33</t>
         </is>
       </c>
       <c r="AR23" t="n">
-        <v>3.43</v>
+        <v>7.11</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.57</v>
+        <v>10.24</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.08</v>
+        <v>10.65</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.97</v>
+        <v>3.83</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.29</v>
+        <v>5.51</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.87</v>
+        <v>5.73</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
@@ -4692,14 +4692,14 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.8))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.7))</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>43</v>
+        <v>43.06</v>
       </c>
       <c r="F24" t="n">
         <v>0.8149999999999999</v>
@@ -4752,10 +4752,10 @@
         <v>397511</v>
       </c>
       <c r="O24" t="n">
-        <v>1350669</v>
+        <v>42658</v>
       </c>
       <c r="P24" t="n">
-        <v>3.398</v>
+        <v>0.107</v>
       </c>
       <c r="Q24" t="n">
         <v>283208</v>
@@ -4773,10 +4773,10 @@
         <v>44.89</v>
       </c>
       <c r="V24" t="n">
-        <v>37.5704</v>
+        <v>37.74</v>
       </c>
       <c r="W24" t="n">
-        <v>34.8761</v>
+        <v>34.9506</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>41.1941</v>
+        <v>41.3718</v>
       </c>
       <c r="AA24" t="n">
-        <v>38.617</v>
+        <v>38.7912</v>
       </c>
       <c r="AB24" t="n">
-        <v>34.1521</v>
+        <v>34.2407</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>1.4227</v>
+        <v>1.4024</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.6092</v>
+        <v>1.5679</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -4819,21 +4819,21 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>62.33</v>
+        <v>62.55</v>
       </c>
       <c r="AI24" t="n">
-        <v>41.6594</v>
+        <v>41.7517</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>41.6594</v>
+        <v>41.7517</v>
       </c>
       <c r="AL24" t="n">
-        <v>37.9958</v>
+        <v>38.862</v>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
@@ -4844,33 +4844,33 @@
         <v>44.1009</v>
       </c>
       <c r="AO24" t="n">
-        <v>45.0132</v>
+        <v>44.739</v>
       </c>
       <c r="AP24" t="n">
         <v>45.3367</v>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 44.1; TP2: Bollinger Upper Band at 45.01; TP3: Classic R1 at 45.34</t>
+          <t>TP1: Fibonacci R1 at 44.1; TP2: Bollinger Upper Band at 44.74; TP3: Classic R1 at 45.34</t>
         </is>
       </c>
       <c r="AR24" t="n">
-        <v>0.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.92</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>1.24</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.86</v>
+        <v>5.63</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.050000000000001</v>
+        <v>7.15</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.83</v>
+        <v>8.59</v>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
@@ -4879,14 +4879,14 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.6))</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.68</v>
+        <v>13.37</v>
       </c>
       <c r="F25" t="n">
         <v>0.2405</v>
@@ -4933,10 +4933,10 @@
         <v>3067925</v>
       </c>
       <c r="O25" t="n">
-        <v>1968151</v>
+        <v>1635278</v>
       </c>
       <c r="P25" t="n">
-        <v>0.642</v>
+        <v>0.533</v>
       </c>
       <c r="Q25" t="n">
         <v>1392261</v>
@@ -4954,10 +4954,10 @@
         <v>12.3</v>
       </c>
       <c r="V25" t="n">
-        <v>10.6288</v>
+        <v>10.7142</v>
       </c>
       <c r="W25" t="n">
-        <v>8.1858</v>
+        <v>8.226599999999999</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>11.7886</v>
+        <v>11.9392</v>
       </c>
       <c r="AA25" t="n">
-        <v>10.9271</v>
+        <v>11.0229</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.4762</v>
+        <v>8.524900000000001</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>0.4859</v>
+        <v>0.5531</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.438</v>
+        <v>0.461</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -5000,18 +5000,18 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>70.29000000000001</v>
+        <v>76.23</v>
       </c>
       <c r="AI25" t="n">
-        <v>11.7749</v>
+        <v>11.8612</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>11.7749</v>
+        <v>12.085</v>
       </c>
       <c r="AL25" t="n">
         <v>11.1606</v>
@@ -5022,36 +5022,36 @@
         </is>
       </c>
       <c r="AN25" t="n">
-        <v>12.6806</v>
+        <v>14.1733</v>
       </c>
       <c r="AO25" t="n">
-        <v>12.8261</v>
+        <v>16.3533</v>
       </c>
       <c r="AP25" t="n">
-        <v>13.1767</v>
+        <v>17.9838</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 12.68; TP2: Fibonacci R1 at 12.83; TP3: Classic R1 at 13.18</t>
+          <t>TP1: Classic R2 at 14.17; TP2: Classic R3 at 16.35; TP3: Extension at 17.98</t>
         </is>
       </c>
       <c r="AR25" t="n">
-        <v>1.47</v>
+        <v>2.26</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.71</v>
+        <v>4.62</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.28</v>
+        <v>6.38</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.69</v>
+        <v>17.28</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.93</v>
+        <v>35.32</v>
       </c>
       <c r="AW25" t="n">
-        <v>11.91</v>
+        <v>48.81</v>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
@@ -5060,14 +5060,14 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.3); entry: enhanced entry at VWMA (overbought (RSI: 70.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.2))</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>345.25</v>
+        <v>406.9</v>
       </c>
       <c r="F26" t="n">
         <v>4.7348</v>
@@ -5120,10 +5120,10 @@
         <v>156711</v>
       </c>
       <c r="O26" t="n">
-        <v>559339</v>
+        <v>199821</v>
       </c>
       <c r="P26" t="n">
-        <v>3.569</v>
+        <v>1.275</v>
       </c>
       <c r="Q26" t="n">
         <v>228119</v>
@@ -5141,10 +5141,10 @@
         <v>74.2</v>
       </c>
       <c r="V26" t="n">
-        <v>96.7372</v>
+        <v>103.3746</v>
       </c>
       <c r="W26" t="n">
-        <v>72.6122</v>
+        <v>74.3364</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>160.5721</v>
+        <v>184.0319</v>
       </c>
       <c r="AA26" t="n">
-        <v>114.0711</v>
+        <v>125.5546</v>
       </c>
       <c r="AB26" t="n">
-        <v>76.8389</v>
+        <v>80.12309999999999</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="AE26" t="n">
-        <v>50.7355</v>
+        <v>63.8272</v>
       </c>
       <c r="AF26" t="n">
-        <v>27.2989</v>
+        <v>34.6046</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -5187,21 +5187,21 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>94.70999999999999</v>
+        <v>95.84</v>
       </c>
       <c r="AI26" t="n">
-        <v>171.2504</v>
+        <v>175.3309</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK26" t="n">
-        <v>206</v>
+        <v>240.525</v>
       </c>
       <c r="AL26" t="n">
-        <v>174.7604</v>
+        <v>208.8583</v>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
@@ -5209,36 +5209,36 @@
         </is>
       </c>
       <c r="AN26" t="n">
-        <v>353.5333</v>
+        <v>524.1933</v>
       </c>
       <c r="AO26" t="n">
-        <v>524.1933</v>
+        <v>666.0275</v>
       </c>
       <c r="AP26" t="n">
-        <v>645.7431</v>
+        <v>591.1391</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 353.53; TP2: Classic R3 at 524.19; TP3: Extension at 645.74</t>
+          <t>TP1: Classic R3 at 524.19; TP2: Extension at 666.03; TP3: Extension at 591.14</t>
         </is>
       </c>
       <c r="AR26" t="n">
-        <v>4.72</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>10.19</v>
+        <v>13.44</v>
       </c>
       <c r="AT26" t="n">
-        <v>14.08</v>
+        <v>11.07</v>
       </c>
       <c r="AU26" t="n">
-        <v>71.62</v>
+        <v>117.94</v>
       </c>
       <c r="AV26" t="n">
-        <v>154.46</v>
+        <v>176.91</v>
       </c>
       <c r="AW26" t="n">
-        <v>213.47</v>
+        <v>145.77</v>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (94.7); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 94.7))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (95.8); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 95.8))</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>19.83</v>
       </c>
       <c r="F27" t="n">
         <v>0.3853</v>
@@ -5303,10 +5303,10 @@
         <v>686446</v>
       </c>
       <c r="O27" t="n">
-        <v>2243474</v>
+        <v>134783</v>
       </c>
       <c r="P27" t="n">
-        <v>3.268</v>
+        <v>0.196</v>
       </c>
       <c r="Q27" t="n">
         <v>193759</v>
@@ -5324,10 +5324,10 @@
         <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>19.555</v>
+        <v>19.5384</v>
       </c>
       <c r="W27" t="n">
-        <v>19.3002</v>
+        <v>19.301</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -5340,13 +5340,13 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>19.5777</v>
+        <v>19.6017</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.5708</v>
+        <v>19.581</v>
       </c>
       <c r="AB27" t="n">
-        <v>18.7323</v>
+        <v>18.7432</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>0.081</v>
+        <v>0.0898</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0116</v>
+        <v>0.0273</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -5370,18 +5370,18 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>60.12</v>
+        <v>55.73</v>
       </c>
       <c r="AI27" t="n">
-        <v>19.6193</v>
+        <v>19.6229</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK27" t="n">
-        <v>19.6193</v>
+        <v>19.6229</v>
       </c>
       <c r="AL27" t="n">
         <v>19.51</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="AN27" t="n">
-        <v>20.0308</v>
+        <v>20.0614</v>
       </c>
       <c r="AO27" t="n">
         <v>20.0876</v>
@@ -5402,26 +5402,26 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 20.03; TP2: Fibonacci R1 at 20.09; TP3: Classic R1 at 20.21</t>
+          <t>TP1: Bollinger Upper Band at 20.06; TP2: Fibonacci R1 at 20.09; TP3: Classic R1 at 20.21</t>
         </is>
       </c>
       <c r="AR27" t="n">
-        <v>3.76</v>
+        <v>3.88</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.28</v>
+        <v>4.11</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.37</v>
+        <v>5.17</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.1))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 55.7))</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="F28" t="n">
         <v>0.3061</v>
@@ -5486,10 +5486,10 @@
         <v>923595</v>
       </c>
       <c r="O28" t="n">
-        <v>901528</v>
+        <v>83024</v>
       </c>
       <c r="P28" t="n">
-        <v>0.976</v>
+        <v>0.09</v>
       </c>
       <c r="Q28" t="n">
         <v>278772</v>
@@ -5507,10 +5507,10 @@
         <v>15.78</v>
       </c>
       <c r="V28" t="n">
-        <v>15.3342</v>
+        <v>15.3256</v>
       </c>
       <c r="W28" t="n">
-        <v>15.2672</v>
+        <v>15.2643</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>15.3692</v>
+        <v>15.3912</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.3319</v>
+        <v>15.3424</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.8982</v>
+        <v>14.9052</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>0.1018</v>
+        <v>0.1067</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.0638</v>
+        <v>0.0723</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -5553,29 +5553,29 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>53.45</v>
+        <v>55.38</v>
       </c>
       <c r="AI28" t="n">
-        <v>15.4253</v>
+        <v>15.4367</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK28" t="n">
+        <v>15.4367</v>
+      </c>
+      <c r="AL28" t="n">
         <v>15.43</v>
       </c>
-      <c r="AL28" t="n">
-        <v>15.2672</v>
-      </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>stop at 200 SMA</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN28" t="n">
-        <v>15.7816</v>
+        <v>15.7792</v>
       </c>
       <c r="AO28" t="n">
         <v>15.799</v>
@@ -5589,22 +5589,22 @@
         </is>
       </c>
       <c r="AR28" t="n">
-        <v>2.16</v>
+        <v>50.94</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.27</v>
+        <v>53.89</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.91</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
@@ -5613,14 +5613,14 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 53.5))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 55.4))</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>31.17</v>
+        <v>30.99</v>
       </c>
       <c r="F29" t="n">
         <v>0.6059</v>
@@ -5667,10 +5667,10 @@
         <v>1437989</v>
       </c>
       <c r="O29" t="n">
-        <v>530249</v>
+        <v>47451</v>
       </c>
       <c r="P29" t="n">
-        <v>0.369</v>
+        <v>0.033</v>
       </c>
       <c r="Q29" t="n">
         <v>531102</v>
@@ -5688,10 +5688,10 @@
         <v>36.45</v>
       </c>
       <c r="V29" t="n">
-        <v>28.465</v>
+        <v>28.6148</v>
       </c>
       <c r="W29" t="n">
-        <v>17.6235</v>
+        <v>17.7177</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5704,13 +5704,13 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>29.667</v>
+        <v>29.793</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.3796</v>
+        <v>27.5212</v>
       </c>
       <c r="AB29" t="n">
-        <v>19.5659</v>
+        <v>19.6795</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>1.0011</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.7915</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -5734,58 +5734,58 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>65.73999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="AI29" t="n">
-        <v>29.6087</v>
+        <v>29.6966</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>29.62</v>
+        <v>29.948</v>
       </c>
       <c r="AL29" t="n">
-        <v>29.5</v>
+        <v>27.6202</v>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN29" t="n">
         <v>32.3265</v>
       </c>
       <c r="AO29" t="n">
-        <v>32.5655</v>
+        <v>32.7849</v>
       </c>
       <c r="AP29" t="n">
         <v>33.4067</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 32.57; TP3: Classic R1 at 33.41</t>
+          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 32.78; TP3: Classic R1 at 33.41</t>
         </is>
       </c>
       <c r="AR29" t="n">
-        <v>22.55</v>
+        <v>1.02</v>
       </c>
       <c r="AS29" t="n">
-        <v>24.55</v>
+        <v>1.22</v>
       </c>
       <c r="AT29" t="n">
-        <v>31.56</v>
+        <v>1.49</v>
       </c>
       <c r="AU29" t="n">
-        <v>9.140000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.94</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>12.78</v>
+        <v>11.55</v>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
@@ -5794,14 +5794,14 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 63.9))</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>36.82</v>
+        <v>37.29</v>
       </c>
       <c r="F30" t="n">
         <v>0.6772</v>
@@ -5854,10 +5854,10 @@
         <v>793904</v>
       </c>
       <c r="O30" t="n">
-        <v>1448512</v>
+        <v>360511</v>
       </c>
       <c r="P30" t="n">
-        <v>1.825</v>
+        <v>0.454</v>
       </c>
       <c r="Q30" t="n">
         <v>837459</v>
@@ -5875,10 +5875,10 @@
         <v>37</v>
       </c>
       <c r="V30" t="n">
-        <v>29.7962</v>
+        <v>29.9788</v>
       </c>
       <c r="W30" t="n">
-        <v>26.8014</v>
+        <v>26.859</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -5891,13 +5891,13 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>33.3553</v>
+        <v>33.73</v>
       </c>
       <c r="AA30" t="n">
-        <v>30.7242</v>
+        <v>30.9817</v>
       </c>
       <c r="AB30" t="n">
-        <v>27.4766</v>
+        <v>27.5743</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -5910,10 +5910,10 @@
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>1.833</v>
+        <v>1.9213</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7028</v>
+        <v>1.7465</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -5921,21 +5921,21 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>70.47</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="AI30" t="n">
-        <v>32.7762</v>
+        <v>33.3463</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>32.7762</v>
+        <v>33.3463</v>
       </c>
       <c r="AL30" t="n">
-        <v>30.2</v>
+        <v>30.3518</v>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="AN30" t="n">
-        <v>37.2443</v>
+        <v>37.697</v>
       </c>
       <c r="AO30" t="n">
         <v>38.3133</v>
@@ -5953,26 +5953,26 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 37.24; TP2: Classic R1 at 38.31; TP3: Fibonacci R2 at 38.76</t>
+          <t>TP1: Bollinger Upper Band at 37.7; TP2: Classic R1 at 38.31; TP3: Fibonacci R2 at 38.76</t>
         </is>
       </c>
       <c r="AR30" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="AU30" t="n">
-        <v>13.63</v>
+        <v>13.05</v>
       </c>
       <c r="AV30" t="n">
-        <v>16.89</v>
+        <v>14.9</v>
       </c>
       <c r="AW30" t="n">
-        <v>18.26</v>
+        <v>16.24</v>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
@@ -5981,14 +5981,14 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.7); entry: enhanced entry at VWMA (overbought (RSI: 71.7))</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="F31" t="n">
         <v>0.0383</v>
@@ -6037,10 +6037,10 @@
         <v>34437426</v>
       </c>
       <c r="O31" t="n">
-        <v>55896003</v>
+        <v>5640433</v>
       </c>
       <c r="P31" t="n">
-        <v>1.623</v>
+        <v>0.164</v>
       </c>
       <c r="Q31" t="n">
         <v>22621100</v>
@@ -6058,10 +6058,10 @@
         <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>1.812</v>
+        <v>1.8176</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6954</v>
+        <v>1.6955</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -6074,13 +6074,13 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1.8905</v>
+        <v>1.8943</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8213</v>
+        <v>1.8255</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6293</v>
+        <v>1.6322</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>0.0359</v>
+        <v>0.0347</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0298</v>
+        <v>0.0308</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>57.32</v>
+        <v>56.08</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.9111</v>
+        <v>1.915</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>1.9111</v>
+        <v>1.915</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.8454</v>
+        <v>1.8589</v>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="AN31" t="n">
-        <v>1.9838</v>
+        <v>1.9869</v>
       </c>
       <c r="AO31" t="n">
         <v>2.0413</v>
@@ -6136,26 +6136,26 @@
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1.98; TP2: Fibonacci R1 at 2.04; TP3: Classic R1 at 2.08</t>
+          <t>TP1: Bollinger Upper Band at 1.99; TP2: Fibonacci R1 at 2.04; TP3: Classic R1 at 2.08</t>
         </is>
       </c>
       <c r="AR31" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.81</v>
+        <v>6.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>9.01</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
@@ -6164,14 +6164,14 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.1))</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6220,10 +6220,10 @@
         <v>5516330</v>
       </c>
       <c r="O32" t="n">
-        <v>2908950</v>
+        <v>635742</v>
       </c>
       <c r="P32" t="n">
-        <v>0.527</v>
+        <v>0.115</v>
       </c>
       <c r="Q32" t="n">
         <v>1206295</v>
@@ -6241,10 +6241,10 @@
         <v>9.9</v>
       </c>
       <c r="V32" t="n">
-        <v>9.641999999999999</v>
+        <v>9.6386</v>
       </c>
       <c r="W32" t="n">
-        <v>9.635999999999999</v>
+        <v>9.6281</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -6257,13 +6257,13 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>9.756399999999999</v>
+        <v>9.7605</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.6587</v>
+        <v>9.664199999999999</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.4801</v>
+        <v>9.4833</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>0.0868</v>
+        <v>0.0791</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0682</v>
+        <v>0.0704</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -6290,26 +6290,26 @@
         <v>52.62</v>
       </c>
       <c r="AI32" t="n">
-        <v>9.811299999999999</v>
+        <v>9.824199999999999</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK32" t="n">
+        <v>9.745200000000001</v>
+      </c>
+      <c r="AL32" t="n">
         <v>9.73</v>
       </c>
-      <c r="AL32" t="n">
-        <v>9.66</v>
-      </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN32" t="n">
-        <v>10.0775</v>
+        <v>10.0849</v>
       </c>
       <c r="AO32" t="n">
         <v>10.2191</v>
@@ -6323,22 +6323,22 @@
         </is>
       </c>
       <c r="AR32" t="n">
-        <v>4.96</v>
+        <v>22.35</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.99</v>
+        <v>31.18</v>
       </c>
       <c r="AT32" t="n">
-        <v>8</v>
+        <v>35.84</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.57</v>
+        <v>3.49</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.03</v>
+        <v>4.86</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.76</v>
+        <v>5.59</v>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
@@ -6347,14 +6347,14 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 52.6))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 52.6))</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6407,10 +6407,10 @@
         <v>2598810</v>
       </c>
       <c r="O33" t="n">
-        <v>3344129</v>
+        <v>296447</v>
       </c>
       <c r="P33" t="n">
-        <v>1.287</v>
+        <v>0.114</v>
       </c>
       <c r="Q33" t="n">
         <v>1017025</v>
@@ -6428,10 +6428,10 @@
         <v>9.75</v>
       </c>
       <c r="V33" t="n">
-        <v>9.226599999999999</v>
+        <v>9.2356</v>
       </c>
       <c r="W33" t="n">
-        <v>8.0015</v>
+        <v>8.012700000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -6444,13 +6444,13 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>9.4337</v>
+        <v>9.4543</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.1873</v>
+        <v>9.205399999999999</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.155099999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>0.1017</v>
+        <v>0.1068</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.0982</v>
+        <v>0.1</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -6477,15 +6477,15 @@
         <v>59.34</v>
       </c>
       <c r="AI33" t="n">
-        <v>9.514699999999999</v>
+        <v>9.5138</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>9.514699999999999</v>
+        <v>9.5138</v>
       </c>
       <c r="AL33" t="n">
         <v>9.300000000000001</v>
@@ -6499,33 +6499,33 @@
         <v>9.6737</v>
       </c>
       <c r="AO33" t="n">
-        <v>9.724500000000001</v>
+        <v>9.7395</v>
       </c>
       <c r="AP33" t="n">
         <v>9.7933</v>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 9.67; TP2: Bollinger Upper Band at 9.72; TP3: Classic R1 at 9.79</t>
+          <t>TP1: Fibonacci R1 at 9.67; TP2: Bollinger Upper Band at 9.74; TP3: Classic R1 at 9.79</t>
         </is>
       </c>
       <c r="AR33" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10.06</v>
+        <v>10.03</v>
       </c>
       <c r="F34" t="n">
         <v>0.1973</v>
@@ -6590,10 +6590,10 @@
         <v>2323879</v>
       </c>
       <c r="O34" t="n">
-        <v>1031422</v>
+        <v>256726</v>
       </c>
       <c r="P34" t="n">
-        <v>0.444</v>
+        <v>0.11</v>
       </c>
       <c r="Q34" t="n">
         <v>639967</v>
@@ -6611,10 +6611,10 @@
         <v>10.3</v>
       </c>
       <c r="V34" t="n">
-        <v>9.955399999999999</v>
+        <v>9.9618</v>
       </c>
       <c r="W34" t="n">
-        <v>9.223100000000001</v>
+        <v>9.228</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -6627,13 +6627,13 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>10.0815</v>
+        <v>10.0766</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.919700000000001</v>
+        <v>9.923999999999999</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.0998</v>
+        <v>9.1091</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>0.0429</v>
+        <v>0.0341</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0649</v>
+        <v>0.0587</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -6657,29 +6657,29 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>50.21</v>
+        <v>49.31</v>
       </c>
       <c r="AI34" t="n">
-        <v>10.2386</v>
+        <v>10.2368</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK34" t="n">
-        <v>9.955399999999999</v>
+        <v>9.881500000000001</v>
       </c>
       <c r="AL34" t="n">
-        <v>9.91</v>
+        <v>9.702999999999999</v>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN34" t="n">
-        <v>10.4103</v>
+        <v>10.4005</v>
       </c>
       <c r="AO34" t="n">
         <v>10.6503</v>
@@ -6689,26 +6689,26 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 10.41; TP2: Fibonacci R1 at 10.65; TP3: Classic R1 at 10.7</t>
+          <t>TP1: Bollinger Upper Band at 10.4; TP2: Fibonacci R1 at 10.65; TP3: Classic R1 at 10.7</t>
         </is>
       </c>
       <c r="AR34" t="n">
-        <v>10.02</v>
+        <v>2.91</v>
       </c>
       <c r="AS34" t="n">
-        <v>15.31</v>
+        <v>4.31</v>
       </c>
       <c r="AT34" t="n">
-        <v>16.47</v>
+        <v>4.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.57</v>
+        <v>5.25</v>
       </c>
       <c r="AV34" t="n">
-        <v>6.98</v>
+        <v>7.78</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.51</v>
+        <v>8.32</v>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.3))</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>15.81</v>
+        <v>15.89</v>
       </c>
       <c r="F35" t="n">
         <v>0.3102</v>
@@ -6777,10 +6777,10 @@
         <v>2820657</v>
       </c>
       <c r="O35" t="n">
-        <v>3350341</v>
+        <v>165416</v>
       </c>
       <c r="P35" t="n">
-        <v>1.188</v>
+        <v>0.059</v>
       </c>
       <c r="Q35" t="n">
         <v>596133</v>
@@ -6798,10 +6798,10 @@
         <v>16.77</v>
       </c>
       <c r="V35" t="n">
-        <v>16.421</v>
+        <v>16.3838</v>
       </c>
       <c r="W35" t="n">
-        <v>16.258</v>
+        <v>16.2571</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -6814,13 +6814,13 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>16.0101</v>
+        <v>15.9987</v>
       </c>
       <c r="AA35" t="n">
-        <v>16.3308</v>
+        <v>16.3135</v>
       </c>
       <c r="AB35" t="n">
-        <v>16.4383</v>
+        <v>16.4328</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -6833,10 +6833,10 @@
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>-0.1441</v>
+        <v>-0.137</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.1532</v>
+        <v>-0.15</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -6844,18 +6844,18 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>44.9</v>
+        <v>46.46</v>
       </c>
       <c r="AI35" t="n">
-        <v>16.0273</v>
+        <v>16.0246</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK35" t="n">
-        <v>15.3575</v>
+        <v>15.3448</v>
       </c>
       <c r="AL35" t="n">
         <v>15.0075</v>
@@ -6866,36 +6866,36 @@
         </is>
       </c>
       <c r="AN35" t="n">
-        <v>16.258</v>
+        <v>16.2571</v>
       </c>
       <c r="AO35" t="n">
         <v>16.5125</v>
       </c>
       <c r="AP35" t="n">
-        <v>16.6985</v>
+        <v>16.6882</v>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 16.26; TP2: Fibonacci R1 at 16.51; TP3: Bollinger Upper Band at 16.7</t>
+          <t>TP1: 200 SMA at 16.26; TP2: Fibonacci R1 at 16.51; TP3: Bollinger Upper Band at 16.69</t>
         </is>
       </c>
       <c r="AR35" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.83</v>
+        <v>3.98</v>
       </c>
       <c r="AU35" t="n">
-        <v>5.86</v>
+        <v>5.95</v>
       </c>
       <c r="AV35" t="n">
-        <v>7.52</v>
+        <v>7.61</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.73</v>
+        <v>8.75</v>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
@@ -6904,14 +6904,14 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 44.9))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.5))</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F36" t="n">
         <v>1.5818</v>
@@ -6964,10 +6964,10 @@
         <v>714482</v>
       </c>
       <c r="O36" t="n">
-        <v>1410083</v>
+        <v>271676</v>
       </c>
       <c r="P36" t="n">
-        <v>1.974</v>
+        <v>0.38</v>
       </c>
       <c r="Q36" t="n">
         <v>339265</v>
@@ -6983,10 +6983,10 @@
         <v>67</v>
       </c>
       <c r="V36" t="n">
-        <v>67.0836</v>
+        <v>67.37220000000001</v>
       </c>
       <c r="W36" t="n">
-        <v>63.108</v>
+        <v>63.2365</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>74.5115</v>
+        <v>75.0343</v>
       </c>
       <c r="AA36" t="n">
-        <v>68.8522</v>
+        <v>69.2893</v>
       </c>
       <c r="AB36" t="n">
-        <v>60.8951</v>
+        <v>61.0852</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>4.7637</v>
+        <v>4.6045</v>
       </c>
       <c r="AF36" t="n">
-        <v>4.2361</v>
+        <v>4.3097</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -7029,18 +7029,18 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>62.01</v>
+        <v>63.38</v>
       </c>
       <c r="AI36" t="n">
-        <v>76.9058</v>
+        <v>77.06489999999999</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK36" t="n">
-        <v>76.9058</v>
+        <v>77.06489999999999</v>
       </c>
       <c r="AL36" t="n">
         <v>66.2534</v>
@@ -7054,33 +7054,33 @@
         <v>86.65989999999999</v>
       </c>
       <c r="AO36" t="n">
-        <v>89.88500000000001</v>
+        <v>90.5487</v>
       </c>
       <c r="AP36" t="n">
         <v>91.63330000000001</v>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 89.89; TP3: Classic R1 at 91.63</t>
+          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 90.55; TP3: Classic R1 at 91.63</t>
         </is>
       </c>
       <c r="AR36" t="n">
-        <v>0.92</v>
+        <v>0.89</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AU36" t="n">
-        <v>12.68</v>
+        <v>12.45</v>
       </c>
       <c r="AV36" t="n">
-        <v>16.88</v>
+        <v>17.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>19.15</v>
+        <v>18.9</v>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
@@ -7089,14 +7089,14 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.4))</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>29.36</v>
+        <v>29</v>
       </c>
       <c r="F37" t="n">
         <v>0.5535</v>
@@ -7149,10 +7149,10 @@
         <v>2098172</v>
       </c>
       <c r="O37" t="n">
-        <v>3842449</v>
+        <v>203605</v>
       </c>
       <c r="P37" t="n">
-        <v>1.831</v>
+        <v>0.097</v>
       </c>
       <c r="Q37" t="n">
         <v>2043158</v>
@@ -7170,10 +7170,10 @@
         <v>28.7</v>
       </c>
       <c r="V37" t="n">
-        <v>24.3398</v>
+        <v>24.4868</v>
       </c>
       <c r="W37" t="n">
-        <v>20.2467</v>
+        <v>20.3134</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -7186,13 +7186,13 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>27.3562</v>
+        <v>27.5127</v>
       </c>
       <c r="AA37" t="n">
-        <v>25.2044</v>
+        <v>25.3533</v>
       </c>
       <c r="AB37" t="n">
-        <v>21.0251</v>
+        <v>21.1044</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -7205,10 +7205,10 @@
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>1.2285</v>
+        <v>1.2117</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.229</v>
+        <v>1.2255</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -7216,21 +7216,21 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>70.48999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="AI37" t="n">
-        <v>27.8456</v>
+        <v>27.9141</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>27.8456</v>
+        <v>27.9141</v>
       </c>
       <c r="AL37" t="n">
-        <v>26.8104</v>
+        <v>26.9934</v>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
@@ -7238,36 +7238,36 @@
         </is>
       </c>
       <c r="AN37" t="n">
+        <v>29.0407</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>29.4064</v>
+      </c>
+      <c r="AP37" t="n">
         <v>30</v>
       </c>
-      <c r="AO37" t="n">
-        <v>30.1593</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>31.97</v>
-      </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 30; TP2: Fibonacci R2 at 30.16; TP3: Classic R2 at 31.97</t>
+          <t>TP1: Fibonacci R1 at 29.04; TP2: Bollinger Upper Band at 29.41; TP3: Classic R1 at 30</t>
         </is>
       </c>
       <c r="AR37" t="n">
-        <v>2.08</v>
+        <v>1.22</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.24</v>
+        <v>1.62</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.98</v>
+        <v>2.27</v>
       </c>
       <c r="AU37" t="n">
-        <v>7.74</v>
+        <v>4.04</v>
       </c>
       <c r="AV37" t="n">
-        <v>8.31</v>
+        <v>5.35</v>
       </c>
       <c r="AW37" t="n">
-        <v>14.81</v>
+        <v>7.47</v>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
@@ -7276,14 +7276,14 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.5); entry: enhanced entry at VWMA (overbought (RSI: 70.5))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.7))</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F38" t="n">
         <v>0.1803</v>
@@ -7336,10 +7336,10 @@
         <v>7767167</v>
       </c>
       <c r="O38" t="n">
-        <v>3076807</v>
+        <v>416918</v>
       </c>
       <c r="P38" t="n">
-        <v>0.396</v>
+        <v>0.054</v>
       </c>
       <c r="Q38" t="n">
         <v>2126205</v>
@@ -7357,10 +7357,10 @@
         <v>9.75</v>
       </c>
       <c r="V38" t="n">
-        <v>9.2148</v>
+        <v>9.2102</v>
       </c>
       <c r="W38" t="n">
-        <v>7.2862</v>
+        <v>7.3043</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -7373,13 +7373,13 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>9.257999999999999</v>
+        <v>9.2439</v>
       </c>
       <c r="AA38" t="n">
-        <v>8.982100000000001</v>
+        <v>8.9872</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.4652</v>
+        <v>7.4816</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>0.0201</v>
+        <v>0.0073</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0683</v>
+        <v>0.0561</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -7403,14 +7403,14 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>46.68</v>
+        <v>46.39</v>
       </c>
       <c r="AI38" t="n">
-        <v>9.398899999999999</v>
+        <v>9.3439</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK38" t="n">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="AN38" t="n">
-        <v>9.6058</v>
+        <v>9.5358</v>
       </c>
       <c r="AO38" t="n">
         <v>9.7621</v>
@@ -7435,11 +7435,11 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.61; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
+          <t>TP1: Bollinger Upper Band at 9.54; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
         </is>
       </c>
       <c r="AR38" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="AS38" t="n">
         <v>4.43</v>
@@ -7448,7 +7448,7 @@
         <v>4.51</v>
       </c>
       <c r="AU38" t="n">
-        <v>7.39</v>
+        <v>6.61</v>
       </c>
       <c r="AV38" t="n">
         <v>9.140000000000001</v>
@@ -7463,14 +7463,14 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 46.4))</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7519,10 +7519,10 @@
         <v>26742704</v>
       </c>
       <c r="O39" t="n">
-        <v>27554417</v>
+        <v>6132106</v>
       </c>
       <c r="P39" t="n">
-        <v>1.03</v>
+        <v>0.229</v>
       </c>
       <c r="Q39" t="n">
         <v>8853419</v>
@@ -7540,10 +7540,10 @@
         <v>0.721</v>
       </c>
       <c r="V39" t="n">
-        <v>0.7023</v>
+        <v>0.7005</v>
       </c>
       <c r="W39" t="n">
-        <v>0.781</v>
+        <v>0.7816</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -7556,13 +7556,13 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>0.701</v>
+        <v>0.6988</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.7194</v>
+        <v>0.7177</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.7259</v>
+        <v>0.7255</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>-0.0063</v>
+        <v>-0.0074</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.0021</v>
+        <v>-0.0032</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -7589,11 +7589,11 @@
         <v>37.38</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.709</v>
+        <v>0.7087</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:39</t>
+          <t>2026-08-04 08:00:42</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7678,10 +7678,10 @@
         <v>6219845</v>
       </c>
       <c r="O40" t="n">
-        <v>6485880</v>
+        <v>766194</v>
       </c>
       <c r="P40" t="n">
-        <v>1.043</v>
+        <v>0.123</v>
       </c>
       <c r="Q40" t="n">
         <v>4697839</v>
@@ -7699,10 +7699,10 @@
         <v>4.11</v>
       </c>
       <c r="V40" t="n">
-        <v>3.7278</v>
+        <v>3.7458</v>
       </c>
       <c r="W40" t="n">
-        <v>2.9791</v>
+        <v>2.9903</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>4.1265</v>
+        <v>4.162</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.811</v>
+        <v>3.838</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.112</v>
+        <v>3.1258</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="AE40" t="n">
-        <v>0.2606</v>
+        <v>0.2573</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.1878</v>
+        <v>0.2017</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -7748,26 +7748,26 @@
         <v>64.48</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.2728</v>
+        <v>4.2806</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK40" t="n">
-        <v>4.2728</v>
+        <v>4.3509</v>
       </c>
       <c r="AL40" t="n">
-        <v>4.2485</v>
+        <v>3.7589</v>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN40" t="n">
-        <v>4.8128</v>
+        <v>4.8535</v>
       </c>
       <c r="AO40" t="n">
         <v>4.9278</v>
@@ -7777,26 +7777,26 @@
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 4.81; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
+          <t>TP1: Bollinger Upper Band at 4.85; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
         </is>
       </c>
       <c r="AR40" t="n">
-        <v>22.22</v>
+        <v>0.85</v>
       </c>
       <c r="AS40" t="n">
-        <v>26.96</v>
+        <v>0.97</v>
       </c>
       <c r="AT40" t="n">
-        <v>39.67</v>
+        <v>1.5</v>
       </c>
       <c r="AU40" t="n">
-        <v>12.64</v>
+        <v>11.55</v>
       </c>
       <c r="AV40" t="n">
-        <v>15.33</v>
+        <v>13.26</v>
       </c>
       <c r="AW40" t="n">
-        <v>22.56</v>
+        <v>20.36</v>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
@@ -7805,14 +7805,14 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 64.5))</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>52.35</v>
+        <v>51.85</v>
       </c>
       <c r="F41" t="n">
         <v>1.0437</v>
@@ -7865,10 +7865,10 @@
         <v>2150582</v>
       </c>
       <c r="O41" t="n">
-        <v>985068</v>
+        <v>179484</v>
       </c>
       <c r="P41" t="n">
-        <v>0.458</v>
+        <v>0.083</v>
       </c>
       <c r="Q41" t="n">
         <v>1271079</v>
@@ -7886,10 +7886,10 @@
         <v>48.49</v>
       </c>
       <c r="V41" t="n">
-        <v>47.474</v>
+        <v>47.591</v>
       </c>
       <c r="W41" t="n">
-        <v>37.045</v>
+        <v>37.2046</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -7902,13 +7902,13 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>49.6113</v>
+        <v>49.8245</v>
       </c>
       <c r="AA41" t="n">
-        <v>47.5716</v>
+        <v>47.7393</v>
       </c>
       <c r="AB41" t="n">
-        <v>38.673</v>
+        <v>38.8041</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>1.6372</v>
+        <v>1.6072</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.1182</v>
+        <v>1.216</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -7932,58 +7932,58 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>66.72</v>
+        <v>63.56</v>
       </c>
       <c r="AI41" t="n">
-        <v>48.8941</v>
+        <v>48.9735</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>48.8941</v>
+        <v>49.3196</v>
       </c>
       <c r="AL41" t="n">
-        <v>48.7632</v>
+        <v>48.2733</v>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AN41" t="n">
         <v>53.2048</v>
       </c>
       <c r="AO41" t="n">
-        <v>53.8368</v>
+        <v>54.1693</v>
       </c>
       <c r="AP41" t="n">
         <v>54.8285</v>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 53.84; TP3: Fibonacci R2 at 54.83</t>
+          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 54.17; TP3: Fibonacci R2 at 54.83</t>
         </is>
       </c>
       <c r="AR41" t="n">
-        <v>32.94</v>
+        <v>3.71</v>
       </c>
       <c r="AS41" t="n">
-        <v>37.77</v>
+        <v>4.64</v>
       </c>
       <c r="AT41" t="n">
-        <v>45.35</v>
+        <v>5.27</v>
       </c>
       <c r="AU41" t="n">
-        <v>8.82</v>
+        <v>7.88</v>
       </c>
       <c r="AV41" t="n">
-        <v>10.11</v>
+        <v>9.83</v>
       </c>
       <c r="AW41" t="n">
-        <v>12.14</v>
+        <v>11.17</v>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
@@ -7992,14 +7992,14 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 63.6))</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8018,7 +8018,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>36.94</v>
+        <v>37.01</v>
       </c>
       <c r="F42" t="n">
         <v>0.7232</v>
@@ -8052,10 +8052,10 @@
         <v>1877096</v>
       </c>
       <c r="O42" t="n">
-        <v>1685954</v>
+        <v>186805</v>
       </c>
       <c r="P42" t="n">
-        <v>0.898</v>
+        <v>0.1</v>
       </c>
       <c r="Q42" t="n">
         <v>950485</v>
@@ -8073,10 +8073,10 @@
         <v>38.8</v>
       </c>
       <c r="V42" t="n">
-        <v>38.8124</v>
+        <v>38.6326</v>
       </c>
       <c r="W42" t="n">
-        <v>35.7573</v>
+        <v>35.7937</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -8089,13 +8089,13 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>37.2119</v>
+        <v>37.1927</v>
       </c>
       <c r="AA42" t="n">
-        <v>38.4193</v>
+        <v>38.364</v>
       </c>
       <c r="AB42" t="n">
-        <v>36.6711</v>
+        <v>36.6745</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -8108,10 +8108,10 @@
         </is>
       </c>
       <c r="AE42" t="n">
-        <v>-0.3613</v>
+        <v>-0.3395</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.4858</v>
+        <v>-0.4566</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -8119,25 +8119,25 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>46.16</v>
+        <v>46.69</v>
       </c>
       <c r="AI42" t="n">
-        <v>37.2257</v>
+        <v>37.329</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>35.6417</v>
+        <v>35.8416</v>
       </c>
       <c r="AL42" t="n">
-        <v>35.4767</v>
+        <v>35.7937</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at 200 SMA</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -8147,30 +8147,30 @@
         <v>38.5567</v>
       </c>
       <c r="AP42" t="n">
-        <v>38.7013</v>
+        <v>38.6254</v>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 38.25; TP2: Classic R1 at 38.56; TP3: Bollinger Upper Band at 38.7</t>
+          <t>TP1: Fibonacci R1 at 38.25; TP2: Classic R1 at 38.56; TP3: Bollinger Upper Band at 38.63</t>
         </is>
       </c>
       <c r="AR42" t="n">
-        <v>15.81</v>
+        <v>50.29</v>
       </c>
       <c r="AS42" t="n">
-        <v>17.67</v>
+        <v>56.69</v>
       </c>
       <c r="AT42" t="n">
-        <v>18.54</v>
+        <v>58.13</v>
       </c>
       <c r="AU42" t="n">
-        <v>7.32</v>
+        <v>6.72</v>
       </c>
       <c r="AV42" t="n">
-        <v>8.18</v>
+        <v>7.58</v>
       </c>
       <c r="AW42" t="n">
-        <v>8.58</v>
+        <v>7.77</v>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
@@ -8179,14 +8179,14 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.7))</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="F43" t="n">
         <v>0.1363</v>
@@ -8233,10 +8233,10 @@
         <v>2863794</v>
       </c>
       <c r="O43" t="n">
-        <v>3252041</v>
+        <v>440121</v>
       </c>
       <c r="P43" t="n">
-        <v>1.136</v>
+        <v>0.154</v>
       </c>
       <c r="Q43" t="n">
         <v>2447417</v>
@@ -8254,10 +8254,10 @@
         <v>6.91</v>
       </c>
       <c r="V43" t="n">
-        <v>6.2404</v>
+        <v>6.2704</v>
       </c>
       <c r="W43" t="n">
-        <v>5.856</v>
+        <v>5.854</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -8270,13 +8270,13 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>6.7084</v>
+        <v>6.7352</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.3043</v>
+        <v>6.3311</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.6893</v>
+        <v>5.7023</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -8289,10 +8289,10 @@
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>0.2359</v>
+        <v>0.2295</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.2114</v>
+        <v>0.215</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -8300,21 +8300,21 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>61.08</v>
+        <v>60.75</v>
       </c>
       <c r="AI43" t="n">
-        <v>6.7436</v>
+        <v>6.7563</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK43" t="n">
-        <v>6.7436</v>
+        <v>6.7563</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.549</v>
+        <v>6.6074</v>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
@@ -8325,33 +8325,33 @@
         <v>7.2151</v>
       </c>
       <c r="AO43" t="n">
-        <v>7.2622</v>
+        <v>7.2936</v>
       </c>
       <c r="AP43" t="n">
         <v>7.45</v>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.26; TP3: Classic R1 at 7.45</t>
+          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.29; TP3: Classic R1 at 7.45</t>
         </is>
       </c>
       <c r="AR43" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.67</v>
+        <v>3.61</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.63</v>
+        <v>4.66</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.99</v>
+        <v>6.79</v>
       </c>
       <c r="AV43" t="n">
-        <v>7.69</v>
+        <v>7.95</v>
       </c>
       <c r="AW43" t="n">
-        <v>10.48</v>
+        <v>10.27</v>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
@@ -8360,14 +8360,14 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.7))</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>380.1</v>
+        <v>377</v>
       </c>
       <c r="F44" t="n">
         <v>7.7408</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>480.96</v>
+        <v>477.03</v>
       </c>
       <c r="M44" t="n">
         <v>0.7903</v>
@@ -8418,10 +8418,10 @@
         <v>34531</v>
       </c>
       <c r="O44" t="n">
-        <v>97060</v>
+        <v>11920</v>
       </c>
       <c r="P44" t="n">
-        <v>2.811</v>
+        <v>0.345</v>
       </c>
       <c r="Q44" t="n">
         <v>13078</v>
@@ -8439,10 +8439,10 @@
         <v>409.99</v>
       </c>
       <c r="V44" t="n">
-        <v>361.2042</v>
+        <v>361.2842</v>
       </c>
       <c r="W44" t="n">
-        <v>342.3466</v>
+        <v>342.811</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -8455,13 +8455,13 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>370.9207</v>
+        <v>371.4997</v>
       </c>
       <c r="AA44" t="n">
-        <v>362.9089</v>
+        <v>363.4614</v>
       </c>
       <c r="AB44" t="n">
-        <v>321.4222</v>
+        <v>321.9752</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="AE44" t="n">
-        <v>6.7134</v>
+        <v>6.3455</v>
       </c>
       <c r="AF44" t="n">
-        <v>4.5813</v>
+        <v>4.9341</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -8485,18 +8485,18 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>55.8</v>
+        <v>54.14</v>
       </c>
       <c r="AI44" t="n">
-        <v>380.9765</v>
+        <v>381.7124</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>362.8512</v>
+        <v>364.2342</v>
       </c>
       <c r="AL44" t="n">
         <v>360</v>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="AN44" t="n">
-        <v>391.2441</v>
+        <v>391.5976</v>
       </c>
       <c r="AO44" t="n">
         <v>423.2347</v>
@@ -8517,26 +8517,26 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 391.24; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
+          <t>TP1: Bollinger Upper Band at 391.6; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
         </is>
       </c>
       <c r="AR44" t="n">
-        <v>9.960000000000001</v>
+        <v>6.46</v>
       </c>
       <c r="AS44" t="n">
-        <v>21.18</v>
+        <v>13.93</v>
       </c>
       <c r="AT44" t="n">
-        <v>25.88</v>
+        <v>17.1</v>
       </c>
       <c r="AU44" t="n">
-        <v>7.82</v>
+        <v>7.51</v>
       </c>
       <c r="AV44" t="n">
-        <v>16.64</v>
+        <v>16.2</v>
       </c>
       <c r="AW44" t="n">
-        <v>20.34</v>
+        <v>19.88</v>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
@@ -8545,14 +8545,14 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 55.8))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 54.1))</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>279.14</v>
+        <v>269.99</v>
       </c>
       <c r="F45" t="n">
         <v>5.4066</v>
@@ -8599,10 +8599,10 @@
         <v>92397</v>
       </c>
       <c r="O45" t="n">
-        <v>170473</v>
+        <v>38210</v>
       </c>
       <c r="P45" t="n">
-        <v>1.845</v>
+        <v>0.414</v>
       </c>
       <c r="Q45" t="n">
         <v>36770</v>
@@ -8620,10 +8620,10 @@
         <v>247.97</v>
       </c>
       <c r="V45" t="n">
-        <v>220.1554</v>
+        <v>221.2952</v>
       </c>
       <c r="W45" t="n">
-        <v>187.1864</v>
+        <v>187.7014</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -8636,13 +8636,13 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>245.1907</v>
+        <v>247.5526</v>
       </c>
       <c r="AA45" t="n">
-        <v>224.6948</v>
+        <v>226.471</v>
       </c>
       <c r="AB45" t="n">
-        <v>182.9885</v>
+        <v>183.8542</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -8655,10 +8655,10 @@
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>16.5496</v>
+        <v>16.4337</v>
       </c>
       <c r="AF45" t="n">
-        <v>11.314</v>
+        <v>12.338</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -8666,21 +8666,21 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>66.20999999999999</v>
+        <v>61.68</v>
       </c>
       <c r="AI45" t="n">
-        <v>255.2713</v>
+        <v>257.1792</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>256.995</v>
+        <v>257.1792</v>
       </c>
       <c r="AL45" t="n">
-        <v>240.49</v>
+        <v>249.79</v>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         </is>
       </c>
       <c r="AN45" t="n">
-        <v>283.3896</v>
+        <v>286.6019</v>
       </c>
       <c r="AO45" t="n">
         <v>288.2818</v>
@@ -8698,26 +8698,26 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 283.39; TP2: Fibonacci R1 at 288.28; TP3: Classic R1 at 307.96</t>
+          <t>TP1: Bollinger Upper Band at 286.6; TP2: Fibonacci R1 at 288.28; TP3: Classic R1 at 307.96</t>
         </is>
       </c>
       <c r="AR45" t="n">
-        <v>1.6</v>
+        <v>3.98</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.9</v>
+        <v>4.21</v>
       </c>
       <c r="AT45" t="n">
-        <v>3.09</v>
+        <v>6.87</v>
       </c>
       <c r="AU45" t="n">
-        <v>10.27</v>
+        <v>11.44</v>
       </c>
       <c r="AV45" t="n">
-        <v>12.17</v>
+        <v>12.09</v>
       </c>
       <c r="AW45" t="n">
-        <v>19.83</v>
+        <v>19.75</v>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
@@ -8726,14 +8726,14 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 66.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.7))</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8.15</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F46" t="n">
         <v>0.1596</v>
@@ -8780,10 +8780,10 @@
         <v>2487325</v>
       </c>
       <c r="O46" t="n">
-        <v>2708107</v>
+        <v>551956</v>
       </c>
       <c r="P46" t="n">
-        <v>1.089</v>
+        <v>0.222</v>
       </c>
       <c r="Q46" t="n">
         <v>2366094</v>
@@ -8801,10 +8801,10 @@
         <v>6.56</v>
       </c>
       <c r="V46" t="n">
-        <v>6.9118</v>
+        <v>6.9544</v>
       </c>
       <c r="W46" t="n">
-        <v>6.4076</v>
+        <v>6.421</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -8817,13 +8817,13 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>7.8424</v>
+        <v>7.8784</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.192</v>
+        <v>7.2323</v>
       </c>
       <c r="AB46" t="n">
-        <v>6.3212</v>
+        <v>6.3401</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>0.4037</v>
+        <v>0.3854</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.4646</v>
+        <v>0.4487</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -8847,21 +8847,21 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>62.5</v>
+        <v>63.76</v>
       </c>
       <c r="AI46" t="n">
-        <v>7.7791</v>
+        <v>7.9333</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>7.7791</v>
+        <v>7.9333</v>
       </c>
       <c r="AL46" t="n">
-        <v>6.9704</v>
+        <v>7.1222</v>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
@@ -8872,33 +8872,33 @@
         <v>8.755100000000001</v>
       </c>
       <c r="AO46" t="n">
-        <v>8.8886</v>
+        <v>8.857799999999999</v>
       </c>
       <c r="AP46" t="n">
         <v>9.2333</v>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.89; TP3: Classic R1 at 9.23</t>
+          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.86; TP3: Classic R1 at 9.23</t>
         </is>
       </c>
       <c r="AR46" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AU46" t="n">
-        <v>12.55</v>
+        <v>10.36</v>
       </c>
       <c r="AV46" t="n">
-        <v>14.26</v>
+        <v>11.65</v>
       </c>
       <c r="AW46" t="n">
-        <v>18.69</v>
+        <v>16.39</v>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
@@ -8907,14 +8907,14 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.8))</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="F47" t="n">
         <v>0.0294</v>
@@ -8967,10 +8967,10 @@
         <v>39851604</v>
       </c>
       <c r="O47" t="n">
-        <v>171902548</v>
+        <v>104556127</v>
       </c>
       <c r="P47" t="n">
-        <v>4.314</v>
+        <v>2.624</v>
       </c>
       <c r="Q47" t="n">
         <v>29028496</v>
@@ -8988,10 +8988,10 @@
         <v>1.57</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3016</v>
+        <v>1.308</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1858</v>
+        <v>1.19</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -9004,13 +9004,13 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>1.4224</v>
+        <v>1.4374</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.3401</v>
+        <v>1.3495</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.1568</v>
+        <v>1.1611</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -9023,10 +9023,10 @@
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>0.0756</v>
+        <v>0.0786</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0603</v>
+        <v>0.064</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -9034,58 +9034,58 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>75.34</v>
+        <v>73.45</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.4405</v>
+        <v>1.4511</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>1.4405</v>
+        <v>1.4511</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN47" t="n">
-        <v>1.6089</v>
+        <v>1.5828</v>
       </c>
       <c r="AO47" t="n">
+        <v>1.6298</v>
+      </c>
+      <c r="AP47" t="n">
         <v>1.66</v>
       </c>
-      <c r="AP47" t="n">
-        <v>1.6772</v>
-      </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1.61; TP2: Classic R1 at 1.66; TP3: Fibonacci R2 at 1.68</t>
+          <t>TP1: Fibonacci R1 at 1.58; TP2: Bollinger Upper Band at 1.63; TP3: Classic R1 at 1.66</t>
         </is>
       </c>
       <c r="AR47" t="n">
-        <v>1.4</v>
+        <v>124</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.82</v>
+        <v>168.25</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.97</v>
+        <v>196.67</v>
       </c>
       <c r="AU47" t="n">
-        <v>11.69</v>
+        <v>9.08</v>
       </c>
       <c r="AV47" t="n">
-        <v>15.24</v>
+        <v>12.32</v>
       </c>
       <c r="AW47" t="n">
-        <v>16.44</v>
+        <v>14.4</v>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
@@ -9094,14 +9094,14 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.3); entry: enhanced entry at VWMA (overbought (RSI: 75.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.5); entry: enhanced entry at VWMA (overbought (RSI: 73.5))</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.901</v>
+        <v>0.907</v>
       </c>
       <c r="F48" t="n">
         <v>0.0164</v>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>13.06</v>
+        <v>13.14</v>
       </c>
       <c r="M48" t="n">
         <v>0.06900000000000001</v>
@@ -9152,10 +9152,10 @@
         <v>19634877</v>
       </c>
       <c r="O48" t="n">
-        <v>36073167</v>
+        <v>3493926</v>
       </c>
       <c r="P48" t="n">
-        <v>1.837</v>
+        <v>0.178</v>
       </c>
       <c r="Q48" t="n">
         <v>22450213</v>
@@ -9173,10 +9173,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5532</v>
+        <v>0.5631</v>
       </c>
       <c r="W48" t="n">
-        <v>0.4272</v>
+        <v>0.43</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -9189,13 +9189,13 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>0.7597</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.6147</v>
+        <v>0.6262</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.4538</v>
+        <v>0.4583</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -9208,10 +9208,10 @@
         </is>
       </c>
       <c r="AE48" t="n">
-        <v>0.1033</v>
+        <v>0.1023</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.1015</v>
+        <v>0.1017</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -9219,18 +9219,18 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>77.01000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.7456</v>
+        <v>0.7593</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>0.7456</v>
+        <v>0.7593</v>
       </c>
       <c r="AL48" t="n">
         <v>0.595</v>
@@ -9247,30 +9247,30 @@
         <v>1.0187</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.0314</v>
+        <v>1.0331</v>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 0.93; TP2: Classic R1 at 1.02; TP3: Bollinger Upper Band at 1.03</t>
+          <t>TP1: Fibonacci R1 at 0.93; TP2: Classic R1 at 1.02; TP3: Fibonacci R2 at 1.03</t>
         </is>
       </c>
       <c r="AR48" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AU48" t="n">
-        <v>24.12</v>
+        <v>21.88</v>
       </c>
       <c r="AV48" t="n">
-        <v>36.62</v>
+        <v>34.16</v>
       </c>
       <c r="AW48" t="n">
-        <v>38.33</v>
+        <v>36.05</v>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.0); entry: enhanced entry at VWMA (overbought (RSI: 77.0))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.4); entry: enhanced entry at VWMA (overbought (RSI: 77.4))</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.53</v>
+        <v>0.524</v>
       </c>
       <c r="F49" t="n">
         <v>0.0103</v>
@@ -9335,10 +9335,10 @@
         <v>20532324</v>
       </c>
       <c r="O49" t="n">
-        <v>32612460</v>
+        <v>4642907</v>
       </c>
       <c r="P49" t="n">
-        <v>1.588</v>
+        <v>0.226</v>
       </c>
       <c r="Q49" t="n">
         <v>19286208</v>
@@ -9356,10 +9356,10 @@
         <v>0.546</v>
       </c>
       <c r="V49" t="n">
-        <v>0.4477</v>
+        <v>0.4497</v>
       </c>
       <c r="W49" t="n">
-        <v>0.4666</v>
+        <v>0.4674</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -9372,13 +9372,13 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>0.4959</v>
+        <v>0.4985</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.4659</v>
+        <v>0.4682</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4429</v>
+        <v>0.4437</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
@@ -9391,10 +9391,10 @@
         </is>
       </c>
       <c r="AE49" t="n">
-        <v>0.0286</v>
+        <v>0.0272</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0245</v>
+        <v>0.0251</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -9402,14 +9402,14 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>62.08</v>
+        <v>60.17</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.5172</v>
+        <v>0.5198</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9447,7 +9447,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9466,7 +9466,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>503.7</v>
+        <v>493.2</v>
       </c>
       <c r="F50" t="n">
         <v>9.111499999999999</v>
@@ -9494,10 +9494,10 @@
         <v>11790</v>
       </c>
       <c r="O50" t="n">
-        <v>45500</v>
+        <v>7461</v>
       </c>
       <c r="P50" t="n">
-        <v>3.859</v>
+        <v>0.633</v>
       </c>
       <c r="Q50" t="n">
         <v>7222</v>
@@ -9515,10 +9515,10 @@
         <v>512</v>
       </c>
       <c r="V50" t="n">
-        <v>398.9838</v>
+        <v>401.7518</v>
       </c>
       <c r="W50" t="n">
-        <v>301.6611</v>
+        <v>303.0021</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -9531,13 +9531,13 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>451.8576</v>
+        <v>455.795</v>
       </c>
       <c r="AA50" t="n">
-        <v>407.7679</v>
+        <v>411.1181</v>
       </c>
       <c r="AB50" t="n">
-        <v>312.0306</v>
+        <v>313.8333</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>25.9575</v>
+        <v>26.0992</v>
       </c>
       <c r="AF50" t="n">
-        <v>25.0625</v>
+        <v>25.2699</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -9561,21 +9561,21 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>78.61</v>
+        <v>71.87</v>
       </c>
       <c r="AI50" t="n">
-        <v>464.9611</v>
+        <v>465.8172</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>464.9611</v>
+        <v>465.8172</v>
       </c>
       <c r="AL50" t="n">
-        <v>442.4273</v>
+        <v>447.0816</v>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
@@ -9583,36 +9583,36 @@
         </is>
       </c>
       <c r="AN50" t="n">
-        <v>514.4535</v>
+        <v>501.4547</v>
       </c>
       <c r="AO50" t="n">
+        <v>517.0126</v>
+      </c>
+      <c r="AP50" t="n">
         <v>518.9933</v>
       </c>
-      <c r="AP50" t="n">
-        <v>529.5386999999999</v>
-      </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 514.45; TP2: Classic R1 at 518.99; TP3: Fibonacci R2 at 529.54</t>
+          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 517.01; TP3: Classic R1 at 518.99</t>
         </is>
       </c>
       <c r="AR50" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AS50" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="AT50" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="AU50" t="n">
-        <v>10.64</v>
+        <v>7.65</v>
       </c>
       <c r="AV50" t="n">
-        <v>11.62</v>
+        <v>10.99</v>
       </c>
       <c r="AW50" t="n">
-        <v>13.89</v>
+        <v>11.42</v>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
@@ -9621,14 +9621,14 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.6); entry: enhanced entry at VWMA (overbought (RSI: 78.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.9); entry: enhanced entry at VWMA (overbought (RSI: 71.9))</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1327.71</v>
+        <v>1280</v>
       </c>
       <c r="F51" t="n">
         <v>23.8879</v>
@@ -9677,10 +9677,10 @@
         <v>2326</v>
       </c>
       <c r="O51" t="n">
-        <v>13978</v>
+        <v>1648</v>
       </c>
       <c r="P51" t="n">
-        <v>6.009</v>
+        <v>0.709</v>
       </c>
       <c r="Q51" t="n">
         <v>942</v>
@@ -9698,10 +9698,10 @@
         <v>1275</v>
       </c>
       <c r="V51" t="n">
-        <v>1165.5276</v>
+        <v>1167.7612</v>
       </c>
       <c r="W51" t="n">
-        <v>911.3147</v>
+        <v>914.1598</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -9714,13 +9714,13 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>1217.6836</v>
+        <v>1223.6185</v>
       </c>
       <c r="AA51" t="n">
-        <v>1151.4698</v>
+        <v>1156.5102</v>
       </c>
       <c r="AB51" t="n">
-        <v>925.187</v>
+        <v>928.7175</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -9733,10 +9733,10 @@
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>31.7112</v>
+        <v>32.8484</v>
       </c>
       <c r="AF51" t="n">
-        <v>28.538</v>
+        <v>29.4001</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -9744,21 +9744,21 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>78.39</v>
+        <v>64.45</v>
       </c>
       <c r="AI51" t="n">
-        <v>1236.1014</v>
+        <v>1240.9278</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK51" t="n">
         <v>1257</v>
       </c>
       <c r="AL51" t="n">
-        <v>1154.6213</v>
+        <v>1156.5558</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
@@ -9766,52 +9766,52 @@
         </is>
       </c>
       <c r="AN51" t="n">
+        <v>1290.7572</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>1312.2368</v>
+      </c>
+      <c r="AP51" t="n">
         <v>1341.2533</v>
       </c>
-      <c r="AO51" t="n">
-        <v>1371.9165</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>1468.5167</v>
-      </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 1341.25; TP2: Fibonacci R2 at 1371.92; TP3: Classic R2 at 1468.52</t>
+          <t>TP1: Bollinger Upper Band at 1290.76; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
         </is>
       </c>
       <c r="AR51" t="n">
-        <v>0.82</v>
+        <v>0.34</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.12</v>
+        <v>0.55</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.07</v>
+        <v>0.84</v>
       </c>
       <c r="AU51" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AW51" t="n">
         <v>6.7</v>
       </c>
-      <c r="AV51" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>16.83</v>
-      </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.4))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.5))</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9830,7 +9830,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>244</v>
+        <v>243.02</v>
       </c>
       <c r="F52" t="n">
         <v>4.782</v>
@@ -9864,10 +9864,10 @@
         <v>93109</v>
       </c>
       <c r="O52" t="n">
-        <v>59521</v>
+        <v>9869</v>
       </c>
       <c r="P52" t="n">
-        <v>0.639</v>
+        <v>0.106</v>
       </c>
       <c r="Q52" t="n">
         <v>39811</v>
@@ -9885,10 +9885,10 @@
         <v>248.96</v>
       </c>
       <c r="V52" t="n">
-        <v>254.6694</v>
+        <v>254.2298</v>
       </c>
       <c r="W52" t="n">
-        <v>245.2021</v>
+        <v>245.6599</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -9901,13 +9901,13 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>244.8346</v>
+        <v>244.6618</v>
       </c>
       <c r="AA52" t="n">
-        <v>250.4443</v>
+        <v>250.1531</v>
       </c>
       <c r="AB52" t="n">
-        <v>234.1449</v>
+        <v>234.2332</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="AE52" t="n">
-        <v>-1.6251</v>
+        <v>-1.6038</v>
       </c>
       <c r="AF52" t="n">
-        <v>-2.6618</v>
+        <v>-2.4502</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -9931,14 +9931,14 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>46.32</v>
+        <v>44.77</v>
       </c>
       <c r="AI52" t="n">
-        <v>243.3361</v>
+        <v>243.2538</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK52" t="n">
@@ -9953,36 +9953,36 @@
         </is>
       </c>
       <c r="AN52" t="n">
-        <v>245.2021</v>
+        <v>245.6599</v>
       </c>
       <c r="AO52" t="n">
         <v>248.1478</v>
       </c>
       <c r="AP52" t="n">
-        <v>250.2763</v>
+        <v>250.0279</v>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 245.2; TP2: Fibonacci R1 at 248.15; TP3: Bollinger Upper Band at 250.28</t>
+          <t>TP1: 200 SMA at 245.66; TP2: Fibonacci R1 at 248.15; TP3: Bollinger Upper Band at 250.03</t>
         </is>
       </c>
       <c r="AR52" t="n">
-        <v>8.970000000000001</v>
+        <v>9.41</v>
       </c>
       <c r="AS52" t="n">
         <v>11.79</v>
       </c>
       <c r="AT52" t="n">
-        <v>13.83</v>
+        <v>13.59</v>
       </c>
       <c r="AU52" t="n">
-        <v>3.97</v>
+        <v>4.17</v>
       </c>
       <c r="AV52" t="n">
         <v>5.22</v>
       </c>
       <c r="AW52" t="n">
-        <v>6.13</v>
+        <v>6.02</v>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
@@ -9991,14 +9991,14 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 46.3))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Ichimoku Kijun-sen (neutral (RSI: 44.8))</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10017,7 +10017,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>186.94</v>
+        <v>189</v>
       </c>
       <c r="F53" t="n">
         <v>3.758</v>
@@ -10045,10 +10045,10 @@
         <v>91987</v>
       </c>
       <c r="O53" t="n">
-        <v>142761</v>
+        <v>69788</v>
       </c>
       <c r="P53" t="n">
-        <v>1.552</v>
+        <v>0.759</v>
       </c>
       <c r="Q53" t="n">
         <v>95843</v>
@@ -10066,10 +10066,10 @@
         <v>197.49</v>
       </c>
       <c r="V53" t="n">
-        <v>146.0726</v>
+        <v>147.0412</v>
       </c>
       <c r="W53" t="n">
-        <v>123.0587</v>
+        <v>123.5466</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -10082,13 +10082,13 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>167.3716</v>
+        <v>169.4314</v>
       </c>
       <c r="AA53" t="n">
-        <v>149.1148</v>
+        <v>150.679</v>
       </c>
       <c r="AB53" t="n">
-        <v>120.0184</v>
+        <v>120.7048</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -10101,10 +10101,10 @@
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>15.2845</v>
+        <v>15.0779</v>
       </c>
       <c r="AF53" t="n">
-        <v>11.5979</v>
+        <v>12.2939</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -10112,58 +10112,58 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>60.83</v>
+        <v>61.5</v>
       </c>
       <c r="AI53" t="n">
-        <v>173.3633</v>
+        <v>173.7487</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK53" t="n">
-        <v>173.3633</v>
+        <v>177.0392</v>
       </c>
       <c r="AL53" t="n">
-        <v>172.34</v>
+        <v>145.354</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN53" t="n">
         <v>208.4527</v>
       </c>
       <c r="AO53" t="n">
-        <v>210.3357</v>
+        <v>212.835</v>
       </c>
       <c r="AP53" t="n">
         <v>224.8967</v>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 210.34; TP3: Classic R1 at 224.9</t>
+          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 212.84; TP3: Classic R1 at 224.9</t>
         </is>
       </c>
       <c r="AR53" t="n">
-        <v>34.29</v>
+        <v>0.99</v>
       </c>
       <c r="AS53" t="n">
-        <v>36.13</v>
+        <v>1.13</v>
       </c>
       <c r="AT53" t="n">
-        <v>50.36</v>
+        <v>1.51</v>
       </c>
       <c r="AU53" t="n">
-        <v>20.24</v>
+        <v>17.74</v>
       </c>
       <c r="AV53" t="n">
-        <v>21.33</v>
+        <v>20.22</v>
       </c>
       <c r="AW53" t="n">
-        <v>29.73</v>
+        <v>27.03</v>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
@@ -10172,14 +10172,14 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.8))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 61.5))</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10232,10 +10232,10 @@
         <v>24738418</v>
       </c>
       <c r="O54" t="n">
-        <v>40424958</v>
+        <v>4582236</v>
       </c>
       <c r="P54" t="n">
-        <v>1.634</v>
+        <v>0.185</v>
       </c>
       <c r="Q54" t="n">
         <v>14803414</v>
@@ -10253,10 +10253,10 @@
         <v>6.69</v>
       </c>
       <c r="V54" t="n">
-        <v>6.634</v>
+        <v>6.6504</v>
       </c>
       <c r="W54" t="n">
-        <v>5.8443</v>
+        <v>5.856</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -10269,13 +10269,13 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>7.2062</v>
+        <v>7.2008</v>
       </c>
       <c r="AA54" t="n">
-        <v>6.758</v>
+        <v>6.7734</v>
       </c>
       <c r="AB54" t="n">
-        <v>5.7891</v>
+        <v>5.8026</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -10288,10 +10288,10 @@
         </is>
       </c>
       <c r="AE54" t="n">
-        <v>0.2172</v>
+        <v>0.1874</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.2835</v>
+        <v>0.2643</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -10302,18 +10302,18 @@
         <v>51.89</v>
       </c>
       <c r="AI54" t="n">
-        <v>7.2847</v>
+        <v>7.2988</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK54" t="n">
         <v>6.99</v>
       </c>
       <c r="AL54" t="n">
-        <v>6.6577</v>
+        <v>6.7152</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
@@ -10327,21 +10327,21 @@
         <v>7.8167</v>
       </c>
       <c r="AP54" t="n">
-        <v>7.8743</v>
+        <v>7.8538</v>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.87</t>
+          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.85</t>
         </is>
       </c>
       <c r="AR54" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.49</v>
+        <v>3.01</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.66</v>
+        <v>3.14</v>
       </c>
       <c r="AU54" t="n">
         <v>9.41</v>
@@ -10350,7 +10350,7 @@
         <v>11.83</v>
       </c>
       <c r="AW54" t="n">
-        <v>12.65</v>
+        <v>12.36</v>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10385,7 +10385,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12.65</v>
+        <v>12.59</v>
       </c>
       <c r="F55" t="n">
         <v>0.2222</v>
@@ -10408,7 +10408,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>14.1</v>
+        <v>14.04</v>
       </c>
       <c r="M55" t="n">
         <v>0.8969</v>
@@ -10417,10 +10417,10 @@
         <v>3424205</v>
       </c>
       <c r="O55" t="n">
-        <v>2650610</v>
+        <v>365238</v>
       </c>
       <c r="P55" t="n">
-        <v>0.774</v>
+        <v>0.107</v>
       </c>
       <c r="Q55" t="n">
         <v>754146</v>
@@ -10438,10 +10438,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="V55" t="n">
-        <v>9.3698</v>
+        <v>9.444800000000001</v>
       </c>
       <c r="W55" t="n">
-        <v>6.1606</v>
+        <v>6.2057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>10.4827</v>
+        <v>10.6834</v>
       </c>
       <c r="AA55" t="n">
-        <v>9.4224</v>
+        <v>9.5466</v>
       </c>
       <c r="AB55" t="n">
-        <v>6.7345</v>
+        <v>6.7928</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -10473,10 +10473,10 @@
         </is>
       </c>
       <c r="AE55" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.8703</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6302</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -10484,58 +10484,58 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>78.25</v>
+        <v>77.19</v>
       </c>
       <c r="AI55" t="n">
-        <v>10.3341</v>
+        <v>10.406</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK55" t="n">
-        <v>10.95</v>
+        <v>11.0483</v>
       </c>
       <c r="AL55" t="n">
-        <v>10.5102</v>
+        <v>9.4033</v>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AN55" t="n">
+        <v>12.7831</v>
+      </c>
+      <c r="AO55" t="n">
         <v>13.4067</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AP55" t="n">
         <v>16.3367</v>
       </c>
-      <c r="AP55" t="n">
-        <v>18.3944</v>
-      </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 13.41; TP2: Classic R3 at 16.34; TP3: Extension at 18.39</t>
+          <t>TP1: Bollinger Upper Band at 12.78; TP2: Classic R2 at 13.41; TP3: Classic R3 at 16.34</t>
         </is>
       </c>
       <c r="AR55" t="n">
-        <v>5.59</v>
+        <v>1.05</v>
       </c>
       <c r="AS55" t="n">
-        <v>12.25</v>
+        <v>1.43</v>
       </c>
       <c r="AT55" t="n">
-        <v>16.93</v>
+        <v>3.21</v>
       </c>
       <c r="AU55" t="n">
-        <v>22.44</v>
+        <v>15.7</v>
       </c>
       <c r="AV55" t="n">
-        <v>49.19</v>
+        <v>21.35</v>
       </c>
       <c r="AW55" t="n">
-        <v>67.98999999999999</v>
+        <v>47.87</v>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
@@ -10544,14 +10544,14 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.2); entry: enhanced entry at Parabolic SAR (overbought (RSI: 77.2))</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10730,7 +10730,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="F57" t="n">
         <v>5.7269</v>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>14.62</v>
+        <v>13.91</v>
       </c>
       <c r="M57" t="n">
         <v>22.7816</v>
@@ -10781,10 +10781,10 @@
         <v>366899</v>
       </c>
       <c r="O57" t="n">
-        <v>989538</v>
+        <v>176435</v>
       </c>
       <c r="P57" t="n">
-        <v>2.697</v>
+        <v>0.481</v>
       </c>
       <c r="Q57" t="n">
         <v>173022</v>
@@ -10802,10 +10802,10 @@
         <v>252.69</v>
       </c>
       <c r="V57" t="n">
-        <v>239.849</v>
+        <v>242.009</v>
       </c>
       <c r="W57" t="n">
-        <v>184.386</v>
+        <v>185.2026</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -10818,13 +10818,13 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>272.8853</v>
+        <v>277.0867</v>
       </c>
       <c r="AA57" t="n">
-        <v>243.866</v>
+        <v>246.734</v>
       </c>
       <c r="AB57" t="n">
-        <v>185.8437</v>
+        <v>187.1488</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -10837,10 +10837,10 @@
         </is>
       </c>
       <c r="AE57" t="n">
-        <v>20.1912</v>
+        <v>21.1897</v>
       </c>
       <c r="AF57" t="n">
-        <v>15.4367</v>
+        <v>16.5873</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -10848,21 +10848,21 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>84.89</v>
+        <v>73</v>
       </c>
       <c r="AI57" t="n">
-        <v>273.6773</v>
+        <v>275.3578</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK57" t="n">
         <v>280.775</v>
       </c>
       <c r="AL57" t="n">
-        <v>264.2685</v>
+        <v>276.2255</v>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
@@ -10870,37 +10870,37 @@
         </is>
       </c>
       <c r="AN57" t="n">
+        <v>325.7871</v>
+      </c>
+      <c r="AO57" t="n">
         <v>337.12</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AP57" t="n">
         <v>398.9</v>
       </c>
-      <c r="AP57" t="n">
-        <v>444.0237</v>
-      </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 337.12; TP2: Classic R3 at 398.9; TP3: Extension at 444.02</t>
+          <t>TP1: Bollinger Upper Band at 325.79; TP2: Classic R2 at 337.12; TP3: Classic R3 at 398.9</t>
         </is>
       </c>
       <c r="AR57" t="n">
-        <v>3.41</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AS57" t="n">
-        <v>7.16</v>
+        <v>12.38</v>
       </c>
       <c r="AT57" t="n">
-        <v>9.890000000000001</v>
+        <v>25.96</v>
       </c>
       <c r="AU57" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="AV57" t="n">
         <v>20.07</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AW57" t="n">
         <v>42.07</v>
       </c>
-      <c r="AW57" t="n">
-        <v>58.14</v>
-      </c>
       <c r="AX57" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -10908,14 +10908,14 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (84.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 84.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 73.0))</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="F58" t="n">
         <v>0.3446</v>
@@ -10968,10 +10968,10 @@
         <v>723230</v>
       </c>
       <c r="O58" t="n">
-        <v>4819169</v>
+        <v>398997</v>
       </c>
       <c r="P58" t="n">
-        <v>6.663</v>
+        <v>0.552</v>
       </c>
       <c r="Q58" t="n">
         <v>507451</v>
@@ -10989,10 +10989,10 @@
         <v>16.34</v>
       </c>
       <c r="V58" t="n">
-        <v>16.03</v>
+        <v>16.083</v>
       </c>
       <c r="W58" t="n">
-        <v>15.6482</v>
+        <v>15.6807</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -11005,13 +11005,13 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>16.6459</v>
+        <v>16.8701</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.137</v>
+        <v>16.2493</v>
       </c>
       <c r="AB58" t="n">
-        <v>15.0214</v>
+        <v>15.0609</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -11024,10 +11024,10 @@
         </is>
       </c>
       <c r="AE58" t="n">
-        <v>0.601</v>
+        <v>0.71</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.2376</v>
+        <v>0.3321</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -11035,21 +11035,21 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>79.41</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AI58" t="n">
-        <v>17.1589</v>
+        <v>17.1901</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK58" t="n">
         <v>17.43</v>
       </c>
       <c r="AL58" t="n">
-        <v>16.3483</v>
+        <v>16.6076</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
@@ -11057,37 +11057,37 @@
         </is>
       </c>
       <c r="AN58" t="n">
+        <v>19.0869</v>
+      </c>
+      <c r="AO58" t="n">
         <v>19.6033</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AP58" t="n">
         <v>20.1064</v>
       </c>
-      <c r="AP58" t="n">
-        <v>21.7567</v>
-      </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 19.6; TP2: Fibonacci R2 at 20.11; TP3: Classic R2 at 21.76</t>
+          <t>TP1: Fibonacci R1 at 19.09; TP2: Classic R1 at 19.6; TP3: Fibonacci R2 at 20.11</t>
         </is>
       </c>
       <c r="AR58" t="n">
         <v>2.01</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="AT58" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AU58" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="AV58" t="n">
         <v>12.47</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AW58" t="n">
         <v>15.36</v>
       </c>
-      <c r="AW58" t="n">
-        <v>24.82</v>
-      </c>
       <c r="AX58" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -11095,14 +11095,14 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.4))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.1))</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.597</v>
+        <v>0.594</v>
       </c>
       <c r="F59" t="n">
         <v>0.0107</v>
@@ -11151,10 +11151,10 @@
         <v>22425456</v>
       </c>
       <c r="O59" t="n">
-        <v>94427036</v>
+        <v>8066415</v>
       </c>
       <c r="P59" t="n">
-        <v>4.211</v>
+        <v>0.36</v>
       </c>
       <c r="Q59" t="n">
         <v>26338384</v>
@@ -11172,10 +11172,10 @@
         <v>0.582</v>
       </c>
       <c r="V59" t="n">
-        <v>0.5438</v>
+        <v>0.5467</v>
       </c>
       <c r="W59" t="n">
-        <v>0.4731</v>
+        <v>0.4738</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -11188,13 +11188,13 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>0.5765</v>
+        <v>0.5782</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.5473</v>
+        <v>0.5492</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.4865</v>
+        <v>0.4875</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -11207,10 +11207,10 @@
         </is>
       </c>
       <c r="AE59" t="n">
-        <v>0.0073</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.0109</v>
+        <v>0.0103</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -11218,18 +11218,18 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>57.66</v>
+        <v>56.66</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.5868</v>
+        <v>0.5873</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK59" t="n">
-        <v>0.5868</v>
+        <v>0.5873</v>
       </c>
       <c r="AL59" t="n">
         <v>0.5770999999999999</v>
@@ -11243,7 +11243,7 @@
         <v>0.5994</v>
       </c>
       <c r="AO59" t="n">
-        <v>0.6055</v>
+        <v>0.6068</v>
       </c>
       <c r="AP59" t="n">
         <v>0.6229</v>
@@ -11254,22 +11254,22 @@
         </is>
       </c>
       <c r="AR59" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AT59" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="AU59" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AV59" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="AW59" t="n">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
@@ -11278,14 +11278,14 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.7))</t>
+          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.7))</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11304,7 +11304,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>118.54</v>
+        <v>121.5</v>
       </c>
       <c r="F60" t="n">
         <v>2.1067</v>
@@ -11334,10 +11334,10 @@
         <v>122002</v>
       </c>
       <c r="O60" t="n">
-        <v>996104</v>
+        <v>78235</v>
       </c>
       <c r="P60" t="n">
-        <v>8.164999999999999</v>
+        <v>0.641</v>
       </c>
       <c r="Q60" t="n">
         <v>39546</v>
@@ -11355,10 +11355,10 @@
         <v>136.77</v>
       </c>
       <c r="V60" t="n">
-        <v>100.3836</v>
+        <v>100.7536</v>
       </c>
       <c r="W60" t="n">
-        <v>89.6288</v>
+        <v>89.8493</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -11371,13 +11371,13 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>105.1947</v>
+        <v>106.7476</v>
       </c>
       <c r="AA60" t="n">
-        <v>100.8114</v>
+        <v>101.6228</v>
       </c>
       <c r="AB60" t="n">
-        <v>89.0014</v>
+        <v>89.32470000000001</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="AE60" t="n">
-        <v>4.074</v>
+        <v>4.8536</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.7213</v>
+        <v>3.1477</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -11401,21 +11401,21 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>79.09</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="AI60" t="n">
-        <v>107.4858</v>
+        <v>107.8359</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK60" t="n">
-        <v>107.4858</v>
+        <v>107.8359</v>
       </c>
       <c r="AL60" t="n">
-        <v>104</v>
+        <v>104.828</v>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
@@ -11429,30 +11429,30 @@
         <v>143.7933</v>
       </c>
       <c r="AP60" t="n">
-        <v>157.6628</v>
+        <v>157.529</v>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 123.25; TP2: Classic R3 at 143.79; TP3: Extension at 157.66</t>
+          <t>TP1: Classic R2 at 123.25; TP2: Classic R3 at 143.79; TP3: Extension at 157.53</t>
         </is>
       </c>
       <c r="AR60" t="n">
-        <v>4.52</v>
+        <v>5.13</v>
       </c>
       <c r="AS60" t="n">
-        <v>10.42</v>
+        <v>11.95</v>
       </c>
       <c r="AT60" t="n">
-        <v>14.39</v>
+        <v>16.52</v>
       </c>
       <c r="AU60" t="n">
-        <v>14.67</v>
+        <v>14.3</v>
       </c>
       <c r="AV60" t="n">
-        <v>33.78</v>
+        <v>33.34</v>
       </c>
       <c r="AW60" t="n">
-        <v>46.68</v>
+        <v>46.08</v>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
@@ -11461,14 +11461,14 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.1); entry: enhanced entry at VWMA (overbought (RSI: 79.1))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.3); entry: enhanced entry at VWMA (overbought (RSI: 81.3))</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>11.23</v>
+        <v>11.37</v>
       </c>
       <c r="F61" t="n">
         <v>0.2074</v>
@@ -11515,10 +11515,10 @@
         <v>1631553</v>
       </c>
       <c r="O61" t="n">
-        <v>2069935</v>
+        <v>255856</v>
       </c>
       <c r="P61" t="n">
-        <v>1.269</v>
+        <v>0.157</v>
       </c>
       <c r="Q61" t="n">
         <v>622861</v>
@@ -11536,10 +11536,10 @@
         <v>11.74</v>
       </c>
       <c r="V61" t="n">
-        <v>9.5646</v>
+        <v>9.605399999999999</v>
       </c>
       <c r="W61" t="n">
-        <v>8.1084</v>
+        <v>8.1327</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -11552,13 +11552,13 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>10.463</v>
+        <v>10.5494</v>
       </c>
       <c r="AA61" t="n">
-        <v>9.808999999999999</v>
+        <v>9.870200000000001</v>
       </c>
       <c r="AB61" t="n">
-        <v>8.3767</v>
+        <v>8.406499999999999</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -11571,10 +11571,10 @@
         </is>
       </c>
       <c r="AE61" t="n">
-        <v>0.498</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.4703</v>
+        <v>0.4779</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -11582,18 +11582,18 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>66.62</v>
+        <v>68.13</v>
       </c>
       <c r="AI61" t="n">
-        <v>10.5535</v>
+        <v>10.5662</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>10.5535</v>
+        <v>10.5662</v>
       </c>
       <c r="AL61" t="n">
         <v>9.059100000000001</v>
@@ -11610,30 +11610,30 @@
         <v>11.97</v>
       </c>
       <c r="AP61" t="n">
-        <v>12.0307</v>
+        <v>12.0717</v>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.03</t>
+          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.07</t>
         </is>
       </c>
       <c r="AR61" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="AS61" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AT61" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="AU61" t="n">
-        <v>8.789999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="AV61" t="n">
-        <v>13.42</v>
+        <v>13.29</v>
       </c>
       <c r="AW61" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
@@ -11642,14 +11642,14 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.1))</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>60.31</v>
+        <v>60.77</v>
       </c>
       <c r="F62" t="n">
         <v>1.0421</v>
@@ -11702,10 +11702,10 @@
         <v>233984</v>
       </c>
       <c r="O62" t="n">
-        <v>1396945</v>
+        <v>157563</v>
       </c>
       <c r="P62" t="n">
-        <v>5.97</v>
+        <v>0.673</v>
       </c>
       <c r="Q62" t="n">
         <v>127057</v>
@@ -11723,10 +11723,10 @@
         <v>54.8</v>
       </c>
       <c r="V62" t="n">
-        <v>51.072</v>
+        <v>51.3452</v>
       </c>
       <c r="W62" t="n">
-        <v>45.7046</v>
+        <v>45.7928</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -11739,13 +11739,13 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>53.3687</v>
+        <v>54.0736</v>
       </c>
       <c r="AA62" t="n">
-        <v>51.0476</v>
+        <v>51.4289</v>
       </c>
       <c r="AB62" t="n">
-        <v>46.2478</v>
+        <v>46.3923</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="AE62" t="n">
-        <v>1.7467</v>
+        <v>2.1153</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.027</v>
+        <v>1.2447</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -11769,21 +11769,21 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>77.94</v>
+        <v>78.66</v>
       </c>
       <c r="AI62" t="n">
-        <v>55.5267</v>
+        <v>55.6912</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK62" t="n">
         <v>57.105</v>
       </c>
       <c r="AL62" t="n">
-        <v>50.5423</v>
+        <v>51.9149</v>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
@@ -11805,13 +11805,13 @@
         </is>
       </c>
       <c r="AR62" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.42</v>
+        <v>1.79</v>
       </c>
       <c r="AU62" t="n">
         <v>13.17</v>
@@ -11829,14 +11829,14 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 77.9))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.7); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.7))</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>8.01</v>
+        <v>7.95</v>
       </c>
       <c r="F63" t="n">
         <v>0.1576</v>
@@ -11889,10 +11889,10 @@
         <v>6699518</v>
       </c>
       <c r="O63" t="n">
-        <v>6777462</v>
+        <v>1310824</v>
       </c>
       <c r="P63" t="n">
-        <v>1.012</v>
+        <v>0.196</v>
       </c>
       <c r="Q63" t="n">
         <v>4765108</v>
@@ -11910,10 +11910,10 @@
         <v>8.51</v>
       </c>
       <c r="V63" t="n">
-        <v>7.4706</v>
+        <v>7.4866</v>
       </c>
       <c r="W63" t="n">
-        <v>5.5157</v>
+        <v>5.5355</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -11926,13 +11926,13 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7.9734</v>
+        <v>7.9711</v>
       </c>
       <c r="AA63" t="n">
-        <v>7.5033</v>
+        <v>7.5208</v>
       </c>
       <c r="AB63" t="n">
-        <v>5.983</v>
+        <v>6.0025</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="AE63" t="n">
-        <v>0.1819</v>
+        <v>0.1593</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.2491</v>
+        <v>0.2311</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -11956,18 +11956,18 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>55.42</v>
+        <v>53.02</v>
       </c>
       <c r="AI63" t="n">
-        <v>8.070399999999999</v>
+        <v>8.0924</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK63" t="n">
-        <v>7.6181</v>
+        <v>7.6533</v>
       </c>
       <c r="AL63" t="n">
         <v>7.4249</v>
@@ -11981,33 +11981,33 @@
         <v>8.395099999999999</v>
       </c>
       <c r="AO63" t="n">
-        <v>8.549899999999999</v>
+        <v>8.5367</v>
       </c>
       <c r="AP63" t="n">
         <v>8.58</v>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.4; TP2: Bollinger Upper Band at 8.55; TP3: Classic R1 at 8.58</t>
+          <t>TP1: Fibonacci R1 at 8.4; TP2: Bollinger Upper Band at 8.54; TP3: Classic R1 at 8.58</t>
         </is>
       </c>
       <c r="AR63" t="n">
-        <v>4.02</v>
+        <v>3.25</v>
       </c>
       <c r="AS63" t="n">
-        <v>4.82</v>
+        <v>3.87</v>
       </c>
       <c r="AT63" t="n">
-        <v>4.98</v>
+        <v>4.06</v>
       </c>
       <c r="AU63" t="n">
-        <v>10.2</v>
+        <v>9.69</v>
       </c>
       <c r="AV63" t="n">
-        <v>12.23</v>
+        <v>11.54</v>
       </c>
       <c r="AW63" t="n">
-        <v>12.63</v>
+        <v>12.11</v>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
@@ -12016,14 +12016,14 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 55.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 53.0))</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12042,7 +12042,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>23.77</v>
+        <v>26.1</v>
       </c>
       <c r="F64" t="n">
         <v>0.4497</v>
@@ -12076,10 +12076,10 @@
         <v>654460</v>
       </c>
       <c r="O64" t="n">
-        <v>3380916</v>
+        <v>3264586</v>
       </c>
       <c r="P64" t="n">
-        <v>5.166</v>
+        <v>4.988</v>
       </c>
       <c r="Q64" t="n">
         <v>636950</v>
@@ -12097,10 +12097,10 @@
         <v>23.48</v>
       </c>
       <c r="V64" t="n">
-        <v>22.3286</v>
+        <v>22.414</v>
       </c>
       <c r="W64" t="n">
-        <v>22.7154</v>
+        <v>22.7359</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -12113,13 +12113,13 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>22.9804</v>
+        <v>23.2775</v>
       </c>
       <c r="AA64" t="n">
-        <v>22.5674</v>
+        <v>22.7059</v>
       </c>
       <c r="AB64" t="n">
-        <v>22.0269</v>
+        <v>22.0674</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -12132,10 +12132,10 @@
         </is>
       </c>
       <c r="AE64" t="n">
-        <v>0.2722</v>
+        <v>0.488</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.2621</v>
+        <v>0.3073</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -12143,14 +12143,14 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>64.58</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="AI64" t="n">
-        <v>23.0853</v>
+        <v>23.3973</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr"/>
@@ -12188,7 +12188,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>40.45</v>
+        <v>41.21</v>
       </c>
       <c r="F65" t="n">
         <v>0.7763</v>
@@ -12241,10 +12241,10 @@
         <v>3823357</v>
       </c>
       <c r="O65" t="n">
-        <v>7758475</v>
+        <v>894921</v>
       </c>
       <c r="P65" t="n">
-        <v>2.029</v>
+        <v>0.234</v>
       </c>
       <c r="Q65" t="n">
         <v>1736564</v>
@@ -12262,10 +12262,10 @@
         <v>39.7</v>
       </c>
       <c r="V65" t="n">
-        <v>38.1516</v>
+        <v>38.3086</v>
       </c>
       <c r="W65" t="n">
-        <v>28.7923</v>
+        <v>28.8899</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -12278,13 +12278,13 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>39.3818</v>
+        <v>39.5559</v>
       </c>
       <c r="AA65" t="n">
-        <v>37.4914</v>
+        <v>37.6372</v>
       </c>
       <c r="AB65" t="n">
-        <v>30.3596</v>
+        <v>30.4676</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
@@ -12297,29 +12297,29 @@
         </is>
       </c>
       <c r="AE65" t="n">
-        <v>0.6254</v>
+        <v>0.699</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.6762</v>
+        <v>0.6807</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>60.11</v>
+        <v>64</v>
       </c>
       <c r="AI65" t="n">
-        <v>39.5215</v>
+        <v>39.6147</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:47</t>
+          <t>2026-08-04 08:00:50</t>
         </is>
       </c>
       <c r="AK65" t="n">
-        <v>39.5215</v>
+        <v>39.6147</v>
       </c>
       <c r="AL65" t="n">
         <v>38.4</v>
@@ -12330,36 +12330,36 @@
         </is>
       </c>
       <c r="AN65" t="n">
-        <v>40.5228</v>
+        <v>41.2639</v>
       </c>
       <c r="AO65" t="n">
-        <v>40.6986</v>
+        <v>42.4633</v>
       </c>
       <c r="AP65" t="n">
-        <v>40.8867</v>
+        <v>45.6033</v>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 40.52; TP2: Bollinger Upper Band at 40.7; TP3: Classic R1 at 40.89</t>
+          <t>TP1: Fibonacci R2 at 41.26; TP2: Classic R2 at 42.46; TP3: Classic R3 at 45.6</t>
         </is>
       </c>
       <c r="AR65" t="n">
-        <v>0.89</v>
+        <v>1.36</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.05</v>
+        <v>2.35</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.22</v>
+        <v>4.93</v>
       </c>
       <c r="AU65" t="n">
-        <v>2.53</v>
+        <v>4.16</v>
       </c>
       <c r="AV65" t="n">
-        <v>2.98</v>
+        <v>7.19</v>
       </c>
       <c r="AW65" t="n">
-        <v>3.45</v>
+        <v>15.12</v>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.0))</t>
         </is>
       </c>
     </row>
@@ -12480,34 +12480,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54094.3</v>
+        <v>54267</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.35</v>
+        <v>0.32</v>
       </c>
       <c r="F2" t="n">
-        <v>60.92</v>
+        <v>62.17</v>
       </c>
       <c r="G2" t="n">
-        <v>52400.17</v>
+        <v>52438.22</v>
       </c>
       <c r="H2" t="n">
-        <v>46776.62</v>
+        <v>46861.9</v>
       </c>
       <c r="I2" t="n">
-        <v>53173.79</v>
+        <v>53277.91</v>
       </c>
       <c r="J2" t="n">
-        <v>52372.09</v>
+        <v>52446.4</v>
       </c>
       <c r="K2" t="n">
-        <v>47139.4</v>
+        <v>47210.32</v>
       </c>
       <c r="L2" t="n">
-        <v>536.95</v>
+        <v>556.7</v>
       </c>
       <c r="M2" t="n">
-        <v>442.6</v>
+        <v>465.42</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:54</t>
+          <t>2026-08-04 08:01:05</t>
         </is>
       </c>
     </row>
@@ -12537,34 +12537,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19293.2</v>
+        <v>19515.3</v>
       </c>
       <c r="E3" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="F3" t="n">
-        <v>86.56</v>
+        <v>87.52</v>
       </c>
       <c r="G3" t="n">
-        <v>16089.25</v>
+        <v>16181.7</v>
       </c>
       <c r="H3" t="n">
-        <v>13560.15</v>
+        <v>13601.48</v>
       </c>
       <c r="I3" t="n">
-        <v>17561.89</v>
+        <v>17747.93</v>
       </c>
       <c r="J3" t="n">
-        <v>16340.18</v>
+        <v>16464.69</v>
       </c>
       <c r="K3" t="n">
-        <v>13785.01</v>
+        <v>13842.02</v>
       </c>
       <c r="L3" t="n">
-        <v>843.13</v>
+        <v>894.24</v>
       </c>
       <c r="M3" t="n">
-        <v>699.28</v>
+        <v>738.27</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-03 21:20:54</t>
+          <t>2026-08-04 08:01:05</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK2" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK3" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>164.2629</v>
+        <v>164.5542</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -4387,10 +4387,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>14.54</v>
+        <v>14.51</v>
       </c>
       <c r="M22" t="n">
-        <v>19.233</v>
+        <v>19.2731</v>
       </c>
       <c r="N22" t="n">
         <v>376421</v>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK22" t="n">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -5121,7 +5121,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>9737.712100000001</v>
+        <v>11635.3698</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="M26" t="n">
-        <v>1542.9572</v>
+        <v>1851.5972</v>
       </c>
       <c r="N26" t="n">
         <v>158467</v>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK26" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK28" t="n">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK30" t="n">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK31" t="n">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK32" t="n">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK33" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK34" t="n">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK35" t="n">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK36" t="n">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK37" t="n">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK38" t="n">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:29</t>
+          <t>2026-08-04 21:45:16</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK41" t="n">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK42" t="n">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK43" t="n">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK44" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK45" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK46" t="n">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK47" t="n">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK48" t="n">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK50" t="n">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK51" t="n">
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>322.7876</v>
+        <v>322.3061</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -9867,10 +9867,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>7.69</v>
+        <v>7.7</v>
       </c>
       <c r="M52" t="n">
-        <v>31.7432</v>
+        <v>31.6837</v>
       </c>
       <c r="N52" t="n">
         <v>93286</v>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK52" t="n">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK53" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK54" t="n">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK55" t="n">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK57" t="n">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK58" t="n">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK59" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK60" t="n">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK61" t="n">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK62" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK63" t="n">
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr"/>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:38</t>
+          <t>2026-08-04 21:45:23</t>
         </is>
       </c>
       <c r="AK65" t="n">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:44</t>
+          <t>2026-08-04 21:46:19</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:57:44</t>
+          <t>2026-08-04 21:46:19</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="F2" t="n">
         <v>0.1817</v>
@@ -742,10 +742,10 @@
         <v>7927426</v>
       </c>
       <c r="O2" t="n">
-        <v>8778734</v>
+        <v>2826496</v>
       </c>
       <c r="P2" t="n">
-        <v>1.107</v>
+        <v>0.357</v>
       </c>
       <c r="Q2" t="n">
         <v>3604221</v>
@@ -763,10 +763,10 @@
         <v>9.15</v>
       </c>
       <c r="V2" t="n">
-        <v>8.1868</v>
+        <v>8.1982</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6507</v>
+        <v>7.6586</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>8.5649</v>
+        <v>8.632</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.3094</v>
+        <v>8.347099999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.9132</v>
+        <v>7.9267</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>0.2966</v>
+        <v>0.3146</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1923</v>
+        <v>0.2168</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>66.22</v>
+        <v>67.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.6568</v>
+        <v>8.7134</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK2" t="n">
-        <v>8.6568</v>
+        <v>8.7134</v>
       </c>
       <c r="AL2" t="n">
-        <v>8.407500000000001</v>
+        <v>8.462</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
@@ -831,36 +831,36 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>9.347</v>
+        <v>9.3924</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.3924</v>
+        <v>9.416700000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.416700000000001</v>
+        <v>9.456300000000001</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.35; TP2: Fibonacci R2 at 9.39; TP3: Classic R1 at 9.42</t>
+          <t>TP1: Fibonacci R2 at 9.39; TP2: Classic R1 at 9.42; TP3: Bollinger Upper Band at 9.46</t>
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AS2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT2" t="n">
         <v>2.95</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AU2" t="n">
-        <v>7.97</v>
+        <v>7.79</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.5</v>
+        <v>8.07</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.2))</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>57.8</v>
+        <v>59.12</v>
       </c>
       <c r="F3" t="n">
         <v>1.1179</v>
@@ -929,10 +929,10 @@
         <v>714971</v>
       </c>
       <c r="O3" t="n">
-        <v>1235953</v>
+        <v>647423</v>
       </c>
       <c r="P3" t="n">
-        <v>1.729</v>
+        <v>0.906</v>
       </c>
       <c r="Q3" t="n">
         <v>158183</v>
@@ -950,10 +950,10 @@
         <v>56.7</v>
       </c>
       <c r="V3" t="n">
-        <v>56.1618</v>
+        <v>56.2546</v>
       </c>
       <c r="W3" t="n">
-        <v>51.5425</v>
+        <v>51.6416</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>56.2904</v>
+        <v>56.5599</v>
       </c>
       <c r="AA3" t="n">
-        <v>55.7251</v>
+        <v>55.8582</v>
       </c>
       <c r="AB3" t="n">
-        <v>50.0342</v>
+        <v>50.1246</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>0.2763</v>
+        <v>0.4672</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2058</v>
+        <v>0.2581</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>59.82</v>
+        <v>65.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>56.4575</v>
+        <v>56.6276</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>56.4575</v>
+        <v>56.7</v>
       </c>
       <c r="AL3" t="n">
-        <v>55.7608</v>
+        <v>55.77</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
@@ -1018,36 +1018,36 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>57.8789</v>
+        <v>60.5667</v>
       </c>
       <c r="AO3" t="n">
-        <v>57.9093</v>
+        <v>64.86669999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>58.3333</v>
+        <v>67.9864</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 57.88; TP2: Fibonacci R1 at 57.91; TP3: Classic R1 at 58.33</t>
+          <t>TP1: Classic R2 at 60.57; TP2: Classic R3 at 64.87; TP3: Extension at 67.99</t>
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>2.04</v>
+        <v>4.16</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.08</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.69</v>
+        <v>12.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.52</v>
+        <v>6.82</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.57</v>
+        <v>14.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.32</v>
+        <v>19.91</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1056,14 +1056,14 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.4))</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30.84</v>
+        <v>31.45</v>
       </c>
       <c r="F4" t="n">
         <v>0.5929</v>
@@ -1116,10 +1116,10 @@
         <v>1572061</v>
       </c>
       <c r="O4" t="n">
-        <v>6448232</v>
+        <v>2559479</v>
       </c>
       <c r="P4" t="n">
-        <v>4.102</v>
+        <v>1.628</v>
       </c>
       <c r="Q4" t="n">
         <v>1178522</v>
@@ -1137,10 +1137,10 @@
         <v>30.0571</v>
       </c>
       <c r="V4" t="n">
-        <v>28.0866</v>
+        <v>28.1556</v>
       </c>
       <c r="W4" t="n">
-        <v>26.9937</v>
+        <v>27.039</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>28.1281</v>
+        <v>28.4444</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.0753</v>
+        <v>28.2076</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.0252</v>
+        <v>26.0792</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>0.2325</v>
+        <v>0.4651</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.055</v>
+        <v>0.0491</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1183,18 +1183,18 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>72.97</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="AI4" t="n">
-        <v>28.6524</v>
+        <v>28.8065</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>28.91</v>
+        <v>29.37</v>
       </c>
       <c r="AL4" t="n">
         <v>27.49</v>
@@ -1208,33 +1208,33 @@
         <v>32.3233</v>
       </c>
       <c r="AO4" t="n">
-        <v>34.03</v>
+        <v>33.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>33.1289</v>
+        <v>33.0203</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 32.32; TP2: Extension at 34.03; TP3: Extension at 33.13</t>
+          <t>TP1: Classic R3 at 32.32; TP2: Extension at 33.8; TP3: Extension at 33.02</t>
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.61</v>
+        <v>2.36</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.97</v>
+        <v>1.94</v>
       </c>
       <c r="AU4" t="n">
-        <v>11.81</v>
+        <v>10.06</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.71</v>
+        <v>15.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.59</v>
+        <v>12.43</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
@@ -1243,14 +1243,14 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 73.0))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.5); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.5))</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23.9</v>
+        <v>24.04</v>
       </c>
       <c r="F5" t="n">
         <v>0.4889</v>
@@ -1303,10 +1303,10 @@
         <v>3278179</v>
       </c>
       <c r="O5" t="n">
-        <v>6355147</v>
+        <v>716453</v>
       </c>
       <c r="P5" t="n">
-        <v>1.939</v>
+        <v>0.219</v>
       </c>
       <c r="Q5" t="n">
         <v>1492003</v>
@@ -1324,10 +1324,10 @@
         <v>24</v>
       </c>
       <c r="V5" t="n">
-        <v>21.9854</v>
+        <v>22.0312</v>
       </c>
       <c r="W5" t="n">
-        <v>19.4649</v>
+        <v>19.5209</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>22.8355</v>
+        <v>22.9502</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.1162</v>
+        <v>22.1916</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.5798</v>
+        <v>19.6241</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.5315</v>
+        <v>0.5611</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4182</v>
+        <v>0.4468</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>61.36</v>
+        <v>62.3</v>
       </c>
       <c r="AI5" t="n">
-        <v>23.2694</v>
+        <v>23.3296</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>23.2694</v>
+        <v>23.3296</v>
       </c>
       <c r="AL5" t="n">
-        <v>22.203</v>
+        <v>22.3149</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>24.1107</v>
+        <v>24.2906</v>
       </c>
       <c r="AO5" t="n">
         <v>24.3367</v>
@@ -1402,26 +1402,26 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 24.11; TP2: Classic R1 at 24.34; TP3: Fibonacci R2 at 24.61</t>
+          <t>TP1: Bollinger Upper Band at 24.29; TP2: Classic R1 at 24.34; TP3: Fibonacci R2 at 24.61</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="AS5" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.62</v>
+        <v>4.12</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.59</v>
+        <v>4.32</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.74</v>
+        <v>5.47</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1430,14 +1430,14 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.3))</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298</v>
+        <v>297.99</v>
       </c>
       <c r="F6" t="n">
         <v>5.8745</v>
@@ -1490,10 +1490,10 @@
         <v>307071</v>
       </c>
       <c r="O6" t="n">
-        <v>135631</v>
+        <v>33140</v>
       </c>
       <c r="P6" t="n">
-        <v>0.442</v>
+        <v>0.108</v>
       </c>
       <c r="Q6" t="n">
         <v>54208</v>
@@ -1511,10 +1511,10 @@
         <v>302.7</v>
       </c>
       <c r="V6" t="n">
-        <v>303.3116</v>
+        <v>302.7714</v>
       </c>
       <c r="W6" t="n">
-        <v>259.7954</v>
+        <v>260.4558</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1527,13 +1527,13 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>298.1672</v>
+        <v>298.1504</v>
       </c>
       <c r="AA6" t="n">
-        <v>299.0532</v>
+        <v>299.0115</v>
       </c>
       <c r="AB6" t="n">
-        <v>263.2347</v>
+        <v>263.5805</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>-0.5857</v>
+        <v>-0.538</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1557,18 +1557,18 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>49.29</v>
+        <v>49.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>299.9881</v>
+        <v>300.2956</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>289.8876</v>
+        <v>290.01</v>
       </c>
       <c r="AL6" t="n">
         <v>285.9946</v>
@@ -1579,36 +1579,36 @@
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>301.6426</v>
+        <v>302.2503</v>
       </c>
       <c r="AO6" t="n">
-        <v>307.3034</v>
+        <v>307.2518</v>
       </c>
       <c r="AP6" t="n">
         <v>308.3187</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 301.64; TP2: Bollinger Upper Band at 307.3; TP3: Fibonacci R1 at 308.32</t>
+          <t>TP1: 100 SMA at 302.25; TP2: Bollinger Upper Band at 307.25; TP3: Fibonacci R1 at 308.32</t>
         </is>
       </c>
       <c r="AR6" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.73</v>
+        <v>4.56</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.01</v>
+        <v>5.95</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1617,14 +1617,14 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.3))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 49.3))</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="F7" t="n">
         <v>0.2669</v>
@@ -1677,10 +1677,10 @@
         <v>6431256</v>
       </c>
       <c r="O7" t="n">
-        <v>16122451</v>
+        <v>5090677</v>
       </c>
       <c r="P7" t="n">
-        <v>2.507</v>
+        <v>0.792</v>
       </c>
       <c r="Q7" t="n">
         <v>4437494</v>
@@ -1698,10 +1698,10 @@
         <v>13.5589</v>
       </c>
       <c r="V7" t="n">
-        <v>11.8774</v>
+        <v>11.9114</v>
       </c>
       <c r="W7" t="n">
-        <v>11.3334</v>
+        <v>11.3429</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1714,13 +1714,13 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>12.0915</v>
+        <v>12.2256</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.8182</v>
+        <v>11.8841</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.099</v>
+        <v>11.1229</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.3163</v>
+        <v>0.3868</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0956</v>
+        <v>0.1539</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1744,21 +1744,21 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>63.17</v>
+        <v>66.37</v>
       </c>
       <c r="AI7" t="n">
-        <v>12.9781</v>
+        <v>13.0362</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>12.9781</v>
+        <v>13.0362</v>
       </c>
       <c r="AL7" t="n">
-        <v>11.4851</v>
+        <v>11.7029</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
@@ -1766,36 +1766,36 @@
         </is>
       </c>
       <c r="AN7" t="n">
-        <v>13.3086</v>
+        <v>13.567</v>
       </c>
       <c r="AO7" t="n">
-        <v>13.4739</v>
+        <v>13.8324</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.3866</v>
+        <v>13.6923</v>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 13.31; TP2: Extension at 13.47; TP3: Extension at 13.39</t>
+          <t>TP1: Bollinger Upper Band at 13.57; TP2: Extension at 13.83; TP3: Extension at 13.69</t>
         </is>
       </c>
       <c r="AR7" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.55</v>
+        <v>4.07</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.82</v>
+        <v>6.11</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.15</v>
+        <v>5.03</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1804,42 +1804,42 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.4))</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JUFO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EGX30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JUFO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>EGX30</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="E8" t="n">
-        <v>33.55</v>
+        <v>27.38</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6727</v>
+        <v>0.5353</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2344</v>
+        <v>0.2355</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7302</v>
+        <v>0.7323</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28.7862</v>
+        <v>20.0922</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1855,40 +1855,40 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.48</v>
+        <v>14.39</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9359</v>
+        <v>1.8649</v>
       </c>
       <c r="N8" t="n">
-        <v>1306159</v>
+        <v>1319126</v>
       </c>
       <c r="O8" t="n">
-        <v>2095998</v>
+        <v>1283558</v>
       </c>
       <c r="P8" t="n">
-        <v>1.605</v>
+        <v>0.973</v>
       </c>
       <c r="Q8" t="n">
-        <v>698671</v>
+        <v>704810</v>
       </c>
       <c r="R8" t="n">
-        <v>6957237</v>
+        <v>1422285</v>
       </c>
       <c r="S8" t="n">
-        <v>9.958</v>
+        <v>2.018</v>
       </c>
       <c r="T8" t="n">
-        <v>29.1</v>
+        <v>26.51</v>
       </c>
       <c r="U8" t="n">
-        <v>31.85</v>
+        <v>27.6942</v>
       </c>
       <c r="V8" t="n">
-        <v>29.8892</v>
+        <v>29.878</v>
       </c>
       <c r="W8" t="n">
-        <v>27.1533</v>
+        <v>27.1715</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>30.2517</v>
+        <v>29.9782</v>
       </c>
       <c r="AA8" t="n">
-        <v>29.7563</v>
+        <v>29.6631</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.4888</v>
+        <v>27.4877</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.4151</v>
+        <v>0.1308</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.0226</v>
+        <v>0.0081</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1931,21 +1931,21 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>72.59999999999999</v>
+        <v>40</v>
       </c>
       <c r="AI8" t="n">
-        <v>31.2718</v>
+        <v>31.1235</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>32.24</v>
+        <v>26.8272</v>
       </c>
       <c r="AL8" t="n">
-        <v>29.1</v>
+        <v>26.51</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
@@ -1953,36 +1953,36 @@
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>36.4067</v>
+        <v>28.5576</v>
       </c>
       <c r="AO8" t="n">
-        <v>38.49</v>
+        <v>30.8533</v>
       </c>
       <c r="AP8" t="n">
-        <v>37.39</v>
+        <v>30.954</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 36.41; TP2: Extension at 38.49; TP3: Extension at 37.39</t>
+          <t>TP1: 100 SMA at 28.56; TP2: Classic R1 at 30.85; TP3: Fibonacci R1 at 30.95</t>
         </is>
       </c>
       <c r="AR8" t="n">
-        <v>1.33</v>
+        <v>5.46</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.99</v>
+        <v>12.69</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.64</v>
+        <v>13.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>12.92</v>
+        <v>6.45</v>
       </c>
       <c r="AV8" t="n">
-        <v>19.39</v>
+        <v>15.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>15.97</v>
+        <v>15.38</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -1991,14 +1991,14 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 72.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 40.0))</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F9" t="n">
         <v>3.6751</v>
@@ -2051,10 +2051,10 @@
         <v>186359</v>
       </c>
       <c r="O9" t="n">
-        <v>182653</v>
+        <v>186118</v>
       </c>
       <c r="P9" t="n">
-        <v>0.98</v>
+        <v>0.999</v>
       </c>
       <c r="Q9" t="n">
         <v>34745</v>
@@ -2072,10 +2072,10 @@
         <v>187.3056</v>
       </c>
       <c r="V9" t="n">
-        <v>182.3896</v>
+        <v>182.499</v>
       </c>
       <c r="W9" t="n">
-        <v>162.5648</v>
+        <v>163.1722</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>183.4514</v>
+        <v>184.5513</v>
       </c>
       <c r="AA9" t="n">
-        <v>182.6152</v>
+        <v>183.1009</v>
       </c>
       <c r="AB9" t="n">
-        <v>157.943</v>
+        <v>158.3118</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>1.6855</v>
+        <v>2.3853</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.3342</v>
+        <v>1.5444</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -2118,58 +2118,58 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>59.32</v>
+        <v>65.64</v>
       </c>
       <c r="AI9" t="n">
-        <v>184.8931</v>
+        <v>186.1949</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>184.8931</v>
+        <v>186.1949</v>
       </c>
       <c r="AL9" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>192.0267</v>
+        <v>195.0639</v>
       </c>
       <c r="AO9" t="n">
-        <v>193.2117</v>
+        <v>197.9267</v>
       </c>
       <c r="AP9" t="n">
-        <v>194.9533</v>
+        <v>207.4767</v>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 192.03; TP2: Bollinger Upper Band at 193.21; TP3: Classic R1 at 194.95</t>
+          <t>TP1: Bollinger Upper Band at 195.06; TP2: Fibonacci R2 at 197.93; TP3: Classic R2 at 207.48</t>
         </is>
       </c>
       <c r="AR9" t="n">
-        <v>0.65</v>
+        <v>1.08</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.76</v>
+        <v>1.43</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.92</v>
+        <v>2.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.86</v>
+        <v>4.76</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.44</v>
+        <v>11.43</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2178,14 +2178,14 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.6))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>724.89</v>
+        <v>726.99</v>
       </c>
       <c r="F10" t="n">
         <v>1.4183</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>158562</v>
+        <v>98206</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>725.021</v>
+        <v>725.2812</v>
       </c>
       <c r="W10" t="n">
-        <v>547.1147999999999</v>
+        <v>548.5497</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2261,13 +2261,13 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>710.582</v>
+        <v>712.1446</v>
       </c>
       <c r="AA10" t="n">
-        <v>698.3566</v>
+        <v>699.4795</v>
       </c>
       <c r="AB10" t="n">
-        <v>569.3873</v>
+        <v>570.9554000000001</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>-0.9738</v>
+        <v>0.4693</v>
       </c>
       <c r="AF10" t="n">
-        <v>-2.0808</v>
+        <v>-1.5708</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2291,18 +2291,18 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>55.8</v>
+        <v>56.54</v>
       </c>
       <c r="AI10" t="n">
-        <v>702.3425</v>
+        <v>705.2807</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>706.5</v>
+        <v>725.2812</v>
       </c>
       <c r="AL10" t="n">
         <v>688.154</v>
@@ -2316,33 +2316,33 @@
         <v>728.646</v>
       </c>
       <c r="AO10" t="n">
-        <v>729.5998</v>
+        <v>731.424</v>
       </c>
       <c r="AP10" t="n">
         <v>736.8</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 728.65; TP2: Bollinger Upper Band at 729.6; TP3: Classic R1 at 736.8</t>
+          <t>TP1: Fibonacci R1 at 728.65; TP2: Bollinger Upper Band at 731.42; TP3: Classic R1 at 736.8</t>
         </is>
       </c>
       <c r="AR10" t="n">
-        <v>1.21</v>
+        <v>0.09</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.26</v>
+        <v>0.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.65</v>
+        <v>0.31</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.13</v>
+        <v>0.46</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.27</v>
+        <v>0.85</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.29</v>
+        <v>1.59</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2351,14 +2351,14 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 56.5))</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.35</v>
+        <v>26.31</v>
       </c>
       <c r="F11" t="n">
         <v>0.4821</v>
@@ -2411,10 +2411,10 @@
         <v>1234952</v>
       </c>
       <c r="O11" t="n">
-        <v>16628714</v>
+        <v>1966331</v>
       </c>
       <c r="P11" t="n">
-        <v>13.465</v>
+        <v>1.592</v>
       </c>
       <c r="Q11" t="n">
         <v>667589</v>
@@ -2432,10 +2432,10 @@
         <v>24.3</v>
       </c>
       <c r="V11" t="n">
-        <v>23.0278</v>
+        <v>23.113</v>
       </c>
       <c r="W11" t="n">
-        <v>22.984</v>
+        <v>23.0041</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2448,13 +2448,13 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>23.3631</v>
+        <v>23.6438</v>
       </c>
       <c r="AA11" t="n">
-        <v>23.1055</v>
+        <v>23.2311</v>
       </c>
       <c r="AB11" t="n">
-        <v>22.9555</v>
+        <v>22.9889</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.357</v>
+        <v>0.5447</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0927</v>
+        <v>0.1831</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>80.33</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>24.3913</v>
+        <v>24.4969</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>24.3913</v>
+        <v>24.4969</v>
       </c>
       <c r="AL11" t="n">
-        <v>22.984</v>
+        <v>23.0041</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
@@ -2516,14 +2516,14 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (80.3); entry: enhanced entry at VWMA (overbought (RSI: 80.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.7); entry: enhanced entry at VWMA (overbought (RSI: 79.7))</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15.45</v>
+        <v>15.35</v>
       </c>
       <c r="F12" t="n">
         <v>0.305</v>
@@ -2576,10 +2576,10 @@
         <v>17305394</v>
       </c>
       <c r="O12" t="n">
-        <v>25040518</v>
+        <v>1942814</v>
       </c>
       <c r="P12" t="n">
-        <v>1.447</v>
+        <v>0.112</v>
       </c>
       <c r="Q12" t="n">
         <v>7334695</v>
@@ -2597,10 +2597,10 @@
         <v>15.38</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9516</v>
+        <v>14.9848</v>
       </c>
       <c r="W12" t="n">
-        <v>10.4888</v>
+        <v>10.5286</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>14.8833</v>
+        <v>14.9277</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.3838</v>
+        <v>14.4216</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.3267</v>
+        <v>11.3668</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>0.0751</v>
+        <v>0.1039</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0321</v>
+        <v>0.0465</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2643,18 +2643,18 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>61.91</v>
+        <v>59.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>14.9373</v>
+        <v>14.9449</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>15.015</v>
+        <v>15.025</v>
       </c>
       <c r="AL12" t="n">
         <v>14.58</v>
@@ -2665,36 +2665,36 @@
         </is>
       </c>
       <c r="AN12" t="n">
+        <v>15.3884</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>15.4289</v>
+      </c>
+      <c r="AP12" t="n">
         <v>15.7933</v>
       </c>
-      <c r="AO12" t="n">
-        <v>16.8533</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>17.5555</v>
-      </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 15.79; TP2: Classic R3 at 16.85; TP3: Extension at 17.56</t>
+          <t>TP1: Fibonacci R2 at 15.39; TP2: Bollinger Upper Band at 15.43; TP3: Classic R2 at 15.79</t>
         </is>
       </c>
       <c r="AR12" t="n">
-        <v>1.79</v>
+        <v>0.82</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.23</v>
+        <v>0.91</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.84</v>
+        <v>1.73</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.18</v>
+        <v>2.42</v>
       </c>
       <c r="AV12" t="n">
-        <v>12.24</v>
+        <v>2.69</v>
       </c>
       <c r="AW12" t="n">
-        <v>16.92</v>
+        <v>5.11</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2703,14 +2703,14 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.9))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 59.6))</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>109.94</v>
       </c>
       <c r="F13" t="n">
         <v>2.1583</v>
@@ -2763,10 +2763,10 @@
         <v>1026172</v>
       </c>
       <c r="O13" t="n">
-        <v>1720667</v>
+        <v>242667</v>
       </c>
       <c r="P13" t="n">
-        <v>1.677</v>
+        <v>0.236</v>
       </c>
       <c r="Q13" t="n">
         <v>350878</v>
@@ -2784,10 +2784,10 @@
         <v>111.2082</v>
       </c>
       <c r="V13" t="n">
-        <v>97.5998</v>
+        <v>97.8836</v>
       </c>
       <c r="W13" t="n">
-        <v>80.7047</v>
+        <v>81.0153</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2800,13 +2800,13 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>103.5268</v>
+        <v>104.1376</v>
       </c>
       <c r="AA13" t="n">
-        <v>98.8793</v>
+        <v>99.31310000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>82.3031</v>
+        <v>82.57810000000001</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>3.6804</v>
+        <v>3.7296</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.9504</v>
+        <v>3.1062</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2830,18 +2830,18 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>66.09</v>
+        <v>63.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>104.1966</v>
+        <v>104.5403</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>105.4032</v>
+        <v>106.9179</v>
       </c>
       <c r="AL13" t="n">
         <v>95.1023</v>
@@ -2852,36 +2852,36 @@
         </is>
       </c>
       <c r="AN13" t="n">
+        <v>110.3933</v>
+      </c>
+      <c r="AO13" t="n">
         <v>111.0823</v>
       </c>
-      <c r="AO13" t="n">
-        <v>112.0985</v>
-      </c>
       <c r="AP13" t="n">
-        <v>117.1867</v>
+        <v>112.8803</v>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 111.08; TP2: Bollinger Upper Band at 112.1; TP3: Classic R2 at 117.19</t>
+          <t>TP1: Classic R1 at 110.39; TP2: Fibonacci R2 at 111.08; TP3: Bollinger Upper Band at 112.88</t>
         </is>
       </c>
       <c r="AR13" t="n">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.14</v>
+        <v>0.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.39</v>
+        <v>3.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.35</v>
+        <v>3.89</v>
       </c>
       <c r="AW13" t="n">
-        <v>11.18</v>
+        <v>5.58</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2890,14 +2890,14 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 66.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 63.7))</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.77</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>0.1158</v>
@@ -2950,10 +2950,10 @@
         <v>12761648</v>
       </c>
       <c r="O14" t="n">
-        <v>18333608</v>
+        <v>6388346</v>
       </c>
       <c r="P14" t="n">
-        <v>1.437</v>
+        <v>0.501</v>
       </c>
       <c r="Q14" t="n">
         <v>7428682</v>
@@ -2969,10 +2969,10 @@
         <v>5.15</v>
       </c>
       <c r="V14" t="n">
-        <v>5.1286</v>
+        <v>5.146</v>
       </c>
       <c r="W14" t="n">
-        <v>4.0888</v>
+        <v>4.1025</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>5.3396</v>
+        <v>5.4025</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.1049</v>
+        <v>5.14</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.3159</v>
+        <v>4.3327</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>0.2056</v>
+        <v>0.2318</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1133</v>
+        <v>0.137</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -3015,21 +3015,21 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>63.9</v>
+        <v>67.97</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.6911</v>
+        <v>5.7088</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>5.705</v>
+        <v>5.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.4018</v>
+        <v>5.5696</v>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
@@ -3037,36 +3037,36 @@
         </is>
       </c>
       <c r="AN14" t="n">
-        <v>5.934</v>
+        <v>6.0529</v>
       </c>
       <c r="AO14" t="n">
         <v>6.06</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.1956</v>
+        <v>6.1784</v>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 5.93; TP2: Classic R3 at 6.06; TP3: Extension at 6.2</t>
+          <t>TP1: Bollinger Upper Band at 6.05; TP2: Classic R3 at 6.06; TP3: Extension at 6.18</t>
         </is>
       </c>
       <c r="AR14" t="n">
-        <v>0.76</v>
+        <v>1.68</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.17</v>
+        <v>1.72</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.01</v>
+        <v>5.27</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.22</v>
+        <v>5.39</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.6</v>
+        <v>7.45</v>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
@@ -3075,14 +3075,14 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 63.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 68.0))</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="F15" t="n">
         <v>0.1112</v>
@@ -3129,10 +3129,10 @@
         <v>24463738</v>
       </c>
       <c r="O15" t="n">
-        <v>25605373</v>
+        <v>4367703</v>
       </c>
       <c r="P15" t="n">
-        <v>1.047</v>
+        <v>0.179</v>
       </c>
       <c r="Q15" t="n">
         <v>15177383</v>
@@ -3150,10 +3150,10 @@
         <v>4.65</v>
       </c>
       <c r="V15" t="n">
-        <v>3.2296</v>
+        <v>3.2984</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2721</v>
+        <v>2.2967</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -3166,13 +3166,13 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>4.3496</v>
+        <v>4.5163</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.502</v>
+        <v>3.6038</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.4322</v>
+        <v>2.4687</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>0.6947</v>
+        <v>0.7471</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.5438</v>
+        <v>0.5844</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -3196,18 +3196,18 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>88.20999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.9244</v>
+        <v>4.0357</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>4.696</v>
+        <v>5.0068</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3218,36 +3218,36 @@
         </is>
       </c>
       <c r="AN15" t="n">
+        <v>6.114</v>
+      </c>
+      <c r="AO15" t="n">
         <v>6.3</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="AP15" t="n">
-        <v>10.2295</v>
-      </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 6.3; TP2: Classic R3 at 8.7; TP3: Extension at 10.23</t>
+          <t>TP1: Bollinger Upper Band at 6.11; TP2: Classic R2 at 6.3; TP3: Classic R3 at 8.7</t>
         </is>
       </c>
       <c r="AR15" t="n">
-        <v>0.95</v>
+        <v>0.55</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.36</v>
+        <v>0.64</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.26</v>
+        <v>1.84</v>
       </c>
       <c r="AU15" t="n">
-        <v>34.16</v>
+        <v>22.11</v>
       </c>
       <c r="AV15" t="n">
-        <v>85.26000000000001</v>
+        <v>25.83</v>
       </c>
       <c r="AW15" t="n">
-        <v>117.83</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
@@ -3256,14 +3256,14 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (88.2); entry: enhanced entry at Parabolic SAR (overbought (RSI: 88.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (88.3); entry: enhanced entry at Parabolic SAR (overbought (RSI: 88.3))</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.24</v>
+        <v>0.245</v>
       </c>
       <c r="F16" t="n">
         <v>0.0047</v>
@@ -3312,10 +3312,10 @@
         <v>268446250</v>
       </c>
       <c r="O16" t="n">
-        <v>331897800</v>
+        <v>101807266</v>
       </c>
       <c r="P16" t="n">
-        <v>1.236</v>
+        <v>0.379</v>
       </c>
       <c r="Q16" t="n">
         <v>143523770</v>
@@ -3333,10 +3333,10 @@
         <v>0.256</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2222</v>
+        <v>0.223</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1812</v>
+        <v>0.1817</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3349,13 +3349,13 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0.2377</v>
+        <v>0.2384</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2253</v>
+        <v>0.226</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1936</v>
+        <v>0.1941</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>0.0051</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.007</v>
+        <v>0.0066</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -3379,18 +3379,18 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>54.45</v>
+        <v>58.01</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.2435</v>
+        <v>0.2444</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>0.235</v>
+        <v>0.2444</v>
       </c>
       <c r="AL16" t="n">
         <v>0.232</v>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>0.2579</v>
+        <v>0.2569</v>
       </c>
       <c r="AO16" t="n">
         <v>0.267</v>
@@ -3415,22 +3415,22 @@
         </is>
       </c>
       <c r="AR16" t="n">
-        <v>7.63</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.67</v>
+        <v>1.82</v>
       </c>
       <c r="AT16" t="n">
-        <v>20.33</v>
+        <v>4.15</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.74</v>
+        <v>5.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.62</v>
+        <v>9.24</v>
       </c>
       <c r="AW16" t="n">
-        <v>25.96</v>
+        <v>21.1</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.0))</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3497,10 +3497,10 @@
         <v>29610845</v>
       </c>
       <c r="O17" t="n">
-        <v>8384444</v>
+        <v>4145849</v>
       </c>
       <c r="P17" t="n">
-        <v>0.283</v>
+        <v>0.14</v>
       </c>
       <c r="Q17" t="n">
         <v>11106403</v>
@@ -3518,10 +3518,10 @@
         <v>1.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6134</v>
+        <v>1.6164</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4728</v>
+        <v>1.4738</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3534,13 +3534,13 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1.6658</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.6139</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5121</v>
+        <v>1.5141</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>0.0267</v>
+        <v>0.0271</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0294</v>
+        <v>0.029</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -3567,18 +3567,18 @@
         <v>58.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.6768</v>
+        <v>1.6804</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>1.6768</v>
+        <v>1.6804</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.604</v>
+        <v>1.62</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -3600,22 +3600,22 @@
         </is>
       </c>
       <c r="AR17" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.73</v>
+        <v>2.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.96</v>
+        <v>4.74</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.52</v>
+        <v>7.3</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38.14</v>
+        <v>38</v>
       </c>
       <c r="F18" t="n">
         <v>0.7586000000000001</v>
@@ -3684,10 +3684,10 @@
         <v>1324809</v>
       </c>
       <c r="O18" t="n">
-        <v>840898</v>
+        <v>794042</v>
       </c>
       <c r="P18" t="n">
-        <v>0.635</v>
+        <v>0.599</v>
       </c>
       <c r="Q18" t="n">
         <v>449219</v>
@@ -3705,10 +3705,10 @@
         <v>38.59</v>
       </c>
       <c r="V18" t="n">
-        <v>37.87</v>
+        <v>37.9002</v>
       </c>
       <c r="W18" t="n">
-        <v>31.0407</v>
+        <v>31.1138</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3721,13 +3721,13 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>38.2337</v>
+        <v>38.2115</v>
       </c>
       <c r="AA18" t="n">
-        <v>37.5286</v>
+        <v>37.5471</v>
       </c>
       <c r="AB18" t="n">
-        <v>31.6082</v>
+        <v>31.6718</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0634</v>
+        <v>-0.0689</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1231</v>
+        <v>0.0847</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3751,21 +3751,21 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>49.72</v>
+        <v>48.66</v>
       </c>
       <c r="AI18" t="n">
-        <v>38.6808</v>
+        <v>38.5745</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK18" t="n">
         <v>36.6681</v>
       </c>
       <c r="AL18" t="n">
-        <v>36.5</v>
+        <v>36.558</v>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>40.1845</v>
+        <v>40.0836</v>
       </c>
       <c r="AO18" t="n">
         <v>40.4652</v>
@@ -3783,20 +3783,20 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 40.18; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
+          <t>TP1: Bollinger Upper Band at 40.08; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
         </is>
       </c>
       <c r="AR18" t="n">
-        <v>20.92</v>
+        <v>31.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>22.58</v>
+        <v>34.48</v>
       </c>
       <c r="AT18" t="n">
-        <v>23.58</v>
+        <v>36.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.59</v>
+        <v>9.31</v>
       </c>
       <c r="AV18" t="n">
         <v>10.36</v>
@@ -3811,14 +3811,14 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 49.7))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 48.7))</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35.6</v>
+        <v>35.21</v>
       </c>
       <c r="F19" t="n">
         <v>0.736</v>
@@ -3867,10 +3867,10 @@
         <v>1236570</v>
       </c>
       <c r="O19" t="n">
-        <v>661263</v>
+        <v>46886</v>
       </c>
       <c r="P19" t="n">
-        <v>0.535</v>
+        <v>0.038</v>
       </c>
       <c r="Q19" t="n">
         <v>695409</v>
@@ -3888,10 +3888,10 @@
         <v>38.25</v>
       </c>
       <c r="V19" t="n">
-        <v>30.5494</v>
+        <v>30.7936</v>
       </c>
       <c r="W19" t="n">
-        <v>19.72</v>
+        <v>19.823</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3904,13 +3904,13 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>35.1555</v>
+        <v>35.1607</v>
       </c>
       <c r="AA19" t="n">
-        <v>31.2296</v>
+        <v>31.3856</v>
       </c>
       <c r="AB19" t="n">
-        <v>21.7661</v>
+        <v>21.8999</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>1.4716</v>
+        <v>1.3095</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8928</v>
+        <v>1.7761</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3934,58 +3934,58 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>55.14</v>
+        <v>53.53</v>
       </c>
       <c r="AI19" t="n">
-        <v>36.2181</v>
+        <v>36.2251</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>34.23</v>
+        <v>34.425</v>
       </c>
       <c r="AL19" t="n">
-        <v>34.0796</v>
+        <v>34.0281</v>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN19" t="n">
         <v>37.3616</v>
       </c>
       <c r="AO19" t="n">
-        <v>37.7974</v>
+        <v>37.7777</v>
       </c>
       <c r="AP19" t="n">
         <v>38.2267</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.8; TP3: Classic R1 at 38.23</t>
+          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.78; TP3: Classic R1 at 38.23</t>
         </is>
       </c>
       <c r="AR19" t="n">
-        <v>20.83</v>
+        <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>23.72</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AT19" t="n">
-        <v>26.58</v>
+        <v>9.58</v>
       </c>
       <c r="AU19" t="n">
-        <v>9.15</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>10.42</v>
+        <v>9.74</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.68</v>
+        <v>11.04</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
@@ -3994,14 +3994,14 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.5))</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.5</v>
+        <v>10.46</v>
       </c>
       <c r="F20" t="n">
         <v>0.2104</v>
@@ -4050,10 +4050,10 @@
         <v>4421118</v>
       </c>
       <c r="O20" t="n">
-        <v>1155165</v>
+        <v>303627</v>
       </c>
       <c r="P20" t="n">
-        <v>0.261</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="Q20" t="n">
         <v>2368573</v>
@@ -4071,10 +4071,10 @@
         <v>10.6802</v>
       </c>
       <c r="V20" t="n">
-        <v>10.0664</v>
+        <v>10.119</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9666</v>
+        <v>7.9855</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>10.6325</v>
+        <v>10.616</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.0653</v>
+        <v>10.0808</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.2898</v>
+        <v>8.311400000000001</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>0.1025</v>
+        <v>0.0794</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.2037</v>
+        <v>0.1788</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -4117,14 +4117,14 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>48.88</v>
+        <v>47.67</v>
       </c>
       <c r="AI20" t="n">
-        <v>10.7886</v>
+        <v>10.7935</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4142,21 +4142,21 @@
         <v>11.0391</v>
       </c>
       <c r="AO20" t="n">
-        <v>11.0555</v>
+        <v>11.0727</v>
       </c>
       <c r="AP20" t="n">
         <v>11.15</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.06; TP3: Classic R1 at 11.15</t>
+          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.07; TP3: Classic R1 at 11.15</t>
         </is>
       </c>
       <c r="AR20" t="n">
         <v>6.47</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.62</v>
+        <v>6.78</v>
       </c>
       <c r="AT20" t="n">
         <v>7.47</v>
@@ -4165,7 +4165,7 @@
         <v>6.96</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.12</v>
+        <v>7.28</v>
       </c>
       <c r="AW20" t="n">
         <v>8.029999999999999</v>
@@ -4177,14 +4177,14 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 48.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 47.7))</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32.18</v>
+        <v>32.28</v>
       </c>
       <c r="F21" t="n">
         <v>0.643</v>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>20.67</v>
+        <v>20.73</v>
       </c>
       <c r="M21" t="n">
         <v>1.557</v>
@@ -4237,10 +4237,10 @@
         <v>697713</v>
       </c>
       <c r="O21" t="n">
-        <v>579082</v>
+        <v>73575</v>
       </c>
       <c r="P21" t="n">
-        <v>0.83</v>
+        <v>0.105</v>
       </c>
       <c r="Q21" t="n">
         <v>252419</v>
@@ -4258,10 +4258,10 @@
         <v>36.7</v>
       </c>
       <c r="V21" t="n">
-        <v>34.9394</v>
+        <v>34.8562</v>
       </c>
       <c r="W21" t="n">
-        <v>32.6361</v>
+        <v>32.7125</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>34.0225</v>
+        <v>33.8566</v>
       </c>
       <c r="AA21" t="n">
-        <v>34.9351</v>
+        <v>34.831</v>
       </c>
       <c r="AB21" t="n">
-        <v>31.4488</v>
+        <v>31.4571</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>-0.8833</v>
+        <v>-0.9089</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.5196</v>
+        <v>-0.5974</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>35.58</v>
+        <v>36.43</v>
       </c>
       <c r="AI21" t="n">
-        <v>34.6023</v>
+        <v>34.5615</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK21" t="n">
         <v>31.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>31.4818</v>
+        <v>31.1817</v>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
@@ -4326,33 +4326,33 @@
         </is>
       </c>
       <c r="AN21" t="n">
-        <v>32.6361</v>
+        <v>32.7125</v>
       </c>
       <c r="AO21" t="n">
-        <v>35.9103</v>
+        <v>35.9181</v>
       </c>
       <c r="AP21" t="n">
         <v>37.0467</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 32.64; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
+          <t>TP1: 200 SMA at 32.71; TP2: 100 SMA at 35.92; TP3: Classic R1 at 37.05</t>
         </is>
       </c>
       <c r="AR21" t="n">
-        <v>62.41</v>
+        <v>3.81</v>
       </c>
       <c r="AS21" t="n">
-        <v>242.28</v>
+        <v>13.88</v>
       </c>
       <c r="AT21" t="n">
-        <v>304.71</v>
+        <v>17.43</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>14.03</v>
       </c>
       <c r="AW21" t="n">
         <v>17.61</v>
@@ -4364,14 +4364,14 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 35.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 36.4))</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>271</v>
+        <v>279.01</v>
       </c>
       <c r="F22" t="n">
         <v>5.2501</v>
@@ -4424,10 +4424,10 @@
         <v>380781</v>
       </c>
       <c r="O22" t="n">
-        <v>588206</v>
+        <v>180627</v>
       </c>
       <c r="P22" t="n">
-        <v>1.545</v>
+        <v>0.474</v>
       </c>
       <c r="Q22" t="n">
         <v>351080</v>
@@ -4445,10 +4445,10 @@
         <v>242</v>
       </c>
       <c r="V22" t="n">
-        <v>186.0786</v>
+        <v>188.4168</v>
       </c>
       <c r="W22" t="n">
-        <v>127.1677</v>
+        <v>128.0769</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -4461,13 +4461,13 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>224.833</v>
+        <v>229.9927</v>
       </c>
       <c r="AA22" t="n">
-        <v>193.0695</v>
+        <v>196.4397</v>
       </c>
       <c r="AB22" t="n">
-        <v>133.2963</v>
+        <v>134.7462</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>23.1416</v>
+        <v>24.5754</v>
       </c>
       <c r="AF22" t="n">
-        <v>18.7341</v>
+        <v>19.9024</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>74.70999999999999</v>
+        <v>76.39</v>
       </c>
       <c r="AI22" t="n">
-        <v>224.3978</v>
+        <v>227.267</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>224.3978</v>
+        <v>227.267</v>
       </c>
       <c r="AL22" t="n">
-        <v>213.5955</v>
+        <v>216.6517</v>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
@@ -4513,36 +4513,36 @@
         </is>
       </c>
       <c r="AN22" t="n">
-        <v>281.1615</v>
+        <v>287.98</v>
       </c>
       <c r="AO22" t="n">
-        <v>287.98</v>
+        <v>288.3643</v>
       </c>
       <c r="AP22" t="n">
         <v>365.95</v>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 281.16; TP2: Classic R2 at 287.98; TP3: Classic R3 at 365.95</t>
+          <t>TP1: Classic R2 at 287.98; TP2: Bollinger Upper Band at 288.36; TP3: Classic R3 at 365.95</t>
         </is>
       </c>
       <c r="AR22" t="n">
-        <v>5.25</v>
+        <v>5.72</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.89</v>
+        <v>5.76</v>
       </c>
       <c r="AT22" t="n">
-        <v>13.1</v>
+        <v>13.06</v>
       </c>
       <c r="AU22" t="n">
-        <v>25.3</v>
+        <v>26.71</v>
       </c>
       <c r="AV22" t="n">
-        <v>28.33</v>
+        <v>26.88</v>
       </c>
       <c r="AW22" t="n">
-        <v>63.08</v>
+        <v>61.02</v>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
@@ -4551,14 +4551,14 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.7); entry: enhanced entry at VWMA (overbought (RSI: 74.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.4); entry: enhanced entry at VWMA (overbought (RSI: 76.4))</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105.2</v>
+        <v>110.5</v>
       </c>
       <c r="F23" t="n">
         <v>2.1763</v>
@@ -4611,10 +4611,10 @@
         <v>296891</v>
       </c>
       <c r="O23" t="n">
-        <v>953125</v>
+        <v>957133</v>
       </c>
       <c r="P23" t="n">
-        <v>3.21</v>
+        <v>3.224</v>
       </c>
       <c r="Q23" t="n">
         <v>153703</v>
@@ -4632,10 +4632,10 @@
         <v>97.5</v>
       </c>
       <c r="V23" t="n">
-        <v>90.04300000000001</v>
+        <v>90.4828</v>
       </c>
       <c r="W23" t="n">
-        <v>81.8498</v>
+        <v>82.0264</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>95.11360000000001</v>
+        <v>96.57899999999999</v>
       </c>
       <c r="AA23" t="n">
-        <v>90.9552</v>
+        <v>91.7217</v>
       </c>
       <c r="AB23" t="n">
-        <v>83.6336</v>
+        <v>83.90089999999999</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>3.5846</v>
+        <v>4.3559</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.3455</v>
+        <v>2.7476</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -4678,18 +4678,18 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>71.5</v>
+        <v>76.23999999999999</v>
       </c>
       <c r="AI23" t="n">
-        <v>100.6007</v>
+        <v>101.6855</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>100.6007</v>
+        <v>101.6855</v>
       </c>
       <c r="AL23" t="n">
         <v>95.48</v>
@@ -4703,33 +4703,33 @@
         <v>115.15</v>
       </c>
       <c r="AO23" t="n">
-        <v>122.4246</v>
+        <v>121.8822</v>
       </c>
       <c r="AP23" t="n">
-        <v>118.5836</v>
+        <v>118.3276</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 115.15; TP2: Extension at 122.42; TP3: Extension at 118.58</t>
+          <t>TP1: Classic R3 at 115.15; TP2: Extension at 121.88; TP3: Extension at 118.33</t>
         </is>
       </c>
       <c r="AR23" t="n">
-        <v>2.84</v>
+        <v>2.17</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.26</v>
+        <v>3.25</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.51</v>
+        <v>2.68</v>
       </c>
       <c r="AU23" t="n">
-        <v>14.46</v>
+        <v>13.24</v>
       </c>
       <c r="AV23" t="n">
-        <v>21.69</v>
+        <v>19.86</v>
       </c>
       <c r="AW23" t="n">
-        <v>17.88</v>
+        <v>16.37</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
@@ -4738,14 +4738,14 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.5); entry: enhanced entry at VWMA (overbought (RSI: 71.5))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.2); entry: enhanced entry at VWMA (overbought (RSI: 76.2))</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>47.01</v>
+        <v>46.4</v>
       </c>
       <c r="F24" t="n">
         <v>0.9239000000000001</v>
@@ -4798,10 +4798,10 @@
         <v>407584</v>
       </c>
       <c r="O24" t="n">
-        <v>865047</v>
+        <v>91352</v>
       </c>
       <c r="P24" t="n">
-        <v>2.122</v>
+        <v>0.224</v>
       </c>
       <c r="Q24" t="n">
         <v>318103</v>
@@ -4819,10 +4819,10 @@
         <v>44.89</v>
       </c>
       <c r="V24" t="n">
-        <v>38.0846</v>
+        <v>38.3436</v>
       </c>
       <c r="W24" t="n">
-        <v>35.0566</v>
+        <v>35.1446</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4835,13 +4835,13 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>42.1862</v>
+        <v>42.5875</v>
       </c>
       <c r="AA24" t="n">
-        <v>39.2349</v>
+        <v>39.5159</v>
       </c>
       <c r="AB24" t="n">
-        <v>34.3995</v>
+        <v>34.5189</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>1.8839</v>
+        <v>1.9898</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.6722</v>
+        <v>1.7357</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -4865,21 +4865,21 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>73.03</v>
+        <v>69.59</v>
       </c>
       <c r="AI24" t="n">
-        <v>42.6194</v>
+        <v>42.8382</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>42.6194</v>
+        <v>42.8382</v>
       </c>
       <c r="AL24" t="n">
-        <v>40.2358</v>
+        <v>40.5284</v>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
@@ -4887,52 +4887,52 @@
         </is>
       </c>
       <c r="AN24" t="n">
+        <v>46.4812</v>
+      </c>
+      <c r="AO24" t="n">
         <v>49.4033</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>57.9833</v>
       </c>
-      <c r="AP24" t="n">
-        <v>63.8523</v>
-      </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 49.4; TP2: Classic R3 at 57.98; TP3: Extension at 63.85</t>
+          <t>TP1: Bollinger Upper Band at 46.48; TP2: Classic R2 at 49.4; TP3: Classic R3 at 57.98</t>
         </is>
       </c>
       <c r="AR24" t="n">
-        <v>2.85</v>
+        <v>1.58</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.45</v>
+        <v>2.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.91</v>
+        <v>6.56</v>
       </c>
       <c r="AU24" t="n">
-        <v>15.92</v>
+        <v>8.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>36.05</v>
+        <v>15.33</v>
       </c>
       <c r="AW24" t="n">
-        <v>49.82</v>
+        <v>35.35</v>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.0); entry: enhanced entry at VWMA (overbought (RSI: 73.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.6))</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.7</v>
+        <v>12.79</v>
       </c>
       <c r="F25" t="n">
         <v>0.2655</v>
@@ -4979,10 +4979,10 @@
         <v>2960210</v>
       </c>
       <c r="O25" t="n">
-        <v>1872907</v>
+        <v>126303</v>
       </c>
       <c r="P25" t="n">
-        <v>0.633</v>
+        <v>0.043</v>
       </c>
       <c r="Q25" t="n">
         <v>1437388</v>
@@ -5000,10 +5000,10 @@
         <v>12.3</v>
       </c>
       <c r="V25" t="n">
-        <v>10.7882</v>
+        <v>10.8654</v>
       </c>
       <c r="W25" t="n">
-        <v>8.2615</v>
+        <v>8.2974</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -5016,13 +5016,13 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>12.0056</v>
+        <v>12.0803</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.086</v>
+        <v>11.1529</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.565799999999999</v>
+        <v>8.607799999999999</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>0.5416</v>
+        <v>0.5381</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.4762</v>
+        <v>0.4886</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -5046,58 +5046,58 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>63.59</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="AI25" t="n">
-        <v>11.9969</v>
+        <v>12.0275</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>12.085</v>
+        <v>12.285</v>
       </c>
       <c r="AL25" t="n">
-        <v>11.1606</v>
+        <v>11.247</v>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN25" t="n">
         <v>12.8261</v>
       </c>
       <c r="AO25" t="n">
-        <v>13.0599</v>
+        <v>13.1328</v>
       </c>
       <c r="AP25" t="n">
         <v>13.1767</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 12.83; TP2: Bollinger Upper Band at 13.06; TP3: Classic R1 at 13.18</t>
+          <t>TP1: Fibonacci R1 at 12.83; TP2: Bollinger Upper Band at 13.13; TP3: Classic R1 at 13.18</t>
         </is>
       </c>
       <c r="AR25" t="n">
-        <v>0.8</v>
+        <v>0.52</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.05</v>
+        <v>0.82</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.18</v>
+        <v>0.86</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.13</v>
+        <v>4.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.07</v>
+        <v>6.9</v>
       </c>
       <c r="AW25" t="n">
-        <v>9.029999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
@@ -5106,14 +5106,14 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 63.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.5))</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>331.44</v>
+        <v>377</v>
       </c>
       <c r="F26" t="n">
         <v>8.2704</v>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>11635.0711</v>
+        <v>16628.9193</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -5157,19 +5157,19 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="M26" t="n">
-        <v>1851.5486</v>
+        <v>2666.3287</v>
       </c>
       <c r="N26" t="n">
         <v>159810</v>
       </c>
       <c r="O26" t="n">
-        <v>346697</v>
+        <v>798772</v>
       </c>
       <c r="P26" t="n">
-        <v>2.169</v>
+        <v>4.998</v>
       </c>
       <c r="Q26" t="n">
         <v>251409</v>
@@ -5187,10 +5187,10 @@
         <v>74.2</v>
       </c>
       <c r="V26" t="n">
-        <v>108.7208</v>
+        <v>114.814</v>
       </c>
       <c r="W26" t="n">
-        <v>75.7208</v>
+        <v>77.2937</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -5203,13 +5203,13 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>198.7084</v>
+        <v>215.6886</v>
       </c>
       <c r="AA26" t="n">
-        <v>133.9073</v>
+        <v>143.4404</v>
       </c>
       <c r="AB26" t="n">
-        <v>82.6966</v>
+        <v>85.625</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="AE26" t="n">
-        <v>67.7931</v>
+        <v>73.2996</v>
       </c>
       <c r="AF26" t="n">
-        <v>41.3367</v>
+        <v>47.7293</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -5233,58 +5233,58 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>73.69</v>
+        <v>76.87</v>
       </c>
       <c r="AI26" t="n">
-        <v>184.4266</v>
+        <v>197.58</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK26" t="n">
-        <v>282.08</v>
+        <v>282.59</v>
       </c>
       <c r="AL26" t="n">
-        <v>249.9467</v>
+        <v>125.9867</v>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AN26" t="n">
-        <v>353.5333</v>
+        <v>397.9763</v>
       </c>
       <c r="AO26" t="n">
-        <v>367.4576</v>
+        <v>524.1933</v>
       </c>
       <c r="AP26" t="n">
-        <v>524.1933</v>
+        <v>616.4858</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 353.53; TP2: Bollinger Upper Band at 367.46; TP3: Classic R3 at 524.19</t>
+          <t>TP1: Bollinger Upper Band at 397.98; TP2: Classic R3 at 524.19; TP3: Extension at 616.49</t>
         </is>
       </c>
       <c r="AR26" t="n">
-        <v>2.22</v>
+        <v>0.74</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.66</v>
+        <v>1.54</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.53</v>
+        <v>2.13</v>
       </c>
       <c r="AU26" t="n">
-        <v>25.33</v>
+        <v>40.83</v>
       </c>
       <c r="AV26" t="n">
-        <v>30.27</v>
+        <v>85.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>85.83</v>
+        <v>118.16</v>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
@@ -5293,14 +5293,14 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.7); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 73.7))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.9))</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>21.38</v>
+        <v>21.08</v>
       </c>
       <c r="F27" t="n">
         <v>0.403</v>
@@ -5349,10 +5349,10 @@
         <v>697130</v>
       </c>
       <c r="O27" t="n">
-        <v>3977299</v>
+        <v>467272</v>
       </c>
       <c r="P27" t="n">
-        <v>5.705</v>
+        <v>0.67</v>
       </c>
       <c r="Q27" t="n">
         <v>230494</v>
@@ -5370,10 +5370,10 @@
         <v>20.28</v>
       </c>
       <c r="V27" t="n">
-        <v>19.5696</v>
+        <v>19.5882</v>
       </c>
       <c r="W27" t="n">
-        <v>19.3125</v>
+        <v>19.3172</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -5386,13 +5386,13 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>19.8021</v>
+        <v>19.9238</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.6651</v>
+        <v>19.7206</v>
       </c>
       <c r="AB27" t="n">
-        <v>18.773</v>
+        <v>18.7959</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>0.2415</v>
+        <v>0.3111</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0747</v>
+        <v>0.122</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -5416,18 +5416,18 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>76.29000000000001</v>
+        <v>69.62</v>
       </c>
       <c r="AI27" t="n">
-        <v>20.0809</v>
+        <v>20.1175</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK27" t="n">
-        <v>20.0809</v>
+        <v>20.225</v>
       </c>
       <c r="AL27" t="n">
         <v>19.51</v>
@@ -5441,49 +5441,49 @@
         <v>22.2233</v>
       </c>
       <c r="AO27" t="n">
-        <v>23.2945</v>
+        <v>23.2224</v>
       </c>
       <c r="AP27" t="n">
-        <v>22.729</v>
+        <v>22.6949</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 22.22; TP2: Extension at 23.29; TP3: Extension at 22.73</t>
+          <t>TP1: Classic R3 at 22.22; TP2: Extension at 23.22; TP3: Extension at 22.69</t>
         </is>
       </c>
       <c r="AR27" t="n">
-        <v>3.75</v>
+        <v>2.79</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.63</v>
+        <v>4.19</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.64</v>
+        <v>3.45</v>
       </c>
       <c r="AU27" t="n">
-        <v>10.67</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>14.82</v>
       </c>
       <c r="AW27" t="n">
-        <v>13.19</v>
+        <v>12.21</v>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.3); entry: enhanced entry at VWMA (overbought (RSI: 76.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 69.6))</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>16.39</v>
+        <v>16.1</v>
       </c>
       <c r="F28" t="n">
         <v>0.3234</v>
@@ -5532,10 +5532,10 @@
         <v>936017</v>
       </c>
       <c r="O28" t="n">
-        <v>2543803</v>
+        <v>353552</v>
       </c>
       <c r="P28" t="n">
-        <v>2.718</v>
+        <v>0.378</v>
       </c>
       <c r="Q28" t="n">
         <v>332678</v>
@@ -5556,7 +5556,7 @@
         <v>15.3448</v>
       </c>
       <c r="W28" t="n">
-        <v>15.2685</v>
+        <v>15.2658</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>15.538</v>
+        <v>15.5915</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.4061</v>
+        <v>15.4333</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.9259</v>
+        <v>14.9376</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -5588,10 +5588,10 @@
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>0.2093</v>
+        <v>0.2266</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.1074</v>
+        <v>0.1312</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -5599,18 +5599,18 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>66.52</v>
+        <v>60.23</v>
       </c>
       <c r="AI28" t="n">
-        <v>15.6559</v>
+        <v>15.6772</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>15.6559</v>
+        <v>15.6772</v>
       </c>
       <c r="AL28" t="n">
         <v>15.43</v>
@@ -5621,36 +5621,36 @@
         </is>
       </c>
       <c r="AN28" t="n">
+        <v>16.1176</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>16.2231</v>
+      </c>
+      <c r="AP28" t="n">
         <v>16.6333</v>
       </c>
-      <c r="AO28" t="n">
-        <v>17.9833</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>18.8724</v>
-      </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 16.63; TP2: Classic R3 at 17.98; TP3: Extension at 18.87</t>
+          <t>TP1: Fibonacci R2 at 16.12; TP2: Bollinger Upper Band at 16.22; TP3: Classic R2 at 16.63</t>
         </is>
       </c>
       <c r="AR28" t="n">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="AS28" t="n">
-        <v>10.3</v>
+        <v>2.21</v>
       </c>
       <c r="AT28" t="n">
-        <v>14.24</v>
+        <v>3.87</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.24</v>
+        <v>2.81</v>
       </c>
       <c r="AV28" t="n">
-        <v>14.87</v>
+        <v>3.48</v>
       </c>
       <c r="AW28" t="n">
-        <v>20.54</v>
+        <v>6.1</v>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
@@ -5659,14 +5659,14 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.5))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.2))</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>31.24</v>
+        <v>31.02</v>
       </c>
       <c r="F29" t="n">
         <v>0.6242</v>
@@ -5713,10 +5713,10 @@
         <v>1440425</v>
       </c>
       <c r="O29" t="n">
-        <v>343433</v>
+        <v>58183</v>
       </c>
       <c r="P29" t="n">
-        <v>0.238</v>
+        <v>0.04</v>
       </c>
       <c r="Q29" t="n">
         <v>505522</v>
@@ -5734,10 +5734,10 @@
         <v>36.45</v>
       </c>
       <c r="V29" t="n">
-        <v>28.7632</v>
+        <v>28.896</v>
       </c>
       <c r="W29" t="n">
-        <v>17.8121</v>
+        <v>17.9019</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5750,13 +5750,13 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>29.9549</v>
+        <v>30.0564</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.6776</v>
+        <v>27.8087</v>
       </c>
       <c r="AB29" t="n">
-        <v>19.7973</v>
+        <v>19.909</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>0.9973</v>
+        <v>0.961</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.8671</v>
+        <v>0.8859</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -5780,18 +5780,18 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>65.94</v>
+        <v>63.41</v>
       </c>
       <c r="AI29" t="n">
-        <v>29.8566</v>
+        <v>29.9562</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="AL29" t="n">
         <v>27.6202</v>
@@ -5805,33 +5805,33 @@
         <v>32.3265</v>
       </c>
       <c r="AO29" t="n">
-        <v>33.0411</v>
+        <v>33.1584</v>
       </c>
       <c r="AP29" t="n">
         <v>33.4067</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 33.04; TP3: Classic R1 at 33.41</t>
+          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 33.16; TP3: Classic R1 at 33.41</t>
         </is>
       </c>
       <c r="AR29" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.1</v>
+        <v>0.92</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.04</v>
+        <v>5.99</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.41</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>10.62</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
@@ -5840,14 +5840,14 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 65.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 63.4))</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34.67</v>
+        <v>35.4</v>
       </c>
       <c r="F30" t="n">
         <v>0.7192</v>
@@ -5900,10 +5900,10 @@
         <v>800067</v>
       </c>
       <c r="O30" t="n">
-        <v>606691</v>
+        <v>133964</v>
       </c>
       <c r="P30" t="n">
-        <v>0.758</v>
+        <v>0.167</v>
       </c>
       <c r="Q30" t="n">
         <v>851250</v>
@@ -5921,10 +5921,10 @@
         <v>37</v>
       </c>
       <c r="V30" t="n">
-        <v>29.9704</v>
+        <v>30.1326</v>
       </c>
       <c r="W30" t="n">
-        <v>26.8569</v>
+        <v>26.9059</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>33.5995</v>
+        <v>33.771</v>
       </c>
       <c r="AA30" t="n">
-        <v>30.9471</v>
+        <v>31.1217</v>
       </c>
       <c r="AB30" t="n">
-        <v>27.5688</v>
+        <v>27.6467</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>1.7454</v>
+        <v>1.6761</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7514</v>
+        <v>1.7363</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>58.29</v>
+        <v>60.81</v>
       </c>
       <c r="AI30" t="n">
-        <v>33.4005</v>
+        <v>33.6202</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>33.4005</v>
+        <v>33.6202</v>
       </c>
       <c r="AL30" t="n">
-        <v>30.5006</v>
+        <v>30.6464</v>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
@@ -5992,33 +5992,33 @@
         <v>36.5522</v>
       </c>
       <c r="AO30" t="n">
-        <v>37.5107</v>
+        <v>37.5178</v>
       </c>
       <c r="AP30" t="n">
         <v>38.3133</v>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.51; TP3: Classic R1 at 38.31</t>
+          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.52; TP3: Classic R1 at 38.31</t>
         </is>
       </c>
       <c r="AR30" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AU30" t="n">
-        <v>9.44</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>12.31</v>
+        <v>11.59</v>
       </c>
       <c r="AW30" t="n">
-        <v>14.71</v>
+        <v>13.96</v>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
@@ -6027,14 +6027,14 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.8))</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6083,10 +6083,10 @@
         <v>34775344</v>
       </c>
       <c r="O31" t="n">
-        <v>24458368</v>
+        <v>2082517</v>
       </c>
       <c r="P31" t="n">
-        <v>0.703</v>
+        <v>0.06</v>
       </c>
       <c r="Q31" t="n">
         <v>22360112</v>
@@ -6104,10 +6104,10 @@
         <v>1.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.8242</v>
+        <v>1.8308</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6961</v>
+        <v>1.6965</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1.8995</v>
+        <v>1.9034</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8304</v>
+        <v>1.8347</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6354</v>
+        <v>1.6384</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>0.0348</v>
+        <v>0.0338</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0317</v>
+        <v>0.0322</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -6153,18 +6153,18 @@
         <v>57.32</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.9193</v>
+        <v>1.9216</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>1.9193</v>
+        <v>1.9216</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.8716</v>
+        <v>1.8835</v>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="AN31" t="n">
-        <v>1.9914</v>
+        <v>1.9898</v>
       </c>
       <c r="AO31" t="n">
         <v>2.0413</v>
@@ -6186,22 +6186,22 @@
         </is>
       </c>
       <c r="AR31" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.43</v>
+        <v>4.24</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.35</v>
+        <v>6.23</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.539999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.1</v>
+        <v>10.15</v>
       </c>
       <c r="F32" t="n">
         <v>0.197</v>
@@ -6266,10 +6266,10 @@
         <v>5510558</v>
       </c>
       <c r="O32" t="n">
-        <v>4805984</v>
+        <v>1398056</v>
       </c>
       <c r="P32" t="n">
-        <v>0.872</v>
+        <v>0.254</v>
       </c>
       <c r="Q32" t="n">
         <v>1108744</v>
@@ -6287,10 +6287,10 @@
         <v>9.880000000000001</v>
       </c>
       <c r="V32" t="n">
-        <v>9.648</v>
+        <v>9.657999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>9.621499999999999</v>
+        <v>9.613300000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>9.7989</v>
+        <v>9.8323</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.683999999999999</v>
+        <v>9.702199999999999</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.4901</v>
+        <v>9.496700000000001</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -6322,10 +6322,10 @@
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>0.1005</v>
+        <v>0.1157</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -6333,21 +6333,21 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>61.2</v>
+        <v>62.44</v>
       </c>
       <c r="AI32" t="n">
-        <v>9.845700000000001</v>
+        <v>9.866400000000001</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>9.859999999999999</v>
+        <v>9.866400000000001</v>
       </c>
       <c r="AL32" t="n">
-        <v>9.77</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="AN32" t="n">
-        <v>10.1429</v>
+        <v>10.1952</v>
       </c>
       <c r="AO32" t="n">
         <v>10.2191</v>
@@ -6365,26 +6365,26 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 10.14; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
+          <t>TP1: Bollinger Upper Band at 10.2; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
         </is>
       </c>
       <c r="AR32" t="n">
-        <v>3.14</v>
+        <v>4.95</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.99</v>
+        <v>5.31</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.78</v>
+        <v>6.38</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.87</v>
+        <v>3.33</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.36</v>
+        <v>4.29</v>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
@@ -6393,14 +6393,14 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>10.74</v>
+        <v>10.99</v>
       </c>
       <c r="F33" t="n">
         <v>0.2056</v>
@@ -6453,10 +6453,10 @@
         <v>2630323</v>
       </c>
       <c r="O33" t="n">
-        <v>9558321</v>
+        <v>4223836</v>
       </c>
       <c r="P33" t="n">
-        <v>3.634</v>
+        <v>1.606</v>
       </c>
       <c r="Q33" t="n">
         <v>1309721</v>
@@ -6474,10 +6474,10 @@
         <v>10.38</v>
       </c>
       <c r="V33" t="n">
-        <v>9.281599999999999</v>
+        <v>9.3188</v>
       </c>
       <c r="W33" t="n">
-        <v>8.0327</v>
+        <v>8.0511</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>9.6328</v>
+        <v>9.762</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.290100000000001</v>
+        <v>9.3567</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.202</v>
+        <v>8.229699999999999</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>0.2366</v>
+        <v>0.315</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1356</v>
+        <v>0.1715</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -6520,21 +6520,21 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>77.19</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="AI33" t="n">
-        <v>9.847200000000001</v>
+        <v>9.9305</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>9.85</v>
+        <v>10.185</v>
       </c>
       <c r="AL33" t="n">
-        <v>9.3621</v>
+        <v>9.520899999999999</v>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
@@ -6545,33 +6545,33 @@
         <v>11.0167</v>
       </c>
       <c r="AO33" t="n">
-        <v>11.6</v>
+        <v>11.4325</v>
       </c>
       <c r="AP33" t="n">
-        <v>11.292</v>
+        <v>11.2129</v>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 11.02; TP2: Extension at 11.6; TP3: Extension at 11.29</t>
+          <t>TP1: Classic R3 at 11.02; TP2: Extension at 11.43; TP3: Extension at 11.21</t>
         </is>
       </c>
       <c r="AR33" t="n">
-        <v>2.39</v>
+        <v>1.25</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.59</v>
+        <v>1.88</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.96</v>
+        <v>1.55</v>
       </c>
       <c r="AU33" t="n">
-        <v>11.84</v>
+        <v>8.17</v>
       </c>
       <c r="AV33" t="n">
-        <v>17.77</v>
+        <v>12.25</v>
       </c>
       <c r="AW33" t="n">
-        <v>14.64</v>
+        <v>10.09</v>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
@@ -6580,14 +6580,14 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 77.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.5); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.5))</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="F34" t="n">
         <v>0.2022</v>
@@ -6636,10 +6636,10 @@
         <v>2332510</v>
       </c>
       <c r="O34" t="n">
-        <v>1622811</v>
+        <v>278453</v>
       </c>
       <c r="P34" t="n">
-        <v>0.696</v>
+        <v>0.119</v>
       </c>
       <c r="Q34" t="n">
         <v>663933</v>
@@ -6657,10 +6657,10 @@
         <v>10.26</v>
       </c>
       <c r="V34" t="n">
-        <v>9.9732</v>
+        <v>9.977</v>
       </c>
       <c r="W34" t="n">
-        <v>9.234</v>
+        <v>9.2346</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -6673,13 +6673,13 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>10.0922</v>
+        <v>10.092</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.9366</v>
+        <v>9.942600000000001</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.1204</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -6692,10 +6692,10 @@
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>0.0426</v>
+        <v>0.0376</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0568</v>
+        <v>0.0529</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -6703,29 +6703,29 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>52.84</v>
+        <v>50.8</v>
       </c>
       <c r="AI34" t="n">
-        <v>10.227</v>
+        <v>10.2386</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK34" t="n">
-        <v>10.125</v>
+        <v>9.977</v>
       </c>
       <c r="AL34" t="n">
-        <v>9.91</v>
+        <v>9.9132</v>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AN34" t="n">
-        <v>10.3881</v>
+        <v>10.3808</v>
       </c>
       <c r="AO34" t="n">
         <v>10.6503</v>
@@ -6735,26 +6735,26 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 10.39; TP2: Fibonacci R1 at 10.65; TP3: Classic R1 at 10.7</t>
+          <t>TP1: Bollinger Upper Band at 10.38; TP2: Fibonacci R1 at 10.65; TP3: Classic R1 at 10.7</t>
         </is>
       </c>
       <c r="AR34" t="n">
-        <v>1.22</v>
+        <v>6.33</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.44</v>
+        <v>10.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.69</v>
+        <v>11.39</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.6</v>
+        <v>4.05</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.19</v>
+        <v>6.75</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.71</v>
+        <v>7.28</v>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
@@ -6763,14 +6763,14 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.8))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.8))</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16.29</v>
+        <v>16.36</v>
       </c>
       <c r="F35" t="n">
         <v>0.3144</v>
@@ -6823,10 +6823,10 @@
         <v>2835647</v>
       </c>
       <c r="O35" t="n">
-        <v>4668490</v>
+        <v>1195590</v>
       </c>
       <c r="P35" t="n">
-        <v>1.646</v>
+        <v>0.422</v>
       </c>
       <c r="Q35" t="n">
         <v>574345</v>
@@ -6844,10 +6844,10 @@
         <v>15.77</v>
       </c>
       <c r="V35" t="n">
-        <v>16.3508</v>
+        <v>16.3242</v>
       </c>
       <c r="W35" t="n">
-        <v>16.2578</v>
+        <v>16.2604</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -6860,13 +6860,13 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>16.0144</v>
+        <v>16.0473</v>
       </c>
       <c r="AA35" t="n">
-        <v>16.3073</v>
+        <v>16.3094</v>
       </c>
       <c r="AB35" t="n">
-        <v>16.43</v>
+        <v>16.4293</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -6879,10 +6879,10 @@
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>-0.1065</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.1431</v>
+        <v>-0.1279</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -6890,58 +6890,58 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>53.57</v>
+        <v>54.65</v>
       </c>
       <c r="AI35" t="n">
-        <v>16.0372</v>
+        <v>16.0223</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK35" t="n">
-        <v>16.0372</v>
+        <v>16.3242</v>
       </c>
       <c r="AL35" t="n">
-        <v>15.58</v>
+        <v>16.2604</v>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at 200 SMA</t>
         </is>
       </c>
       <c r="AN35" t="n">
         <v>16.5125</v>
       </c>
       <c r="AO35" t="n">
-        <v>16.7146</v>
+        <v>16.716</v>
       </c>
       <c r="AP35" t="n">
-        <v>16.72</v>
+        <v>16.9703</v>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 16.51; TP2: Bollinger Upper Band at 16.71; TP3: Classic R1 at 16.72</t>
+          <t>TP1: Fibonacci R1 at 16.51; TP2: Bollinger Upper Band at 16.72; TP3: 100 SMA at 16.97</t>
         </is>
       </c>
       <c r="AR35" t="n">
-        <v>1.04</v>
+        <v>2.95</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.48</v>
+        <v>6.14</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.49</v>
+        <v>10.12</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.96</v>
+        <v>1.15</v>
       </c>
       <c r="AV35" t="n">
-        <v>4.22</v>
+        <v>2.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.26</v>
+        <v>3.96</v>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
@@ -6950,14 +6950,14 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 53.6))</t>
+          <t>Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 54.7))</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="F36" t="n">
         <v>1.565</v>
@@ -7010,10 +7010,10 @@
         <v>725015</v>
       </c>
       <c r="O36" t="n">
-        <v>1811834</v>
+        <v>380597</v>
       </c>
       <c r="P36" t="n">
-        <v>2.499</v>
+        <v>0.525</v>
       </c>
       <c r="Q36" t="n">
         <v>365915</v>
@@ -7031,10 +7031,10 @@
         <v>67</v>
       </c>
       <c r="V36" t="n">
-        <v>67.6564</v>
+        <v>67.9636</v>
       </c>
       <c r="W36" t="n">
-        <v>63.364</v>
+        <v>63.504</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -7047,13 +7047,13 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>75.47410000000001</v>
+        <v>76.0004</v>
       </c>
       <c r="AA36" t="n">
-        <v>69.6922</v>
+        <v>70.1357</v>
       </c>
       <c r="AB36" t="n">
-        <v>61.2686</v>
+        <v>61.4649</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>4.4165</v>
+        <v>4.3109</v>
       </c>
       <c r="AF36" t="n">
         <v>4.3107</v>
@@ -7077,18 +7077,18 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>64.43000000000001</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AI36" t="n">
-        <v>77.6875</v>
+        <v>77.8288</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK36" t="n">
-        <v>77.6875</v>
+        <v>77.8288</v>
       </c>
       <c r="AL36" t="n">
         <v>66.2534</v>
@@ -7102,33 +7102,33 @@
         <v>86.65989999999999</v>
       </c>
       <c r="AO36" t="n">
-        <v>91.0241</v>
+        <v>91.3344</v>
       </c>
       <c r="AP36" t="n">
         <v>91.63330000000001</v>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 91.02; TP3: Classic R1 at 91.63</t>
+          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 91.33; TP3: Classic R1 at 91.63</t>
         </is>
       </c>
       <c r="AR36" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AS36" t="n">
         <v>1.17</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AU36" t="n">
-        <v>11.55</v>
+        <v>11.35</v>
       </c>
       <c r="AV36" t="n">
-        <v>17.17</v>
+        <v>17.35</v>
       </c>
       <c r="AW36" t="n">
-        <v>17.95</v>
+        <v>17.74</v>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.2))</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="F37" t="n">
         <v>0.5789</v>
@@ -7180,7 +7180,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>23.6217</v>
+        <v>23.6816</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -7188,19 +7188,19 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>14.7</v>
+        <v>14.65</v>
       </c>
       <c r="M37" t="n">
-        <v>1.9729</v>
+        <v>1.9795</v>
       </c>
       <c r="N37" t="n">
         <v>2122939</v>
       </c>
       <c r="O37" t="n">
-        <v>3732429</v>
+        <v>628341</v>
       </c>
       <c r="P37" t="n">
-        <v>1.758</v>
+        <v>0.296</v>
       </c>
       <c r="Q37" t="n">
         <v>2077073</v>
@@ -7218,10 +7218,10 @@
         <v>28.7</v>
       </c>
       <c r="V37" t="n">
-        <v>24.6718</v>
+        <v>24.8482</v>
       </c>
       <c r="W37" t="n">
-        <v>20.3851</v>
+        <v>20.4551</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -7234,13 +7234,13 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>27.7972</v>
+        <v>28.0356</v>
       </c>
       <c r="AA37" t="n">
-        <v>25.5551</v>
+        <v>25.7412</v>
       </c>
       <c r="AB37" t="n">
-        <v>21.1979</v>
+        <v>21.2885</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>1.3044</v>
+        <v>1.3463</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.2413</v>
+        <v>1.2623</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -7264,21 +7264,21 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>73.17</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="AI37" t="n">
-        <v>28.1072</v>
+        <v>28.2335</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>28.1072</v>
+        <v>28.2335</v>
       </c>
       <c r="AL37" t="n">
-        <v>27.1654</v>
+        <v>27.4322</v>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
@@ -7292,30 +7292,30 @@
         <v>36.71</v>
       </c>
       <c r="AP37" t="n">
-        <v>39.9963</v>
+        <v>39.948</v>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 31.97; TP2: Classic R3 at 36.71; TP3: Extension at 40.0</t>
+          <t>TP1: Classic R2 at 31.97; TP2: Classic R3 at 36.71; TP3: Extension at 39.95</t>
         </is>
       </c>
       <c r="AR37" t="n">
-        <v>4.1</v>
+        <v>4.66</v>
       </c>
       <c r="AS37" t="n">
-        <v>9.130000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="AT37" t="n">
-        <v>12.62</v>
+        <v>14.62</v>
       </c>
       <c r="AU37" t="n">
-        <v>13.74</v>
+        <v>13.23</v>
       </c>
       <c r="AV37" t="n">
-        <v>30.61</v>
+        <v>30.02</v>
       </c>
       <c r="AW37" t="n">
-        <v>42.3</v>
+        <v>41.49</v>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
@@ -7324,14 +7324,14 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.2); entry: enhanced entry at VWMA (overbought (RSI: 73.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.2); entry: enhanced entry at VWMA (overbought (RSI: 71.2))</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="F38" t="n">
         <v>0.1837</v>
@@ -7384,10 +7384,10 @@
         <v>7732701</v>
       </c>
       <c r="O38" t="n">
-        <v>3763743</v>
+        <v>770004</v>
       </c>
       <c r="P38" t="n">
-        <v>0.487</v>
+        <v>0.1</v>
       </c>
       <c r="Q38" t="n">
         <v>2098210</v>
@@ -7405,10 +7405,10 @@
         <v>9.75</v>
       </c>
       <c r="V38" t="n">
-        <v>9.213200000000001</v>
+        <v>9.2094</v>
       </c>
       <c r="W38" t="n">
-        <v>7.3216</v>
+        <v>7.3378</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -7421,13 +7421,13 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>9.262700000000001</v>
+        <v>9.271000000000001</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.0052</v>
+        <v>9.018700000000001</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.5012</v>
+        <v>7.5196</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>0.0226</v>
+        <v>0.028</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0506</v>
+        <v>0.0461</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -7451,21 +7451,21 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>53.98</v>
+        <v>53.64</v>
       </c>
       <c r="AI38" t="n">
-        <v>9.337999999999999</v>
+        <v>9.350199999999999</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>9.337999999999999</v>
+        <v>9.2094</v>
       </c>
       <c r="AL38" t="n">
-        <v>9.0883</v>
+        <v>9.119199999999999</v>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="AN38" t="n">
-        <v>9.5237</v>
+        <v>9.5168</v>
       </c>
       <c r="AO38" t="n">
         <v>9.7621</v>
@@ -7487,22 +7487,22 @@
         </is>
       </c>
       <c r="AR38" t="n">
-        <v>0.74</v>
+        <v>3.41</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.7</v>
+        <v>6.13</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.76</v>
+        <v>6.29</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.99</v>
+        <v>3.34</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.54</v>
+        <v>6</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.7</v>
+        <v>6.16</v>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
@@ -7511,14 +7511,14 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 54.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 53.6))</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.671</v>
+        <v>0.68</v>
       </c>
       <c r="F39" t="n">
         <v>0.0134</v>
@@ -7567,10 +7567,10 @@
         <v>26823227</v>
       </c>
       <c r="O39" t="n">
-        <v>29815013</v>
+        <v>15240736</v>
       </c>
       <c r="P39" t="n">
-        <v>1.112</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="Q39" t="n">
         <v>9507098</v>
@@ -7588,10 +7588,10 @@
         <v>0.721</v>
       </c>
       <c r="V39" t="n">
-        <v>0.699</v>
+        <v>0.6978</v>
       </c>
       <c r="W39" t="n">
-        <v>0.7823</v>
+        <v>0.783</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -7604,13 +7604,13 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>0.6958</v>
+        <v>0.6943</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.7157</v>
+        <v>0.7143</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.7249</v>
+        <v>0.7244</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -7623,10 +7623,10 @@
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>-0.0089</v>
+        <v>-0.0091</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.0044</v>
+        <v>-0.0053</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -7634,14 +7634,14 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>35.34</v>
+        <v>40.82</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.706</v>
+        <v>0.7058</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:45</t>
+          <t>2026-08-06 08:06:52</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7679,7 +7679,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.6</v>
+        <v>4.59</v>
       </c>
       <c r="F40" t="n">
         <v>0.0892</v>
@@ -7726,10 +7726,10 @@
         <v>6204577</v>
       </c>
       <c r="O40" t="n">
-        <v>10867987</v>
+        <v>971397</v>
       </c>
       <c r="P40" t="n">
-        <v>1.752</v>
+        <v>0.157</v>
       </c>
       <c r="Q40" t="n">
         <v>4433921</v>
@@ -7747,10 +7747,10 @@
         <v>4.11</v>
       </c>
       <c r="V40" t="n">
-        <v>3.7688</v>
+        <v>3.7906</v>
       </c>
       <c r="W40" t="n">
-        <v>3.0017</v>
+        <v>3.0131</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>4.2012</v>
+        <v>4.2382</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.8668</v>
+        <v>3.8952</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.1402</v>
+        <v>3.1546</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="AE40" t="n">
-        <v>0.258</v>
+        <v>0.2566</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.2126</v>
+        <v>0.2214</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -7793,14 +7793,14 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>66.16</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.3174</v>
+        <v>4.3573</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -7815,33 +7815,33 @@
         </is>
       </c>
       <c r="AN40" t="n">
-        <v>4.9067</v>
+        <v>4.9278</v>
       </c>
       <c r="AO40" t="n">
-        <v>4.9278</v>
+        <v>4.9541</v>
       </c>
       <c r="AP40" t="n">
         <v>5.2367</v>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 4.91; TP2: Fibonacci R1 at 4.93; TP3: Classic R1 at 5.24</t>
+          <t>TP1: Fibonacci R1 at 4.93; TP2: Bollinger Upper Band at 4.95; TP3: Classic R1 at 5.24</t>
         </is>
       </c>
       <c r="AR40" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="AT40" t="n">
         <v>1.38</v>
       </c>
       <c r="AU40" t="n">
-        <v>12.03</v>
+        <v>12.51</v>
       </c>
       <c r="AV40" t="n">
-        <v>12.51</v>
+        <v>13.11</v>
       </c>
       <c r="AW40" t="n">
         <v>19.56</v>
@@ -7853,14 +7853,14 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 66.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 65.7))</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>52.08</v>
+        <v>52.05</v>
       </c>
       <c r="F41" t="n">
         <v>1.0344</v>
@@ -7913,10 +7913,10 @@
         <v>2151784</v>
       </c>
       <c r="O41" t="n">
-        <v>1269183</v>
+        <v>155099</v>
       </c>
       <c r="P41" t="n">
-        <v>0.59</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="Q41" t="n">
         <v>1266736</v>
@@ -7934,10 +7934,10 @@
         <v>48.49</v>
       </c>
       <c r="V41" t="n">
-        <v>47.695</v>
+        <v>47.786</v>
       </c>
       <c r="W41" t="n">
-        <v>37.3659</v>
+        <v>37.5269</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>50.0367</v>
+        <v>50.2284</v>
       </c>
       <c r="AA41" t="n">
-        <v>47.9084</v>
+        <v>48.0709</v>
       </c>
       <c r="AB41" t="n">
-        <v>38.9359</v>
+        <v>39.0664</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -7969,10 +7969,10 @@
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>1.5819</v>
+        <v>1.5435</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.2888</v>
+        <v>1.3397</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -7980,18 +7980,18 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>64.31999999999999</v>
+        <v>64.11</v>
       </c>
       <c r="AI41" t="n">
-        <v>49.2866</v>
+        <v>49.4673</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>49.8093</v>
+        <v>50.2402</v>
       </c>
       <c r="AL41" t="n">
         <v>48.2733</v>
@@ -8005,33 +8005,33 @@
         <v>53.2048</v>
       </c>
       <c r="AO41" t="n">
-        <v>54.5038</v>
+        <v>54.7315</v>
       </c>
       <c r="AP41" t="n">
         <v>54.8285</v>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 54.5; TP3: Fibonacci R2 at 54.83</t>
+          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 54.73; TP3: Fibonacci R2 at 54.83</t>
         </is>
       </c>
       <c r="AR41" t="n">
-        <v>2.21</v>
+        <v>1.51</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.06</v>
+        <v>2.28</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.27</v>
+        <v>2.33</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.82</v>
+        <v>5.9</v>
       </c>
       <c r="AV41" t="n">
-        <v>9.43</v>
+        <v>8.94</v>
       </c>
       <c r="AW41" t="n">
-        <v>10.08</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 64.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 64.1))</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>37</v>
+        <v>37.09</v>
       </c>
       <c r="F42" t="n">
         <v>0.7426</v>
@@ -8100,10 +8100,10 @@
         <v>1881547</v>
       </c>
       <c r="O42" t="n">
-        <v>1446853</v>
+        <v>179999</v>
       </c>
       <c r="P42" t="n">
-        <v>0.769</v>
+        <v>0.096</v>
       </c>
       <c r="Q42" t="n">
         <v>954589</v>
@@ -8121,10 +8121,10 @@
         <v>38.8</v>
       </c>
       <c r="V42" t="n">
-        <v>38.4712</v>
+        <v>38.3228</v>
       </c>
       <c r="W42" t="n">
-        <v>35.8311</v>
+        <v>35.8689</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -8137,13 +8137,13 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>37.1907</v>
+        <v>37.1811</v>
       </c>
       <c r="AA42" t="n">
-        <v>38.3177</v>
+        <v>38.2695</v>
       </c>
       <c r="AB42" t="n">
-        <v>36.6796</v>
+        <v>36.6837</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -8156,10 +8156,10 @@
         </is>
       </c>
       <c r="AE42" t="n">
-        <v>-0.3077</v>
+        <v>-0.2839</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.4244</v>
+        <v>-0.3963</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -8167,21 +8167,21 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>46.7</v>
+        <v>47.44</v>
       </c>
       <c r="AI42" t="n">
-        <v>37.4143</v>
+        <v>37.3984</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>36.1087</v>
+        <v>36.088</v>
       </c>
       <c r="AL42" t="n">
-        <v>35.8311</v>
+        <v>35.8689</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
@@ -8192,33 +8192,33 @@
         <v>38.25</v>
       </c>
       <c r="AO42" t="n">
-        <v>38.5083</v>
+        <v>38.488</v>
       </c>
       <c r="AP42" t="n">
         <v>38.5567</v>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 38.25; TP2: Bollinger Upper Band at 38.51; TP3: Classic R1 at 38.56</t>
+          <t>TP1: Fibonacci R1 at 38.25; TP2: Bollinger Upper Band at 38.49; TP3: Classic R1 at 38.56</t>
         </is>
       </c>
       <c r="AR42" t="n">
-        <v>7.72</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.65</v>
+        <v>10.96</v>
       </c>
       <c r="AT42" t="n">
-        <v>8.82</v>
+        <v>11.27</v>
       </c>
       <c r="AU42" t="n">
-        <v>5.93</v>
+        <v>5.99</v>
       </c>
       <c r="AV42" t="n">
         <v>6.65</v>
       </c>
       <c r="AW42" t="n">
-        <v>6.78</v>
+        <v>6.84</v>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
@@ -8227,85 +8227,87 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.7))</t>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 47.4))</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NCCW</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>EGX70</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NCCW</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>EGX70</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
       <c r="E43" t="n">
-        <v>7.12</v>
+        <v>6.33</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1413</v>
+        <v>0.1183</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0239</v>
+        <v>0.0241</v>
       </c>
       <c r="H43" t="n">
         <v>0.3869</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>6.2675</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD-Comparison (fallback)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>2837003</v>
+        <v>2880235</v>
       </c>
       <c r="O43" t="n">
-        <v>7390746</v>
+        <v>7237688</v>
       </c>
       <c r="P43" t="n">
-        <v>2.605</v>
+        <v>2.513</v>
       </c>
       <c r="Q43" t="n">
-        <v>2477449</v>
+        <v>2134628</v>
       </c>
       <c r="R43" t="n">
-        <v>1986923</v>
+        <v>3167453</v>
       </c>
       <c r="S43" t="n">
-        <v>0.802</v>
+        <v>1.484</v>
       </c>
       <c r="T43" t="n">
         <v>5.82</v>
       </c>
       <c r="U43" t="n">
-        <v>7.28</v>
+        <v>6.28</v>
       </c>
       <c r="V43" t="n">
-        <v>6.3102</v>
+        <v>6.33</v>
       </c>
       <c r="W43" t="n">
-        <v>5.852</v>
+        <v>5.8456</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -8318,13 +8320,13 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>6.7796</v>
+        <v>6.7368</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.3655</v>
+        <v>6.3641</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.7173</v>
+        <v>5.7234</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -8337,69 +8339,69 @@
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>0.2378</v>
+        <v>0.173</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.2207</v>
+        <v>0.2112</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>63.57</v>
+        <v>43.09</v>
       </c>
       <c r="AI43" t="n">
-        <v>6.8026</v>
+        <v>6.7876</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK43" t="n">
-        <v>6.8026</v>
+        <v>6.2449</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.6612</v>
+        <v>6.18</v>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AN43" t="n">
         <v>7.2151</v>
       </c>
       <c r="AO43" t="n">
-        <v>7.3467</v>
+        <v>7.311</v>
       </c>
       <c r="AP43" t="n">
         <v>7.45</v>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.35; TP3: Classic R1 at 7.45</t>
+          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.31; TP3: Classic R1 at 7.45</t>
         </is>
       </c>
       <c r="AR43" t="n">
-        <v>2.92</v>
+        <v>14.96</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.85</v>
+        <v>16.44</v>
       </c>
       <c r="AT43" t="n">
-        <v>4.58</v>
+        <v>18.58</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.06</v>
+        <v>15.54</v>
       </c>
       <c r="AV43" t="n">
-        <v>8</v>
+        <v>17.07</v>
       </c>
       <c r="AW43" t="n">
-        <v>9.52</v>
+        <v>19.3</v>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
@@ -8408,14 +8410,14 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 43.1))</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8434,7 +8436,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>388.1</v>
+        <v>384.48</v>
       </c>
       <c r="F44" t="n">
         <v>7.4206</v>
@@ -8459,7 +8461,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>491.08</v>
+        <v>486.5</v>
       </c>
       <c r="M44" t="n">
         <v>0.7903</v>
@@ -8468,10 +8470,10 @@
         <v>35081</v>
       </c>
       <c r="O44" t="n">
-        <v>108236</v>
+        <v>14403</v>
       </c>
       <c r="P44" t="n">
-        <v>3.085</v>
+        <v>0.411</v>
       </c>
       <c r="Q44" t="n">
         <v>13496</v>
@@ -8489,10 +8491,10 @@
         <v>377</v>
       </c>
       <c r="V44" t="n">
-        <v>361.701</v>
+        <v>361.9908</v>
       </c>
       <c r="W44" t="n">
-        <v>343.32</v>
+        <v>343.8427</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -8505,13 +8507,13 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>372.6266</v>
+        <v>373.7555</v>
       </c>
       <c r="AA44" t="n">
-        <v>364.2291</v>
+        <v>365.0233</v>
       </c>
       <c r="AB44" t="n">
-        <v>322.5812</v>
+        <v>323.1971</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -8524,10 +8526,10 @@
         </is>
       </c>
       <c r="AE44" t="n">
-        <v>6.5458</v>
+        <v>6.6688</v>
       </c>
       <c r="AF44" t="n">
-        <v>5.1892</v>
+        <v>5.4851</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -8535,18 +8537,18 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>58.25</v>
+        <v>56.39</v>
       </c>
       <c r="AI44" t="n">
-        <v>381.5751</v>
+        <v>382.327</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>383.5</v>
+        <v>382.327</v>
       </c>
       <c r="AL44" t="n">
         <v>360</v>
@@ -8557,7 +8559,7 @@
         </is>
       </c>
       <c r="AN44" t="n">
-        <v>392.1623</v>
+        <v>393.5553</v>
       </c>
       <c r="AO44" t="n">
         <v>423.2347</v>
@@ -8567,26 +8569,26 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 392.16; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
+          <t>TP1: Bollinger Upper Band at 393.56; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
         </is>
       </c>
       <c r="AR44" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="AV44" t="n">
-        <v>10.36</v>
+        <v>10.7</v>
       </c>
       <c r="AW44" t="n">
-        <v>13.86</v>
+        <v>14.21</v>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
@@ -8595,14 +8597,14 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 58.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.4))</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8621,7 +8623,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>303.07</v>
+        <v>295.5</v>
       </c>
       <c r="F45" t="n">
         <v>5.5096</v>
@@ -8649,10 +8651,10 @@
         <v>93154</v>
       </c>
       <c r="O45" t="n">
-        <v>253719</v>
+        <v>41352</v>
       </c>
       <c r="P45" t="n">
-        <v>2.724</v>
+        <v>0.444</v>
       </c>
       <c r="Q45" t="n">
         <v>37522</v>
@@ -8670,10 +8672,10 @@
         <v>247.97</v>
       </c>
       <c r="V45" t="n">
-        <v>223.3772</v>
+        <v>225.2046</v>
       </c>
       <c r="W45" t="n">
-        <v>188.4283</v>
+        <v>189.0892</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -8686,13 +8688,13 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>253.3578</v>
+        <v>257.3714</v>
       </c>
       <c r="AA45" t="n">
-        <v>229.7014</v>
+        <v>232.2817</v>
       </c>
       <c r="AB45" t="n">
-        <v>185.0997</v>
+        <v>186.1982</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -8705,10 +8707,10 @@
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>19.1647</v>
+        <v>20.1064</v>
       </c>
       <c r="AF45" t="n">
-        <v>13.78</v>
+        <v>15.0453</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -8716,21 +8718,21 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>71.15000000000001</v>
+        <v>67.39</v>
       </c>
       <c r="AI45" t="n">
-        <v>267.2307</v>
+        <v>269.3754</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>267.2307</v>
+        <v>269.3754</v>
       </c>
       <c r="AL45" t="n">
-        <v>257.974</v>
+        <v>265.1759</v>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
@@ -8738,36 +8740,36 @@
         </is>
       </c>
       <c r="AN45" t="n">
+        <v>304.0176</v>
+      </c>
+      <c r="AO45" t="n">
         <v>307.9633</v>
       </c>
-      <c r="AO45" t="n">
+      <c r="AP45" t="n">
         <v>308.8515</v>
       </c>
-      <c r="AP45" t="n">
-        <v>342.1467</v>
-      </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 307.96; TP2: Fibonacci R2 at 308.85; TP3: Classic R2 at 342.15</t>
+          <t>TP1: Bollinger Upper Band at 304.02; TP2: Classic R1 at 307.96; TP3: Fibonacci R2 at 308.85</t>
         </is>
       </c>
       <c r="AR45" t="n">
-        <v>4.4</v>
+        <v>8.25</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.5</v>
+        <v>9.19</v>
       </c>
       <c r="AT45" t="n">
-        <v>8.09</v>
+        <v>9.4</v>
       </c>
       <c r="AU45" t="n">
-        <v>15.24</v>
+        <v>12.86</v>
       </c>
       <c r="AV45" t="n">
-        <v>15.57</v>
+        <v>14.32</v>
       </c>
       <c r="AW45" t="n">
-        <v>28.03</v>
+        <v>14.65</v>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
@@ -8776,14 +8778,14 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.2); entry: enhanced entry at VWMA (overbought (RSI: 71.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.4))</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8802,7 +8804,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8.19</v>
+        <v>8.18</v>
       </c>
       <c r="F46" t="n">
         <v>0.1657</v>
@@ -8830,10 +8832,10 @@
         <v>2505584</v>
       </c>
       <c r="O46" t="n">
-        <v>2252277</v>
+        <v>379529</v>
       </c>
       <c r="P46" t="n">
-        <v>0.899</v>
+        <v>0.151</v>
       </c>
       <c r="Q46" t="n">
         <v>2507353</v>
@@ -8851,10 +8853,10 @@
         <v>8.9</v>
       </c>
       <c r="V46" t="n">
-        <v>7.001</v>
+        <v>7.0456</v>
       </c>
       <c r="W46" t="n">
-        <v>6.4343</v>
+        <v>6.4475</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -8867,13 +8869,13 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>7.9149</v>
+        <v>7.9402</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.2729</v>
+        <v>7.3084</v>
       </c>
       <c r="AB46" t="n">
-        <v>6.3593</v>
+        <v>6.3774</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -8886,10 +8888,10 @@
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>0.3692</v>
+        <v>0.3465</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.4338</v>
+        <v>0.4164</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -8897,21 +8899,21 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>61.73</v>
+        <v>61.41</v>
       </c>
       <c r="AI46" t="n">
-        <v>8.0383</v>
+        <v>8.0853</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>8.0383</v>
+        <v>8.0853</v>
       </c>
       <c r="AL46" t="n">
-        <v>7.2118</v>
+        <v>7.305</v>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
@@ -8922,33 +8924,33 @@
         <v>8.755100000000001</v>
       </c>
       <c r="AO46" t="n">
-        <v>8.860200000000001</v>
+        <v>8.846</v>
       </c>
       <c r="AP46" t="n">
         <v>9.2333</v>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.86; TP3: Classic R1 at 9.23</t>
+          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.85; TP3: Classic R1 at 9.23</t>
         </is>
       </c>
       <c r="AR46" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AU46" t="n">
-        <v>8.92</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="AV46" t="n">
-        <v>10.22</v>
+        <v>9.41</v>
       </c>
       <c r="AW46" t="n">
-        <v>14.87</v>
+        <v>14.2</v>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
@@ -8957,14 +8959,14 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.7))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.4))</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8983,7 +8985,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="F47" t="n">
         <v>0.0303</v>
@@ -9017,10 +9019,10 @@
         <v>41263295</v>
       </c>
       <c r="O47" t="n">
-        <v>78082506</v>
+        <v>17735575</v>
       </c>
       <c r="P47" t="n">
-        <v>1.892</v>
+        <v>0.43</v>
       </c>
       <c r="Q47" t="n">
         <v>32234196</v>
@@ -9036,10 +9038,10 @@
         <v>1.57</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3122</v>
+        <v>1.3174</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1934</v>
+        <v>1.1972</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -9052,13 +9054,13 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>1.4373</v>
+        <v>1.4432</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.3528</v>
+        <v>1.3585</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.1637</v>
+        <v>1.1671</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -9071,10 +9073,10 @@
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>0.0692</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0643</v>
+        <v>0.0645</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
@@ -9082,32 +9084,32 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>59.68</v>
+        <v>60.6</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.4544</v>
+        <v>1.4564</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>1.4544</v>
+        <v>1.4575</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.4538</v>
+        <v>1.32</v>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN47" t="n">
         <v>1.5828</v>
       </c>
       <c r="AO47" t="n">
-        <v>1.6209</v>
+        <v>1.6159</v>
       </c>
       <c r="AP47" t="n">
         <v>1.66</v>
@@ -9118,22 +9120,22 @@
         </is>
       </c>
       <c r="AR47" t="n">
-        <v>218.92</v>
+        <v>0.91</v>
       </c>
       <c r="AS47" t="n">
-        <v>283.88</v>
+        <v>1.15</v>
       </c>
       <c r="AT47" t="n">
-        <v>350.54</v>
+        <v>1.47</v>
       </c>
       <c r="AU47" t="n">
-        <v>8.83</v>
+        <v>8.6</v>
       </c>
       <c r="AV47" t="n">
-        <v>11.45</v>
+        <v>10.87</v>
       </c>
       <c r="AW47" t="n">
-        <v>14.14</v>
+        <v>13.89</v>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
@@ -9142,14 +9144,14 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 60.6))</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9168,7 +9170,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.116</v>
+        <v>1.135</v>
       </c>
       <c r="F48" t="n">
         <v>0.0202</v>
@@ -9191,7 +9193,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>16.17</v>
+        <v>16.45</v>
       </c>
       <c r="M48" t="n">
         <v>0.06900000000000001</v>
@@ -9200,10 +9202,10 @@
         <v>20009945</v>
       </c>
       <c r="O48" t="n">
-        <v>70935053</v>
+        <v>16565868</v>
       </c>
       <c r="P48" t="n">
-        <v>3.545</v>
+        <v>0.828</v>
       </c>
       <c r="Q48" t="n">
         <v>24508494</v>
@@ -9221,10 +9223,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5793</v>
+        <v>0.5939</v>
       </c>
       <c r="W48" t="n">
-        <v>0.4344</v>
+        <v>0.4383</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -9237,13 +9239,13 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>0.8152</v>
+        <v>0.8456</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.6493</v>
+        <v>0.6683</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.4659</v>
+        <v>0.4726</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -9256,10 +9258,10 @@
         </is>
       </c>
       <c r="AE48" t="n">
-        <v>0.1235</v>
+        <v>0.1337</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.1074</v>
+        <v>0.1126</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -9267,58 +9269,58 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>86</v>
+        <v>86.52</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.8085</v>
+        <v>0.8226</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>0.8095</v>
+        <v>0.825</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.595</v>
+        <v>0.8226</v>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN48" t="n">
+        <v>1.1429</v>
+      </c>
+      <c r="AO48" t="n">
         <v>1.2073</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>1.6633</v>
       </c>
-      <c r="AP48" t="n">
-        <v>1.9895</v>
-      </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 1.21; TP2: Classic R3 at 1.66; TP3: Extension at 1.99</t>
+          <t>TP1: Bollinger Upper Band at 1.14; TP2: Classic R2 at 1.21; TP3: Classic R3 at 1.66</t>
         </is>
       </c>
       <c r="AR48" t="n">
-        <v>1.85</v>
+        <v>134.7</v>
       </c>
       <c r="AS48" t="n">
-        <v>3.98</v>
+        <v>161.99</v>
       </c>
       <c r="AT48" t="n">
-        <v>5.5</v>
+        <v>355.21</v>
       </c>
       <c r="AU48" t="n">
-        <v>49.14</v>
+        <v>38.53</v>
       </c>
       <c r="AV48" t="n">
-        <v>105.47</v>
+        <v>46.34</v>
       </c>
       <c r="AW48" t="n">
-        <v>145.77</v>
+        <v>101.61</v>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
@@ -9327,14 +9329,14 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (86.0); entry: enhanced entry at Parabolic SAR (overbought (RSI: 86.0))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (86.5); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 86.5))</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9353,7 +9355,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.515</v>
+        <v>0.514</v>
       </c>
       <c r="F49" t="n">
         <v>0.0103</v>
@@ -9383,10 +9385,10 @@
         <v>20479849</v>
       </c>
       <c r="O49" t="n">
-        <v>21864026</v>
+        <v>5424832</v>
       </c>
       <c r="P49" t="n">
-        <v>1.068</v>
+        <v>0.265</v>
       </c>
       <c r="Q49" t="n">
         <v>18534609</v>
@@ -9402,10 +9404,10 @@
         <v>0.53</v>
       </c>
       <c r="V49" t="n">
-        <v>0.4514</v>
+        <v>0.4532</v>
       </c>
       <c r="W49" t="n">
-        <v>0.468</v>
+        <v>0.4687</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -9418,13 +9420,13 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>0.4995</v>
+        <v>0.5009</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.4698</v>
+        <v>0.4715</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4444</v>
+        <v>0.4451</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
@@ -9437,10 +9439,10 @@
         </is>
       </c>
       <c r="AE49" t="n">
-        <v>0.0247</v>
+        <v>0.0228</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0249</v>
+        <v>0.0245</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -9448,14 +9450,14 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>57.47</v>
+        <v>57.14</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5216</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9493,7 +9495,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9512,7 +9514,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>487.46</v>
+        <v>483.03</v>
       </c>
       <c r="F50" t="n">
         <v>9.7738</v>
@@ -9540,10 +9542,10 @@
         <v>12027</v>
       </c>
       <c r="O50" t="n">
-        <v>6865</v>
+        <v>2353</v>
       </c>
       <c r="P50" t="n">
-        <v>0.571</v>
+        <v>0.196</v>
       </c>
       <c r="Q50" t="n">
         <v>7771</v>
@@ -9561,10 +9563,10 @@
         <v>512</v>
       </c>
       <c r="V50" t="n">
-        <v>404.3772</v>
+        <v>407.0378</v>
       </c>
       <c r="W50" t="n">
-        <v>304.2734</v>
+        <v>305.5485</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -9577,13 +9579,13 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>458.2765</v>
+        <v>460.6339</v>
       </c>
       <c r="AA50" t="n">
-        <v>413.8783</v>
+        <v>416.5902</v>
       </c>
       <c r="AB50" t="n">
-        <v>315.4998</v>
+        <v>317.1668</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -9596,10 +9598,10 @@
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>25.073</v>
+        <v>24.0174</v>
       </c>
       <c r="AF50" t="n">
-        <v>25.1514</v>
+        <v>24.9246</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -9607,21 +9609,21 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>68.52</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AI50" t="n">
-        <v>467.0829</v>
+        <v>467.6419</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>467.0829</v>
+        <v>467.6419</v>
       </c>
       <c r="AL50" t="n">
-        <v>451.4567</v>
+        <v>455.5693</v>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
@@ -9632,33 +9634,33 @@
         <v>501.4547</v>
       </c>
       <c r="AO50" t="n">
-        <v>516.4404</v>
+        <v>514.0105</v>
       </c>
       <c r="AP50" t="n">
         <v>518.9933</v>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 516.44; TP3: Classic R1 at 518.99</t>
+          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 514.01; TP3: Classic R1 at 518.99</t>
         </is>
       </c>
       <c r="AR50" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.16</v>
+        <v>3.84</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="AU50" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="AV50" t="n">
-        <v>10.57</v>
+        <v>9.92</v>
       </c>
       <c r="AW50" t="n">
-        <v>11.11</v>
+        <v>10.98</v>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
@@ -9667,14 +9669,14 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.9))</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9693,7 +9695,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1259.56</v>
+        <v>1265</v>
       </c>
       <c r="F51" t="n">
         <v>25.2348</v>
@@ -9721,10 +9723,10 @@
         <v>2387</v>
       </c>
       <c r="O51" t="n">
-        <v>1513</v>
+        <v>258</v>
       </c>
       <c r="P51" t="n">
-        <v>0.634</v>
+        <v>0.108</v>
       </c>
       <c r="Q51" t="n">
         <v>1079</v>
@@ -9742,10 +9744,10 @@
         <v>1275</v>
       </c>
       <c r="V51" t="n">
-        <v>1169.8348</v>
+        <v>1171.975</v>
       </c>
       <c r="W51" t="n">
-        <v>916.8232</v>
+        <v>919.6207000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -9758,13 +9760,13 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>1225.6731</v>
+        <v>1229.4185</v>
       </c>
       <c r="AA51" t="n">
-        <v>1159.953</v>
+        <v>1164.0725</v>
       </c>
       <c r="AB51" t="n">
-        <v>931.853</v>
+        <v>935.1679</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -9777,10 +9779,10 @@
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>30.7565</v>
+        <v>30.1934</v>
       </c>
       <c r="AF51" t="n">
-        <v>29.4687</v>
+        <v>29.6136</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -9788,21 +9790,21 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>59.82</v>
+        <v>60.68</v>
       </c>
       <c r="AI51" t="n">
-        <v>1244.637</v>
+        <v>1248.6434</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK51" t="n">
-        <v>1257</v>
+        <v>1264.51</v>
       </c>
       <c r="AL51" t="n">
-        <v>1164.1691</v>
+        <v>1171.1494</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
@@ -9810,7 +9812,7 @@
         </is>
       </c>
       <c r="AN51" t="n">
-        <v>1289.9119</v>
+        <v>1291.8306</v>
       </c>
       <c r="AO51" t="n">
         <v>1312.2368</v>
@@ -9820,26 +9822,26 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1289.91; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
+          <t>TP1: Bollinger Upper Band at 1291.83; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
         </is>
       </c>
       <c r="AR51" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AU51" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="AV51" t="n">
-        <v>4.39</v>
+        <v>3.77</v>
       </c>
       <c r="AW51" t="n">
-        <v>6.7</v>
+        <v>6.07</v>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
@@ -9848,14 +9850,14 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 59.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 60.7))</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9874,7 +9876,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>253.22</v>
+        <v>255.15</v>
       </c>
       <c r="F52" t="n">
         <v>4.8762</v>
@@ -9908,10 +9910,10 @@
         <v>93348</v>
       </c>
       <c r="O52" t="n">
-        <v>158545</v>
+        <v>27951</v>
       </c>
       <c r="P52" t="n">
-        <v>1.698</v>
+        <v>0.299</v>
       </c>
       <c r="Q52" t="n">
         <v>38791</v>
@@ -9929,10 +9931,10 @@
         <v>248.96</v>
       </c>
       <c r="V52" t="n">
-        <v>253.818</v>
+        <v>253.221</v>
       </c>
       <c r="W52" t="n">
-        <v>246.187</v>
+        <v>246.717</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -9945,13 +9947,13 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>245.5794</v>
+        <v>246.4909</v>
       </c>
       <c r="AA52" t="n">
-        <v>250.3182</v>
+        <v>250.5077</v>
       </c>
       <c r="AB52" t="n">
-        <v>234.4339</v>
+        <v>234.64</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -9964,10 +9966,10 @@
         </is>
       </c>
       <c r="AE52" t="n">
-        <v>-0.6818</v>
+        <v>0.1279</v>
       </c>
       <c r="AF52" t="n">
-        <v>-2.0813</v>
+        <v>-1.6395</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -9975,58 +9977,58 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>60.23</v>
+        <v>62.43</v>
       </c>
       <c r="AI52" t="n">
-        <v>244.1689</v>
+        <v>244.3668</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK52" t="n">
-        <v>244.1689</v>
+        <v>253.221</v>
       </c>
       <c r="AL52" t="n">
-        <v>239.459</v>
+        <v>246.717</v>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at 200 SMA</t>
         </is>
       </c>
       <c r="AN52" t="n">
+        <v>258.8027</v>
+      </c>
+      <c r="AO52" t="n">
         <v>258.9567</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>258.9862</v>
       </c>
       <c r="AP52" t="n">
         <v>276.4467</v>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 258.96; TP2: 100 SMA at 258.99; TP3: Classic R3 at 276.45</t>
+          <t>TP1: 100 SMA at 258.8; TP2: Classic R2 at 258.96; TP3: Classic R3 at 276.45</t>
         </is>
       </c>
       <c r="AR52" t="n">
-        <v>3.14</v>
+        <v>0.86</v>
       </c>
       <c r="AS52" t="n">
-        <v>3.15</v>
+        <v>0.88</v>
       </c>
       <c r="AT52" t="n">
-        <v>6.85</v>
+        <v>3.57</v>
       </c>
       <c r="AU52" t="n">
-        <v>6.06</v>
+        <v>2.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>6.07</v>
+        <v>2.27</v>
       </c>
       <c r="AW52" t="n">
-        <v>13.22</v>
+        <v>9.17</v>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
@@ -10035,14 +10037,14 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at VWMA (overbought (RSI: 60.2))</t>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 62.4))</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10061,7 +10063,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>202</v>
+        <v>197.01</v>
       </c>
       <c r="F53" t="n">
         <v>3.8473</v>
@@ -10089,10 +10091,10 @@
         <v>93211</v>
       </c>
       <c r="O53" t="n">
-        <v>534027</v>
+        <v>64098</v>
       </c>
       <c r="P53" t="n">
-        <v>5.729</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="Q53" t="n">
         <v>96410</v>
@@ -10110,10 +10112,10 @@
         <v>197.49</v>
       </c>
       <c r="V53" t="n">
-        <v>148.3132</v>
+        <v>149.703</v>
       </c>
       <c r="W53" t="n">
-        <v>124.1303</v>
+        <v>124.6617</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -10126,13 +10128,13 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>172.8546</v>
+        <v>175.1551</v>
       </c>
       <c r="AA53" t="n">
-        <v>152.8321</v>
+        <v>154.5646</v>
       </c>
       <c r="AB53" t="n">
-        <v>121.5505</v>
+        <v>122.3013</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -10145,10 +10147,10 @@
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>16.011</v>
+        <v>15.9284</v>
       </c>
       <c r="AF53" t="n">
-        <v>13.0849</v>
+        <v>13.6536</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -10156,18 +10158,18 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>65.45</v>
+        <v>62.73</v>
       </c>
       <c r="AI53" t="n">
-        <v>177.3174</v>
+        <v>177.9459</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK53" t="n">
-        <v>177.3174</v>
+        <v>177.9459</v>
       </c>
       <c r="AL53" t="n">
         <v>175</v>
@@ -10181,33 +10183,33 @@
         <v>208.4527</v>
       </c>
       <c r="AO53" t="n">
-        <v>217.5058</v>
+        <v>219.5295</v>
       </c>
       <c r="AP53" t="n">
         <v>224.8967</v>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 217.51; TP3: Classic R1 at 224.9</t>
+          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 219.53; TP3: Classic R1 at 224.9</t>
         </is>
       </c>
       <c r="AR53" t="n">
-        <v>13.44</v>
+        <v>10.36</v>
       </c>
       <c r="AS53" t="n">
-        <v>17.34</v>
+        <v>14.12</v>
       </c>
       <c r="AT53" t="n">
-        <v>20.53</v>
+        <v>15.94</v>
       </c>
       <c r="AU53" t="n">
-        <v>17.56</v>
+        <v>17.14</v>
       </c>
       <c r="AV53" t="n">
-        <v>22.66</v>
+        <v>23.37</v>
       </c>
       <c r="AW53" t="n">
-        <v>26.83</v>
+        <v>26.38</v>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
@@ -10216,14 +10218,14 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.7))</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10276,10 +10278,10 @@
         <v>24825730</v>
       </c>
       <c r="O54" t="n">
-        <v>24699717</v>
+        <v>752774</v>
       </c>
       <c r="P54" t="n">
-        <v>0.995</v>
+        <v>0.03</v>
       </c>
       <c r="Q54" t="n">
         <v>14713050</v>
@@ -10297,10 +10299,10 @@
         <v>6.69</v>
       </c>
       <c r="V54" t="n">
-        <v>6.6732</v>
+        <v>6.6958</v>
       </c>
       <c r="W54" t="n">
-        <v>5.8672</v>
+        <v>5.8784</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -10313,13 +10315,13 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>7.2036</v>
+        <v>7.2061</v>
       </c>
       <c r="AA54" t="n">
-        <v>6.7913</v>
+        <v>6.8085</v>
       </c>
       <c r="AB54" t="n">
-        <v>5.8168</v>
+        <v>5.8309</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -10332,10 +10334,10 @@
         </is>
       </c>
       <c r="AE54" t="n">
-        <v>0.1683</v>
+        <v>0.1514</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.2451</v>
+        <v>0.2264</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -10346,18 +10348,18 @@
         <v>54.29</v>
       </c>
       <c r="AI54" t="n">
-        <v>7.3162</v>
+        <v>7.332</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK54" t="n">
-        <v>6.99</v>
+        <v>6.995</v>
       </c>
       <c r="AL54" t="n">
-        <v>6.7691</v>
+        <v>6.8877</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
@@ -10368,33 +10370,33 @@
         <v>7.6476</v>
       </c>
       <c r="AO54" t="n">
+        <v>7.7773</v>
+      </c>
+      <c r="AP54" t="n">
         <v>7.8167</v>
       </c>
-      <c r="AP54" t="n">
-        <v>7.8379</v>
-      </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.65; TP2: Classic R1 at 7.82; TP3: Bollinger Upper Band at 7.84</t>
+          <t>TP1: Fibonacci R1 at 7.65; TP2: Bollinger Upper Band at 7.78; TP3: Classic R1 at 7.82</t>
         </is>
       </c>
       <c r="AR54" t="n">
-        <v>2.98</v>
+        <v>6.08</v>
       </c>
       <c r="AS54" t="n">
-        <v>3.74</v>
+        <v>7.29</v>
       </c>
       <c r="AT54" t="n">
-        <v>3.84</v>
+        <v>7.66</v>
       </c>
       <c r="AU54" t="n">
-        <v>9.41</v>
+        <v>9.33</v>
       </c>
       <c r="AV54" t="n">
-        <v>11.83</v>
+        <v>11.18</v>
       </c>
       <c r="AW54" t="n">
-        <v>12.13</v>
+        <v>11.75</v>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
@@ -10410,7 +10412,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10429,7 +10431,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12.86</v>
+        <v>12.65</v>
       </c>
       <c r="F55" t="n">
         <v>0.2573</v>
@@ -10452,7 +10454,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>14.34</v>
+        <v>14.1</v>
       </c>
       <c r="M55" t="n">
         <v>0.8969</v>
@@ -10461,10 +10463,10 @@
         <v>3426788</v>
       </c>
       <c r="O55" t="n">
-        <v>393581</v>
+        <v>59992</v>
       </c>
       <c r="P55" t="n">
-        <v>0.115</v>
+        <v>0.018</v>
       </c>
       <c r="Q55" t="n">
         <v>776996</v>
@@ -10482,10 +10484,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="V55" t="n">
-        <v>9.532</v>
+        <v>9.6088</v>
       </c>
       <c r="W55" t="n">
-        <v>6.2536</v>
+        <v>6.2991</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -10498,13 +10500,13 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>10.9165</v>
+        <v>11.0816</v>
       </c>
       <c r="AA55" t="n">
-        <v>9.687799999999999</v>
+        <v>9.804</v>
       </c>
       <c r="AB55" t="n">
-        <v>6.8561</v>
+        <v>6.9138</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -10517,10 +10519,10 @@
         </is>
       </c>
       <c r="AE55" t="n">
-        <v>0.9524</v>
+        <v>0.9704</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.6985</v>
+        <v>0.7528</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -10528,18 +10530,18 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>78.81999999999999</v>
+        <v>74.92</v>
       </c>
       <c r="AI55" t="n">
-        <v>10.6114</v>
+        <v>10.6663</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK55" t="n">
-        <v>11.4896</v>
+        <v>11.8515</v>
       </c>
       <c r="AL55" t="n">
         <v>9.4033</v>
@@ -10550,36 +10552,36 @@
         </is>
       </c>
       <c r="AN55" t="n">
-        <v>13.2116</v>
+        <v>13.4067</v>
       </c>
       <c r="AO55" t="n">
-        <v>13.4067</v>
+        <v>13.4463</v>
       </c>
       <c r="AP55" t="n">
         <v>16.3367</v>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 13.21; TP2: Classic R2 at 13.41; TP3: Classic R3 at 16.34</t>
+          <t>TP1: Classic R2 at 13.41; TP2: Bollinger Upper Band at 13.45; TP3: Classic R3 at 16.34</t>
         </is>
       </c>
       <c r="AR55" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.92</v>
+        <v>0.65</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AU55" t="n">
-        <v>14.99</v>
+        <v>13.12</v>
       </c>
       <c r="AV55" t="n">
-        <v>16.69</v>
+        <v>13.46</v>
       </c>
       <c r="AW55" t="n">
-        <v>42.19</v>
+        <v>37.84</v>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
@@ -10588,14 +10590,14 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.8); entry: enhanced entry at Parabolic SAR (overbought (RSI: 78.8))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.9); entry: enhanced entry at Parabolic SAR (overbought (RSI: 74.9))</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10714,7 +10716,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10774,7 +10776,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10793,7 +10795,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>317.8</v>
+        <v>315</v>
       </c>
       <c r="F57" t="n">
         <v>6.2083</v>
@@ -10816,7 +10818,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>13.95</v>
+        <v>13.83</v>
       </c>
       <c r="M57" t="n">
         <v>22.7816</v>
@@ -10825,10 +10827,10 @@
         <v>371623</v>
       </c>
       <c r="O57" t="n">
-        <v>262057</v>
+        <v>83537</v>
       </c>
       <c r="P57" t="n">
-        <v>0.705</v>
+        <v>0.225</v>
       </c>
       <c r="Q57" t="n">
         <v>192429</v>
@@ -10846,10 +10848,10 @@
         <v>252.69</v>
       </c>
       <c r="V57" t="n">
-        <v>244.055</v>
+        <v>246.1548</v>
       </c>
       <c r="W57" t="n">
-        <v>186.0028</v>
+        <v>186.7878</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -10862,13 +10864,13 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>280.4472</v>
+        <v>283.7379</v>
       </c>
       <c r="AA57" t="n">
-        <v>249.2948</v>
+        <v>251.8715</v>
       </c>
       <c r="AB57" t="n">
-        <v>188.3897</v>
+        <v>189.6495</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -10881,10 +10883,10 @@
         </is>
       </c>
       <c r="AE57" t="n">
-        <v>21.4249</v>
+        <v>21.5166</v>
       </c>
       <c r="AF57" t="n">
-        <v>17.4783</v>
+        <v>18.2859</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -10892,18 +10894,18 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>71.12</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="AI57" t="n">
-        <v>281.3536</v>
+        <v>283.248</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK57" t="n">
-        <v>286.2694</v>
+        <v>294.7063</v>
       </c>
       <c r="AL57" t="n">
         <v>251.78</v>
@@ -10914,7 +10916,7 @@
         </is>
       </c>
       <c r="AN57" t="n">
-        <v>330.5792</v>
+        <v>334.962</v>
       </c>
       <c r="AO57" t="n">
         <v>337.12</v>
@@ -10924,26 +10926,26 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 330.58; TP2: Classic R2 at 337.12; TP3: Classic R3 at 398.9</t>
+          <t>TP1: Bollinger Upper Band at 334.96; TP2: Classic R2 at 337.12; TP3: Classic R3 at 398.9</t>
         </is>
       </c>
       <c r="AR57" t="n">
-        <v>1.28</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.47</v>
+        <v>0.99</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.27</v>
+        <v>2.43</v>
       </c>
       <c r="AU57" t="n">
-        <v>15.48</v>
+        <v>13.66</v>
       </c>
       <c r="AV57" t="n">
-        <v>17.76</v>
+        <v>14.39</v>
       </c>
       <c r="AW57" t="n">
-        <v>39.34</v>
+        <v>35.36</v>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
@@ -10952,14 +10954,14 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.1); entry: enhanced entry at Parabolic SAR (overbought (RSI: 71.1))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 69.4))</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10978,7 +10980,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>18.14</v>
+        <v>18.31</v>
       </c>
       <c r="F58" t="n">
         <v>0.3717</v>
@@ -11012,10 +11014,10 @@
         <v>743212</v>
       </c>
       <c r="O58" t="n">
-        <v>1673908</v>
+        <v>198207</v>
       </c>
       <c r="P58" t="n">
-        <v>2.252</v>
+        <v>0.267</v>
       </c>
       <c r="Q58" t="n">
         <v>600156</v>
@@ -11033,10 +11035,10 @@
         <v>16.34</v>
       </c>
       <c r="V58" t="n">
-        <v>16.1212</v>
+        <v>16.1666</v>
       </c>
       <c r="W58" t="n">
-        <v>15.7072</v>
+        <v>15.7363</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -11049,13 +11051,13 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>16.9583</v>
+        <v>17.0871</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.3091</v>
+        <v>16.3876</v>
       </c>
       <c r="AB58" t="n">
-        <v>15.0878</v>
+        <v>15.1199</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -11068,10 +11070,10 @@
         </is>
       </c>
       <c r="AE58" t="n">
-        <v>0.6953</v>
+        <v>0.7131</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.3999</v>
+        <v>0.4625</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -11079,21 +11081,21 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>64.31</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="AI58" t="n">
-        <v>17.469</v>
+        <v>17.5145</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK58" t="n">
-        <v>17.469</v>
+        <v>17.5145</v>
       </c>
       <c r="AL58" t="n">
-        <v>16.8462</v>
+        <v>17.0657</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
@@ -11101,36 +11103,36 @@
         </is>
       </c>
       <c r="AN58" t="n">
-        <v>18.9737</v>
+        <v>19.0869</v>
       </c>
       <c r="AO58" t="n">
-        <v>19.0869</v>
+        <v>19.1845</v>
       </c>
       <c r="AP58" t="n">
         <v>19.6033</v>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 18.97; TP2: Fibonacci R1 at 19.09; TP3: Classic R1 at 19.6</t>
+          <t>TP1: Fibonacci R1 at 19.09; TP2: Bollinger Upper Band at 19.18; TP3: Classic R1 at 19.6</t>
         </is>
       </c>
       <c r="AR58" t="n">
-        <v>2.42</v>
+        <v>3.5</v>
       </c>
       <c r="AS58" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.43</v>
+        <v>4.65</v>
       </c>
       <c r="AU58" t="n">
-        <v>8.609999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="AV58" t="n">
-        <v>9.26</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="AW58" t="n">
-        <v>12.22</v>
+        <v>11.93</v>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
@@ -11139,14 +11141,14 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.5))</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11165,7 +11167,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.747</v>
+        <v>0.751</v>
       </c>
       <c r="F59" t="n">
         <v>0.0124</v>
@@ -11195,10 +11197,10 @@
         <v>23071575</v>
       </c>
       <c r="O59" t="n">
-        <v>245134355</v>
+        <v>111491617</v>
       </c>
       <c r="P59" t="n">
-        <v>10.625</v>
+        <v>4.832</v>
       </c>
       <c r="Q59" t="n">
         <v>24690239</v>
@@ -11216,10 +11218,10 @@
         <v>0.638</v>
       </c>
       <c r="V59" t="n">
-        <v>0.5534</v>
+        <v>0.5594</v>
       </c>
       <c r="W59" t="n">
-        <v>0.4754</v>
+        <v>0.4768</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -11232,13 +11234,13 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>0.5968</v>
+        <v>0.6115</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5656</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.4904</v>
+        <v>0.493</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -11251,10 +11253,10 @@
         </is>
       </c>
       <c r="AE59" t="n">
-        <v>0.0223</v>
+        <v>0.0319</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.0131</v>
+        <v>0.0168</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -11262,18 +11264,18 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>78.16</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.6197</v>
+        <v>0.633</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK59" t="n">
-        <v>0.6435</v>
+        <v>0.678</v>
       </c>
       <c r="AL59" t="n">
         <v>0.586</v>
@@ -11300,14 +11302,14 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.5); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.5))</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11326,7 +11328,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>121.8</v>
+        <v>129</v>
       </c>
       <c r="F60" t="n">
         <v>2.3138</v>
@@ -11354,10 +11356,10 @@
         <v>126779</v>
       </c>
       <c r="O60" t="n">
-        <v>223788</v>
+        <v>594652</v>
       </c>
       <c r="P60" t="n">
-        <v>1.765</v>
+        <v>4.69</v>
       </c>
       <c r="Q60" t="n">
         <v>46537</v>
@@ -11375,10 +11377,10 @@
         <v>136.77</v>
       </c>
       <c r="V60" t="n">
-        <v>101.0582</v>
+        <v>101.6268</v>
       </c>
       <c r="W60" t="n">
-        <v>90.0445</v>
+        <v>90.3091</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -11391,13 +11393,13 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>107.6995</v>
+        <v>109.7281</v>
       </c>
       <c r="AA60" t="n">
-        <v>102.2034</v>
+        <v>103.2542</v>
       </c>
       <c r="AB60" t="n">
-        <v>89.5928</v>
+        <v>89.9849</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -11410,10 +11412,10 @@
         </is>
       </c>
       <c r="AE60" t="n">
-        <v>5.0887</v>
+        <v>6.1386</v>
       </c>
       <c r="AF60" t="n">
-        <v>3.4646</v>
+        <v>3.9994</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -11421,21 +11423,21 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>76.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="AI60" t="n">
-        <v>108.9631</v>
+        <v>111.1727</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK60" t="n">
-        <v>108.9631</v>
+        <v>111.815</v>
       </c>
       <c r="AL60" t="n">
-        <v>105.6229</v>
+        <v>106.386</v>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
@@ -11443,36 +11445,36 @@
         </is>
       </c>
       <c r="AN60" t="n">
-        <v>123.2533</v>
+        <v>143.7933</v>
       </c>
       <c r="AO60" t="n">
-        <v>143.7933</v>
+        <v>159.7824</v>
       </c>
       <c r="AP60" t="n">
-        <v>157.0984</v>
+        <v>151.3402</v>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 123.25; TP2: Classic R3 at 143.79; TP3: Extension at 157.1</t>
+          <t>TP1: Classic R3 at 143.79; TP2: Extension at 159.78; TP3: Extension at 151.34</t>
         </is>
       </c>
       <c r="AR60" t="n">
-        <v>4.28</v>
+        <v>5.89</v>
       </c>
       <c r="AS60" t="n">
-        <v>10.43</v>
+        <v>8.84</v>
       </c>
       <c r="AT60" t="n">
-        <v>14.41</v>
+        <v>7.28</v>
       </c>
       <c r="AU60" t="n">
-        <v>13.11</v>
+        <v>28.6</v>
       </c>
       <c r="AV60" t="n">
-        <v>31.97</v>
+        <v>42.9</v>
       </c>
       <c r="AW60" t="n">
-        <v>44.18</v>
+        <v>35.35</v>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
@@ -11481,14 +11483,14 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.9); entry: enhanced entry at VWMA (overbought (RSI: 76.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 81.4))</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11507,7 +11509,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>11.11</v>
+        <v>11.23</v>
       </c>
       <c r="F61" t="n">
         <v>0.2218</v>
@@ -11535,10 +11537,10 @@
         <v>1639346</v>
       </c>
       <c r="O61" t="n">
-        <v>760782</v>
+        <v>50948</v>
       </c>
       <c r="P61" t="n">
-        <v>0.464</v>
+        <v>0.031</v>
       </c>
       <c r="Q61" t="n">
         <v>613916</v>
@@ -11556,10 +11558,10 @@
         <v>11.74</v>
       </c>
       <c r="V61" t="n">
-        <v>9.6404</v>
+        <v>9.683199999999999</v>
       </c>
       <c r="W61" t="n">
-        <v>8.154500000000001</v>
+        <v>8.178100000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -11572,13 +11574,13 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>10.5804</v>
+        <v>10.6422</v>
       </c>
       <c r="AA61" t="n">
-        <v>9.909000000000001</v>
+        <v>9.960800000000001</v>
       </c>
       <c r="AB61" t="n">
-        <v>8.4308</v>
+        <v>8.4587</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -11591,36 +11593,36 @@
         </is>
       </c>
       <c r="AE61" t="n">
-        <v>0.4743</v>
+        <v>0.4679</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.4739</v>
+        <v>0.4727</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>64.01000000000001</v>
+        <v>65.58</v>
       </c>
       <c r="AI61" t="n">
-        <v>10.5943</v>
+        <v>10.6144</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>10.5943</v>
+        <v>10.6144</v>
       </c>
       <c r="AL61" t="n">
-        <v>9.059100000000001</v>
+        <v>9.3527</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AN61" t="n">
@@ -11630,30 +11632,30 @@
         <v>11.97</v>
       </c>
       <c r="AP61" t="n">
-        <v>12.0381</v>
+        <v>11.9763</v>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.04</t>
+          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 11.98</t>
         </is>
       </c>
       <c r="AR61" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS61" t="n">
-        <v>0.9</v>
+        <v>1.07</v>
       </c>
       <c r="AT61" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="AU61" t="n">
-        <v>8.369999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="AV61" t="n">
-        <v>12.99</v>
+        <v>12.77</v>
       </c>
       <c r="AW61" t="n">
-        <v>13.63</v>
+        <v>12.83</v>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
@@ -11662,14 +11664,14 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.0))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.6))</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11688,7 +11690,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>58.7</v>
+        <v>58.8</v>
       </c>
       <c r="F62" t="n">
         <v>1.1778</v>
@@ -11722,10 +11724,10 @@
         <v>240313</v>
       </c>
       <c r="O62" t="n">
-        <v>306478</v>
+        <v>25548</v>
       </c>
       <c r="P62" t="n">
-        <v>1.275</v>
+        <v>0.106</v>
       </c>
       <c r="Q62" t="n">
         <v>121621</v>
@@ -11743,10 +11745,10 @@
         <v>54.8</v>
       </c>
       <c r="V62" t="n">
-        <v>51.5058</v>
+        <v>51.6702</v>
       </c>
       <c r="W62" t="n">
-        <v>45.8631</v>
+        <v>45.9351</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -11759,13 +11761,13 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>54.3617</v>
+        <v>54.7844</v>
       </c>
       <c r="AA62" t="n">
-        <v>51.6474</v>
+        <v>51.9279</v>
       </c>
       <c r="AB62" t="n">
-        <v>46.4973</v>
+        <v>46.6198</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -11778,10 +11780,10 @@
         </is>
       </c>
       <c r="AE62" t="n">
-        <v>2.1058</v>
+        <v>2.193</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.3943</v>
+        <v>1.554</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -11789,18 +11791,18 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>69.59999999999999</v>
+        <v>69.83</v>
       </c>
       <c r="AI62" t="n">
-        <v>56.1214</v>
+        <v>56.2741</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK62" t="n">
-        <v>57.9</v>
+        <v>58.06</v>
       </c>
       <c r="AL62" t="n">
         <v>50</v>
@@ -11811,36 +11813,36 @@
         </is>
       </c>
       <c r="AN62" t="n">
-        <v>59.9503</v>
+        <v>60.5522</v>
       </c>
       <c r="AO62" t="n">
         <v>64.6233</v>
       </c>
       <c r="AP62" t="n">
-        <v>67.19159999999999</v>
+        <v>67.1305</v>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 59.95; TP2: Classic R3 at 64.62; TP3: Extension at 67.19</t>
+          <t>TP1: Bollinger Upper Band at 60.55; TP2: Classic R3 at 64.62; TP3: Extension at 67.13</t>
         </is>
       </c>
       <c r="AR62" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="AS62" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AU62" t="n">
-        <v>3.54</v>
+        <v>4.29</v>
       </c>
       <c r="AV62" t="n">
-        <v>11.61</v>
+        <v>11.3</v>
       </c>
       <c r="AW62" t="n">
-        <v>16.05</v>
+        <v>15.62</v>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
@@ -11849,14 +11851,14 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 69.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 69.8))</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11875,7 +11877,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7.98</v>
+        <v>7.96</v>
       </c>
       <c r="F63" t="n">
         <v>0.1591</v>
@@ -11909,10 +11911,10 @@
         <v>6727223</v>
       </c>
       <c r="O63" t="n">
-        <v>4135296</v>
+        <v>1412504</v>
       </c>
       <c r="P63" t="n">
-        <v>0.615</v>
+        <v>0.21</v>
       </c>
       <c r="Q63" t="n">
         <v>4721958</v>
@@ -11930,10 +11932,10 @@
         <v>8.51</v>
       </c>
       <c r="V63" t="n">
-        <v>7.5058</v>
+        <v>7.524</v>
       </c>
       <c r="W63" t="n">
-        <v>5.5555</v>
+        <v>5.5755</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -11946,13 +11948,13 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7.9737</v>
+        <v>7.9724</v>
       </c>
       <c r="AA63" t="n">
-        <v>7.5396</v>
+        <v>7.5561</v>
       </c>
       <c r="AB63" t="n">
-        <v>6.0224</v>
+        <v>6.0417</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -11965,10 +11967,10 @@
         </is>
       </c>
       <c r="AE63" t="n">
-        <v>0.1434</v>
+        <v>0.1265</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.2138</v>
+        <v>0.1964</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -11976,58 +11978,58 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>54.16</v>
+        <v>53.26</v>
       </c>
       <c r="AI63" t="n">
-        <v>8.1044</v>
+        <v>8.132400000000001</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK63" t="n">
-        <v>7.6841</v>
+        <v>7.855</v>
       </c>
       <c r="AL63" t="n">
-        <v>7.4249</v>
+        <v>7.7507</v>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>stop at Fibonacci S1</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AN63" t="n">
         <v>8.395099999999999</v>
       </c>
       <c r="AO63" t="n">
-        <v>8.526899999999999</v>
+        <v>8.4923</v>
       </c>
       <c r="AP63" t="n">
         <v>8.58</v>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.4; TP2: Bollinger Upper Band at 8.53; TP3: Classic R1 at 8.58</t>
+          <t>TP1: Fibonacci R1 at 8.4; TP2: Bollinger Upper Band at 8.49; TP3: Classic R1 at 8.58</t>
         </is>
       </c>
       <c r="AR63" t="n">
-        <v>2.74</v>
+        <v>5.18</v>
       </c>
       <c r="AS63" t="n">
-        <v>3.25</v>
+        <v>6.11</v>
       </c>
       <c r="AT63" t="n">
-        <v>3.46</v>
+        <v>6.95</v>
       </c>
       <c r="AU63" t="n">
-        <v>9.25</v>
+        <v>6.88</v>
       </c>
       <c r="AV63" t="n">
-        <v>10.97</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AW63" t="n">
-        <v>11.66</v>
+        <v>9.23</v>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
@@ -12036,14 +12038,14 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 54.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.3))</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12062,7 +12064,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>24.77</v>
+        <v>25.2</v>
       </c>
       <c r="F64" t="n">
         <v>0.4891</v>
@@ -12096,10 +12098,10 @@
         <v>686697</v>
       </c>
       <c r="O64" t="n">
-        <v>1245307</v>
+        <v>222315</v>
       </c>
       <c r="P64" t="n">
-        <v>1.813</v>
+        <v>0.324</v>
       </c>
       <c r="Q64" t="n">
         <v>720244</v>
@@ -12117,10 +12119,10 @@
         <v>23.95</v>
       </c>
       <c r="V64" t="n">
-        <v>22.447</v>
+        <v>22.524</v>
       </c>
       <c r="W64" t="n">
-        <v>22.7397</v>
+        <v>22.7523</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -12133,13 +12135,13 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>23.2817</v>
+        <v>23.4644</v>
       </c>
       <c r="AA64" t="n">
-        <v>22.7266</v>
+        <v>22.8236</v>
       </c>
       <c r="AB64" t="n">
-        <v>22.0786</v>
+        <v>22.1096</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -12152,10 +12154,10 @@
         </is>
       </c>
       <c r="AE64" t="n">
-        <v>0.4469</v>
+        <v>0.5438</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.3148</v>
+        <v>0.3606</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -12163,14 +12165,14 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>73.25</v>
+        <v>76.11</v>
       </c>
       <c r="AI64" t="n">
-        <v>23.4085</v>
+        <v>23.465</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr"/>
@@ -12208,7 +12210,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12227,7 +12229,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42</v>
+        <v>42.45</v>
       </c>
       <c r="F65" t="n">
         <v>0.8284</v>
@@ -12261,10 +12263,10 @@
         <v>3863627</v>
       </c>
       <c r="O65" t="n">
-        <v>4635318</v>
+        <v>361229</v>
       </c>
       <c r="P65" t="n">
-        <v>1.2</v>
+        <v>0.093</v>
       </c>
       <c r="Q65" t="n">
         <v>1754099</v>
@@ -12282,10 +12284,10 @@
         <v>39.7</v>
       </c>
       <c r="V65" t="n">
-        <v>38.4864</v>
+        <v>38.6414</v>
       </c>
       <c r="W65" t="n">
-        <v>28.9939</v>
+        <v>29.0996</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -12298,13 +12300,13 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>39.8137</v>
+        <v>40.0648</v>
       </c>
       <c r="AA65" t="n">
-        <v>37.8192</v>
+        <v>38.0008</v>
       </c>
       <c r="AB65" t="n">
-        <v>30.5852</v>
+        <v>30.7033</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
@@ -12317,10 +12319,10 @@
         </is>
       </c>
       <c r="AE65" t="n">
-        <v>0.8296</v>
+        <v>0.9402</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7594</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -12328,25 +12330,25 @@
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>67.45</v>
+        <v>69.31</v>
       </c>
       <c r="AI65" t="n">
-        <v>39.9606</v>
+        <v>40.013</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-08-05 16:45:52</t>
+          <t>2026-08-06 08:06:57</t>
         </is>
       </c>
       <c r="AK65" t="n">
-        <v>40.6</v>
+        <v>40.76</v>
       </c>
       <c r="AL65" t="n">
-        <v>38.4</v>
+        <v>38.5347</v>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN65" t="n">
@@ -12356,30 +12358,30 @@
         <v>45.6033</v>
       </c>
       <c r="AP65" t="n">
-        <v>47.5146</v>
+        <v>47.4534</v>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 42.46; TP2: Classic R3 at 45.6; TP3: Extension at 47.51</t>
+          <t>TP1: Classic R2 at 42.46; TP2: Classic R3 at 45.6; TP3: Extension at 47.45</t>
         </is>
       </c>
       <c r="AR65" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AS65" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="AU65" t="n">
-        <v>4.59</v>
+        <v>4.18</v>
       </c>
       <c r="AV65" t="n">
-        <v>12.32</v>
+        <v>11.88</v>
       </c>
       <c r="AW65" t="n">
-        <v>17.03</v>
+        <v>16.42</v>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
@@ -12388,7 +12390,7 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 67.5))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 69.3))</t>
         </is>
       </c>
     </row>
@@ -12500,34 +12502,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54659.6</v>
+        <v>54805.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="F2" t="n">
-        <v>64.81</v>
+        <v>65.81</v>
       </c>
       <c r="G2" t="n">
-        <v>52495.97</v>
+        <v>52536.58</v>
       </c>
       <c r="H2" t="n">
-        <v>46950.9</v>
+        <v>47039.44</v>
       </c>
       <c r="I2" t="n">
-        <v>53429.72</v>
+        <v>53560.77</v>
       </c>
       <c r="J2" t="n">
-        <v>52542.04</v>
+        <v>52630.81</v>
       </c>
       <c r="K2" t="n">
-        <v>47286.76</v>
+        <v>47361.57</v>
       </c>
       <c r="L2" t="n">
-        <v>611.6</v>
+        <v>644.64</v>
       </c>
       <c r="M2" t="n">
-        <v>497.65</v>
+        <v>527.05</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -12536,7 +12538,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-05 16:46:02</t>
+          <t>2026-08-06 08:07:09</t>
         </is>
       </c>
     </row>
@@ -12557,34 +12559,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19765.3</v>
+        <v>20009.4</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.16</v>
+        <v>1.23</v>
       </c>
       <c r="F3" t="n">
-        <v>87.68000000000001</v>
+        <v>88.63</v>
       </c>
       <c r="G3" t="n">
-        <v>16289.28</v>
+        <v>16394.04</v>
       </c>
       <c r="H3" t="n">
-        <v>13645.27</v>
+        <v>13688.62</v>
       </c>
       <c r="I3" t="n">
-        <v>17964.33</v>
+        <v>18159.1</v>
       </c>
       <c r="J3" t="n">
-        <v>16604.74</v>
+        <v>16738.26</v>
       </c>
       <c r="K3" t="n">
-        <v>13903.74</v>
+        <v>13964.49</v>
       </c>
       <c r="L3" t="n">
-        <v>961.38</v>
+        <v>1004.9</v>
       </c>
       <c r="M3" t="n">
-        <v>786.49</v>
+        <v>830.17</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -12593,7 +12595,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-05 16:46:02</t>
+          <t>2026-08-06 08:07:09</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9.27</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.1835</v>
@@ -742,10 +742,10 @@
         <v>7895172</v>
       </c>
       <c r="O2" t="n">
-        <v>4627603</v>
+        <v>8848972</v>
       </c>
       <c r="P2" t="n">
-        <v>0.586</v>
+        <v>1.121</v>
       </c>
       <c r="Q2" t="n">
         <v>3770499</v>
@@ -763,10 +763,10 @@
         <v>9.3695</v>
       </c>
       <c r="V2" t="n">
-        <v>8.1982</v>
+        <v>8.195</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6586</v>
+        <v>7.6578</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>8.632</v>
+        <v>8.6168</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.347099999999999</v>
+        <v>8.3408</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.9267</v>
+        <v>7.9251</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>0.3146</v>
+        <v>0.3018</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2168</v>
+        <v>0.2142</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>67.22</v>
+        <v>63.7</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.718</v>
+        <v>8.722200000000001</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK2" t="n">
-        <v>8.718</v>
+        <v>8.722200000000001</v>
       </c>
       <c r="AL2" t="n">
         <v>8.462</v>
@@ -837,30 +837,30 @@
         <v>9.416700000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.456300000000001</v>
+        <v>9.923299999999999</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 9.39; TP2: Classic R1 at 9.42; TP3: Bollinger Upper Band at 9.46</t>
+          <t>TP1: Fibonacci R2 at 9.39; TP2: Classic R1 at 9.42; TP3: Classic R2 at 9.92</t>
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.88</v>
+        <v>4.62</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.74</v>
+        <v>7.68</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.01</v>
+        <v>7.96</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.470000000000001</v>
+        <v>13.77</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.7))</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58.94</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>1.1527</v>
@@ -929,10 +929,10 @@
         <v>716819</v>
       </c>
       <c r="O3" t="n">
-        <v>857198</v>
+        <v>1161742</v>
       </c>
       <c r="P3" t="n">
-        <v>1.196</v>
+        <v>1.621</v>
       </c>
       <c r="Q3" t="n">
         <v>179038</v>
@@ -950,10 +950,10 @@
         <v>58.5</v>
       </c>
       <c r="V3" t="n">
-        <v>56.251</v>
+        <v>56.2522</v>
       </c>
       <c r="W3" t="n">
-        <v>51.6407</v>
+        <v>51.641</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>56.5428</v>
+        <v>56.5485</v>
       </c>
       <c r="AA3" t="n">
-        <v>55.8511</v>
+        <v>55.8535</v>
       </c>
       <c r="AB3" t="n">
-        <v>50.1228</v>
+        <v>50.1234</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>0.4529</v>
+        <v>0.4577</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2553</v>
+        <v>0.2562</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -996,18 +996,18 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>64.69</v>
+        <v>64.92</v>
       </c>
       <c r="AI3" t="n">
-        <v>56.6582</v>
+        <v>56.72</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>56.7</v>
+        <v>56.72</v>
       </c>
       <c r="AL3" t="n">
         <v>55.77</v>
@@ -1024,30 +1024,30 @@
         <v>64.86669999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>67.9864</v>
+        <v>67.97880000000001</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 60.57; TP2: Classic R3 at 64.87; TP3: Extension at 67.99</t>
+          <t>TP1: Classic R2 at 60.57; TP2: Classic R3 at 64.87; TP3: Extension at 67.98</t>
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.14</v>
+        <v>11.85</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.82</v>
+        <v>6.78</v>
       </c>
       <c r="AV3" t="n">
-        <v>14.4</v>
+        <v>14.36</v>
       </c>
       <c r="AW3" t="n">
-        <v>19.91</v>
+        <v>19.85</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.7))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.9))</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>32.61</v>
+        <v>31.59</v>
       </c>
       <c r="F4" t="n">
         <v>0.615</v>
@@ -1116,10 +1116,10 @@
         <v>1584348</v>
       </c>
       <c r="O4" t="n">
-        <v>5849295</v>
+        <v>8629992</v>
       </c>
       <c r="P4" t="n">
-        <v>3.692</v>
+        <v>5.447</v>
       </c>
       <c r="Q4" t="n">
         <v>1292426</v>
@@ -1137,10 +1137,10 @@
         <v>31.5318</v>
       </c>
       <c r="V4" t="n">
-        <v>28.1788</v>
+        <v>28.1584</v>
       </c>
       <c r="W4" t="n">
-        <v>27.0448</v>
+        <v>27.0397</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>28.5549</v>
+        <v>28.4578</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.2531</v>
+        <v>28.2131</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.0907</v>
+        <v>26.0806</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>0.5576</v>
+        <v>0.4763</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0513</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1183,18 +1183,18 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>79.13</v>
+        <v>75.97</v>
       </c>
       <c r="AI4" t="n">
-        <v>29.0961</v>
+        <v>29.1133</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>29.655</v>
+        <v>29.7</v>
       </c>
       <c r="AL4" t="n">
         <v>27.49</v>
@@ -1204,16 +1204,38 @@
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
+      <c r="AN4" t="n">
+        <v>32.3233</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>33.635</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>32.9424</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 32.32; TP2: Extension at 33.63; TP3: Extension at 32.94</t>
+        </is>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>10.92</v>
+      </c>
       <c r="AX4" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -1221,7 +1243,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.1))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.0))</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1269,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23.93</v>
+        <v>23.47</v>
       </c>
       <c r="F5" t="n">
         <v>0.4766</v>
@@ -1281,10 +1303,10 @@
         <v>3299828</v>
       </c>
       <c r="O5" t="n">
-        <v>1774753</v>
+        <v>3568752</v>
       </c>
       <c r="P5" t="n">
-        <v>0.538</v>
+        <v>1.081</v>
       </c>
       <c r="Q5" t="n">
         <v>1470988</v>
@@ -1302,10 +1324,10 @@
         <v>24</v>
       </c>
       <c r="V5" t="n">
-        <v>22.029</v>
+        <v>22.0198</v>
       </c>
       <c r="W5" t="n">
-        <v>19.5203</v>
+        <v>19.518</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1318,13 +1340,13 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>22.9397</v>
+        <v>22.8959</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.1873</v>
+        <v>22.1693</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.623</v>
+        <v>19.6185</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1337,10 +1359,10 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.5523</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.445</v>
+        <v>0.4377</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1348,18 +1370,18 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>61.57</v>
+        <v>57.03</v>
       </c>
       <c r="AI5" t="n">
-        <v>23.3371</v>
+        <v>23.3295</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>23.3371</v>
+        <v>23.3295</v>
       </c>
       <c r="AL5" t="n">
         <v>22.3149</v>
@@ -1370,36 +1392,36 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>24.2676</v>
+        <v>23.7306</v>
       </c>
       <c r="AO5" t="n">
+        <v>24.1871</v>
+      </c>
+      <c r="AP5" t="n">
         <v>24.3367</v>
       </c>
-      <c r="AP5" t="n">
-        <v>24.6061</v>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 24.27; TP2: Classic R1 at 24.34; TP3: Fibonacci R2 at 24.61</t>
+          <t>TP1: Fibonacci R1 at 23.73; TP2: Bollinger Upper Band at 24.19; TP3: Classic R1 at 24.34</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.91</v>
+        <v>0.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.24</v>
+        <v>0.99</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.99</v>
+        <v>1.72</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.28</v>
+        <v>3.68</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.44</v>
+        <v>4.32</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1408,7 +1430,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.0))</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1456,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298</v>
+        <v>297.79</v>
       </c>
       <c r="F6" t="n">
         <v>5.9428</v>
@@ -1468,10 +1490,10 @@
         <v>307264</v>
       </c>
       <c r="O6" t="n">
-        <v>60574</v>
+        <v>82594</v>
       </c>
       <c r="P6" t="n">
-        <v>0.197</v>
+        <v>0.269</v>
       </c>
       <c r="Q6" t="n">
         <v>56061</v>
@@ -1489,10 +1511,10 @@
         <v>302.7</v>
       </c>
       <c r="V6" t="n">
-        <v>302.7716</v>
+        <v>302.7674</v>
       </c>
       <c r="W6" t="n">
-        <v>260.4559</v>
+        <v>260.4548</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1505,13 +1527,13 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>298.1513</v>
+        <v>298.1313</v>
       </c>
       <c r="AA6" t="n">
-        <v>299.0119</v>
+        <v>299.0036</v>
       </c>
       <c r="AB6" t="n">
-        <v>263.5806</v>
+        <v>263.5786</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1524,10 +1546,10 @@
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>-0.5372</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.5135</v>
+        <v>-0.5168</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1535,18 +1557,18 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>49.29</v>
+        <v>49.04</v>
       </c>
       <c r="AI6" t="n">
-        <v>300.2723</v>
+        <v>300.2475</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>290.3389</v>
+        <v>290.3239</v>
       </c>
       <c r="AL6" t="n">
         <v>285.9946</v>
@@ -1557,10 +1579,10 @@
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>302.2504</v>
+        <v>302.2483</v>
       </c>
       <c r="AO6" t="n">
-        <v>307.2521</v>
+        <v>307.2461</v>
       </c>
       <c r="AP6" t="n">
         <v>308.3187</v>
@@ -1571,22 +1593,22 @@
         </is>
       </c>
       <c r="AR6" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.14</v>
+        <v>4.16</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.1</v>
+        <v>4.11</v>
       </c>
       <c r="AV6" t="n">
         <v>5.83</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.19</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1595,7 +1617,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.0))</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1643,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
       <c r="F7" t="n">
         <v>0.2612</v>
@@ -1655,10 +1677,10 @@
         <v>6460684</v>
       </c>
       <c r="O7" t="n">
-        <v>13376851</v>
+        <v>16249366</v>
       </c>
       <c r="P7" t="n">
-        <v>2.071</v>
+        <v>2.515</v>
       </c>
       <c r="Q7" t="n">
         <v>4078695</v>
@@ -1676,10 +1698,10 @@
         <v>13.5589</v>
       </c>
       <c r="V7" t="n">
-        <v>11.9164</v>
+        <v>11.9114</v>
       </c>
       <c r="W7" t="n">
-        <v>11.3442</v>
+        <v>11.3429</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1692,13 +1714,13 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>12.2494</v>
+        <v>12.2256</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.8939</v>
+        <v>11.8841</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.1254</v>
+        <v>11.1229</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1711,10 +1733,10 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.4068</v>
+        <v>0.3868</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1579</v>
+        <v>0.1539</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1722,18 +1744,18 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>68.11</v>
+        <v>66.37</v>
       </c>
       <c r="AI7" t="n">
-        <v>13.068</v>
+        <v>13.0588</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>13.068</v>
+        <v>13.0588</v>
       </c>
       <c r="AL7" t="n">
         <v>11.7029</v>
@@ -1743,16 +1765,38 @@
           <t>stop at Parabolic SAR</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>13.567</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>13.8211</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13.6869</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 13.57; TP2: Extension at 13.82; TP3: Extension at 13.69</t>
+        </is>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.81</v>
+      </c>
       <c r="AX7" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -1760,7 +1804,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.4))</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1830,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>27.17</v>
+        <v>26.9</v>
       </c>
       <c r="F8" t="n">
         <v>0.5353</v>
@@ -1817,22 +1861,22 @@
         <v>1.8649</v>
       </c>
       <c r="N8" t="n">
-        <v>1330781</v>
+        <v>1319126</v>
       </c>
       <c r="O8" t="n">
-        <v>1693297</v>
+        <v>2336198</v>
       </c>
       <c r="P8" t="n">
-        <v>1.272</v>
+        <v>1.771</v>
       </c>
       <c r="Q8" t="n">
-        <v>746222</v>
+        <v>704810</v>
       </c>
       <c r="R8" t="n">
         <v>1422285</v>
       </c>
       <c r="S8" t="n">
-        <v>1.906</v>
+        <v>2.018</v>
       </c>
       <c r="T8" t="n">
         <v>26.51</v>
@@ -1841,10 +1885,10 @@
         <v>27.6942</v>
       </c>
       <c r="V8" t="n">
-        <v>29.8738</v>
+        <v>29.8684</v>
       </c>
       <c r="W8" t="n">
-        <v>27.1705</v>
+        <v>27.1691</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1857,13 +1901,13 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>29.9582</v>
+        <v>29.9325</v>
       </c>
       <c r="AA8" t="n">
-        <v>29.6548</v>
+        <v>29.6443</v>
       </c>
       <c r="AB8" t="n">
-        <v>27.4856</v>
+        <v>27.4829</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1876,10 +1920,10 @@
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.114</v>
+        <v>0.0925</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0047</v>
+        <v>0.0004</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1887,18 +1931,18 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>39.4</v>
+        <v>38.65</v>
       </c>
       <c r="AI8" t="n">
-        <v>31.065</v>
+        <v>30.9698</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>26.7813</v>
+        <v>26.7188</v>
       </c>
       <c r="AL8" t="n">
         <v>26.51</v>
@@ -1909,36 +1953,36 @@
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>27.1705</v>
+        <v>27.1691</v>
       </c>
       <c r="AO8" t="n">
-        <v>28.5555</v>
+        <v>28.5528</v>
       </c>
       <c r="AP8" t="n">
         <v>30.8533</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 27.17; TP2: 100 SMA at 28.56; TP3: Classic R1 at 30.85</t>
+          <t>TP1: 200 SMA at 27.17; TP2: 100 SMA at 28.55; TP3: Classic R1 at 30.85</t>
         </is>
       </c>
       <c r="AR8" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.54</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.01</v>
+        <v>19.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.62</v>
+        <v>6.86</v>
       </c>
       <c r="AW8" t="n">
-        <v>15.2</v>
+        <v>15.47</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -1947,7 +1991,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 39.4))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 38.7))</t>
         </is>
       </c>
     </row>
@@ -1973,7 +2017,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>192.8</v>
+        <v>191.53</v>
       </c>
       <c r="F9" t="n">
         <v>3.7691</v>
@@ -2007,10 +2051,10 @@
         <v>182504</v>
       </c>
       <c r="O9" t="n">
-        <v>251317</v>
+        <v>280484</v>
       </c>
       <c r="P9" t="n">
-        <v>1.377</v>
+        <v>1.537</v>
       </c>
       <c r="Q9" t="n">
         <v>38504</v>
@@ -2028,10 +2072,10 @@
         <v>194.883</v>
       </c>
       <c r="V9" t="n">
-        <v>182.455</v>
+        <v>182.4296</v>
       </c>
       <c r="W9" t="n">
-        <v>163.1612</v>
+        <v>163.1549</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2044,13 +2088,13 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>184.3417</v>
+        <v>184.2208</v>
       </c>
       <c r="AA9" t="n">
-        <v>183.0146</v>
+        <v>182.9648</v>
       </c>
       <c r="AB9" t="n">
-        <v>158.2899</v>
+        <v>158.2772</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2063,10 +2107,10 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>2.2098</v>
+        <v>2.1085</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5093</v>
+        <v>1.4891</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -2074,14 +2118,14 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>63.57</v>
+        <v>62.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>186.2049</v>
+        <v>186.1282</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -2096,37 +2140,37 @@
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>194.5497</v>
+        <v>192.0267</v>
       </c>
       <c r="AO9" t="n">
+        <v>194.2851</v>
+      </c>
+      <c r="AP9" t="n">
         <v>194.9533</v>
       </c>
-      <c r="AP9" t="n">
-        <v>197.9267</v>
-      </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 194.55; TP2: Classic R1 at 194.95; TP3: Fibonacci R2 at 197.93</t>
+          <t>TP1: Fibonacci R1 at 192.03; TP2: Bollinger Upper Band at 194.29; TP3: Classic R1 at 194.95</t>
         </is>
       </c>
       <c r="AR9" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="AS9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AT9" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AT9" t="n">
-        <v>0.99</v>
-      </c>
       <c r="AU9" t="n">
-        <v>3.48</v>
+        <v>2.14</v>
       </c>
       <c r="AV9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AW9" t="n">
         <v>3.69</v>
       </c>
-      <c r="AW9" t="n">
-        <v>5.27</v>
-      </c>
       <c r="AX9" t="inlineStr">
         <is>
           <t>Buy</t>
@@ -2134,7 +2178,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 63.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 62.2))</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2204,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="F10" t="n">
         <v>1.4169</v>
@@ -2192,7 +2236,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>126491</v>
+        <v>143821</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -2201,10 +2245,10 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>725.2214</v>
+        <v>725.1214</v>
       </c>
       <c r="W10" t="n">
-        <v>548.5348</v>
+        <v>548.5098</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2217,13 +2261,13 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>711.8599</v>
+        <v>711.3837</v>
       </c>
       <c r="AA10" t="n">
-        <v>699.3622</v>
+        <v>699.1662</v>
       </c>
       <c r="AB10" t="n">
-        <v>570.9257</v>
+        <v>570.8759</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2236,10 +2280,10 @@
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>0.2308</v>
+        <v>-0.1681</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1.6185</v>
+        <v>-1.6982</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2247,14 +2291,14 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>55.39</v>
+        <v>53.24</v>
       </c>
       <c r="AI10" t="n">
-        <v>705.3439</v>
+        <v>705.2382</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2272,21 +2316,21 @@
         <v>728.646</v>
       </c>
       <c r="AO10" t="n">
-        <v>730.8105</v>
+        <v>729.922</v>
       </c>
       <c r="AP10" t="n">
         <v>736.8</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 728.65; TP2: Bollinger Upper Band at 730.81; TP3: Classic R1 at 736.8</t>
+          <t>TP1: Fibonacci R1 at 728.65; TP2: Bollinger Upper Band at 729.92; TP3: Classic R1 at 736.8</t>
         </is>
       </c>
       <c r="AR10" t="n">
         <v>1.21</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AT10" t="n">
         <v>1.65</v>
@@ -2295,7 +2339,7 @@
         <v>3.13</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.44</v>
+        <v>3.32</v>
       </c>
       <c r="AW10" t="n">
         <v>4.29</v>
@@ -2307,7 +2351,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.2))</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2377,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.33</v>
+        <v>25.88</v>
       </c>
       <c r="F11" t="n">
         <v>0.5255</v>
@@ -2367,10 +2411,10 @@
         <v>1297772</v>
       </c>
       <c r="O11" t="n">
-        <v>4615730</v>
+        <v>5566988</v>
       </c>
       <c r="P11" t="n">
-        <v>3.557</v>
+        <v>4.29</v>
       </c>
       <c r="Q11" t="n">
         <v>1040711</v>
@@ -2388,10 +2432,10 @@
         <v>23.47</v>
       </c>
       <c r="V11" t="n">
-        <v>23.1134</v>
+        <v>23.1044</v>
       </c>
       <c r="W11" t="n">
-        <v>23.0042</v>
+        <v>23.0019</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2404,13 +2448,13 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>23.6457</v>
+        <v>23.6028</v>
       </c>
       <c r="AA11" t="n">
-        <v>23.2319</v>
+        <v>23.2143</v>
       </c>
       <c r="AB11" t="n">
-        <v>22.9891</v>
+        <v>22.9846</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2423,10 +2467,10 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.5463</v>
+        <v>0.5104</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1834</v>
+        <v>0.1762</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2434,21 +2478,21 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>80.02</v>
+        <v>73.55</v>
       </c>
       <c r="AI11" t="n">
-        <v>24.5936</v>
+        <v>24.5771</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>24.5936</v>
+        <v>24.5771</v>
       </c>
       <c r="AL11" t="n">
-        <v>23.0042</v>
+        <v>23.0019</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
@@ -2472,7 +2516,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (80.0); entry: enhanced entry at VWMA (overbought (RSI: 80.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.6); entry: enhanced entry at VWMA (overbought (RSI: 73.6))</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2542,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15.29</v>
+        <v>15.15</v>
       </c>
       <c r="F12" t="n">
         <v>0.3081</v>
@@ -2532,10 +2576,10 @@
         <v>17297057</v>
       </c>
       <c r="O12" t="n">
-        <v>5063409</v>
+        <v>6772138</v>
       </c>
       <c r="P12" t="n">
-        <v>0.293</v>
+        <v>0.392</v>
       </c>
       <c r="Q12" t="n">
         <v>7505388</v>
@@ -2553,10 +2597,10 @@
         <v>16.08</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9836</v>
+        <v>14.9808</v>
       </c>
       <c r="W12" t="n">
-        <v>10.5283</v>
+        <v>10.5276</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2569,13 +2613,13 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>14.922</v>
+        <v>14.9087</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.4193</v>
+        <v>14.4138</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.3662</v>
+        <v>11.3648</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -2588,10 +2632,10 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>0.0992</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0455</v>
+        <v>0.0433</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2599,14 +2643,14 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>58.31</v>
+        <v>55.48</v>
       </c>
       <c r="AI12" t="n">
-        <v>14.9479</v>
+        <v>14.9468</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -2624,33 +2668,33 @@
         <v>15.3884</v>
       </c>
       <c r="AO12" t="n">
-        <v>15.4162</v>
+        <v>15.7933</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.7933</v>
+        <v>16.8533</v>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 15.39; TP2: Bollinger Upper Band at 15.42; TP3: Classic R2 at 15.79</t>
+          <t>TP1: Fibonacci R2 at 15.39; TP2: Classic R2 at 15.79; TP3: Classic R3 at 16.85</t>
         </is>
       </c>
       <c r="AR12" t="n">
         <v>0.82</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.88</v>
+        <v>1.73</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.73</v>
+        <v>4.11</v>
       </c>
       <c r="AU12" t="n">
         <v>2.42</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.6</v>
+        <v>5.11</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.11</v>
+        <v>12.17</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2659,7 +2703,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 58.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.5))</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2729,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>109.89</v>
+        <v>109.49</v>
       </c>
       <c r="F13" t="n">
         <v>2.2136</v>
@@ -2702,7 +2746,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>314.9873</v>
+        <v>315.2301</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2713,16 +2757,16 @@
         <v>2.94</v>
       </c>
       <c r="M13" t="n">
-        <v>37.7678</v>
+        <v>37.8016</v>
       </c>
       <c r="N13" t="n">
         <v>1032117</v>
       </c>
       <c r="O13" t="n">
-        <v>511819</v>
+        <v>647426</v>
       </c>
       <c r="P13" t="n">
-        <v>0.496</v>
+        <v>0.627</v>
       </c>
       <c r="Q13" t="n">
         <v>344782</v>
@@ -2740,10 +2784,10 @@
         <v>111.2082</v>
       </c>
       <c r="V13" t="n">
-        <v>97.8826</v>
+        <v>97.8746</v>
       </c>
       <c r="W13" t="n">
-        <v>81.0151</v>
+        <v>81.01309999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2756,13 +2800,13 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>104.1328</v>
+        <v>104.0947</v>
       </c>
       <c r="AA13" t="n">
-        <v>99.3111</v>
+        <v>99.2954</v>
       </c>
       <c r="AB13" t="n">
-        <v>82.5776</v>
+        <v>82.5736</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -2775,10 +2819,10 @@
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>3.7256</v>
+        <v>3.6937</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.1054</v>
+        <v>3.099</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2786,14 +2830,14 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>63.56</v>
+        <v>62.69</v>
       </c>
       <c r="AI13" t="n">
-        <v>104.6169</v>
+        <v>104.6412</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2814,11 +2858,11 @@
         <v>111.0823</v>
       </c>
       <c r="AP13" t="n">
-        <v>112.8709</v>
+        <v>112.797</v>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 110.39; TP2: Fibonacci R2 at 111.08; TP3: Bollinger Upper Band at 112.87</t>
+          <t>TP1: Classic R1 at 110.39; TP2: Fibonacci R2 at 111.08; TP3: Bollinger Upper Band at 112.8</t>
         </is>
       </c>
       <c r="AR13" t="n">
@@ -2837,7 +2881,7 @@
         <v>3.89</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2846,7 +2890,7 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 63.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 62.7))</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2916,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.26</v>
+        <v>6.17</v>
       </c>
       <c r="F14" t="n">
         <v>0.1151</v>
@@ -2906,10 +2950,10 @@
         <v>12822504</v>
       </c>
       <c r="O14" t="n">
-        <v>27838921</v>
+        <v>31286931</v>
       </c>
       <c r="P14" t="n">
-        <v>2.171</v>
+        <v>2.44</v>
       </c>
       <c r="Q14" t="n">
         <v>7395142</v>
@@ -2927,10 +2971,10 @@
         <v>5.15</v>
       </c>
       <c r="V14" t="n">
-        <v>5.1512</v>
+        <v>5.1494</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1038</v>
+        <v>4.1034</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2943,13 +2987,13 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>5.4273</v>
+        <v>5.4187</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.1502</v>
+        <v>5.1467</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.3353</v>
+        <v>4.3344</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2962,10 +3006,10 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>0.2525</v>
+        <v>0.2453</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1412</v>
+        <v>0.1397</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2973,18 +3017,18 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>71.59</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.7505</v>
+        <v>5.7472</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>5.7505</v>
+        <v>5.75</v>
       </c>
       <c r="AL14" t="n">
         <v>5.5696</v>
@@ -3011,7 +3055,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.6); entry: enhanced entry at VWMA (overbought (RSI: 71.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 70.4))</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3081,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.07</v>
+        <v>5.88</v>
       </c>
       <c r="F15" t="n">
         <v>0.1214</v>
@@ -3065,10 +3109,10 @@
         <v>24553107</v>
       </c>
       <c r="O15" t="n">
-        <v>6431807</v>
+        <v>8876240</v>
       </c>
       <c r="P15" t="n">
-        <v>0.262</v>
+        <v>0.362</v>
       </c>
       <c r="Q15" t="n">
         <v>15639241</v>
@@ -3086,10 +3130,10 @@
         <v>4.65</v>
       </c>
       <c r="V15" t="n">
-        <v>3.2978</v>
+        <v>3.294</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2965</v>
+        <v>2.2956</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -3102,13 +3146,13 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>4.5134</v>
+        <v>4.4953</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.6027</v>
+        <v>3.5952</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.4684</v>
+        <v>2.4665</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3121,10 +3165,10 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>0.7447</v>
+        <v>0.7296</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.584</v>
+        <v>0.5809</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -3132,14 +3176,14 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>87.55</v>
+        <v>81.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.0429</v>
+        <v>4.0488</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3154,7 +3198,7 @@
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>6.1066</v>
+        <v>6.0615</v>
       </c>
       <c r="AO15" t="n">
         <v>6.3</v>
@@ -3164,11 +3208,11 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 6.11; TP2: Classic R2 at 6.3; TP3: Classic R3 at 8.7</t>
+          <t>TP1: Bollinger Upper Band at 6.06; TP2: Classic R2 at 6.3; TP3: Classic R3 at 8.7</t>
         </is>
       </c>
       <c r="AR15" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="AS15" t="n">
         <v>0.64</v>
@@ -3177,7 +3221,7 @@
         <v>1.84</v>
       </c>
       <c r="AU15" t="n">
-        <v>21.97</v>
+        <v>21.07</v>
       </c>
       <c r="AV15" t="n">
         <v>25.83</v>
@@ -3192,7 +3236,7 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (87.6); entry: enhanced entry at Parabolic SAR (overbought (RSI: 87.6))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.7); entry: enhanced entry at Parabolic SAR (overbought (RSI: 81.7))</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3262,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.244</v>
+        <v>0.241</v>
       </c>
       <c r="F16" t="n">
         <v>0.0048</v>
@@ -3248,10 +3292,10 @@
         <v>269403709</v>
       </c>
       <c r="O16" t="n">
-        <v>137907828</v>
+        <v>183426954</v>
       </c>
       <c r="P16" t="n">
-        <v>0.512</v>
+        <v>0.681</v>
       </c>
       <c r="Q16" t="n">
         <v>146684688</v>
@@ -3269,7 +3313,7 @@
         <v>0.256</v>
       </c>
       <c r="V16" t="n">
-        <v>0.223</v>
+        <v>0.2229</v>
       </c>
       <c r="W16" t="n">
         <v>0.1817</v>
@@ -3285,10 +3329,10 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0.2383</v>
+        <v>0.238</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.226</v>
+        <v>0.2259</v>
       </c>
       <c r="AB16" t="n">
         <v>0.1941</v>
@@ -3304,10 +3348,10 @@
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>0.005</v>
+        <v>0.0048</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0066</v>
+        <v>0.0065</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -3315,14 +3359,14 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>57.34</v>
+        <v>55.21</v>
       </c>
       <c r="AI16" t="n">
         <v>0.2444</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3337,7 +3381,7 @@
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>0.2568</v>
+        <v>0.2567</v>
       </c>
       <c r="AO16" t="n">
         <v>0.267</v>
@@ -3351,7 +3395,7 @@
         </is>
       </c>
       <c r="AR16" t="n">
-        <v>7.27</v>
+        <v>7.23</v>
       </c>
       <c r="AS16" t="n">
         <v>10.67</v>
@@ -3360,7 +3404,7 @@
         <v>20.33</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.279999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="AV16" t="n">
         <v>13.62</v>
@@ -3375,7 +3419,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 57.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 55.2))</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3445,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="F17" t="n">
         <v>0.0341</v>
@@ -3433,10 +3477,10 @@
         <v>28853950</v>
       </c>
       <c r="O17" t="n">
-        <v>7241148</v>
+        <v>10568126</v>
       </c>
       <c r="P17" t="n">
-        <v>0.251</v>
+        <v>0.366</v>
       </c>
       <c r="Q17" t="n">
         <v>8711853</v>
@@ -3454,10 +3498,10 @@
         <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6164</v>
+        <v>1.616</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4738</v>
+        <v>1.4737</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3470,13 +3514,13 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>1.6681</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6139</v>
+        <v>1.6131</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5141</v>
+        <v>1.5139</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3489,10 +3533,10 @@
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>0.0271</v>
+        <v>0.0255</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.029</v>
+        <v>0.0286</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -3500,21 +3544,21 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>58.8</v>
+        <v>55.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.6806</v>
+        <v>1.6803</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>1.6806</v>
+        <v>1.6803</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.62</v>
+        <v>1.6204</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -3536,22 +3580,22 @@
         </is>
       </c>
       <c r="AR17" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.73</v>
+        <v>4.74</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
@@ -3560,7 +3604,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.8))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 55.4))</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3630,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38.12</v>
+        <v>38.4</v>
       </c>
       <c r="F18" t="n">
         <v>0.7606000000000001</v>
@@ -3620,10 +3664,10 @@
         <v>1323561</v>
       </c>
       <c r="O18" t="n">
-        <v>862840</v>
+        <v>983992</v>
       </c>
       <c r="P18" t="n">
-        <v>0.652</v>
+        <v>0.743</v>
       </c>
       <c r="Q18" t="n">
         <v>439881</v>
@@ -3641,10 +3685,10 @@
         <v>38.59</v>
       </c>
       <c r="V18" t="n">
-        <v>37.9026</v>
+        <v>37.9082</v>
       </c>
       <c r="W18" t="n">
-        <v>31.1144</v>
+        <v>31.1158</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3657,13 +3701,13 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>38.2229</v>
+        <v>38.2496</v>
       </c>
       <c r="AA18" t="n">
-        <v>37.5518</v>
+        <v>37.5628</v>
       </c>
       <c r="AB18" t="n">
-        <v>31.673</v>
+        <v>31.6758</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -3676,10 +3720,10 @@
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0593</v>
+        <v>-0.037</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0866</v>
+        <v>0.0911</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3687,29 +3731,29 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>49.56</v>
+        <v>51.66</v>
       </c>
       <c r="AI18" t="n">
-        <v>38.5786</v>
+        <v>38.5924</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>36.6681</v>
+        <v>37.9082</v>
       </c>
       <c r="AL18" t="n">
-        <v>36.558</v>
+        <v>37.1204</v>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Bollinger Lower Band</t>
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>40.0812</v>
+        <v>40.0826</v>
       </c>
       <c r="AO18" t="n">
         <v>40.4652</v>
@@ -3723,22 +3767,22 @@
         </is>
       </c>
       <c r="AR18" t="n">
-        <v>30.99</v>
+        <v>2.76</v>
       </c>
       <c r="AS18" t="n">
-        <v>34.48</v>
+        <v>3.25</v>
       </c>
       <c r="AT18" t="n">
-        <v>36.01</v>
+        <v>3.46</v>
       </c>
       <c r="AU18" t="n">
-        <v>9.31</v>
+        <v>5.74</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.36</v>
+        <v>6.75</v>
       </c>
       <c r="AW18" t="n">
-        <v>10.81</v>
+        <v>7.19</v>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
@@ -3747,7 +3791,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 49.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 51.7))</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3817,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35.4</v>
+        <v>34.96</v>
       </c>
       <c r="F19" t="n">
         <v>0.7099</v>
@@ -3803,10 +3847,10 @@
         <v>1238255</v>
       </c>
       <c r="O19" t="n">
-        <v>75832</v>
+        <v>147333</v>
       </c>
       <c r="P19" t="n">
-        <v>0.061</v>
+        <v>0.119</v>
       </c>
       <c r="Q19" t="n">
         <v>693429</v>
@@ -3824,10 +3868,10 @@
         <v>38.25</v>
       </c>
       <c r="V19" t="n">
-        <v>30.7974</v>
+        <v>30.7886</v>
       </c>
       <c r="W19" t="n">
-        <v>19.824</v>
+        <v>19.8218</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3840,13 +3884,13 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>35.1788</v>
+        <v>35.1369</v>
       </c>
       <c r="AA19" t="n">
-        <v>31.3931</v>
+        <v>31.3758</v>
       </c>
       <c r="AB19" t="n">
-        <v>21.9018</v>
+        <v>21.8974</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -3859,10 +3903,10 @@
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>1.3247</v>
+        <v>1.2896</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7792</v>
+        <v>1.7721</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3870,55 +3914,55 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>54.3</v>
+        <v>52.54</v>
       </c>
       <c r="AI19" t="n">
-        <v>36.2244</v>
+        <v>36.2185</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK19" t="n">
         <v>34.425</v>
       </c>
       <c r="AL19" t="n">
-        <v>34.0318</v>
+        <v>34.0281</v>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN19" t="n">
         <v>37.3616</v>
       </c>
       <c r="AO19" t="n">
-        <v>37.7752</v>
+        <v>37.7864</v>
       </c>
       <c r="AP19" t="n">
         <v>38.2267</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.78; TP3: Classic R1 at 38.23</t>
+          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.79; TP3: Classic R1 at 38.23</t>
         </is>
       </c>
       <c r="AR19" t="n">
-        <v>7.47</v>
+        <v>7.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.52</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.67</v>
+        <v>9.58</v>
       </c>
       <c r="AU19" t="n">
         <v>8.529999999999999</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.73</v>
+        <v>9.76</v>
       </c>
       <c r="AW19" t="n">
         <v>11.04</v>
@@ -3930,7 +3974,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.5))</t>
         </is>
       </c>
     </row>
@@ -3956,7 +4000,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.53</v>
+        <v>10.5</v>
       </c>
       <c r="F20" t="n">
         <v>0.2094</v>
@@ -3986,10 +4030,10 @@
         <v>4418644</v>
       </c>
       <c r="O20" t="n">
-        <v>627727</v>
+        <v>862671</v>
       </c>
       <c r="P20" t="n">
-        <v>0.142</v>
+        <v>0.195</v>
       </c>
       <c r="Q20" t="n">
         <v>2244436</v>
@@ -4007,10 +4051,10 @@
         <v>10.6802</v>
       </c>
       <c r="V20" t="n">
-        <v>10.1204</v>
+        <v>10.1198</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9859</v>
+        <v>7.9857</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -4023,13 +4067,13 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>10.6227</v>
+        <v>10.6199</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.0836</v>
+        <v>10.0824</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.312099999999999</v>
+        <v>8.3118</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -4042,10 +4086,10 @@
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.18</v>
+        <v>0.1795</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -4053,67 +4097,67 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>49.84</v>
+        <v>48.88</v>
       </c>
       <c r="AI20" t="n">
-        <v>10.7922</v>
+        <v>10.7905</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>10.3209</v>
+        <v>10.21</v>
       </c>
       <c r="AL20" t="n">
         <v>10.21</v>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AN20" t="n">
         <v>11.0391</v>
       </c>
       <c r="AO20" t="n">
-        <v>11.0642</v>
+        <v>11.0675</v>
       </c>
       <c r="AP20" t="n">
         <v>11.15</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.06; TP3: Classic R1 at 11.15</t>
+          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.07; TP3: Classic R1 at 11.15</t>
         </is>
       </c>
       <c r="AR20" t="n">
-        <v>6.47</v>
+        <v>21734357.51</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.7</v>
+        <v>22478846.46</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.47</v>
+        <v>24641534.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.96</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.029999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 49.8))</t>
+          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (neutral (RSI: 48.9))</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4183,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>32.1</v>
+        <v>31.75</v>
       </c>
       <c r="F21" t="n">
         <v>0.6417</v>
@@ -4164,7 +4208,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>20.62</v>
+        <v>20.39</v>
       </c>
       <c r="M21" t="n">
         <v>1.557</v>
@@ -4173,10 +4217,10 @@
         <v>698798</v>
       </c>
       <c r="O21" t="n">
-        <v>381200</v>
+        <v>883947</v>
       </c>
       <c r="P21" t="n">
-        <v>0.546</v>
+        <v>1.265</v>
       </c>
       <c r="Q21" t="n">
         <v>253928</v>
@@ -4194,10 +4238,10 @@
         <v>36.7</v>
       </c>
       <c r="V21" t="n">
-        <v>34.8526</v>
+        <v>34.8456</v>
       </c>
       <c r="W21" t="n">
-        <v>32.7116</v>
+        <v>32.7098</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -4210,13 +4254,13 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>33.8394</v>
+        <v>33.8061</v>
       </c>
       <c r="AA21" t="n">
-        <v>34.824</v>
+        <v>34.8102</v>
       </c>
       <c r="AB21" t="n">
-        <v>31.4553</v>
+        <v>31.4518</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -4229,10 +4273,10 @@
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>-0.9232</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.6059</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -4240,58 +4284,58 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>35.2</v>
+        <v>33.65</v>
       </c>
       <c r="AI21" t="n">
-        <v>34.5231</v>
+        <v>34.4488</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>31.5</v>
+        <v>31.0769</v>
       </c>
       <c r="AL21" t="n">
-        <v>31.1477</v>
+        <v>29.9767</v>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Classic S1</t>
         </is>
       </c>
       <c r="AN21" t="n">
-        <v>32.7116</v>
+        <v>32.7098</v>
       </c>
       <c r="AO21" t="n">
-        <v>35.9163</v>
+        <v>35.9128</v>
       </c>
       <c r="AP21" t="n">
         <v>37.0467</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 32.71; TP2: 100 SMA at 35.92; TP3: Classic R1 at 37.05</t>
+          <t>TP1: 200 SMA at 32.71; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
         </is>
       </c>
       <c r="AR21" t="n">
-        <v>3.44</v>
+        <v>1.48</v>
       </c>
       <c r="AS21" t="n">
-        <v>12.54</v>
+        <v>4.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>15.74</v>
+        <v>5.43</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.85</v>
+        <v>5.25</v>
       </c>
       <c r="AV21" t="n">
-        <v>14.02</v>
+        <v>15.56</v>
       </c>
       <c r="AW21" t="n">
-        <v>17.61</v>
+        <v>19.21</v>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
@@ -4300,7 +4344,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (neutral (RSI: 35.2))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 33.7))</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4370,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>308.12</v>
+        <v>307.88</v>
       </c>
       <c r="F22" t="n">
         <v>5.4044</v>
@@ -4343,7 +4387,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>159.9561</v>
+        <v>160.2392</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -4351,19 +4395,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>14.54</v>
+        <v>14.51</v>
       </c>
       <c r="M22" t="n">
-        <v>18.6414</v>
+        <v>18.6803</v>
       </c>
       <c r="N22" t="n">
         <v>382613</v>
       </c>
       <c r="O22" t="n">
-        <v>1144923</v>
+        <v>1348066</v>
       </c>
       <c r="P22" t="n">
-        <v>2.992</v>
+        <v>3.523</v>
       </c>
       <c r="Q22" t="n">
         <v>349260</v>
@@ -4381,10 +4425,10 @@
         <v>242</v>
       </c>
       <c r="V22" t="n">
-        <v>188.999</v>
+        <v>188.9942</v>
       </c>
       <c r="W22" t="n">
-        <v>128.2224</v>
+        <v>128.2212</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -4397,13 +4441,13 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>232.7651</v>
+        <v>232.7422</v>
       </c>
       <c r="AA22" t="n">
-        <v>197.5813</v>
+        <v>197.5719</v>
       </c>
       <c r="AB22" t="n">
-        <v>135.0358</v>
+        <v>135.0334</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -4416,10 +4460,10 @@
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>26.8975</v>
+        <v>26.8784</v>
       </c>
       <c r="AF22" t="n">
-        <v>20.3668</v>
+        <v>20.363</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4427,14 +4471,14 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>80.97</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>232.0334</v>
+        <v>232.8901</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK22" t="n">
@@ -4487,7 +4531,7 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 81.0))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (80.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 80.9))</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4557,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>107.75</v>
+        <v>107</v>
       </c>
       <c r="F23" t="n">
         <v>2.0979</v>
@@ -4547,10 +4591,10 @@
         <v>300099</v>
       </c>
       <c r="O23" t="n">
-        <v>1508396</v>
+        <v>1617845</v>
       </c>
       <c r="P23" t="n">
-        <v>5.026</v>
+        <v>5.391</v>
       </c>
       <c r="Q23" t="n">
         <v>157036</v>
@@ -4568,10 +4612,10 @@
         <v>97.5</v>
       </c>
       <c r="V23" t="n">
-        <v>90.4278</v>
+        <v>90.4128</v>
       </c>
       <c r="W23" t="n">
-        <v>82.01260000000001</v>
+        <v>82.0089</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -4584,13 +4628,13 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>96.3171</v>
+        <v>96.2457</v>
       </c>
       <c r="AA23" t="n">
-        <v>91.6138</v>
+        <v>91.5844</v>
       </c>
       <c r="AB23" t="n">
-        <v>83.87350000000001</v>
+        <v>83.8661</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -4603,10 +4647,10 @@
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>4.1366</v>
+        <v>4.0767</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.7037</v>
+        <v>2.6918</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -4614,18 +4658,18 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>74</v>
+        <v>73.31</v>
       </c>
       <c r="AI23" t="n">
-        <v>101.7503</v>
+        <v>101.7001</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>101.7503</v>
+        <v>101.7001</v>
       </c>
       <c r="AL23" t="n">
         <v>95.48</v>
@@ -4639,33 +4683,33 @@
         <v>115.15</v>
       </c>
       <c r="AO23" t="n">
-        <v>121.8499</v>
+        <v>121.875</v>
       </c>
       <c r="AP23" t="n">
-        <v>118.3123</v>
+        <v>118.3242</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 115.15; TP2: Extension at 121.85; TP3: Extension at 118.31</t>
+          <t>TP1: Classic R3 at 115.15; TP2: Extension at 121.88; TP3: Extension at 118.32</t>
         </is>
       </c>
       <c r="AR23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AU23" t="n">
-        <v>13.17</v>
+        <v>13.23</v>
       </c>
       <c r="AV23" t="n">
-        <v>19.75</v>
+        <v>19.84</v>
       </c>
       <c r="AW23" t="n">
-        <v>16.28</v>
+        <v>16.35</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
@@ -4674,7 +4718,7 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.0); entry: enhanced entry at VWMA (overbought (RSI: 74.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.3); entry: enhanced entry at VWMA (overbought (RSI: 73.3))</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4744,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="F24" t="n">
         <v>0.9375</v>
@@ -4734,10 +4778,10 @@
         <v>410274</v>
       </c>
       <c r="O24" t="n">
-        <v>176006</v>
+        <v>432839</v>
       </c>
       <c r="P24" t="n">
-        <v>0.429</v>
+        <v>1.055</v>
       </c>
       <c r="Q24" t="n">
         <v>333334</v>
@@ -4755,10 +4799,10 @@
         <v>44.89</v>
       </c>
       <c r="V24" t="n">
-        <v>38.3336</v>
+        <v>38.3356</v>
       </c>
       <c r="W24" t="n">
-        <v>35.1421</v>
+        <v>35.1426</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4771,13 +4815,13 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>42.5399</v>
+        <v>42.5494</v>
       </c>
       <c r="AA24" t="n">
-        <v>39.4962</v>
+        <v>39.5002</v>
       </c>
       <c r="AB24" t="n">
-        <v>34.5139</v>
+        <v>34.5149</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -4790,10 +4834,10 @@
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>1.9499</v>
+        <v>1.9579</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7277</v>
+        <v>1.7293</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -4801,18 +4845,18 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>67</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="AI24" t="n">
-        <v>42.8525</v>
+        <v>42.9065</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>42.8525</v>
+        <v>42.9065</v>
       </c>
       <c r="AL24" t="n">
         <v>40.5284</v>
@@ -4826,33 +4870,33 @@
         <v>46.1258</v>
       </c>
       <c r="AO24" t="n">
-        <v>46.3637</v>
+        <v>46.3863</v>
       </c>
       <c r="AP24" t="n">
         <v>49.4033</v>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 46.13; TP2: Bollinger Upper Band at 46.36; TP3: Classic R2 at 49.4</t>
+          <t>TP1: Fibonacci R2 at 46.13; TP2: Bollinger Upper Band at 46.39; TP3: Classic R2 at 49.4</t>
         </is>
       </c>
       <c r="AR24" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.64</v>
+        <v>7.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.19</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AW24" t="n">
-        <v>15.29</v>
+        <v>15.14</v>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
@@ -4861,7 +4905,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.5))</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4931,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.55</v>
+        <v>12.48</v>
       </c>
       <c r="F25" t="n">
         <v>0.2533</v>
@@ -4915,10 +4959,10 @@
         <v>2943614</v>
       </c>
       <c r="O25" t="n">
-        <v>429504</v>
+        <v>683848</v>
       </c>
       <c r="P25" t="n">
-        <v>0.146</v>
+        <v>0.232</v>
       </c>
       <c r="Q25" t="n">
         <v>1403699</v>
@@ -4934,10 +4978,10 @@
         <v>12.3</v>
       </c>
       <c r="V25" t="n">
-        <v>10.8606</v>
+        <v>10.8592</v>
       </c>
       <c r="W25" t="n">
-        <v>8.296200000000001</v>
+        <v>8.2958</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -4950,13 +4994,13 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>12.0575</v>
+        <v>12.0508</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.1434</v>
+        <v>11.1407</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.605399999999999</v>
+        <v>8.604699999999999</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -4969,10 +5013,10 @@
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>0.5189</v>
+        <v>0.5133</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.4848</v>
+        <v>0.4837</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -4980,14 +5024,14 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>60.95</v>
+        <v>59.8</v>
       </c>
       <c r="AI25" t="n">
-        <v>12.0302</v>
+        <v>12.0319</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -5005,21 +5049,21 @@
         <v>12.8261</v>
       </c>
       <c r="AO25" t="n">
-        <v>13.0919</v>
+        <v>13.0817</v>
       </c>
       <c r="AP25" t="n">
         <v>13.1767</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 12.83; TP2: Bollinger Upper Band at 13.09; TP3: Classic R1 at 13.18</t>
+          <t>TP1: Fibonacci R1 at 12.83; TP2: Bollinger Upper Band at 13.08; TP3: Classic R1 at 13.18</t>
         </is>
       </c>
       <c r="AR25" t="n">
         <v>0.52</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AT25" t="n">
         <v>0.86</v>
@@ -5028,7 +5072,7 @@
         <v>4.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.57</v>
+        <v>6.49</v>
       </c>
       <c r="AW25" t="n">
         <v>7.26</v>
@@ -5040,7 +5084,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.0))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 59.8))</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5110,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>357.5</v>
+        <v>379</v>
       </c>
       <c r="F26" t="n">
         <v>6.6097</v>
@@ -5100,10 +5144,10 @@
         <v>160786</v>
       </c>
       <c r="O26" t="n">
-        <v>1524181</v>
+        <v>1981739</v>
       </c>
       <c r="P26" t="n">
-        <v>9.48</v>
+        <v>12.325</v>
       </c>
       <c r="Q26" t="n">
         <v>250828</v>
@@ -5119,10 +5163,10 @@
         <v>74.2</v>
       </c>
       <c r="V26" t="n">
-        <v>114.424</v>
+        <v>114.854</v>
       </c>
       <c r="W26" t="n">
-        <v>77.1962</v>
+        <v>77.30370000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -5135,13 +5179,13 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>213.8314</v>
+        <v>215.8791</v>
       </c>
       <c r="AA26" t="n">
-        <v>142.6757</v>
+        <v>143.5188</v>
       </c>
       <c r="AB26" t="n">
-        <v>85.431</v>
+        <v>85.64490000000001</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -5154,10 +5198,10 @@
         </is>
       </c>
       <c r="AE26" t="n">
-        <v>71.744</v>
+        <v>73.45910000000001</v>
       </c>
       <c r="AF26" t="n">
-        <v>47.4182</v>
+        <v>47.7612</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -5165,14 +5209,14 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>75.59999999999999</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="AI26" t="n">
-        <v>204.6438</v>
+        <v>212.313</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK26" t="n">
@@ -5187,7 +5231,7 @@
         </is>
       </c>
       <c r="AN26" t="n">
-        <v>393.6149</v>
+        <v>398.4394</v>
       </c>
       <c r="AO26" t="n">
         <v>524.1933</v>
@@ -5197,11 +5241,11 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 393.61; TP2: Classic R3 at 524.19; TP3: Extension at 616.49</t>
+          <t>TP1: Bollinger Upper Band at 398.44; TP2: Classic R3 at 524.19; TP3: Extension at 616.49</t>
         </is>
       </c>
       <c r="AR26" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="AS26" t="n">
         <v>1.54</v>
@@ -5210,7 +5254,7 @@
         <v>2.13</v>
       </c>
       <c r="AU26" t="n">
-        <v>39.29</v>
+        <v>41</v>
       </c>
       <c r="AV26" t="n">
         <v>85.5</v>
@@ -5225,7 +5269,7 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 77.0))</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5295,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20.94</v>
+        <v>20.87</v>
       </c>
       <c r="F27" t="n">
         <v>0.4264</v>
@@ -5281,10 +5325,10 @@
         <v>709379</v>
       </c>
       <c r="O27" t="n">
-        <v>724883</v>
+        <v>962877</v>
       </c>
       <c r="P27" t="n">
-        <v>1.022</v>
+        <v>1.357</v>
       </c>
       <c r="Q27" t="n">
         <v>322309</v>
@@ -5302,10 +5346,10 @@
         <v>22.2</v>
       </c>
       <c r="V27" t="n">
-        <v>19.5854</v>
+        <v>19.584</v>
       </c>
       <c r="W27" t="n">
-        <v>19.3165</v>
+        <v>19.3161</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -5318,13 +5362,13 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>19.9105</v>
+        <v>19.9038</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.7151</v>
+        <v>19.7123</v>
       </c>
       <c r="AB27" t="n">
-        <v>18.7945</v>
+        <v>18.7939</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -5337,10 +5381,10 @@
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>0.3</v>
+        <v>0.2944</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.1197</v>
+        <v>0.1186</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -5348,14 +5392,14 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>66.89</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AI27" t="n">
-        <v>20.1253</v>
+        <v>20.132</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -5370,36 +5414,36 @@
         </is>
       </c>
       <c r="AN27" t="n">
+        <v>20.9033</v>
+      </c>
+      <c r="AO27" t="n">
         <v>22.2233</v>
       </c>
-      <c r="AO27" t="n">
-        <v>23.2224</v>
-      </c>
       <c r="AP27" t="n">
-        <v>22.6949</v>
+        <v>22.9867</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 22.22; TP2: Extension at 23.22; TP3: Extension at 22.69</t>
+          <t>TP1: Classic R2 at 20.9; TP2: Classic R3 at 22.22; TP3: Extension at 22.99</t>
         </is>
       </c>
       <c r="AR27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS27" t="n">
         <v>2.79</v>
       </c>
-      <c r="AS27" t="n">
-        <v>4.19</v>
-      </c>
       <c r="AT27" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="AU27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV27" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="AV27" t="n">
-        <v>14.82</v>
-      </c>
       <c r="AW27" t="n">
-        <v>12.21</v>
+        <v>13.65</v>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
@@ -5408,7 +5452,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 66.9))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.6))</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5478,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>16.37</v>
+        <v>16.25</v>
       </c>
       <c r="F28" t="n">
         <v>0.3269</v>
@@ -5464,10 +5508,10 @@
         <v>943226</v>
       </c>
       <c r="O28" t="n">
-        <v>807882</v>
+        <v>1092805</v>
       </c>
       <c r="P28" t="n">
-        <v>0.857</v>
+        <v>1.159</v>
       </c>
       <c r="Q28" t="n">
         <v>361460</v>
@@ -5485,10 +5529,10 @@
         <v>16.42</v>
       </c>
       <c r="V28" t="n">
-        <v>15.3502</v>
+        <v>15.3478</v>
       </c>
       <c r="W28" t="n">
-        <v>15.2672</v>
+        <v>15.2666</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -5501,13 +5545,13 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>15.6172</v>
+        <v>15.6058</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.4439</v>
+        <v>15.4392</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.9403</v>
+        <v>14.9391</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -5520,10 +5564,10 @@
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>0.2482</v>
+        <v>0.2386</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.1355</v>
+        <v>0.1336</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -5531,18 +5575,18 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>66.04000000000001</v>
+        <v>63.33</v>
       </c>
       <c r="AI28" t="n">
-        <v>15.6961</v>
+        <v>15.6988</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>15.6961</v>
+        <v>15.6988</v>
       </c>
       <c r="AL28" t="n">
         <v>15.43</v>
@@ -5553,36 +5597,36 @@
         </is>
       </c>
       <c r="AN28" t="n">
+        <v>16.2579</v>
+      </c>
+      <c r="AO28" t="n">
         <v>16.6333</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>17.9833</v>
       </c>
-      <c r="AP28" t="n">
-        <v>18.857</v>
-      </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 16.63; TP2: Classic R3 at 17.98; TP3: Extension at 18.86</t>
+          <t>TP1: Bollinger Upper Band at 16.26; TP2: Classic R2 at 16.63; TP3: Classic R3 at 17.98</t>
         </is>
       </c>
       <c r="AR28" t="n">
-        <v>3.52</v>
+        <v>2.08</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>3.48</v>
       </c>
       <c r="AT28" t="n">
-        <v>11.88</v>
+        <v>8.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.97</v>
+        <v>3.56</v>
       </c>
       <c r="AV28" t="n">
-        <v>14.57</v>
+        <v>5.95</v>
       </c>
       <c r="AW28" t="n">
-        <v>20.14</v>
+        <v>14.55</v>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
@@ -5591,7 +5635,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.3))</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5661,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30.91</v>
+        <v>30.8</v>
       </c>
       <c r="F29" t="n">
         <v>0.623</v>
@@ -5645,10 +5689,10 @@
         <v>1440973</v>
       </c>
       <c r="O29" t="n">
-        <v>141390</v>
+        <v>215456</v>
       </c>
       <c r="P29" t="n">
-        <v>0.098</v>
+        <v>0.15</v>
       </c>
       <c r="Q29" t="n">
         <v>491469</v>
@@ -5666,10 +5710,10 @@
         <v>32.7</v>
       </c>
       <c r="V29" t="n">
-        <v>28.8938</v>
+        <v>28.8916</v>
       </c>
       <c r="W29" t="n">
-        <v>17.9013</v>
+        <v>17.9008</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5682,13 +5726,13 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>30.0459</v>
+        <v>30.0354</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.8043</v>
+        <v>27.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>19.9079</v>
+        <v>19.9068</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -5701,10 +5745,10 @@
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>0.9522</v>
+        <v>0.9435</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.8841</v>
+        <v>0.8824</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -5712,14 +5756,14 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>62.22</v>
+        <v>61.07</v>
       </c>
       <c r="AI29" t="n">
-        <v>29.9608</v>
+        <v>29.9637</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -5737,21 +5781,21 @@
         <v>32.3265</v>
       </c>
       <c r="AO29" t="n">
-        <v>33.1442</v>
+        <v>33.1306</v>
       </c>
       <c r="AP29" t="n">
         <v>33.4067</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 33.14; TP3: Classic R1 at 33.41</t>
+          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 33.13; TP3: Classic R1 at 33.41</t>
         </is>
       </c>
       <c r="AR29" t="n">
         <v>0.63</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AT29" t="n">
         <v>1.01</v>
@@ -5760,7 +5804,7 @@
         <v>5.99</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AW29" t="n">
         <v>9.529999999999999</v>
@@ -5772,7 +5816,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 62.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 61.1))</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5842,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34.78</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
         <v>0.6914</v>
@@ -5832,10 +5876,10 @@
         <v>801725</v>
       </c>
       <c r="O30" t="n">
-        <v>191944</v>
+        <v>429281</v>
       </c>
       <c r="P30" t="n">
-        <v>0.239</v>
+        <v>0.535</v>
       </c>
       <c r="Q30" t="n">
         <v>851139</v>
@@ -5851,10 +5895,10 @@
         <v>37</v>
       </c>
       <c r="V30" t="n">
-        <v>30.1202</v>
+        <v>30.1046</v>
       </c>
       <c r="W30" t="n">
-        <v>26.9028</v>
+        <v>26.8989</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -5867,13 +5911,13 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>33.7119</v>
+        <v>33.6376</v>
       </c>
       <c r="AA30" t="n">
-        <v>31.0974</v>
+        <v>31.0668</v>
       </c>
       <c r="AB30" t="n">
-        <v>27.6406</v>
+        <v>27.6328</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -5886,10 +5930,10 @@
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>1.6266</v>
+        <v>1.5644</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.7264</v>
+        <v>1.714</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -5897,18 +5941,18 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>58.69</v>
+        <v>55.03</v>
       </c>
       <c r="AI30" t="n">
-        <v>33.6197</v>
+        <v>33.6178</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>33.6197</v>
+        <v>33.6178</v>
       </c>
       <c r="AL30" t="n">
         <v>30.6464</v>
@@ -5922,33 +5966,33 @@
         <v>36.5522</v>
       </c>
       <c r="AO30" t="n">
-        <v>37.4442</v>
+        <v>37.3797</v>
       </c>
       <c r="AP30" t="n">
         <v>38.3133</v>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.44; TP3: Classic R1 at 38.31</t>
+          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.38; TP3: Classic R1 at 38.31</t>
         </is>
       </c>
       <c r="AR30" t="n">
         <v>0.99</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AT30" t="n">
         <v>1.58</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.720000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.38</v>
+        <v>11.19</v>
       </c>
       <c r="AW30" t="n">
-        <v>13.96</v>
+        <v>13.97</v>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
@@ -5957,7 +6001,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 55.0))</t>
         </is>
       </c>
     </row>
@@ -5983,7 +6027,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="F31" t="n">
         <v>0.0387</v>
@@ -6013,10 +6057,10 @@
         <v>34859816</v>
       </c>
       <c r="O31" t="n">
-        <v>7476127</v>
+        <v>34055975</v>
       </c>
       <c r="P31" t="n">
-        <v>0.214</v>
+        <v>0.977</v>
       </c>
       <c r="Q31" t="n">
         <v>18184957</v>
@@ -6032,10 +6076,10 @@
         <v>1.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.831</v>
+        <v>1.8324</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6966</v>
+        <v>1.6969</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -6048,13 +6092,13 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1.9043</v>
+        <v>1.911</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8351</v>
+        <v>1.8378</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6385</v>
+        <v>1.6392</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -6067,10 +6111,10 @@
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>0.0346</v>
+        <v>0.0402</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0323</v>
+        <v>0.0334</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -6078,18 +6122,18 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>58.38</v>
+        <v>64.56</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.9218</v>
+        <v>1.9252</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>1.9218</v>
+        <v>1.9252</v>
       </c>
       <c r="AL31" t="n">
         <v>1.8835</v>
@@ -6100,36 +6144,36 @@
         </is>
       </c>
       <c r="AN31" t="n">
-        <v>1.9912</v>
+        <v>2.0413</v>
       </c>
       <c r="AO31" t="n">
-        <v>2.0413</v>
+        <v>2.0833</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.0833</v>
+        <v>2.1121</v>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1.99; TP2: Fibonacci R1 at 2.04; TP3: Classic R1 at 2.08</t>
+          <t>TP1: Fibonacci R1 at 2.04; TP2: Classic R1 at 2.08; TP3: Fibonacci R2 at 2.11</t>
         </is>
       </c>
       <c r="AR31" t="n">
-        <v>1.81</v>
+        <v>2.79</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.12</v>
+        <v>3.79</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.21</v>
+        <v>4.48</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.61</v>
+        <v>6.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.22</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
@@ -6138,7 +6182,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.6))</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6208,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.22</v>
+        <v>10.15</v>
       </c>
       <c r="F32" t="n">
         <v>0.2014</v>
@@ -6194,10 +6238,10 @@
         <v>5424706</v>
       </c>
       <c r="O32" t="n">
-        <v>3284092</v>
+        <v>4300442</v>
       </c>
       <c r="P32" t="n">
-        <v>0.605</v>
+        <v>0.793</v>
       </c>
       <c r="Q32" t="n">
         <v>1199479</v>
@@ -6215,10 +6259,10 @@
         <v>10.26</v>
       </c>
       <c r="V32" t="n">
-        <v>9.6594</v>
+        <v>9.657999999999999</v>
       </c>
       <c r="W32" t="n">
-        <v>9.6137</v>
+        <v>9.613300000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -6231,13 +6275,13 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>9.839</v>
+        <v>9.8323</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.705</v>
+        <v>9.702199999999999</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.497400000000001</v>
+        <v>9.496700000000001</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -6250,10 +6294,10 @@
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>0.1213</v>
+        <v>0.1157</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0861</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -6261,18 +6305,18 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>64.05</v>
+        <v>62.44</v>
       </c>
       <c r="AI32" t="n">
-        <v>9.876300000000001</v>
+        <v>9.876899999999999</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>9.876300000000001</v>
+        <v>9.876899999999999</v>
       </c>
       <c r="AL32" t="n">
         <v>9.800000000000001</v>
@@ -6283,36 +6327,36 @@
         </is>
       </c>
       <c r="AN32" t="n">
+        <v>10.1952</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>10.2191</v>
+      </c>
+      <c r="AP32" t="n">
         <v>10.29</v>
       </c>
-      <c r="AO32" t="n">
-        <v>10.4409</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>10.8</v>
-      </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 10.29; TP2: Fibonacci R2 at 10.44; TP3: Classic R2 at 10.8</t>
+          <t>TP1: Bollinger Upper Band at 10.2; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
         </is>
       </c>
       <c r="AR32" t="n">
-        <v>5.42</v>
+        <v>4.14</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.4</v>
+        <v>4.45</v>
       </c>
       <c r="AT32" t="n">
-        <v>12.11</v>
+        <v>5.37</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.19</v>
+        <v>3.22</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.72</v>
+        <v>3.46</v>
       </c>
       <c r="AW32" t="n">
-        <v>9.35</v>
+        <v>4.18</v>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
@@ -6321,7 +6365,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.0))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.4))</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6391,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>10.97</v>
+        <v>10.9</v>
       </c>
       <c r="F33" t="n">
         <v>0.2142</v>
@@ -6381,10 +6425,10 @@
         <v>2664764</v>
       </c>
       <c r="O33" t="n">
-        <v>6181360</v>
+        <v>7310437</v>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>2.743</v>
       </c>
       <c r="Q33" t="n">
         <v>1445471</v>
@@ -6402,10 +6446,10 @@
         <v>9.75</v>
       </c>
       <c r="V33" t="n">
-        <v>9.3184</v>
+        <v>9.317</v>
       </c>
       <c r="W33" t="n">
-        <v>8.051</v>
+        <v>8.050700000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -6418,13 +6462,13 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>9.7601</v>
+        <v>9.753500000000001</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.356</v>
+        <v>9.353199999999999</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.2295</v>
+        <v>8.2288</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -6437,10 +6481,10 @@
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>0.3134</v>
+        <v>0.3078</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1712</v>
+        <v>0.17</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -6448,14 +6492,14 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>79.34</v>
+        <v>78.73</v>
       </c>
       <c r="AI33" t="n">
-        <v>9.9579</v>
+        <v>9.9666</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK33" t="n">
@@ -6508,7 +6552,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.3); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.3))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.7); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.7))</t>
         </is>
       </c>
     </row>
@@ -6534,7 +6578,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10.13</v>
+        <v>10.05</v>
       </c>
       <c r="F34" t="n">
         <v>0.2024</v>
@@ -6564,10 +6608,10 @@
         <v>2330625</v>
       </c>
       <c r="O34" t="n">
-        <v>475564</v>
+        <v>1009985</v>
       </c>
       <c r="P34" t="n">
-        <v>0.204</v>
+        <v>0.433</v>
       </c>
       <c r="Q34" t="n">
         <v>675406</v>
@@ -6585,10 +6629,10 @@
         <v>10.26</v>
       </c>
       <c r="V34" t="n">
-        <v>9.9778</v>
+        <v>9.9762</v>
       </c>
       <c r="W34" t="n">
-        <v>9.2348</v>
+        <v>9.234400000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -6601,13 +6645,13 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>10.0958</v>
+        <v>10.0882</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.9442</v>
+        <v>9.9411</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.1304</v>
+        <v>9.1297</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -6620,10 +6664,10 @@
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>0.0408</v>
+        <v>0.0345</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0536</v>
+        <v>0.0523</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -6631,29 +6675,29 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>52.14</v>
+        <v>49.53</v>
       </c>
       <c r="AI34" t="n">
-        <v>10.2384</v>
+        <v>10.2351</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK34" t="n">
-        <v>9.9778</v>
+        <v>9.9087</v>
       </c>
       <c r="AL34" t="n">
-        <v>9.916499999999999</v>
+        <v>9.702999999999999</v>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN34" t="n">
-        <v>10.3815</v>
+        <v>10.3813</v>
       </c>
       <c r="AO34" t="n">
         <v>10.6503</v>
@@ -6667,22 +6711,22 @@
         </is>
       </c>
       <c r="AR34" t="n">
-        <v>6.59</v>
+        <v>2.3</v>
       </c>
       <c r="AS34" t="n">
-        <v>10.98</v>
+        <v>3.61</v>
       </c>
       <c r="AT34" t="n">
-        <v>11.84</v>
+        <v>3.86</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.05</v>
+        <v>4.77</v>
       </c>
       <c r="AV34" t="n">
-        <v>6.74</v>
+        <v>7.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.27</v>
+        <v>8.02</v>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
@@ -6691,7 +6735,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 52.1))</t>
+          <t>near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.5))</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6761,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16.37</v>
+        <v>16.35</v>
       </c>
       <c r="F35" t="n">
         <v>0.3249</v>
@@ -6751,10 +6795,10 @@
         <v>2848240</v>
       </c>
       <c r="O35" t="n">
-        <v>1848447</v>
+        <v>2511994</v>
       </c>
       <c r="P35" t="n">
-        <v>0.649</v>
+        <v>0.882</v>
       </c>
       <c r="Q35" t="n">
         <v>658319</v>
@@ -6772,10 +6816,10 @@
         <v>16.77</v>
       </c>
       <c r="V35" t="n">
-        <v>16.3244</v>
+        <v>16.324</v>
       </c>
       <c r="W35" t="n">
-        <v>16.2604</v>
+        <v>16.2603</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -6788,13 +6832,13 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>16.0483</v>
+        <v>16.0463</v>
       </c>
       <c r="AA35" t="n">
-        <v>16.3098</v>
+        <v>16.309</v>
       </c>
       <c r="AB35" t="n">
-        <v>16.4294</v>
+        <v>16.4292</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -6807,10 +6851,10 @@
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>-0.0663</v>
+        <v>-0.0679</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.1277</v>
+        <v>-0.128</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -6818,21 +6862,21 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>54.81</v>
+        <v>54.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>16.027</v>
+        <v>16.0304</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK35" t="n">
-        <v>16.3244</v>
+        <v>16.324</v>
       </c>
       <c r="AL35" t="n">
-        <v>16.2604</v>
+        <v>16.2603</v>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
@@ -6843,33 +6887,33 @@
         <v>16.5125</v>
       </c>
       <c r="AO35" t="n">
-        <v>16.7175</v>
+        <v>16.7146</v>
       </c>
       <c r="AP35" t="n">
-        <v>16.9704</v>
+        <v>16.72</v>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 16.51; TP2: Bollinger Upper Band at 16.72; TP3: 100 SMA at 16.97</t>
+          <t>TP1: Fibonacci R1 at 16.51; TP2: Bollinger Upper Band at 16.71; TP3: Classic R1 at 16.72</t>
         </is>
       </c>
       <c r="AR35" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="AS35" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="AT35" t="n">
-        <v>10.1</v>
+        <v>6.22</v>
       </c>
       <c r="AU35" t="n">
         <v>1.15</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AW35" t="n">
-        <v>3.96</v>
+        <v>2.43</v>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
@@ -6878,7 +6922,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 54.8))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 54.5))</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6948,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>80</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F36" t="n">
         <v>1.6173</v>
@@ -6938,10 +6982,10 @@
         <v>730425</v>
       </c>
       <c r="O36" t="n">
-        <v>908370</v>
+        <v>1187037</v>
       </c>
       <c r="P36" t="n">
-        <v>1.244</v>
+        <v>1.625</v>
       </c>
       <c r="Q36" t="n">
         <v>376287</v>
@@ -6959,10 +7003,10 @@
         <v>87.98999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>67.9436</v>
+        <v>67.9234</v>
       </c>
       <c r="W36" t="n">
-        <v>63.499</v>
+        <v>63.4939</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -6975,13 +7019,13 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>75.9051</v>
+        <v>75.80889999999999</v>
       </c>
       <c r="AA36" t="n">
-        <v>70.0964</v>
+        <v>70.0568</v>
       </c>
       <c r="AB36" t="n">
-        <v>61.455</v>
+        <v>61.4449</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -6994,10 +7038,10 @@
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>4.2311</v>
+        <v>4.1505</v>
       </c>
       <c r="AF36" t="n">
-        <v>4.2948</v>
+        <v>4.2786</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -7005,18 +7049,18 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>61.83</v>
+        <v>59.61</v>
       </c>
       <c r="AI36" t="n">
-        <v>77.8582</v>
+        <v>77.8353</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK36" t="n">
-        <v>77.8582</v>
+        <v>77.8353</v>
       </c>
       <c r="AL36" t="n">
         <v>66.2534</v>
@@ -7030,14 +7074,14 @@
         <v>86.65989999999999</v>
       </c>
       <c r="AO36" t="n">
-        <v>91.21550000000001</v>
+        <v>91.1069</v>
       </c>
       <c r="AP36" t="n">
         <v>91.63330000000001</v>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 91.22; TP3: Classic R1 at 91.63</t>
+          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 91.11; TP3: Classic R1 at 91.63</t>
         </is>
       </c>
       <c r="AR36" t="n">
@@ -7050,13 +7094,13 @@
         <v>1.19</v>
       </c>
       <c r="AU36" t="n">
-        <v>11.3</v>
+        <v>11.34</v>
       </c>
       <c r="AV36" t="n">
-        <v>17.16</v>
+        <v>17.05</v>
       </c>
       <c r="AW36" t="n">
-        <v>17.69</v>
+        <v>17.73</v>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
@@ -7065,7 +7109,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.8))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.6))</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7135,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30.56</v>
+        <v>30.07</v>
       </c>
       <c r="F37" t="n">
         <v>0.6082</v>
@@ -7125,10 +7169,10 @@
         <v>2136236</v>
       </c>
       <c r="O37" t="n">
-        <v>2680847</v>
+        <v>4318140</v>
       </c>
       <c r="P37" t="n">
-        <v>1.255</v>
+        <v>2.021</v>
       </c>
       <c r="Q37" t="n">
         <v>2152320</v>
@@ -7146,10 +7190,10 @@
         <v>28.7</v>
       </c>
       <c r="V37" t="n">
-        <v>24.8534</v>
+        <v>24.8436</v>
       </c>
       <c r="W37" t="n">
-        <v>20.4564</v>
+        <v>20.454</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -7162,13 +7206,13 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>28.0603</v>
+        <v>28.0137</v>
       </c>
       <c r="AA37" t="n">
-        <v>25.7514</v>
+        <v>25.7322</v>
       </c>
       <c r="AB37" t="n">
-        <v>21.2911</v>
+        <v>21.2862</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -7181,10 +7225,10 @@
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>1.367</v>
+        <v>1.3279</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.2664</v>
+        <v>1.2586</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -7192,18 +7236,18 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>73.39</v>
+        <v>69.03</v>
       </c>
       <c r="AI37" t="n">
-        <v>28.3015</v>
+        <v>28.3228</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>28.3015</v>
+        <v>28.3228</v>
       </c>
       <c r="AL37" t="n">
         <v>27.4322</v>
@@ -7214,36 +7258,36 @@
         </is>
       </c>
       <c r="AN37" t="n">
+        <v>30.1593</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="AP37" t="n">
         <v>31.97</v>
       </c>
-      <c r="AO37" t="n">
-        <v>36.71</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>39.9221</v>
-      </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 31.97; TP2: Classic R3 at 36.71; TP3: Extension at 39.92</t>
+          <t>TP1: Fibonacci R2 at 30.16; TP2: Bollinger Upper Band at 30.23; TP3: Classic R2 at 31.97</t>
         </is>
       </c>
       <c r="AR37" t="n">
-        <v>4.22</v>
+        <v>2.06</v>
       </c>
       <c r="AS37" t="n">
-        <v>9.67</v>
+        <v>2.14</v>
       </c>
       <c r="AT37" t="n">
-        <v>13.37</v>
+        <v>4.1</v>
       </c>
       <c r="AU37" t="n">
-        <v>12.96</v>
+        <v>6.48</v>
       </c>
       <c r="AV37" t="n">
-        <v>29.71</v>
+        <v>6.73</v>
       </c>
       <c r="AW37" t="n">
-        <v>41.06</v>
+        <v>12.88</v>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
@@ -7252,7 +7296,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.4); entry: enhanced entry at VWMA (overbought (RSI: 73.4))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 69.0))</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7322,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9.369999999999999</v>
+        <v>9.26</v>
       </c>
       <c r="F38" t="n">
         <v>0.1867</v>
@@ -7295,7 +7339,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>14.7635</v>
+        <v>14.3853</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -7303,19 +7347,19 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>7.13</v>
+        <v>7.38</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3121</v>
+        <v>1.2684</v>
       </c>
       <c r="N38" t="n">
         <v>7618128</v>
       </c>
       <c r="O38" t="n">
-        <v>2014521</v>
+        <v>5830746</v>
       </c>
       <c r="P38" t="n">
-        <v>0.264</v>
+        <v>0.765</v>
       </c>
       <c r="Q38" t="n">
         <v>2126270</v>
@@ -7333,10 +7377,10 @@
         <v>9.75</v>
       </c>
       <c r="V38" t="n">
-        <v>9.2098</v>
+        <v>9.207599999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>7.3379</v>
+        <v>7.3374</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -7349,13 +7393,13 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>9.2729</v>
+        <v>9.2624</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.019500000000001</v>
+        <v>9.0152</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.5198</v>
+        <v>7.5187</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -7368,10 +7412,10 @@
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>0.0296</v>
+        <v>0.0208</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0464</v>
+        <v>0.0446</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -7379,21 +7423,21 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>54.27</v>
+        <v>50.78</v>
       </c>
       <c r="AI38" t="n">
-        <v>9.3507</v>
+        <v>9.343299999999999</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>9.3507</v>
+        <v>9.207599999999999</v>
       </c>
       <c r="AL38" t="n">
-        <v>9.119400000000001</v>
+        <v>9.113799999999999</v>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
@@ -7401,7 +7445,7 @@
         </is>
       </c>
       <c r="AN38" t="n">
-        <v>9.518599999999999</v>
+        <v>9.513199999999999</v>
       </c>
       <c r="AO38" t="n">
         <v>9.7621</v>
@@ -7411,26 +7455,26 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.52; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
+          <t>TP1: Bollinger Upper Band at 9.51; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
         </is>
       </c>
       <c r="AR38" t="n">
-        <v>0.73</v>
+        <v>3.26</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.78</v>
+        <v>5.91</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.84</v>
+        <v>6.07</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.8</v>
+        <v>3.32</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.4</v>
+        <v>6.02</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.56</v>
+        <v>6.18</v>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
@@ -7439,7 +7483,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 54.3))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.8))</t>
         </is>
       </c>
     </row>
@@ -7465,7 +7509,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.681</v>
+        <v>0.677</v>
       </c>
       <c r="F39" t="n">
         <v>0.0134</v>
@@ -7495,10 +7539,10 @@
         <v>26841895</v>
       </c>
       <c r="O39" t="n">
-        <v>22497533</v>
+        <v>32022029</v>
       </c>
       <c r="P39" t="n">
-        <v>0.838</v>
+        <v>1.193</v>
       </c>
       <c r="Q39" t="n">
         <v>9410269</v>
@@ -7516,7 +7560,7 @@
         <v>0.721</v>
       </c>
       <c r="V39" t="n">
-        <v>0.6978</v>
+        <v>0.6977</v>
       </c>
       <c r="W39" t="n">
         <v>0.783</v>
@@ -7532,10 +7576,10 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>0.6944</v>
+        <v>0.694</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.7144</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="AB39" t="n">
         <v>0.7244</v>
@@ -7551,10 +7595,10 @@
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.0053</v>
+        <v>-0.0054</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -7562,14 +7606,14 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>41.37</v>
+        <v>39.1</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.7056</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-06 09:36:52</t>
+          <t>2026-08-06 10:55:10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7626,7 +7670,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="F40" t="n">
         <v>0.0917</v>
@@ -7654,10 +7698,10 @@
         <v>6231932</v>
       </c>
       <c r="O40" t="n">
-        <v>2032989</v>
+        <v>2458531</v>
       </c>
       <c r="P40" t="n">
-        <v>0.326</v>
+        <v>0.395</v>
       </c>
       <c r="Q40" t="n">
         <v>4539405</v>
@@ -7675,10 +7719,10 @@
         <v>4.98</v>
       </c>
       <c r="V40" t="n">
-        <v>3.7906</v>
+        <v>3.79</v>
       </c>
       <c r="W40" t="n">
-        <v>3.0131</v>
+        <v>3.013</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -7691,13 +7735,13 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>4.2382</v>
+        <v>4.2353</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.8952</v>
+        <v>3.894</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.1546</v>
+        <v>3.1543</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -7710,10 +7754,10 @@
         </is>
       </c>
       <c r="AE40" t="n">
-        <v>0.2566</v>
+        <v>0.2542</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.2214</v>
+        <v>0.2209</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -7721,14 +7765,14 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>65.73999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.3581</v>
+        <v>4.3582</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -7746,7 +7790,7 @@
         <v>4.9278</v>
       </c>
       <c r="AO40" t="n">
-        <v>4.9541</v>
+        <v>4.9495</v>
       </c>
       <c r="AP40" t="n">
         <v>5.2367</v>
@@ -7769,7 +7813,7 @@
         <v>12.51</v>
       </c>
       <c r="AV40" t="n">
-        <v>13.11</v>
+        <v>13</v>
       </c>
       <c r="AW40" t="n">
         <v>19.56</v>
@@ -7781,7 +7825,7 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 65.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 64.5))</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7851,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>52.41</v>
+        <v>52.4</v>
       </c>
       <c r="F41" t="n">
         <v>1.0386</v>
@@ -7824,7 +7868,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>132.6444</v>
+        <v>118.2397</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -7832,19 +7876,19 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.74</v>
+        <v>4.31</v>
       </c>
       <c r="M41" t="n">
-        <v>13.9375</v>
+        <v>12.0956</v>
       </c>
       <c r="N41" t="n">
         <v>2154531</v>
       </c>
       <c r="O41" t="n">
-        <v>577893</v>
+        <v>685344</v>
       </c>
       <c r="P41" t="n">
-        <v>0.268</v>
+        <v>0.318</v>
       </c>
       <c r="Q41" t="n">
         <v>1245469</v>
@@ -7862,7 +7906,7 @@
         <v>48.49</v>
       </c>
       <c r="V41" t="n">
-        <v>47.7932</v>
+        <v>47.793</v>
       </c>
       <c r="W41" t="n">
         <v>37.5287</v>
@@ -7878,13 +7922,13 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>50.2627</v>
+        <v>50.2618</v>
       </c>
       <c r="AA41" t="n">
-        <v>48.085</v>
+        <v>48.0846</v>
       </c>
       <c r="AB41" t="n">
-        <v>39.07</v>
+        <v>39.0699</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -7897,10 +7941,10 @@
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>1.5722</v>
+        <v>1.5714</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.3455</v>
+        <v>1.3453</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -7908,14 +7952,14 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>65.54000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>49.4944</v>
+        <v>49.5008</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK41" t="n">
@@ -7933,14 +7977,14 @@
         <v>53.2048</v>
       </c>
       <c r="AO41" t="n">
-        <v>54.7863</v>
+        <v>54.7847</v>
       </c>
       <c r="AP41" t="n">
         <v>54.8285</v>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 54.79; TP3: Fibonacci R2 at 54.83</t>
+          <t>TP1: Fibonacci R1 at 53.2; TP2: Bollinger Upper Band at 54.78; TP3: Fibonacci R2 at 54.83</t>
         </is>
       </c>
       <c r="AR41" t="n">
@@ -7994,7 +8038,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>37.19</v>
+        <v>37</v>
       </c>
       <c r="F42" t="n">
         <v>0.7379</v>
@@ -8028,10 +8072,10 @@
         <v>1885613</v>
       </c>
       <c r="O42" t="n">
-        <v>502954</v>
+        <v>1160694</v>
       </c>
       <c r="P42" t="n">
-        <v>0.267</v>
+        <v>0.616</v>
       </c>
       <c r="Q42" t="n">
         <v>955007</v>
@@ -8049,10 +8093,10 @@
         <v>38.8</v>
       </c>
       <c r="V42" t="n">
-        <v>38.3248</v>
+        <v>38.321</v>
       </c>
       <c r="W42" t="n">
-        <v>35.8694</v>
+        <v>35.8685</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -8065,13 +8109,13 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>37.1906</v>
+        <v>37.1725</v>
       </c>
       <c r="AA42" t="n">
-        <v>38.2734</v>
+        <v>38.266</v>
       </c>
       <c r="AB42" t="n">
-        <v>36.6847</v>
+        <v>36.6828</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -8084,10 +8128,10 @@
         </is>
       </c>
       <c r="AE42" t="n">
-        <v>-0.276</v>
+        <v>-0.2911</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.3947</v>
+        <v>-0.3977</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -8095,21 +8139,21 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>48.23</v>
+        <v>46.7</v>
       </c>
       <c r="AI42" t="n">
-        <v>37.3971</v>
+        <v>37.3885</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>36.0955</v>
+        <v>36.0799</v>
       </c>
       <c r="AL42" t="n">
-        <v>35.8694</v>
+        <v>35.8685</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
@@ -8120,7 +8164,7 @@
         <v>38.25</v>
       </c>
       <c r="AO42" t="n">
-        <v>38.4905</v>
+        <v>38.4871</v>
       </c>
       <c r="AP42" t="n">
         <v>38.5567</v>
@@ -8131,22 +8175,22 @@
         </is>
       </c>
       <c r="AR42" t="n">
-        <v>9.529999999999999</v>
+        <v>10.27</v>
       </c>
       <c r="AS42" t="n">
-        <v>10.6</v>
+        <v>11.39</v>
       </c>
       <c r="AT42" t="n">
-        <v>10.89</v>
+        <v>11.72</v>
       </c>
       <c r="AU42" t="n">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="AV42" t="n">
-        <v>6.64</v>
+        <v>6.67</v>
       </c>
       <c r="AW42" t="n">
-        <v>6.82</v>
+        <v>6.86</v>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
@@ -8155,7 +8199,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 48.2))</t>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.7))</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8225,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6.39</v>
+        <v>6.26</v>
       </c>
       <c r="F43" t="n">
         <v>0.1183</v>
@@ -8211,10 +8255,10 @@
         <v>2877836</v>
       </c>
       <c r="O43" t="n">
-        <v>11237040</v>
+        <v>12454010</v>
       </c>
       <c r="P43" t="n">
-        <v>3.905</v>
+        <v>4.328</v>
       </c>
       <c r="Q43" t="n">
         <v>2134370</v>
@@ -8232,10 +8276,10 @@
         <v>6.28</v>
       </c>
       <c r="V43" t="n">
-        <v>6.3312</v>
+        <v>6.3286</v>
       </c>
       <c r="W43" t="n">
-        <v>5.8459</v>
+        <v>5.8453</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -8248,13 +8292,13 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>6.7425</v>
+        <v>6.7301</v>
       </c>
       <c r="AA43" t="n">
-        <v>6.3664</v>
+        <v>6.3613</v>
       </c>
       <c r="AB43" t="n">
-        <v>5.724</v>
+        <v>5.7227</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -8267,10 +8311,10 @@
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>0.1778</v>
+        <v>0.1674</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.2121</v>
+        <v>0.2101</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
@@ -8278,21 +8322,21 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>44.17</v>
+        <v>41.89</v>
       </c>
       <c r="AI43" t="n">
-        <v>6.7764</v>
+        <v>6.7564</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK43" t="n">
-        <v>6.2449</v>
+        <v>6.18</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.1841</v>
+        <v>6.1586</v>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
@@ -8303,33 +8347,33 @@
         <v>7.2151</v>
       </c>
       <c r="AO43" t="n">
-        <v>7.3059</v>
+        <v>7.3184</v>
       </c>
       <c r="AP43" t="n">
         <v>7.45</v>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.31; TP3: Classic R1 at 7.45</t>
+          <t>TP1: Fibonacci R1 at 7.22; TP2: Bollinger Upper Band at 7.32; TP3: Classic R1 at 7.45</t>
         </is>
       </c>
       <c r="AR43" t="n">
-        <v>15.98</v>
+        <v>48.43</v>
       </c>
       <c r="AS43" t="n">
-        <v>17.47</v>
+        <v>53.27</v>
       </c>
       <c r="AT43" t="n">
-        <v>19.84</v>
+        <v>59.42</v>
       </c>
       <c r="AU43" t="n">
-        <v>15.54</v>
+        <v>16.75</v>
       </c>
       <c r="AV43" t="n">
-        <v>16.99</v>
+        <v>18.42</v>
       </c>
       <c r="AW43" t="n">
-        <v>19.3</v>
+        <v>20.55</v>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
@@ -8338,7 +8382,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 44.2))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Classic S1 (neutral (RSI: 41.9))</t>
         </is>
       </c>
     </row>
@@ -8398,10 +8442,10 @@
         <v>35503</v>
       </c>
       <c r="O44" t="n">
-        <v>27353</v>
+        <v>36789</v>
       </c>
       <c r="P44" t="n">
-        <v>0.77</v>
+        <v>1.036</v>
       </c>
       <c r="Q44" t="n">
         <v>14978</v>
@@ -8468,11 +8512,11 @@
         <v>54.25</v>
       </c>
       <c r="AI44" t="n">
-        <v>382.2643</v>
+        <v>382.2502</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK44" t="n">
@@ -8551,7 +8595,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>296.6</v>
+        <v>294.99</v>
       </c>
       <c r="F45" t="n">
         <v>6.0439</v>
@@ -8579,10 +8623,10 @@
         <v>94109</v>
       </c>
       <c r="O45" t="n">
-        <v>118985</v>
+        <v>133230</v>
       </c>
       <c r="P45" t="n">
-        <v>1.264</v>
+        <v>1.416</v>
       </c>
       <c r="Q45" t="n">
         <v>42089</v>
@@ -8600,10 +8644,10 @@
         <v>247.97</v>
       </c>
       <c r="V45" t="n">
-        <v>225.2266</v>
+        <v>225.1944</v>
       </c>
       <c r="W45" t="n">
-        <v>189.0947</v>
+        <v>189.0867</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -8616,13 +8660,13 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>257.4761</v>
+        <v>257.3228</v>
       </c>
       <c r="AA45" t="n">
-        <v>232.3248</v>
+        <v>232.2617</v>
       </c>
       <c r="AB45" t="n">
-        <v>186.2091</v>
+        <v>186.1931</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -8635,10 +8679,10 @@
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>20.1941</v>
+        <v>20.0657</v>
       </c>
       <c r="AF45" t="n">
-        <v>15.0628</v>
+        <v>15.0372</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -8646,18 +8690,18 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>67.91</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="AI45" t="n">
-        <v>270.1849</v>
+        <v>270.2452</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>270.1849</v>
+        <v>270.2452</v>
       </c>
       <c r="AL45" t="n">
         <v>265.1759</v>
@@ -8668,7 +8712,7 @@
         </is>
       </c>
       <c r="AN45" t="n">
-        <v>304.2588</v>
+        <v>303.907</v>
       </c>
       <c r="AO45" t="n">
         <v>307.9633</v>
@@ -8678,26 +8722,26 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 304.26; TP2: Classic R1 at 307.96; TP3: Fibonacci R2 at 308.85</t>
+          <t>TP1: Bollinger Upper Band at 303.91; TP2: Classic R1 at 307.96; TP3: Fibonacci R2 at 308.85</t>
         </is>
       </c>
       <c r="AR45" t="n">
-        <v>6.8</v>
+        <v>6.64</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.54</v>
+        <v>7.44</v>
       </c>
       <c r="AT45" t="n">
-        <v>7.72</v>
+        <v>7.62</v>
       </c>
       <c r="AU45" t="n">
-        <v>12.61</v>
+        <v>12.46</v>
       </c>
       <c r="AV45" t="n">
-        <v>13.98</v>
+        <v>13.96</v>
       </c>
       <c r="AW45" t="n">
-        <v>14.31</v>
+        <v>14.29</v>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
@@ -8706,7 +8750,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.9))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.1))</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8776,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="F46" t="n">
         <v>0.1633</v>
@@ -8760,10 +8804,10 @@
         <v>2507878</v>
       </c>
       <c r="O46" t="n">
-        <v>810484</v>
+        <v>2164697</v>
       </c>
       <c r="P46" t="n">
-        <v>0.323</v>
+        <v>0.863</v>
       </c>
       <c r="Q46" t="n">
         <v>2521174</v>
@@ -8781,10 +8825,10 @@
         <v>8.9</v>
       </c>
       <c r="V46" t="n">
-        <v>7.0454</v>
+        <v>7.042</v>
       </c>
       <c r="W46" t="n">
-        <v>6.4475</v>
+        <v>6.4466</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -8797,13 +8841,13 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>7.9392</v>
+        <v>7.923</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.308</v>
+        <v>7.3014</v>
       </c>
       <c r="AB46" t="n">
-        <v>6.3773</v>
+        <v>6.3756</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -8816,10 +8860,10 @@
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>0.3457</v>
+        <v>0.3321</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.4162</v>
+        <v>0.4135</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -8827,21 +8871,21 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>61.11</v>
+        <v>56.31</v>
       </c>
       <c r="AI46" t="n">
-        <v>8.085699999999999</v>
+        <v>8.083</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>8.085699999999999</v>
+        <v>7.555</v>
       </c>
       <c r="AL46" t="n">
-        <v>7.3047</v>
+        <v>7.2969</v>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
@@ -8852,33 +8896,33 @@
         <v>8.755100000000001</v>
       </c>
       <c r="AO46" t="n">
-        <v>8.8453</v>
+        <v>8.8361</v>
       </c>
       <c r="AP46" t="n">
         <v>9.2333</v>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.85; TP3: Classic R1 at 9.23</t>
+          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.84; TP3: Classic R1 at 9.23</t>
         </is>
       </c>
       <c r="AR46" t="n">
-        <v>0.86</v>
+        <v>4.65</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.97</v>
+        <v>4.96</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.47</v>
+        <v>6.5</v>
       </c>
       <c r="AU46" t="n">
-        <v>8.279999999999999</v>
+        <v>15.88</v>
       </c>
       <c r="AV46" t="n">
-        <v>9.390000000000001</v>
+        <v>16.96</v>
       </c>
       <c r="AW46" t="n">
-        <v>14.19</v>
+        <v>22.21</v>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
@@ -8887,7 +8931,7 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 56.3))</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8957,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="F47" t="n">
         <v>0.0297</v>
@@ -8947,10 +8991,10 @@
         <v>41568258</v>
       </c>
       <c r="O47" t="n">
-        <v>31894200</v>
+        <v>54027331</v>
       </c>
       <c r="P47" t="n">
-        <v>0.767</v>
+        <v>1.3</v>
       </c>
       <c r="Q47" t="n">
         <v>31669522</v>
@@ -8966,10 +9010,10 @@
         <v>1.57</v>
       </c>
       <c r="V47" t="n">
-        <v>1.3172</v>
+        <v>1.317</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1972</v>
+        <v>1.1971</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -8982,13 +9026,13 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>1.4423</v>
+        <v>1.4413</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.3581</v>
+        <v>1.3577</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.167</v>
+        <v>1.1669</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -9001,25 +9045,25 @@
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>0.0648</v>
+        <v>0.064</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.0644</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>59.68</v>
+        <v>58.3</v>
       </c>
       <c r="AI47" t="n">
         <v>1.4566</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK47" t="n">
@@ -9037,7 +9081,7 @@
         <v>1.5828</v>
       </c>
       <c r="AO47" t="n">
-        <v>1.6147</v>
+        <v>1.6137</v>
       </c>
       <c r="AP47" t="n">
         <v>1.66</v>
@@ -9060,7 +9104,7 @@
         <v>8.6</v>
       </c>
       <c r="AV47" t="n">
-        <v>10.78</v>
+        <v>10.72</v>
       </c>
       <c r="AW47" t="n">
         <v>13.89</v>
@@ -9072,7 +9116,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 59.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 58.3))</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9142,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.16</v>
+        <v>1.125</v>
       </c>
       <c r="F48" t="n">
         <v>0.0223</v>
@@ -9121,7 +9165,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>16.81</v>
+        <v>16.3</v>
       </c>
       <c r="M48" t="n">
         <v>0.06900000000000001</v>
@@ -9130,10 +9174,10 @@
         <v>20237762</v>
       </c>
       <c r="O48" t="n">
-        <v>27745867</v>
+        <v>38469949</v>
       </c>
       <c r="P48" t="n">
-        <v>1.371</v>
+        <v>1.901</v>
       </c>
       <c r="Q48" t="n">
         <v>25050107</v>
@@ -9151,10 +9195,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5944</v>
+        <v>0.5937</v>
       </c>
       <c r="W48" t="n">
-        <v>0.4384</v>
+        <v>0.4383</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -9167,13 +9211,13 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>0.848</v>
+        <v>0.8447</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.6693</v>
+        <v>0.6679</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.4728</v>
+        <v>0.4725</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -9186,10 +9230,10 @@
         </is>
       </c>
       <c r="AE48" t="n">
-        <v>0.1357</v>
+        <v>0.1329</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.113</v>
+        <v>0.1125</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -9197,18 +9241,18 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>87.15000000000001</v>
+        <v>86.25</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.8266</v>
+        <v>0.8287</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>0.8275</v>
+        <v>0.8287</v>
       </c>
       <c r="AL48" t="n">
         <v>0.8226</v>
@@ -9219,36 +9263,36 @@
         </is>
       </c>
       <c r="AN48" t="n">
+        <v>1.1405</v>
+      </c>
+      <c r="AO48" t="n">
         <v>1.2073</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>1.6633</v>
       </c>
-      <c r="AP48" t="n">
-        <v>1.9826</v>
-      </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 1.21; TP2: Classic R3 at 1.66; TP3: Extension at 1.98</t>
+          <t>TP1: Bollinger Upper Band at 1.14; TP2: Classic R2 at 1.21; TP3: Classic R3 at 1.66</t>
         </is>
       </c>
       <c r="AR48" t="n">
-        <v>78.15000000000001</v>
+        <v>51.76</v>
       </c>
       <c r="AS48" t="n">
-        <v>171.98</v>
+        <v>62.85</v>
       </c>
       <c r="AT48" t="n">
-        <v>237.67</v>
+        <v>138.54</v>
       </c>
       <c r="AU48" t="n">
-        <v>45.9</v>
+        <v>37.63</v>
       </c>
       <c r="AV48" t="n">
-        <v>101</v>
+        <v>45.69</v>
       </c>
       <c r="AW48" t="n">
-        <v>139.59</v>
+        <v>100.72</v>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
@@ -9257,7 +9301,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (87.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 87.1))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (86.3); entry: enhanced entry at VWMA (overbought (RSI: 86.3))</t>
         </is>
       </c>
     </row>
@@ -9283,7 +9327,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.513</v>
+        <v>0.512</v>
       </c>
       <c r="F49" t="n">
         <v>0.0103</v>
@@ -9313,10 +9357,10 @@
         <v>20438708</v>
       </c>
       <c r="O49" t="n">
-        <v>9788594</v>
+        <v>14949510</v>
       </c>
       <c r="P49" t="n">
-        <v>0.479</v>
+        <v>0.731</v>
       </c>
       <c r="Q49" t="n">
         <v>17915257</v>
@@ -9350,10 +9394,10 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>0.5008</v>
+        <v>0.5007</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.4715</v>
+        <v>0.4714</v>
       </c>
       <c r="AB49" t="n">
         <v>0.4451</v>
@@ -9380,14 +9424,14 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>56.82</v>
+        <v>56.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.5216</v>
+        <v>0.5215</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9472,10 +9516,10 @@
         <v>12041</v>
       </c>
       <c r="O50" t="n">
-        <v>8463</v>
+        <v>10209</v>
       </c>
       <c r="P50" t="n">
-        <v>0.703</v>
+        <v>0.848</v>
       </c>
       <c r="Q50" t="n">
         <v>7586</v>
@@ -9542,15 +9586,15 @@
         <v>68.23999999999999</v>
       </c>
       <c r="AI50" t="n">
-        <v>467.8658</v>
+        <v>467.9243</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>467.8658</v>
+        <v>467.9243</v>
       </c>
       <c r="AL50" t="n">
         <v>455.5693</v>
@@ -9575,22 +9619,22 @@
         </is>
       </c>
       <c r="AR50" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="AT50" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="AU50" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="AV50" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AW50" t="n">
-        <v>10.93</v>
+        <v>10.91</v>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
@@ -9625,7 +9669,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1299.94</v>
+        <v>1270.5</v>
       </c>
       <c r="F51" t="n">
         <v>25.1186</v>
@@ -9653,10 +9697,10 @@
         <v>2390</v>
       </c>
       <c r="O51" t="n">
-        <v>1867</v>
+        <v>2941</v>
       </c>
       <c r="P51" t="n">
-        <v>0.781</v>
+        <v>1.23</v>
       </c>
       <c r="Q51" t="n">
         <v>1079</v>
@@ -9674,10 +9718,10 @@
         <v>1275</v>
       </c>
       <c r="V51" t="n">
-        <v>1172.6738</v>
+        <v>1172.085</v>
       </c>
       <c r="W51" t="n">
-        <v>919.7954</v>
+        <v>919.6482</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -9690,13 +9734,13 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>1232.7462</v>
+        <v>1229.9424</v>
       </c>
       <c r="AA51" t="n">
-        <v>1165.4427</v>
+        <v>1164.2882</v>
       </c>
       <c r="AB51" t="n">
-        <v>935.5155999999999</v>
+        <v>935.2226000000001</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -9709,10 +9753,10 @@
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>32.9807</v>
+        <v>30.6322</v>
       </c>
       <c r="AF51" t="n">
-        <v>30.1711</v>
+        <v>29.7014</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -9720,21 +9764,21 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>65.42</v>
+        <v>61.51</v>
       </c>
       <c r="AI51" t="n">
-        <v>1250.08</v>
+        <v>1249.5702</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK51" t="n">
         <v>1264.51</v>
       </c>
       <c r="AL51" t="n">
-        <v>1167.3486</v>
+        <v>1170.7694</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
@@ -9742,37 +9786,37 @@
         </is>
       </c>
       <c r="AN51" t="n">
+        <v>1292.7606</v>
+      </c>
+      <c r="AO51" t="n">
         <v>1312.2368</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>1341.2533</v>
       </c>
-      <c r="AP51" t="n">
-        <v>1371.9165</v>
-      </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 1312.24; TP2: Classic R1 at 1341.25; TP3: Fibonacci R2 at 1371.92</t>
+          <t>TP1: Bollinger Upper Band at 1292.76; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
         </is>
       </c>
       <c r="AR51" t="n">
-        <v>0.49</v>
+        <v>0.3</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="AU51" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AV51" t="n">
         <v>3.77</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AW51" t="n">
         <v>6.07</v>
       </c>
-      <c r="AW51" t="n">
-        <v>8.49</v>
-      </c>
       <c r="AX51" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -9780,7 +9824,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 65.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.5))</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9850,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>255.2</v>
+        <v>253.12</v>
       </c>
       <c r="F52" t="n">
         <v>5.0498</v>
@@ -9823,7 +9867,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>332.4615</v>
+        <v>341.889</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -9831,19 +9875,19 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>7.69</v>
+        <v>7.42</v>
       </c>
       <c r="M52" t="n">
-        <v>32.9427</v>
+        <v>34.117</v>
       </c>
       <c r="N52" t="n">
         <v>93241</v>
       </c>
       <c r="O52" t="n">
-        <v>44140</v>
+        <v>72508</v>
       </c>
       <c r="P52" t="n">
-        <v>0.473</v>
+        <v>0.778</v>
       </c>
       <c r="Q52" t="n">
         <v>38616</v>
@@ -9861,10 +9905,10 @@
         <v>255.5774</v>
       </c>
       <c r="V52" t="n">
-        <v>253.222</v>
+        <v>253.1804</v>
       </c>
       <c r="W52" t="n">
-        <v>246.7172</v>
+        <v>246.7068</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -9877,13 +9921,13 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>246.4956</v>
+        <v>246.2975</v>
       </c>
       <c r="AA52" t="n">
-        <v>250.5097</v>
+        <v>250.4281</v>
       </c>
       <c r="AB52" t="n">
-        <v>234.6405</v>
+        <v>234.6198</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -9896,10 +9940,10 @@
         </is>
       </c>
       <c r="AE52" t="n">
-        <v>0.1319</v>
+        <v>-0.034</v>
       </c>
       <c r="AF52" t="n">
-        <v>-1.6387</v>
+        <v>-1.6719</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -9907,29 +9951,29 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>62.48</v>
+        <v>60.05</v>
       </c>
       <c r="AI52" t="n">
-        <v>244.4723</v>
+        <v>244.5624</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK52" t="n">
-        <v>253.222</v>
+        <v>249.1856</v>
       </c>
       <c r="AL52" t="n">
-        <v>249.1856</v>
+        <v>246.7068</v>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at 200 SMA</t>
         </is>
       </c>
       <c r="AN52" t="n">
-        <v>258.8032</v>
+        <v>258.7824</v>
       </c>
       <c r="AO52" t="n">
         <v>258.9567</v>
@@ -9939,26 +9983,26 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 258.8; TP2: Classic R2 at 258.96; TP3: Classic R3 at 276.45</t>
+          <t>TP1: 100 SMA at 258.78; TP2: Classic R2 at 258.96; TP3: Classic R3 at 276.45</t>
         </is>
       </c>
       <c r="AR52" t="n">
-        <v>1.38</v>
+        <v>3.87</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.42</v>
+        <v>3.94</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.75</v>
+        <v>11</v>
       </c>
       <c r="AU52" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.26</v>
+        <v>3.92</v>
       </c>
       <c r="AW52" t="n">
-        <v>9.17</v>
+        <v>10.94</v>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
@@ -9967,7 +10011,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 62.5))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (overbought (RSI: 60.0))</t>
         </is>
       </c>
     </row>
@@ -9993,7 +10037,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>197.59</v>
+        <v>193.5</v>
       </c>
       <c r="F53" t="n">
         <v>4.0284</v>
@@ -10021,10 +10065,10 @@
         <v>95299</v>
       </c>
       <c r="O53" t="n">
-        <v>88508</v>
+        <v>117933</v>
       </c>
       <c r="P53" t="n">
-        <v>0.929</v>
+        <v>1.238</v>
       </c>
       <c r="Q53" t="n">
         <v>103262</v>
@@ -10042,10 +10086,10 @@
         <v>197.49</v>
       </c>
       <c r="V53" t="n">
-        <v>149.7146</v>
+        <v>149.6328</v>
       </c>
       <c r="W53" t="n">
-        <v>124.6646</v>
+        <v>124.6442</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -10058,13 +10102,13 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>175.2103</v>
+        <v>174.8208</v>
       </c>
       <c r="AA53" t="n">
-        <v>154.5873</v>
+        <v>154.4269</v>
       </c>
       <c r="AB53" t="n">
-        <v>122.3071</v>
+        <v>122.2664</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -10077,10 +10121,10 @@
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>15.9747</v>
+        <v>15.6484</v>
       </c>
       <c r="AF53" t="n">
-        <v>13.6629</v>
+        <v>13.5976</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -10088,18 +10132,18 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>63.04</v>
+        <v>60.96</v>
       </c>
       <c r="AI53" t="n">
-        <v>178.0215</v>
+        <v>178.0351</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK53" t="n">
-        <v>178.0215</v>
+        <v>178.0351</v>
       </c>
       <c r="AL53" t="n">
         <v>175</v>
@@ -10113,33 +10157,33 @@
         <v>208.4527</v>
       </c>
       <c r="AO53" t="n">
-        <v>219.6222</v>
+        <v>218.9944</v>
       </c>
       <c r="AP53" t="n">
         <v>224.8967</v>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 219.62; TP3: Classic R1 at 224.9</t>
+          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 218.99; TP3: Classic R1 at 224.9</t>
         </is>
       </c>
       <c r="AR53" t="n">
-        <v>10.07</v>
+        <v>10.02</v>
       </c>
       <c r="AS53" t="n">
-        <v>13.77</v>
+        <v>13.5</v>
       </c>
       <c r="AT53" t="n">
-        <v>15.51</v>
+        <v>15.44</v>
       </c>
       <c r="AU53" t="n">
         <v>17.09</v>
       </c>
       <c r="AV53" t="n">
-        <v>23.37</v>
+        <v>23.01</v>
       </c>
       <c r="AW53" t="n">
-        <v>26.33</v>
+        <v>26.32</v>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
@@ -10148,7 +10192,7 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.0))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.0))</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10218,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7.23</v>
+        <v>7.19</v>
       </c>
       <c r="F54" t="n">
         <v>0.1442</v>
@@ -10208,10 +10252,10 @@
         <v>24851881</v>
       </c>
       <c r="O54" t="n">
-        <v>1733508</v>
+        <v>5784364</v>
       </c>
       <c r="P54" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.233</v>
       </c>
       <c r="Q54" t="n">
         <v>14881478</v>
@@ -10229,10 +10273,10 @@
         <v>7.79</v>
       </c>
       <c r="V54" t="n">
-        <v>6.6958</v>
+        <v>6.695</v>
       </c>
       <c r="W54" t="n">
-        <v>5.8784</v>
+        <v>5.8782</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -10245,13 +10289,13 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>7.2061</v>
+        <v>7.2023</v>
       </c>
       <c r="AA54" t="n">
-        <v>6.8085</v>
+        <v>6.8069</v>
       </c>
       <c r="AB54" t="n">
-        <v>5.8309</v>
+        <v>5.8305</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -10264,10 +10308,10 @@
         </is>
       </c>
       <c r="AE54" t="n">
-        <v>0.1514</v>
+        <v>0.1482</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.2264</v>
+        <v>0.2257</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -10275,21 +10319,21 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>54.29</v>
+        <v>52.87</v>
       </c>
       <c r="AI54" t="n">
-        <v>7.3319</v>
+        <v>7.331</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK54" t="n">
         <v>6.995</v>
       </c>
       <c r="AL54" t="n">
-        <v>6.8877</v>
+        <v>6.8835</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
@@ -10300,7 +10344,7 @@
         <v>7.6476</v>
       </c>
       <c r="AO54" t="n">
-        <v>7.7773</v>
+        <v>7.7775</v>
       </c>
       <c r="AP54" t="n">
         <v>7.8167</v>
@@ -10311,19 +10355,19 @@
         </is>
       </c>
       <c r="AR54" t="n">
-        <v>6.08</v>
+        <v>5.85</v>
       </c>
       <c r="AS54" t="n">
-        <v>7.29</v>
+        <v>7.02</v>
       </c>
       <c r="AT54" t="n">
-        <v>7.66</v>
+        <v>7.37</v>
       </c>
       <c r="AU54" t="n">
         <v>9.33</v>
       </c>
       <c r="AV54" t="n">
-        <v>11.18</v>
+        <v>11.19</v>
       </c>
       <c r="AW54" t="n">
         <v>11.75</v>
@@ -10335,7 +10379,7 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 52.9))</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10405,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12.62</v>
+        <v>12.55</v>
       </c>
       <c r="F55" t="n">
         <v>0.2565</v>
@@ -10384,7 +10428,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>14.07</v>
+        <v>13.99</v>
       </c>
       <c r="M55" t="n">
         <v>0.8969</v>
@@ -10393,10 +10437,10 @@
         <v>3418730</v>
       </c>
       <c r="O55" t="n">
-        <v>141698</v>
+        <v>174492</v>
       </c>
       <c r="P55" t="n">
-        <v>0.041</v>
+        <v>0.051</v>
       </c>
       <c r="Q55" t="n">
         <v>762066</v>
@@ -10414,10 +10458,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="V55" t="n">
-        <v>9.6082</v>
+        <v>9.6068</v>
       </c>
       <c r="W55" t="n">
-        <v>6.299</v>
+        <v>6.2986</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -10430,13 +10474,13 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>11.0788</v>
+        <v>11.0721</v>
       </c>
       <c r="AA55" t="n">
-        <v>9.8028</v>
+        <v>9.8001</v>
       </c>
       <c r="AB55" t="n">
-        <v>6.9135</v>
+        <v>6.9128</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -10449,10 +10493,10 @@
         </is>
       </c>
       <c r="AE55" t="n">
-        <v>0.968</v>
+        <v>0.9625</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.7524</v>
+        <v>0.7513</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -10460,14 +10504,14 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>74.39</v>
+        <v>73.19</v>
       </c>
       <c r="AI55" t="n">
-        <v>10.6714</v>
+        <v>10.6731</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK55" t="n">
@@ -10485,21 +10529,21 @@
         <v>13.4067</v>
       </c>
       <c r="AO55" t="n">
-        <v>13.4406</v>
+        <v>13.4275</v>
       </c>
       <c r="AP55" t="n">
         <v>16.3367</v>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 13.41; TP2: Bollinger Upper Band at 13.44; TP3: Classic R3 at 16.34</t>
+          <t>TP1: Classic R2 at 13.41; TP2: Bollinger Upper Band at 13.43; TP3: Classic R3 at 16.34</t>
         </is>
       </c>
       <c r="AR55" t="n">
         <v>0.64</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="AT55" t="n">
         <v>1.83</v>
@@ -10508,7 +10552,7 @@
         <v>13.12</v>
       </c>
       <c r="AV55" t="n">
-        <v>13.41</v>
+        <v>13.3</v>
       </c>
       <c r="AW55" t="n">
         <v>37.84</v>
@@ -10520,7 +10564,7 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.4); entry: enhanced entry at Parabolic SAR (overbought (RSI: 74.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.2); entry: enhanced entry at Parabolic SAR (overbought (RSI: 73.2))</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10690,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10725,7 +10769,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>323.07</v>
+        <v>318.2</v>
       </c>
       <c r="F57" t="n">
         <v>6.3377</v>
@@ -10748,7 +10792,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>14.18</v>
+        <v>13.97</v>
       </c>
       <c r="M57" t="n">
         <v>22.7816</v>
@@ -10757,10 +10801,10 @@
         <v>371138</v>
       </c>
       <c r="O57" t="n">
-        <v>331197</v>
+        <v>425554</v>
       </c>
       <c r="P57" t="n">
-        <v>0.892</v>
+        <v>1.147</v>
       </c>
       <c r="Q57" t="n">
         <v>186797</v>
@@ -10778,10 +10822,10 @@
         <v>252.69</v>
       </c>
       <c r="V57" t="n">
-        <v>246.3162</v>
+        <v>246.2188</v>
       </c>
       <c r="W57" t="n">
-        <v>186.8281</v>
+        <v>186.8038</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -10794,13 +10838,13 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>284.5065</v>
+        <v>284.0427</v>
       </c>
       <c r="AA57" t="n">
-        <v>252.188</v>
+        <v>251.997</v>
       </c>
       <c r="AB57" t="n">
-        <v>189.7298</v>
+        <v>189.6813</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -10813,10 +10857,10 @@
         </is>
       </c>
       <c r="AE57" t="n">
-        <v>22.1603</v>
+        <v>21.7718</v>
       </c>
       <c r="AF57" t="n">
-        <v>18.4147</v>
+        <v>18.337</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -10824,14 +10868,14 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>72.44</v>
+        <v>71.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>284.5052</v>
+        <v>284.69</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK57" t="n">
@@ -10846,7 +10890,7 @@
         </is>
       </c>
       <c r="AN57" t="n">
-        <v>336.522</v>
+        <v>335.5581</v>
       </c>
       <c r="AO57" t="n">
         <v>337.12</v>
@@ -10856,11 +10900,11 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 336.52; TP2: Classic R2 at 337.12; TP3: Classic R3 at 398.9</t>
+          <t>TP1: Bollinger Upper Band at 335.56; TP2: Classic R2 at 337.12; TP3: Classic R3 at 398.9</t>
         </is>
       </c>
       <c r="AR57" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AS57" t="n">
         <v>0.99</v>
@@ -10869,7 +10913,7 @@
         <v>2.43</v>
       </c>
       <c r="AU57" t="n">
-        <v>14.19</v>
+        <v>13.86</v>
       </c>
       <c r="AV57" t="n">
         <v>14.39</v>
@@ -10884,7 +10928,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.4); entry: enhanced entry at Parabolic SAR (overbought (RSI: 72.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.2); entry: enhanced entry at Parabolic SAR (overbought (RSI: 71.2))</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10954,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>18.35</v>
+        <v>18.06</v>
       </c>
       <c r="F58" t="n">
         <v>0.3618</v>
@@ -10944,10 +10988,10 @@
         <v>748383</v>
       </c>
       <c r="O58" t="n">
-        <v>553622</v>
+        <v>1115649</v>
       </c>
       <c r="P58" t="n">
-        <v>0.74</v>
+        <v>1.491</v>
       </c>
       <c r="Q58" t="n">
         <v>602099</v>
@@ -10965,10 +11009,10 @@
         <v>19.59</v>
       </c>
       <c r="V58" t="n">
-        <v>16.1674</v>
+        <v>16.1616</v>
       </c>
       <c r="W58" t="n">
-        <v>15.7365</v>
+        <v>15.735</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -10981,13 +11025,13 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>17.0909</v>
+        <v>17.0633</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.3891</v>
+        <v>16.3777</v>
       </c>
       <c r="AB58" t="n">
-        <v>15.1203</v>
+        <v>15.1174</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -11000,10 +11044,10 @@
         </is>
       </c>
       <c r="AE58" t="n">
-        <v>0.7163</v>
+        <v>0.6932</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.4632</v>
+        <v>0.4585</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -11011,18 +11055,18 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>65.75</v>
+        <v>63.29</v>
       </c>
       <c r="AI58" t="n">
-        <v>17.5215</v>
+        <v>17.5247</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK58" t="n">
-        <v>17.5215</v>
+        <v>17.5247</v>
       </c>
       <c r="AL58" t="n">
         <v>17.0657</v>
@@ -11036,33 +11080,33 @@
         <v>19.0869</v>
       </c>
       <c r="AO58" t="n">
-        <v>19.1918</v>
+        <v>19.1414</v>
       </c>
       <c r="AP58" t="n">
         <v>19.6033</v>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 19.09; TP2: Bollinger Upper Band at 19.19; TP3: Classic R1 at 19.6</t>
+          <t>TP1: Fibonacci R1 at 19.09; TP2: Bollinger Upper Band at 19.14; TP3: Classic R1 at 19.6</t>
         </is>
       </c>
       <c r="AR58" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="AT58" t="n">
-        <v>4.57</v>
+        <v>4.53</v>
       </c>
       <c r="AU58" t="n">
-        <v>8.93</v>
+        <v>8.91</v>
       </c>
       <c r="AV58" t="n">
-        <v>9.529999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AW58" t="n">
-        <v>11.88</v>
+        <v>11.86</v>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
@@ -11071,7 +11115,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.3))</t>
         </is>
       </c>
     </row>
@@ -11097,7 +11141,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.748</v>
+        <v>0.738</v>
       </c>
       <c r="F59" t="n">
         <v>0.0149</v>
@@ -11127,10 +11171,10 @@
         <v>24044331</v>
       </c>
       <c r="O59" t="n">
-        <v>158216530</v>
+        <v>170027482</v>
       </c>
       <c r="P59" t="n">
-        <v>6.58</v>
+        <v>7.071</v>
       </c>
       <c r="Q59" t="n">
         <v>30218560</v>
@@ -11148,7 +11192,7 @@
         <v>0.778</v>
       </c>
       <c r="V59" t="n">
-        <v>0.5594</v>
+        <v>0.5592</v>
       </c>
       <c r="W59" t="n">
         <v>0.4768</v>
@@ -11164,13 +11208,13 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>0.6112</v>
+        <v>0.6102</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.5655</v>
+        <v>0.5651</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.493</v>
+        <v>0.4929</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -11183,10 +11227,10 @@
         </is>
       </c>
       <c r="AE59" t="n">
-        <v>0.0316</v>
+        <v>0.0308</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.0168</v>
+        <v>0.0166</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -11194,14 +11238,14 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>78.23999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.6367</v>
+        <v>0.6364</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK59" t="n">
@@ -11215,16 +11259,38 @@
           <t>stop at Parabolic SAR</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
-      <c r="AQ59" t="inlineStr"/>
-      <c r="AR59" t="inlineStr"/>
-      <c r="AS59" t="inlineStr"/>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AU59" t="inlineStr"/>
-      <c r="AV59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr"/>
+      <c r="AN59" t="n">
+        <v>0.7418</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0.7737000000000001</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0.7568</v>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>TP1: Classic R3 at 0.74; TP2: Extension at 0.77; TP3: Extension at 0.76</t>
+        </is>
+      </c>
+      <c r="AR59" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>11.62</v>
+      </c>
       <c r="AX59" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -11232,7 +11298,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.8); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 75.8))</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11324,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>129.26</v>
+        <v>139.75</v>
       </c>
       <c r="F60" t="n">
         <v>2.429</v>
@@ -11286,10 +11352,10 @@
         <v>127449</v>
       </c>
       <c r="O60" t="n">
-        <v>920767</v>
+        <v>1891181</v>
       </c>
       <c r="P60" t="n">
-        <v>7.225</v>
+        <v>14.839</v>
       </c>
       <c r="Q60" t="n">
         <v>51762</v>
@@ -11307,10 +11373,10 @@
         <v>136.77</v>
       </c>
       <c r="V60" t="n">
-        <v>101.632</v>
+        <v>101.8418</v>
       </c>
       <c r="W60" t="n">
-        <v>90.3104</v>
+        <v>90.3629</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -11323,13 +11389,13 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>109.7528</v>
+        <v>110.7519</v>
       </c>
       <c r="AA60" t="n">
-        <v>103.2644</v>
+        <v>103.6758</v>
       </c>
       <c r="AB60" t="n">
-        <v>89.9875</v>
+        <v>90.0919</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -11342,10 +11408,10 @@
         </is>
       </c>
       <c r="AE60" t="n">
-        <v>6.1594</v>
+        <v>6.9962</v>
       </c>
       <c r="AF60" t="n">
-        <v>4.0035</v>
+        <v>4.1709</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -11353,58 +11419,58 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>81.53</v>
+        <v>85.59</v>
       </c>
       <c r="AI60" t="n">
-        <v>112.1761</v>
+        <v>117.3762</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK60" t="n">
-        <v>112.1761</v>
+        <v>117.395</v>
       </c>
       <c r="AL60" t="n">
-        <v>106.386</v>
+        <v>114.25</v>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN60" t="n">
         <v>143.7933</v>
       </c>
       <c r="AO60" t="n">
-        <v>159.6019</v>
+        <v>156.9924</v>
       </c>
       <c r="AP60" t="n">
-        <v>151.255</v>
+        <v>150.0233</v>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 143.79; TP2: Extension at 159.6; TP3: Extension at 151.25</t>
+          <t>TP1: Classic R3 at 143.79; TP2: Extension at 156.99; TP3: Extension at 150.02</t>
         </is>
       </c>
       <c r="AR60" t="n">
-        <v>5.46</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AS60" t="n">
-        <v>8.19</v>
+        <v>12.59</v>
       </c>
       <c r="AT60" t="n">
-        <v>6.75</v>
+        <v>10.37</v>
       </c>
       <c r="AU60" t="n">
-        <v>28.19</v>
+        <v>22.49</v>
       </c>
       <c r="AV60" t="n">
-        <v>42.28</v>
+        <v>33.73</v>
       </c>
       <c r="AW60" t="n">
-        <v>34.84</v>
+        <v>27.79</v>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
@@ -11413,7 +11479,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.5); entry: enhanced entry at VWMA (overbought (RSI: 81.5))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (85.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 85.6))</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11505,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>11.25</v>
+        <v>11.4</v>
       </c>
       <c r="F61" t="n">
         <v>0.2224</v>
@@ -11467,10 +11533,10 @@
         <v>1640370</v>
       </c>
       <c r="O61" t="n">
-        <v>224351</v>
+        <v>573607</v>
       </c>
       <c r="P61" t="n">
-        <v>0.137</v>
+        <v>0.35</v>
       </c>
       <c r="Q61" t="n">
         <v>578694</v>
@@ -11488,10 +11554,10 @@
         <v>11.74</v>
       </c>
       <c r="V61" t="n">
-        <v>9.6836</v>
+        <v>9.6866</v>
       </c>
       <c r="W61" t="n">
-        <v>8.1782</v>
+        <v>8.178900000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -11504,13 +11570,13 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>10.6441</v>
+        <v>10.6584</v>
       </c>
       <c r="AA61" t="n">
-        <v>9.961600000000001</v>
+        <v>9.967499999999999</v>
       </c>
       <c r="AB61" t="n">
-        <v>8.4589</v>
+        <v>8.4604</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -11523,32 +11589,32 @@
         </is>
       </c>
       <c r="AE61" t="n">
-        <v>0.4695</v>
+        <v>0.4815</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.473</v>
+        <v>0.4754</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>65.81999999999999</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="AI61" t="n">
-        <v>10.6163</v>
+        <v>10.6213</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>10.6163</v>
+        <v>10.6213</v>
       </c>
       <c r="AL61" t="n">
-        <v>9.351900000000001</v>
+        <v>9.3445</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
@@ -11562,30 +11628,30 @@
         <v>11.97</v>
       </c>
       <c r="AP61" t="n">
-        <v>11.9791</v>
+        <v>12.0015</v>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 11.98</t>
+          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.0</t>
         </is>
       </c>
       <c r="AR61" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AT61" t="n">
         <v>1.08</v>
       </c>
       <c r="AU61" t="n">
-        <v>8.140000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="AV61" t="n">
-        <v>12.75</v>
+        <v>12.7</v>
       </c>
       <c r="AW61" t="n">
-        <v>12.84</v>
+        <v>12.99</v>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
@@ -11594,7 +11660,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.6))</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11686,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>61.3</v>
+        <v>59.99</v>
       </c>
       <c r="F62" t="n">
         <v>1.1706</v>
@@ -11654,10 +11720,10 @@
         <v>241336</v>
       </c>
       <c r="O62" t="n">
-        <v>178098</v>
+        <v>303138</v>
       </c>
       <c r="P62" t="n">
-        <v>0.738</v>
+        <v>1.256</v>
       </c>
       <c r="Q62" t="n">
         <v>124597</v>
@@ -11675,10 +11741,10 @@
         <v>54.8</v>
       </c>
       <c r="V62" t="n">
-        <v>51.7202</v>
+        <v>51.694</v>
       </c>
       <c r="W62" t="n">
-        <v>45.9476</v>
+        <v>45.941</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -11691,13 +11757,13 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>55.0225</v>
+        <v>54.8977</v>
       </c>
       <c r="AA62" t="n">
-        <v>52.0259</v>
+        <v>51.9745</v>
       </c>
       <c r="AB62" t="n">
-        <v>46.6446</v>
+        <v>46.6316</v>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
@@ -11710,10 +11776,10 @@
         </is>
       </c>
       <c r="AE62" t="n">
-        <v>2.3924</v>
+        <v>2.2879</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.5939</v>
+        <v>1.573</v>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
@@ -11721,14 +11787,14 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>74.62</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="AI62" t="n">
-        <v>56.3678</v>
+        <v>56.3922</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK62" t="n">
@@ -11743,36 +11809,36 @@
         </is>
       </c>
       <c r="AN62" t="n">
+        <v>60.8038</v>
+      </c>
+      <c r="AO62" t="n">
         <v>64.6233</v>
       </c>
-      <c r="AO62" t="n">
-        <v>67.9049</v>
-      </c>
       <c r="AP62" t="n">
-        <v>66.17230000000001</v>
+        <v>67.1305</v>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 64.62; TP2: Extension at 67.9; TP3: Extension at 66.17</t>
+          <t>TP1: Bollinger Upper Band at 60.8; TP2: Classic R3 at 64.62; TP3: Extension at 67.13</t>
         </is>
       </c>
       <c r="AR62" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AS62" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AS62" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AT62" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU62" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="AV62" t="n">
         <v>11.3</v>
       </c>
-      <c r="AV62" t="n">
-        <v>16.96</v>
-      </c>
       <c r="AW62" t="n">
-        <v>13.97</v>
+        <v>15.62</v>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
@@ -11781,7 +11847,7 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 74.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.3); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 72.3))</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11873,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="F63" t="n">
         <v>0.1591</v>
@@ -11841,10 +11907,10 @@
         <v>6734341</v>
       </c>
       <c r="O63" t="n">
-        <v>4060677</v>
+        <v>6678131</v>
       </c>
       <c r="P63" t="n">
-        <v>0.603</v>
+        <v>0.992</v>
       </c>
       <c r="Q63" t="n">
         <v>4751926</v>
@@ -11862,7 +11928,7 @@
         <v>8.51</v>
       </c>
       <c r="V63" t="n">
-        <v>7.5232</v>
+        <v>7.523</v>
       </c>
       <c r="W63" t="n">
         <v>5.5753</v>
@@ -11878,13 +11944,13 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>7.9686</v>
+        <v>7.9676</v>
       </c>
       <c r="AA63" t="n">
-        <v>7.5545</v>
+        <v>7.5541</v>
       </c>
       <c r="AB63" t="n">
-        <v>6.0413</v>
+        <v>6.0412</v>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
@@ -11897,10 +11963,10 @@
         </is>
       </c>
       <c r="AE63" t="n">
-        <v>0.1233</v>
+        <v>0.1225</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.1957</v>
+        <v>0.1956</v>
       </c>
       <c r="AG63" t="inlineStr">
         <is>
@@ -11908,21 +11974,21 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>51.55</v>
+        <v>51.13</v>
       </c>
       <c r="AI63" t="n">
-        <v>8.129</v>
+        <v>8.125500000000001</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK63" t="n">
         <v>7.855</v>
       </c>
       <c r="AL63" t="n">
-        <v>7.7448</v>
+        <v>7.7432</v>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
@@ -11933,7 +11999,7 @@
         <v>8.395099999999999</v>
       </c>
       <c r="AO63" t="n">
-        <v>8.494199999999999</v>
+        <v>8.4948</v>
       </c>
       <c r="AP63" t="n">
         <v>8.58</v>
@@ -11944,19 +12010,19 @@
         </is>
       </c>
       <c r="AR63" t="n">
-        <v>4.9</v>
+        <v>4.83</v>
       </c>
       <c r="AS63" t="n">
-        <v>5.8</v>
+        <v>5.72</v>
       </c>
       <c r="AT63" t="n">
-        <v>6.58</v>
+        <v>6.49</v>
       </c>
       <c r="AU63" t="n">
         <v>6.88</v>
       </c>
       <c r="AV63" t="n">
-        <v>8.140000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="AW63" t="n">
         <v>9.23</v>
@@ -11968,7 +12034,7 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 51.5))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 51.1))</t>
         </is>
       </c>
     </row>
@@ -11994,7 +12060,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>24.91</v>
+        <v>24.9</v>
       </c>
       <c r="F64" t="n">
         <v>0.494</v>
@@ -12028,10 +12094,10 @@
         <v>687399</v>
       </c>
       <c r="O64" t="n">
-        <v>791859</v>
+        <v>1054147</v>
       </c>
       <c r="P64" t="n">
-        <v>1.152</v>
+        <v>1.534</v>
       </c>
       <c r="Q64" t="n">
         <v>725886</v>
@@ -12049,10 +12115,10 @@
         <v>23.95</v>
       </c>
       <c r="V64" t="n">
-        <v>22.5182</v>
+        <v>22.518</v>
       </c>
       <c r="W64" t="n">
-        <v>22.7509</v>
+        <v>22.7508</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -12065,13 +12131,13 @@
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>23.4368</v>
+        <v>23.4359</v>
       </c>
       <c r="AA64" t="n">
-        <v>22.8122</v>
+        <v>22.8118</v>
       </c>
       <c r="AB64" t="n">
-        <v>22.1067</v>
+        <v>22.1066</v>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
@@ -12084,10 +12150,10 @@
         </is>
       </c>
       <c r="AE64" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5199</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.356</v>
+        <v>0.3558</v>
       </c>
       <c r="AG64" t="inlineStr">
         <is>
@@ -12095,14 +12161,14 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>74.26000000000001</v>
+        <v>74.19</v>
       </c>
       <c r="AI64" t="n">
-        <v>23.4879</v>
+        <v>23.4987</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr"/>
@@ -12159,7 +12225,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>42.21</v>
+        <v>42.2</v>
       </c>
       <c r="F65" t="n">
         <v>0.8376</v>
@@ -12193,10 +12259,10 @@
         <v>3868027</v>
       </c>
       <c r="O65" t="n">
-        <v>513279</v>
+        <v>1151273</v>
       </c>
       <c r="P65" t="n">
-        <v>0.133</v>
+        <v>0.298</v>
       </c>
       <c r="Q65" t="n">
         <v>1795008</v>
@@ -12214,10 +12280,10 @@
         <v>39.7</v>
       </c>
       <c r="V65" t="n">
-        <v>38.6366</v>
+        <v>38.6364</v>
       </c>
       <c r="W65" t="n">
-        <v>29.0984</v>
+        <v>29.0983</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -12230,13 +12296,13 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>40.0419</v>
+        <v>40.041</v>
       </c>
       <c r="AA65" t="n">
-        <v>37.9914</v>
+        <v>37.991</v>
       </c>
       <c r="AB65" t="n">
-        <v>30.7009</v>
+        <v>30.7008</v>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
@@ -12249,10 +12315,10 @@
         </is>
       </c>
       <c r="AE65" t="n">
-        <v>0.9211</v>
+        <v>0.9203</v>
       </c>
       <c r="AF65" t="n">
-        <v>0.7556</v>
+        <v>0.7554</v>
       </c>
       <c r="AG65" t="inlineStr">
         <is>
@@ -12260,14 +12326,14 @@
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>68.34999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="AI65" t="n">
-        <v>40.0161</v>
+        <v>40.0334</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:01</t>
+          <t>2026-08-06 10:55:18</t>
         </is>
       </c>
       <c r="AK65" t="n">
@@ -12432,34 +12498,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54888.7</v>
+        <v>54587.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.42</v>
+        <v>-0.13</v>
       </c>
       <c r="F2" t="n">
-        <v>66.36</v>
+        <v>63.89</v>
       </c>
       <c r="G2" t="n">
-        <v>52538.24</v>
+        <v>52532.21</v>
       </c>
       <c r="H2" t="n">
-        <v>47039.85</v>
+        <v>47038.35</v>
       </c>
       <c r="I2" t="n">
-        <v>53568.67</v>
+        <v>53539.95</v>
       </c>
       <c r="J2" t="n">
-        <v>52634.06</v>
+        <v>52622.23</v>
       </c>
       <c r="K2" t="n">
-        <v>47362.4</v>
+        <v>47359.4</v>
       </c>
       <c r="L2" t="n">
-        <v>651.26</v>
+        <v>627.2</v>
       </c>
       <c r="M2" t="n">
-        <v>528.37</v>
+        <v>523.5599999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -12468,7 +12534,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:18</t>
+          <t>2026-08-06 10:55:29</t>
         </is>
       </c>
     </row>
@@ -12489,34 +12555,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19959.8</v>
+        <v>19868.7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.98</v>
+        <v>0.52</v>
       </c>
       <c r="F3" t="n">
-        <v>88.45</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>16393.04</v>
+        <v>16391.22</v>
       </c>
       <c r="H3" t="n">
-        <v>13688.37</v>
+        <v>13687.92</v>
       </c>
       <c r="I3" t="n">
-        <v>18154.38</v>
+        <v>18145.7</v>
       </c>
       <c r="J3" t="n">
-        <v>16736.31</v>
+        <v>16732.74</v>
       </c>
       <c r="K3" t="n">
-        <v>13964</v>
+        <v>13963.09</v>
       </c>
       <c r="L3" t="n">
-        <v>1000.94</v>
+        <v>993.6799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>829.38</v>
+        <v>827.9299999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -12525,7 +12591,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-06 09:37:18</t>
+          <t>2026-08-06 10:55:29</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK2" t="n">
@@ -876,7 +876,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK3" t="n">
@@ -1063,7 +1063,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1250,7 +1250,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -1437,7 +1437,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1624,7 +1624,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -1789,7 +1789,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -1974,7 +1974,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -2161,7 +2161,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2334,7 +2334,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK11" t="n">
@@ -2499,7 +2499,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -2686,7 +2686,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -2873,7 +2873,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -3038,7 +3038,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3219,7 +3219,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -3402,7 +3402,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3585,7 +3585,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3772,7 +3772,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -3955,7 +3955,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4138,7 +4138,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4325,7 +4325,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK22" t="n">
@@ -4512,7 +4512,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4699,7 +4699,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -4886,7 +4886,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -5067,7 +5067,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK26" t="n">
@@ -5254,7 +5254,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -5437,7 +5437,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK28" t="n">
@@ -5620,7 +5620,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -5803,7 +5803,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK30" t="n">
@@ -5990,7 +5990,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK31" t="n">
@@ -6173,7 +6173,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK32" t="n">
@@ -6356,7 +6356,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK33" t="n">
@@ -6543,7 +6543,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK34" t="n">
@@ -6726,7 +6726,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK35" t="n">
@@ -6913,7 +6913,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK36" t="n">
@@ -7100,7 +7100,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK37" t="n">
@@ -7287,7 +7287,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK38" t="n">
@@ -7474,7 +7474,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-07 16:00:57</t>
+          <t>2026-08-08 15:36:30</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7635,7 +7635,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK40" t="n">
@@ -7816,7 +7816,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK41" t="n">
@@ -8003,7 +8003,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK42" t="n">
@@ -8190,7 +8190,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK43" t="n">
@@ -8373,7 +8373,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK44" t="n">
@@ -8560,7 +8560,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK45" t="n">
@@ -8741,7 +8741,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK46" t="n">
@@ -8922,7 +8922,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK47" t="n">
@@ -9109,7 +9109,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK48" t="n">
@@ -9294,7 +9294,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9455,7 +9455,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK50" t="n">
@@ -9636,7 +9636,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK51" t="n">
@@ -9817,7 +9817,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK52" t="n">
@@ -10004,7 +10004,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK53" t="n">
@@ -10185,7 +10185,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK54" t="n">
@@ -10372,7 +10372,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK55" t="n">
@@ -10557,7 +10557,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10736,7 +10736,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK57" t="n">
@@ -10921,7 +10921,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK58" t="n">
@@ -11108,7 +11108,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK59" t="n">
@@ -11269,7 +11269,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK60" t="n">
@@ -11450,7 +11450,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK61" t="n">
@@ -11631,7 +11631,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK62" t="n">
@@ -11818,7 +11818,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK63" t="n">
@@ -12005,7 +12005,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr"/>
@@ -12170,7 +12170,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:07</t>
+          <t>2026-08-08 15:36:36</t>
         </is>
       </c>
       <c r="AK65" t="n">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:20</t>
+          <t>2026-08-08 15:37:27</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-07 16:01:20</t>
+          <t>2026-08-08 15:37:27</t>
         </is>
       </c>
     </row>

--- a/Stock_Analysis_Output.xlsx
+++ b/Stock_Analysis_Output.xlsx
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9.1</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>0.1829</v>
@@ -742,10 +742,10 @@
         <v>7893392</v>
       </c>
       <c r="O2" t="n">
-        <v>10362074</v>
+        <v>866726</v>
       </c>
       <c r="P2" t="n">
-        <v>1.313</v>
+        <v>0.11</v>
       </c>
       <c r="Q2" t="n">
         <v>3794606</v>
@@ -763,10 +763,10 @@
         <v>9.15</v>
       </c>
       <c r="V2" t="n">
-        <v>8.194800000000001</v>
+        <v>8.2094</v>
       </c>
       <c r="W2" t="n">
-        <v>7.6578</v>
+        <v>7.6653</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -779,13 +779,13 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>8.6158</v>
+        <v>8.6648</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.340400000000001</v>
+        <v>8.3714</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.925</v>
+        <v>7.937</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>0.301</v>
+        <v>0.3035</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2141</v>
+        <v>0.232</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>63.43</v>
+        <v>63.92</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.724299999999999</v>
+        <v>8.7681</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK2" t="n">
-        <v>8.724299999999999</v>
+        <v>8.7681</v>
       </c>
       <c r="AL2" t="n">
-        <v>8.462</v>
+        <v>8.5143</v>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
@@ -837,30 +837,30 @@
         <v>9.416700000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.923299999999999</v>
+        <v>9.482100000000001</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 9.39; TP2: Classic R1 at 9.42; TP3: Classic R2 at 9.92</t>
+          <t>TP1: Fibonacci R2 at 9.39; TP2: Classic R1 at 9.42; TP3: Bollinger Upper Band at 9.48</t>
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.57</v>
+        <v>2.81</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.66</v>
+        <v>7.12</v>
       </c>
       <c r="AV2" t="n">
-        <v>7.94</v>
+        <v>7.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>13.74</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.9))</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>62.03</v>
       </c>
       <c r="F3" t="n">
         <v>1.1856</v>
@@ -929,10 +929,10 @@
         <v>717795</v>
       </c>
       <c r="O3" t="n">
-        <v>1335440</v>
+        <v>1523856</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>2.123</v>
       </c>
       <c r="Q3" t="n">
         <v>186125</v>
@@ -950,10 +950,10 @@
         <v>60.3</v>
       </c>
       <c r="V3" t="n">
-        <v>56.2522</v>
+        <v>56.4148</v>
       </c>
       <c r="W3" t="n">
-        <v>51.641</v>
+        <v>51.7526</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>56.5485</v>
+        <v>57.0705</v>
       </c>
       <c r="AA3" t="n">
-        <v>55.8535</v>
+        <v>56.0957</v>
       </c>
       <c r="AB3" t="n">
-        <v>50.1234</v>
+        <v>50.2419</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>0.4577</v>
+        <v>0.8363</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2562</v>
+        <v>0.3722</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>64.92</v>
+        <v>73.92</v>
       </c>
       <c r="AI3" t="n">
-        <v>56.7515</v>
+        <v>57.3491</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>56.7515</v>
+        <v>59.225</v>
       </c>
       <c r="AL3" t="n">
-        <v>55.77</v>
+        <v>56</v>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
@@ -1018,52 +1018,52 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>60.5667</v>
+        <v>64.86669999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>64.86669999999999</v>
+        <v>67.6875</v>
       </c>
       <c r="AP3" t="n">
-        <v>67.9667</v>
+        <v>66.1981</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 60.57; TP2: Classic R3 at 64.87; TP3: Extension at 67.97</t>
+          <t>TP1: Classic R3 at 64.87; TP2: Extension at 67.69; TP3: Extension at 66.2</t>
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>3.89</v>
+        <v>1.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.27</v>
+        <v>2.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>11.43</v>
+        <v>2.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.72</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="AV3" t="n">
-        <v>14.3</v>
+        <v>14.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>19.76</v>
+        <v>11.77</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.9))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.9); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 73.9))</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31.89</v>
+        <v>32.57</v>
       </c>
       <c r="F4" t="n">
         <v>0.6408</v>
@@ -1091,7 +1091,7 @@
         <v>0.2476</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2712</v>
+        <v>1.2368</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         <v>1614123</v>
       </c>
       <c r="O4" t="n">
-        <v>9491039</v>
+        <v>883341</v>
       </c>
       <c r="P4" t="n">
-        <v>5.88</v>
+        <v>0.547</v>
       </c>
       <c r="Q4" t="n">
         <v>1410644</v>
@@ -1137,10 +1137,10 @@
         <v>28.99</v>
       </c>
       <c r="V4" t="n">
-        <v>28.1644</v>
+        <v>28.2614</v>
       </c>
       <c r="W4" t="n">
-        <v>27.0412</v>
+        <v>27.091</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>28.4863</v>
+        <v>28.8753</v>
       </c>
       <c r="AA4" t="n">
-        <v>28.2249</v>
+        <v>28.3953</v>
       </c>
       <c r="AB4" t="n">
-        <v>26.0835</v>
+        <v>26.1481</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>0.5002</v>
+        <v>0.7585</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0561</v>
+        <v>0.1966</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1183,14 +1183,14 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>76.98999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>29.2005</v>
+        <v>29.2826</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1204,38 +1204,16 @@
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>32.3233</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>33.635</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>32.9424</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>TP1: Classic R3 at 32.32; TP2: Extension at 33.63; TP3: Extension at 32.94</t>
-        </is>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>10.92</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -1243,14 +1221,14 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 77.0))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.2))</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1269,7 +1247,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>23.5</v>
+        <v>24.01</v>
       </c>
       <c r="F5" t="n">
         <v>0.4722</v>
@@ -1303,10 +1281,10 @@
         <v>3316951</v>
       </c>
       <c r="O5" t="n">
-        <v>5070515</v>
+        <v>696147</v>
       </c>
       <c r="P5" t="n">
-        <v>1.529</v>
+        <v>0.21</v>
       </c>
       <c r="Q5" t="n">
         <v>1485711</v>
@@ -1324,10 +1302,10 @@
         <v>23.5653</v>
       </c>
       <c r="V5" t="n">
-        <v>22.0204</v>
+        <v>22.0682</v>
       </c>
       <c r="W5" t="n">
-        <v>19.5182</v>
+        <v>19.5747</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1340,13 +1318,13 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>22.8988</v>
+        <v>23.0046</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.1704</v>
+        <v>22.2426</v>
       </c>
       <c r="AB5" t="n">
-        <v>19.6188</v>
+        <v>19.6625</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1359,10 +1337,10 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>0.518</v>
+        <v>0.5423</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4381</v>
+        <v>0.459</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1370,21 +1348,21 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>57.31</v>
+        <v>60.86</v>
       </c>
       <c r="AI5" t="n">
-        <v>23.3342</v>
+        <v>23.366</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>23.3342</v>
+        <v>23.366</v>
       </c>
       <c r="AL5" t="n">
-        <v>22.3149</v>
+        <v>22.4223</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
@@ -1392,36 +1370,36 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>23.7306</v>
+        <v>24.3367</v>
       </c>
       <c r="AO5" t="n">
-        <v>24.1915</v>
+        <v>24.3458</v>
       </c>
       <c r="AP5" t="n">
-        <v>24.3367</v>
+        <v>24.6061</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 23.73; TP2: Bollinger Upper Band at 24.19; TP3: Classic R1 at 24.34</t>
+          <t>TP1: Classic R1 at 24.34; TP2: Bollinger Upper Band at 24.35; TP3: Fibonacci R2 at 24.61</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.39</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.84</v>
+        <v>1.04</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.98</v>
+        <v>1.31</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.7</v>
+        <v>4.15</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.67</v>
+        <v>4.19</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.3</v>
+        <v>5.31</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
@@ -1430,14 +1408,14 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 57.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.9))</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1456,7 +1434,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>298.8</v>
+        <v>297.79</v>
       </c>
       <c r="F6" t="n">
         <v>6.0043</v>
@@ -1490,10 +1468,10 @@
         <v>307403</v>
       </c>
       <c r="O6" t="n">
-        <v>129602</v>
+        <v>32956</v>
       </c>
       <c r="P6" t="n">
-        <v>0.422</v>
+        <v>0.107</v>
       </c>
       <c r="Q6" t="n">
         <v>57186</v>
@@ -1511,10 +1489,10 @@
         <v>302.7</v>
       </c>
       <c r="V6" t="n">
-        <v>302.7876</v>
+        <v>302.2732</v>
       </c>
       <c r="W6" t="n">
-        <v>260.4599</v>
+        <v>261.1224</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1527,13 +1505,13 @@
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>298.2275</v>
+        <v>298.1858</v>
       </c>
       <c r="AA6" t="n">
-        <v>299.0432</v>
+        <v>298.9941</v>
       </c>
       <c r="AB6" t="n">
-        <v>263.5886</v>
+        <v>263.9289</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1546,10 +1524,10 @@
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>-0.4734</v>
+        <v>-0.4605</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.5007</v>
+        <v>-0.4927</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -1557,58 +1535,58 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>50.25</v>
+        <v>48.99</v>
       </c>
       <c r="AI6" t="n">
-        <v>300.2531</v>
+        <v>300.4226</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>294.5</v>
+        <v>291.0381</v>
       </c>
       <c r="AL6" t="n">
-        <v>290.3867</v>
+        <v>285.9946</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN6" t="n">
-        <v>302.2584</v>
+        <v>302.7163</v>
       </c>
       <c r="AO6" t="n">
-        <v>307.2843</v>
+        <v>307.1109</v>
       </c>
       <c r="AP6" t="n">
         <v>308.3187</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 302.26; TP2: Bollinger Upper Band at 307.28; TP3: Fibonacci R1 at 308.32</t>
+          <t>TP1: 100 SMA at 302.72; TP2: Bollinger Upper Band at 307.11; TP3: Fibonacci R1 at 308.32</t>
         </is>
       </c>
       <c r="AR6" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.36</v>
+        <v>3.43</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.63</v>
+        <v>4.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.34</v>
+        <v>5.52</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.69</v>
+        <v>5.94</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1617,14 +1595,14 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (overbought (RSI: 50.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 49.0))</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1643,7 +1621,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>13.6</v>
+        <v>13.79</v>
       </c>
       <c r="F7" t="n">
         <v>0.2733</v>
@@ -1677,10 +1655,10 @@
         <v>6522238</v>
       </c>
       <c r="O7" t="n">
-        <v>18844750</v>
+        <v>2078651</v>
       </c>
       <c r="P7" t="n">
-        <v>2.889</v>
+        <v>0.319</v>
       </c>
       <c r="Q7" t="n">
         <v>4143675</v>
@@ -1698,10 +1676,10 @@
         <v>11.87</v>
       </c>
       <c r="V7" t="n">
-        <v>11.9134</v>
+        <v>11.965</v>
       </c>
       <c r="W7" t="n">
-        <v>11.3434</v>
+        <v>11.354</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1714,13 +1692,13 @@
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>12.2351</v>
+        <v>12.3832</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.8881</v>
+        <v>11.9627</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.1239</v>
+        <v>11.1504</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1733,10 +1711,10 @@
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.3948</v>
+        <v>0.467</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1555</v>
+        <v>0.2178</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -1744,37 +1722,59 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>67.09</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>13.0719</v>
+        <v>13.1037</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>13.0719</v>
+        <v>13.1037</v>
       </c>
       <c r="AL7" t="n">
-        <v>11.7029</v>
+        <v>11.912</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
           <t>stop at Parabolic SAR</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>13.8776</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>14.2646</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14.0602</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>TP1: Bollinger Upper Band at 13.88; TP2: Extension at 14.26; TP3: Extension at 14.06</t>
+        </is>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>7.3</v>
+      </c>
       <c r="AX7" t="inlineStr">
         <is>
           <t>Buy</t>
@@ -1782,14 +1782,14 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.1))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.5))</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26.61</v>
+        <v>26.93</v>
       </c>
       <c r="F8" t="n">
         <v>0.5347</v>
@@ -1839,16 +1839,16 @@
         <v>1.8489</v>
       </c>
       <c r="N8" t="n">
-        <v>1328652</v>
+        <v>1340307</v>
       </c>
       <c r="O8" t="n">
-        <v>2801191</v>
+        <v>366595</v>
       </c>
       <c r="P8" t="n">
-        <v>2.108</v>
+        <v>0.274</v>
       </c>
       <c r="Q8" t="n">
-        <v>700042</v>
+        <v>741454</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
@@ -1861,10 +1861,10 @@
         <v>27.6942</v>
       </c>
       <c r="V8" t="n">
-        <v>23.5918</v>
+        <v>23.695</v>
       </c>
       <c r="W8" t="n">
-        <v>21.6596</v>
+        <v>21.7002</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>22.9107</v>
+        <v>23.2935</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.1943</v>
+        <v>23.3408</v>
       </c>
       <c r="AB8" t="n">
-        <v>21.8405</v>
+        <v>21.8911</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>-0.3815</v>
+        <v>-0.0134</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.4941</v>
+        <v>-0.398</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -1907,14 +1907,14 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>64.26000000000001</v>
+        <v>65.16</v>
       </c>
       <c r="AI8" t="n">
-        <v>22.3401</v>
+        <v>22.352</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -1929,36 +1929,36 @@
         </is>
       </c>
       <c r="AN8" t="n">
+        <v>26.9893</v>
+      </c>
+      <c r="AO8" t="n">
         <v>29.1253</v>
       </c>
-      <c r="AO8" t="n">
-        <v>30.4329</v>
-      </c>
       <c r="AP8" t="n">
-        <v>29.7426</v>
+        <v>30.1243</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 29.13; TP2: Extension at 30.43; TP3: Extension at 29.74</t>
+          <t>TP1: Bollinger Upper Band at 26.99; TP2: Classic R3 at 29.13; TP3: Extension at 30.12</t>
         </is>
       </c>
       <c r="AR8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AS8" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AT8" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="AU8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AV8" t="n">
         <v>9.869999999999999</v>
       </c>
-      <c r="AV8" t="n">
-        <v>14.8</v>
-      </c>
       <c r="AW8" t="n">
-        <v>12.19</v>
+        <v>13.63</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
@@ -1967,14 +1967,14 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (overbought (RSI: 64.3))</t>
+          <t>near support, Golden Cross confirmed; entry: enhanced entry at Swing Support (overbought (RSI: 65.2))</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>192</v>
+        <v>194.99</v>
       </c>
       <c r="F9" t="n">
         <v>3.8582</v>
@@ -2027,10 +2027,10 @@
         <v>179574</v>
       </c>
       <c r="O9" t="n">
-        <v>312515</v>
+        <v>62849</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>0.35</v>
       </c>
       <c r="Q9" t="n">
         <v>39323</v>
@@ -2048,10 +2048,10 @@
         <v>194.883</v>
       </c>
       <c r="V9" t="n">
-        <v>182.439</v>
+        <v>182.5774</v>
       </c>
       <c r="W9" t="n">
-        <v>163.1572</v>
+        <v>163.7586</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>184.2656</v>
+        <v>185.2869</v>
       </c>
       <c r="AA9" t="n">
-        <v>182.9832</v>
+        <v>183.4541</v>
       </c>
       <c r="AB9" t="n">
-        <v>158.2819</v>
+        <v>158.6472</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>2.146</v>
+        <v>2.7209</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.4966</v>
+        <v>1.7414</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>62.75</v>
+        <v>65.84</v>
       </c>
       <c r="AI9" t="n">
-        <v>186.2758</v>
+        <v>186.7313</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>188.01</v>
+        <v>186.7313</v>
       </c>
       <c r="AL9" t="n">
-        <v>178</v>
+        <v>178.44</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
@@ -2116,52 +2116,52 @@
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>192.0267</v>
+        <v>196.0185</v>
       </c>
       <c r="AO9" t="n">
-        <v>194.3802</v>
+        <v>197.9267</v>
       </c>
       <c r="AP9" t="n">
-        <v>194.9533</v>
+        <v>207.4767</v>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 192.03; TP2: Bollinger Upper Band at 194.38; TP3: Classic R1 at 194.95</t>
+          <t>TP1: Bollinger Upper Band at 196.02; TP2: Fibonacci R2 at 197.93; TP3: Classic R2 at 207.48</t>
         </is>
       </c>
       <c r="AR9" t="n">
-        <v>0.4</v>
+        <v>1.12</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.64</v>
+        <v>1.35</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.14</v>
+        <v>4.97</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.39</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.69</v>
+        <v>11.11</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Swing Support (overbought (RSI: 62.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.8))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="F10" t="n">
         <v>1.4277</v>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>176743</v>
+        <v>40156</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -2221,10 +2221,10 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>725.1414</v>
+        <v>725.5014</v>
       </c>
       <c r="W10" t="n">
-        <v>548.5148</v>
+        <v>549.8748000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2237,13 +2237,13 @@
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>711.4789</v>
+        <v>712.4809</v>
       </c>
       <c r="AA10" t="n">
-        <v>699.2054000000001</v>
+        <v>700.0993</v>
       </c>
       <c r="AB10" t="n">
-        <v>570.8859</v>
+        <v>572.3895</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>-0.0883</v>
+        <v>0.766</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1.6823</v>
+        <v>-1.1926</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -2267,18 +2267,18 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>53.65</v>
+        <v>54.42</v>
       </c>
       <c r="AI10" t="n">
-        <v>705.4049</v>
+        <v>706.5881000000001</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>706.5</v>
+        <v>706.5881000000001</v>
       </c>
       <c r="AL10" t="n">
         <v>688.154</v>
@@ -2292,33 +2292,33 @@
         <v>728.646</v>
       </c>
       <c r="AO10" t="n">
-        <v>730.0854</v>
+        <v>731.6262</v>
       </c>
       <c r="AP10" t="n">
         <v>736.8</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 728.65; TP2: Bollinger Upper Band at 730.09; TP3: Classic R1 at 736.8</t>
+          <t>TP1: Fibonacci R1 at 728.65; TP2: Bollinger Upper Band at 731.63; TP3: Classic R1 at 736.8</t>
         </is>
       </c>
       <c r="AR10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2327,14 +2327,14 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 54.4))</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>26.18</v>
       </c>
       <c r="F11" t="n">
         <v>0.5225</v>
@@ -2387,10 +2387,10 @@
         <v>1317640</v>
       </c>
       <c r="O11" t="n">
-        <v>5987703</v>
+        <v>382160</v>
       </c>
       <c r="P11" t="n">
-        <v>4.544</v>
+        <v>0.29</v>
       </c>
       <c r="Q11" t="n">
         <v>1057168</v>
@@ -2408,10 +2408,10 @@
         <v>23.47</v>
       </c>
       <c r="V11" t="n">
-        <v>23.1068</v>
+        <v>23.198</v>
       </c>
       <c r="W11" t="n">
-        <v>23.0025</v>
+        <v>23.0217</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>23.6143</v>
+        <v>23.8586</v>
       </c>
       <c r="AA11" t="n">
-        <v>23.219</v>
+        <v>23.3351</v>
       </c>
       <c r="AB11" t="n">
-        <v>22.9858</v>
+        <v>23.0176</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>0.52</v>
+        <v>0.6562</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1782</v>
+        <v>0.2738</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2454,25 +2454,25 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>75.17</v>
+        <v>76.02</v>
       </c>
       <c r="AI11" t="n">
-        <v>24.6014</v>
+        <v>24.6288</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>24.6014</v>
+        <v>24.6288</v>
       </c>
       <c r="AL11" t="n">
-        <v>23.0025</v>
+        <v>23.3577</v>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>stop at 200 SMA</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr"/>
@@ -2492,14 +2492,14 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (75.2); entry: enhanced entry at VWMA (overbought (RSI: 75.2))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.0); entry: enhanced entry at VWMA (overbought (RSI: 76.0))</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15.44</v>
+        <v>15.54</v>
       </c>
       <c r="F12" t="n">
         <v>0.3103</v>
@@ -2552,10 +2552,10 @@
         <v>17253152</v>
       </c>
       <c r="O12" t="n">
-        <v>9066159</v>
+        <v>3867569</v>
       </c>
       <c r="P12" t="n">
-        <v>0.525</v>
+        <v>0.224</v>
       </c>
       <c r="Q12" t="n">
         <v>7525158</v>
@@ -2573,10 +2573,10 @@
         <v>16.08</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9866</v>
+        <v>15.0294</v>
       </c>
       <c r="W12" t="n">
-        <v>10.529</v>
+        <v>10.5702</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2589,13 +2589,13 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>14.9363</v>
+        <v>14.9938</v>
       </c>
       <c r="AA12" t="n">
-        <v>14.4252</v>
+        <v>14.4689</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.3677</v>
+        <v>11.4092</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>0.1111</v>
+        <v>0.1461</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0479</v>
+        <v>0.0675</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2619,18 +2619,18 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>61.67</v>
+        <v>63.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>14.9564</v>
+        <v>14.9654</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>15.025</v>
+        <v>15.0294</v>
       </c>
       <c r="AL12" t="n">
         <v>14.58</v>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>15.45</v>
+        <v>15.5492</v>
       </c>
       <c r="AO12" t="n">
         <v>15.7933</v>
@@ -2651,26 +2651,26 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 15.45; TP2: Classic R2 at 15.79; TP3: Classic R3 at 16.85</t>
+          <t>TP1: Bollinger Upper Band at 15.55; TP2: Classic R2 at 15.79; TP3: Classic R3 at 16.85</t>
         </is>
       </c>
       <c r="AR12" t="n">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.83</v>
+        <v>3.46</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2679,14 +2679,14 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 63.2))</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>109.01</v>
+        <v>109.8</v>
       </c>
       <c r="F13" t="n">
         <v>2.1905</v>
@@ -2739,10 +2739,10 @@
         <v>1034672</v>
       </c>
       <c r="O13" t="n">
-        <v>1051620</v>
+        <v>66126</v>
       </c>
       <c r="P13" t="n">
-        <v>1.016</v>
+        <v>0.064</v>
       </c>
       <c r="Q13" t="n">
         <v>344845</v>
@@ -2760,10 +2760,10 @@
         <v>111.2082</v>
       </c>
       <c r="V13" t="n">
-        <v>97.86499999999999</v>
+        <v>98.1512</v>
       </c>
       <c r="W13" t="n">
-        <v>81.0107</v>
+        <v>81.31950000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2776,13 +2776,13 @@
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>104.049</v>
+        <v>104.5967</v>
       </c>
       <c r="AA13" t="n">
-        <v>99.2766</v>
+        <v>99.6893</v>
       </c>
       <c r="AB13" t="n">
-        <v>82.5688</v>
+        <v>82.8398</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>3.6554</v>
+        <v>3.6572</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.0914</v>
+        <v>3.2045</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2806,18 +2806,18 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>61.69</v>
+        <v>62.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>104.717</v>
+        <v>104.8665</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>106.9179</v>
+        <v>108.12</v>
       </c>
       <c r="AL13" t="n">
         <v>95.1023</v>
@@ -2834,30 +2834,30 @@
         <v>111.0823</v>
       </c>
       <c r="AP13" t="n">
-        <v>112.7121</v>
+        <v>113.3992</v>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 110.39; TP2: Fibonacci R2 at 111.08; TP3: Bollinger Upper Band at 112.71</t>
+          <t>TP1: Classic R1 at 110.39; TP2: Fibonacci R2 at 111.08; TP3: Bollinger Upper Band at 113.4</t>
         </is>
       </c>
       <c r="AR13" t="n">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.89</v>
+        <v>2.74</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.42</v>
+        <v>4.88</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
@@ -2866,14 +2866,14 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 61.7))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 62.7))</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2892,7 +2892,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.31</v>
+        <v>6.52</v>
       </c>
       <c r="F14" t="n">
         <v>0.1268</v>
@@ -2926,10 +2926,10 @@
         <v>12955531</v>
       </c>
       <c r="O14" t="n">
-        <v>37862971</v>
+        <v>8743707</v>
       </c>
       <c r="P14" t="n">
-        <v>2.923</v>
+        <v>0.675</v>
       </c>
       <c r="Q14" t="n">
         <v>8112530</v>
@@ -2947,10 +2947,10 @@
         <v>5.15</v>
       </c>
       <c r="V14" t="n">
-        <v>5.1522</v>
+        <v>5.181</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1041</v>
+        <v>4.1204</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>5.4321</v>
+        <v>5.5357</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.1522</v>
+        <v>5.2058</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.3358</v>
+        <v>4.3575</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>0.2565</v>
+        <v>0.3102</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.142</v>
+        <v>0.1756</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>72.2</v>
+        <v>74.64</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.7715</v>
+        <v>5.7952</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>5.7715</v>
+        <v>5.7952</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.5696</v>
+        <v>5.7138</v>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
@@ -3031,14 +3031,14 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (72.2); entry: enhanced entry at VWMA (overbought (RSI: 72.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.6); entry: enhanced entry at VWMA (overbought (RSI: 74.6))</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
       <c r="F15" t="n">
         <v>0.1186</v>
@@ -3085,10 +3085,10 @@
         <v>24595800</v>
       </c>
       <c r="O15" t="n">
-        <v>13361341</v>
+        <v>2110361</v>
       </c>
       <c r="P15" t="n">
-        <v>0.543</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>15716623</v>
@@ -3106,10 +3106,10 @@
         <v>4.65</v>
       </c>
       <c r="V15" t="n">
-        <v>3.2944</v>
+        <v>3.361</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2957</v>
+        <v>2.3188</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -3122,13 +3122,13 @@
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>4.4972</v>
+        <v>4.628</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.596</v>
+        <v>3.6852</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.4667</v>
+        <v>2.5006</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>0.7312</v>
+        <v>0.749</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.5813</v>
+        <v>0.6148</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -3152,18 +3152,18 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>82.3</v>
+        <v>81.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.0637</v>
+        <v>4.2337</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>5.0068</v>
+        <v>5.2554</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="AN15" t="n">
-        <v>6.0661</v>
+        <v>6.221</v>
       </c>
       <c r="AO15" t="n">
         <v>6.3</v>
@@ -3184,26 +3184,26 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 6.07; TP2: Classic R2 at 6.3; TP3: Classic R3 at 8.7</t>
+          <t>TP1: Bollinger Upper Band at 6.22; TP2: Classic R2 at 6.3; TP3: Classic R3 at 8.7</t>
         </is>
       </c>
       <c r="AR15" t="n">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AU15" t="n">
-        <v>21.16</v>
+        <v>18.37</v>
       </c>
       <c r="AV15" t="n">
-        <v>25.83</v>
+        <v>19.88</v>
       </c>
       <c r="AW15" t="n">
-        <v>73.76000000000001</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
@@ -3212,14 +3212,14 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.3); entry: enhanced entry at Parabolic SAR (overbought (RSI: 82.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.4); entry: enhanced entry at Parabolic SAR (overbought (RSI: 81.4))</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.243</v>
+        <v>0.246</v>
       </c>
       <c r="F16" t="n">
         <v>0.0049</v>
@@ -3268,10 +3268,10 @@
         <v>270450604</v>
       </c>
       <c r="O16" t="n">
-        <v>263817500</v>
+        <v>75641761</v>
       </c>
       <c r="P16" t="n">
-        <v>0.975</v>
+        <v>0.28</v>
       </c>
       <c r="Q16" t="n">
         <v>147923347</v>
@@ -3289,10 +3289,10 @@
         <v>0.256</v>
       </c>
       <c r="V16" t="n">
-        <v>0.223</v>
+        <v>0.2239</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1817</v>
+        <v>0.1822</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3305,13 +3305,13 @@
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0.2382</v>
+        <v>0.239</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.226</v>
+        <v>0.2268</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.1941</v>
+        <v>0.1946</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>0.0049</v>
+        <v>0.005</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0066</v>
+        <v>0.0063</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -3335,18 +3335,18 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>56.66</v>
+        <v>58.8</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.2444</v>
+        <v>0.2455</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>0.235</v>
+        <v>0.2455</v>
       </c>
       <c r="AL16" t="n">
         <v>0.232</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="AN16" t="n">
-        <v>0.2567</v>
+        <v>0.2559</v>
       </c>
       <c r="AO16" t="n">
         <v>0.267</v>
@@ -3371,22 +3371,22 @@
         </is>
       </c>
       <c r="AR16" t="n">
-        <v>7.23</v>
+        <v>0.77</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.67</v>
+        <v>1.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>20.33</v>
+        <v>3.75</v>
       </c>
       <c r="AU16" t="n">
-        <v>9.23</v>
+        <v>4.24</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.62</v>
+        <v>8.76</v>
       </c>
       <c r="AW16" t="n">
-        <v>25.96</v>
+        <v>20.58</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
@@ -3395,14 +3395,14 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 56.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 58.8))</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="F17" t="n">
         <v>0.034</v>
@@ -3453,10 +3453,10 @@
         <v>28455742</v>
       </c>
       <c r="O17" t="n">
-        <v>13540368</v>
+        <v>906467</v>
       </c>
       <c r="P17" t="n">
-        <v>0.476</v>
+        <v>0.032</v>
       </c>
       <c r="Q17" t="n">
         <v>8297639</v>
@@ -3472,10 +3472,10 @@
         <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.616</v>
+        <v>1.6194</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4737</v>
+        <v>1.4747</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3488,13 +3488,13 @@
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1.6681</v>
+        <v>1.6712</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6131</v>
+        <v>1.6165</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5139</v>
+        <v>1.5158</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>0.0255</v>
+        <v>0.025</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0286</v>
+        <v>0.0279</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>55.43</v>
+        <v>56.76</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.6804</v>
+        <v>1.683</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>1.6804</v>
+        <v>1.683</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.6204</v>
+        <v>1.6278</v>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
@@ -3554,22 +3554,22 @@
         </is>
       </c>
       <c r="AR17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.37</v>
+        <v>3.21</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.74</v>
+        <v>4.57</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.3</v>
+        <v>7.13</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
@@ -3578,14 +3578,14 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 55.4))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.8))</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38.64</v>
+        <v>38.85</v>
       </c>
       <c r="F18" t="n">
         <v>0.7765</v>
@@ -3638,10 +3638,10 @@
         <v>1324787</v>
       </c>
       <c r="O18" t="n">
-        <v>1081738</v>
+        <v>346152</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.261</v>
       </c>
       <c r="Q18" t="n">
         <v>456531</v>
@@ -3659,10 +3659,10 @@
         <v>39.17</v>
       </c>
       <c r="V18" t="n">
-        <v>37.913</v>
+        <v>37.9864</v>
       </c>
       <c r="W18" t="n">
-        <v>31.117</v>
+        <v>31.195</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3675,13 +3675,13 @@
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>38.2724</v>
+        <v>38.3274</v>
       </c>
       <c r="AA18" t="n">
-        <v>37.5722</v>
+        <v>37.6223</v>
       </c>
       <c r="AB18" t="n">
-        <v>31.6782</v>
+        <v>31.7495</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0179</v>
+        <v>0.0348</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0949</v>
+        <v>0.0829</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -3705,21 +3705,21 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>53.32</v>
+        <v>54.79</v>
       </c>
       <c r="AI18" t="n">
-        <v>38.6075</v>
+        <v>38.5516</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>38.6075</v>
+        <v>38.5516</v>
       </c>
       <c r="AL18" t="n">
-        <v>37.1352</v>
+        <v>37.1537</v>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="AN18" t="n">
-        <v>40.0918</v>
+        <v>40.0093</v>
       </c>
       <c r="AO18" t="n">
         <v>40.4652</v>
@@ -3737,26 +3737,26 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 40.09; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
+          <t>TP1: Bollinger Upper Band at 40.01; TP2: Fibonacci R1 at 40.47; TP3: Classic R1 at 40.63</t>
         </is>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.81</v>
+        <v>4.96</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
@@ -3765,14 +3765,14 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 53.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 54.8))</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35.1</v>
+        <v>35.5</v>
       </c>
       <c r="F19" t="n">
         <v>0.7053</v>
@@ -3821,10 +3821,10 @@
         <v>1239047</v>
       </c>
       <c r="O19" t="n">
-        <v>317542</v>
+        <v>158572</v>
       </c>
       <c r="P19" t="n">
-        <v>0.256</v>
+        <v>0.128</v>
       </c>
       <c r="Q19" t="n">
         <v>672952</v>
@@ -3842,10 +3842,10 @@
         <v>38.25</v>
       </c>
       <c r="V19" t="n">
-        <v>30.7914</v>
+        <v>31.0694</v>
       </c>
       <c r="W19" t="n">
-        <v>19.8224</v>
+        <v>19.9283</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>35.1502</v>
+        <v>35.1835</v>
       </c>
       <c r="AA19" t="n">
-        <v>31.3813</v>
+        <v>31.5429</v>
       </c>
       <c r="AB19" t="n">
-        <v>21.8988</v>
+        <v>22.0341</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>1.3007</v>
+        <v>1.184</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7744</v>
+        <v>1.6563</v>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
@@ -3888,18 +3888,18 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>53.09</v>
+        <v>54.55</v>
       </c>
       <c r="AI19" t="n">
-        <v>36.2105</v>
+        <v>36.1947</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>34.425</v>
+        <v>34.535</v>
       </c>
       <c r="AL19" t="n">
         <v>34.35</v>
@@ -3913,49 +3913,49 @@
         <v>37.3616</v>
       </c>
       <c r="AO19" t="n">
-        <v>37.7808</v>
+        <v>37.7175</v>
       </c>
       <c r="AP19" t="n">
         <v>38.2267</v>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.78; TP3: Classic R1 at 38.23</t>
+          <t>TP1: Fibonacci R1 at 37.36; TP2: Bollinger Upper Band at 37.72; TP3: Classic R1 at 38.23</t>
         </is>
       </c>
       <c r="AR19" t="n">
-        <v>39.15</v>
+        <v>15.28</v>
       </c>
       <c r="AS19" t="n">
-        <v>44.74</v>
+        <v>17.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>50.69</v>
+        <v>19.95</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.529999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.04</v>
+        <v>10.69</v>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 53.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.5))</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10.52</v>
+        <v>10.55</v>
       </c>
       <c r="F20" t="n">
         <v>0.2114</v>
@@ -4004,10 +4004,10 @@
         <v>4419729</v>
       </c>
       <c r="O20" t="n">
-        <v>1174538</v>
+        <v>231480</v>
       </c>
       <c r="P20" t="n">
-        <v>0.266</v>
+        <v>0.052</v>
       </c>
       <c r="Q20" t="n">
         <v>2229572</v>
@@ -4025,10 +4025,10 @@
         <v>10.6802</v>
       </c>
       <c r="V20" t="n">
-        <v>10.1202</v>
+        <v>10.181</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9858</v>
+        <v>8.0053</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -4041,13 +4041,13 @@
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>10.6218</v>
+        <v>10.6149</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.0832</v>
+        <v>10.1015</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.311999999999999</v>
+        <v>8.334199999999999</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="AE20" t="n">
-        <v>0.0842</v>
+        <v>0.0713</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1798</v>
+        <v>0.1581</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -4071,58 +4071,58 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>49.52</v>
+        <v>50.53</v>
       </c>
       <c r="AI20" t="n">
-        <v>10.7891</v>
+        <v>10.7294</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK20" t="n">
+        <v>10.4458</v>
+      </c>
+      <c r="AL20" t="n">
         <v>10.3209</v>
       </c>
-      <c r="AL20" t="n">
-        <v>10.21</v>
-      </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN20" t="n">
+        <v>11.0252</v>
+      </c>
+      <c r="AO20" t="n">
         <v>11.0391</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>11.0653</v>
       </c>
       <c r="AP20" t="n">
         <v>11.15</v>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.04; TP2: Bollinger Upper Band at 11.07; TP3: Classic R1 at 11.15</t>
+          <t>TP1: Bollinger Upper Band at 11.03; TP2: Fibonacci R1 at 11.04; TP3: Classic R1 at 11.15</t>
         </is>
       </c>
       <c r="AR20" t="n">
-        <v>6.47</v>
+        <v>4.64</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.71</v>
+        <v>4.75</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.47</v>
+        <v>5.64</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.96</v>
+        <v>5.55</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.21</v>
+        <v>5.68</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.029999999999999</v>
+        <v>6.74</v>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
@@ -4131,14 +4131,14 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Fibonacci S1 (neutral (RSI: 49.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Bollinger Lower Band (overbought (RSI: 50.5))</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>31.64</v>
+        <v>31.66</v>
       </c>
       <c r="F21" t="n">
         <v>0.6358</v>
@@ -4182,7 +4182,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>20.32</v>
+        <v>20.33</v>
       </c>
       <c r="M21" t="n">
         <v>1.557</v>
@@ -4191,10 +4191,10 @@
         <v>703316</v>
       </c>
       <c r="O21" t="n">
-        <v>1419114</v>
+        <v>245720</v>
       </c>
       <c r="P21" t="n">
-        <v>2.018</v>
+        <v>0.349</v>
       </c>
       <c r="Q21" t="n">
         <v>253016</v>
@@ -4212,10 +4212,10 @@
         <v>36.7</v>
       </c>
       <c r="V21" t="n">
-        <v>34.8434</v>
+        <v>34.7664</v>
       </c>
       <c r="W21" t="n">
-        <v>32.7093</v>
+        <v>32.7831</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -4228,13 +4228,13 @@
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>33.7956</v>
+        <v>33.5922</v>
       </c>
       <c r="AA21" t="n">
-        <v>34.8059</v>
+        <v>34.6825</v>
       </c>
       <c r="AB21" t="n">
-        <v>31.4507</v>
+        <v>31.4528</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
@@ -4247,10 +4247,10 @@
         </is>
       </c>
       <c r="AE21" t="n">
-        <v>-0.9599</v>
+        <v>-1.0074</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.6076</v>
+        <v>-0.6876</v>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
@@ -4258,18 +4258,18 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>33.19</v>
+        <v>33.37</v>
       </c>
       <c r="AI21" t="n">
-        <v>34.373</v>
+        <v>34.1575</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>31.0535</v>
+        <v>30.6969</v>
       </c>
       <c r="AL21" t="n">
         <v>29.9767</v>
@@ -4280,36 +4280,36 @@
         </is>
       </c>
       <c r="AN21" t="n">
-        <v>32.7093</v>
+        <v>32.7831</v>
       </c>
       <c r="AO21" t="n">
-        <v>35.9117</v>
+        <v>35.9113</v>
       </c>
       <c r="AP21" t="n">
         <v>37.0467</v>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>TP1: 200 SMA at 32.71; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
+          <t>TP1: 200 SMA at 32.78; TP2: 100 SMA at 35.91; TP3: Classic R1 at 37.05</t>
         </is>
       </c>
       <c r="AR21" t="n">
-        <v>1.54</v>
+        <v>2.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.51</v>
+        <v>7.24</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.57</v>
+        <v>8.82</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.33</v>
+        <v>6.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>15.64</v>
+        <v>16.99</v>
       </c>
       <c r="AW21" t="n">
-        <v>19.3</v>
+        <v>20.69</v>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
@@ -4318,14 +4318,14 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 33.2))</t>
+          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 33.4))</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>310</v>
+        <v>336.99</v>
       </c>
       <c r="F22" t="n">
         <v>6.2294</v>
@@ -4378,10 +4378,10 @@
         <v>388779</v>
       </c>
       <c r="O22" t="n">
-        <v>1627520</v>
+        <v>601604</v>
       </c>
       <c r="P22" t="n">
-        <v>4.186</v>
+        <v>1.547</v>
       </c>
       <c r="Q22" t="n">
         <v>364123</v>
@@ -4399,10 +4399,10 @@
         <v>242</v>
       </c>
       <c r="V22" t="n">
-        <v>189.0366</v>
+        <v>192.6286</v>
       </c>
       <c r="W22" t="n">
-        <v>128.2318</v>
+        <v>129.4084</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -4415,13 +4415,13 @@
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>232.9441</v>
+        <v>242.8532</v>
       </c>
       <c r="AA22" t="n">
-        <v>197.655</v>
+        <v>203.1191</v>
       </c>
       <c r="AB22" t="n">
-        <v>135.0545</v>
+        <v>137.0638</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>27.0475</v>
+        <v>31.9525</v>
       </c>
       <c r="AF22" t="n">
-        <v>20.3968</v>
+        <v>22.7079</v>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
@@ -4445,21 +4445,21 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>81.2</v>
+        <v>84.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>234.2503</v>
+        <v>239.6155</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>237.775</v>
+        <v>250.51</v>
       </c>
       <c r="AL22" t="n">
-        <v>216.6517</v>
+        <v>222.5526</v>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
@@ -4470,33 +4470,33 @@
         <v>365.95</v>
       </c>
       <c r="AO22" t="n">
-        <v>430.0375</v>
+        <v>423.67</v>
       </c>
       <c r="AP22" t="n">
-        <v>396.1993</v>
+        <v>393.1938</v>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 365.95; TP2: Extension at 430.04; TP3: Extension at 396.2</t>
+          <t>TP1: Classic R3 at 365.95; TP2: Extension at 423.67; TP3: Extension at 393.19</t>
         </is>
       </c>
       <c r="AR22" t="n">
-        <v>6.07</v>
+        <v>4.13</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.1</v>
+        <v>6.19</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU22" t="n">
-        <v>53.91</v>
+        <v>46.08</v>
       </c>
       <c r="AV22" t="n">
-        <v>80.86</v>
+        <v>69.12</v>
       </c>
       <c r="AW22" t="n">
-        <v>66.63</v>
+        <v>56.96</v>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
@@ -4505,14 +4505,14 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 81.2))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (84.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 84.2))</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>107</v>
+        <v>110.6</v>
       </c>
       <c r="F23" t="n">
         <v>2.1501</v>
@@ -4565,10 +4565,10 @@
         <v>306887</v>
       </c>
       <c r="O23" t="n">
-        <v>1768110</v>
+        <v>228836</v>
       </c>
       <c r="P23" t="n">
-        <v>5.761</v>
+        <v>0.746</v>
       </c>
       <c r="Q23" t="n">
         <v>162055</v>
@@ -4586,10 +4586,10 @@
         <v>97.5</v>
       </c>
       <c r="V23" t="n">
-        <v>90.4128</v>
+        <v>90.8592</v>
       </c>
       <c r="W23" t="n">
-        <v>82.0089</v>
+        <v>82.1827</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -4602,13 +4602,13 @@
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>96.2457</v>
+        <v>97.61279999999999</v>
       </c>
       <c r="AA23" t="n">
-        <v>91.5844</v>
+        <v>92.3301</v>
       </c>
       <c r="AB23" t="n">
-        <v>83.8661</v>
+        <v>84.13209999999999</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>4.0767</v>
+        <v>4.703</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.6918</v>
+        <v>3.094</v>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
@@ -4632,21 +4632,21 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>73.31</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="AI23" t="n">
-        <v>101.771</v>
+        <v>102.0539</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>101.771</v>
+        <v>102.0539</v>
       </c>
       <c r="AL23" t="n">
-        <v>95.48</v>
+        <v>98.14279999999999</v>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
@@ -4657,33 +4657,33 @@
         <v>115.15</v>
       </c>
       <c r="AO23" t="n">
-        <v>121.8395</v>
+        <v>121.6981</v>
       </c>
       <c r="AP23" t="n">
-        <v>118.3075</v>
+        <v>118.2407</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 115.15; TP2: Extension at 121.84; TP3: Extension at 118.31</t>
+          <t>TP1: Classic R3 at 115.15; TP2: Extension at 121.7; TP3: Extension at 118.24</t>
         </is>
       </c>
       <c r="AR23" t="n">
-        <v>2.13</v>
+        <v>3.35</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.19</v>
+        <v>5.02</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.63</v>
+        <v>4.14</v>
       </c>
       <c r="AU23" t="n">
-        <v>13.15</v>
+        <v>12.83</v>
       </c>
       <c r="AV23" t="n">
-        <v>19.72</v>
+        <v>19.25</v>
       </c>
       <c r="AW23" t="n">
-        <v>16.25</v>
+        <v>15.86</v>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
@@ -4692,14 +4692,14 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.3); entry: enhanced entry at VWMA (overbought (RSI: 73.3))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.5); entry: enhanced entry at VWMA (overbought (RSI: 76.5))</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>45.98</v>
+        <v>45.51</v>
       </c>
       <c r="F24" t="n">
         <v>0.924</v>
@@ -4752,10 +4752,10 @@
         <v>411632</v>
       </c>
       <c r="O24" t="n">
-        <v>490848</v>
+        <v>92078</v>
       </c>
       <c r="P24" t="n">
-        <v>1.192</v>
+        <v>0.224</v>
       </c>
       <c r="Q24" t="n">
         <v>336836</v>
@@ -4773,10 +4773,10 @@
         <v>44.89</v>
       </c>
       <c r="V24" t="n">
-        <v>38.3352</v>
+        <v>38.5876</v>
       </c>
       <c r="W24" t="n">
-        <v>35.1425</v>
+        <v>35.2255</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -4789,13 +4789,13 @@
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>42.5475</v>
+        <v>42.8297</v>
       </c>
       <c r="AA24" t="n">
-        <v>39.4994</v>
+        <v>39.7351</v>
       </c>
       <c r="AB24" t="n">
-        <v>34.5147</v>
+        <v>34.6241</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="AE24" t="n">
-        <v>1.9563</v>
+        <v>1.9533</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.729</v>
+        <v>1.7739</v>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -4819,21 +4819,21 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>67.41</v>
+        <v>64.95</v>
       </c>
       <c r="AI24" t="n">
-        <v>42.9176</v>
+        <v>43.2251</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>42.9176</v>
+        <v>43.2251</v>
       </c>
       <c r="AL24" t="n">
-        <v>40.5284</v>
+        <v>40.8092</v>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
@@ -4844,33 +4844,33 @@
         <v>46.1258</v>
       </c>
       <c r="AO24" t="n">
-        <v>46.3817</v>
+        <v>46.4184</v>
       </c>
       <c r="AP24" t="n">
         <v>49.4033</v>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R2 at 46.13; TP2: Bollinger Upper Band at 46.38; TP3: Classic R2 at 49.4</t>
+          <t>TP1: Fibonacci R2 at 46.13; TP2: Bollinger Upper Band at 46.42; TP3: Classic R2 at 49.4</t>
         </is>
       </c>
       <c r="AR24" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.48</v>
+        <v>6.71</v>
       </c>
       <c r="AV24" t="n">
-        <v>8.07</v>
+        <v>7.39</v>
       </c>
       <c r="AW24" t="n">
-        <v>15.11</v>
+        <v>14.29</v>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
@@ -4879,14 +4879,14 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.4))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.9))</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>12.52</v>
+        <v>12.65</v>
       </c>
       <c r="F25" t="n">
         <v>0.2516</v>
@@ -4933,10 +4933,10 @@
         <v>2925008</v>
       </c>
       <c r="O25" t="n">
-        <v>956107</v>
+        <v>21729</v>
       </c>
       <c r="P25" t="n">
-        <v>0.327</v>
+        <v>0.007</v>
       </c>
       <c r="Q25" t="n">
         <v>1410597</v>
@@ -4954,10 +4954,10 @@
         <v>12.3</v>
       </c>
       <c r="V25" t="n">
-        <v>10.86</v>
+        <v>10.94</v>
       </c>
       <c r="W25" t="n">
-        <v>8.295999999999999</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>12.0546</v>
+        <v>12.1113</v>
       </c>
       <c r="AA25" t="n">
-        <v>11.1423</v>
+        <v>11.2014</v>
       </c>
       <c r="AB25" t="n">
-        <v>8.6051</v>
+        <v>8.6454</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="AE25" t="n">
-        <v>0.5165</v>
+        <v>0.5013</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.4843</v>
+        <v>0.4877</v>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
@@ -5000,21 +5000,21 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>60.45</v>
+        <v>61.91</v>
       </c>
       <c r="AI25" t="n">
-        <v>12.0352</v>
+        <v>12.0544</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>12.285</v>
+        <v>12.29</v>
       </c>
       <c r="AL25" t="n">
-        <v>11.247</v>
+        <v>11.3479</v>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
@@ -5025,33 +5025,33 @@
         <v>12.8261</v>
       </c>
       <c r="AO25" t="n">
-        <v>13.0874</v>
+        <v>13.1197</v>
       </c>
       <c r="AP25" t="n">
         <v>13.1767</v>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 12.83; TP2: Bollinger Upper Band at 13.09; TP3: Classic R1 at 13.18</t>
+          <t>TP1: Fibonacci R1 at 12.83; TP2: Bollinger Upper Band at 13.12; TP3: Classic R1 at 13.18</t>
         </is>
       </c>
       <c r="AR25" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.77</v>
+        <v>0.88</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="AV25" t="n">
-        <v>6.53</v>
+        <v>6.75</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
@@ -5060,14 +5060,14 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 60.5))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.9))</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>397.72</v>
+        <v>466</v>
       </c>
       <c r="F26" t="n">
         <v>7.9921</v>
@@ -5120,10 +5120,10 @@
         <v>170200</v>
       </c>
       <c r="O26" t="n">
-        <v>2414902</v>
+        <v>467098</v>
       </c>
       <c r="P26" t="n">
-        <v>14.189</v>
+        <v>2.744</v>
       </c>
       <c r="Q26" t="n">
         <v>307680</v>
@@ -5141,10 +5141,10 @@
         <v>74.2</v>
       </c>
       <c r="V26" t="n">
-        <v>115.2284</v>
+        <v>123.1364</v>
       </c>
       <c r="W26" t="n">
-        <v>77.3973</v>
+        <v>79.4023</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>217.6619</v>
+        <v>241.3132</v>
       </c>
       <c r="AA26" t="n">
-        <v>144.2529</v>
+        <v>156.8705</v>
       </c>
       <c r="AB26" t="n">
-        <v>85.8312</v>
+        <v>89.614</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="AE26" t="n">
-        <v>74.9525</v>
+        <v>85.15430000000001</v>
       </c>
       <c r="AF26" t="n">
-        <v>48.0599</v>
+        <v>55.4788</v>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
@@ -5187,18 +5187,18 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>78.06999999999999</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="AI26" t="n">
-        <v>220.0841</v>
+        <v>228.0098</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK26" t="n">
-        <v>282.59</v>
+        <v>283.13</v>
       </c>
       <c r="AL26" t="n">
         <v>125.9867</v>
@@ -5209,36 +5209,36 @@
         </is>
       </c>
       <c r="AN26" t="n">
-        <v>402.9103</v>
+        <v>524.1933</v>
       </c>
       <c r="AO26" t="n">
-        <v>524.1933</v>
+        <v>644.725</v>
       </c>
       <c r="AP26" t="n">
-        <v>616.4858</v>
+        <v>581.0843</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 402.91; TP2: Classic R3 at 524.19; TP3: Extension at 616.49</t>
+          <t>TP1: Classic R3 at 524.19; TP2: Extension at 644.73; TP3: Extension at 581.08</t>
         </is>
       </c>
       <c r="AR26" t="n">
-        <v>0.77</v>
+        <v>1.53</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>42.58</v>
+        <v>85.14</v>
       </c>
       <c r="AV26" t="n">
-        <v>85.5</v>
+        <v>127.71</v>
       </c>
       <c r="AW26" t="n">
-        <v>118.16</v>
+        <v>105.24</v>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
@@ -5247,14 +5247,14 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (78.1); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 78.1))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.5); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 81.5))</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5273,7 +5273,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>20.84</v>
       </c>
       <c r="F27" t="n">
         <v>0.422</v>
@@ -5303,10 +5303,10 @@
         <v>710294</v>
       </c>
       <c r="O27" t="n">
-        <v>1303344</v>
+        <v>144439</v>
       </c>
       <c r="P27" t="n">
-        <v>1.835</v>
+        <v>0.203</v>
       </c>
       <c r="Q27" t="n">
         <v>328979</v>
@@ -5324,10 +5324,10 @@
         <v>22.2</v>
       </c>
       <c r="V27" t="n">
-        <v>19.5866</v>
+        <v>19.6126</v>
       </c>
       <c r="W27" t="n">
-        <v>19.3168</v>
+        <v>19.3211</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -5340,13 +5340,13 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>19.9162</v>
+        <v>20.0042</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.7174</v>
+        <v>19.7615</v>
       </c>
       <c r="AB27" t="n">
-        <v>18.7951</v>
+        <v>18.8155</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -5359,10 +5359,10 @@
         </is>
       </c>
       <c r="AE27" t="n">
-        <v>0.3047</v>
+        <v>0.3381</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.1207</v>
+        <v>0.1642</v>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
@@ -5370,14 +5370,14 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>68.03</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AI27" t="n">
-        <v>20.1538</v>
+        <v>20.1702</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -5392,37 +5392,37 @@
         </is>
       </c>
       <c r="AN27" t="n">
+        <v>20.9033</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>21.0206</v>
+      </c>
+      <c r="AP27" t="n">
         <v>22.2233</v>
       </c>
-      <c r="AO27" t="n">
-        <v>23.2224</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>22.6949</v>
-      </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>TP1: Classic R3 at 22.22; TP2: Extension at 23.22; TP3: Extension at 22.69</t>
+          <t>TP1: Classic R2 at 20.9; TP2: Bollinger Upper Band at 21.02; TP3: Classic R3 at 22.22</t>
         </is>
       </c>
       <c r="AR27" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT27" t="n">
         <v>2.79</v>
       </c>
-      <c r="AS27" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AU27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AW27" t="n">
         <v>9.880000000000001</v>
       </c>
-      <c r="AV27" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>12.21</v>
-      </c>
       <c r="AX27" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 68.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 64.8))</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>16.17</v>
+        <v>16.2</v>
       </c>
       <c r="F28" t="n">
         <v>0.3249</v>
@@ -5486,10 +5486,10 @@
         <v>947901</v>
       </c>
       <c r="O28" t="n">
-        <v>1471137</v>
+        <v>84117</v>
       </c>
       <c r="P28" t="n">
-        <v>1.552</v>
+        <v>0.089</v>
       </c>
       <c r="Q28" t="n">
         <v>373572</v>
@@ -5507,10 +5507,10 @@
         <v>16.19</v>
       </c>
       <c r="V28" t="n">
-        <v>15.3462</v>
+        <v>15.3532</v>
       </c>
       <c r="W28" t="n">
-        <v>15.2662</v>
+        <v>15.2639</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>15.5982</v>
+        <v>15.6555</v>
       </c>
       <c r="AA28" t="n">
-        <v>15.4361</v>
+        <v>15.466</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.9383</v>
+        <v>14.9508</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="AE28" t="n">
-        <v>0.2322</v>
+        <v>0.2499</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.1324</v>
+        <v>0.1559</v>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
@@ -5553,18 +5553,18 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>61.64</v>
+        <v>62.05</v>
       </c>
       <c r="AI28" t="n">
-        <v>15.7029</v>
+        <v>15.7142</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>15.7029</v>
+        <v>15.7142</v>
       </c>
       <c r="AL28" t="n">
         <v>15.43</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="AN28" t="n">
-        <v>16.2388</v>
+        <v>16.327</v>
       </c>
       <c r="AO28" t="n">
         <v>16.6333</v>
@@ -5585,26 +5585,26 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 16.24; TP2: Classic R2 at 16.63; TP3: Classic R3 at 17.98</t>
+          <t>TP1: Bollinger Upper Band at 16.33; TP2: Classic R2 at 16.63; TP3: Classic R3 at 17.98</t>
         </is>
       </c>
       <c r="AR28" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.41</v>
+        <v>3.23</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.359999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.92</v>
+        <v>5.85</v>
       </c>
       <c r="AW28" t="n">
-        <v>14.52</v>
+        <v>14.44</v>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
@@ -5613,14 +5613,14 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.6))</t>
+          <t>undervalued, buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.0))</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5639,7 +5639,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30.9</v>
+        <v>31.45</v>
       </c>
       <c r="F29" t="n">
         <v>0.6209</v>
@@ -5669,10 +5669,10 @@
         <v>1441158</v>
       </c>
       <c r="O29" t="n">
-        <v>338108</v>
+        <v>234192</v>
       </c>
       <c r="P29" t="n">
-        <v>0.235</v>
+        <v>0.163</v>
       </c>
       <c r="Q29" t="n">
         <v>466141</v>
@@ -5690,10 +5690,10 @@
         <v>32.7</v>
       </c>
       <c r="V29" t="n">
-        <v>28.8936</v>
+        <v>29.0346</v>
       </c>
       <c r="W29" t="n">
-        <v>17.9013</v>
+        <v>17.9943</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -5706,13 +5706,13 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>30.0449</v>
+        <v>30.1787</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.804</v>
+        <v>27.9469</v>
       </c>
       <c r="AB29" t="n">
-        <v>19.9078</v>
+        <v>20.0226</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -5725,10 +5725,10 @@
         </is>
       </c>
       <c r="AE29" t="n">
-        <v>0.9514</v>
+        <v>0.9485</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.884</v>
+        <v>0.8969</v>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
@@ -5736,18 +5736,18 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>62.11</v>
+        <v>65.59</v>
       </c>
       <c r="AI29" t="n">
-        <v>29.9722</v>
+        <v>30.07</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK29" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="AL29" t="n">
         <v>27.6202</v>
@@ -5761,33 +5761,33 @@
         <v>32.3265</v>
       </c>
       <c r="AO29" t="n">
-        <v>33.143</v>
+        <v>33.3263</v>
       </c>
       <c r="AP29" t="n">
         <v>33.4067</v>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 33.14; TP3: Classic R1 at 33.41</t>
+          <t>TP1: Fibonacci R1 at 32.33; TP2: Bollinger Upper Band at 33.33; TP3: Classic R1 at 33.41</t>
         </is>
       </c>
       <c r="AR29" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.99</v>
+        <v>5.64</v>
       </c>
       <c r="AV29" t="n">
-        <v>8.67</v>
+        <v>8.91</v>
       </c>
       <c r="AW29" t="n">
-        <v>9.529999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
@@ -5796,14 +5796,14 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 62.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 65.6))</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>34</v>
+        <v>34.26</v>
       </c>
       <c r="F30" t="n">
         <v>0.6832</v>
@@ -5856,10 +5856,10 @@
         <v>804484</v>
       </c>
       <c r="O30" t="n">
-        <v>695448</v>
+        <v>41361</v>
       </c>
       <c r="P30" t="n">
-        <v>0.864</v>
+        <v>0.051</v>
       </c>
       <c r="Q30" t="n">
         <v>850850</v>
@@ -5877,10 +5877,10 @@
         <v>37</v>
       </c>
       <c r="V30" t="n">
-        <v>30.1046</v>
+        <v>30.249</v>
       </c>
       <c r="W30" t="n">
-        <v>26.8989</v>
+        <v>26.9415</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -5893,13 +5893,13 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>33.6376</v>
+        <v>33.6969</v>
       </c>
       <c r="AA30" t="n">
-        <v>31.0668</v>
+        <v>31.192</v>
       </c>
       <c r="AB30" t="n">
-        <v>27.6328</v>
+        <v>27.6987</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="AE30" t="n">
-        <v>1.5644</v>
+        <v>1.4255</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.714</v>
+        <v>1.6563</v>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
@@ -5923,21 +5923,21 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>55.03</v>
+        <v>56.05</v>
       </c>
       <c r="AI30" t="n">
-        <v>33.621</v>
+        <v>33.9723</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK30" t="n">
-        <v>33.621</v>
+        <v>33.9723</v>
       </c>
       <c r="AL30" t="n">
-        <v>30.6464</v>
+        <v>30.7892</v>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
@@ -5948,33 +5948,33 @@
         <v>36.5522</v>
       </c>
       <c r="AO30" t="n">
-        <v>37.3797</v>
+        <v>37.3408</v>
       </c>
       <c r="AP30" t="n">
         <v>38.3133</v>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.38; TP3: Classic R1 at 38.31</t>
+          <t>TP1: Fibonacci R1 at 36.55; TP2: Bollinger Upper Band at 37.34; TP3: Classic R1 at 38.31</t>
         </is>
       </c>
       <c r="AR30" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.720000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.18</v>
+        <v>9.92</v>
       </c>
       <c r="AW30" t="n">
-        <v>13.96</v>
+        <v>12.78</v>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
@@ -5983,14 +5983,14 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 55.0))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 56.1))</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="F31" t="n">
         <v>0.0398</v>
@@ -6039,10 +6039,10 @@
         <v>35045723</v>
       </c>
       <c r="O31" t="n">
-        <v>49318546</v>
+        <v>60997022</v>
       </c>
       <c r="P31" t="n">
-        <v>1.407</v>
+        <v>1.74</v>
       </c>
       <c r="Q31" t="n">
         <v>18371193</v>
@@ -6060,10 +6060,10 @@
         <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>1.8316</v>
+        <v>1.842</v>
       </c>
       <c r="W31" t="n">
-        <v>1.6967</v>
+        <v>1.6979</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -6076,13 +6076,13 @@
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>1.9072</v>
+        <v>1.9236</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8363</v>
+        <v>1.8458</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6388</v>
+        <v>1.6432</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="AE31" t="n">
-        <v>0.037</v>
+        <v>0.0463</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.0328</v>
+        <v>0.0355</v>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
@@ -6106,21 +6106,21 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>61.28</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.9246</v>
+        <v>1.9351</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK31" t="n">
-        <v>1.9246</v>
+        <v>1.945</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.8835</v>
+        <v>1.8947</v>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
@@ -6128,36 +6128,36 @@
         </is>
       </c>
       <c r="AN31" t="n">
-        <v>1.9968</v>
+        <v>2.0833</v>
       </c>
       <c r="AO31" t="n">
-        <v>2.0413</v>
+        <v>2.1121</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.0833</v>
+        <v>2.2267</v>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 2.0; TP2: Fibonacci R1 at 2.04; TP3: Classic R1 at 2.08</t>
+          <t>TP1: Classic R1 at 2.08; TP2: Fibonacci R2 at 2.11; TP3: Classic R2 at 2.23</t>
         </is>
       </c>
       <c r="AR31" t="n">
-        <v>1.76</v>
+        <v>2.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.86</v>
+        <v>5.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.75</v>
+        <v>7.11</v>
       </c>
       <c r="AV31" t="n">
-        <v>6.06</v>
+        <v>8.59</v>
       </c>
       <c r="AW31" t="n">
-        <v>8.24</v>
+        <v>14.48</v>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
@@ -6166,14 +6166,14 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 69.0))</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6192,7 +6192,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.11</v>
+        <v>10.18</v>
       </c>
       <c r="F32" t="n">
         <v>0.2032</v>
@@ -6222,10 +6222,10 @@
         <v>5366713</v>
       </c>
       <c r="O32" t="n">
-        <v>5016931</v>
+        <v>367092</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="Q32" t="n">
         <v>1203993</v>
@@ -6243,10 +6243,10 @@
         <v>10.26</v>
       </c>
       <c r="V32" t="n">
-        <v>9.6572</v>
+        <v>9.6724</v>
       </c>
       <c r="W32" t="n">
-        <v>9.613099999999999</v>
+        <v>9.6061</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -6259,13 +6259,13 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>9.8285</v>
+        <v>9.862</v>
       </c>
       <c r="AA32" t="n">
-        <v>9.700699999999999</v>
+        <v>9.7195</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.4963</v>
+        <v>9.5031</v>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="AE32" t="n">
-        <v>0.1125</v>
+        <v>0.1262</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.0844</v>
+        <v>0.0927</v>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
@@ -6289,21 +6289,21 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>61.45</v>
+        <v>63.27</v>
       </c>
       <c r="AI32" t="n">
-        <v>9.876899999999999</v>
+        <v>9.883599999999999</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>9.876899999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AL32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.868399999999999</v>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
@@ -6311,36 +6311,36 @@
         </is>
       </c>
       <c r="AN32" t="n">
-        <v>10.1864</v>
+        <v>10.2191</v>
       </c>
       <c r="AO32" t="n">
-        <v>10.2191</v>
+        <v>10.2388</v>
       </c>
       <c r="AP32" t="n">
         <v>10.29</v>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 10.19; TP2: Fibonacci R1 at 10.22; TP3: Classic R1 at 10.29</t>
+          <t>TP1: Fibonacci R1 at 10.22; TP2: Bollinger Upper Band at 10.24; TP3: Classic R1 at 10.29</t>
         </is>
       </c>
       <c r="AR32" t="n">
-        <v>4.03</v>
+        <v>10.1</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.45</v>
+        <v>10.72</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.38</v>
+        <v>12.34</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.18</v>
+        <v>3.94</v>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
@@ -6349,14 +6349,14 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.5))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 63.3))</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>10.99</v>
       </c>
       <c r="F33" t="n">
         <v>0.221</v>
@@ -6409,10 +6409,10 @@
         <v>2700114</v>
       </c>
       <c r="O33" t="n">
-        <v>8908422</v>
+        <v>1332597</v>
       </c>
       <c r="P33" t="n">
-        <v>3.299</v>
+        <v>0.494</v>
       </c>
       <c r="Q33" t="n">
         <v>1499132</v>
@@ -6430,10 +6430,10 @@
         <v>9.75</v>
       </c>
       <c r="V33" t="n">
-        <v>9.319000000000001</v>
+        <v>9.3622</v>
       </c>
       <c r="W33" t="n">
-        <v>8.0511</v>
+        <v>8.069699999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>9.763</v>
+        <v>9.879799999999999</v>
       </c>
       <c r="AA33" t="n">
-        <v>9.357100000000001</v>
+        <v>9.421200000000001</v>
       </c>
       <c r="AB33" t="n">
-        <v>8.229799999999999</v>
+        <v>8.257300000000001</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -6465,10 +6465,10 @@
         </is>
       </c>
       <c r="AE33" t="n">
-        <v>0.3158</v>
+        <v>0.3734</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.1716</v>
+        <v>0.212</v>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
@@ -6476,21 +6476,21 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>79.59</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="AI33" t="n">
-        <v>9.998900000000001</v>
+        <v>10.0289</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>10.185</v>
+        <v>10.195</v>
       </c>
       <c r="AL33" t="n">
-        <v>9.520899999999999</v>
+        <v>9.754799999999999</v>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
@@ -6501,10 +6501,10 @@
         <v>11.0167</v>
       </c>
       <c r="AO33" t="n">
-        <v>11.4325</v>
+        <v>11.4276</v>
       </c>
       <c r="AP33" t="n">
-        <v>11.2129</v>
+        <v>11.2106</v>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
@@ -6512,22 +6512,22 @@
         </is>
       </c>
       <c r="AR33" t="n">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.88</v>
+        <v>2.8</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.55</v>
+        <v>2.31</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.17</v>
+        <v>8.06</v>
       </c>
       <c r="AV33" t="n">
-        <v>12.25</v>
+        <v>12.09</v>
       </c>
       <c r="AW33" t="n">
-        <v>10.09</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
@@ -6536,14 +6536,14 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.6); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.6))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (79.2); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 79.2))</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10.14</v>
+        <v>10.09</v>
       </c>
       <c r="F34" t="n">
         <v>0.2038</v>
@@ -6592,10 +6592,10 @@
         <v>2332289</v>
       </c>
       <c r="O34" t="n">
-        <v>1275416</v>
+        <v>157961</v>
       </c>
       <c r="P34" t="n">
-        <v>0.547</v>
+        <v>0.068</v>
       </c>
       <c r="Q34" t="n">
         <v>690975</v>
@@ -6613,10 +6613,10 @@
         <v>10.26</v>
       </c>
       <c r="V34" t="n">
-        <v>9.978</v>
+        <v>9.9856</v>
       </c>
       <c r="W34" t="n">
-        <v>9.2349</v>
+        <v>9.2319</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -6629,13 +6629,13 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>10.0968</v>
+        <v>10.0961</v>
       </c>
       <c r="AA34" t="n">
-        <v>9.944599999999999</v>
+        <v>9.9503</v>
       </c>
       <c r="AB34" t="n">
-        <v>9.1305</v>
+        <v>9.1401</v>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
@@ -6648,10 +6648,10 @@
         </is>
       </c>
       <c r="AE34" t="n">
-        <v>0.0416</v>
+        <v>0.0365</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0537</v>
+        <v>0.0503</v>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
@@ -6659,21 +6659,21 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>52.49</v>
+        <v>50.67</v>
       </c>
       <c r="AI34" t="n">
-        <v>10.2366</v>
+        <v>10.2386</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK34" t="n">
-        <v>9.978</v>
+        <v>9.9856</v>
       </c>
       <c r="AL34" t="n">
-        <v>9.917199999999999</v>
+        <v>9.9206</v>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="AN34" t="n">
-        <v>10.3818</v>
+        <v>10.3814</v>
       </c>
       <c r="AO34" t="n">
         <v>10.6503</v>
@@ -6695,22 +6695,22 @@
         </is>
       </c>
       <c r="AR34" t="n">
-        <v>6.64</v>
+        <v>6.09</v>
       </c>
       <c r="AS34" t="n">
-        <v>11.05</v>
+        <v>10.23</v>
       </c>
       <c r="AT34" t="n">
-        <v>11.92</v>
+        <v>11.04</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AV34" t="n">
-        <v>6.74</v>
+        <v>6.66</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.27</v>
+        <v>7.19</v>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
@@ -6719,14 +6719,14 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 52.5))</t>
+          <t>buy-volume spike (vs 2‑month), near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 50.7))</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6779,10 +6779,10 @@
         <v>2871474</v>
       </c>
       <c r="O35" t="n">
-        <v>6519577</v>
+        <v>1143786</v>
       </c>
       <c r="P35" t="n">
-        <v>2.27</v>
+        <v>0.398</v>
       </c>
       <c r="Q35" t="n">
         <v>760108</v>
@@ -6800,10 +6800,10 @@
         <v>16.77</v>
       </c>
       <c r="V35" t="n">
-        <v>16.3308</v>
+        <v>16.318</v>
       </c>
       <c r="W35" t="n">
-        <v>16.262</v>
+        <v>16.2661</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -6816,13 +6816,13 @@
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>16.0787</v>
+        <v>16.1369</v>
       </c>
       <c r="AA35" t="n">
-        <v>16.3223</v>
+        <v>16.3367</v>
       </c>
       <c r="AB35" t="n">
-        <v>16.4326</v>
+        <v>16.4352</v>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
         </is>
       </c>
       <c r="AE35" t="n">
-        <v>-0.0408</v>
+        <v>0.0112</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.1226</v>
+        <v>-0.0958</v>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
@@ -6849,18 +6849,18 @@
         <v>59.16</v>
       </c>
       <c r="AI35" t="n">
-        <v>16.0932</v>
+        <v>16.0956</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK35" t="n">
         <v>16.66</v>
       </c>
       <c r="AL35" t="n">
-        <v>16.262</v>
+        <v>16.2661</v>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
@@ -6871,21 +6871,21 @@
         <v>16.72</v>
       </c>
       <c r="AO35" t="n">
-        <v>16.778</v>
+        <v>16.8474</v>
       </c>
       <c r="AP35" t="n">
-        <v>16.9736</v>
+        <v>16.9694</v>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>TP1: Classic R1 at 16.72; TP2: Bollinger Upper Band at 16.78; TP3: 100 SMA at 16.97</t>
+          <t>TP1: Classic R1 at 16.72; TP2: Bollinger Upper Band at 16.85; TP3: 100 SMA at 16.97</t>
         </is>
       </c>
       <c r="AR35" t="n">
         <v>0.15</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.3</v>
+        <v>0.48</v>
       </c>
       <c r="AT35" t="n">
         <v>0.79</v>
@@ -6894,10 +6894,10 @@
         <v>0.36</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.71</v>
+        <v>1.12</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>79</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F36" t="n">
         <v>1.5875</v>
@@ -6966,10 +6966,10 @@
         <v>734006</v>
       </c>
       <c r="O36" t="n">
-        <v>1360429</v>
+        <v>328068</v>
       </c>
       <c r="P36" t="n">
-        <v>1.853</v>
+        <v>0.447</v>
       </c>
       <c r="Q36" t="n">
         <v>376754</v>
@@ -6987,10 +6987,10 @@
         <v>87.98999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>67.92359999999999</v>
+        <v>68.2296</v>
       </c>
       <c r="W36" t="n">
-        <v>63.494</v>
+        <v>63.6207</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>75.8099</v>
+        <v>76.1994</v>
       </c>
       <c r="AA36" t="n">
-        <v>70.05719999999999</v>
+        <v>70.4432</v>
       </c>
       <c r="AB36" t="n">
-        <v>61.445</v>
+        <v>61.6287</v>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
@@ -7022,10 +7022,10 @@
         </is>
       </c>
       <c r="AE36" t="n">
-        <v>4.1513</v>
+        <v>3.9681</v>
       </c>
       <c r="AF36" t="n">
-        <v>4.2788</v>
+        <v>4.2167</v>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
@@ -7033,18 +7033,18 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>59.64</v>
+        <v>60.98</v>
       </c>
       <c r="AI36" t="n">
-        <v>77.8434</v>
+        <v>77.9833</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK36" t="n">
-        <v>77.8434</v>
+        <v>77.9833</v>
       </c>
       <c r="AL36" t="n">
         <v>66.2534</v>
@@ -7058,33 +7058,33 @@
         <v>86.65989999999999</v>
       </c>
       <c r="AO36" t="n">
-        <v>91.1079</v>
+        <v>91.1168</v>
       </c>
       <c r="AP36" t="n">
         <v>91.63330000000001</v>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 91.11; TP3: Classic R1 at 91.63</t>
+          <t>TP1: Fibonacci R1 at 86.66; TP2: Bollinger Upper Band at 91.12; TP3: Classic R1 at 91.63</t>
         </is>
       </c>
       <c r="AR36" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AU36" t="n">
-        <v>11.33</v>
+        <v>11.13</v>
       </c>
       <c r="AV36" t="n">
-        <v>17.04</v>
+        <v>16.84</v>
       </c>
       <c r="AW36" t="n">
-        <v>17.71</v>
+        <v>17.5</v>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
@@ -7093,14 +7093,14 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 59.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 61.0))</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>30.6</v>
+        <v>30.85</v>
       </c>
       <c r="F37" t="n">
         <v>0.6149</v>
@@ -7153,10 +7153,10 @@
         <v>2155371</v>
       </c>
       <c r="O37" t="n">
-        <v>4935095</v>
+        <v>330729</v>
       </c>
       <c r="P37" t="n">
-        <v>2.29</v>
+        <v>0.153</v>
       </c>
       <c r="Q37" t="n">
         <v>2232204</v>
@@ -7174,10 +7174,10 @@
         <v>28.7</v>
       </c>
       <c r="V37" t="n">
-        <v>24.8542</v>
+        <v>25.0572</v>
       </c>
       <c r="W37" t="n">
-        <v>20.4566</v>
+        <v>20.5303</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -7190,13 +7190,13 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>28.0641</v>
+        <v>28.3295</v>
       </c>
       <c r="AA37" t="n">
-        <v>25.7529</v>
+        <v>25.9528</v>
       </c>
       <c r="AB37" t="n">
-        <v>21.2914</v>
+        <v>21.3866</v>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="AE37" t="n">
-        <v>1.3702</v>
+        <v>1.426</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.2671</v>
+        <v>1.2989</v>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
@@ -7220,21 +7220,21 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>73.53</v>
+        <v>74.48</v>
       </c>
       <c r="AI37" t="n">
-        <v>28.3721</v>
+        <v>28.4314</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>28.3721</v>
+        <v>28.4314</v>
       </c>
       <c r="AL37" t="n">
-        <v>27.4322</v>
+        <v>27.789</v>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
@@ -7248,30 +7248,30 @@
         <v>36.71</v>
       </c>
       <c r="AP37" t="n">
-        <v>39.8951</v>
+        <v>39.8724</v>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 31.97; TP2: Classic R3 at 36.71; TP3: Extension at 39.9</t>
+          <t>TP1: Classic R2 at 31.97; TP2: Classic R3 at 36.71; TP3: Extension at 39.87</t>
         </is>
       </c>
       <c r="AR37" t="n">
-        <v>3.83</v>
+        <v>5.51</v>
       </c>
       <c r="AS37" t="n">
-        <v>8.869999999999999</v>
+        <v>12.89</v>
       </c>
       <c r="AT37" t="n">
-        <v>12.26</v>
+        <v>17.81</v>
       </c>
       <c r="AU37" t="n">
-        <v>12.68</v>
+        <v>12.45</v>
       </c>
       <c r="AV37" t="n">
-        <v>29.39</v>
+        <v>29.12</v>
       </c>
       <c r="AW37" t="n">
-        <v>40.61</v>
+        <v>40.24</v>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
@@ -7280,14 +7280,14 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.5); entry: enhanced entry at VWMA (overbought (RSI: 73.5))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (74.5); entry: enhanced entry at VWMA (overbought (RSI: 74.5))</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9.27</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F38" t="n">
         <v>0.1863</v>
@@ -7340,10 +7340,10 @@
         <v>7486629</v>
       </c>
       <c r="O38" t="n">
-        <v>6589536</v>
+        <v>725949</v>
       </c>
       <c r="P38" t="n">
-        <v>0.88</v>
+        <v>0.097</v>
       </c>
       <c r="Q38" t="n">
         <v>2160309</v>
@@ -7361,10 +7361,10 @@
         <v>9.75</v>
       </c>
       <c r="V38" t="n">
-        <v>9.207800000000001</v>
+        <v>9.212199999999999</v>
       </c>
       <c r="W38" t="n">
-        <v>7.3374</v>
+        <v>7.3551</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>9.263400000000001</v>
+        <v>9.2735</v>
       </c>
       <c r="AA38" t="n">
-        <v>9.015599999999999</v>
+        <v>9.029500000000001</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.5188</v>
+        <v>7.5372</v>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="AE38" t="n">
-        <v>0.0216</v>
+        <v>0.0285</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.0448</v>
+        <v>0.0415</v>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>51.09</v>
+        <v>54.04</v>
       </c>
       <c r="AI38" t="n">
-        <v>9.343299999999999</v>
+        <v>9.334300000000001</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>9.207800000000001</v>
+        <v>9.334300000000001</v>
       </c>
       <c r="AL38" t="n">
-        <v>9.114800000000001</v>
+        <v>9.123699999999999</v>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="AN38" t="n">
-        <v>9.513199999999999</v>
+        <v>9.4923</v>
       </c>
       <c r="AO38" t="n">
         <v>9.7621</v>
@@ -7439,42 +7439,42 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 9.51; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
+          <t>TP1: Bollinger Upper Band at 9.49; TP2: Fibonacci R1 at 9.76; TP3: Classic R1 at 9.78</t>
         </is>
       </c>
       <c r="AR38" t="n">
-        <v>3.28</v>
+        <v>0.75</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.96</v>
+        <v>2.03</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.11</v>
+        <v>2.1</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.32</v>
+        <v>1.69</v>
       </c>
       <c r="AV38" t="n">
-        <v>6.02</v>
+        <v>4.58</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.18</v>
+        <v>4.74</v>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 51.1))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 54.0))</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7493,7 +7493,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.673</v>
+        <v>0.678</v>
       </c>
       <c r="F39" t="n">
         <v>0.0135</v>
@@ -7523,10 +7523,10 @@
         <v>26941783</v>
       </c>
       <c r="O39" t="n">
-        <v>46246375</v>
+        <v>6201067</v>
       </c>
       <c r="P39" t="n">
-        <v>1.717</v>
+        <v>0.23</v>
       </c>
       <c r="Q39" t="n">
         <v>9409186</v>
@@ -7544,10 +7544,10 @@
         <v>0.721</v>
       </c>
       <c r="V39" t="n">
-        <v>0.6976</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="W39" t="n">
-        <v>0.783</v>
+        <v>0.7837</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -7560,13 +7560,13 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>0.6936</v>
+        <v>0.6921</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.7141</v>
+        <v>0.7126</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.7244</v>
+        <v>0.7239</v>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
@@ -7579,10 +7579,10 @@
         </is>
       </c>
       <c r="AE39" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0097</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.0054</v>
+        <v>-0.0063</v>
       </c>
       <c r="AG39" t="inlineStr">
         <is>
@@ -7590,14 +7590,14 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>36.64</v>
+        <v>39.9</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.7044</v>
+        <v>0.7043</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:30</t>
+          <t>2026-08-09 08:04:02</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr"/>
@@ -7635,7 +7635,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4.52</v>
+        <v>4.8</v>
       </c>
       <c r="F40" t="n">
         <v>0.09080000000000001</v>
@@ -7682,10 +7682,10 @@
         <v>6235983</v>
       </c>
       <c r="O40" t="n">
-        <v>3401294</v>
+        <v>13751661</v>
       </c>
       <c r="P40" t="n">
-        <v>0.545</v>
+        <v>2.205</v>
       </c>
       <c r="Q40" t="n">
         <v>4527809</v>
@@ -7703,10 +7703,10 @@
         <v>4.98</v>
       </c>
       <c r="V40" t="n">
-        <v>3.7892</v>
+        <v>3.8172</v>
       </c>
       <c r="W40" t="n">
-        <v>3.0128</v>
+        <v>3.0254</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -7719,13 +7719,13 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>4.2315</v>
+        <v>4.2857</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.8924</v>
+        <v>3.928</v>
       </c>
       <c r="AB40" t="n">
-        <v>3.1539</v>
+        <v>3.1703</v>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="AE40" t="n">
-        <v>0.2511</v>
+        <v>0.2651</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.2203</v>
+        <v>0.2292</v>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
@@ -7749,18 +7749,18 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>62.93</v>
+        <v>68.69</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.3584</v>
+        <v>4.3949</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK40" t="n">
-        <v>4.38</v>
+        <v>4.45</v>
       </c>
       <c r="AL40" t="n">
         <v>3.7589</v>
@@ -7774,33 +7774,33 @@
         <v>4.9278</v>
       </c>
       <c r="AO40" t="n">
-        <v>4.9436</v>
+        <v>5.0192</v>
       </c>
       <c r="AP40" t="n">
         <v>5.2367</v>
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 4.93; TP2: Bollinger Upper Band at 4.94; TP3: Classic R1 at 5.24</t>
+          <t>TP1: Fibonacci R1 at 4.93; TP2: Bollinger Upper Band at 5.02; TP3: Classic R1 at 5.24</t>
         </is>
       </c>
       <c r="AR40" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="AU40" t="n">
-        <v>12.51</v>
+        <v>10.74</v>
       </c>
       <c r="AV40" t="n">
-        <v>12.87</v>
+        <v>12.79</v>
       </c>
       <c r="AW40" t="n">
-        <v>19.56</v>
+        <v>17.68</v>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 62.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 68.7))</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>54.26</v>
       </c>
       <c r="F41" t="n">
         <v>1.065</v>
@@ -7869,10 +7869,10 @@
         <v>2158684</v>
       </c>
       <c r="O41" t="n">
-        <v>1046661</v>
+        <v>537550</v>
       </c>
       <c r="P41" t="n">
-        <v>0.485</v>
+        <v>0.249</v>
       </c>
       <c r="Q41" t="n">
         <v>1261159</v>
@@ -7890,10 +7890,10 @@
         <v>48.49</v>
       </c>
       <c r="V41" t="n">
-        <v>47.805</v>
+        <v>47.9702</v>
       </c>
       <c r="W41" t="n">
-        <v>37.5317</v>
+        <v>37.7032</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -7906,13 +7906,13 @@
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>50.3189</v>
+        <v>50.6943</v>
       </c>
       <c r="AA41" t="n">
-        <v>48.1081</v>
+        <v>48.3494</v>
       </c>
       <c r="AB41" t="n">
-        <v>39.0758</v>
+        <v>39.2269</v>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
@@ -7925,10 +7925,10 @@
         </is>
       </c>
       <c r="AE41" t="n">
-        <v>1.6192</v>
+        <v>1.7306</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.3549</v>
+        <v>1.43</v>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
@@ -7936,18 +7936,18 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>67.51000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="AI41" t="n">
-        <v>49.5355</v>
+        <v>49.736</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK41" t="n">
-        <v>50.2402</v>
+        <v>50.6193</v>
       </c>
       <c r="AL41" t="n">
         <v>48.2733</v>
@@ -7958,36 +7958,36 @@
         </is>
       </c>
       <c r="AN41" t="n">
-        <v>53.2048</v>
+        <v>54.8285</v>
       </c>
       <c r="AO41" t="n">
-        <v>54.8285</v>
+        <v>55.1533</v>
       </c>
       <c r="AP41" t="n">
-        <v>54.8856</v>
+        <v>55.4871</v>
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 53.2; TP2: Fibonacci R2 at 54.83; TP3: Bollinger Upper Band at 54.89</t>
+          <t>TP1: Fibonacci R2 at 54.83; TP2: Classic R1 at 55.15; TP3: Bollinger Upper Band at 55.49</t>
         </is>
       </c>
       <c r="AR41" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.33</v>
+        <v>1.93</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="AU41" t="n">
-        <v>5.9</v>
+        <v>8.32</v>
       </c>
       <c r="AV41" t="n">
-        <v>9.130000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="AW41" t="n">
-        <v>9.25</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
@@ -7996,14 +7996,14 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 67.5))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (71.3); entry: enhanced entry at Parabolic SAR (overbought (RSI: 71.3))</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>37</v>
+        <v>37.06</v>
       </c>
       <c r="F42" t="n">
         <v>0.7435</v>
@@ -8056,10 +8056,10 @@
         <v>1890451</v>
       </c>
       <c r="O42" t="n">
-        <v>1492046</v>
+        <v>185953</v>
       </c>
       <c r="P42" t="n">
-        <v>0.789</v>
+        <v>0.098</v>
       </c>
       <c r="Q42" t="n">
         <v>958395</v>
@@ -8077,10 +8077,10 @@
         <v>38.8</v>
       </c>
       <c r="V42" t="n">
-        <v>38.321</v>
+        <v>38.1922</v>
       </c>
       <c r="W42" t="n">
-        <v>35.8685</v>
+        <v>35.9065</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -8093,13 +8093,13 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>37.1725</v>
+        <v>37.1618</v>
       </c>
       <c r="AA42" t="n">
-        <v>38.266</v>
+        <v>38.2187</v>
       </c>
       <c r="AB42" t="n">
-        <v>36.6828</v>
+        <v>36.6866</v>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         </is>
       </c>
       <c r="AE42" t="n">
-        <v>-0.2911</v>
+        <v>-0.27</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.3977</v>
+        <v>-0.3722</v>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
@@ -8123,21 +8123,21 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>46.7</v>
+        <v>47.23</v>
       </c>
       <c r="AI42" t="n">
-        <v>37.3854</v>
+        <v>37.4247</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>36.0799</v>
+        <v>36.0961</v>
       </c>
       <c r="AL42" t="n">
-        <v>35.8685</v>
+        <v>35.9065</v>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>38.25</v>
       </c>
       <c r="AO42" t="n">
-        <v>38.4871</v>
+        <v>38.4869</v>
       </c>
       <c r="AP42" t="n">
         <v>38.5567</v>
@@ -8159,22 +8159,22 @@
         </is>
       </c>
       <c r="AR42" t="n">
-        <v>10.27</v>
+        <v>11.37</v>
       </c>
       <c r="AS42" t="n">
-        <v>11.39</v>
+        <v>12.62</v>
       </c>
       <c r="AT42" t="n">
-        <v>11.72</v>
+        <v>12.98</v>
       </c>
       <c r="AU42" t="n">
-        <v>6.01</v>
+        <v>5.97</v>
       </c>
       <c r="AV42" t="n">
-        <v>6.67</v>
+        <v>6.62</v>
       </c>
       <c r="AW42" t="n">
-        <v>6.86</v>
+        <v>6.82</v>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
@@ -8183,14 +8183,14 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 46.7))</t>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at Bollinger Lower Band (neutral (RSI: 47.2))</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6.38</v>
+        <v>6.15</v>
       </c>
       <c r="F43" t="n">
         <v>0.1282</v>
@@ -8236,16 +8236,16 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>2920750</v>
+        <v>2918351</v>
       </c>
       <c r="O43" t="n">
-        <v>13653510</v>
+        <v>3506388</v>
       </c>
       <c r="P43" t="n">
-        <v>4.675</v>
+        <v>1.201</v>
       </c>
       <c r="Q43" t="n">
-        <v>2116516</v>
+        <v>2116258</v>
       </c>
       <c r="R43" t="n">
         <v>3161868</v>
@@ -8260,10 +8260,10 @@
         <v>6.4</v>
       </c>
       <c r="V43" t="n">
-        <v>5.2184</v>
+        <v>5.2539</v>
       </c>
       <c r="W43" t="n">
-        <v>4.8572</v>
+        <v>4.8561</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>5.4255</v>
+        <v>5.4945</v>
       </c>
       <c r="AA43" t="n">
-        <v>5.2069</v>
+        <v>5.2439</v>
       </c>
       <c r="AB43" t="n">
-        <v>4.7423</v>
+        <v>4.7563</v>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
@@ -8295,25 +8295,25 @@
         </is>
       </c>
       <c r="AE43" t="n">
-        <v>0.0679</v>
+        <v>0.1182</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.0814</v>
+        <v>0.0888</v>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>66.64</v>
+        <v>61.89</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.5903</v>
+        <v>5.617</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK43" t="n">
@@ -8328,36 +8328,36 @@
         </is>
       </c>
       <c r="AN43" t="n">
-        <v>6.6667</v>
+        <v>6.2083</v>
       </c>
       <c r="AO43" t="n">
-        <v>7.725</v>
+        <v>6.2624</v>
       </c>
       <c r="AP43" t="n">
-        <v>8.402699999999999</v>
+        <v>6.3133</v>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 6.67; TP2: Classic R3 at 7.72; TP3: Extension at 8.4</t>
+          <t>TP1: Classic R1 at 6.21; TP2: Fibonacci R2 at 6.26; TP3: Bollinger Upper Band at 6.31</t>
         </is>
       </c>
       <c r="AR43" t="n">
-        <v>5.47</v>
+        <v>1.97</v>
       </c>
       <c r="AS43" t="n">
-        <v>13.56</v>
+        <v>2.38</v>
       </c>
       <c r="AT43" t="n">
-        <v>18.74</v>
+        <v>2.77</v>
       </c>
       <c r="AU43" t="n">
-        <v>12.03</v>
+        <v>4.33</v>
       </c>
       <c r="AV43" t="n">
-        <v>29.81</v>
+        <v>5.24</v>
       </c>
       <c r="AW43" t="n">
-        <v>41.2</v>
+        <v>6.09</v>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
@@ -8366,14 +8366,14 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 66.6))</t>
+          <t>undervalued, Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.9))</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8392,7 +8392,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>379.1</v>
+        <v>378.9</v>
       </c>
       <c r="F44" t="n">
         <v>7.6179</v>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>479.69</v>
+        <v>479.44</v>
       </c>
       <c r="M44" t="n">
         <v>0.7903</v>
@@ -8426,10 +8426,10 @@
         <v>35690</v>
       </c>
       <c r="O44" t="n">
-        <v>50638</v>
+        <v>6727</v>
       </c>
       <c r="P44" t="n">
-        <v>1.419</v>
+        <v>0.188</v>
       </c>
       <c r="Q44" t="n">
         <v>15183</v>
@@ -8447,10 +8447,10 @@
         <v>380</v>
       </c>
       <c r="V44" t="n">
-        <v>361.8832</v>
+        <v>362.3814</v>
       </c>
       <c r="W44" t="n">
-        <v>343.8158</v>
+        <v>344.3122</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -8463,13 +8463,13 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>373.2431</v>
+        <v>373.7819</v>
       </c>
       <c r="AA44" t="n">
-        <v>364.8123</v>
+        <v>365.3647</v>
       </c>
       <c r="AB44" t="n">
-        <v>323.1436</v>
+        <v>323.6984</v>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="AE44" t="n">
-        <v>6.2396</v>
+        <v>5.9126</v>
       </c>
       <c r="AF44" t="n">
-        <v>5.3993</v>
+        <v>5.5019</v>
       </c>
       <c r="AG44" t="inlineStr">
         <is>
@@ -8493,18 +8493,18 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>53.84</v>
+        <v>53.74</v>
       </c>
       <c r="AI44" t="n">
-        <v>382.2002</v>
+        <v>382.8322</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>361.8832</v>
+        <v>362.3814</v>
       </c>
       <c r="AL44" t="n">
         <v>360</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="AN44" t="n">
-        <v>392.81</v>
+        <v>393.2675</v>
       </c>
       <c r="AO44" t="n">
         <v>423.2347</v>
@@ -8525,26 +8525,26 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 392.81; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
+          <t>TP1: Bollinger Upper Band at 393.27; TP2: Fibonacci R1 at 423.23; TP3: Classic R1 at 436.65</t>
         </is>
       </c>
       <c r="AR44" t="n">
-        <v>16.42</v>
+        <v>12.97</v>
       </c>
       <c r="AS44" t="n">
-        <v>32.58</v>
+        <v>25.55</v>
       </c>
       <c r="AT44" t="n">
-        <v>39.7</v>
+        <v>31.19</v>
       </c>
       <c r="AU44" t="n">
-        <v>8.550000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="AV44" t="n">
-        <v>16.95</v>
+        <v>16.79</v>
       </c>
       <c r="AW44" t="n">
-        <v>20.66</v>
+        <v>20.5</v>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
@@ -8553,14 +8553,14 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 53.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at 50 SMA (overbought (RSI: 53.7))</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>292.79</v>
+        <v>293.7</v>
       </c>
       <c r="F45" t="n">
         <v>5.8836</v>
@@ -8607,10 +8607,10 @@
         <v>94571</v>
       </c>
       <c r="O45" t="n">
-        <v>141821</v>
+        <v>12339</v>
       </c>
       <c r="P45" t="n">
-        <v>1.5</v>
+        <v>0.13</v>
       </c>
       <c r="Q45" t="n">
         <v>42669</v>
@@ -8628,10 +8628,10 @@
         <v>247.97</v>
       </c>
       <c r="V45" t="n">
-        <v>225.1504</v>
+        <v>227.0386</v>
       </c>
       <c r="W45" t="n">
-        <v>189.0757</v>
+        <v>189.7347</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -8644,13 +8644,13 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>257.1133</v>
+        <v>260.5977</v>
       </c>
       <c r="AA45" t="n">
-        <v>232.1754</v>
+        <v>234.5882</v>
       </c>
       <c r="AB45" t="n">
-        <v>186.1712</v>
+        <v>187.2411</v>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
@@ -8663,10 +8663,10 @@
         </is>
       </c>
       <c r="AE45" t="n">
-        <v>19.8902</v>
+        <v>20.3046</v>
       </c>
       <c r="AF45" t="n">
-        <v>15.0021</v>
+        <v>16.0626</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -8674,58 +8674,58 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>66.13</v>
+        <v>66.36</v>
       </c>
       <c r="AI45" t="n">
-        <v>270.2082</v>
+        <v>271.4866</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>270.2082</v>
+        <v>271.5136</v>
       </c>
       <c r="AL45" t="n">
-        <v>265.1759</v>
+        <v>221.6915</v>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Fibonacci S1</t>
         </is>
       </c>
       <c r="AN45" t="n">
-        <v>303.4392</v>
+        <v>307.9633</v>
       </c>
       <c r="AO45" t="n">
-        <v>307.9633</v>
+        <v>308.3397</v>
       </c>
       <c r="AP45" t="n">
         <v>308.8515</v>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 303.44; TP2: Classic R1 at 307.96; TP3: Fibonacci R2 at 308.85</t>
+          <t>TP1: Classic R1 at 307.96; TP2: Bollinger Upper Band at 308.34; TP3: Fibonacci R2 at 308.85</t>
         </is>
       </c>
       <c r="AR45" t="n">
-        <v>6.6</v>
+        <v>0.73</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.5</v>
+        <v>0.74</v>
       </c>
       <c r="AT45" t="n">
-        <v>7.68</v>
+        <v>0.75</v>
       </c>
       <c r="AU45" t="n">
-        <v>12.3</v>
+        <v>13.42</v>
       </c>
       <c r="AV45" t="n">
-        <v>13.97</v>
+        <v>13.56</v>
       </c>
       <c r="AW45" t="n">
-        <v>14.3</v>
+        <v>13.75</v>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
@@ -8734,14 +8734,14 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 66.1))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 66.4))</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F46" t="n">
         <v>0.1608</v>
@@ -8788,10 +8788,10 @@
         <v>2516168</v>
       </c>
       <c r="O46" t="n">
-        <v>2567838</v>
+        <v>976398</v>
       </c>
       <c r="P46" t="n">
-        <v>1.021</v>
+        <v>0.388</v>
       </c>
       <c r="Q46" t="n">
         <v>2475974</v>
@@ -8809,10 +8809,10 @@
         <v>8.9</v>
       </c>
       <c r="V46" t="n">
-        <v>7.042</v>
+        <v>7.085</v>
       </c>
       <c r="W46" t="n">
-        <v>6.4466</v>
+        <v>6.4604</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -8825,13 +8825,13 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>7.923</v>
+        <v>7.9494</v>
       </c>
       <c r="AA46" t="n">
-        <v>7.3014</v>
+        <v>7.3366</v>
       </c>
       <c r="AB46" t="n">
-        <v>6.3756</v>
+        <v>6.3937</v>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="AE46" t="n">
-        <v>0.3321</v>
+        <v>0.3152</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.4135</v>
+        <v>0.3938</v>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
@@ -8855,58 +8855,58 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>56.31</v>
+        <v>60.26</v>
       </c>
       <c r="AI46" t="n">
-        <v>8.082599999999999</v>
+        <v>8.1122</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>7.555</v>
+        <v>8.1122</v>
       </c>
       <c r="AL46" t="n">
-        <v>7.2969</v>
+        <v>7.75</v>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>stop at Bollinger Lower Band</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN46" t="n">
         <v>8.755100000000001</v>
       </c>
       <c r="AO46" t="n">
-        <v>8.8361</v>
+        <v>8.8141</v>
       </c>
       <c r="AP46" t="n">
         <v>9.2333</v>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.84; TP3: Classic R1 at 9.23</t>
+          <t>TP1: Fibonacci R1 at 8.76; TP2: Bollinger Upper Band at 8.81; TP3: Classic R1 at 9.23</t>
         </is>
       </c>
       <c r="AR46" t="n">
-        <v>4.65</v>
+        <v>1.78</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.96</v>
+        <v>1.94</v>
       </c>
       <c r="AT46" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="AU46" t="n">
-        <v>15.88</v>
+        <v>7.93</v>
       </c>
       <c r="AV46" t="n">
-        <v>16.96</v>
+        <v>8.65</v>
       </c>
       <c r="AW46" t="n">
-        <v>22.21</v>
+        <v>13.82</v>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
@@ -8915,14 +8915,14 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 56.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 60.3))</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="F47" t="n">
         <v>0.0297</v>
@@ -8975,10 +8975,10 @@
         <v>41822282</v>
       </c>
       <c r="O47" t="n">
-        <v>66369592</v>
+        <v>68686872</v>
       </c>
       <c r="P47" t="n">
-        <v>1.587</v>
+        <v>1.642</v>
       </c>
       <c r="Q47" t="n">
         <v>31605960</v>
@@ -8996,10 +8996,10 @@
         <v>1.57</v>
       </c>
       <c r="V47" t="n">
-        <v>1.317</v>
+        <v>1.324</v>
       </c>
       <c r="W47" t="n">
-        <v>1.1971</v>
+        <v>1.2013</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -9012,13 +9012,13 @@
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>1.4413</v>
+        <v>1.4526</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.3577</v>
+        <v>1.3657</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.1669</v>
+        <v>1.1708</v>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
@@ -9031,69 +9031,69 @@
         </is>
       </c>
       <c r="AE47" t="n">
-        <v>0.064</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0645</v>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>58.3</v>
+        <v>65.2</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.4568</v>
+        <v>1.4618</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>1.4575</v>
+        <v>1.4618</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.32</v>
+        <v>1.4612</v>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN47" t="n">
         <v>1.5828</v>
       </c>
       <c r="AO47" t="n">
-        <v>1.6137</v>
+        <v>1.6153</v>
       </c>
       <c r="AP47" t="n">
         <v>1.66</v>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 1.58; TP2: Bollinger Upper Band at 1.61; TP3: Classic R1 at 1.66</t>
+          <t>TP1: Fibonacci R1 at 1.58; TP2: Bollinger Upper Band at 1.62; TP3: Classic R1 at 1.66</t>
         </is>
       </c>
       <c r="AR47" t="n">
-        <v>0.91</v>
+        <v>178.99</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.14</v>
+        <v>227.09</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.47</v>
+        <v>293.24</v>
       </c>
       <c r="AU47" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="AV47" t="n">
-        <v>10.72</v>
+        <v>10.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>13.89</v>
+        <v>13.55</v>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
@@ -9102,14 +9102,14 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Parabolic SAR (overbought (RSI: 58.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 65.2))</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.091</v>
+        <v>1.1</v>
       </c>
       <c r="F48" t="n">
         <v>0.0219</v>
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>15.81</v>
+        <v>15.94</v>
       </c>
       <c r="M48" t="n">
         <v>0.06900000000000001</v>
@@ -9160,10 +9160,10 @@
         <v>20408169</v>
       </c>
       <c r="O48" t="n">
-        <v>48052965</v>
+        <v>5031786</v>
       </c>
       <c r="P48" t="n">
-        <v>2.355</v>
+        <v>0.247</v>
       </c>
       <c r="Q48" t="n">
         <v>25044689</v>
@@ -9181,10 +9181,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="V48" t="n">
-        <v>0.593</v>
+        <v>0.6071</v>
       </c>
       <c r="W48" t="n">
-        <v>0.4381</v>
+        <v>0.4419</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -9197,13 +9197,13 @@
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>0.8414</v>
+        <v>0.8661</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.6666</v>
+        <v>0.6836</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.4721</v>
+        <v>0.4784</v>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
@@ -9216,10 +9216,10 @@
         </is>
       </c>
       <c r="AE48" t="n">
-        <v>0.1302</v>
+        <v>0.1347</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.1119</v>
+        <v>0.1165</v>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
@@ -9227,29 +9227,29 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>81.84</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.8298</v>
+        <v>0.8404</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>0.8298</v>
+        <v>0.845</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.8226</v>
+        <v>0.805</v>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>stop at Parabolic SAR</t>
+          <t>stop at Swing Support</t>
         </is>
       </c>
       <c r="AN48" t="n">
-        <v>1.1326</v>
+        <v>1.157</v>
       </c>
       <c r="AO48" t="n">
         <v>1.2073</v>
@@ -9259,26 +9259,26 @@
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1.13; TP2: Classic R2 at 1.21; TP3: Classic R3 at 1.66</t>
+          <t>TP1: Bollinger Upper Band at 1.16; TP2: Classic R2 at 1.21; TP3: Classic R3 at 1.66</t>
         </is>
       </c>
       <c r="AR48" t="n">
-        <v>42.36</v>
+        <v>7.8</v>
       </c>
       <c r="AS48" t="n">
-        <v>52.81</v>
+        <v>9.06</v>
       </c>
       <c r="AT48" t="n">
-        <v>116.61</v>
+        <v>20.47</v>
       </c>
       <c r="AU48" t="n">
-        <v>36.49</v>
+        <v>36.93</v>
       </c>
       <c r="AV48" t="n">
-        <v>45.49</v>
+        <v>42.88</v>
       </c>
       <c r="AW48" t="n">
-        <v>100.45</v>
+        <v>96.84</v>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
@@ -9287,14 +9287,14 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (81.8); entry: enhanced entry at VWMA (overbought (RSI: 81.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (82.2); entry: enhanced entry at Parabolic SAR (overbought (RSI: 82.2))</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.512</v>
+        <v>0.526</v>
       </c>
       <c r="F49" t="n">
         <v>0.0103</v>
@@ -9343,10 +9343,10 @@
         <v>20469882</v>
       </c>
       <c r="O49" t="n">
-        <v>21367815</v>
+        <v>9259622</v>
       </c>
       <c r="P49" t="n">
-        <v>1.044</v>
+        <v>0.452</v>
       </c>
       <c r="Q49" t="n">
         <v>17761901</v>
@@ -9364,10 +9364,10 @@
         <v>0.53</v>
       </c>
       <c r="V49" t="n">
-        <v>0.4532</v>
+        <v>0.4553</v>
       </c>
       <c r="W49" t="n">
-        <v>0.4687</v>
+        <v>0.4695</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -9380,13 +9380,13 @@
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>0.5007</v>
+        <v>0.5031</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.4714</v>
+        <v>0.4736</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.4451</v>
+        <v>0.4459</v>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="AE49" t="n">
-        <v>0.0227</v>
+        <v>0.0219</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.0245</v>
+        <v>0.024</v>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
@@ -9410,14 +9410,14 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>56.5</v>
+        <v>59.88</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.5215</v>
+        <v>0.5223</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr"/>
@@ -9448,14 +9448,14 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>undervalued, near support, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
+          <t>undervalued, Death Cross (confirmed downtrend); entry: no entry in bearish/unknown regime</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>486.49</v>
+        <v>487.99</v>
       </c>
       <c r="F50" t="n">
         <v>9.7424</v>
@@ -9502,10 +9502,10 @@
         <v>12075</v>
       </c>
       <c r="O50" t="n">
-        <v>10835</v>
+        <v>1818</v>
       </c>
       <c r="P50" t="n">
-        <v>0.897</v>
+        <v>0.151</v>
       </c>
       <c r="Q50" t="n">
         <v>7545</v>
@@ -9523,10 +9523,10 @@
         <v>512</v>
       </c>
       <c r="V50" t="n">
-        <v>407.107</v>
+        <v>409.9266</v>
       </c>
       <c r="W50" t="n">
-        <v>305.5658</v>
+        <v>306.8408</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -9539,13 +9539,13 @@
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>460.9635</v>
+        <v>463.5374</v>
       </c>
       <c r="AA50" t="n">
-        <v>416.7258</v>
+        <v>419.5205</v>
       </c>
       <c r="AB50" t="n">
-        <v>317.2012</v>
+        <v>318.9006</v>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
@@ -9558,10 +9558,10 @@
         </is>
       </c>
       <c r="AE50" t="n">
-        <v>24.2934</v>
+        <v>23.5254</v>
       </c>
       <c r="AF50" t="n">
-        <v>24.9798</v>
+        <v>24.6889</v>
       </c>
       <c r="AG50" t="inlineStr">
         <is>
@@ -9569,21 +9569,21 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>67.93000000000001</v>
+        <v>68.38</v>
       </c>
       <c r="AI50" t="n">
-        <v>467.9355</v>
+        <v>468.1745</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK50" t="n">
-        <v>467.9355</v>
+        <v>468.1745</v>
       </c>
       <c r="AL50" t="n">
-        <v>455.5693</v>
+        <v>459.4352</v>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
@@ -9594,33 +9594,33 @@
         <v>501.4547</v>
       </c>
       <c r="AO50" t="n">
-        <v>514.4758</v>
+        <v>510.5957</v>
       </c>
       <c r="AP50" t="n">
         <v>518.9933</v>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 514.48; TP3: Classic R1 at 518.99</t>
+          <t>TP1: Fibonacci R1 at 501.45; TP2: Bollinger Upper Band at 510.6; TP3: Classic R1 at 518.99</t>
         </is>
       </c>
       <c r="AR50" t="n">
-        <v>2.71</v>
+        <v>3.81</v>
       </c>
       <c r="AS50" t="n">
-        <v>3.76</v>
+        <v>4.85</v>
       </c>
       <c r="AT50" t="n">
-        <v>4.13</v>
+        <v>5.81</v>
       </c>
       <c r="AU50" t="n">
-        <v>7.16</v>
+        <v>7.11</v>
       </c>
       <c r="AV50" t="n">
-        <v>9.949999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="AW50" t="n">
-        <v>10.91</v>
+        <v>10.85</v>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
@@ -9629,14 +9629,14 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 68.4))</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1268.53</v>
+        <v>1283</v>
       </c>
       <c r="F51" t="n">
         <v>25.4909</v>
@@ -9683,10 +9683,10 @@
         <v>2381</v>
       </c>
       <c r="O51" t="n">
-        <v>3556</v>
+        <v>2054</v>
       </c>
       <c r="P51" t="n">
-        <v>1.493</v>
+        <v>0.863</v>
       </c>
       <c r="Q51" t="n">
         <v>1070</v>
@@ -9704,10 +9704,10 @@
         <v>1275</v>
       </c>
       <c r="V51" t="n">
-        <v>1172.0456</v>
+        <v>1174.899</v>
       </c>
       <c r="W51" t="n">
-        <v>919.6384</v>
+        <v>922.4983999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -9720,13 +9720,13 @@
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>1229.7547</v>
+        <v>1234.8257</v>
       </c>
       <c r="AA51" t="n">
-        <v>1164.211</v>
+        <v>1168.8694</v>
       </c>
       <c r="AB51" t="n">
-        <v>935.203</v>
+        <v>938.6636999999999</v>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="AE51" t="n">
-        <v>30.475</v>
+        <v>31.0615</v>
       </c>
       <c r="AF51" t="n">
-        <v>29.67</v>
+        <v>29.9483</v>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
@@ -9750,21 +9750,21 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>61.22</v>
+        <v>63.42</v>
       </c>
       <c r="AI51" t="n">
-        <v>1249.6599</v>
+        <v>1252.5727</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK51" t="n">
         <v>1264.51</v>
       </c>
       <c r="AL51" t="n">
-        <v>1170.9156</v>
+        <v>1175.7525</v>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         </is>
       </c>
       <c r="AN51" t="n">
-        <v>1292.4174</v>
+        <v>1297.3345</v>
       </c>
       <c r="AO51" t="n">
         <v>1312.2368</v>
@@ -9782,20 +9782,20 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 1292.42; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
+          <t>TP1: Bollinger Upper Band at 1297.33; TP2: Fibonacci R1 at 1312.24; TP3: Classic R1 at 1341.25</t>
         </is>
       </c>
       <c r="AR51" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="AU51" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AV51" t="n">
         <v>3.77</v>
@@ -9810,14 +9810,14 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 61.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 63.4))</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>254.37</v>
+        <v>259</v>
       </c>
       <c r="F52" t="n">
         <v>5.1115</v>
@@ -9870,10 +9870,10 @@
         <v>92660</v>
       </c>
       <c r="O52" t="n">
-        <v>78652</v>
+        <v>46431</v>
       </c>
       <c r="P52" t="n">
-        <v>0.849</v>
+        <v>0.501</v>
       </c>
       <c r="Q52" t="n">
         <v>38628</v>
@@ -9891,10 +9891,10 @@
         <v>255.5774</v>
       </c>
       <c r="V52" t="n">
-        <v>253.2054</v>
+        <v>252.5764</v>
       </c>
       <c r="W52" t="n">
-        <v>246.7131</v>
+        <v>247.2582</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -9907,13 +9907,13 @@
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>246.4166</v>
+        <v>247.615</v>
       </c>
       <c r="AA52" t="n">
-        <v>250.4771</v>
+        <v>250.8114</v>
       </c>
       <c r="AB52" t="n">
-        <v>234.6322</v>
+        <v>234.8747</v>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="AE52" t="n">
-        <v>0.06569999999999999</v>
+        <v>1.0199</v>
       </c>
       <c r="AF52" t="n">
-        <v>-1.6519</v>
+        <v>-1.1175</v>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
@@ -9937,18 +9937,18 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>61.57</v>
+        <v>66.47</v>
       </c>
       <c r="AI52" t="n">
-        <v>244.6507</v>
+        <v>245.0174</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK52" t="n">
-        <v>253.2054</v>
+        <v>252.5764</v>
       </c>
       <c r="AL52" t="n">
         <v>249.1856</v>
@@ -9959,52 +9959,52 @@
         </is>
       </c>
       <c r="AN52" t="n">
-        <v>258.7949</v>
+        <v>276.4467</v>
       </c>
       <c r="AO52" t="n">
-        <v>258.9567</v>
+        <v>288.3819</v>
       </c>
       <c r="AP52" t="n">
-        <v>276.4467</v>
+        <v>282.08</v>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>TP1: 100 SMA at 258.79; TP2: Classic R2 at 258.96; TP3: Classic R3 at 276.45</t>
+          <t>TP1: Classic R3 at 276.45; TP2: Extension at 288.38; TP3: Extension at 282.08</t>
         </is>
       </c>
       <c r="AR52" t="n">
-        <v>1.39</v>
+        <v>7.04</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.43</v>
+        <v>10.56</v>
       </c>
       <c r="AT52" t="n">
-        <v>5.78</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AU52" t="n">
-        <v>2.21</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AV52" t="n">
-        <v>2.27</v>
+        <v>14.18</v>
       </c>
       <c r="AW52" t="n">
-        <v>9.18</v>
+        <v>11.68</v>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>undervalued, near support, Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 61.6))</t>
+          <t>undervalued, Golden Cross confirmed; entry: enhanced entry at 50 SMA (overbought (RSI: 66.5))</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>196.01</v>
+        <v>200.03</v>
       </c>
       <c r="F53" t="n">
         <v>3.9388</v>
@@ -10051,10 +10051,10 @@
         <v>95848</v>
       </c>
       <c r="O53" t="n">
-        <v>140401</v>
+        <v>34438</v>
       </c>
       <c r="P53" t="n">
-        <v>1.465</v>
+        <v>0.359</v>
       </c>
       <c r="Q53" t="n">
         <v>103218</v>
@@ -10072,10 +10072,10 @@
         <v>197.49</v>
       </c>
       <c r="V53" t="n">
-        <v>149.683</v>
+        <v>150.9056</v>
       </c>
       <c r="W53" t="n">
-        <v>124.6567</v>
+        <v>125.1774</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -10088,13 +10088,13 @@
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>175.0599</v>
+        <v>177.438</v>
       </c>
       <c r="AA53" t="n">
-        <v>154.5253</v>
+        <v>156.3098</v>
       </c>
       <c r="AB53" t="n">
-        <v>122.2914</v>
+        <v>123.0649</v>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
@@ -10107,10 +10107,10 @@
         </is>
       </c>
       <c r="AE53" t="n">
-        <v>15.8486</v>
+        <v>15.8615</v>
       </c>
       <c r="AF53" t="n">
-        <v>13.6377</v>
+        <v>14.0824</v>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>62.22</v>
+        <v>63.52</v>
       </c>
       <c r="AI53" t="n">
-        <v>178.1368</v>
+        <v>180.7815</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK53" t="n">
-        <v>178.1368</v>
+        <v>180.7815</v>
       </c>
       <c r="AL53" t="n">
-        <v>175</v>
+        <v>175.7354</v>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
@@ -10143,33 +10143,33 @@
         <v>208.4527</v>
       </c>
       <c r="AO53" t="n">
-        <v>219.3725</v>
+        <v>221.3944</v>
       </c>
       <c r="AP53" t="n">
         <v>224.8967</v>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 219.37; TP3: Classic R1 at 224.9</t>
+          <t>TP1: Fibonacci R1 at 208.45; TP2: Bollinger Upper Band at 221.39; TP3: Classic R1 at 224.9</t>
         </is>
       </c>
       <c r="AR53" t="n">
-        <v>9.66</v>
+        <v>5.48</v>
       </c>
       <c r="AS53" t="n">
-        <v>13.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="AT53" t="n">
-        <v>14.91</v>
+        <v>8.74</v>
       </c>
       <c r="AU53" t="n">
-        <v>17.02</v>
+        <v>15.31</v>
       </c>
       <c r="AV53" t="n">
-        <v>23.15</v>
+        <v>22.47</v>
       </c>
       <c r="AW53" t="n">
-        <v>26.25</v>
+        <v>24.4</v>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
@@ -10178,14 +10178,14 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 62.2))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 63.5))</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>7.25</v>
+        <v>7.35</v>
       </c>
       <c r="F54" t="n">
         <v>0.1457</v>
@@ -10238,10 +10238,10 @@
         <v>24636250</v>
       </c>
       <c r="O54" t="n">
-        <v>7585030</v>
+        <v>5038321</v>
       </c>
       <c r="P54" t="n">
-        <v>0.308</v>
+        <v>0.205</v>
       </c>
       <c r="Q54" t="n">
         <v>14553455</v>
@@ -10259,10 +10259,10 @@
         <v>7.79</v>
       </c>
       <c r="V54" t="n">
-        <v>6.6962</v>
+        <v>6.7262</v>
       </c>
       <c r="W54" t="n">
-        <v>5.8785</v>
+        <v>5.8904</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -10275,13 +10275,13 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>7.208</v>
+        <v>7.2215</v>
       </c>
       <c r="AA54" t="n">
-        <v>6.8093</v>
+        <v>6.8305</v>
       </c>
       <c r="AB54" t="n">
-        <v>5.8311</v>
+        <v>5.8462</v>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
@@ -10294,10 +10294,10 @@
         </is>
       </c>
       <c r="AE54" t="n">
-        <v>0.153</v>
+        <v>0.1473</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.2267</v>
+        <v>0.2108</v>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
@@ -10305,21 +10305,21 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>54.9</v>
+        <v>57.9</v>
       </c>
       <c r="AI54" t="n">
-        <v>7.3313</v>
+        <v>7.3508</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK54" t="n">
-        <v>6.995</v>
+        <v>7.13</v>
       </c>
       <c r="AL54" t="n">
-        <v>6.8896</v>
+        <v>6.9739</v>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
@@ -10330,33 +10330,33 @@
         <v>7.6476</v>
       </c>
       <c r="AO54" t="n">
-        <v>7.7774</v>
+        <v>7.7431</v>
       </c>
       <c r="AP54" t="n">
         <v>7.8167</v>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 7.65; TP2: Bollinger Upper Band at 7.78; TP3: Classic R1 at 7.82</t>
+          <t>TP1: Fibonacci R1 at 7.65; TP2: Bollinger Upper Band at 7.74; TP3: Classic R1 at 7.82</t>
         </is>
       </c>
       <c r="AR54" t="n">
-        <v>6.19</v>
+        <v>3.32</v>
       </c>
       <c r="AS54" t="n">
-        <v>7.42</v>
+        <v>3.93</v>
       </c>
       <c r="AT54" t="n">
-        <v>7.79</v>
+        <v>4.4</v>
       </c>
       <c r="AU54" t="n">
-        <v>9.33</v>
+        <v>7.26</v>
       </c>
       <c r="AV54" t="n">
-        <v>11.19</v>
+        <v>8.6</v>
       </c>
       <c r="AW54" t="n">
-        <v>11.75</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
@@ -10365,14 +10365,14 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 54.9))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 57.9))</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10391,7 +10391,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12.8</v>
+        <v>12.81</v>
       </c>
       <c r="F55" t="n">
         <v>0.2572</v>
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>14.27</v>
+        <v>14.28</v>
       </c>
       <c r="M55" t="n">
         <v>0.8969</v>
@@ -10423,10 +10423,10 @@
         <v>3413296</v>
       </c>
       <c r="O55" t="n">
-        <v>432616</v>
+        <v>76369</v>
       </c>
       <c r="P55" t="n">
-        <v>0.127</v>
+        <v>0.022</v>
       </c>
       <c r="Q55" t="n">
         <v>752621</v>
@@ -10444,10 +10444,10 @@
         <v>9.289999999999999</v>
       </c>
       <c r="V55" t="n">
-        <v>9.611800000000001</v>
+        <v>9.691000000000001</v>
       </c>
       <c r="W55" t="n">
-        <v>6.2999</v>
+        <v>6.3461</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -10460,13 +10460,13 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>11.0959</v>
+        <v>11.2592</v>
       </c>
       <c r="AA55" t="n">
-        <v>9.809900000000001</v>
+        <v>9.9275</v>
       </c>
       <c r="AB55" t="n">
-        <v>6.9152</v>
+        <v>6.9739</v>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
@@ -10479,10 +10479,10 @@
         </is>
       </c>
       <c r="AE55" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.7552</v>
+        <v>0.8033</v>
       </c>
       <c r="AG55" t="inlineStr">
         <is>
@@ -10490,18 +10490,18 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>77.67</v>
+        <v>77.72</v>
       </c>
       <c r="AI55" t="n">
-        <v>10.6921</v>
+        <v>10.7469</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK55" t="n">
-        <v>11.8515</v>
+        <v>12.1482</v>
       </c>
       <c r="AL55" t="n">
         <v>9.4033</v>
@@ -10515,33 +10515,33 @@
         <v>13.4067</v>
       </c>
       <c r="AO55" t="n">
-        <v>13.4758</v>
+        <v>13.684</v>
       </c>
       <c r="AP55" t="n">
         <v>16.3367</v>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>TP1: Classic R2 at 13.41; TP2: Bollinger Upper Band at 13.48; TP3: Classic R3 at 16.34</t>
+          <t>TP1: Classic R2 at 13.41; TP2: Bollinger Upper Band at 13.68; TP3: Classic R3 at 16.34</t>
         </is>
       </c>
       <c r="AR55" t="n">
-        <v>0.64</v>
+        <v>0.46</v>
       </c>
       <c r="AS55" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AU55" t="n">
-        <v>13.12</v>
+        <v>10.36</v>
       </c>
       <c r="AV55" t="n">
-        <v>13.71</v>
+        <v>12.64</v>
       </c>
       <c r="AW55" t="n">
-        <v>37.84</v>
+        <v>34.48</v>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK56" t="n">
@@ -10736,7 +10736,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>316.59</v>
+        <v>329.7</v>
       </c>
       <c r="F57" t="n">
         <v>6.3618</v>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>13.9</v>
+        <v>14.47</v>
       </c>
       <c r="M57" t="n">
         <v>22.7816</v>
@@ -10787,10 +10787,10 @@
         <v>372299</v>
       </c>
       <c r="O57" t="n">
-        <v>582433</v>
+        <v>83792</v>
       </c>
       <c r="P57" t="n">
-        <v>1.564</v>
+        <v>0.225</v>
       </c>
       <c r="Q57" t="n">
         <v>187420</v>
@@ -10808,10 +10808,10 @@
         <v>252.69</v>
       </c>
       <c r="V57" t="n">
-        <v>246.1866</v>
+        <v>248.6024</v>
       </c>
       <c r="W57" t="n">
-        <v>186.7957</v>
+        <v>187.6362</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -10824,13 +10824,13 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>283.8893</v>
+        <v>288.2523</v>
       </c>
       <c r="AA57" t="n">
-        <v>251.9339</v>
+        <v>254.9835</v>
       </c>
       <c r="AB57" t="n">
-        <v>189.6653</v>
+        <v>191.0587</v>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="AE57" t="n">
-        <v>21.6434</v>
+        <v>22.6138</v>
       </c>
       <c r="AF57" t="n">
-        <v>18.3113</v>
+        <v>19.1718</v>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
@@ -10854,18 +10854,18 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>70.34</v>
+        <v>73.69</v>
       </c>
       <c r="AI57" t="n">
-        <v>285.1904</v>
+        <v>286.3865</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK57" t="n">
-        <v>294.7063</v>
+        <v>301.7933</v>
       </c>
       <c r="AL57" t="n">
         <v>251.78</v>
@@ -10876,36 +10876,36 @@
         </is>
       </c>
       <c r="AN57" t="n">
-        <v>335.2545</v>
+        <v>337.12</v>
       </c>
       <c r="AO57" t="n">
-        <v>337.12</v>
+        <v>341.528</v>
       </c>
       <c r="AP57" t="n">
         <v>398.9</v>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>TP1: Bollinger Upper Band at 335.25; TP2: Classic R2 at 337.12; TP3: Classic R3 at 398.9</t>
+          <t>TP1: Classic R2 at 337.12; TP2: Bollinger Upper Band at 341.53; TP3: Classic R3 at 398.9</t>
         </is>
       </c>
       <c r="AR57" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AS57" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="AT57" t="n">
-        <v>2.43</v>
+        <v>1.94</v>
       </c>
       <c r="AU57" t="n">
-        <v>13.76</v>
+        <v>11.71</v>
       </c>
       <c r="AV57" t="n">
-        <v>14.39</v>
+        <v>13.17</v>
       </c>
       <c r="AW57" t="n">
-        <v>35.36</v>
+        <v>32.18</v>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
@@ -10914,14 +10914,14 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (70.3); entry: enhanced entry at Parabolic SAR (overbought (RSI: 70.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.7); entry: enhanced entry at Parabolic SAR (overbought (RSI: 73.7))</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10940,7 +10940,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>18.2</v>
+        <v>18.21</v>
       </c>
       <c r="F58" t="n">
         <v>0.3657</v>
@@ -10974,10 +10974,10 @@
         <v>753440</v>
       </c>
       <c r="O58" t="n">
-        <v>1419392</v>
+        <v>134369</v>
       </c>
       <c r="P58" t="n">
-        <v>1.884</v>
+        <v>0.178</v>
       </c>
       <c r="Q58" t="n">
         <v>612795</v>
@@ -10995,10 +10995,10 @@
         <v>19.59</v>
       </c>
       <c r="V58" t="n">
-        <v>16.1644</v>
+        <v>16.2182</v>
       </c>
       <c r="W58" t="n">
-        <v>15.7357</v>
+        <v>15.7605</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -11011,13 +11011,13 @@
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>17.0766</v>
+        <v>17.1845</v>
       </c>
       <c r="AA58" t="n">
-        <v>16.3832</v>
+        <v>16.4549</v>
       </c>
       <c r="AB58" t="n">
-        <v>15.1188</v>
+        <v>15.1496</v>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="AE58" t="n">
-        <v>0.7044</v>
+        <v>0.7043</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.4608</v>
+        <v>0.5095</v>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
@@ -11041,21 +11041,21 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>64.73</v>
+        <v>64.81</v>
       </c>
       <c r="AI58" t="n">
-        <v>17.5329</v>
+        <v>17.5583</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK58" t="n">
-        <v>17.5329</v>
+        <v>17.5583</v>
       </c>
       <c r="AL58" t="n">
-        <v>17.0657</v>
+        <v>17.2677</v>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
@@ -11066,33 +11066,33 @@
         <v>19.0869</v>
       </c>
       <c r="AO58" t="n">
-        <v>19.165</v>
+        <v>19.3274</v>
       </c>
       <c r="AP58" t="n">
         <v>19.6033</v>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 19.09; TP2: Bollinger Upper Band at 19.16; TP3: Classic R1 at 19.6</t>
+          <t>TP1: Fibonacci R1 at 19.09; TP2: Bollinger Upper Band at 19.33; TP3: Classic R1 at 19.6</t>
         </is>
       </c>
       <c r="AR58" t="n">
-        <v>3.33</v>
+        <v>5.26</v>
       </c>
       <c r="AS58" t="n">
-        <v>3.49</v>
+        <v>6.09</v>
       </c>
       <c r="AT58" t="n">
-        <v>4.43</v>
+        <v>7.04</v>
       </c>
       <c r="AU58" t="n">
-        <v>8.859999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AV58" t="n">
-        <v>9.31</v>
+        <v>10.08</v>
       </c>
       <c r="AW58" t="n">
-        <v>11.81</v>
+        <v>11.65</v>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
@@ -11101,14 +11101,14 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.7))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 64.8))</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -11127,7 +11127,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.742</v>
+        <v>0.744</v>
       </c>
       <c r="F59" t="n">
         <v>0.0149</v>
@@ -11157,10 +11157,10 @@
         <v>24808590</v>
       </c>
       <c r="O59" t="n">
-        <v>192593253</v>
+        <v>24965405</v>
       </c>
       <c r="P59" t="n">
-        <v>7.763</v>
+        <v>1.006</v>
       </c>
       <c r="Q59" t="n">
         <v>31088454</v>
@@ -11178,10 +11178,10 @@
         <v>0.778</v>
       </c>
       <c r="V59" t="n">
-        <v>0.5592</v>
+        <v>0.5653</v>
       </c>
       <c r="W59" t="n">
-        <v>0.4768</v>
+        <v>0.4782</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -11194,13 +11194,13 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>0.6106</v>
+        <v>0.6233</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.5652</v>
+        <v>0.5722</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.4929</v>
+        <v>0.4954</v>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
@@ -11213,10 +11213,10 @@
         </is>
       </c>
       <c r="AE59" t="n">
-        <v>0.0311</v>
+        <v>0.0379</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.0167</v>
+        <v>0.0209</v>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
@@ -11224,21 +11224,21 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>76.81</v>
+        <v>76.98</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.6387</v>
+        <v>0.6433</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK59" t="n">
         <v>0.678</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.5569</v>
+        <v>0.5776</v>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
@@ -11262,14 +11262,14 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (76.8); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 76.8))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (77.0); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 77.0))</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>135.99</v>
+        <v>150</v>
       </c>
       <c r="F60" t="n">
         <v>2.7327</v>
@@ -11316,10 +11316,10 @@
         <v>135977</v>
       </c>
       <c r="O60" t="n">
-        <v>2168293</v>
+        <v>1073136</v>
       </c>
       <c r="P60" t="n">
-        <v>15.946</v>
+        <v>7.892</v>
       </c>
       <c r="Q60" t="n">
         <v>78181</v>
@@ -11337,10 +11337,10 @@
         <v>136.77</v>
       </c>
       <c r="V60" t="n">
-        <v>101.7666</v>
+        <v>102.7444</v>
       </c>
       <c r="W60" t="n">
-        <v>90.3441</v>
+        <v>90.7226</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -11353,13 +11353,13 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>110.3938</v>
+        <v>114.1658</v>
       </c>
       <c r="AA60" t="n">
-        <v>103.5284</v>
+        <v>105.3508</v>
       </c>
       <c r="AB60" t="n">
-        <v>90.0545</v>
+        <v>90.65089999999999</v>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
@@ -11372,10 +11372,10 @@
         </is>
       </c>
       <c r="AE60" t="n">
-        <v>6.6962</v>
+        <v>8.997</v>
       </c>
       <c r="AF60" t="n">
-        <v>4.1109</v>
+        <v>5.0881</v>
       </c>
       <c r="AG60" t="inlineStr">
         <is>
@@ -11383,18 +11383,18 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>84.36</v>
+        <v>88.36</v>
       </c>
       <c r="AI60" t="n">
-        <v>117.108</v>
+        <v>122.3131</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK60" t="n">
-        <v>117.395</v>
+        <v>126.48</v>
       </c>
       <c r="AL60" t="n">
         <v>114.25</v>
@@ -11404,38 +11404,16 @@
           <t>stop at Swing Support</t>
         </is>
       </c>
-      <c r="AN60" t="n">
-        <v>143.7933</v>
-      </c>
-      <c r="AO60" t="n">
-        <v>156.9924</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>150.0233</v>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>TP1: Classic R3 at 143.79; TP2: Extension at 156.99; TP3: Extension at 150.02</t>
-        </is>
-      </c>
-      <c r="AR60" t="n">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>12.59</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>22.49</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>33.73</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>27.79</v>
-      </c>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr"/>
       <c r="AX60" t="inlineStr">
         <is>
           <t>Watch</t>
@@ -11443,14 +11421,14 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (84.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 84.4))</t>
+          <t>buy-volume spike (vs 2‑month), Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (88.4); entry: enhanced entry at Ichimoku Kijun-sen (overbought (RSI: 88.4))</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11469,7 +11447,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>11.38</v>
+        <v>12.05</v>
       </c>
       <c r="F61" t="n">
         <v>0.2287</v>
@@ -11497,10 +11475,10 @@
         <v>1642361</v>
       </c>
       <c r="O61" t="n">
-        <v>759643</v>
+        <v>2292337</v>
       </c>
       <c r="P61" t="n">
-        <v>0.463</v>
+        <v>1.396</v>
       </c>
       <c r="Q61" t="n">
         <v>594275</v>
@@ -11518,10 +11496,10 @@
         <v>11.74</v>
       </c>
       <c r="V61" t="n">
-        <v>9.686199999999999</v>
+        <v>9.7538</v>
       </c>
       <c r="W61" t="n">
-        <v>8.178800000000001</v>
+        <v>8.2066</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -11534,13 +11512,13 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>10.6565</v>
+        <v>10.7892</v>
       </c>
       <c r="AA61" t="n">
-        <v>9.966699999999999</v>
+        <v>10.0484</v>
       </c>
       <c r="AB61" t="n">
-        <v>8.4602</v>
+        <v>8.495900000000001</v>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
@@ -11553,10 +11531,10 @@
         </is>
       </c>
       <c r="AE61" t="n">
-        <v>0.4799</v>
+        <v>0.5322</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.4751</v>
+        <v>0.4865</v>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
@@ -11564,58 +11542,58 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>67.34999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="AI61" t="n">
-        <v>10.6235</v>
+        <v>10.6929</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>2026-08-08 15:36:36</t>
+          <t>2026-08-09 08:04:10</t>
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>10.6235</v>
+        <v>10.6929</v>
       </c>
       <c r="AL61" t="n">
         <v>10.32</v>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>stop at Swing Support</t>
+          <t>stop at Parabolic SAR</t>
         </is>
       </c>
       <c r="AN61" t="n">
-        <v>11.4809</v>
+        <v>12.2291</v>
       </c>
       <c r="AO61" t="n">
-        <v>11.97</v>
+        <v>13.44</v>
       </c>
       <c r="AP61" t="n">
-        <v>11.9983</v>
+        <v>16.61</v>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>TP1: Fibonacci R1 at 11.48; TP2: Classic R1 at 11.97; TP3: Bollinger Upper Band at 12.0</t>
+          <t>TP1: Fibonacci R2 at 12.23; TP2: Classic R2 at 13.44; TP3: Classic R3 at 16.61</t>
         </is>
       </c>
       <c r="AR61" t="n">
-        <v>2.83</v>
+        <v>4.12</v>
       </c>
       <c r="AS61" t="n">
-        <v>4.44</v>
+        <v>7.37</v>
       </c>
       <c r="AT61" t="n">
-        <v>4.53</v>
+        <v>15.87</v>
       </c>
       <c r="AU61" t="n">
-        <v>8.07</v>
+        <v>14.37</v>
       </c>
       <c r="AV61" t="n">
-        <v>12.68</v>
+        <v>25.69</v>
       </c>
       <c r="AW61" t="n">
-        <v>12.94</v>
+        <v>55.34</v>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
@@ -11624,14 +11602,14 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish; entry: enhanced entry at VWMA (overbought (RSI: 67.3))</t>
+          <t>Golden Cross confirmed, Diamond Cross (EMA20&gt;EMA50) - short-term momentum bullish, RSI overbought (73.8); entry: enhanced entry at VWMA (overbought (RSI: 73.8))</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11650,7 +11628,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>59.14</v>
+        <v>59.5</v>
       </c>
       <c r="F62" t="n">
         <v>1.1884</v>
@@ -11684,10 +11662,10 @@
         <v>242579</v>
       </c>
       <c r="O62" t="n">
-        <v>377194</v>
+        <v>32389</v>
       </c>
       <c r="P62" t="n">
-        <v>1.555</v>
+        <v>0.134</v>
       </c>
       <c r="Q62" t="n">
         <v>125618</v>
@@ -11705,10 +11683,10 @@
         <v>54.8</v>
       </c>
       <c r="V62" t="n">
-        <v>51.677</v>
+        <v>51.893</v>
       </c>
       <c r="W62" t="n">
-        <v>45.9368</v>
+        <v>46.0129</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -11721,13 +11699,13 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>54.8168</v>
+        <v>55.2628</v>
       </c>
       <c r="AA62" t="n">
-        <v>51.9412</v>
+        <v>52.2376</v>
       </c>
    